--- a/data/MARR.MI.xlsx
+++ b/data/MARR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="1533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="1534">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,70 +44,70 @@
     <t xml:space="preserve">MARR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2894010543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.181300163269</t>
+    <t xml:space="preserve">13.2894020080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1812992095947</t>
   </si>
   <si>
     <t xml:space="preserve">12.9939203262329</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9506797790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5903367996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6551971435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7344741821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4389944076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4462013244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9849643707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0858612060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6462440490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2155838012695</t>
+    <t xml:space="preserve">12.9506788253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5903358459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.655198097229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7344751358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4389963150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4462003707886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9849634170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0858602523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6462430953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2155828475952</t>
   </si>
   <si>
     <t xml:space="preserve">12.8353700637817</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6768198013306</t>
+    <t xml:space="preserve">12.6768207550049</t>
   </si>
   <si>
     <t xml:space="preserve">12.5615100860596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5543050765991</t>
+    <t xml:space="preserve">12.5543041229248</t>
   </si>
   <si>
     <t xml:space="preserve">12.6407871246338</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7200603485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9722986221313</t>
+    <t xml:space="preserve">12.7200613021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9722995758057</t>
   </si>
   <si>
     <t xml:space="preserve">12.7777156829834</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3308916091919</t>
+    <t xml:space="preserve">12.3308944702148</t>
   </si>
   <si>
     <t xml:space="preserve">12.5110635757446</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">12.2948570251465</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4084167480469</t>
+    <t xml:space="preserve">11.4084157943726</t>
   </si>
   <si>
     <t xml:space="preserve">11.4516582489014</t>
@@ -125,55 +125,55 @@
     <t xml:space="preserve">11.8840684890747</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5885877609253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8912754058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9273071289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0426168441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2011690139771</t>
+    <t xml:space="preserve">11.5885887145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8912734985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9273080825806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0426187515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2011671066284</t>
   </si>
   <si>
     <t xml:space="preserve">12.3957548141479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7056446075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6047525405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5759239196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9362668991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1596755981445</t>
+    <t xml:space="preserve">12.7056474685669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6047515869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5759248733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9362659454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1596765518188</t>
   </si>
   <si>
     <t xml:space="preserve">12.9434719085693</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0731945037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.885817527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.597544670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0786514282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3597173690796</t>
+    <t xml:space="preserve">13.0731964111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8858184814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5975427627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.078652381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3597183227539</t>
   </si>
   <si>
     <t xml:space="preserve">12.6696128845215</t>
@@ -182,16 +182,16 @@
     <t xml:space="preserve">12.8137493133545</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6984405517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8714036941528</t>
+    <t xml:space="preserve">12.6984395980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8714056015015</t>
   </si>
   <si>
     <t xml:space="preserve">12.453408241272</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3453054428101</t>
+    <t xml:space="preserve">12.3453044891357</t>
   </si>
   <si>
     <t xml:space="preserve">12.684027671814</t>
@@ -200,64 +200,64 @@
     <t xml:space="preserve">12.7560949325562</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1524715423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2677793502808</t>
+    <t xml:space="preserve">13.1524696350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2677812576294</t>
   </si>
   <si>
     <t xml:space="preserve">13.3326406478882</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0804014205933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1885042190552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2605724334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7073965072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4911909103394</t>
+    <t xml:space="preserve">13.0804033279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1885032653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.260573387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7073984146118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.491189956665</t>
   </si>
   <si>
     <t xml:space="preserve">13.3470554351807</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0011281967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9002304077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8281631469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7921304702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.058783531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1020221710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8065452575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2821941375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1380577087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8425750732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8930244445801</t>
+    <t xml:space="preserve">13.001127243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9002313613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.828164100647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7921295166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0587844848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1020231246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8065433502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2821931838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1380558013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8425760269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8930253982544</t>
   </si>
   <si>
     <t xml:space="preserve">12.9074382781982</t>
@@ -266,10 +266,10 @@
     <t xml:space="preserve">13.0227479934692</t>
   </si>
   <si>
-    <t xml:space="preserve">12.662407875061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8786115646362</t>
+    <t xml:space="preserve">12.6624069213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8786096572876</t>
   </si>
   <si>
     <t xml:space="preserve">12.6335783004761</t>
@@ -278,25 +278,25 @@
     <t xml:space="preserve">12.7488870620728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0258741378784</t>
+    <t xml:space="preserve">13.0258750915527</t>
   </si>
   <si>
     <t xml:space="preserve">13.0183887481689</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2579441070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2504596710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4301271438599</t>
+    <t xml:space="preserve">13.2579431533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2504587173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4301261901855</t>
   </si>
   <si>
     <t xml:space="preserve">13.4825286865234</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3103494644165</t>
+    <t xml:space="preserve">13.3103485107422</t>
   </si>
   <si>
     <t xml:space="preserve">13.2654314041138</t>
@@ -308,10 +308,10 @@
     <t xml:space="preserve">13.3702383041382</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2878904342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2729187011719</t>
+    <t xml:space="preserve">13.2878894805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2729177474976</t>
   </si>
   <si>
     <t xml:space="preserve">13.2804040908813</t>
@@ -326,118 +326,118 @@
     <t xml:space="preserve">12.6141376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3146934509277</t>
+    <t xml:space="preserve">12.3146924972534</t>
   </si>
   <si>
     <t xml:space="preserve">12.44944190979</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8087778091431</t>
+    <t xml:space="preserve">12.8087797164917</t>
   </si>
   <si>
     <t xml:space="preserve">12.7938041687012</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0782785415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4419574737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7831773757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2847480773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7339143753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4226417541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5274448394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0558204650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4525852203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3328075408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7595148086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7295722961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7220840454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.53493309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4900159835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7370586395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0140447616577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7071123123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8493490219116</t>
+    <t xml:space="preserve">13.0782766342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4419584274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7831764221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2847461700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7339153289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4226408004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5274467468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0558214187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4525842666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3328065872192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7595167160034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7295713424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7220849990845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5349321365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4900150299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7370595932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0140438079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7071142196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8493499755859</t>
   </si>
   <si>
     <t xml:space="preserve">14.1113653182983</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9766159057617</t>
+    <t xml:space="preserve">13.976616859436</t>
   </si>
   <si>
     <t xml:space="preserve">14.0814189910889</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7445468902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9990739822388</t>
+    <t xml:space="preserve">13.7445449829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9990749359131</t>
   </si>
   <si>
     <t xml:space="preserve">13.5049886703491</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6397371292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6621961593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6097936630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3477792739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.415153503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2205152511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0857639312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.100736618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0633058547974</t>
+    <t xml:space="preserve">13.6397380828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6621952056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6097946166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3477802276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4151544570923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.220516204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0857629776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1007375717163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.063307762146</t>
   </si>
   <si>
     <t xml:space="preserve">13.2354869842529</t>
@@ -446,31 +446,31 @@
     <t xml:space="preserve">13.1456518173218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9285564422607</t>
+    <t xml:space="preserve">12.9285554885864</t>
   </si>
   <si>
     <t xml:space="preserve">13.2055416107178</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1082248687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.198055267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1157093048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0109024047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9135818481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8611822128296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9435291290283</t>
+    <t xml:space="preserve">13.1082229614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1980571746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1157083511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0109004974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9135828018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8611812591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.943528175354</t>
   </si>
   <si>
     <t xml:space="preserve">13.1905698776245</t>
@@ -482,13 +482,13 @@
     <t xml:space="preserve">13.3552656173706</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2130270004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3402919769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9659862518311</t>
+    <t xml:space="preserve">13.2130289077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.340292930603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9659852981567</t>
   </si>
   <si>
     <t xml:space="preserve">12.8761539459229</t>
@@ -506,16 +506,16 @@
     <t xml:space="preserve">12.7114562988281</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8686676025391</t>
+    <t xml:space="preserve">12.8686656951904</t>
   </si>
   <si>
     <t xml:space="preserve">12.7563753128052</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7488889694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6815147399902</t>
+    <t xml:space="preserve">12.7488880157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6815137863159</t>
   </si>
   <si>
     <t xml:space="preserve">12.5767059326172</t>
@@ -524,70 +524,70 @@
     <t xml:space="preserve">12.5467624664307</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5317897796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5617341995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5542488098145</t>
+    <t xml:space="preserve">12.5317907333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5617351531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5542497634888</t>
   </si>
   <si>
     <t xml:space="preserve">12.4194984436035</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2772617340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4719018936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5018463134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3970403671265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9778156280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3596096038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4943609237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3820676803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4045257568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2697744369507</t>
+    <t xml:space="preserve">12.2772607803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4719009399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5018453598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3970394134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9778165817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3596086502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4943599700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3820686340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4045267105103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2697763442993</t>
   </si>
   <si>
     <t xml:space="preserve">12.1649694442749</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2548046112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3371505737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3221778869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7264289855957</t>
+    <t xml:space="preserve">12.2548036575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3371496200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3221769332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.72642993927</t>
   </si>
   <si>
     <t xml:space="preserve">12.6740264892578</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7863187789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0932521820068</t>
+    <t xml:space="preserve">12.7863178253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0932512283325</t>
   </si>
   <si>
     <t xml:space="preserve">12.9510135650635</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">13.1606254577637</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1830835342407</t>
+    <t xml:space="preserve">13.183084487915</t>
   </si>
   <si>
     <t xml:space="preserve">13.1681127548218</t>
@@ -617,22 +617,22 @@
     <t xml:space="preserve">13.00341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1755981445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.400182723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3852109909058</t>
+    <t xml:space="preserve">13.1755990982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4001808166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3852100372314</t>
   </si>
   <si>
     <t xml:space="preserve">13.8643236160278</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9167242050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5199594497681</t>
+    <t xml:space="preserve">13.9167251586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5199604034424</t>
   </si>
   <si>
     <t xml:space="preserve">13.4450988769531</t>
@@ -644,7 +644,7 @@
     <t xml:space="preserve">13.4600715637207</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5124740600586</t>
+    <t xml:space="preserve">13.5124731063843</t>
   </si>
   <si>
     <t xml:space="preserve">13.4376134872437</t>
@@ -656,10 +656,10 @@
     <t xml:space="preserve">13.6247673034668</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8044338226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7819738388062</t>
+    <t xml:space="preserve">13.8044347763062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7819757461548</t>
   </si>
   <si>
     <t xml:space="preserve">13.6996259689331</t>
@@ -668,10 +668,10 @@
     <t xml:space="preserve">13.8418636322021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.677170753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8568382263184</t>
+    <t xml:space="preserve">13.6771697998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.856837272644</t>
   </si>
   <si>
     <t xml:space="preserve">13.7670011520386</t>
@@ -680,94 +680,94 @@
     <t xml:space="preserve">13.5648794174194</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8942680358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3359498977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5605344772339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5156173706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6952819824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9722719192505</t>
+    <t xml:space="preserve">13.8942670822144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3359489440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5605354309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5156164169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6952838897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9722709655762</t>
   </si>
   <si>
     <t xml:space="preserve">14.9348392486572</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9423246383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8225469589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2043399810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7133960723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1369638442993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.159423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2866897583008</t>
+    <t xml:space="preserve">14.942325592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.822548866272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2043428421021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.713397026062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.136962890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1594228744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2866868972778</t>
   </si>
   <si>
     <t xml:space="preserve">15.3615493774414</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2267999649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3465766906738</t>
+    <t xml:space="preserve">15.2267990112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3465776443481</t>
   </si>
   <si>
     <t xml:space="preserve">15.6834545135498</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7208824157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5337314605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.458869934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1669111251831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1968545913696</t>
+    <t xml:space="preserve">15.7208833694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5337295532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4588689804077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1669101715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1968536376953</t>
   </si>
   <si>
     <t xml:space="preserve">15.5487031936646</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4214372634888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6011066436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6460218429565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7358589172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5861330032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9080362319946</t>
+    <t xml:space="preserve">15.4214391708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6011037826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6460237503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7358570098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5861320495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9080400466919</t>
   </si>
   <si>
     <t xml:space="preserve">16.42458152771</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">16.1251354217529</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6984272003174</t>
+    <t xml:space="preserve">15.6984262466431</t>
   </si>
   <si>
     <t xml:space="preserve">16.2823448181152</t>
@@ -785,25 +785,25 @@
     <t xml:space="preserve">16.3272609710693</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2598857879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.267370223999</t>
+    <t xml:space="preserve">16.2598838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2673721313477</t>
   </si>
   <si>
     <t xml:space="preserve">16.5967617034912</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7839164733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6641387939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.521900177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4470367431641</t>
+    <t xml:space="preserve">16.78391456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6641368865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5218982696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4470386505127</t>
   </si>
   <si>
     <t xml:space="preserve">16.6416778564453</t>
@@ -812,10 +812,10 @@
     <t xml:space="preserve">17.0758762359619</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7988872528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7464866638184</t>
+    <t xml:space="preserve">16.7988891601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7464847564697</t>
   </si>
   <si>
     <t xml:space="preserve">16.8737487792969</t>
@@ -827,28 +827,28 @@
     <t xml:space="preserve">17.1058197021484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3946380615234</t>
+    <t xml:space="preserve">16.3946342468262</t>
   </si>
   <si>
     <t xml:space="preserve">16.506929397583</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6847553253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1950378417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1641139984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0094833374023</t>
+    <t xml:space="preserve">16.6847534179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1950359344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1641120910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0094814300537</t>
   </si>
   <si>
     <t xml:space="preserve">16.7620697021484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6306343078613</t>
+    <t xml:space="preserve">16.6306324005127</t>
   </si>
   <si>
     <t xml:space="preserve">16.8471164703369</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">16.9398956298828</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7698001861572</t>
+    <t xml:space="preserve">16.7698020935059</t>
   </si>
   <si>
     <t xml:space="preserve">16.9940185546875</t>
@@ -869,22 +869,22 @@
     <t xml:space="preserve">17.1254558563232</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9553604125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5455875396729</t>
+    <t xml:space="preserve">16.955358505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5455856323242</t>
   </si>
   <si>
     <t xml:space="preserve">16.7156810760498</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8548488616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7466087341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0404071807861</t>
+    <t xml:space="preserve">16.854850769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7466068267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0404109954834</t>
   </si>
   <si>
     <t xml:space="preserve">16.731143951416</t>
@@ -896,13 +896,13 @@
     <t xml:space="preserve">16.5687789916992</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6229019165039</t>
+    <t xml:space="preserve">16.6229000091553</t>
   </si>
   <si>
     <t xml:space="preserve">16.7079486846924</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7234115600586</t>
+    <t xml:space="preserve">16.7234134674072</t>
   </si>
   <si>
     <t xml:space="preserve">16.1822032928467</t>
@@ -911,10 +911,10 @@
     <t xml:space="preserve">16.0894203186035</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0816917419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1590061187744</t>
+    <t xml:space="preserve">16.0816898345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.159008026123</t>
   </si>
   <si>
     <t xml:space="preserve">15.9347906112671</t>
@@ -923,22 +923,22 @@
     <t xml:space="preserve">16.2363224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0739593505859</t>
+    <t xml:space="preserve">16.0739612579346</t>
   </si>
   <si>
     <t xml:space="preserve">15.9966449737549</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3909568786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4914665222168</t>
+    <t xml:space="preserve">16.3909530639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4914646148682</t>
   </si>
   <si>
     <t xml:space="preserve">16.8935070037842</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2414283752441</t>
+    <t xml:space="preserve">17.2414264678955</t>
   </si>
   <si>
     <t xml:space="preserve">17.0558700561523</t>
@@ -947,13 +947,13 @@
     <t xml:space="preserve">17.2878189086914</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2955513000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3960590362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8316535949707</t>
+    <t xml:space="preserve">17.2955493927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3960609436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8316555023193</t>
   </si>
   <si>
     <t xml:space="preserve">17.2800884246826</t>
@@ -962,22 +962,22 @@
     <t xml:space="preserve">16.7002182006836</t>
   </si>
   <si>
-    <t xml:space="preserve">16.553316116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.483736038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7775363922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5146579742432</t>
+    <t xml:space="preserve">16.5533180236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4837341308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7775344848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5146617889404</t>
   </si>
   <si>
     <t xml:space="preserve">16.3832225799561</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3986854553223</t>
+    <t xml:space="preserve">16.3986835479736</t>
   </si>
   <si>
     <t xml:space="preserve">16.2749805450439</t>
@@ -989,37 +989,37 @@
     <t xml:space="preserve">16.0584964752197</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9657182693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9502544403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0353031158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2827110290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4141483306885</t>
+    <t xml:space="preserve">15.9657173156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.950252532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0352993011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2827129364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4141464233398</t>
   </si>
   <si>
     <t xml:space="preserve">16.6074390411377</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5919742584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9321670532227</t>
+    <t xml:space="preserve">16.5919761657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9321632385254</t>
   </si>
   <si>
     <t xml:space="preserve">17.0481395721436</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2646217346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9476280212402</t>
+    <t xml:space="preserve">17.2646255493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9476261138916</t>
   </si>
   <si>
     <t xml:space="preserve">17.0713329315186</t>
@@ -1031,40 +1031,40 @@
     <t xml:space="preserve">17.079065322876</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2723522186279</t>
+    <t xml:space="preserve">17.2723560333252</t>
   </si>
   <si>
     <t xml:space="preserve">17.3032817840576</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3728637695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3187427520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5584201812744</t>
+    <t xml:space="preserve">17.3728656768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3187446594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5584239959717</t>
   </si>
   <si>
     <t xml:space="preserve">17.5893516540527</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4656448364258</t>
+    <t xml:space="preserve">17.4656429290771</t>
   </si>
   <si>
     <t xml:space="preserve">17.7207870483398</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5738868713379</t>
+    <t xml:space="preserve">17.5738887786865</t>
   </si>
   <si>
     <t xml:space="preserve">17.5429611206055</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6975898742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.107364654541</t>
+    <t xml:space="preserve">17.6975917816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1073665618896</t>
   </si>
   <si>
     <t xml:space="preserve">18.0377807617188</t>
@@ -1076,10 +1076,10 @@
     <t xml:space="preserve">17.68212890625</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5197658538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3110103607178</t>
+    <t xml:space="preserve">17.5197639465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3110122680664</t>
   </si>
   <si>
     <t xml:space="preserve">17.1099910736084</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">17.3574028015137</t>
   </si>
   <si>
-    <t xml:space="preserve">17.179573059082</t>
+    <t xml:space="preserve">17.1795749664307</t>
   </si>
   <si>
     <t xml:space="preserve">17.1409168243408</t>
@@ -1097,31 +1097,31 @@
     <t xml:space="preserve">17.0867958068848</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8857746124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6151676177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.530122756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3522968292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0430335998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8265504837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9270582199097</t>
+    <t xml:space="preserve">16.8857765197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6151695251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5301208496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3522930145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0430316925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.826548576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9270601272583</t>
   </si>
   <si>
     <t xml:space="preserve">16.1976661682129</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6692905426025</t>
+    <t xml:space="preserve">16.6692924499512</t>
   </si>
   <si>
     <t xml:space="preserve">16.8703117370605</t>
@@ -1133,58 +1133,58 @@
     <t xml:space="preserve">16.9630928039551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8084583282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9244346618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4218788146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0507621765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4605369567871</t>
+    <t xml:space="preserve">16.8084602355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9244327545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4218807220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0507659912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4605388641357</t>
   </si>
   <si>
     <t xml:space="preserve">16.452808380127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.754337310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6383666992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7929973602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4064178466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3342094421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3805980682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4888401031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5506916046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6898593902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4115219116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6434688568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2568893432617</t>
+    <t xml:space="preserve">16.7543392181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6383647918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7929954528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4064159393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.33420753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.38059425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4888381958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5506935119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6898574829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4115257263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6434707641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.256893157959</t>
   </si>
   <si>
     <t xml:space="preserve">17.2259654998779</t>
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">16.4991970062256</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9785556793213</t>
+    <t xml:space="preserve">16.9785537719727</t>
   </si>
   <si>
     <t xml:space="preserve">16.3445625305176</t>
@@ -1205,76 +1205,76 @@
     <t xml:space="preserve">16.2981758117676</t>
   </si>
   <si>
-    <t xml:space="preserve">16.901237487793</t>
+    <t xml:space="preserve">16.9012393951416</t>
   </si>
   <si>
     <t xml:space="preserve">16.6538276672363</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2672481536865</t>
+    <t xml:space="preserve">16.2672500610352</t>
   </si>
   <si>
     <t xml:space="preserve">16.3136386871338</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4269886016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4475555419922</t>
+    <t xml:space="preserve">17.4269866943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4475574493408</t>
   </si>
   <si>
     <t xml:space="preserve">18.3857021331787</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8805255889893</t>
+    <t xml:space="preserve">18.8805236816406</t>
   </si>
   <si>
     <t xml:space="preserve">19.1433963775635</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0042285919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9114475250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6949653625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6795024871826</t>
+    <t xml:space="preserve">19.0042304992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9114513397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6949672698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.679500579834</t>
   </si>
   <si>
     <t xml:space="preserve">18.7413558959961</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6640396118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7877464294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2516384124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4371967315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3444213867188</t>
+    <t xml:space="preserve">18.664041519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7877445220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2516403198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4371929168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3444175720215</t>
   </si>
   <si>
     <t xml:space="preserve">19.4062728881836</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5609035491943</t>
+    <t xml:space="preserve">19.5609016418457</t>
   </si>
   <si>
     <t xml:space="preserve">19.3289566040039</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1743240356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1124687194824</t>
+    <t xml:space="preserve">19.1743221282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1124706268311</t>
   </si>
   <si>
     <t xml:space="preserve">19.1588611602783</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">19.2825660705566</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2361755371094</t>
+    <t xml:space="preserve">19.236177444458</t>
   </si>
   <si>
     <t xml:space="preserve">19.205249786377</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">19.5918292999268</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4835891723633</t>
+    <t xml:space="preserve">19.4835872650146</t>
   </si>
   <si>
     <t xml:space="preserve">19.5145130157471</t>
@@ -1310,13 +1310,13 @@
     <t xml:space="preserve">19.4526615142822</t>
   </si>
   <si>
-    <t xml:space="preserve">19.607292175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1382942199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3547744750977</t>
+    <t xml:space="preserve">19.6072940826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1382904052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3547763824463</t>
   </si>
   <si>
     <t xml:space="preserve">18.0764389038086</t>
@@ -1325,28 +1325,28 @@
     <t xml:space="preserve">18.0300483703613</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1737804412842</t>
+    <t xml:space="preserve">18.1737785339355</t>
   </si>
   <si>
     <t xml:space="preserve">17.9502010345459</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3654174804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.205717086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6209354400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5091495513916</t>
+    <t xml:space="preserve">18.3654193878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2057189941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6209373474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.509147644043</t>
   </si>
   <si>
     <t xml:space="preserve">18.5889987945557</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5570583343506</t>
+    <t xml:space="preserve">18.557056427002</t>
   </si>
   <si>
     <t xml:space="preserve">18.4931793212891</t>
@@ -1358,13 +1358,13 @@
     <t xml:space="preserve">18.4292984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6848182678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6369094848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4133281707764</t>
+    <t xml:space="preserve">18.6848163604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6369075775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4133262634277</t>
   </si>
   <si>
     <t xml:space="preserve">18.461238861084</t>
@@ -1373,16 +1373,16 @@
     <t xml:space="preserve">18.3175086975098</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8064708709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8224391937256</t>
+    <t xml:space="preserve">17.8064727783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8224411010742</t>
   </si>
   <si>
     <t xml:space="preserve">17.7106513977051</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9182605743408</t>
+    <t xml:space="preserve">17.9182624816895</t>
   </si>
   <si>
     <t xml:space="preserve">17.9661693572998</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">18.03005027771</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8863201141357</t>
+    <t xml:space="preserve">17.8863220214844</t>
   </si>
   <si>
     <t xml:space="preserve">17.9981117248535</t>
@@ -1400,40 +1400,40 @@
     <t xml:space="preserve">18.3973579406738</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5251178741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4452686309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1479434967041</t>
+    <t xml:space="preserve">18.5251197814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4452667236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1479473114014</t>
   </si>
   <si>
     <t xml:space="preserve">19.1639156341553</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0201854705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8604888916016</t>
+    <t xml:space="preserve">19.0201873779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8604869842529</t>
   </si>
   <si>
     <t xml:space="preserve">18.7806377410889</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5730266571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.06809425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7646656036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4772090911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7007865905762</t>
+    <t xml:space="preserve">18.5730285644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0680923461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7646675109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4772071838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7007884979248</t>
   </si>
   <si>
     <t xml:space="preserve">19.2437648773193</t>
@@ -1442,31 +1442,31 @@
     <t xml:space="preserve">19.4513740539551</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4992847442627</t>
+    <t xml:space="preserve">19.4992828369141</t>
   </si>
   <si>
     <t xml:space="preserve">19.2118263244629</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1319732666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0042114257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1160068511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0361576080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1798839569092</t>
+    <t xml:space="preserve">19.1319751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0042152404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1160049438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0361557006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1798858642578</t>
   </si>
   <si>
     <t xml:space="preserve">19.3236141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3395843505859</t>
+    <t xml:space="preserve">19.3395824432373</t>
   </si>
   <si>
     <t xml:space="preserve">19.3076438903809</t>
@@ -1475,25 +1475,25 @@
     <t xml:space="preserve">19.722864151001</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4673442840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3874931335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5631618499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8825607299805</t>
+    <t xml:space="preserve">19.467342376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3874950408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5631637573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8825588226318</t>
   </si>
   <si>
     <t xml:space="preserve">20.3616600036621</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4415092468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2658367156982</t>
+    <t xml:space="preserve">20.4415073394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2658405303955</t>
   </si>
   <si>
     <t xml:space="preserve">20.7609081268311</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">21.0962753295898</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8247871398926</t>
+    <t xml:space="preserve">20.8247852325439</t>
   </si>
   <si>
     <t xml:space="preserve">20.249870300293</t>
@@ -1511,16 +1511,16 @@
     <t xml:space="preserve">20.4734477996826</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1540508270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1700210571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7548027038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5312213897705</t>
+    <t xml:space="preserve">20.154052734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1700191497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7548007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5312232971191</t>
   </si>
   <si>
     <t xml:space="preserve">19.4034652709961</t>
@@ -1532,10 +1532,10 @@
     <t xml:space="preserve">18.7327289581299</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3813896179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2536315917969</t>
+    <t xml:space="preserve">18.3813877105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2536296844482</t>
   </si>
   <si>
     <t xml:space="preserve">17.9342288970947</t>
@@ -1544,7 +1544,7 @@
     <t xml:space="preserve">18.3494491577148</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9243659973145</t>
+    <t xml:space="preserve">18.9243679046631</t>
   </si>
   <si>
     <t xml:space="preserve">18.7486953735352</t>
@@ -1553,10 +1553,10 @@
     <t xml:space="preserve">18.1258697509766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7905006408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4391613006592</t>
+    <t xml:space="preserve">17.7905025482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4391632080078</t>
   </si>
   <si>
     <t xml:space="preserve">17.1357326507568</t>
@@ -1571,28 +1571,28 @@
     <t xml:space="preserve">17.550952911377</t>
   </si>
   <si>
-    <t xml:space="preserve">16.896183013916</t>
+    <t xml:space="preserve">16.8961849212646</t>
   </si>
   <si>
     <t xml:space="preserve">17.0718536376953</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9281272888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8323059082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0558834075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1836452484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4551315307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.816333770752</t>
+    <t xml:space="preserve">16.9281253814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8323040008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0558853149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1836433410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4551334381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8163356781006</t>
   </si>
   <si>
     <t xml:space="preserve">16.3532085418701</t>
@@ -1601,25 +1601,25 @@
     <t xml:space="preserve">15.9859008789062</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0976886749268</t>
+    <t xml:space="preserve">16.0976905822754</t>
   </si>
   <si>
     <t xml:space="preserve">16.1136589050293</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4269514083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.331130027771</t>
+    <t xml:space="preserve">15.4269504547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3311328887939</t>
   </si>
   <si>
     <t xml:space="preserve">15.6505317687988</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4748601913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4429225921631</t>
+    <t xml:space="preserve">15.4748611450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4429206848145</t>
   </si>
   <si>
     <t xml:space="preserve">15.7703037261963</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">15.842170715332</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7383651733398</t>
+    <t xml:space="preserve">15.7383632659912</t>
   </si>
   <si>
     <t xml:space="preserve">16.4490261077881</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">16.4809665679932</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6246948242188</t>
+    <t xml:space="preserve">16.6246967315674</t>
   </si>
   <si>
     <t xml:space="preserve">16.768424987793</t>
@@ -1655,7 +1655,7 @@
     <t xml:space="preserve">17.1676750183105</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3433437347412</t>
+    <t xml:space="preserve">17.3433418273926</t>
   </si>
   <si>
     <t xml:space="preserve">17.2794628143311</t>
@@ -1664,7 +1664,7 @@
     <t xml:space="preserve">16.9440956115723</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0079727172852</t>
+    <t xml:space="preserve">17.0079746246338</t>
   </si>
   <si>
     <t xml:space="preserve">16.6406669616699</t>
@@ -1673,25 +1673,25 @@
     <t xml:space="preserve">16.241418838501</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5608177185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7045440673828</t>
+    <t xml:space="preserve">16.5608139038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7045459747314</t>
   </si>
   <si>
     <t xml:space="preserve">16.8482761383057</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3752841949463</t>
+    <t xml:space="preserve">17.3752822875977</t>
   </si>
   <si>
     <t xml:space="preserve">17.103796005249</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8802127838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9121551513672</t>
+    <t xml:space="preserve">16.8802165985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9121570587158</t>
   </si>
   <si>
     <t xml:space="preserve">16.8642463684082</t>
@@ -1700,28 +1700,28 @@
     <t xml:space="preserve">16.7205142974854</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6885757446289</t>
+    <t xml:space="preserve">16.6885738372803</t>
   </si>
   <si>
     <t xml:space="preserve">16.6087265014648</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7364864349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3052997589111</t>
+    <t xml:space="preserve">16.7364845275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3052978515625</t>
   </si>
   <si>
     <t xml:space="preserve">15.8980646133423</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1935081481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2094783782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3851470947266</t>
+    <t xml:space="preserve">16.193510055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2094764709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3851490020752</t>
   </si>
   <si>
     <t xml:space="preserve">16.28932762146</t>
@@ -1730,37 +1730,37 @@
     <t xml:space="preserve">16.2573890686035</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2254486083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9140348434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.417085647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5288753509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7843990325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5767841339111</t>
+    <t xml:space="preserve">16.2254505157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9140357971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4170875549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5288772583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7843971252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5767860412598</t>
   </si>
   <si>
     <t xml:space="preserve">16.369176864624</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1775398254395</t>
+    <t xml:space="preserve">16.1775379180908</t>
   </si>
   <si>
     <t xml:space="preserve">16.4889526367188</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2494049072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.329252243042</t>
+    <t xml:space="preserve">16.2494010925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3292541503906</t>
   </si>
   <si>
     <t xml:space="preserve">16.4091014862061</t>
@@ -1769,13 +1769,13 @@
     <t xml:space="preserve">16.1695537567139</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0497798919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5688018798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6486530303955</t>
+    <t xml:space="preserve">16.0497779846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5688037872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6486511230469</t>
   </si>
   <si>
     <t xml:space="preserve">17.2874488830566</t>
@@ -1784,22 +1784,22 @@
     <t xml:space="preserve">17.0878257751465</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0479011535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.808349609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9680480957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7285022735596</t>
+    <t xml:space="preserve">17.0478992462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8083515167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9680500030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7285041809082</t>
   </si>
   <si>
     <t xml:space="preserve">16.8882007598877</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1277503967285</t>
+    <t xml:space="preserve">17.1277484893799</t>
   </si>
   <si>
     <t xml:space="preserve">16.8793506622314</t>
@@ -1808,31 +1808,31 @@
     <t xml:space="preserve">17.0452404022217</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9208221435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7964038848877</t>
+    <t xml:space="preserve">16.9208240509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7964057922363</t>
   </si>
   <si>
     <t xml:space="preserve">17.2111301422119</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1281871795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1696586608887</t>
+    <t xml:space="preserve">17.1281852722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1696605682373</t>
   </si>
   <si>
     <t xml:space="preserve">17.418493270874</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3770236968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4599647521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2940769195557</t>
+    <t xml:space="preserve">17.3770217895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4599666595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.294075012207</t>
   </si>
   <si>
     <t xml:space="preserve">16.9622955322266</t>
@@ -1844,37 +1844,37 @@
     <t xml:space="preserve">16.6305122375488</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3402061462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4895076751709</t>
+    <t xml:space="preserve">16.3402080535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4895057678223</t>
   </si>
   <si>
     <t xml:space="preserve">16.5392742156982</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7088012695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6673278808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5014400482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.542911529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2526035308838</t>
+    <t xml:space="preserve">17.7088031768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.667329788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5014381408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5429096221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2526016235352</t>
   </si>
   <si>
     <t xml:space="preserve">16.7134590148926</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4231510162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.373384475708</t>
+    <t xml:space="preserve">16.4231491088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3733825683594</t>
   </si>
   <si>
     <t xml:space="preserve">16.2406711578369</t>
@@ -1883,13 +1883,13 @@
     <t xml:space="preserve">16.1743144989014</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2738513946533</t>
+    <t xml:space="preserve">16.2738494873047</t>
   </si>
   <si>
     <t xml:space="preserve">16.124547958374</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3070259094238</t>
+    <t xml:space="preserve">16.3070278167725</t>
   </si>
   <si>
     <t xml:space="preserve">15.8591232299805</t>
@@ -1901,13 +1901,13 @@
     <t xml:space="preserve">15.7927675247192</t>
   </si>
   <si>
-    <t xml:space="preserve">16.074779510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5273427963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4278106689453</t>
+    <t xml:space="preserve">16.0747814178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5273418426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.427809715271</t>
   </si>
   <si>
     <t xml:space="preserve">15.6600532531738</t>
@@ -1916,43 +1916,43 @@
     <t xml:space="preserve">15.1789722442627</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3614530563354</t>
+    <t xml:space="preserve">15.3614540100098</t>
   </si>
   <si>
     <t xml:space="preserve">15.6932334899902</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6102876663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4609870910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4443998336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3780422210693</t>
+    <t xml:space="preserve">15.6102886199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4609842300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4443988800049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3780431747437</t>
   </si>
   <si>
     <t xml:space="preserve">15.2950973510742</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9254789352417</t>
+    <t xml:space="preserve">15.925479888916</t>
   </si>
   <si>
     <t xml:space="preserve">16.2904376983643</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3899745941162</t>
+    <t xml:space="preserve">16.3899726867676</t>
   </si>
   <si>
     <t xml:space="preserve">16.4397392272949</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6719875335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9576358795166</t>
+    <t xml:space="preserve">16.6719856262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9576377868652</t>
   </si>
   <si>
     <t xml:space="preserve">17.0867118835449</t>
@@ -1967,22 +1967,22 @@
     <t xml:space="preserve">16.5890426635742</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2572631835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8757123947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9088897705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1577243804932</t>
+    <t xml:space="preserve">16.2572612762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.87571144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9088916778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1577281951904</t>
   </si>
   <si>
     <t xml:space="preserve">16.1411361694336</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4729194641113</t>
+    <t xml:space="preserve">16.4729175567627</t>
   </si>
   <si>
     <t xml:space="preserve">15.7595891952515</t>
@@ -1991,13 +1991,13 @@
     <t xml:space="preserve">15.6766443252563</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5936994552612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.477578163147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7430000305176</t>
+    <t xml:space="preserve">15.5936975479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4775772094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7429990768433</t>
   </si>
   <si>
     <t xml:space="preserve">15.7098217010498</t>
@@ -2006,7 +2006,7 @@
     <t xml:space="preserve">15.8425340652466</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3567924499512</t>
+    <t xml:space="preserve">16.3567943572998</t>
   </si>
   <si>
     <t xml:space="preserve">16.3236179351807</t>
@@ -2021,43 +2021,43 @@
     <t xml:space="preserve">17.0037689208984</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2240829467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0084266662598</t>
+    <t xml:space="preserve">16.2240810394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0084247589111</t>
   </si>
   <si>
     <t xml:space="preserve">16.1909046173096</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5558605194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.532000541687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7974262237549</t>
+    <t xml:space="preserve">16.5558624267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5320014953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7974252700806</t>
   </si>
   <si>
     <t xml:space="preserve">14.1836318969727</t>
   </si>
   <si>
-    <t xml:space="preserve">13.93479347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6361923217773</t>
+    <t xml:space="preserve">13.9347944259644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.636191368103</t>
   </si>
   <si>
     <t xml:space="preserve">13.4371242523193</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2712326049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3873558044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7616310119629</t>
+    <t xml:space="preserve">13.2712335586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3873567581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7616300582886</t>
   </si>
   <si>
     <t xml:space="preserve">11.9607000350952</t>
@@ -2069,7 +2069,7 @@
     <t xml:space="preserve">11.0317125320435</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4796180725098</t>
+    <t xml:space="preserve">11.4796171188354</t>
   </si>
   <si>
     <t xml:space="preserve">10.1690816879272</t>
@@ -2078,7 +2078,7 @@
     <t xml:space="preserve">10.3681516647339</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95342445373535</t>
+    <t xml:space="preserve">9.95342540740967</t>
   </si>
   <si>
     <t xml:space="preserve">10.3183832168579</t>
@@ -2087,7 +2087,7 @@
     <t xml:space="preserve">11.8777532577515</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4417810440063</t>
+    <t xml:space="preserve">12.441780090332</t>
   </si>
   <si>
     <t xml:space="preserve">12.8565073013306</t>
@@ -2105,31 +2105,31 @@
     <t xml:space="preserve">10.9155883789062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6667528152466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2022609710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.451096534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5174512863159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5340404510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4013299942017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1524925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0529584884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97001361846924</t>
+    <t xml:space="preserve">10.6667537689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.202260017395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4510955810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5174531936646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5340414047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.401328086853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1524934768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0529594421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97001457214355</t>
   </si>
   <si>
     <t xml:space="preserve">10.4676856994629</t>
@@ -2138,19 +2138,19 @@
     <t xml:space="preserve">10.6999320983887</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3017950057983</t>
+    <t xml:space="preserve">10.301794052124</t>
   </si>
   <si>
     <t xml:space="preserve">10.0695476531982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2520275115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0031929016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0363693237305</t>
+    <t xml:space="preserve">10.2520265579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.003191947937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0363702774048</t>
   </si>
   <si>
     <t xml:space="preserve">10.1193151473999</t>
@@ -2159,76 +2159,76 @@
     <t xml:space="preserve">9.92024707794189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4557523727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50552177429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32304096221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14056205749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07420539855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68800163269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1359033584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38939666748047</t>
+    <t xml:space="preserve">9.45575428009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50552082061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32304191589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14056301116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07420444488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68800067901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1359043121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70458889007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38939762115479</t>
   </si>
   <si>
     <t xml:space="preserve">10.4345073699951</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2188491821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4179182052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.99853515625</t>
+    <t xml:space="preserve">10.2188501358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4179191589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9985342025757</t>
   </si>
   <si>
     <t xml:space="preserve">10.899001121521</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9819459915161</t>
+    <t xml:space="preserve">10.9819450378418</t>
   </si>
   <si>
     <t xml:space="preserve">10.8160543441772</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8824110031128</t>
+    <t xml:space="preserve">10.8824100494385</t>
   </si>
   <si>
     <t xml:space="preserve">11.8113975524902</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7782201766968</t>
+    <t xml:space="preserve">11.7782182693481</t>
   </si>
   <si>
     <t xml:space="preserve">11.595739364624</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3634939193726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6833429336548</t>
+    <t xml:space="preserve">11.3634929656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6833419799805</t>
   </si>
   <si>
     <t xml:space="preserve">10.948766708374</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9653568267822</t>
+    <t xml:space="preserve">10.9653558731079</t>
   </si>
   <si>
     <t xml:space="preserve">11.2639589309692</t>
@@ -2237,22 +2237,22 @@
     <t xml:space="preserve">11.2805490493774</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1810140609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3303146362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2971363067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0814809799194</t>
+    <t xml:space="preserve">11.1810150146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3303155899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.297137260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0814800262451</t>
   </si>
   <si>
     <t xml:space="preserve">11.0151224136353</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0648908615112</t>
+    <t xml:space="preserve">11.0648899078369</t>
   </si>
   <si>
     <t xml:space="preserve">10.8326444625854</t>
@@ -2264,10 +2264,10 @@
     <t xml:space="preserve">10.5838088989258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3847408294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6501636505127</t>
+    <t xml:space="preserve">10.3847398757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6501655578613</t>
   </si>
   <si>
     <t xml:space="preserve">10.3515615463257</t>
@@ -2288,13 +2288,13 @@
     <t xml:space="preserve">10.6169862747192</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4842758178711</t>
+    <t xml:space="preserve">10.4842748641968</t>
   </si>
   <si>
     <t xml:space="preserve">10.0197811126709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3349733352661</t>
+    <t xml:space="preserve">10.3349723815918</t>
   </si>
   <si>
     <t xml:space="preserve">10.7828769683838</t>
@@ -2306,22 +2306,22 @@
     <t xml:space="preserve">11.1312465667725</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4132604598999</t>
+    <t xml:space="preserve">11.4132614135742</t>
   </si>
   <si>
     <t xml:space="preserve">11.4298486709595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2307806015015</t>
+    <t xml:space="preserve">11.2307815551758</t>
   </si>
   <si>
     <t xml:space="preserve">10.8658227920532</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3137264251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3966703414917</t>
+    <t xml:space="preserve">11.3137273788452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.396671295166</t>
   </si>
   <si>
     <t xml:space="preserve">11.5127944946289</t>
@@ -2333,31 +2333,31 @@
     <t xml:space="preserve">12.2095346450806</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9772882461548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0602340698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2593021392822</t>
+    <t xml:space="preserve">11.9772872924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0602331161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2593011856079</t>
   </si>
   <si>
     <t xml:space="preserve">11.3800830841064</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1146583557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6335744857788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2686157226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55528736114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6216459274292</t>
+    <t xml:space="preserve">11.1146574020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6335763931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2686166763306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55528831481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62164497375488</t>
   </si>
   <si>
     <t xml:space="preserve">9.65482234954834</t>
@@ -2369,7 +2369,7 @@
     <t xml:space="preserve">9.75435733795166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4915494918823</t>
+    <t xml:space="preserve">12.491548538208</t>
   </si>
   <si>
     <t xml:space="preserve">13.0058088302612</t>
@@ -2378,16 +2378,16 @@
     <t xml:space="preserve">12.1929454803467</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8399181365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3210000991821</t>
+    <t xml:space="preserve">12.839919090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3210010528564</t>
   </si>
   <si>
     <t xml:space="preserve">12.4086027145386</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2758903503418</t>
+    <t xml:space="preserve">12.2758913040161</t>
   </si>
   <si>
     <t xml:space="preserve">12.7237949371338</t>
@@ -2396,19 +2396,19 @@
     <t xml:space="preserve">12.9062747955322</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1053438186646</t>
+    <t xml:space="preserve">13.1053428649902</t>
   </si>
   <si>
     <t xml:space="preserve">12.9892196655273</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0721654891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0223970413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0887537002563</t>
+    <t xml:space="preserve">13.0721645355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0223960876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.088752746582</t>
   </si>
   <si>
     <t xml:space="preserve">13.038987159729</t>
@@ -2417,25 +2417,25 @@
     <t xml:space="preserve">12.6740274429321</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4583711624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5081367492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7403841018677</t>
+    <t xml:space="preserve">12.4583702087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5081377029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7403831481934</t>
   </si>
   <si>
     <t xml:space="preserve">12.3754243850708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4749593734741</t>
+    <t xml:space="preserve">12.4749584197998</t>
   </si>
   <si>
     <t xml:space="preserve">12.6574392318726</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9560413360596</t>
+    <t xml:space="preserve">12.9560403823853</t>
   </si>
   <si>
     <t xml:space="preserve">12.9228630065918</t>
@@ -2450,16 +2450,16 @@
     <t xml:space="preserve">14.3661088943481</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5817670822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6978912353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7642459869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6315326690674</t>
+    <t xml:space="preserve">14.5817680358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6978921890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7642478942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6315336227417</t>
   </si>
   <si>
     <t xml:space="preserve">14.1006851196289</t>
@@ -2468,16 +2468,16 @@
     <t xml:space="preserve">14.4324645996094</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7808351516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7476568222046</t>
+    <t xml:space="preserve">14.7808361053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7476577758789</t>
   </si>
   <si>
     <t xml:space="preserve">14.4988212585449</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3495206832886</t>
+    <t xml:space="preserve">14.3495197296143</t>
   </si>
   <si>
     <t xml:space="preserve">14.2499876022339</t>
@@ -2486,10 +2486,10 @@
     <t xml:space="preserve">14.2333965301514</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7854948043823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0177392959595</t>
+    <t xml:space="preserve">13.7854928970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0177402496338</t>
   </si>
   <si>
     <t xml:space="preserve">14.0509195327759</t>
@@ -2498,22 +2498,22 @@
     <t xml:space="preserve">14.283164024353</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0462608337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.930136680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3946313858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3448619842529</t>
+    <t xml:space="preserve">15.0462598800659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9301376342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3946304321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3448648452759</t>
   </si>
   <si>
     <t xml:space="preserve">15.9918365478516</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8969593048096</t>
+    <t xml:space="preserve">14.8969583511353</t>
   </si>
   <si>
     <t xml:space="preserve">14.9799041748047</t>
@@ -2522,13 +2522,13 @@
     <t xml:space="preserve">14.9135475158691</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9964942932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8259449005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6434659957886</t>
+    <t xml:space="preserve">14.9964933395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.825945854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6434679031372</t>
   </si>
   <si>
     <t xml:space="preserve">16.0250148773193</t>
@@ -2537,16 +2537,16 @@
     <t xml:space="preserve">16.0913696289062</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0581912994385</t>
+    <t xml:space="preserve">16.0581932067871</t>
   </si>
   <si>
     <t xml:space="preserve">15.5605211257935</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0130825042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2619190216064</t>
+    <t xml:space="preserve">15.0130815505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2619171142578</t>
   </si>
   <si>
     <t xml:space="preserve">15.2287425994873</t>
@@ -2555,25 +2555,25 @@
     <t xml:space="preserve">15.1457939147949</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4941663742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6268768310547</t>
+    <t xml:space="preserve">15.4941673278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.626877784729</t>
   </si>
   <si>
     <t xml:space="preserve">15.2121515274048</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5024604797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2702102661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2536220550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5439319610596</t>
+    <t xml:space="preserve">15.502459526062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2702131271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.253623008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5439329147339</t>
   </si>
   <si>
     <t xml:space="preserve">15.5771102905273</t>
@@ -2585,16 +2585,16 @@
     <t xml:space="preserve">15.7181177139282</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7347049713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8840093612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7512950897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4361028671265</t>
+    <t xml:space="preserve">15.7347040176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8840065002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7512941360474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4361038208008</t>
   </si>
   <si>
     <t xml:space="preserve">16.3982677459717</t>
@@ -2603,22 +2603,22 @@
     <t xml:space="preserve">16.5807476043701</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8674182891846</t>
+    <t xml:space="preserve">15.8674192428589</t>
   </si>
   <si>
     <t xml:space="preserve">16.0830764770508</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1079578399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4646224975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.622220993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8212890625</t>
+    <t xml:space="preserve">16.1079597473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4646244049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6222190856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8212871551514</t>
   </si>
   <si>
     <t xml:space="preserve">16.7051639556885</t>
@@ -2630,10 +2630,10 @@
     <t xml:space="preserve">16.9374122619629</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1364784240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3023700714111</t>
+    <t xml:space="preserve">17.1364803314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3023719787598</t>
   </si>
   <si>
     <t xml:space="preserve">17.4350833892822</t>
@@ -2648,64 +2648,64 @@
     <t xml:space="preserve">16.7217540740967</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1530666351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0535335540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0369453430176</t>
+    <t xml:space="preserve">17.1530704498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0535354614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0369472503662</t>
   </si>
   <si>
     <t xml:space="preserve">16.8876457214355</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7715225219727</t>
+    <t xml:space="preserve">16.7715187072754</t>
   </si>
   <si>
     <t xml:space="preserve">16.8544673919678</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2028369903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1033020019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1198902130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7383441925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3521347045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2691917419434</t>
+    <t xml:space="preserve">17.2028350830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1033039093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1198921203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7383422851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3521366119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.269193649292</t>
   </si>
   <si>
     <t xml:space="preserve">16.8710556030273</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9171857833862</t>
+    <t xml:space="preserve">15.9171848297119</t>
   </si>
   <si>
     <t xml:space="preserve">16.2074966430664</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2323760986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6056327819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6958503723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1981792449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.165002822876</t>
+    <t xml:space="preserve">16.2323780059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6056308746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6958522796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1981773376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1649990081787</t>
   </si>
   <si>
     <t xml:space="preserve">17.617561340332</t>
@@ -2714,22 +2714,22 @@
     <t xml:space="preserve">18.0820560455322</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6507415771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8000411987305</t>
+    <t xml:space="preserve">17.6507396697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8000392913818</t>
   </si>
   <si>
     <t xml:space="preserve">17.4019050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3189563751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.020357131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7881107330322</t>
+    <t xml:space="preserve">17.3189601898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0203590393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7881088256836</t>
   </si>
   <si>
     <t xml:space="preserve">16.9705905914307</t>
@@ -2738,22 +2738,22 @@
     <t xml:space="preserve">17.1862468719482</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4065647125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4148559570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.049898147583</t>
+    <t xml:space="preserve">16.4065628051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4148578643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0498962402344</t>
   </si>
   <si>
     <t xml:space="preserve">16.1660213470459</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5346164703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0701217651367</t>
+    <t xml:space="preserve">17.5346183776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.070125579834</t>
   </si>
   <si>
     <t xml:space="preserve">17.2360153198242</t>
@@ -2768,28 +2768,28 @@
     <t xml:space="preserve">17.276216506958</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2424755096436</t>
+    <t xml:space="preserve">17.2424736022949</t>
   </si>
   <si>
     <t xml:space="preserve">17.3437023162842</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5461578369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4111862182617</t>
+    <t xml:space="preserve">17.5461559295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4111881256104</t>
   </si>
   <si>
     <t xml:space="preserve">17.3774433135986</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6642570495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4449291229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4618015289307</t>
+    <t xml:space="preserve">17.6642589569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4449310302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4618034362793</t>
   </si>
   <si>
     <t xml:space="preserve">17.1749897003174</t>
@@ -2801,10 +2801,10 @@
     <t xml:space="preserve">17.0062770843506</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9556636810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8628692626953</t>
+    <t xml:space="preserve">16.9556617736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8628711700439</t>
   </si>
   <si>
     <t xml:space="preserve">17.090633392334</t>
@@ -2813,7 +2813,7 @@
     <t xml:space="preserve">16.8713073730469</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7532081604004</t>
+    <t xml:space="preserve">16.7532062530518</t>
   </si>
   <si>
     <t xml:space="preserve">17.2087326049805</t>
@@ -2825,22 +2825,22 @@
     <t xml:space="preserve">16.0952262878418</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1458396911621</t>
+    <t xml:space="preserve">16.1458377838135</t>
   </si>
   <si>
     <t xml:space="preserve">15.7915410995483</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6903162002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8590278625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4119386672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5216016769409</t>
+    <t xml:space="preserve">15.690315246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8590259552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4119396209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5215997695923</t>
   </si>
   <si>
     <t xml:space="preserve">15.0998191833496</t>
@@ -2849,52 +2849,52 @@
     <t xml:space="preserve">15.420373916626</t>
   </si>
   <si>
-    <t xml:space="preserve">15.60595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5806503295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8337211608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0446109771729</t>
+    <t xml:space="preserve">15.6059589385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5806512832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.833722114563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0446128845215</t>
   </si>
   <si>
     <t xml:space="preserve">15.8758993148804</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8927698135376</t>
+    <t xml:space="preserve">15.8927707672119</t>
   </si>
   <si>
     <t xml:space="preserve">16.0108680725098</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9349460601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7662363052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7746725082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5131635665894</t>
+    <t xml:space="preserve">15.934947013855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7662353515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7746715545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5131645202637</t>
   </si>
   <si>
     <t xml:space="preserve">15.4878606796265</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1841745376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.234787940979</t>
+    <t xml:space="preserve">15.184175491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2347888946533</t>
   </si>
   <si>
     <t xml:space="preserve">15.3950662612915</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9433832168579</t>
+    <t xml:space="preserve">15.9433841705322</t>
   </si>
   <si>
     <t xml:space="preserve">16.112096786499</t>
@@ -2906,7 +2906,7 @@
     <t xml:space="preserve">16.4495220184326</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5890855789185</t>
+    <t xml:space="preserve">15.5890865325928</t>
   </si>
   <si>
     <t xml:space="preserve">15.6987504959106</t>
@@ -2918,40 +2918,40 @@
     <t xml:space="preserve">15.9686918258667</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3145523071289</t>
+    <t xml:space="preserve">16.3145542144775</t>
   </si>
   <si>
     <t xml:space="preserve">15.9180765151978</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0193061828613</t>
+    <t xml:space="preserve">16.0193042755127</t>
   </si>
   <si>
     <t xml:space="preserve">15.5384721755981</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0154609680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1504325866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5300350189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8168497085571</t>
+    <t xml:space="preserve">15.0154628753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1504316329956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5300369262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8168506622314</t>
   </si>
   <si>
     <t xml:space="preserve">15.5637807846069</t>
   </si>
   <si>
-    <t xml:space="preserve">15.884334564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1374034881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8674612045288</t>
+    <t xml:space="preserve">15.8843355178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1374053955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8674621582031</t>
   </si>
   <si>
     <t xml:space="preserve">15.4541168212891</t>
@@ -2990,13 +2990,13 @@
     <t xml:space="preserve">14.0537977218628</t>
   </si>
   <si>
-    <t xml:space="preserve">14.121283531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4295597076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5898380279541</t>
+    <t xml:space="preserve">14.1212825775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4295587539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5898370742798</t>
   </si>
   <si>
     <t xml:space="preserve">13.142746925354</t>
@@ -3005,13 +3005,13 @@
     <t xml:space="preserve">12.7294006347656</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6028652191162</t>
+    <t xml:space="preserve">12.6028642654419</t>
   </si>
   <si>
     <t xml:space="preserve">12.906548500061</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3367671966553</t>
+    <t xml:space="preserve">13.3367681503296</t>
   </si>
   <si>
     <t xml:space="preserve">13.1258764266968</t>
@@ -3020,10 +3020,10 @@
     <t xml:space="preserve">13.513916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9188280105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.319896697998</t>
+    <t xml:space="preserve">13.9188270568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3198957443237</t>
   </si>
   <si>
     <t xml:space="preserve">13.5307874679565</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">12.9318552017212</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7631425857544</t>
+    <t xml:space="preserve">12.7631435394287</t>
   </si>
   <si>
     <t xml:space="preserve">12.6366081237793</t>
@@ -3047,7 +3047,7 @@
     <t xml:space="preserve">12.484766960144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6872224807739</t>
+    <t xml:space="preserve">12.6872215270996</t>
   </si>
   <si>
     <t xml:space="preserve">12.6619157791138</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">12.7209644317627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4678955078125</t>
+    <t xml:space="preserve">12.4678945541382</t>
   </si>
   <si>
     <t xml:space="preserve">12.1304683685303</t>
@@ -3065,25 +3065,25 @@
     <t xml:space="preserve">12.2823104858398</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3497953414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3666677474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.585994720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4126882553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3958177566528</t>
+    <t xml:space="preserve">12.349796295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3666667938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5859937667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4126873016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3958168029785</t>
   </si>
   <si>
     <t xml:space="preserve">13.4464302062988</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7838573455811</t>
+    <t xml:space="preserve">13.7838563919067</t>
   </si>
   <si>
     <t xml:space="preserve">13.3114595413208</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">12.7040939331055</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7715787887573</t>
+    <t xml:space="preserve">12.7715797424316</t>
   </si>
   <si>
     <t xml:space="preserve">12.4004096984863</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">11.8773994445801</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1473388671875</t>
+    <t xml:space="preserve">12.1473398208618</t>
   </si>
   <si>
     <t xml:space="preserve">12.1642122268677</t>
@@ -3143,7 +3143,7 @@
     <t xml:space="preserve">11.6487464904785</t>
   </si>
   <si>
-    <t xml:space="preserve">11.474102973938</t>
+    <t xml:space="preserve">11.4741039276123</t>
   </si>
   <si>
     <t xml:space="preserve">11.3693170547485</t>
@@ -3158,7 +3158,7 @@
     <t xml:space="preserve">12.4346437454224</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1028203964233</t>
+    <t xml:space="preserve">12.102819442749</t>
   </si>
   <si>
     <t xml:space="preserve">12.0154991149902</t>
@@ -3167,7 +3167,7 @@
     <t xml:space="preserve">11.9805698394775</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1901435852051</t>
+    <t xml:space="preserve">12.1901426315308</t>
   </si>
   <si>
     <t xml:space="preserve">12.3298578262329</t>
@@ -3188,7 +3188,7 @@
     <t xml:space="preserve">11.1946725845337</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7186050415039</t>
+    <t xml:space="preserve">11.7186040878296</t>
   </si>
   <si>
     <t xml:space="preserve">11.5788888931274</t>
@@ -3200,13 +3200,13 @@
     <t xml:space="preserve">11.8583192825317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7709970474243</t>
+    <t xml:space="preserve">11.7709980010986</t>
   </si>
   <si>
     <t xml:space="preserve">11.9631052017212</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7535333633423</t>
+    <t xml:space="preserve">11.753532409668</t>
   </si>
   <si>
     <t xml:space="preserve">11.49156665802</t>
@@ -3215,16 +3215,16 @@
     <t xml:space="preserve">11.2645301818848</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8104562759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0549573898315</t>
+    <t xml:space="preserve">10.8104553222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0549583435059</t>
   </si>
   <si>
     <t xml:space="preserve">11.1772079467773</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3867807388306</t>
+    <t xml:space="preserve">11.3867797851562</t>
   </si>
   <si>
     <t xml:space="preserve">11.2470655441284</t>
@@ -3236,13 +3236,13 @@
     <t xml:space="preserve">10.8453845977783</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3343868255615</t>
+    <t xml:space="preserve">11.3343877792358</t>
   </si>
   <si>
     <t xml:space="preserve">11.3169231414795</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4042453765869</t>
+    <t xml:space="preserve">11.4042463302612</t>
   </si>
   <si>
     <t xml:space="preserve">11.2296009063721</t>
@@ -3254,16 +3254,16 @@
     <t xml:space="preserve">11.7884616851807</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8233909606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.805926322937</t>
+    <t xml:space="preserve">11.823390007019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8059272766113</t>
   </si>
   <si>
     <t xml:space="preserve">11.5614242553711</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4566383361816</t>
+    <t xml:space="preserve">11.4566373825073</t>
   </si>
   <si>
     <t xml:space="preserve">11.5439605712891</t>
@@ -3275,7 +3275,7 @@
     <t xml:space="preserve">11.1073503494263</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0898866653442</t>
+    <t xml:space="preserve">11.0898857116699</t>
   </si>
   <si>
     <t xml:space="preserve">10.7231340408325</t>
@@ -3287,7 +3287,7 @@
     <t xml:space="preserve">10.6707401275635</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5135622024536</t>
+    <t xml:space="preserve">10.5135612487793</t>
   </si>
   <si>
     <t xml:space="preserve">10.2865238189697</t>
@@ -3299,7 +3299,7 @@
     <t xml:space="preserve">10.0594873428345</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1468095779419</t>
+    <t xml:space="preserve">10.1468086242676</t>
   </si>
   <si>
     <t xml:space="preserve">9.78005695343018</t>
@@ -3317,28 +3317,28 @@
     <t xml:space="preserve">9.98962879180908</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1992025375366</t>
+    <t xml:space="preserve">10.1992034912109</t>
   </si>
   <si>
     <t xml:space="preserve">9.29105472564697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51809120178223</t>
+    <t xml:space="preserve">9.51809215545654</t>
   </si>
   <si>
     <t xml:space="preserve">9.2211971282959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25612545013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0640172958374</t>
+    <t xml:space="preserve">9.25612640380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06401634216309</t>
   </si>
   <si>
     <t xml:space="preserve">8.80205154418945</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81951522827148</t>
+    <t xml:space="preserve">8.8195161819458</t>
   </si>
   <si>
     <t xml:space="preserve">8.60121154785156</t>
@@ -3347,19 +3347,19 @@
     <t xml:space="preserve">8.48769187927246</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19079875946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44403076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46149635314941</t>
+    <t xml:space="preserve">8.19079780578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44403171539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4614953994751</t>
   </si>
   <si>
     <t xml:space="preserve">8.3392448425293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56628322601318</t>
+    <t xml:space="preserve">8.56628227233887</t>
   </si>
   <si>
     <t xml:space="preserve">8.34797668457031</t>
@@ -3374,7 +3374,7 @@
     <t xml:space="preserve">8.85444450378418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88937282562256</t>
+    <t xml:space="preserve">8.88937377929688</t>
   </si>
   <si>
     <t xml:space="preserve">9.04655265808105</t>
@@ -3383,7 +3383,7 @@
     <t xml:space="preserve">9.01162433624268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83698081970215</t>
+    <t xml:space="preserve">8.83697986602783</t>
   </si>
   <si>
     <t xml:space="preserve">8.7321949005127</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">9.72766399383545</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55301952362061</t>
+    <t xml:space="preserve">9.55302047729492</t>
   </si>
   <si>
     <t xml:space="preserve">9.622878074646</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">9.91977119445801</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2690601348877</t>
+    <t xml:space="preserve">10.269061088562</t>
   </si>
   <si>
     <t xml:space="preserve">9.65780639648438</t>
@@ -3431,7 +3431,7 @@
     <t xml:space="preserve">9.67527103424072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8324499130249</t>
+    <t xml:space="preserve">9.83245086669922</t>
   </si>
   <si>
     <t xml:space="preserve">10.0420236587524</t>
@@ -3455,7 +3455,7 @@
     <t xml:space="preserve">10.0944156646729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0769519805908</t>
+    <t xml:space="preserve">10.0769510269165</t>
   </si>
   <si>
     <t xml:space="preserve">9.79752159118652</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">10.0070943832397</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4437046051025</t>
+    <t xml:space="preserve">10.4437036514282</t>
   </si>
   <si>
     <t xml:space="preserve">10.6532764434814</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">10.7405977249146</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7580623626709</t>
+    <t xml:space="preserve">10.7580633163452</t>
   </si>
   <si>
     <t xml:space="preserve">10.9152431488037</t>
@@ -3488,13 +3488,13 @@
     <t xml:space="preserve">11.0200290679932</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3518524169922</t>
+    <t xml:space="preserve">11.3518514633179</t>
   </si>
   <si>
     <t xml:space="preserve">11.0025644302368</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9676351547241</t>
+    <t xml:space="preserve">10.9676361083984</t>
   </si>
   <si>
     <t xml:space="preserve">10.5310258865356</t>
@@ -3506,7 +3506,7 @@
     <t xml:space="preserve">10.7056694030762</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6008834838867</t>
+    <t xml:space="preserve">10.6008825302124</t>
   </si>
   <si>
     <t xml:space="preserve">10.565954208374</t>
@@ -3521,10 +3521,10 @@
     <t xml:space="preserve">10.2166662216187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0245571136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84991455078125</t>
+    <t xml:space="preserve">10.0245580673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84991359710693</t>
   </si>
   <si>
     <t xml:space="preserve">10.1118803024292</t>
@@ -3542,13 +3542,13 @@
     <t xml:space="preserve">11.9456415176392</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7011394500732</t>
+    <t xml:space="preserve">11.7011404037476</t>
   </si>
   <si>
     <t xml:space="preserve">12.1202850341797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.399715423584</t>
+    <t xml:space="preserve">12.3997144699097</t>
   </si>
   <si>
     <t xml:space="preserve">11.9281768798828</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">11.8757839202881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0678911209106</t>
+    <t xml:space="preserve">12.067892074585</t>
   </si>
   <si>
     <t xml:space="preserve">12.0329627990723</t>
@@ -3575,7 +3575,7 @@
     <t xml:space="preserve">12.8712539672852</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6442155838013</t>
+    <t xml:space="preserve">12.6442165374756</t>
   </si>
   <si>
     <t xml:space="preserve">12.9491119384766</t>
@@ -4611,6 +4611,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.63000011444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47999954223633</t>
   </si>
 </sst>
 </file>
@@ -69611,7 +69614,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6496296296</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>89476</v>
@@ -69632,6 +69635,32 @@
         <v>1512</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6493981481</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>117264</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>9.59000015258789</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>9.35999965667725</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>9.59000015258789</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>9.47999954223633</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>1533</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARR.MI.xlsx
+++ b/data/MARR.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4479513168335</t>
+    <t xml:space="preserve">13.4479522705078</t>
   </si>
   <si>
     <t xml:space="preserve">MARR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2894020080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1812992095947</t>
+    <t xml:space="preserve">13.2894010543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1812982559204</t>
   </si>
   <si>
     <t xml:space="preserve">12.9939203262329</t>
@@ -59,19 +59,19 @@
     <t xml:space="preserve">12.5903358459473</t>
   </si>
   <si>
-    <t xml:space="preserve">12.655198097229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7344751358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4389963150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4462003707886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9849634170532</t>
+    <t xml:space="preserve">12.6551990509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7344741821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4389953613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4462022781372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9849615097046</t>
   </si>
   <si>
     <t xml:space="preserve">12.0858602523804</t>
@@ -83,40 +83,40 @@
     <t xml:space="preserve">12.2155828475952</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8353700637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6768207550049</t>
+    <t xml:space="preserve">12.8353710174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6768198013306</t>
   </si>
   <si>
     <t xml:space="preserve">12.5615100860596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5543041229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6407871246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7200613021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9722995758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7777156829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3308944702148</t>
+    <t xml:space="preserve">12.5543050765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6407852172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7200603485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.97230052948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7777147293091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3308916091919</t>
   </si>
   <si>
     <t xml:space="preserve">12.5110635757446</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2948570251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4084157943726</t>
+    <t xml:space="preserve">12.2948589324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4084167480469</t>
   </si>
   <si>
     <t xml:space="preserve">11.4516582489014</t>
@@ -125,76 +125,76 @@
     <t xml:space="preserve">11.8840684890747</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5885887145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8912734985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9273080825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0426187515259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2011671066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3957548141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7056474685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6047515869141</t>
+    <t xml:space="preserve">11.5885877609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8912744522095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9273090362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0426168441772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2011680603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3957529067993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7056465148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6047506332397</t>
   </si>
   <si>
     <t xml:space="preserve">12.5759248733521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9362659454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1596765518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9434719085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0731964111328</t>
+    <t xml:space="preserve">12.9362649917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1596784591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9434728622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0731954574585</t>
   </si>
   <si>
     <t xml:space="preserve">12.8858184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5975427627563</t>
+    <t xml:space="preserve">12.5975437164307</t>
   </si>
   <si>
     <t xml:space="preserve">12.078652381897</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3597183227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6696128845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8137493133545</t>
+    <t xml:space="preserve">12.3597192764282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6696138381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8137502670288</t>
   </si>
   <si>
     <t xml:space="preserve">12.6984395980835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8714056015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.453408241272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3453044891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.684027671814</t>
+    <t xml:space="preserve">12.8714027404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4534091949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3453035354614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6840286254883</t>
   </si>
   <si>
     <t xml:space="preserve">12.7560949325562</t>
@@ -206,28 +206,28 @@
     <t xml:space="preserve">13.2677812576294</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3326406478882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0804033279419</t>
+    <t xml:space="preserve">13.3326416015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0804014205933</t>
   </si>
   <si>
     <t xml:space="preserve">13.1885032653809</t>
   </si>
   <si>
-    <t xml:space="preserve">13.260573387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7073984146118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.491189956665</t>
+    <t xml:space="preserve">13.2605724334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7073974609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4911937713623</t>
   </si>
   <si>
     <t xml:space="preserve">13.3470554351807</t>
   </si>
   <si>
-    <t xml:space="preserve">13.001127243042</t>
+    <t xml:space="preserve">13.0011281967163</t>
   </si>
   <si>
     <t xml:space="preserve">12.9002313613892</t>
@@ -236,10 +236,10 @@
     <t xml:space="preserve">12.828164100647</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7921295166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0587844848633</t>
+    <t xml:space="preserve">12.7921285629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.058783531189</t>
   </si>
   <si>
     <t xml:space="preserve">13.1020231246948</t>
@@ -248,145 +248,145 @@
     <t xml:space="preserve">12.8065433502197</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2821931838989</t>
+    <t xml:space="preserve">13.2821941375732</t>
   </si>
   <si>
     <t xml:space="preserve">13.1380558013916</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8425760269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8930253982544</t>
+    <t xml:space="preserve">12.8425769805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8930234909058</t>
   </si>
   <si>
     <t xml:space="preserve">12.9074382781982</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0227479934692</t>
+    <t xml:space="preserve">13.0227451324463</t>
   </si>
   <si>
     <t xml:space="preserve">12.6624069213867</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8786096572876</t>
+    <t xml:space="preserve">12.8786115646362</t>
   </si>
   <si>
     <t xml:space="preserve">12.6335783004761</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7488870620728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0258750915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0183887481689</t>
+    <t xml:space="preserve">12.7488899230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0258741378784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0183877944946</t>
   </si>
   <si>
     <t xml:space="preserve">13.2579431533813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2504587173462</t>
+    <t xml:space="preserve">13.2504596710205</t>
   </si>
   <si>
     <t xml:space="preserve">13.4301261901855</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4825286865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3103485107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2654314041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.475043296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3702383041382</t>
+    <t xml:space="preserve">13.4825296401978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3103494644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2654323577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4750442504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3702363967896</t>
   </si>
   <si>
     <t xml:space="preserve">13.2878894805908</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2729177474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2804040908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8012924194336</t>
+    <t xml:space="preserve">13.2729167938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.280403137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8012914657593</t>
   </si>
   <si>
     <t xml:space="preserve">12.8836374282837</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6141376495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3146924972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.44944190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8087797164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7938041687012</t>
+    <t xml:space="preserve">12.6141395568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3146934509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4494409561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8087768554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7938060760498</t>
   </si>
   <si>
     <t xml:space="preserve">13.0782766342163</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4419584274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7831764221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2847461700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7339153289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4226408004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5274467468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0558214187622</t>
+    <t xml:space="preserve">12.4419565200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7831773757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2847480773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7339162826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4226417541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5274438858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0558195114136</t>
   </si>
   <si>
     <t xml:space="preserve">13.4525842666626</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3328065872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7595167160034</t>
+    <t xml:space="preserve">13.3328075408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7595148086548</t>
   </si>
   <si>
     <t xml:space="preserve">13.7295713424683</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7220849990845</t>
+    <t xml:space="preserve">13.7220869064331</t>
   </si>
   <si>
     <t xml:space="preserve">13.5349321365356</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4900150299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7370595932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0140438079834</t>
+    <t xml:space="preserve">13.4900159835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7370586395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0140466690063</t>
   </si>
   <si>
     <t xml:space="preserve">13.7071142196655</t>
@@ -395,82 +395,82 @@
     <t xml:space="preserve">13.8493499755859</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1113653182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.976616859436</t>
+    <t xml:space="preserve">14.111364364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9766149520874</t>
   </si>
   <si>
     <t xml:space="preserve">14.0814189910889</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7445449829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9990749359131</t>
+    <t xml:space="preserve">13.7445440292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9990720748901</t>
   </si>
   <si>
     <t xml:space="preserve">13.5049886703491</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6397380828857</t>
+    <t xml:space="preserve">13.6397361755371</t>
   </si>
   <si>
     <t xml:space="preserve">13.6621952056885</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6097946166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3477802276611</t>
+    <t xml:space="preserve">13.6097936630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3477783203125</t>
   </si>
   <si>
     <t xml:space="preserve">13.4151544570923</t>
   </si>
   <si>
-    <t xml:space="preserve">13.220516204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0857629776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1007375717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.063307762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2354869842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1456518173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9285554885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2055416107178</t>
+    <t xml:space="preserve">13.2205152511597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0857639312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1007356643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0633068084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2354879379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1456527709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9285564422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2055435180664</t>
   </si>
   <si>
     <t xml:space="preserve">13.1082229614258</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1980571746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1157083511353</t>
+    <t xml:space="preserve">13.1980562210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1157093048096</t>
   </si>
   <si>
     <t xml:space="preserve">13.0109004974365</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9135828018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8611812591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.943528175354</t>
+    <t xml:space="preserve">12.9135837554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8611822128296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9435272216797</t>
   </si>
   <si>
     <t xml:space="preserve">13.1905698776245</t>
@@ -479,43 +479,43 @@
     <t xml:space="preserve">13.4076681137085</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3552656173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2130289077759</t>
+    <t xml:space="preserve">13.3552665710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2130279541016</t>
   </si>
   <si>
     <t xml:space="preserve">13.340292930603</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9659852981567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8761539459229</t>
+    <t xml:space="preserve">12.9659843444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8761520385742</t>
   </si>
   <si>
     <t xml:space="preserve">12.8312349319458</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9809598922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7638607025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7114562988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8686656951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7563753128052</t>
+    <t xml:space="preserve">12.9809589385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7638597488403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7114572525024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8686666488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7563743591309</t>
   </si>
   <si>
     <t xml:space="preserve">12.7488880157471</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6815137863159</t>
+    <t xml:space="preserve">12.6815147399902</t>
   </si>
   <si>
     <t xml:space="preserve">12.5767059326172</t>
@@ -524,10 +524,10 @@
     <t xml:space="preserve">12.5467624664307</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5317907333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5617351531982</t>
+    <t xml:space="preserve">12.5317897796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5617332458496</t>
   </si>
   <si>
     <t xml:space="preserve">12.5542497634888</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">12.2772607803345</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4719009399414</t>
+    <t xml:space="preserve">12.4718999862671</t>
   </si>
   <si>
     <t xml:space="preserve">12.5018453598022</t>
@@ -560,13 +560,13 @@
     <t xml:space="preserve">12.3820686340332</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4045267105103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2697763442993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1649694442749</t>
+    <t xml:space="preserve">12.4045257568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.269775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1649703979492</t>
   </si>
   <si>
     <t xml:space="preserve">12.2548036575317</t>
@@ -584,79 +584,79 @@
     <t xml:space="preserve">12.6740264892578</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7863178253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0932512283325</t>
+    <t xml:space="preserve">12.7863187789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0932493209839</t>
   </si>
   <si>
     <t xml:space="preserve">12.9510135650635</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1306819915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9884452819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1381664276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1606254577637</t>
+    <t xml:space="preserve">13.1306810379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9884433746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.138165473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.160626411438</t>
   </si>
   <si>
     <t xml:space="preserve">13.183084487915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1681127548218</t>
+    <t xml:space="preserve">13.1681118011475</t>
   </si>
   <si>
     <t xml:space="preserve">13.2280006408691</t>
   </si>
   <si>
-    <t xml:space="preserve">13.00341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1755990982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4001808166504</t>
+    <t xml:space="preserve">13.0034170150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1756000518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4001817703247</t>
   </si>
   <si>
     <t xml:space="preserve">13.3852100372314</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8643236160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9167251586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5199604034424</t>
+    <t xml:space="preserve">13.8643226623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9167261123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5199584960938</t>
   </si>
   <si>
     <t xml:space="preserve">13.4450988769531</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3627510070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4600715637207</t>
+    <t xml:space="preserve">13.3627519607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4600706100464</t>
   </si>
   <si>
     <t xml:space="preserve">13.5124731063843</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4376134872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8268909454346</t>
+    <t xml:space="preserve">13.437611579895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8268918991089</t>
   </si>
   <si>
     <t xml:space="preserve">13.6247673034668</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8044347763062</t>
+    <t xml:space="preserve">13.8044338226318</t>
   </si>
   <si>
     <t xml:space="preserve">13.7819757461548</t>
@@ -668,16 +668,16 @@
     <t xml:space="preserve">13.8418636322021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6771697998047</t>
+    <t xml:space="preserve">13.6771688461304</t>
   </si>
   <si>
     <t xml:space="preserve">13.856837272644</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7670011520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5648794174194</t>
+    <t xml:space="preserve">13.7670030593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5648784637451</t>
   </si>
   <si>
     <t xml:space="preserve">13.8942670822144</t>
@@ -686,46 +686,46 @@
     <t xml:space="preserve">14.3359489440918</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5605354309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5156164169312</t>
+    <t xml:space="preserve">14.5605344772339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5156154632568</t>
   </si>
   <si>
     <t xml:space="preserve">14.6952838897705</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9722709655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9348392486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.942325592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.822548866272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2043428421021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.713397026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.136962890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1594228744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2866868972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3615493774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2267990112305</t>
+    <t xml:space="preserve">14.9722690582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9348411560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9423227310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.822546005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2043409347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7133989334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1369657516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1594247817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2866888046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.36155128479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2268009185791</t>
   </si>
   <si>
     <t xml:space="preserve">15.3465776443481</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">15.6834545135498</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7208833694458</t>
+    <t xml:space="preserve">15.7208852767944</t>
   </si>
   <si>
     <t xml:space="preserve">15.5337295532227</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">15.1669101715088</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1968536376953</t>
+    <t xml:space="preserve">15.1968555450439</t>
   </si>
   <si>
     <t xml:space="preserve">15.5487031936646</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">15.4214391708374</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6011037826538</t>
+    <t xml:space="preserve">15.6011056900024</t>
   </si>
   <si>
     <t xml:space="preserve">15.6460237503052</t>
@@ -767,7 +767,7 @@
     <t xml:space="preserve">15.5861320495605</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9080400466919</t>
+    <t xml:space="preserve">15.9080381393433</t>
   </si>
   <si>
     <t xml:space="preserve">16.42458152771</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">16.3272609710693</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2598838806152</t>
+    <t xml:space="preserve">16.2598876953125</t>
   </si>
   <si>
     <t xml:space="preserve">16.2673721313477</t>
@@ -800,28 +800,28 @@
     <t xml:space="preserve">16.6641368865967</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5218982696533</t>
+    <t xml:space="preserve">16.521900177002</t>
   </si>
   <si>
     <t xml:space="preserve">16.4470386505127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6416778564453</t>
+    <t xml:space="preserve">16.6416759490967</t>
   </si>
   <si>
     <t xml:space="preserve">17.0758762359619</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7988891601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7464847564697</t>
+    <t xml:space="preserve">16.7988872528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7464866638184</t>
   </si>
   <si>
     <t xml:space="preserve">16.8737487792969</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9560947418213</t>
+    <t xml:space="preserve">16.9560966491699</t>
   </si>
   <si>
     <t xml:space="preserve">17.1058197021484</t>
@@ -830,31 +830,31 @@
     <t xml:space="preserve">16.3946342468262</t>
   </si>
   <si>
-    <t xml:space="preserve">16.506929397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6847534179688</t>
+    <t xml:space="preserve">16.5069274902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6847515106201</t>
   </si>
   <si>
     <t xml:space="preserve">17.1950359344482</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1641120910645</t>
+    <t xml:space="preserve">17.1641139984131</t>
   </si>
   <si>
     <t xml:space="preserve">17.0094814300537</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7620697021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6306324005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8471164703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0249443054199</t>
+    <t xml:space="preserve">16.7620716094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6306343078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8471183776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0249462127686</t>
   </si>
   <si>
     <t xml:space="preserve">16.9398956298828</t>
@@ -863,16 +863,16 @@
     <t xml:space="preserve">16.7698020935059</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9940185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1254558563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.955358505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5455856323242</t>
+    <t xml:space="preserve">16.9940204620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1254539489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9553604125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5455837249756</t>
   </si>
   <si>
     <t xml:space="preserve">16.7156810760498</t>
@@ -890,16 +890,16 @@
     <t xml:space="preserve">16.731143951416</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5378532409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5687789916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6229000091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7079486846924</t>
+    <t xml:space="preserve">16.5378551483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5687808990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6229019165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.707950592041</t>
   </si>
   <si>
     <t xml:space="preserve">16.7234134674072</t>
@@ -908,7 +908,7 @@
     <t xml:space="preserve">16.1822032928467</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0894203186035</t>
+    <t xml:space="preserve">16.0894222259521</t>
   </si>
   <si>
     <t xml:space="preserve">16.0816898345947</t>
@@ -920,34 +920,34 @@
     <t xml:space="preserve">15.9347906112671</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2363224029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0739612579346</t>
+    <t xml:space="preserve">16.2363243103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0739593505859</t>
   </si>
   <si>
     <t xml:space="preserve">15.9966449737549</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3909530639648</t>
+    <t xml:space="preserve">16.3909549713135</t>
   </si>
   <si>
     <t xml:space="preserve">16.4914646148682</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8935070037842</t>
+    <t xml:space="preserve">16.8935050964355</t>
   </si>
   <si>
     <t xml:space="preserve">17.2414264678955</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0558700561523</t>
+    <t xml:space="preserve">17.055871963501</t>
   </si>
   <si>
     <t xml:space="preserve">17.2878189086914</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2955493927002</t>
+    <t xml:space="preserve">17.2955513000488</t>
   </si>
   <si>
     <t xml:space="preserve">17.3960609436035</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">16.8316555023193</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2800884246826</t>
+    <t xml:space="preserve">17.280086517334</t>
   </si>
   <si>
     <t xml:space="preserve">16.7002182006836</t>
@@ -983,7 +983,7 @@
     <t xml:space="preserve">16.2749805450439</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2285900115967</t>
+    <t xml:space="preserve">16.2285919189453</t>
   </si>
   <si>
     <t xml:space="preserve">16.0584964752197</t>
@@ -998,43 +998,43 @@
     <t xml:space="preserve">16.0352993011475</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2827129364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4141464233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6074390411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5919761657715</t>
+    <t xml:space="preserve">16.2827110290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4141502380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6074371337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5919723510742</t>
   </si>
   <si>
     <t xml:space="preserve">16.9321632385254</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0481395721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2646255493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9476261138916</t>
+    <t xml:space="preserve">17.0481376647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2646217346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9476299285889</t>
   </si>
   <si>
     <t xml:space="preserve">17.0713329315186</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0636005401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.079065322876</t>
+    <t xml:space="preserve">17.0636024475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0790634155273</t>
   </si>
   <si>
     <t xml:space="preserve">17.2723560333252</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3032817840576</t>
+    <t xml:space="preserve">17.3032836914062</t>
   </si>
   <si>
     <t xml:space="preserve">17.3728656768799</t>
@@ -1046,16 +1046,16 @@
     <t xml:space="preserve">17.5584239959717</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5893516540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4656429290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7207870483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5738887786865</t>
+    <t xml:space="preserve">17.5893497467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4656448364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7207832336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5738868713379</t>
   </si>
   <si>
     <t xml:space="preserve">17.5429611206055</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">18.1073665618896</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0377807617188</t>
+    <t xml:space="preserve">18.0377788543701</t>
   </si>
   <si>
     <t xml:space="preserve">17.6125450134277</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">17.5197639465332</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3110122680664</t>
+    <t xml:space="preserve">17.311014175415</t>
   </si>
   <si>
     <t xml:space="preserve">17.1099910736084</t>
@@ -1088,13 +1088,13 @@
     <t xml:space="preserve">17.3574028015137</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1795749664307</t>
+    <t xml:space="preserve">17.1795768737793</t>
   </si>
   <si>
     <t xml:space="preserve">17.1409168243408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0867958068848</t>
+    <t xml:space="preserve">17.0867977142334</t>
   </si>
   <si>
     <t xml:space="preserve">16.8857765197754</t>
@@ -1103,10 +1103,10 @@
     <t xml:space="preserve">16.6151695251465</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5301208496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3522930145264</t>
+    <t xml:space="preserve">16.530122756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3522968292236</t>
   </si>
   <si>
     <t xml:space="preserve">16.0430316925049</t>
@@ -1121,13 +1121,13 @@
     <t xml:space="preserve">16.1976661682129</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6692924499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8703117370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7852649688721</t>
+    <t xml:space="preserve">16.6692905426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8703136444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7852668762207</t>
   </si>
   <si>
     <t xml:space="preserve">16.9630928039551</t>
@@ -1136,7 +1136,7 @@
     <t xml:space="preserve">16.8084602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9244327545166</t>
+    <t xml:space="preserve">16.924430847168</t>
   </si>
   <si>
     <t xml:space="preserve">16.4218807220459</t>
@@ -1145,19 +1145,19 @@
     <t xml:space="preserve">16.0507659912109</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4605388641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.452808380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7543392181396</t>
+    <t xml:space="preserve">16.4605407714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4528064727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.754337310791</t>
   </si>
   <si>
     <t xml:space="preserve">16.6383647918701</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7929954528809</t>
+    <t xml:space="preserve">16.7929992675781</t>
   </si>
   <si>
     <t xml:space="preserve">16.4064159393311</t>
@@ -1166,40 +1166,40 @@
     <t xml:space="preserve">17.33420753479</t>
   </si>
   <si>
-    <t xml:space="preserve">17.38059425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4888381958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5506935119629</t>
+    <t xml:space="preserve">17.3805961608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4888401031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5506916046143</t>
   </si>
   <si>
     <t xml:space="preserve">17.6898574829102</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4115257263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6434707641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.256893157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2259654998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.504301071167</t>
+    <t xml:space="preserve">17.4115219116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6434688568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2568912506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2259635925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5042991638184</t>
   </si>
   <si>
     <t xml:space="preserve">16.4991970062256</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9785537719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3445625305176</t>
+    <t xml:space="preserve">16.9785556793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3445644378662</t>
   </si>
   <si>
     <t xml:space="preserve">16.2981758117676</t>
@@ -1220,100 +1220,100 @@
     <t xml:space="preserve">17.4269866943359</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4475574493408</t>
+    <t xml:space="preserve">18.4475555419922</t>
   </si>
   <si>
     <t xml:space="preserve">18.3857021331787</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8805236816406</t>
+    <t xml:space="preserve">18.8805198669434</t>
   </si>
   <si>
     <t xml:space="preserve">19.1433963775635</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0042304992676</t>
+    <t xml:space="preserve">19.0042285919189</t>
   </si>
   <si>
     <t xml:space="preserve">18.9114513397217</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6949672698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.679500579834</t>
+    <t xml:space="preserve">18.6949653625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6795024871826</t>
   </si>
   <si>
     <t xml:space="preserve">18.7413558959961</t>
   </si>
   <si>
-    <t xml:space="preserve">18.664041519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7877445220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2516403198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4371929168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3444175720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4062728881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5609016418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3289566040039</t>
+    <t xml:space="preserve">18.6640377044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7877426147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2516422271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.437198638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3444213867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.406270980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5609035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3289546966553</t>
   </si>
   <si>
     <t xml:space="preserve">19.1743221282959</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1124706268311</t>
+    <t xml:space="preserve">19.1124725341797</t>
   </si>
   <si>
     <t xml:space="preserve">19.1588611602783</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2825660705566</t>
+    <t xml:space="preserve">19.2825679779053</t>
   </si>
   <si>
     <t xml:space="preserve">19.236177444458</t>
   </si>
   <si>
-    <t xml:space="preserve">19.205249786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2671051025391</t>
+    <t xml:space="preserve">19.2052516937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2671031951904</t>
   </si>
   <si>
     <t xml:space="preserve">19.5299777984619</t>
   </si>
   <si>
-    <t xml:space="preserve">19.638219833374</t>
+    <t xml:space="preserve">19.6382160186768</t>
   </si>
   <si>
     <t xml:space="preserve">19.5918292999268</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4835872650146</t>
+    <t xml:space="preserve">19.4835891723633</t>
   </si>
   <si>
     <t xml:space="preserve">19.5145130157471</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4526615142822</t>
+    <t xml:space="preserve">19.4526596069336</t>
   </si>
   <si>
     <t xml:space="preserve">19.6072940826416</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1382904052734</t>
+    <t xml:space="preserve">18.1382923126221</t>
   </si>
   <si>
     <t xml:space="preserve">18.3547763824463</t>
@@ -1322,91 +1322,91 @@
     <t xml:space="preserve">18.0764389038086</t>
   </si>
   <si>
+    <t xml:space="preserve">18.03005027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1737766265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9501991271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3654174804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.205717086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6209392547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.509147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5890007019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5570583343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4931793212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1578102111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4292964935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6848163604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6369094848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4133262634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.461238861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3175067901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8064708709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8224411010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7106533050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9182605743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9661712646484</t>
+  </si>
+  <si>
     <t xml:space="preserve">18.0300483703613</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1737785339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9502010345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3654193878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2057189941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6209373474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.509147644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5889987945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.557056427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4931793212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1578102111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4292984008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6848163604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6369075775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4133262634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.461238861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3175086975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8064727783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8224411010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7106513977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9182624816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9661693572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.03005027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8863220214844</t>
+    <t xml:space="preserve">17.8863201141357</t>
   </si>
   <si>
     <t xml:space="preserve">17.9981117248535</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3973579406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5251197814941</t>
+    <t xml:space="preserve">18.3973598480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5251216888428</t>
   </si>
   <si>
     <t xml:space="preserve">18.4452667236328</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1479473114014</t>
+    <t xml:space="preserve">19.1479434967041</t>
   </si>
   <si>
     <t xml:space="preserve">19.1639156341553</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">18.5730285644531</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0680923461914</t>
+    <t xml:space="preserve">19.0680961608887</t>
   </si>
   <si>
     <t xml:space="preserve">18.7646675109863</t>
@@ -1433,22 +1433,22 @@
     <t xml:space="preserve">18.4772071838379</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7007884979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2437648773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4513740539551</t>
+    <t xml:space="preserve">18.7007865905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2437629699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4513759613037</t>
   </si>
   <si>
     <t xml:space="preserve">19.4992828369141</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2118263244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1319751739502</t>
+    <t xml:space="preserve">19.2118244171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1319732666016</t>
   </si>
   <si>
     <t xml:space="preserve">19.0042152404785</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">19.0361557006836</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1798858642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3236141204834</t>
+    <t xml:space="preserve">19.1798839569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.323616027832</t>
   </si>
   <si>
     <t xml:space="preserve">19.3395824432373</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">19.3076438903809</t>
   </si>
   <si>
-    <t xml:space="preserve">19.722864151001</t>
+    <t xml:space="preserve">19.7228660583496</t>
   </si>
   <si>
     <t xml:space="preserve">19.467342376709</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">19.5631637573242</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8825588226318</t>
+    <t xml:space="preserve">19.8825626373291</t>
   </si>
   <si>
     <t xml:space="preserve">20.3616600036621</t>
@@ -1502,34 +1502,34 @@
     <t xml:space="preserve">21.0962753295898</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8247852325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.249870300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4734477996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.154052734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1700191497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7548007965088</t>
+    <t xml:space="preserve">20.8247871398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2498722076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.473445892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1540508270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1700210571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7548027038574</t>
   </si>
   <si>
     <t xml:space="preserve">19.5312232971191</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4034652709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8125762939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7327289581299</t>
+    <t xml:space="preserve">19.4034614562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8125782012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7327270507812</t>
   </si>
   <si>
     <t xml:space="preserve">18.3813877105713</t>
@@ -1538,10 +1538,10 @@
     <t xml:space="preserve">18.2536296844482</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9342288970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3494491577148</t>
+    <t xml:space="preserve">17.9342308044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3494472503662</t>
   </si>
   <si>
     <t xml:space="preserve">18.9243679046631</t>
@@ -1550,22 +1550,22 @@
     <t xml:space="preserve">18.7486953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1258697509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7905025482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4391632080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1357326507568</t>
+    <t xml:space="preserve">18.1258716583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7905006408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4391651153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1357307434082</t>
   </si>
   <si>
     <t xml:space="preserve">17.2155838012695</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9760360717773</t>
+    <t xml:space="preserve">16.9760341644287</t>
   </si>
   <si>
     <t xml:space="preserve">17.550952911377</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">17.0718536376953</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9281253814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8323040008545</t>
+    <t xml:space="preserve">16.9281272888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8323059082031</t>
   </si>
   <si>
     <t xml:space="preserve">17.0558853149414</t>
@@ -1598,7 +1598,7 @@
     <t xml:space="preserve">16.3532085418701</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9859008789062</t>
+    <t xml:space="preserve">15.9858989715576</t>
   </si>
   <si>
     <t xml:space="preserve">16.0976905822754</t>
@@ -1607,37 +1607,37 @@
     <t xml:space="preserve">16.1136589050293</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4269504547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3311328887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6505317687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4748611450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4429206848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7703037261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.842170715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7383632659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4490261077881</t>
+    <t xml:space="preserve">15.4269514083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3311338424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6505289077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4748620986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4429235458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7703056335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8421688079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7383651733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4490280151367</t>
   </si>
   <si>
     <t xml:space="preserve">16.2733573913574</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1615715026855</t>
+    <t xml:space="preserve">16.1615695953369</t>
   </si>
   <si>
     <t xml:space="preserve">16.321268081665</t>
@@ -1646,52 +1646,52 @@
     <t xml:space="preserve">16.4809665679932</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6246967315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.768424987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1676750183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3433418273926</t>
+    <t xml:space="preserve">16.6246948242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7684268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1676731109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3433437347412</t>
   </si>
   <si>
     <t xml:space="preserve">17.2794628143311</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9440956115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0079746246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6406669616699</t>
+    <t xml:space="preserve">16.9440937042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0079727172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6406688690186</t>
   </si>
   <si>
     <t xml:space="preserve">16.241418838501</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5608139038086</t>
+    <t xml:space="preserve">16.5608158111572</t>
   </si>
   <si>
     <t xml:space="preserve">16.7045459747314</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8482761383057</t>
+    <t xml:space="preserve">16.848274230957</t>
   </si>
   <si>
     <t xml:space="preserve">17.3752822875977</t>
   </si>
   <si>
-    <t xml:space="preserve">17.103796005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8802165985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9121570587158</t>
+    <t xml:space="preserve">17.1037921905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8802146911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9121551513672</t>
   </si>
   <si>
     <t xml:space="preserve">16.8642463684082</t>
@@ -1706,19 +1706,19 @@
     <t xml:space="preserve">16.6087265014648</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7364845275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3052978515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8980646133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.193510055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2094764709473</t>
+    <t xml:space="preserve">16.7364864349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3052997589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8980665206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1935081481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2094783782959</t>
   </si>
   <si>
     <t xml:space="preserve">16.3851490020752</t>
@@ -1730,7 +1730,7 @@
     <t xml:space="preserve">16.2573890686035</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2254505157471</t>
+    <t xml:space="preserve">16.2254467010498</t>
   </si>
   <si>
     <t xml:space="preserve">15.9140357971191</t>
@@ -1739,28 +1739,28 @@
     <t xml:space="preserve">16.4170875549316</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5288772583008</t>
+    <t xml:space="preserve">16.5288791656494</t>
   </si>
   <si>
     <t xml:space="preserve">16.7843971252441</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5767860412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.369176864624</t>
+    <t xml:space="preserve">16.5767879486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3691787719727</t>
   </si>
   <si>
     <t xml:space="preserve">16.1775379180908</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4889526367188</t>
+    <t xml:space="preserve">16.4889507293701</t>
   </si>
   <si>
     <t xml:space="preserve">16.2494010925293</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3292541503906</t>
+    <t xml:space="preserve">16.3292560577393</t>
   </si>
   <si>
     <t xml:space="preserve">16.4091014862061</t>
@@ -1772,19 +1772,19 @@
     <t xml:space="preserve">16.0497779846191</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5688037872314</t>
+    <t xml:space="preserve">16.5688018798828</t>
   </si>
   <si>
     <t xml:space="preserve">16.6486511230469</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2874488830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0878257751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0478992462158</t>
+    <t xml:space="preserve">17.287446975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0878219604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0479011535645</t>
   </si>
   <si>
     <t xml:space="preserve">16.8083515167236</t>
@@ -1793,13 +1793,13 @@
     <t xml:space="preserve">16.9680500030518</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7285041809082</t>
+    <t xml:space="preserve">16.7285022735596</t>
   </si>
   <si>
     <t xml:space="preserve">16.8882007598877</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1277484893799</t>
+    <t xml:space="preserve">17.1277523040771</t>
   </si>
   <si>
     <t xml:space="preserve">16.8793506622314</t>
@@ -1811,22 +1811,22 @@
     <t xml:space="preserve">16.9208240509033</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7964057922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2111301422119</t>
+    <t xml:space="preserve">16.7964019775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2111320495605</t>
   </si>
   <si>
     <t xml:space="preserve">17.1281852722168</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1696605682373</t>
+    <t xml:space="preserve">17.1696586608887</t>
   </si>
   <si>
     <t xml:space="preserve">17.418493270874</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3770217895508</t>
+    <t xml:space="preserve">17.3770198822021</t>
   </si>
   <si>
     <t xml:space="preserve">17.4599666595459</t>
@@ -1850,22 +1850,22 @@
     <t xml:space="preserve">16.4895057678223</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5392742156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7088031768799</t>
+    <t xml:space="preserve">16.5392761230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7088012695312</t>
   </si>
   <si>
     <t xml:space="preserve">17.667329788208</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5014381408691</t>
+    <t xml:space="preserve">17.5014400482178</t>
   </si>
   <si>
     <t xml:space="preserve">17.5429096221924</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2526016235352</t>
+    <t xml:space="preserve">17.2526035308838</t>
   </si>
   <si>
     <t xml:space="preserve">16.7134590148926</t>
@@ -1880,10 +1880,10 @@
     <t xml:space="preserve">16.2406711578369</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1743144989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2738494873047</t>
+    <t xml:space="preserve">16.17431640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2738513946533</t>
   </si>
   <si>
     <t xml:space="preserve">16.124547958374</t>
@@ -1892,10 +1892,10 @@
     <t xml:space="preserve">16.3070278167725</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8591232299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7264089584351</t>
+    <t xml:space="preserve">15.8591241836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7264108657837</t>
   </si>
   <si>
     <t xml:space="preserve">15.7927675247192</t>
@@ -1904,19 +1904,19 @@
     <t xml:space="preserve">16.0747814178467</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5273418426514</t>
+    <t xml:space="preserve">15.5273427963257</t>
   </si>
   <si>
     <t xml:space="preserve">15.427809715271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6600532531738</t>
+    <t xml:space="preserve">15.6600542068481</t>
   </si>
   <si>
     <t xml:space="preserve">15.1789722442627</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3614540100098</t>
+    <t xml:space="preserve">15.3614530563354</t>
   </si>
   <si>
     <t xml:space="preserve">15.6932334899902</t>
@@ -1925,16 +1925,16 @@
     <t xml:space="preserve">15.6102886199951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4609842300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4443988800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3780431747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2950973510742</t>
+    <t xml:space="preserve">15.4609880447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4443998336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.378041267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2950983047485</t>
   </si>
   <si>
     <t xml:space="preserve">15.925479888916</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">16.4397392272949</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6719856262207</t>
+    <t xml:space="preserve">16.6719875335693</t>
   </si>
   <si>
     <t xml:space="preserve">17.9576377868652</t>
@@ -1958,61 +1958,61 @@
     <t xml:space="preserve">17.0867118835449</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3355464935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8378753662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5890426635742</t>
+    <t xml:space="preserve">17.3355484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8378734588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5890407562256</t>
   </si>
   <si>
     <t xml:space="preserve">16.2572612762451</t>
   </si>
   <si>
-    <t xml:space="preserve">15.87571144104</t>
+    <t xml:space="preserve">15.8757133483887</t>
   </si>
   <si>
     <t xml:space="preserve">15.9088916778564</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1577281951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1411361694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4729175567627</t>
+    <t xml:space="preserve">16.1577243804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1411380767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.47292137146</t>
   </si>
   <si>
     <t xml:space="preserve">15.7595891952515</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6766443252563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5936975479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4775772094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7429990768433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7098217010498</t>
+    <t xml:space="preserve">15.676643371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5936994552612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.477575302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7430009841919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7098226547241</t>
   </si>
   <si>
     <t xml:space="preserve">15.8425340652466</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3567943572998</t>
+    <t xml:space="preserve">16.3567924499512</t>
   </si>
   <si>
     <t xml:space="preserve">16.3236179351807</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9752464294434</t>
+    <t xml:space="preserve">15.975248336792</t>
   </si>
   <si>
     <t xml:space="preserve">17.5843849182129</t>
@@ -2024,13 +2024,13 @@
     <t xml:space="preserve">16.2240810394287</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0084247589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1909046173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5558624267578</t>
+    <t xml:space="preserve">16.0084266662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1909065246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5558605194092</t>
   </si>
   <si>
     <t xml:space="preserve">14.5320014953613</t>
@@ -2039,13 +2039,13 @@
     <t xml:space="preserve">14.7974252700806</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1836318969727</t>
+    <t xml:space="preserve">14.183629989624</t>
   </si>
   <si>
     <t xml:space="preserve">13.9347944259644</t>
   </si>
   <si>
-    <t xml:space="preserve">13.636191368103</t>
+    <t xml:space="preserve">13.6361923217773</t>
   </si>
   <si>
     <t xml:space="preserve">13.4371242523193</t>
@@ -2054,16 +2054,16 @@
     <t xml:space="preserve">13.2712335586548</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3873567581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7616300582886</t>
+    <t xml:space="preserve">13.3873558044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7616310119629</t>
   </si>
   <si>
     <t xml:space="preserve">11.9607000350952</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4251918792725</t>
+    <t xml:space="preserve">12.4251909255981</t>
   </si>
   <si>
     <t xml:space="preserve">11.0317125320435</t>
@@ -2072,19 +2072,19 @@
     <t xml:space="preserve">11.4796171188354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1690816879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3681516647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95342540740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3183832168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8777532577515</t>
+    <t xml:space="preserve">10.1690826416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3681507110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95342445373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3183822631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8777542114258</t>
   </si>
   <si>
     <t xml:space="preserve">12.441780090332</t>
@@ -2096,19 +2096,19 @@
     <t xml:space="preserve">12.1763563156128</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2924795150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2141923904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9155883789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6667537689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.202260017395</t>
+    <t xml:space="preserve">12.2924785614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2141933441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9155893325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6667547225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2022609710693</t>
   </si>
   <si>
     <t xml:space="preserve">10.4510955810547</t>
@@ -2120,13 +2120,13 @@
     <t xml:space="preserve">10.5340414047241</t>
   </si>
   <si>
-    <t xml:space="preserve">10.401328086853</t>
+    <t xml:space="preserve">10.4013290405273</t>
   </si>
   <si>
     <t xml:space="preserve">10.1524934768677</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0529594421387</t>
+    <t xml:space="preserve">10.0529584884644</t>
   </si>
   <si>
     <t xml:space="preserve">9.97001457214355</t>
@@ -2141,31 +2141,31 @@
     <t xml:space="preserve">10.301794052124</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0695476531982</t>
+    <t xml:space="preserve">10.0695486068726</t>
   </si>
   <si>
     <t xml:space="preserve">10.2520265579224</t>
   </si>
   <si>
-    <t xml:space="preserve">10.003191947937</t>
+    <t xml:space="preserve">10.0031929016113</t>
   </si>
   <si>
     <t xml:space="preserve">10.0363702774048</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1193151473999</t>
+    <t xml:space="preserve">10.1193141937256</t>
   </si>
   <si>
     <t xml:space="preserve">9.92024707794189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45575428009033</t>
+    <t xml:space="preserve">9.45575332641602</t>
   </si>
   <si>
     <t xml:space="preserve">9.50552082061768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32304191589355</t>
+    <t xml:space="preserve">9.32304096221924</t>
   </si>
   <si>
     <t xml:space="preserve">9.14056301116943</t>
@@ -2180,7 +2180,7 @@
     <t xml:space="preserve">10.1359043121338</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70458889007568</t>
+    <t xml:space="preserve">9.70458984375</t>
   </si>
   <si>
     <t xml:space="preserve">9.38939762115479</t>
@@ -2189,16 +2189,16 @@
     <t xml:space="preserve">10.4345073699951</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2188501358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4179191589355</t>
+    <t xml:space="preserve">10.2188491821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4179182052612</t>
   </si>
   <si>
     <t xml:space="preserve">10.9985342025757</t>
   </si>
   <si>
-    <t xml:space="preserve">10.899001121521</t>
+    <t xml:space="preserve">10.8990001678467</t>
   </si>
   <si>
     <t xml:space="preserve">10.9819450378418</t>
@@ -2207,13 +2207,13 @@
     <t xml:space="preserve">10.8160543441772</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8824100494385</t>
+    <t xml:space="preserve">10.8824110031128</t>
   </si>
   <si>
     <t xml:space="preserve">11.8113975524902</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7782182693481</t>
+    <t xml:space="preserve">11.7782192230225</t>
   </si>
   <si>
     <t xml:space="preserve">11.595739364624</t>
@@ -2222,13 +2222,13 @@
     <t xml:space="preserve">11.3634929656982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6833419799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.948766708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9653558731079</t>
+    <t xml:space="preserve">10.6833429336548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9487676620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9653568267822</t>
   </si>
   <si>
     <t xml:space="preserve">11.2639589309692</t>
@@ -2240,16 +2240,16 @@
     <t xml:space="preserve">11.1810150146484</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3303155899048</t>
+    <t xml:space="preserve">11.3303146362305</t>
   </si>
   <si>
     <t xml:space="preserve">11.297137260437</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0814800262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0151224136353</t>
+    <t xml:space="preserve">11.0814790725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0151233673096</t>
   </si>
   <si>
     <t xml:space="preserve">11.0648899078369</t>
@@ -2264,22 +2264,22 @@
     <t xml:space="preserve">10.5838088989258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3847398757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6501655578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3515615463257</t>
+    <t xml:space="preserve">10.3847389221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.650164604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3515605926514</t>
   </si>
   <si>
     <t xml:space="preserve">10.2354383468628</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9321784973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5506296157837</t>
+    <t xml:space="preserve">10.9321794509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.550630569458</t>
   </si>
   <si>
     <t xml:space="preserve">10.5008640289307</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">10.4842748641968</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0197811126709</t>
+    <t xml:space="preserve">10.0197801589966</t>
   </si>
   <si>
     <t xml:space="preserve">10.3349723815918</t>
@@ -2300,16 +2300,16 @@
     <t xml:space="preserve">10.7828769683838</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6003980636597</t>
+    <t xml:space="preserve">10.6003971099854</t>
   </si>
   <si>
     <t xml:space="preserve">11.1312465667725</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4132614135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4298486709595</t>
+    <t xml:space="preserve">11.4132604598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4298496246338</t>
   </si>
   <si>
     <t xml:space="preserve">11.2307815551758</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">11.396671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5127944946289</t>
+    <t xml:space="preserve">11.5127954483032</t>
   </si>
   <si>
     <t xml:space="preserve">11.8611650466919</t>
@@ -2333,7 +2333,7 @@
     <t xml:space="preserve">12.2095346450806</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9772872924805</t>
+    <t xml:space="preserve">11.9772891998291</t>
   </si>
   <si>
     <t xml:space="preserve">12.0602331161499</t>
@@ -2345,10 +2345,10 @@
     <t xml:space="preserve">11.3800830841064</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1146574020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6335763931274</t>
+    <t xml:space="preserve">11.1146564483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6335754394531</t>
   </si>
   <si>
     <t xml:space="preserve">10.2686166763306</t>
@@ -2357,31 +2357,31 @@
     <t xml:space="preserve">9.55528831481934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62164497375488</t>
+    <t xml:space="preserve">9.62164402008057</t>
   </si>
   <si>
     <t xml:space="preserve">9.65482234954834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.605055809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75435733795166</t>
+    <t xml:space="preserve">9.60505485534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75435638427734</t>
   </si>
   <si>
     <t xml:space="preserve">12.491548538208</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0058088302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1929454803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.839919090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3210010528564</t>
+    <t xml:space="preserve">13.0058097839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1929445266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8399181365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3210000991821</t>
   </si>
   <si>
     <t xml:space="preserve">12.4086027145386</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">12.9062747955322</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1053428649902</t>
+    <t xml:space="preserve">13.1053419113159</t>
   </si>
   <si>
     <t xml:space="preserve">12.9892196655273</t>
@@ -2405,10 +2405,10 @@
     <t xml:space="preserve">13.0721645355225</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0223960876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.088752746582</t>
+    <t xml:space="preserve">13.0223970413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0887537002563</t>
   </si>
   <si>
     <t xml:space="preserve">13.038987159729</t>
@@ -2423,16 +2423,16 @@
     <t xml:space="preserve">12.5081377029419</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7403831481934</t>
+    <t xml:space="preserve">12.7403841018677</t>
   </si>
   <si>
     <t xml:space="preserve">12.3754243850708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4749584197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6574392318726</t>
+    <t xml:space="preserve">12.4749593734741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6574382781982</t>
   </si>
   <si>
     <t xml:space="preserve">12.9560403823853</t>
@@ -2444,19 +2444,19 @@
     <t xml:space="preserve">13.536657333374</t>
   </si>
   <si>
-    <t xml:space="preserve">13.984561920166</t>
+    <t xml:space="preserve">13.9845628738403</t>
   </si>
   <si>
     <t xml:space="preserve">14.3661088943481</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5817680358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6978921890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7642478942871</t>
+    <t xml:space="preserve">14.5817699432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6978902816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7642459869385</t>
   </si>
   <si>
     <t xml:space="preserve">14.6315336227417</t>
@@ -2465,13 +2465,13 @@
     <t xml:space="preserve">14.1006851196289</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4324645996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7808361053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7476577758789</t>
+    <t xml:space="preserve">14.4324655532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7808351516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7476568222046</t>
   </si>
   <si>
     <t xml:space="preserve">14.4988212585449</t>
@@ -2480,103 +2480,103 @@
     <t xml:space="preserve">14.3495197296143</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2499876022339</t>
+    <t xml:space="preserve">14.2499866485596</t>
   </si>
   <si>
     <t xml:space="preserve">14.2333965301514</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7854928970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0177402496338</t>
+    <t xml:space="preserve">13.7854948043823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0177412033081</t>
   </si>
   <si>
     <t xml:space="preserve">14.0509195327759</t>
   </si>
   <si>
-    <t xml:space="preserve">14.283164024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0462598800659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9301376342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3946304321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3448648452759</t>
+    <t xml:space="preserve">14.2831649780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0462589263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.930136680603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3946313858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3448619842529</t>
   </si>
   <si>
     <t xml:space="preserve">15.9918365478516</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8969583511353</t>
+    <t xml:space="preserve">14.8969573974609</t>
   </si>
   <si>
     <t xml:space="preserve">14.9799041748047</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9135475158691</t>
+    <t xml:space="preserve">14.9135465621948</t>
   </si>
   <si>
     <t xml:space="preserve">14.9964933395386</t>
   </si>
   <si>
-    <t xml:space="preserve">15.825945854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6434679031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0250148773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0913696289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0581932067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5605211257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0130815505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2619171142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2287425994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1457939147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4941673278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.626877784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2121515274048</t>
+    <t xml:space="preserve">15.8259439468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6434659957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0250129699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0913677215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0581912994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5605220794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0130834579468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2619190216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.228741645813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1457948684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4941654205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6268768310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2121505737305</t>
   </si>
   <si>
     <t xml:space="preserve">15.502459526062</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2702131271362</t>
+    <t xml:space="preserve">15.2702121734619</t>
   </si>
   <si>
     <t xml:space="preserve">15.253623008728</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5439329147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5771102905273</t>
+    <t xml:space="preserve">15.5439319610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5771112442017</t>
   </si>
   <si>
     <t xml:space="preserve">15.8508291244507</t>
@@ -2585,7 +2585,7 @@
     <t xml:space="preserve">15.7181177139282</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7347040176392</t>
+    <t xml:space="preserve">15.7347059249878</t>
   </si>
   <si>
     <t xml:space="preserve">15.8840065002441</t>
@@ -2594,7 +2594,7 @@
     <t xml:space="preserve">15.7512941360474</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4361038208008</t>
+    <t xml:space="preserve">15.4361047744751</t>
   </si>
   <si>
     <t xml:space="preserve">16.3982677459717</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">15.8674192428589</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0830764770508</t>
+    <t xml:space="preserve">16.0830745697021</t>
   </si>
   <si>
     <t xml:space="preserve">16.1079597473145</t>
@@ -2624,31 +2624,31 @@
     <t xml:space="preserve">16.7051639556885</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9042339324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9374122619629</t>
+    <t xml:space="preserve">16.9042320251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9374103546143</t>
   </si>
   <si>
     <t xml:space="preserve">17.1364803314209</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3023719787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4350833892822</t>
+    <t xml:space="preserve">17.3023700714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4350814819336</t>
   </si>
   <si>
     <t xml:space="preserve">17.4516735076904</t>
   </si>
   <si>
-    <t xml:space="preserve">17.219425201416</t>
+    <t xml:space="preserve">17.2194271087646</t>
   </si>
   <si>
     <t xml:space="preserve">16.7217540740967</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1530704498291</t>
+    <t xml:space="preserve">17.1530685424805</t>
   </si>
   <si>
     <t xml:space="preserve">17.0535354614258</t>
@@ -2663,25 +2663,25 @@
     <t xml:space="preserve">16.7715187072754</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8544673919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2028350830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1033039093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1198921203613</t>
+    <t xml:space="preserve">16.8544654846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2028369903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1033020019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1198902130127</t>
   </si>
   <si>
     <t xml:space="preserve">16.7383422851562</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3521366119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.269193649292</t>
+    <t xml:space="preserve">17.3521385192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2691917419434</t>
   </si>
   <si>
     <t xml:space="preserve">16.8710556030273</t>
@@ -2690,49 +2690,49 @@
     <t xml:space="preserve">15.9171848297119</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2074966430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2323780059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6056308746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6958522796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1981773376465</t>
+    <t xml:space="preserve">16.2074947357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2323741912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6056327819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6958503723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1981792449951</t>
   </si>
   <si>
     <t xml:space="preserve">18.1649990081787</t>
   </si>
   <si>
-    <t xml:space="preserve">17.617561340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0820560455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6507396697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8000392913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4019050598145</t>
+    <t xml:space="preserve">17.6175632476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0820541381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6507415771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8000411987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4019031524658</t>
   </si>
   <si>
     <t xml:space="preserve">17.3189601898193</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0203590393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7881088256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9705905914307</t>
+    <t xml:space="preserve">17.020357131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7881107330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.970588684082</t>
   </si>
   <si>
     <t xml:space="preserve">17.1862468719482</t>
@@ -2741,25 +2741,25 @@
     <t xml:space="preserve">16.4065628051758</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4148578643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0498962402344</t>
+    <t xml:space="preserve">16.4148559570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.049898147583</t>
   </si>
   <si>
     <t xml:space="preserve">16.1660213470459</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5346183776855</t>
+    <t xml:space="preserve">17.5346164703369</t>
   </si>
   <si>
     <t xml:space="preserve">17.070125579834</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2360153198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6839199066162</t>
+    <t xml:space="preserve">17.2360134124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6839179992676</t>
   </si>
   <si>
     <t xml:space="preserve">17.4848499298096</t>
@@ -2774,22 +2774,22 @@
     <t xml:space="preserve">17.3437023162842</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5461559295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4111881256104</t>
+    <t xml:space="preserve">17.5461578369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4111862182617</t>
   </si>
   <si>
     <t xml:space="preserve">17.3774433135986</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6642589569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4449310302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4618034362793</t>
+    <t xml:space="preserve">17.6642570495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4449291229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4618015289307</t>
   </si>
   <si>
     <t xml:space="preserve">17.1749897003174</t>
@@ -2801,19 +2801,19 @@
     <t xml:space="preserve">17.0062770843506</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9556617736816</t>
+    <t xml:space="preserve">16.9556636810303</t>
   </si>
   <si>
     <t xml:space="preserve">16.8628711700439</t>
   </si>
   <si>
-    <t xml:space="preserve">17.090633392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8713073730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7532062530518</t>
+    <t xml:space="preserve">17.0906314849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8713054656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.753210067749</t>
   </si>
   <si>
     <t xml:space="preserve">17.2087326049805</t>
@@ -2822,52 +2822,52 @@
     <t xml:space="preserve">16.2048892974854</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0952262878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1458377838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7915410995483</t>
+    <t xml:space="preserve">16.0952243804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1458396911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7915420532227</t>
   </si>
   <si>
     <t xml:space="preserve">15.690315246582</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8590259552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4119396209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5215997695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0998191833496</t>
+    <t xml:space="preserve">15.8590278625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4119386672974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5216016769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0998182296753</t>
   </si>
   <si>
     <t xml:space="preserve">15.420373916626</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6059589385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5806512832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.833722114563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0446128845215</t>
+    <t xml:space="preserve">15.6059560775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5806503295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8337211608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0446109771729</t>
   </si>
   <si>
     <t xml:space="preserve">15.8758993148804</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8927707672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0108680725098</t>
+    <t xml:space="preserve">15.8927698135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0108699798584</t>
   </si>
   <si>
     <t xml:space="preserve">15.934947013855</t>
@@ -2882,10 +2882,10 @@
     <t xml:space="preserve">15.5131645202637</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4878606796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.184175491333</t>
+    <t xml:space="preserve">15.4878597259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1841745376587</t>
   </si>
   <si>
     <t xml:space="preserve">15.2347888946533</t>
@@ -2894,34 +2894,34 @@
     <t xml:space="preserve">15.3950662612915</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9433841705322</t>
+    <t xml:space="preserve">15.9433832168579</t>
   </si>
   <si>
     <t xml:space="preserve">16.112096786499</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2976818084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4495220184326</t>
+    <t xml:space="preserve">16.297679901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4495239257812</t>
   </si>
   <si>
     <t xml:space="preserve">15.5890865325928</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6987504959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0361766815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9686918258667</t>
+    <t xml:space="preserve">15.698751449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0361747741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9686908721924</t>
   </si>
   <si>
     <t xml:space="preserve">16.3145542144775</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9180765151978</t>
+    <t xml:space="preserve">15.9180774688721</t>
   </si>
   <si>
     <t xml:space="preserve">16.0193042755127</t>
@@ -2930,67 +2930,67 @@
     <t xml:space="preserve">15.5384721755981</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0154628753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1504316329956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5300369262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8168506622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5637807846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8843355178833</t>
+    <t xml:space="preserve">15.0154609680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1504306793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5300359725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8168497085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5637817382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8843336105347</t>
   </si>
   <si>
     <t xml:space="preserve">16.1374053955078</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8674621582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4541168212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9732847213745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0238981246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1673030853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4372434616089</t>
+    <t xml:space="preserve">15.8674631118774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4541158676147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9732856750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0238962173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1673021316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4372444152832</t>
   </si>
   <si>
     <t xml:space="preserve">15.6312656402588</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4794235229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1588678359985</t>
+    <t xml:space="preserve">15.4794225692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1588668823242</t>
   </si>
   <si>
     <t xml:space="preserve">14.7623929977417</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4080944061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7416791915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0537977218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1212825775146</t>
+    <t xml:space="preserve">14.4080934524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7416801452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0537986755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.121283531189</t>
   </si>
   <si>
     <t xml:space="preserve">13.4295587539673</t>
@@ -3017,7 +3017,7 @@
     <t xml:space="preserve">13.1258764266968</t>
   </si>
   <si>
-    <t xml:space="preserve">13.513916015625</t>
+    <t xml:space="preserve">13.5139169692993</t>
   </si>
   <si>
     <t xml:space="preserve">13.9188270568848</t>
@@ -3029,16 +3029,16 @@
     <t xml:space="preserve">13.5307874679565</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8728065490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9318552017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7631435394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6366081237793</t>
+    <t xml:space="preserve">12.8728055953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9318561553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7631425857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.636607170105</t>
   </si>
   <si>
     <t xml:space="preserve">12.4172811508179</t>
@@ -3047,7 +3047,7 @@
     <t xml:space="preserve">12.484766960144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6872215270996</t>
+    <t xml:space="preserve">12.6872224807739</t>
   </si>
   <si>
     <t xml:space="preserve">12.6619157791138</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">12.2823104858398</t>
   </si>
   <si>
-    <t xml:space="preserve">12.349796295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3666667938232</t>
+    <t xml:space="preserve">12.3497953414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3666658401489</t>
   </si>
   <si>
     <t xml:space="preserve">12.5859937667847</t>
@@ -3077,22 +3077,22 @@
     <t xml:space="preserve">13.4126873016357</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3958168029785</t>
+    <t xml:space="preserve">13.3958158493042</t>
   </si>
   <si>
     <t xml:space="preserve">13.4464302062988</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7838563919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3114595413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2271041870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9571619033813</t>
+    <t xml:space="preserve">13.7838573455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3114604949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.227105140686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9571628570557</t>
   </si>
   <si>
     <t xml:space="preserve">13.0752620697021</t>
@@ -3101,13 +3101,13 @@
     <t xml:space="preserve">12.7040939331055</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7715797424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4004096984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2148246765137</t>
+    <t xml:space="preserve">12.7715787887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.400408744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.214825630188</t>
   </si>
   <si>
     <t xml:space="preserve">12.0461120605469</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">11.8773994445801</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1473398208618</t>
+    <t xml:space="preserve">12.1473407745361</t>
   </si>
   <si>
     <t xml:space="preserve">12.1642122268677</t>
@@ -3125,13 +3125,13 @@
     <t xml:space="preserve">12.2316961288452</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4510231018066</t>
+    <t xml:space="preserve">12.451024055481</t>
   </si>
   <si>
     <t xml:space="preserve">12.3835382461548</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2991819381714</t>
+    <t xml:space="preserve">12.2991809844971</t>
   </si>
   <si>
     <t xml:space="preserve">11.8267850875854</t>
@@ -3140,19 +3140,19 @@
     <t xml:space="preserve">11.6749439239502</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6487464904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4741039276123</t>
+    <t xml:space="preserve">11.6487474441528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.474102973938</t>
   </si>
   <si>
     <t xml:space="preserve">11.3693170547485</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8932476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9107131958008</t>
+    <t xml:space="preserve">11.8932485580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9107122421265</t>
   </si>
   <si>
     <t xml:space="preserve">12.4346437454224</t>
@@ -3161,7 +3161,7 @@
     <t xml:space="preserve">12.102819442749</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0154991149902</t>
+    <t xml:space="preserve">12.0154981613159</t>
   </si>
   <si>
     <t xml:space="preserve">11.9805698394775</t>
@@ -3170,16 +3170,16 @@
     <t xml:space="preserve">12.1901426315308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3298578262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5568952560425</t>
+    <t xml:space="preserve">12.3298568725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5568943023682</t>
   </si>
   <si>
     <t xml:space="preserve">12.3123931884766</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5963525772095</t>
+    <t xml:space="preserve">11.5963535308838</t>
   </si>
   <si>
     <t xml:space="preserve">11.4391746520996</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">11.7186040878296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5788888931274</t>
+    <t xml:space="preserve">11.5788898468018</t>
   </si>
   <si>
     <t xml:space="preserve">11.8408555984497</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">11.9631052017212</t>
   </si>
   <si>
-    <t xml:space="preserve">11.753532409668</t>
+    <t xml:space="preserve">11.7535333633423</t>
   </si>
   <si>
     <t xml:space="preserve">11.49156665802</t>
@@ -3215,46 +3215,46 @@
     <t xml:space="preserve">11.2645301818848</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8104553222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0549583435059</t>
+    <t xml:space="preserve">10.8104562759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0549573898315</t>
   </si>
   <si>
     <t xml:space="preserve">11.1772079467773</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3867797851562</t>
+    <t xml:space="preserve">11.3867807388306</t>
   </si>
   <si>
     <t xml:space="preserve">11.2470655441284</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0374927520752</t>
+    <t xml:space="preserve">11.0374937057495</t>
   </si>
   <si>
     <t xml:space="preserve">10.8453845977783</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3343877792358</t>
+    <t xml:space="preserve">11.3343868255615</t>
   </si>
   <si>
     <t xml:space="preserve">11.3169231414795</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4042463302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2296009063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6138172149658</t>
+    <t xml:space="preserve">11.4042453765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2296018600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6138191223145</t>
   </si>
   <si>
     <t xml:space="preserve">11.7884616851807</t>
   </si>
   <si>
-    <t xml:space="preserve">11.823390007019</t>
+    <t xml:space="preserve">11.8233909606934</t>
   </si>
   <si>
     <t xml:space="preserve">11.8059272766113</t>
@@ -3263,13 +3263,13 @@
     <t xml:space="preserve">11.5614242553711</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4566373825073</t>
+    <t xml:space="preserve">11.456639289856</t>
   </si>
   <si>
     <t xml:space="preserve">11.5439605712891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4217090606689</t>
+    <t xml:space="preserve">11.4217100143433</t>
   </si>
   <si>
     <t xml:space="preserve">11.1073503494263</t>
@@ -3278,28 +3278,28 @@
     <t xml:space="preserve">11.0898857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7231340408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6882057189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6707401275635</t>
+    <t xml:space="preserve">10.7231330871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6882047653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6707410812378</t>
   </si>
   <si>
     <t xml:space="preserve">10.5135612487793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2865238189697</t>
+    <t xml:space="preserve">10.286524772644</t>
   </si>
   <si>
     <t xml:space="preserve">10.2341318130493</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0594873428345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1468086242676</t>
+    <t xml:space="preserve">10.0594882965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1468095779419</t>
   </si>
   <si>
     <t xml:space="preserve">9.78005695343018</t>
@@ -3308,13 +3308,13 @@
     <t xml:space="preserve">9.90230846405029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81498527526855</t>
+    <t xml:space="preserve">9.81498622894287</t>
   </si>
   <si>
     <t xml:space="preserve">9.76259326934814</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98962879180908</t>
+    <t xml:space="preserve">9.9896297454834</t>
   </si>
   <si>
     <t xml:space="preserve">10.1992034912109</t>
@@ -3323,46 +3323,46 @@
     <t xml:space="preserve">9.29105472564697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51809215545654</t>
+    <t xml:space="preserve">9.51809120178223</t>
   </si>
   <si>
     <t xml:space="preserve">9.2211971282959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25612640380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06401634216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80205154418945</t>
+    <t xml:space="preserve">9.25612545013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0640172958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80205059051514</t>
   </si>
   <si>
     <t xml:space="preserve">8.8195161819458</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60121154785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48769187927246</t>
+    <t xml:space="preserve">8.60121250152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48769283294678</t>
   </si>
   <si>
     <t xml:space="preserve">8.19079780578613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44403171539307</t>
+    <t xml:space="preserve">8.44403266906738</t>
   </si>
   <si>
     <t xml:space="preserve">8.4614953994751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3392448425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56628227233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34797668457031</t>
+    <t xml:space="preserve">8.33924579620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56628322601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34797859191895</t>
   </si>
   <si>
     <t xml:space="preserve">8.54881763458252</t>
@@ -3380,28 +3380,28 @@
     <t xml:space="preserve">9.04655265808105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01162433624268</t>
+    <t xml:space="preserve">9.01162338256836</t>
   </si>
   <si>
     <t xml:space="preserve">8.83697986602783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7321949005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02908897399902</t>
+    <t xml:space="preserve">8.73219394683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02908802032471</t>
   </si>
   <si>
     <t xml:space="preserve">9.09894561767578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41330528259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30851936340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27358913421631</t>
+    <t xml:space="preserve">9.41330432891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.308518409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27359008789062</t>
   </si>
   <si>
     <t xml:space="preserve">9.39584064483643</t>
@@ -3410,19 +3410,19 @@
     <t xml:space="preserve">9.72766399383545</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55302047729492</t>
+    <t xml:space="preserve">9.55301952362061</t>
   </si>
   <si>
     <t xml:space="preserve">9.622878074646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91977119445801</t>
+    <t xml:space="preserve">9.91977214813232</t>
   </si>
   <si>
     <t xml:space="preserve">10.269061088562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65780639648438</t>
+    <t xml:space="preserve">9.65780735015869</t>
   </si>
   <si>
     <t xml:space="preserve">9.64034175872803</t>
@@ -3446,16 +3446,16 @@
     <t xml:space="preserve">9.97216606140137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88484287261963</t>
+    <t xml:space="preserve">9.88484382629395</t>
   </si>
   <si>
     <t xml:space="preserve">9.8673791885376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0944156646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0769510269165</t>
+    <t xml:space="preserve">10.0944166183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0769519805908</t>
   </si>
   <si>
     <t xml:space="preserve">9.79752159118652</t>
@@ -3476,19 +3476,19 @@
     <t xml:space="preserve">10.6358118057251</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7405977249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7580633163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9152431488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0200290679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3518514633179</t>
+    <t xml:space="preserve">10.7405986785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7580623626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9152421951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0200281143188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3518524169922</t>
   </si>
   <si>
     <t xml:space="preserve">11.0025644302368</t>
@@ -3500,31 +3500,31 @@
     <t xml:space="preserve">10.5310258865356</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6183481216431</t>
+    <t xml:space="preserve">10.6183471679688</t>
   </si>
   <si>
     <t xml:space="preserve">10.7056694030762</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6008825302124</t>
+    <t xml:space="preserve">10.6008834838867</t>
   </si>
   <si>
     <t xml:space="preserve">10.565954208374</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4786329269409</t>
+    <t xml:space="preserve">10.4786319732666</t>
   </si>
   <si>
     <t xml:space="preserve">10.1817378997803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2166662216187</t>
+    <t xml:space="preserve">10.216667175293</t>
   </si>
   <si>
     <t xml:space="preserve">10.0245580673218</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84991359710693</t>
+    <t xml:space="preserve">9.84991455078125</t>
   </si>
   <si>
     <t xml:space="preserve">10.1118803024292</t>
@@ -3536,13 +3536,13 @@
     <t xml:space="preserve">10.3563814163208</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5264949798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9456415176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7011404037476</t>
+    <t xml:space="preserve">11.5264959335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9456405639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7011394500732</t>
   </si>
   <si>
     <t xml:space="preserve">12.1202850341797</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">11.8757839202881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.067892074585</t>
+    <t xml:space="preserve">12.0678911209106</t>
   </si>
   <si>
     <t xml:space="preserve">12.0329627990723</t>
@@ -3572,13 +3572,13 @@
     <t xml:space="preserve">13.063362121582</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8712539672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6442165374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9491119384766</t>
+    <t xml:space="preserve">12.8712530136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6442155838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9491128921509</t>
   </si>
   <si>
     <t xml:space="preserve">13.0746583938599</t>
@@ -3587,13 +3587,13 @@
     <t xml:space="preserve">12.9132423400879</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0387878417969</t>
+    <t xml:space="preserve">13.0387887954712</t>
   </si>
   <si>
     <t xml:space="preserve">13.0567235946655</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1284637451172</t>
+    <t xml:space="preserve">13.1284627914429</t>
   </si>
   <si>
     <t xml:space="preserve">13.2540082931519</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">13.5947751998901</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4871635437012</t>
+    <t xml:space="preserve">13.4871644973755</t>
   </si>
   <si>
     <t xml:space="preserve">13.4512939453125</t>
@@ -3623,7 +3623,7 @@
     <t xml:space="preserve">13.5051002502441</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2002038955688</t>
+    <t xml:space="preserve">13.2002029418945</t>
   </si>
   <si>
     <t xml:space="preserve">12.9849824905396</t>
@@ -3656,7 +3656,7 @@
     <t xml:space="preserve">12.5366058349609</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4110612869263</t>
+    <t xml:space="preserve">12.411060333252</t>
   </si>
   <si>
     <t xml:space="preserve">12.2496452331543</t>
@@ -3683,7 +3683,7 @@
     <t xml:space="preserve">12.285514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2675809860229</t>
+    <t xml:space="preserve">12.2675800323486</t>
   </si>
   <si>
     <t xml:space="preserve">12.6262817382812</t>
@@ -3695,7 +3695,7 @@
     <t xml:space="preserve">12.5724763870239</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2137746810913</t>
+    <t xml:space="preserve">12.2137756347656</t>
   </si>
   <si>
     <t xml:space="preserve">12.5007352828979</t>
@@ -3707,10 +3707,10 @@
     <t xml:space="preserve">11.2990875244141</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5681133270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.639853477478</t>
+    <t xml:space="preserve">11.5681123733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6398525238037</t>
   </si>
   <si>
     <t xml:space="preserve">11.675724029541</t>
@@ -3722,22 +3722,22 @@
     <t xml:space="preserve">11.6577882766724</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4605026245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3708276748657</t>
+    <t xml:space="preserve">11.4605016708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.37082862854</t>
   </si>
   <si>
     <t xml:space="preserve">11.3528928756714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3349571228027</t>
+    <t xml:space="preserve">11.3349580764771</t>
   </si>
   <si>
     <t xml:space="preserve">11.2811527252197</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4963731765747</t>
+    <t xml:space="preserve">11.4963722229004</t>
   </si>
   <si>
     <t xml:space="preserve">11.5501775741577</t>
@@ -3752,16 +3752,16 @@
     <t xml:space="preserve">11.8012685775757</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7833347320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.908878326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9268140792847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.016489982605</t>
+    <t xml:space="preserve">11.7833337783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9088792800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.926815032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0164890289307</t>
   </si>
   <si>
     <t xml:space="preserve">12.0882301330566</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">10.5278797149658</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7610359191895</t>
+    <t xml:space="preserve">10.7610349655151</t>
   </si>
   <si>
     <t xml:space="preserve">10.5816850662231</t>
@@ -3815,7 +3815,7 @@
     <t xml:space="preserve">10.2947235107422</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3664636611938</t>
+    <t xml:space="preserve">10.3664646148682</t>
   </si>
   <si>
     <t xml:space="preserve">10.2229833602905</t>
@@ -3836,19 +3836,19 @@
     <t xml:space="preserve">9.86428260803223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68493175506592</t>
+    <t xml:space="preserve">9.68493270874023</t>
   </si>
   <si>
     <t xml:space="preserve">9.75667190551758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77460765838623</t>
+    <t xml:space="preserve">9.77460670471191</t>
   </si>
   <si>
     <t xml:space="preserve">9.70286750793457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79254245758057</t>
+    <t xml:space="preserve">9.79254150390625</t>
   </si>
   <si>
     <t xml:space="preserve">9.66699695587158</t>
@@ -3863,7 +3863,7 @@
     <t xml:space="preserve">10.0436325073242</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1871128082275</t>
+    <t xml:space="preserve">10.1871137619019</t>
   </si>
   <si>
     <t xml:space="preserve">10.5099449157715</t>
@@ -3872,7 +3872,7 @@
     <t xml:space="preserve">10.7431001663208</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8148403167725</t>
+    <t xml:space="preserve">10.8148412704468</t>
   </si>
   <si>
     <t xml:space="preserve">10.4740753173828</t>
@@ -3884,7 +3884,7 @@
     <t xml:space="preserve">9.9001522064209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95395851135254</t>
+    <t xml:space="preserve">9.95395755767822</t>
   </si>
   <si>
     <t xml:space="preserve">10.0795030593872</t>
@@ -3896,7 +3896,7 @@
     <t xml:space="preserve">9.98982810974121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2588529586792</t>
+    <t xml:space="preserve">10.2588539123535</t>
   </si>
   <si>
     <t xml:space="preserve">10.3126592636108</t>
@@ -3908,7 +3908,7 @@
     <t xml:space="preserve">10.4561395645142</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3305940628052</t>
+    <t xml:space="preserve">10.3305950164795</t>
   </si>
   <si>
     <t xml:space="preserve">10.2050485610962</t>
@@ -3923,7 +3923,7 @@
     <t xml:space="preserve">9.91808795928955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88221836090088</t>
+    <t xml:space="preserve">9.88221740722656</t>
   </si>
   <si>
     <t xml:space="preserve">10.0974388122559</t>
@@ -3944,31 +3944,31 @@
     <t xml:space="preserve">9.3262300491333</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45177555084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5996198654175</t>
+    <t xml:space="preserve">9.4517765045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5996189117432</t>
   </si>
   <si>
     <t xml:space="preserve">9.93602275848389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4920091629028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5637493133545</t>
+    <t xml:space="preserve">10.4920101165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5637502670288</t>
   </si>
   <si>
     <t xml:space="preserve">10.4382047653198</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6713600158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9045162200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8327760696411</t>
+    <t xml:space="preserve">10.6713590621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9045152664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8327751159668</t>
   </si>
   <si>
     <t xml:space="preserve">10.7251653671265</t>
@@ -3983,7 +3983,7 @@
     <t xml:space="preserve">10.9224510192871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6892957687378</t>
+    <t xml:space="preserve">10.6892948150635</t>
   </si>
   <si>
     <t xml:space="preserve">11.2094125747681</t>
@@ -69640,7 +69640,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6493981481</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>117264</v>
@@ -69661,6 +69661,32 @@
         <v>1533</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6494675926</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>109691</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>9.59000015258789</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>9.43000030517578</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>9.47999954223633</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>9.47000026702881</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>1475</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARR.MI.xlsx
+++ b/data/MARR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="1532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="1533">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,67 +38,67 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4479503631592</t>
+    <t xml:space="preserve">13.4479522705078</t>
   </si>
   <si>
     <t xml:space="preserve">MARR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2894020080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1812992095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9939203262329</t>
+    <t xml:space="preserve">13.2894010543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1812982559204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9939212799072</t>
   </si>
   <si>
     <t xml:space="preserve">12.9506797790527</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5903377532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6551990509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7344722747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4389953613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4462013244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9849643707275</t>
+    <t xml:space="preserve">12.5903387069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.655198097229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7344741821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4389944076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4462003707886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9849634170532</t>
   </si>
   <si>
     <t xml:space="preserve">12.0858602523804</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6462421417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2155828475952</t>
+    <t xml:space="preserve">11.6462430953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2155818939209</t>
   </si>
   <si>
     <t xml:space="preserve">12.8353681564331</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6768178939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5615091323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5543041229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6407852172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7200613021851</t>
+    <t xml:space="preserve">12.6768188476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5615119934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5543031692505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6407861709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7200603485107</t>
   </si>
   <si>
     <t xml:space="preserve">12.97230052948</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">12.7777147293091</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3308916091919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5110626220703</t>
+    <t xml:space="preserve">12.3308935165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5110635757446</t>
   </si>
   <si>
     <t xml:space="preserve">12.2948570251465</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">11.4084167480469</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4516582489014</t>
+    <t xml:space="preserve">11.4516592025757</t>
   </si>
   <si>
     <t xml:space="preserve">11.8840675354004</t>
@@ -128,40 +128,40 @@
     <t xml:space="preserve">11.5885877609253</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8912754058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9273080825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0426177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2011690139771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3957557678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7056474685669</t>
+    <t xml:space="preserve">11.8912744522095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9273099899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0426168441772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2011671066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3957538604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7056465148926</t>
   </si>
   <si>
     <t xml:space="preserve">12.6047506332397</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5759239196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9362678527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1596784591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.943470954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0731973648071</t>
+    <t xml:space="preserve">12.5759248733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9362668991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1596755981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9434719085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0731954574585</t>
   </si>
   <si>
     <t xml:space="preserve">12.885817527771</t>
@@ -173,55 +173,55 @@
     <t xml:space="preserve">12.078652381897</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3597202301025</t>
+    <t xml:space="preserve">12.3597183227539</t>
   </si>
   <si>
     <t xml:space="preserve">12.6696128845215</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8137493133545</t>
+    <t xml:space="preserve">12.8137502670288</t>
   </si>
   <si>
     <t xml:space="preserve">12.6984395980835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8714036941528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.453408241272</t>
+    <t xml:space="preserve">12.8714046478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4534091949463</t>
   </si>
   <si>
     <t xml:space="preserve">12.3453044891357</t>
   </si>
   <si>
-    <t xml:space="preserve">12.684027671814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7560949325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1524705886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2677803039551</t>
+    <t xml:space="preserve">12.684024810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7560939788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1524715423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2677793502808</t>
   </si>
   <si>
     <t xml:space="preserve">13.3326416015625</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0804023742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1885042190552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2605714797974</t>
+    <t xml:space="preserve">13.0804014205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1885032653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2605724334717</t>
   </si>
   <si>
     <t xml:space="preserve">13.7073974609375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4911937713623</t>
+    <t xml:space="preserve">13.4911918640137</t>
   </si>
   <si>
     <t xml:space="preserve">13.3470544815063</t>
@@ -233,13 +233,13 @@
     <t xml:space="preserve">12.9002323150635</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8281631469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7921276092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.058780670166</t>
+    <t xml:space="preserve">12.828161239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7921285629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0587816238403</t>
   </si>
   <si>
     <t xml:space="preserve">13.1020231246948</t>
@@ -248,37 +248,37 @@
     <t xml:space="preserve">12.8065423965454</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2821922302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1380577087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8425769805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8930234909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9074363708496</t>
+    <t xml:space="preserve">13.2821931838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1380558013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8425760269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8930263519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9074382781982</t>
   </si>
   <si>
     <t xml:space="preserve">13.0227479934692</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6624069213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8786115646362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6335792541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7488889694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0258741378784</t>
+    <t xml:space="preserve">12.6624059677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8786106109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6335783004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7488880157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0258750915527</t>
   </si>
   <si>
     <t xml:space="preserve">13.0183897018433</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">13.25794506073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2504596710205</t>
+    <t xml:space="preserve">13.2504587173462</t>
   </si>
   <si>
     <t xml:space="preserve">13.4301261901855</t>
@@ -296,31 +296,31 @@
     <t xml:space="preserve">13.4825296401978</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3103475570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2654285430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.475043296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3702383041382</t>
+    <t xml:space="preserve">13.3103494644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2654304504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4750442504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3702363967896</t>
   </si>
   <si>
     <t xml:space="preserve">13.2878894805908</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2729187011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.280403137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.801290512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8836364746094</t>
+    <t xml:space="preserve">13.2729167938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2804021835327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8012914657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8836374282837</t>
   </si>
   <si>
     <t xml:space="preserve">12.6141386032104</t>
@@ -332,49 +332,49 @@
     <t xml:space="preserve">12.4494428634644</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8087778091431</t>
+    <t xml:space="preserve">12.8087797164917</t>
   </si>
   <si>
     <t xml:space="preserve">12.7938060760498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0782775878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4419574737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7831764221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2847461700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7339162826538</t>
+    <t xml:space="preserve">13.0782785415649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4419565200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7831773757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2847480773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7339181900024</t>
   </si>
   <si>
     <t xml:space="preserve">13.4226417541504</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5274457931519</t>
+    <t xml:space="preserve">13.5274467468262</t>
   </si>
   <si>
     <t xml:space="preserve">13.0558204650879</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4525833129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3328056335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7595157623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7295713424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7220878601074</t>
+    <t xml:space="preserve">13.4525852203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3328046798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7595167160034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7295732498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7220869064331</t>
   </si>
   <si>
     <t xml:space="preserve">13.5349321365356</t>
@@ -395,109 +395,109 @@
     <t xml:space="preserve">13.8493499755859</t>
   </si>
   <si>
-    <t xml:space="preserve">14.111364364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9766139984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0814189910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7445440292358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9990730285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5049896240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6397361755371</t>
+    <t xml:space="preserve">14.1113662719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9766149520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0814208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7445459365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9990749359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5049886703491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6397380828857</t>
   </si>
   <si>
     <t xml:space="preserve">13.6621971130371</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6097936630249</t>
+    <t xml:space="preserve">13.6097955703735</t>
   </si>
   <si>
     <t xml:space="preserve">13.3477783203125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4151554107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.220516204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0857648849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.100736618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0633058547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2354860305786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1456518173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9285554885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2055406570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1082229614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.198055267334</t>
+    <t xml:space="preserve">13.4151544570923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2205142974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0857629776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1007375717163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.063307762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2354879379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1456527709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9285545349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2055425643921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1082220077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1980543136597</t>
   </si>
   <si>
     <t xml:space="preserve">13.1157093048096</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0109024047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9135847091675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8611793518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.943528175354</t>
+    <t xml:space="preserve">13.0109014511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9135837554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8611822128296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9435291290283</t>
   </si>
   <si>
     <t xml:space="preserve">13.1905698776245</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4076662063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3552665710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2130298614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3402938842773</t>
+    <t xml:space="preserve">13.4076681137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.355263710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2130279541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3402919769287</t>
   </si>
   <si>
     <t xml:space="preserve">12.9659862518311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8761539459229</t>
+    <t xml:space="preserve">12.8761529922485</t>
   </si>
   <si>
     <t xml:space="preserve">12.8312349319458</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9809608459473</t>
+    <t xml:space="preserve">12.9809589385986</t>
   </si>
   <si>
     <t xml:space="preserve">12.7638597488403</t>
@@ -509,79 +509,79 @@
     <t xml:space="preserve">12.8686656951904</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7563762664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6815118789673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5767049789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5467615127563</t>
+    <t xml:space="preserve">12.7563772201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6815137863159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5767087936401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5467643737793</t>
   </si>
   <si>
     <t xml:space="preserve">12.5317907333374</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5617341995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5542497634888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4194984436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2772617340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.47190284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5018472671509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3970394134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9778156280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3596096038818</t>
+    <t xml:space="preserve">12.5617361068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5542507171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4194974899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2772598266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4719018936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5018463134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3970384597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9778175354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3596086502075</t>
   </si>
   <si>
     <t xml:space="preserve">12.4943599700928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3820686340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4045257568359</t>
+    <t xml:space="preserve">12.3820667266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4045238494873</t>
   </si>
   <si>
     <t xml:space="preserve">12.269775390625</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1649703979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2548036575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3371505737305</t>
+    <t xml:space="preserve">12.1649694442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2548046112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3371515274048</t>
   </si>
   <si>
     <t xml:space="preserve">12.3221778869629</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7264289855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6740293502808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7863187789917</t>
+    <t xml:space="preserve">12.72642993927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6740264892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.786319732666</t>
   </si>
   <si>
     <t xml:space="preserve">13.0932493209839</t>
@@ -590,49 +590,49 @@
     <t xml:space="preserve">12.9510145187378</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1306800842285</t>
+    <t xml:space="preserve">13.1306819915771</t>
   </si>
   <si>
     <t xml:space="preserve">12.9884452819824</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1381664276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1606245040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.183084487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1681118011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2280006408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0034170150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1755981445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.400182723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3852109909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8643236160278</t>
+    <t xml:space="preserve">13.138165473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1606254577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1830854415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1681108474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2279996871948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.00341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1755962371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4001817703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3852081298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8643226623535</t>
   </si>
   <si>
     <t xml:space="preserve">13.9167251586914</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5199613571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4450998306274</t>
+    <t xml:space="preserve">13.5199604034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4450988769531</t>
   </si>
   <si>
     <t xml:space="preserve">13.3627519607544</t>
@@ -641,19 +641,19 @@
     <t xml:space="preserve">13.4600706100464</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5124731063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4376125335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8268928527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6247663497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8044328689575</t>
+    <t xml:space="preserve">13.51247215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4376134872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8268909454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6247673034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8044338226318</t>
   </si>
   <si>
     <t xml:space="preserve">13.7819747924805</t>
@@ -662,40 +662,40 @@
     <t xml:space="preserve">13.6996250152588</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8418645858765</t>
+    <t xml:space="preserve">13.8418626785278</t>
   </si>
   <si>
     <t xml:space="preserve">13.6771697998047</t>
   </si>
   <si>
-    <t xml:space="preserve">13.856837272644</t>
+    <t xml:space="preserve">13.8568353652954</t>
   </si>
   <si>
     <t xml:space="preserve">13.7670021057129</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5648794174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8942670822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3359489440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5605335235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5156145095825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6952829360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9722700119019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9348382949829</t>
+    <t xml:space="preserve">13.5648775100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8942651748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3359498977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5605325698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5156154632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6952848434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9722709655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9348411560059</t>
   </si>
   <si>
     <t xml:space="preserve">14.9423265457153</t>
@@ -704,67 +704,67 @@
     <t xml:space="preserve">14.8225469589233</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2043399810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7133979797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.136962890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.159423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2866897583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.36155128479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2267980575562</t>
+    <t xml:space="preserve">15.2043409347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7133989334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1369647979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1594247817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2866888046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3615503311157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2267990112305</t>
   </si>
   <si>
     <t xml:space="preserve">15.3465766906738</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6834535598755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7208824157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5337324142456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588689804077</t>
+    <t xml:space="preserve">15.6834545135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7208833694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5337295532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4588680267334</t>
   </si>
   <si>
     <t xml:space="preserve">15.1669111251831</t>
   </si>
   <si>
-    <t xml:space="preserve">15.196852684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5487031936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4214391708374</t>
+    <t xml:space="preserve">15.1968545913696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5487051010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4214363098145</t>
   </si>
   <si>
     <t xml:space="preserve">15.6011056900024</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6460227966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.735857963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5861349105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9080362319946</t>
+    <t xml:space="preserve">15.6460199356079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7358570098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5861358642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9080381393433</t>
   </si>
   <si>
     <t xml:space="preserve">16.4245796203613</t>
@@ -779,10 +779,10 @@
     <t xml:space="preserve">16.2823429107666</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3272609710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2598876953125</t>
+    <t xml:space="preserve">16.3272590637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2598838806152</t>
   </si>
   <si>
     <t xml:space="preserve">16.2673721313477</t>
@@ -794,28 +794,28 @@
     <t xml:space="preserve">16.7839164733887</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6641387939453</t>
+    <t xml:space="preserve">16.6641368865967</t>
   </si>
   <si>
     <t xml:space="preserve">16.521900177002</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4470367431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6416816711426</t>
+    <t xml:space="preserve">16.4470405578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6416759490967</t>
   </si>
   <si>
     <t xml:space="preserve">17.0758743286133</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7988872528076</t>
+    <t xml:space="preserve">16.7988891601562</t>
   </si>
   <si>
     <t xml:space="preserve">16.7464847564697</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8737506866455</t>
+    <t xml:space="preserve">16.8737487792969</t>
   </si>
   <si>
     <t xml:space="preserve">16.9560966491699</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">17.1058197021484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3946342468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5069274902344</t>
+    <t xml:space="preserve">16.3946361541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5069255828857</t>
   </si>
   <si>
     <t xml:space="preserve">16.6847534179688</t>
@@ -836,7 +836,7 @@
     <t xml:space="preserve">17.1950378417969</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1641120910645</t>
+    <t xml:space="preserve">17.1641101837158</t>
   </si>
   <si>
     <t xml:space="preserve">17.0094814300537</t>
@@ -845,28 +845,28 @@
     <t xml:space="preserve">16.7620716094971</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6306324005127</t>
+    <t xml:space="preserve">16.6306343078613</t>
   </si>
   <si>
     <t xml:space="preserve">16.8471183776855</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0249462127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9398975372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7698040008545</t>
+    <t xml:space="preserve">17.0249443054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9398956298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7698020935059</t>
   </si>
   <si>
     <t xml:space="preserve">16.9940166473389</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1254558563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.955358505249</t>
+    <t xml:space="preserve">17.1254539489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9553623199463</t>
   </si>
   <si>
     <t xml:space="preserve">16.5455856323242</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">16.7156810760498</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8548488616943</t>
+    <t xml:space="preserve">16.854850769043</t>
   </si>
   <si>
     <t xml:space="preserve">16.7466068267822</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">17.0404090881348</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7311458587646</t>
+    <t xml:space="preserve">16.7311420440674</t>
   </si>
   <si>
     <t xml:space="preserve">16.5378532409668</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">16.5687789916992</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6229019165039</t>
+    <t xml:space="preserve">16.6229000091553</t>
   </si>
   <si>
     <t xml:space="preserve">16.707950592041</t>
@@ -905,25 +905,25 @@
     <t xml:space="preserve">16.1822032928467</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0894203186035</t>
+    <t xml:space="preserve">16.0894241333008</t>
   </si>
   <si>
     <t xml:space="preserve">16.0816898345947</t>
   </si>
   <si>
-    <t xml:space="preserve">16.159008026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9347925186157</t>
+    <t xml:space="preserve">16.1590042114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9347906112671</t>
   </si>
   <si>
     <t xml:space="preserve">16.2363224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0739612579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9966449737549</t>
+    <t xml:space="preserve">16.0739593505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9966421127319</t>
   </si>
   <si>
     <t xml:space="preserve">16.3909549713135</t>
@@ -935,19 +935,19 @@
     <t xml:space="preserve">16.8935070037842</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2414264678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0558681488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2878189086914</t>
+    <t xml:space="preserve">17.2414283752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0558700561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.28782081604</t>
   </si>
   <si>
     <t xml:space="preserve">17.2955493927002</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3960609436035</t>
+    <t xml:space="preserve">17.3960628509521</t>
   </si>
   <si>
     <t xml:space="preserve">16.8316535949707</t>
@@ -962,76 +962,76 @@
     <t xml:space="preserve">16.5533180236816</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4837322235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7775325775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5146598815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3832225799561</t>
+    <t xml:space="preserve">16.4837303161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7775344848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5146579742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3832244873047</t>
   </si>
   <si>
     <t xml:space="preserve">16.3986854553223</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2749805450439</t>
+    <t xml:space="preserve">16.2749786376953</t>
   </si>
   <si>
     <t xml:space="preserve">16.2285919189453</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0584964752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9657173156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9502544403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0353031158447</t>
+    <t xml:space="preserve">16.0584983825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9657163619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9502553939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0353012084961</t>
   </si>
   <si>
     <t xml:space="preserve">16.2827129364014</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4141464233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6074390411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5919742584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9321632385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0481395721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2646217346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9476261138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0713329315186</t>
+    <t xml:space="preserve">16.4141502380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6074371337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5919723510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.932165145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0481357574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2646236419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9476280212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0713348388672</t>
   </si>
   <si>
     <t xml:space="preserve">17.0636024475098</t>
   </si>
   <si>
-    <t xml:space="preserve">17.079065322876</t>
+    <t xml:space="preserve">17.0790634155273</t>
   </si>
   <si>
     <t xml:space="preserve">17.2723560333252</t>
   </si>
   <si>
-    <t xml:space="preserve">17.303279876709</t>
+    <t xml:space="preserve">17.3032817840576</t>
   </si>
   <si>
     <t xml:space="preserve">17.3728637695312</t>
@@ -1046,40 +1046,40 @@
     <t xml:space="preserve">17.5893497467041</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4656429290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7207870483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5738849639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5429630279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6975917816162</t>
+    <t xml:space="preserve">17.4656448364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7207851409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5738830566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5429611206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6975898742676</t>
   </si>
   <si>
     <t xml:space="preserve">18.1073665618896</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0377807617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6125469207764</t>
+    <t xml:space="preserve">18.0377826690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6125450134277</t>
   </si>
   <si>
     <t xml:space="preserve">17.6821269989014</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5197658538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.311014175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1099910736084</t>
+    <t xml:space="preserve">17.5197639465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3110103607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1099891662598</t>
   </si>
   <si>
     <t xml:space="preserve">17.3574028015137</t>
@@ -1094,34 +1094,34 @@
     <t xml:space="preserve">17.0867958068848</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8857746124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6151695251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.530122756958</t>
+    <t xml:space="preserve">16.8857765197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6151714324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5301208496094</t>
   </si>
   <si>
     <t xml:space="preserve">16.3522968292236</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0430355072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.826548576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9270582199097</t>
+    <t xml:space="preserve">16.0430316925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8265466690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9270572662354</t>
   </si>
   <si>
     <t xml:space="preserve">16.1976661682129</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6692924499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8703117370605</t>
+    <t xml:space="preserve">16.6692905426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8703136444092</t>
   </si>
   <si>
     <t xml:space="preserve">16.7852630615234</t>
@@ -1130,31 +1130,31 @@
     <t xml:space="preserve">16.9630908966064</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8084583282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9244327545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4218807220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0507640838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.460542678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.452808380127</t>
+    <t xml:space="preserve">16.8084602355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9244346618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4218788146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0507621765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4605388641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4528045654297</t>
   </si>
   <si>
     <t xml:space="preserve">16.7543392181396</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6383647918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7929973602295</t>
+    <t xml:space="preserve">16.6383628845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7929954528809</t>
   </si>
   <si>
     <t xml:space="preserve">16.4064159393311</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">17.3342094421387</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3805961608887</t>
+    <t xml:space="preserve">17.3805980682373</t>
   </si>
   <si>
     <t xml:space="preserve">17.4888381958008</t>
@@ -1175,7 +1175,7 @@
     <t xml:space="preserve">17.6898593902588</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4115238189697</t>
+    <t xml:space="preserve">17.4115257263184</t>
   </si>
   <si>
     <t xml:space="preserve">17.6434707641602</t>
@@ -1187,22 +1187,22 @@
     <t xml:space="preserve">17.2259654998779</t>
   </si>
   <si>
-    <t xml:space="preserve">17.504301071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4991970062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9785556793213</t>
+    <t xml:space="preserve">17.5043029785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.499195098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.978551864624</t>
   </si>
   <si>
     <t xml:space="preserve">16.3445644378662</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2981739044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9012393951416</t>
+    <t xml:space="preserve">16.2981758117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9012413024902</t>
   </si>
   <si>
     <t xml:space="preserve">16.6538276672363</t>
@@ -1214,7 +1214,7 @@
     <t xml:space="preserve">16.3136386871338</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4269886016846</t>
+    <t xml:space="preserve">17.4269866943359</t>
   </si>
   <si>
     <t xml:space="preserve">18.4475574493408</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">18.8805236816406</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1433963775635</t>
+    <t xml:space="preserve">19.1433982849121</t>
   </si>
   <si>
     <t xml:space="preserve">19.0042285919189</t>
@@ -1238,49 +1238,49 @@
     <t xml:space="preserve">18.6949672698975</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6795043945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7413558959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6640396118164</t>
+    <t xml:space="preserve">18.6795024871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7413539886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6640377044678</t>
   </si>
   <si>
     <t xml:space="preserve">18.7877426147461</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2516384124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4371967315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3444175720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.406270980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5609035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3289546966553</t>
+    <t xml:space="preserve">19.2516403198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.437198638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3444194793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4062728881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5609016418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3289566040039</t>
   </si>
   <si>
     <t xml:space="preserve">19.1743240356445</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1124706268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1588611602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2825679779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2361755371094</t>
+    <t xml:space="preserve">19.1124725341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.158863067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2825660705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.236177444458</t>
   </si>
   <si>
     <t xml:space="preserve">19.205249786377</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">19.2671031951904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5299777984619</t>
+    <t xml:space="preserve">19.5299758911133</t>
   </si>
   <si>
     <t xml:space="preserve">19.6382179260254</t>
@@ -1301,28 +1301,28 @@
     <t xml:space="preserve">19.4835891723633</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5145130157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4526596069336</t>
+    <t xml:space="preserve">19.5145149230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4526615142822</t>
   </si>
   <si>
     <t xml:space="preserve">19.607292175293</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1382904052734</t>
+    <t xml:space="preserve">18.1382923126221</t>
   </si>
   <si>
     <t xml:space="preserve">18.3547763824463</t>
   </si>
   <si>
-    <t xml:space="preserve">18.07643699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.03005027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1737804412842</t>
+    <t xml:space="preserve">18.0764389038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0300483703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1737785339355</t>
   </si>
   <si>
     <t xml:space="preserve">17.9502010345459</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">18.6209373474121</t>
   </si>
   <si>
-    <t xml:space="preserve">18.509147644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5889987945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5570583343506</t>
+    <t xml:space="preserve">18.5091495513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.588996887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.557056427002</t>
   </si>
   <si>
     <t xml:space="preserve">18.4931793212891</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">18.1578102111816</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4292964935303</t>
+    <t xml:space="preserve">18.4293003082275</t>
   </si>
   <si>
     <t xml:space="preserve">18.684814453125</t>
@@ -1364,10 +1364,10 @@
     <t xml:space="preserve">18.4133281707764</t>
   </si>
   <si>
-    <t xml:space="preserve">18.461238861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3175106048584</t>
+    <t xml:space="preserve">18.4612407684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3175086975098</t>
   </si>
   <si>
     <t xml:space="preserve">17.8064708709717</t>
@@ -1376,22 +1376,22 @@
     <t xml:space="preserve">17.8224411010742</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7106513977051</t>
+    <t xml:space="preserve">17.7106533050537</t>
   </si>
   <si>
     <t xml:space="preserve">17.9182605743408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9661693572998</t>
+    <t xml:space="preserve">17.9661712646484</t>
   </si>
   <si>
     <t xml:space="preserve">17.8863220214844</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9981117248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3973617553711</t>
+    <t xml:space="preserve">17.9981098175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3973598480225</t>
   </si>
   <si>
     <t xml:space="preserve">18.5251178741455</t>
@@ -1403,28 +1403,28 @@
     <t xml:space="preserve">19.1479454040527</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1639175415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0201873779297</t>
+    <t xml:space="preserve">19.1639137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0201854705811</t>
   </si>
   <si>
     <t xml:space="preserve">18.8604869842529</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7806358337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5730285644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0680961608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7646675109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4772052764893</t>
+    <t xml:space="preserve">18.7806377410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5730266571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.06809425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7646656036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4772090911865</t>
   </si>
   <si>
     <t xml:space="preserve">18.7007884979248</t>
@@ -1433,25 +1433,25 @@
     <t xml:space="preserve">19.2437648773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4513740539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4992847442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2118244171143</t>
+    <t xml:space="preserve">19.4513721466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4992828369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2118225097656</t>
   </si>
   <si>
     <t xml:space="preserve">19.1319732666016</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0042152404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1160087585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.036153793335</t>
+    <t xml:space="preserve">19.0042171478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1160068511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0361576080322</t>
   </si>
   <si>
     <t xml:space="preserve">19.1798839569092</t>
@@ -1466,13 +1466,13 @@
     <t xml:space="preserve">19.3076457977295</t>
   </si>
   <si>
-    <t xml:space="preserve">19.722864151001</t>
+    <t xml:space="preserve">19.7228622436523</t>
   </si>
   <si>
     <t xml:space="preserve">19.467342376709</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3874950408936</t>
+    <t xml:space="preserve">19.3874931335449</t>
   </si>
   <si>
     <t xml:space="preserve">19.5631637573242</t>
@@ -1481,22 +1481,22 @@
     <t xml:space="preserve">19.8825607299805</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3616580963135</t>
+    <t xml:space="preserve">20.3616600036621</t>
   </si>
   <si>
     <t xml:space="preserve">20.4415092468262</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2658386230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7609100341797</t>
+    <t xml:space="preserve">20.2658405303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7609081268311</t>
   </si>
   <si>
     <t xml:space="preserve">21.0962753295898</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8247871398926</t>
+    <t xml:space="preserve">20.8247890472412</t>
   </si>
   <si>
     <t xml:space="preserve">20.249870300293</t>
@@ -1511,22 +1511,22 @@
     <t xml:space="preserve">20.1700191497803</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7548007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5312232971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4034633636475</t>
+    <t xml:space="preserve">19.7548027038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5312252044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4034614562988</t>
   </si>
   <si>
     <t xml:space="preserve">18.8125762939453</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7327251434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3813877105713</t>
+    <t xml:space="preserve">18.7327270507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3813896179199</t>
   </si>
   <si>
     <t xml:space="preserve">18.2536296844482</t>
@@ -1535,7 +1535,7 @@
     <t xml:space="preserve">17.9342308044434</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3494491577148</t>
+    <t xml:space="preserve">18.3494472503662</t>
   </si>
   <si>
     <t xml:space="preserve">18.9243659973145</t>
@@ -1556,16 +1556,16 @@
     <t xml:space="preserve">17.1357326507568</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2155818939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9760341644287</t>
+    <t xml:space="preserve">17.2155838012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9760360717773</t>
   </si>
   <si>
     <t xml:space="preserve">17.5509510040283</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8961849212646</t>
+    <t xml:space="preserve">16.8961868286133</t>
   </si>
   <si>
     <t xml:space="preserve">17.0718536376953</t>
@@ -1574,16 +1574,16 @@
     <t xml:space="preserve">16.9281253814697</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8323040008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.05588722229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1836452484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4551315307617</t>
+    <t xml:space="preserve">16.8323059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0558834075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1836433410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4551334381104</t>
   </si>
   <si>
     <t xml:space="preserve">16.8163356781006</t>
@@ -1592,55 +1592,55 @@
     <t xml:space="preserve">16.3532085418701</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9859008789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0976905822754</t>
+    <t xml:space="preserve">15.9858980178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0976867675781</t>
   </si>
   <si>
     <t xml:space="preserve">16.1136589050293</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4269514083862</t>
+    <t xml:space="preserve">15.4269523620605</t>
   </si>
   <si>
     <t xml:space="preserve">15.3311319351196</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6505317687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4748611450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4429216384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7703056335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.842170715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7383632659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4490299224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2733554840088</t>
+    <t xml:space="preserve">15.6505289077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4748620986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4429206848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7703037261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8421678543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7383651733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4490261077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2733592987061</t>
   </si>
   <si>
     <t xml:space="preserve">16.1615695953369</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3212661743164</t>
+    <t xml:space="preserve">16.3212699890137</t>
   </si>
   <si>
     <t xml:space="preserve">16.4809646606445</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6246967315674</t>
+    <t xml:space="preserve">16.624698638916</t>
   </si>
   <si>
     <t xml:space="preserve">16.768424987793</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">17.1676731109619</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3433437347412</t>
+    <t xml:space="preserve">17.3433418273926</t>
   </si>
   <si>
     <t xml:space="preserve">17.2794628143311</t>
@@ -1661,16 +1661,16 @@
     <t xml:space="preserve">17.0079746246338</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6406688690186</t>
+    <t xml:space="preserve">16.6406669616699</t>
   </si>
   <si>
     <t xml:space="preserve">16.2414169311523</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5608158111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7045459747314</t>
+    <t xml:space="preserve">16.5608177185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7045478820801</t>
   </si>
   <si>
     <t xml:space="preserve">16.8482761383057</t>
@@ -1679,43 +1679,43 @@
     <t xml:space="preserve">17.3752841949463</t>
   </si>
   <si>
-    <t xml:space="preserve">17.103796005249</t>
+    <t xml:space="preserve">17.1037921905518</t>
   </si>
   <si>
     <t xml:space="preserve">16.8802146911621</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9121570587158</t>
+    <t xml:space="preserve">16.9121532440186</t>
   </si>
   <si>
     <t xml:space="preserve">16.8642463684082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.720516204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6885757446289</t>
+    <t xml:space="preserve">16.7205142974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6885738372803</t>
   </si>
   <si>
     <t xml:space="preserve">16.6087265014648</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7364845275879</t>
+    <t xml:space="preserve">16.7364864349365</t>
   </si>
   <si>
     <t xml:space="preserve">16.3052978515625</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8980665206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.193510055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2094764709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3851490020752</t>
+    <t xml:space="preserve">15.8980646133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1935081481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2094783782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3851470947266</t>
   </si>
   <si>
     <t xml:space="preserve">16.28932762146</t>
@@ -1724,28 +1724,28 @@
     <t xml:space="preserve">16.2573890686035</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2254447937012</t>
+    <t xml:space="preserve">16.2254486083984</t>
   </si>
   <si>
     <t xml:space="preserve">15.9140357971191</t>
   </si>
   <si>
-    <t xml:space="preserve">16.417085647583</t>
+    <t xml:space="preserve">16.4170875549316</t>
   </si>
   <si>
     <t xml:space="preserve">16.5288772583008</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7843952178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5767860412598</t>
+    <t xml:space="preserve">16.7843971252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5767841339111</t>
   </si>
   <si>
     <t xml:space="preserve">16.369176864624</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1775379180908</t>
+    <t xml:space="preserve">16.1775398254395</t>
   </si>
   <si>
     <t xml:space="preserve">16.4889507293701</t>
@@ -1754,31 +1754,31 @@
     <t xml:space="preserve">16.2494029998779</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3292541503906</t>
+    <t xml:space="preserve">16.329252243042</t>
   </si>
   <si>
     <t xml:space="preserve">16.4091014862061</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1695537567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0497779846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5688037872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6486511230469</t>
+    <t xml:space="preserve">16.1695556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0497817993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5687999725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6486530303955</t>
   </si>
   <si>
     <t xml:space="preserve">17.2874488830566</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0878238677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0479011535645</t>
+    <t xml:space="preserve">17.0878257751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0478992462158</t>
   </si>
   <si>
     <t xml:space="preserve">16.808349609375</t>
@@ -1787,31 +1787,31 @@
     <t xml:space="preserve">16.9680500030518</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7285003662109</t>
+    <t xml:space="preserve">16.7285022735596</t>
   </si>
   <si>
     <t xml:space="preserve">16.8882007598877</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1277523040771</t>
+    <t xml:space="preserve">17.1277503967285</t>
   </si>
   <si>
     <t xml:space="preserve">16.8793506622314</t>
   </si>
   <si>
-    <t xml:space="preserve">17.045238494873</t>
+    <t xml:space="preserve">17.0452404022217</t>
   </si>
   <si>
     <t xml:space="preserve">16.9208221435547</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7964038848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2111301422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1281852722168</t>
+    <t xml:space="preserve">16.7964057922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2111282348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1281833648682</t>
   </si>
   <si>
     <t xml:space="preserve">17.1696586608887</t>
@@ -1820,25 +1820,25 @@
     <t xml:space="preserve">17.418493270874</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3770198822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4599647521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.294075012207</t>
+    <t xml:space="preserve">17.3770236968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4599666595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2940769195557</t>
   </si>
   <si>
     <t xml:space="preserve">16.9622955322266</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7549304962158</t>
+    <t xml:space="preserve">16.7549324035645</t>
   </si>
   <si>
     <t xml:space="preserve">16.6305141448975</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3402061462402</t>
+    <t xml:space="preserve">16.3402080535889</t>
   </si>
   <si>
     <t xml:space="preserve">16.4895057678223</t>
@@ -1853,22 +1853,22 @@
     <t xml:space="preserve">17.667329788208</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5014381408691</t>
+    <t xml:space="preserve">17.5014400482178</t>
   </si>
   <si>
     <t xml:space="preserve">17.5429096221924</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2526016235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7134571075439</t>
+    <t xml:space="preserve">17.2526035308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7134590148926</t>
   </si>
   <si>
     <t xml:space="preserve">16.4231510162354</t>
   </si>
   <si>
-    <t xml:space="preserve">16.373384475708</t>
+    <t xml:space="preserve">16.3733825683594</t>
   </si>
   <si>
     <t xml:space="preserve">16.2406730651855</t>
@@ -1886,46 +1886,46 @@
     <t xml:space="preserve">16.3070278167725</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8591241836548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.726411819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7927694320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0747833251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5273427963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4278106689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6600542068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1789722442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3614511489868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6932334899902</t>
+    <t xml:space="preserve">15.8591232299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7264099121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7927665710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0747814178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5273418426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4278078079224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6600551605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1789703369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3614521026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6932344436646</t>
   </si>
   <si>
     <t xml:space="preserve">15.6102876663208</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4609851837158</t>
+    <t xml:space="preserve">15.4609870910645</t>
   </si>
   <si>
     <t xml:space="preserve">15.4443988800049</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3780422210693</t>
+    <t xml:space="preserve">15.378041267395</t>
   </si>
   <si>
     <t xml:space="preserve">15.2950963973999</t>
@@ -1934,46 +1934,46 @@
     <t xml:space="preserve">15.925479888916</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2904376983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3899745941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4397411346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6719856262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9576358795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0867137908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3355484008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8378753662109</t>
+    <t xml:space="preserve">16.2904396057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3899726867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4397392272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.671989440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9576377868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0867118835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3355464935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8378772735596</t>
   </si>
   <si>
     <t xml:space="preserve">16.5890407562256</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2572612762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8757133483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9088935852051</t>
+    <t xml:space="preserve">16.2572593688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8757123947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9088897705078</t>
   </si>
   <si>
     <t xml:space="preserve">16.1577281951904</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1411380767822</t>
+    <t xml:space="preserve">16.1411361694336</t>
   </si>
   <si>
     <t xml:space="preserve">16.4729194641113</t>
@@ -1982,22 +1982,22 @@
     <t xml:space="preserve">15.7595891952515</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6766443252563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5936994552612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.477575302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7429990768433</t>
+    <t xml:space="preserve">15.6766424179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5936985015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.477578163147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7430009841919</t>
   </si>
   <si>
     <t xml:space="preserve">15.7098236083984</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8425340652466</t>
+    <t xml:space="preserve">15.8425350189209</t>
   </si>
   <si>
     <t xml:space="preserve">16.3567943572998</t>
@@ -2012,25 +2012,25 @@
     <t xml:space="preserve">17.5843849182129</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0037689208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2240829467773</t>
+    <t xml:space="preserve">17.0037670135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2240810394287</t>
   </si>
   <si>
     <t xml:space="preserve">16.0084247589111</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1909065246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5558643341064</t>
+    <t xml:space="preserve">16.1909046173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5558624267578</t>
   </si>
   <si>
     <t xml:space="preserve">14.532000541687</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7974252700806</t>
+    <t xml:space="preserve">14.7974243164062</t>
   </si>
   <si>
     <t xml:space="preserve">14.1836309432983</t>
@@ -2039,58 +2039,58 @@
     <t xml:space="preserve">13.9347953796387</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6361923217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4371242523193</t>
+    <t xml:space="preserve">13.636194229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.437123298645</t>
   </si>
   <si>
     <t xml:space="preserve">13.2712335586548</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3873567581177</t>
+    <t xml:space="preserve">13.3873558044434</t>
   </si>
   <si>
     <t xml:space="preserve">11.7616310119629</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9606990814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4251909255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0317125320435</t>
+    <t xml:space="preserve">11.9607000350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4251918792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0317115783691</t>
   </si>
   <si>
     <t xml:space="preserve">11.4796171188354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1690816879272</t>
+    <t xml:space="preserve">10.1690826416016</t>
   </si>
   <si>
     <t xml:space="preserve">10.3681507110596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95342540740967</t>
+    <t xml:space="preserve">9.95342445373535</t>
   </si>
   <si>
     <t xml:space="preserve">10.3183832168579</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8777542114258</t>
+    <t xml:space="preserve">11.8777523040771</t>
   </si>
   <si>
     <t xml:space="preserve">12.4417810440063</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8565073013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1763572692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2924785614014</t>
+    <t xml:space="preserve">12.8565082550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1763563156128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2924795150757</t>
   </si>
   <si>
     <t xml:space="preserve">11.2141923904419</t>
@@ -2099,16 +2099,16 @@
     <t xml:space="preserve">10.9155893325806</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6667537689209</t>
+    <t xml:space="preserve">10.6667528152466</t>
   </si>
   <si>
     <t xml:space="preserve">10.2022609710693</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4510955810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5174531936646</t>
+    <t xml:space="preserve">10.451096534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5174522399902</t>
   </si>
   <si>
     <t xml:space="preserve">10.5340414047241</t>
@@ -2117,34 +2117,34 @@
     <t xml:space="preserve">10.4013290405273</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1524925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0529584884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97001361846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4676847457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6999311447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.301794052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0695486068726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2520265579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.003191947937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0363712310791</t>
+    <t xml:space="preserve">10.1524934768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0529594421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97001457214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4676866531372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6999320983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3017950057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0695466995239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2520275115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0031929016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0363702774048</t>
   </si>
   <si>
     <t xml:space="preserve">10.1193151473999</t>
@@ -2153,25 +2153,25 @@
     <t xml:space="preserve">9.92024707794189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45575332641602</t>
+    <t xml:space="preserve">9.4557523727417</t>
   </si>
   <si>
     <t xml:space="preserve">9.50552082061768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32304191589355</t>
+    <t xml:space="preserve">9.32304096221924</t>
   </si>
   <si>
     <t xml:space="preserve">9.14056301116943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07420444488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6879997253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1359043121338</t>
+    <t xml:space="preserve">9.07420539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68800067901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1359033584595</t>
   </si>
   <si>
     <t xml:space="preserve">9.70458889007568</t>
@@ -2180,19 +2180,19 @@
     <t xml:space="preserve">9.38939762115479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4345064163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2188491821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4179172515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.99853515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8990001678467</t>
+    <t xml:space="preserve">10.4345073699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2188501358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4179182052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9985342025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.899001121521</t>
   </si>
   <si>
     <t xml:space="preserve">10.9819450378418</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">11.8113965988159</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7782182693481</t>
+    <t xml:space="preserve">11.7782192230225</t>
   </si>
   <si>
     <t xml:space="preserve">11.595739364624</t>
@@ -2216,37 +2216,37 @@
     <t xml:space="preserve">11.3634929656982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6833438873291</t>
+    <t xml:space="preserve">10.6833429336548</t>
   </si>
   <si>
     <t xml:space="preserve">10.9487676620483</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9653577804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2639598846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2805490493774</t>
+    <t xml:space="preserve">10.9653558731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2639579772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2805480957031</t>
   </si>
   <si>
     <t xml:space="preserve">11.1810140609741</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3303155899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2971382141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0814790725708</t>
+    <t xml:space="preserve">11.3303146362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.297137260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0814809799194</t>
   </si>
   <si>
     <t xml:space="preserve">11.0151233673096</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0648908615112</t>
+    <t xml:space="preserve">11.0648918151855</t>
   </si>
   <si>
     <t xml:space="preserve">10.8326454162598</t>
@@ -2267,28 +2267,28 @@
     <t xml:space="preserve">10.3515615463257</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2354383468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9321775436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5506315231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5008640289307</t>
+    <t xml:space="preserve">10.2354393005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9321784973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5506296157837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5008630752563</t>
   </si>
   <si>
     <t xml:space="preserve">10.6169862747192</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4842758178711</t>
+    <t xml:space="preserve">10.4842748641968</t>
   </si>
   <si>
     <t xml:space="preserve">10.0197811126709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3349723815918</t>
+    <t xml:space="preserve">10.3349733352661</t>
   </si>
   <si>
     <t xml:space="preserve">10.7828769683838</t>
@@ -2300,49 +2300,49 @@
     <t xml:space="preserve">11.1312465667725</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4132604598999</t>
+    <t xml:space="preserve">11.4132614135742</t>
   </si>
   <si>
     <t xml:space="preserve">11.4298496246338</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2307815551758</t>
+    <t xml:space="preserve">11.2307806015015</t>
   </si>
   <si>
     <t xml:space="preserve">10.8658227920532</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3137264251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.396671295166</t>
+    <t xml:space="preserve">11.3137273788452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3966703414917</t>
   </si>
   <si>
     <t xml:space="preserve">11.5127944946289</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8611650466919</t>
+    <t xml:space="preserve">11.8611640930176</t>
   </si>
   <si>
     <t xml:space="preserve">12.2095355987549</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9772872924805</t>
+    <t xml:space="preserve">11.9772882461548</t>
   </si>
   <si>
     <t xml:space="preserve">12.0602331161499</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2593011856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3800821304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1146574020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6335763931274</t>
+    <t xml:space="preserve">12.2593021392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3800830841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1146583557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6335754394531</t>
   </si>
   <si>
     <t xml:space="preserve">10.2686166763306</t>
@@ -2351,13 +2351,13 @@
     <t xml:space="preserve">9.55528831481934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62164497375488</t>
+    <t xml:space="preserve">9.62164402008057</t>
   </si>
   <si>
     <t xml:space="preserve">9.65482234954834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60505485534668</t>
+    <t xml:space="preserve">9.605055809021</t>
   </si>
   <si>
     <t xml:space="preserve">9.75435733795166</t>
@@ -2372,160 +2372,160 @@
     <t xml:space="preserve">12.1929454803467</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8399181365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3210000991821</t>
+    <t xml:space="preserve">12.8399171829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3209991455078</t>
   </si>
   <si>
     <t xml:space="preserve">12.4086036682129</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2758903503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7237958908081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9062738418579</t>
+    <t xml:space="preserve">12.2758922576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7237939834595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9062747955322</t>
   </si>
   <si>
     <t xml:space="preserve">13.1053428649902</t>
   </si>
   <si>
-    <t xml:space="preserve">12.989218711853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0721635818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0223960876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0887537002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0389862060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6740283966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4583702087402</t>
+    <t xml:space="preserve">12.9892206192017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0721645355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0223979949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.088752746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.038987159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6740274429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4583692550659</t>
   </si>
   <si>
     <t xml:space="preserve">12.5081377029419</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7403831481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3754243850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4749593734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6574392318726</t>
+    <t xml:space="preserve">12.7403841018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3754262924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4749584197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6574382781982</t>
   </si>
   <si>
     <t xml:space="preserve">12.9560413360596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9228630065918</t>
+    <t xml:space="preserve">12.9228639602661</t>
   </si>
   <si>
     <t xml:space="preserve">13.536657333374</t>
   </si>
   <si>
-    <t xml:space="preserve">13.984561920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3661098480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5817670822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6978912353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7642469406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.631534576416</t>
+    <t xml:space="preserve">13.9845609664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3661108016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5817680358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6978902816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7642459869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6315336227417</t>
   </si>
   <si>
     <t xml:space="preserve">14.1006851196289</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4324645996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.780837059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7476577758789</t>
+    <t xml:space="preserve">14.4324655532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7808361053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7476587295532</t>
   </si>
   <si>
     <t xml:space="preserve">14.4988212585449</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3495197296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2499866485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7854928970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0177402496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0509204864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.283164024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0462589263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9301376342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3946304321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3448648452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9918384552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8969564437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9799041748047</t>
+    <t xml:space="preserve">14.3495216369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2499876022339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2333974838257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.785493850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0177392959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0509185791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2831649780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0462598800659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9301385879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3946285247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3448629379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9918355941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8969602584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.979905128479</t>
   </si>
   <si>
     <t xml:space="preserve">14.9135475158691</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9964923858643</t>
+    <t xml:space="preserve">14.9964942932129</t>
   </si>
   <si>
     <t xml:space="preserve">15.825945854187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6434659957886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0250129699707</t>
+    <t xml:space="preserve">15.6434669494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0250148773193</t>
   </si>
   <si>
     <t xml:space="preserve">16.0913715362549</t>
@@ -2537,19 +2537,19 @@
     <t xml:space="preserve">15.5605211257935</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0130825042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2619199752808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.228741645813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1457948684692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4941654205322</t>
+    <t xml:space="preserve">15.0130834579468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2619180679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2287406921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1457939147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4941644668579</t>
   </si>
   <si>
     <t xml:space="preserve">15.626877784729</t>
@@ -2561,46 +2561,46 @@
     <t xml:space="preserve">15.502459526062</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2702140808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2536239624023</t>
+    <t xml:space="preserve">15.2702121734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.253623008728</t>
   </si>
   <si>
     <t xml:space="preserve">15.5439329147339</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5771112442017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8508291244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7181177139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7347059249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8840065002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.751296043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4361047744751</t>
+    <t xml:space="preserve">15.5771102905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.850830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7181186676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7347040176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8840074539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7512941360474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4361019134521</t>
   </si>
   <si>
     <t xml:space="preserve">16.3982696533203</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5807476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8674182891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0830745697021</t>
+    <t xml:space="preserve">16.5807456970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8674173355103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0830764770508</t>
   </si>
   <si>
     <t xml:space="preserve">16.1079597473145</t>
@@ -2609,91 +2609,91 @@
     <t xml:space="preserve">16.4646244049072</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6222190856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8212871551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7051639556885</t>
+    <t xml:space="preserve">16.622220993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8212890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7051658630371</t>
   </si>
   <si>
     <t xml:space="preserve">16.9042320251465</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9374103546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1364784240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3023719787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4350833892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4516716003418</t>
+    <t xml:space="preserve">16.9374122619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1364803314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3023700714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4350852966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4516735076904</t>
   </si>
   <si>
     <t xml:space="preserve">17.2194232940674</t>
   </si>
   <si>
-    <t xml:space="preserve">16.721752166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1530685424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0535335540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0369472503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8876438140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7715187072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8544635772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2028350830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1033039093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1198921203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7383422851562</t>
+    <t xml:space="preserve">16.7217540740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1530666351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0535354614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0369453430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8876457214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.771520614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8544673919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2028369903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1033000946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1198902130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7383441925049</t>
   </si>
   <si>
     <t xml:space="preserve">17.3521385192871</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2691917419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8710556030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9171867370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2074947357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2323799133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6056289672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6958522796631</t>
+    <t xml:space="preserve">17.269193649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8710536956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9171848297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2074966430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2323780059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6056308746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6958503723145</t>
   </si>
   <si>
     <t xml:space="preserve">18.1981773376465</t>
@@ -2705,31 +2705,31 @@
     <t xml:space="preserve">17.617561340332</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0820541381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6507415771484</t>
+    <t xml:space="preserve">18.0820560455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6507396697998</t>
   </si>
   <si>
     <t xml:space="preserve">17.8000392913818</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4019031524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3189582824707</t>
+    <t xml:space="preserve">17.4019050598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3189601898193</t>
   </si>
   <si>
     <t xml:space="preserve">17.0203590393066</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7881088256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.970588684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1862468719482</t>
+    <t xml:space="preserve">16.7881107330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9705867767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1862449645996</t>
   </si>
   <si>
     <t xml:space="preserve">16.4065628051758</t>
@@ -2738,13 +2738,13 @@
     <t xml:space="preserve">16.4148578643799</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0499000549316</t>
+    <t xml:space="preserve">16.049898147583</t>
   </si>
   <si>
     <t xml:space="preserve">16.1660194396973</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5346145629883</t>
+    <t xml:space="preserve">17.5346164703369</t>
   </si>
   <si>
     <t xml:space="preserve">17.0701236724854</t>
@@ -2753,7 +2753,7 @@
     <t xml:space="preserve">17.2360134124756</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6839179992676</t>
+    <t xml:space="preserve">17.6839160919189</t>
   </si>
   <si>
     <t xml:space="preserve">17.4848499298096</t>
@@ -2765,34 +2765,34 @@
     <t xml:space="preserve">17.2424736022949</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3437004089355</t>
+    <t xml:space="preserve">17.3437023162842</t>
   </si>
   <si>
     <t xml:space="preserve">17.5461559295654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4111881256104</t>
+    <t xml:space="preserve">17.4111862182617</t>
   </si>
   <si>
     <t xml:space="preserve">17.3774452209473</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6642570495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4449291229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4618015289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1749877929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.040018081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.006275177002</t>
+    <t xml:space="preserve">17.6642589569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4449310302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4618034362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1749897003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0400199890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0062770843506</t>
   </si>
   <si>
     <t xml:space="preserve">16.9556617736816</t>
@@ -2801,7 +2801,7 @@
     <t xml:space="preserve">16.8628711700439</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0906314849854</t>
+    <t xml:space="preserve">17.090633392334</t>
   </si>
   <si>
     <t xml:space="preserve">16.8713054656982</t>
@@ -2825,25 +2825,25 @@
     <t xml:space="preserve">15.7915420532227</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6903162002563</t>
+    <t xml:space="preserve">15.6903142929077</t>
   </si>
   <si>
     <t xml:space="preserve">15.8590278625488</t>
   </si>
   <si>
-    <t xml:space="preserve">15.411937713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5216026306152</t>
+    <t xml:space="preserve">15.4119396209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5216007232666</t>
   </si>
   <si>
     <t xml:space="preserve">15.0998182296753</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4203748703003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6059589385986</t>
+    <t xml:space="preserve">15.420373916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.60595703125</t>
   </si>
   <si>
     <t xml:space="preserve">15.5806493759155</t>
@@ -2852,19 +2852,19 @@
     <t xml:space="preserve">15.833722114563</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0446128845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8758983612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8927707672119</t>
+    <t xml:space="preserve">16.0446109771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8759002685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8927688598633</t>
   </si>
   <si>
     <t xml:space="preserve">16.0108680725098</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9349489212036</t>
+    <t xml:space="preserve">15.934947013855</t>
   </si>
   <si>
     <t xml:space="preserve">15.7662353515625</t>
@@ -2879,28 +2879,28 @@
     <t xml:space="preserve">15.4878597259521</t>
   </si>
   <si>
-    <t xml:space="preserve">15.184175491333</t>
+    <t xml:space="preserve">15.1841745376587</t>
   </si>
   <si>
     <t xml:space="preserve">15.2347888946533</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3950653076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9433841705322</t>
+    <t xml:space="preserve">15.3950672149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9433832168579</t>
   </si>
   <si>
     <t xml:space="preserve">16.112096786499</t>
   </si>
   <si>
-    <t xml:space="preserve">16.297679901123</t>
+    <t xml:space="preserve">16.2976818084717</t>
   </si>
   <si>
     <t xml:space="preserve">16.4495239257812</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5890865325928</t>
+    <t xml:space="preserve">15.5890846252441</t>
   </si>
   <si>
     <t xml:space="preserve">15.698751449585</t>
@@ -2909,25 +2909,25 @@
     <t xml:space="preserve">16.0361766815186</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9686908721924</t>
+    <t xml:space="preserve">15.968692779541</t>
   </si>
   <si>
     <t xml:space="preserve">16.3145523071289</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9180784225464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0193061828613</t>
+    <t xml:space="preserve">15.9180765151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0193042755127</t>
   </si>
   <si>
     <t xml:space="preserve">15.5384731292725</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0154619216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.150429725647</t>
+    <t xml:space="preserve">15.0154609680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1504316329956</t>
   </si>
   <si>
     <t xml:space="preserve">15.5300378799438</t>
@@ -2948,10 +2948,10 @@
     <t xml:space="preserve">15.8674631118774</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4541158676147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9732828140259</t>
+    <t xml:space="preserve">15.4541139602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9732847213745</t>
   </si>
   <si>
     <t xml:space="preserve">15.0238971710205</t>
@@ -2960,28 +2960,28 @@
     <t xml:space="preserve">15.1673030853271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4372434616089</t>
+    <t xml:space="preserve">15.4372453689575</t>
   </si>
   <si>
     <t xml:space="preserve">15.6312646865845</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4794225692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1588668823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7623929977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4080953598022</t>
+    <t xml:space="preserve">15.4794235229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1588659286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7623920440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4080944061279</t>
   </si>
   <si>
     <t xml:space="preserve">13.7416791915894</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0537967681885</t>
+    <t xml:space="preserve">14.0537977218628</t>
   </si>
   <si>
     <t xml:space="preserve">14.1212825775146</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">13.5898370742798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.142746925354</t>
+    <t xml:space="preserve">13.1427459716797</t>
   </si>
   <si>
     <t xml:space="preserve">12.7294006347656</t>
@@ -3005,7 +3005,7 @@
     <t xml:space="preserve">12.9065494537354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3367671966553</t>
+    <t xml:space="preserve">13.3367681503296</t>
   </si>
   <si>
     <t xml:space="preserve">13.1258754730225</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">13.5139169692993</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9188280105591</t>
+    <t xml:space="preserve">13.9188270568848</t>
   </si>
   <si>
     <t xml:space="preserve">13.3198957443237</t>
@@ -3029,13 +3029,13 @@
     <t xml:space="preserve">12.9318561553955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7631435394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.636607170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4172821044922</t>
+    <t xml:space="preserve">12.7631425857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6366081237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4172801971436</t>
   </si>
   <si>
     <t xml:space="preserve">12.4847660064697</t>
@@ -3071,10 +3071,10 @@
     <t xml:space="preserve">13.4126873016357</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3958168029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4464292526245</t>
+    <t xml:space="preserve">13.3958158493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4464302062988</t>
   </si>
   <si>
     <t xml:space="preserve">13.7838573455811</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">12.9571619033813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0752620697021</t>
+    <t xml:space="preserve">13.0752630233765</t>
   </si>
   <si>
     <t xml:space="preserve">12.7040939331055</t>
@@ -3104,10 +3104,10 @@
     <t xml:space="preserve">12.214825630188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0461120605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8773984909058</t>
+    <t xml:space="preserve">12.0461111068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8773994445801</t>
   </si>
   <si>
     <t xml:space="preserve">12.1473398208618</t>
@@ -3119,22 +3119,22 @@
     <t xml:space="preserve">12.2316970825195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.451024055481</t>
+    <t xml:space="preserve">12.4510231018066</t>
   </si>
   <si>
     <t xml:space="preserve">12.3835391998291</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2991809844971</t>
+    <t xml:space="preserve">12.2991819381714</t>
   </si>
   <si>
     <t xml:space="preserve">11.8267850875854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749439239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6487474441528</t>
+    <t xml:space="preserve">11.6749429702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6487464904785</t>
   </si>
   <si>
     <t xml:space="preserve">11.474102973938</t>
@@ -3146,10 +3146,10 @@
     <t xml:space="preserve">11.8932485580444</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9107122421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.434642791748</t>
+    <t xml:space="preserve">11.9107131958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4346437454224</t>
   </si>
   <si>
     <t xml:space="preserve">12.102819442749</t>
@@ -3161,7 +3161,7 @@
     <t xml:space="preserve">11.9805698394775</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1901416778564</t>
+    <t xml:space="preserve">12.1901426315308</t>
   </si>
   <si>
     <t xml:space="preserve">12.3298578262329</t>
@@ -3179,13 +3179,13 @@
     <t xml:space="preserve">11.4391746520996</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1946725845337</t>
+    <t xml:space="preserve">11.1946716308594</t>
   </si>
   <si>
     <t xml:space="preserve">11.7186040878296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5788898468018</t>
+    <t xml:space="preserve">11.5788888931274</t>
   </si>
   <si>
     <t xml:space="preserve">11.8408555984497</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">11.8583192825317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7709970474243</t>
+    <t xml:space="preserve">11.7709980010986</t>
   </si>
   <si>
     <t xml:space="preserve">11.9631052017212</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">11.7535333633423</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4915676116943</t>
+    <t xml:space="preserve">11.49156665802</t>
   </si>
   <si>
     <t xml:space="preserve">11.2645292282104</t>
@@ -3212,16 +3212,16 @@
     <t xml:space="preserve">10.8104562759399</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0549573898315</t>
+    <t xml:space="preserve">11.0549583435059</t>
   </si>
   <si>
     <t xml:space="preserve">11.1772079467773</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3867807388306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2470664978027</t>
+    <t xml:space="preserve">11.3867797851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2470655441284</t>
   </si>
   <si>
     <t xml:space="preserve">11.0374937057495</t>
@@ -3230,13 +3230,13 @@
     <t xml:space="preserve">10.8453845977783</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3343877792358</t>
+    <t xml:space="preserve">11.3343868255615</t>
   </si>
   <si>
     <t xml:space="preserve">11.3169231414795</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4042463302612</t>
+    <t xml:space="preserve">11.4042453765869</t>
   </si>
   <si>
     <t xml:space="preserve">11.2296009063721</t>
@@ -3245,13 +3245,13 @@
     <t xml:space="preserve">11.6138181686401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.788462638855</t>
+    <t xml:space="preserve">11.7884616851807</t>
   </si>
   <si>
     <t xml:space="preserve">11.8233909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">11.805926322937</t>
+    <t xml:space="preserve">11.8059272766113</t>
   </si>
   <si>
     <t xml:space="preserve">11.5614242553711</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">11.4566383361816</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5439615249634</t>
+    <t xml:space="preserve">11.5439605712891</t>
   </si>
   <si>
     <t xml:space="preserve">11.4217090606689</t>
@@ -3275,7 +3275,7 @@
     <t xml:space="preserve">10.7231340408325</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6882047653198</t>
+    <t xml:space="preserve">10.6882057189941</t>
   </si>
   <si>
     <t xml:space="preserve">10.6707410812378</t>
@@ -3284,7 +3284,7 @@
     <t xml:space="preserve">10.5135612487793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2865238189697</t>
+    <t xml:space="preserve">10.286524772644</t>
   </si>
   <si>
     <t xml:space="preserve">10.2341318130493</t>
@@ -3299,10 +3299,10 @@
     <t xml:space="preserve">9.78005695343018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90230751037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81498622894287</t>
+    <t xml:space="preserve">9.90230846405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81498527526855</t>
   </si>
   <si>
     <t xml:space="preserve">9.76259326934814</t>
@@ -3311,28 +3311,28 @@
     <t xml:space="preserve">9.9896297454834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1992025375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29105472564697</t>
+    <t xml:space="preserve">10.1992034912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29105567932129</t>
   </si>
   <si>
     <t xml:space="preserve">9.51809120178223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2211971282959</t>
+    <t xml:space="preserve">9.22119808197021</t>
   </si>
   <si>
     <t xml:space="preserve">9.25612640380859</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06401634216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80205059051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81951522827148</t>
+    <t xml:space="preserve">9.0640172958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80205154418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8195161819458</t>
   </si>
   <si>
     <t xml:space="preserve">8.60121154785156</t>
@@ -3347,34 +3347,34 @@
     <t xml:space="preserve">8.44403171539307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46149635314941</t>
+    <t xml:space="preserve">8.46149444580078</t>
   </si>
   <si>
     <t xml:space="preserve">8.3392448425293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56628322601318</t>
+    <t xml:space="preserve">8.56628227233887</t>
   </si>
   <si>
     <t xml:space="preserve">8.34797763824463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54881858825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59247875213623</t>
+    <t xml:space="preserve">8.54881763458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59247970581055</t>
   </si>
   <si>
     <t xml:space="preserve">8.85444450378418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88937282562256</t>
+    <t xml:space="preserve">8.88937377929688</t>
   </si>
   <si>
     <t xml:space="preserve">9.04655265808105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01162433624268</t>
+    <t xml:space="preserve">9.01162338256836</t>
   </si>
   <si>
     <t xml:space="preserve">8.83697986602783</t>
@@ -3383,31 +3383,31 @@
     <t xml:space="preserve">8.73219394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02908802032471</t>
+    <t xml:space="preserve">9.02908897399902</t>
   </si>
   <si>
     <t xml:space="preserve">9.09894561767578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41330432891846</t>
+    <t xml:space="preserve">9.41330528259277</t>
   </si>
   <si>
     <t xml:space="preserve">9.308518409729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27358913421631</t>
+    <t xml:space="preserve">9.27359008789062</t>
   </si>
   <si>
     <t xml:space="preserve">9.39584064483643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72766494750977</t>
+    <t xml:space="preserve">9.72766399383545</t>
   </si>
   <si>
     <t xml:space="preserve">9.55301952362061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.622878074646</t>
+    <t xml:space="preserve">9.62287712097168</t>
   </si>
   <si>
     <t xml:space="preserve">9.91977214813232</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">9.65780639648438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64034271240234</t>
+    <t xml:space="preserve">9.64034175872803</t>
   </si>
   <si>
     <t xml:space="preserve">9.67527103424072</t>
@@ -3428,19 +3428,19 @@
     <t xml:space="preserve">9.83245086669922</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0420227050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69273567199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93723773956299</t>
+    <t xml:space="preserve">10.0420236587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69273471832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93723678588867</t>
   </si>
   <si>
     <t xml:space="preserve">9.97216606140137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88484382629395</t>
+    <t xml:space="preserve">9.88484287261963</t>
   </si>
   <si>
     <t xml:space="preserve">9.8673791885376</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">10.0944166183472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0769519805908</t>
+    <t xml:space="preserve">10.0769510269165</t>
   </si>
   <si>
     <t xml:space="preserve">9.79752159118652</t>
@@ -3473,25 +3473,25 @@
     <t xml:space="preserve">10.7405986785889</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7580623626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9152421951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0200281143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3518524169922</t>
+    <t xml:space="preserve">10.7580633163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9152431488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0200290679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3518514633179</t>
   </si>
   <si>
     <t xml:space="preserve">11.0025644302368</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9676351547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5310258865356</t>
+    <t xml:space="preserve">10.9676361083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.53102684021</t>
   </si>
   <si>
     <t xml:space="preserve">10.6183471679688</t>
@@ -3503,28 +3503,28 @@
     <t xml:space="preserve">10.6008834838867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5659551620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4786329269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1817388534546</t>
+    <t xml:space="preserve">10.565954208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4786319732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1817378997803</t>
   </si>
   <si>
     <t xml:space="preserve">10.216667175293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0245590209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84991455078125</t>
+    <t xml:space="preserve">10.0245580673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84991359710693</t>
   </si>
   <si>
     <t xml:space="preserve">10.1118803024292</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5834178924561</t>
+    <t xml:space="preserve">10.5834188461304</t>
   </si>
   <si>
     <t xml:space="preserve">10.3563814163208</t>
@@ -3551,22 +3551,22 @@
     <t xml:space="preserve">11.8757839202881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0678911209106</t>
+    <t xml:space="preserve">12.067892074585</t>
   </si>
   <si>
     <t xml:space="preserve">12.0329627990723</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4650430679321</t>
+    <t xml:space="preserve">13.4650440216064</t>
   </si>
   <si>
     <t xml:space="preserve">13.1681480407715</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0633630752563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8712539672852</t>
+    <t xml:space="preserve">13.063362121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8712530136108</t>
   </si>
   <si>
     <t xml:space="preserve">12.6442165374756</t>
@@ -4608,6 +4608,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.47999954223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78999996185303</t>
   </si>
 </sst>
 </file>
@@ -69764,7 +69767,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.6495601852</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>78034</v>
@@ -69785,6 +69788,32 @@
         <v>1487</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6494097222</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>305083</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>9.80000019073486</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>9.61999988555908</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>9.61999988555908</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>9.78999996185303</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>1532</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARR.MI.xlsx
+++ b/data/MARR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="1536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1537" uniqueCount="1537">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,16 +44,16 @@
     <t xml:space="preserve">MARR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2894010543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1812982559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9939212799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9506797790527</t>
+    <t xml:space="preserve">13.2894020080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.181300163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9939193725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9506807327271</t>
   </si>
   <si>
     <t xml:space="preserve">12.5903387069702</t>
@@ -71,82 +71,82 @@
     <t xml:space="preserve">12.4462013244629</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9849624633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0858602523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6462421417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2155847549438</t>
+    <t xml:space="preserve">11.9849634170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0858612060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6462430953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2155828475952</t>
   </si>
   <si>
     <t xml:space="preserve">12.8353710174561</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6768188476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5615110397339</t>
+    <t xml:space="preserve">12.6768198013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5615100860596</t>
   </si>
   <si>
     <t xml:space="preserve">12.5543041229248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6407861709595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7200613021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.97230052948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7777166366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3308925628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5110645294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2948579788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4084167480469</t>
+    <t xml:space="preserve">12.6407852172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7200603485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9722995758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7777156829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3308944702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5110626220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2948570251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4084177017212</t>
   </si>
   <si>
     <t xml:space="preserve">11.4516582489014</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8840675354004</t>
+    <t xml:space="preserve">11.8840684890747</t>
   </si>
   <si>
     <t xml:space="preserve">11.5885877609253</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8912744522095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9273090362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0426187515259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2011690139771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3957548141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7056465148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6047525405884</t>
+    <t xml:space="preserve">11.8912754058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9273080825806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0426177978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2011680603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3957538604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7056446075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6047515869141</t>
   </si>
   <si>
     <t xml:space="preserve">12.5759248733521</t>
@@ -155,10 +155,10 @@
     <t xml:space="preserve">12.9362668991089</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1596775054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.943473815918</t>
+    <t xml:space="preserve">13.1596765518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9434728622437</t>
   </si>
   <si>
     <t xml:space="preserve">13.0731954574585</t>
@@ -176,25 +176,25 @@
     <t xml:space="preserve">12.3597183227539</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6696119308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8137493133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6984415054321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8714036941528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4534072875977</t>
+    <t xml:space="preserve">12.6696128845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8137483596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6984405517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8714046478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.453408241272</t>
   </si>
   <si>
     <t xml:space="preserve">12.3453054428101</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6840267181396</t>
+    <t xml:space="preserve">12.6840286254883</t>
   </si>
   <si>
     <t xml:space="preserve">12.7560949325562</t>
@@ -215,16 +215,16 @@
     <t xml:space="preserve">13.1885042190552</t>
   </si>
   <si>
-    <t xml:space="preserve">13.260573387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7073965072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4911890029907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3470554351807</t>
+    <t xml:space="preserve">13.2605724334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7073955535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.491189956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3470544815063</t>
   </si>
   <si>
     <t xml:space="preserve">13.001127243042</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">13.1020231246948</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8065423965454</t>
+    <t xml:space="preserve">12.8065433502197</t>
   </si>
   <si>
     <t xml:space="preserve">13.2821931838989</t>
@@ -260,10 +260,10 @@
     <t xml:space="preserve">12.8930234909058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9074382781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0227470397949</t>
+    <t xml:space="preserve">12.9074373245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0227489471436</t>
   </si>
   <si>
     <t xml:space="preserve">12.6624059677124</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">12.8786106109619</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6335802078247</t>
+    <t xml:space="preserve">12.6335783004761</t>
   </si>
   <si>
     <t xml:space="preserve">12.7488870620728</t>
@@ -281,22 +281,22 @@
     <t xml:space="preserve">13.0258741378784</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0183877944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.25794506073</t>
+    <t xml:space="preserve">13.0183868408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2579441070557</t>
   </si>
   <si>
     <t xml:space="preserve">13.2504587173462</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4301271438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4825305938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3103475570679</t>
+    <t xml:space="preserve">13.4301261901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4825296401978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3103485107422</t>
   </si>
   <si>
     <t xml:space="preserve">13.2654323577881</t>
@@ -308,13 +308,13 @@
     <t xml:space="preserve">13.3702373504639</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2878904342651</t>
+    <t xml:space="preserve">13.2878894805908</t>
   </si>
   <si>
     <t xml:space="preserve">13.2729187011719</t>
   </si>
   <si>
-    <t xml:space="preserve">13.280403137207</t>
+    <t xml:space="preserve">13.2804040908813</t>
   </si>
   <si>
     <t xml:space="preserve">12.8012924194336</t>
@@ -323,28 +323,28 @@
     <t xml:space="preserve">12.8836374282837</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6141376495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3146915435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.44944190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8087778091431</t>
+    <t xml:space="preserve">12.6141366958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3146924972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4494428634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8087787628174</t>
   </si>
   <si>
     <t xml:space="preserve">12.7938051223755</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0782785415649</t>
+    <t xml:space="preserve">13.0782775878906</t>
   </si>
   <si>
     <t xml:space="preserve">12.4419574737549</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7831773757935</t>
+    <t xml:space="preserve">11.7831764221191</t>
   </si>
   <si>
     <t xml:space="preserve">12.2847471237183</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">12.7339153289795</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4226388931274</t>
+    <t xml:space="preserve">13.4226398468018</t>
   </si>
   <si>
     <t xml:space="preserve">13.5274457931519</t>
@@ -365,76 +365,76 @@
     <t xml:space="preserve">13.4525852203369</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3328075408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7595157623291</t>
+    <t xml:space="preserve">13.3328065872192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7595167160034</t>
   </si>
   <si>
     <t xml:space="preserve">13.7295722961426</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7220859527588</t>
+    <t xml:space="preserve">13.7220849990845</t>
   </si>
   <si>
     <t xml:space="preserve">13.53493309021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4900159835815</t>
+    <t xml:space="preserve">13.4900150299072</t>
   </si>
   <si>
     <t xml:space="preserve">13.7370586395264</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0140428543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7071123123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8493490219116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.111364364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9766149520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0814199447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7445449829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9990720748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5049886703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6397380828857</t>
+    <t xml:space="preserve">14.0140438079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7071142196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8493499755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1113653182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9766159057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0814189910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7445459365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9990749359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5049896240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6397371292114</t>
   </si>
   <si>
     <t xml:space="preserve">13.6621961593628</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6097946166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3477802276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4151544570923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2205152511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0857639312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.100736618042</t>
+    <t xml:space="preserve">13.6097936630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3477792739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.415153503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2205142974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0857629776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1007375717163</t>
   </si>
   <si>
     <t xml:space="preserve">13.0633068084717</t>
@@ -446,25 +446,25 @@
     <t xml:space="preserve">13.1456518173218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9285554885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2055425643921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1082239151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1980562210083</t>
+    <t xml:space="preserve">12.9285564422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2055416107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1082229614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.198055267334</t>
   </si>
   <si>
     <t xml:space="preserve">13.1157093048096</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0109024047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9135828018188</t>
+    <t xml:space="preserve">13.0109014511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9135837554932</t>
   </si>
   <si>
     <t xml:space="preserve">12.8611812591553</t>
@@ -479,22 +479,22 @@
     <t xml:space="preserve">13.4076671600342</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3552656173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2130289077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3402919769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9659862518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8761529922485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8312339782715</t>
+    <t xml:space="preserve">13.3552665710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2130279541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.340292930603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9659843444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8761539459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8312349319458</t>
   </si>
   <si>
     <t xml:space="preserve">12.9809589385986</t>
@@ -503,13 +503,13 @@
     <t xml:space="preserve">12.7638607025146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7114562988281</t>
+    <t xml:space="preserve">12.7114572525024</t>
   </si>
   <si>
     <t xml:space="preserve">12.8686676025391</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7563753128052</t>
+    <t xml:space="preserve">12.7563743591309</t>
   </si>
   <si>
     <t xml:space="preserve">12.7488889694214</t>
@@ -521,19 +521,19 @@
     <t xml:space="preserve">12.5767059326172</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5467624664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5317907333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5617361068726</t>
+    <t xml:space="preserve">12.5467615127563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5317897796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5617351531982</t>
   </si>
   <si>
     <t xml:space="preserve">12.5542497634888</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4194993972778</t>
+    <t xml:space="preserve">12.4194984436035</t>
   </si>
   <si>
     <t xml:space="preserve">12.2772617340088</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">12.4719009399414</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5018472671509</t>
+    <t xml:space="preserve">12.5018463134766</t>
   </si>
   <si>
     <t xml:space="preserve">12.3970394134521</t>
@@ -554,10 +554,10 @@
     <t xml:space="preserve">12.3596086502075</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4943590164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3820667266846</t>
+    <t xml:space="preserve">12.4943599700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3820686340332</t>
   </si>
   <si>
     <t xml:space="preserve">12.4045257568359</t>
@@ -569,67 +569,67 @@
     <t xml:space="preserve">12.1649694442749</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2548046112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3371505737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3221788406372</t>
+    <t xml:space="preserve">12.2548036575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3371496200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3221778869629</t>
   </si>
   <si>
     <t xml:space="preserve">12.7264289855957</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6740274429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7863178253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0932521820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9510116577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1306819915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9884462356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.138165473938</t>
+    <t xml:space="preserve">12.6740264892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7863187789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0932512283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9510135650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1306810379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9884452819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1381664276123</t>
   </si>
   <si>
     <t xml:space="preserve">13.1606254577637</t>
   </si>
   <si>
-    <t xml:space="preserve">13.183084487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1681108474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2280015945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.00341796875</t>
+    <t xml:space="preserve">13.1830854415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1681127548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2280006408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0034170150757</t>
   </si>
   <si>
     <t xml:space="preserve">13.1755990982056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4001808166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3852100372314</t>
+    <t xml:space="preserve">13.4001817703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3852109909058</t>
   </si>
   <si>
     <t xml:space="preserve">13.8643226623535</t>
   </si>
   <si>
-    <t xml:space="preserve">13.91672706604</t>
+    <t xml:space="preserve">13.9167261123657</t>
   </si>
   <si>
     <t xml:space="preserve">13.5199594497681</t>
@@ -638,79 +638,79 @@
     <t xml:space="preserve">13.4450988769531</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3627510070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4600715637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5124740600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.437614440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8268899917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6247682571411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8044328689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7819728851318</t>
+    <t xml:space="preserve">13.3627519607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.460072517395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5124731063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4376134872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8268909454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6247673034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8044338226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7819747924805</t>
   </si>
   <si>
     <t xml:space="preserve">13.6996269226074</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8418655395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.677170753479</t>
+    <t xml:space="preserve">13.8418645858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6771697998047</t>
   </si>
   <si>
     <t xml:space="preserve">13.8568382263184</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7670011520386</t>
+    <t xml:space="preserve">13.7670021057129</t>
   </si>
   <si>
     <t xml:space="preserve">13.5648784637451</t>
   </si>
   <si>
-    <t xml:space="preserve">13.89426612854</t>
+    <t xml:space="preserve">13.8942670822144</t>
   </si>
   <si>
     <t xml:space="preserve">14.3359498977661</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5605335235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5156154632568</t>
+    <t xml:space="preserve">14.5605354309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5156173706055</t>
   </si>
   <si>
     <t xml:space="preserve">14.6952838897705</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9722690582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9348411560059</t>
+    <t xml:space="preserve">14.9722719192505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9348392486572</t>
   </si>
   <si>
     <t xml:space="preserve">14.9423236846924</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8225469589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2043380737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7133979797363</t>
+    <t xml:space="preserve">14.8225479125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2043409347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.713397026062</t>
   </si>
   <si>
     <t xml:space="preserve">15.1369647979736</t>
@@ -719,22 +719,22 @@
     <t xml:space="preserve">15.1594228744507</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2866888046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3615503311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2267980575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3465766906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6834554672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7208843231201</t>
+    <t xml:space="preserve">15.2866868972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3615493774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2267990112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3465795516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6834545135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7208814620972</t>
   </si>
   <si>
     <t xml:space="preserve">15.533730506897</t>
@@ -749,28 +749,28 @@
     <t xml:space="preserve">15.1968536376953</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5487051010132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4214382171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6011056900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6460199356079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.735857963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5861330032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9080371856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.42458152771</t>
+    <t xml:space="preserve">15.5487012863159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.421441078186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6011037826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6460218429565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7358570098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5861339569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9080400466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4245796203613</t>
   </si>
   <si>
     <t xml:space="preserve">16.1251354217529</t>
@@ -785,49 +785,49 @@
     <t xml:space="preserve">16.3272609710693</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2598857879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.267370223999</t>
+    <t xml:space="preserve">16.2598876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2673721313477</t>
   </si>
   <si>
     <t xml:space="preserve">16.5967617034912</t>
   </si>
   <si>
-    <t xml:space="preserve">16.78391456604</t>
+    <t xml:space="preserve">16.7839164733887</t>
   </si>
   <si>
     <t xml:space="preserve">16.6641368865967</t>
   </si>
   <si>
-    <t xml:space="preserve">16.521900177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4470386505127</t>
+    <t xml:space="preserve">16.5218982696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4470367431641</t>
   </si>
   <si>
     <t xml:space="preserve">16.6416759490967</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0758724212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7988872528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7464847564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8737506866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9560966491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1058177947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3946380615234</t>
+    <t xml:space="preserve">17.0758762359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7988891601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7464866638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8737468719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9560947418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1058197021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3946361541748</t>
   </si>
   <si>
     <t xml:space="preserve">16.5069274902344</t>
@@ -836,10 +836,10 @@
     <t xml:space="preserve">16.6847534179688</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1950397491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1641120910645</t>
+    <t xml:space="preserve">17.1950359344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1641139984131</t>
   </si>
   <si>
     <t xml:space="preserve">17.0094814300537</t>
@@ -854,25 +854,25 @@
     <t xml:space="preserve">16.8471183776855</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0249423980713</t>
+    <t xml:space="preserve">17.0249462127686</t>
   </si>
   <si>
     <t xml:space="preserve">16.9398975372314</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7698001861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9940166473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1254539489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9553623199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5455875396729</t>
+    <t xml:space="preserve">16.7698020935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9940185546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.125452041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.955358505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5455856323242</t>
   </si>
   <si>
     <t xml:space="preserve">16.7156810760498</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">16.8548488616943</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7466087341309</t>
+    <t xml:space="preserve">16.7466068267822</t>
   </si>
   <si>
     <t xml:space="preserve">17.0404090881348</t>
@@ -890,7 +890,7 @@
     <t xml:space="preserve">16.731143951416</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5378551483154</t>
+    <t xml:space="preserve">16.5378532409668</t>
   </si>
   <si>
     <t xml:space="preserve">16.5687808990479</t>
@@ -899,34 +899,34 @@
     <t xml:space="preserve">16.6229019165039</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7079486846924</t>
+    <t xml:space="preserve">16.707950592041</t>
   </si>
   <si>
     <t xml:space="preserve">16.7234115600586</t>
   </si>
   <si>
-    <t xml:space="preserve">16.182201385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0894222259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0816898345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1590042114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9347896575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2363224029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0739593505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9966449737549</t>
+    <t xml:space="preserve">16.1822032928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0894203186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0816879272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1590061187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9347906112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2363204956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0739612579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9966430664062</t>
   </si>
   <si>
     <t xml:space="preserve">16.3909549713135</t>
@@ -938,58 +938,58 @@
     <t xml:space="preserve">16.8935070037842</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2414264678955</t>
+    <t xml:space="preserve">17.2414283752441</t>
   </si>
   <si>
     <t xml:space="preserve">17.0558700561523</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2878170013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2955493927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3960609436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8316516876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2800903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7002201080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.553316116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.483736038208</t>
+    <t xml:space="preserve">17.2878189086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2955513000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3960590362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8316535949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.280086517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7002182006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5533180236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4837341308594</t>
   </si>
   <si>
     <t xml:space="preserve">16.7775344848633</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5146598815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3832225799561</t>
+    <t xml:space="preserve">16.5146617889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3832206726074</t>
   </si>
   <si>
     <t xml:space="preserve">16.3986835479736</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2749786376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2285919189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0584983825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9657163619995</t>
+    <t xml:space="preserve">16.2749805450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2285900115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0584945678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9657173156738</t>
   </si>
   <si>
     <t xml:space="preserve">15.9502544403076</t>
@@ -998,7 +998,7 @@
     <t xml:space="preserve">16.0353012084961</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2827110290527</t>
+    <t xml:space="preserve">16.2827129364014</t>
   </si>
   <si>
     <t xml:space="preserve">16.4141464233398</t>
@@ -1010,25 +1010,25 @@
     <t xml:space="preserve">16.5919761657715</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9321670532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0481395721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2646236419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9476299285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0713329315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0636043548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0790634155273</t>
+    <t xml:space="preserve">16.932165145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0481376647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2646255493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9476280212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0713310241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0636005401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.079065322876</t>
   </si>
   <si>
     <t xml:space="preserve">17.2723541259766</t>
@@ -1040,10 +1040,10 @@
     <t xml:space="preserve">17.3728637695312</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3187427520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5584201812744</t>
+    <t xml:space="preserve">17.3187446594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.558422088623</t>
   </si>
   <si>
     <t xml:space="preserve">17.5893516540527</t>
@@ -1052,19 +1052,19 @@
     <t xml:space="preserve">17.4656448364258</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7207870483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5738849639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5429611206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6975936889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1073627471924</t>
+    <t xml:space="preserve">17.7207851409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5738868713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5429592132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6975917816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1073665618896</t>
   </si>
   <si>
     <t xml:space="preserve">18.0377807617188</t>
@@ -1082,28 +1082,28 @@
     <t xml:space="preserve">17.3110122680664</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1099910736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.357400894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1795749664307</t>
+    <t xml:space="preserve">17.109992980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3574028015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1795768737793</t>
   </si>
   <si>
     <t xml:space="preserve">17.1409168243408</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0867958068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8857727050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6151695251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.530122756958</t>
+    <t xml:space="preserve">17.0867977142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8857746124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6151676177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5301208496094</t>
   </si>
   <si>
     <t xml:space="preserve">16.352294921875</t>
@@ -1112,10 +1112,10 @@
     <t xml:space="preserve">16.0430335998535</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8265476226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.927059173584</t>
+    <t xml:space="preserve">15.826548576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9270620346069</t>
   </si>
   <si>
     <t xml:space="preserve">16.1976661682129</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">16.7852649688721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9630928039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8084621429443</t>
+    <t xml:space="preserve">16.9630908966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8084602355957</t>
   </si>
   <si>
     <t xml:space="preserve">16.9244327545166</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4218788146973</t>
+    <t xml:space="preserve">16.4218807220459</t>
   </si>
   <si>
     <t xml:space="preserve">16.0507640838623</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">16.6383647918701</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7929973602295</t>
+    <t xml:space="preserve">16.7929992675781</t>
   </si>
   <si>
     <t xml:space="preserve">16.4064159393311</t>
@@ -1169,43 +1169,43 @@
     <t xml:space="preserve">17.3805961608887</t>
   </si>
   <si>
-    <t xml:space="preserve">17.488842010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5506916046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6898593902588</t>
+    <t xml:space="preserve">17.4888401031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5506935119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6898612976074</t>
   </si>
   <si>
     <t xml:space="preserve">17.4115257263184</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6434707641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2568893432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2259674072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5043029785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4991970062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9785556793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3445625305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2981739044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.901237487793</t>
+    <t xml:space="preserve">17.6434688568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.256893157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2259635925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.504301071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.499195098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9785537719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3445644378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2981758117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9012355804443</t>
   </si>
   <si>
     <t xml:space="preserve">16.6538276672363</t>
@@ -1217,16 +1217,16 @@
     <t xml:space="preserve">16.3136386871338</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4269886016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4475555419922</t>
+    <t xml:space="preserve">17.4269847869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4475574493408</t>
   </si>
   <si>
     <t xml:space="preserve">18.3857040405273</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8805236816406</t>
+    <t xml:space="preserve">18.8805255889893</t>
   </si>
   <si>
     <t xml:space="preserve">19.1433963775635</t>
@@ -1235,40 +1235,40 @@
     <t xml:space="preserve">19.0042285919189</t>
   </si>
   <si>
-    <t xml:space="preserve">18.911449432373</t>
+    <t xml:space="preserve">18.9114513397217</t>
   </si>
   <si>
     <t xml:space="preserve">18.6949653625488</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6795043945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7413539886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6640396118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7877464294434</t>
+    <t xml:space="preserve">18.6795024871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7413558959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.664041519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7877445220947</t>
   </si>
   <si>
     <t xml:space="preserve">19.2516384124756</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4371967315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3444213867188</t>
+    <t xml:space="preserve">19.4371948242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3444194793701</t>
   </si>
   <si>
     <t xml:space="preserve">19.4062728881836</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5609016418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3289546966553</t>
+    <t xml:space="preserve">19.5609035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3289566040039</t>
   </si>
   <si>
     <t xml:space="preserve">19.1743240356445</t>
@@ -1277,19 +1277,19 @@
     <t xml:space="preserve">19.1124706268311</t>
   </si>
   <si>
-    <t xml:space="preserve">19.158863067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2825679779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2361755371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.205249786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2671031951904</t>
+    <t xml:space="preserve">19.1588611602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.282564163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.236177444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2052516937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2671051025391</t>
   </si>
   <si>
     <t xml:space="preserve">19.5299777984619</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">19.638219833374</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5918312072754</t>
+    <t xml:space="preserve">19.5918292999268</t>
   </si>
   <si>
     <t xml:space="preserve">19.4835872650146</t>
@@ -1307,103 +1307,103 @@
     <t xml:space="preserve">19.5145130157471</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4526615142822</t>
+    <t xml:space="preserve">19.4526596069336</t>
   </si>
   <si>
     <t xml:space="preserve">19.607292175293</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1382904052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3547744750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0764389038086</t>
+    <t xml:space="preserve">18.1382923126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3547763824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0764408111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0300464630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1737804412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9502010345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3654193878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.205717086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6209354400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.509147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5889987945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.557056427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4931793212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1578102111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4292984008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6848163604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6369094848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4133262634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.461238861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3175086975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8064708709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8224411010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7106513977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9182643890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9661693572998</t>
   </si>
   <si>
     <t xml:space="preserve">18.0300483703613</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1737804412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9501991271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3654193878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.205717086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6209354400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5091495513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5889987945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5570583343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4931774139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1578102111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4292984008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6848163604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6369075775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4133281707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.461238861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3175106048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8064708709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8224391937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7106513977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9182624816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9661712646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.03005027771</t>
-  </si>
-  <si>
     <t xml:space="preserve">17.8863220214844</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9981117248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3973579406738</t>
+    <t xml:space="preserve">17.9981098175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3973598480225</t>
   </si>
   <si>
     <t xml:space="preserve">18.5251197814941</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4452686309814</t>
+    <t xml:space="preserve">18.4452667236328</t>
   </si>
   <si>
     <t xml:space="preserve">19.1479454040527</t>
@@ -1412,52 +1412,52 @@
     <t xml:space="preserve">19.1639137268066</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0201854705811</t>
+    <t xml:space="preserve">19.0201873779297</t>
   </si>
   <si>
     <t xml:space="preserve">18.8604888916016</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7806377410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5730266571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.06809425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7646656036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4772090911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7007865905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2437648773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4513740539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4992828369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2118244171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1319732666016</t>
+    <t xml:space="preserve">18.7806358337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5730304718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0680923461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7646675109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4772071838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7007884979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.243766784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4513759613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4992847442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2118263244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1319713592529</t>
   </si>
   <si>
     <t xml:space="preserve">19.0042133331299</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1160049438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0361576080322</t>
+    <t xml:space="preserve">19.1160068511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0361557006836</t>
   </si>
   <si>
     <t xml:space="preserve">19.1798858642578</t>
@@ -1475,16 +1475,16 @@
     <t xml:space="preserve">19.7228622436523</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4673442840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3874931335449</t>
+    <t xml:space="preserve">19.467342376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3874950408936</t>
   </si>
   <si>
     <t xml:space="preserve">19.5631618499756</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8825626373291</t>
+    <t xml:space="preserve">19.8825588226318</t>
   </si>
   <si>
     <t xml:space="preserve">20.3616619110107</t>
@@ -1493,28 +1493,28 @@
     <t xml:space="preserve">20.4415092468262</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2658386230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7609081268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0962772369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8247871398926</t>
+    <t xml:space="preserve">20.2658405303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7609062194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0962753295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8247852325439</t>
   </si>
   <si>
     <t xml:space="preserve">20.249870300293</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4734497070312</t>
+    <t xml:space="preserve">20.4734477996826</t>
   </si>
   <si>
     <t xml:space="preserve">20.1540508270264</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1700229644775</t>
+    <t xml:space="preserve">20.1700210571289</t>
   </si>
   <si>
     <t xml:space="preserve">19.7548007965088</t>
@@ -1529,31 +1529,31 @@
     <t xml:space="preserve">18.8125743865967</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7327251434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3813877105713</t>
+    <t xml:space="preserve">18.7327289581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3813858032227</t>
   </si>
   <si>
     <t xml:space="preserve">18.2536296844482</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9342308044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3494491577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9243659973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7486972808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1258716583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7905006408691</t>
+    <t xml:space="preserve">17.9342288970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3494472503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9243679046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7486953735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1258697509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7905025482178</t>
   </si>
   <si>
     <t xml:space="preserve">17.4391613006592</t>
@@ -1565,16 +1565,16 @@
     <t xml:space="preserve">17.2155838012695</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9760360717773</t>
+    <t xml:space="preserve">16.976037979126</t>
   </si>
   <si>
     <t xml:space="preserve">17.550952911377</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8961849212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0718517303467</t>
+    <t xml:space="preserve">16.896183013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0718536376953</t>
   </si>
   <si>
     <t xml:space="preserve">16.9281253814697</t>
@@ -1586,94 +1586,94 @@
     <t xml:space="preserve">17.0558853149414</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1836452484131</t>
+    <t xml:space="preserve">17.1836433410645</t>
   </si>
   <si>
     <t xml:space="preserve">17.4551315307617</t>
   </si>
   <si>
-    <t xml:space="preserve">16.816333770752</t>
+    <t xml:space="preserve">16.8163356781006</t>
   </si>
   <si>
     <t xml:space="preserve">16.3532085418701</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9858999252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0976886749268</t>
+    <t xml:space="preserve">15.9859008789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0976905822754</t>
   </si>
   <si>
     <t xml:space="preserve">16.1136589050293</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4269523620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3311319351196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6505308151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4748620986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4429216384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7703046798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8421697616577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7383642196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4490261077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2733612060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1615695953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3212699890137</t>
+    <t xml:space="preserve">15.4269504547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3311309814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6505317687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4748611450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4429225921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7703037261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8421688079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7383651733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4490280151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2733554840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1615715026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.321268081665</t>
   </si>
   <si>
     <t xml:space="preserve">16.4809665679932</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6246967315674</t>
+    <t xml:space="preserve">16.6246948242188</t>
   </si>
   <si>
     <t xml:space="preserve">16.768424987793</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1676731109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3433437347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2794628143311</t>
+    <t xml:space="preserve">17.1676750183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3433418273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2794609069824</t>
   </si>
   <si>
     <t xml:space="preserve">16.9440956115723</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0079727172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6406650543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.241418838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5608177185059</t>
+    <t xml:space="preserve">17.0079746246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6406669616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2414169311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5608158111572</t>
   </si>
   <si>
     <t xml:space="preserve">16.7045459747314</t>
@@ -1682,37 +1682,37 @@
     <t xml:space="preserve">16.8482761383057</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3752841949463</t>
+    <t xml:space="preserve">17.375280380249</t>
   </si>
   <si>
     <t xml:space="preserve">17.103796005249</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8802127838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9121551513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8642463684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.720516204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6885738372803</t>
+    <t xml:space="preserve">16.8802165985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9121570587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8642444610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7205142974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6885719299316</t>
   </si>
   <si>
     <t xml:space="preserve">16.6087265014648</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7364845275879</t>
+    <t xml:space="preserve">16.7364864349365</t>
   </si>
   <si>
     <t xml:space="preserve">16.3052978515625</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8980627059937</t>
+    <t xml:space="preserve">15.8980646133423</t>
   </si>
   <si>
     <t xml:space="preserve">16.193510055542</t>
@@ -1721,7 +1721,7 @@
     <t xml:space="preserve">16.2094764709473</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3851470947266</t>
+    <t xml:space="preserve">16.3851490020752</t>
   </si>
   <si>
     <t xml:space="preserve">16.2893295288086</t>
@@ -1730,22 +1730,22 @@
     <t xml:space="preserve">16.2573890686035</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2254486083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9140338897705</t>
+    <t xml:space="preserve">16.2254505157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9140357971191</t>
   </si>
   <si>
     <t xml:space="preserve">16.4170875549316</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5288772583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7843971252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5767860412598</t>
+    <t xml:space="preserve">16.5288753509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7843952178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5767879486084</t>
   </si>
   <si>
     <t xml:space="preserve">16.3691787719727</t>
@@ -1754,16 +1754,16 @@
     <t xml:space="preserve">16.1775379180908</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4889545440674</t>
+    <t xml:space="preserve">16.4889526367188</t>
   </si>
   <si>
     <t xml:space="preserve">16.2494029998779</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3292541503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4091033935547</t>
+    <t xml:space="preserve">16.329252243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4091014862061</t>
   </si>
   <si>
     <t xml:space="preserve">16.1695518493652</t>
@@ -1778,13 +1778,13 @@
     <t xml:space="preserve">16.6486530303955</t>
   </si>
   <si>
-    <t xml:space="preserve">17.287446975708</t>
+    <t xml:space="preserve">17.2874488830566</t>
   </si>
   <si>
     <t xml:space="preserve">17.0878238677979</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0478992462158</t>
+    <t xml:space="preserve">17.0479011535645</t>
   </si>
   <si>
     <t xml:space="preserve">16.808349609375</t>
@@ -1793,13 +1793,13 @@
     <t xml:space="preserve">16.9680500030518</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7285041809082</t>
+    <t xml:space="preserve">16.7285022735596</t>
   </si>
   <si>
     <t xml:space="preserve">16.8882007598877</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1277484893799</t>
+    <t xml:space="preserve">17.1277503967285</t>
   </si>
   <si>
     <t xml:space="preserve">16.8793506622314</t>
@@ -1808,7 +1808,7 @@
     <t xml:space="preserve">17.0452404022217</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9208240509033</t>
+    <t xml:space="preserve">16.9208221435547</t>
   </si>
   <si>
     <t xml:space="preserve">16.7964038848877</t>
@@ -1817,7 +1817,7 @@
     <t xml:space="preserve">17.2111301422119</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1281871795654</t>
+    <t xml:space="preserve">17.1281852722168</t>
   </si>
   <si>
     <t xml:space="preserve">17.1696586608887</t>
@@ -1826,25 +1826,25 @@
     <t xml:space="preserve">17.418493270874</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3770236968994</t>
+    <t xml:space="preserve">17.3770217895508</t>
   </si>
   <si>
     <t xml:space="preserve">17.4599647521973</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2940769195557</t>
+    <t xml:space="preserve">17.294075012207</t>
   </si>
   <si>
     <t xml:space="preserve">16.9622955322266</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7549324035645</t>
+    <t xml:space="preserve">16.7549304962158</t>
   </si>
   <si>
     <t xml:space="preserve">16.6305122375488</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3402061462402</t>
+    <t xml:space="preserve">16.3402080535889</t>
   </si>
   <si>
     <t xml:space="preserve">16.4895057678223</t>
@@ -1853,16 +1853,16 @@
     <t xml:space="preserve">16.5392742156982</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7088012695312</t>
+    <t xml:space="preserve">17.7088031768799</t>
   </si>
   <si>
     <t xml:space="preserve">17.6673278808594</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5014400482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.542911529541</t>
+    <t xml:space="preserve">17.5014381408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5429096221924</t>
   </si>
   <si>
     <t xml:space="preserve">17.2526035308838</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">16.2406711578369</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1743144989014</t>
+    <t xml:space="preserve">16.1743125915527</t>
   </si>
   <si>
     <t xml:space="preserve">16.2738513946533</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">16.3070259094238</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8591232299805</t>
+    <t xml:space="preserve">15.8591241836548</t>
   </si>
   <si>
     <t xml:space="preserve">15.7264089584351</t>
@@ -1907,7 +1907,7 @@
     <t xml:space="preserve">15.5273418426514</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4278106689453</t>
+    <t xml:space="preserve">15.427809715271</t>
   </si>
   <si>
     <t xml:space="preserve">15.6600532531738</t>
@@ -1919,22 +1919,22 @@
     <t xml:space="preserve">15.3614540100098</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6932325363159</t>
+    <t xml:space="preserve">15.6932334899902</t>
   </si>
   <si>
     <t xml:space="preserve">15.6102886199951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4609870910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4443998336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3780422210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2950983047485</t>
+    <t xml:space="preserve">15.4609861373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4443988800049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.378041267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2950973510742</t>
   </si>
   <si>
     <t xml:space="preserve">15.925479888916</t>
@@ -1952,10 +1952,10 @@
     <t xml:space="preserve">16.6719875335693</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9576358795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0867118835449</t>
+    <t xml:space="preserve">17.9576377868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0867137908936</t>
   </si>
   <si>
     <t xml:space="preserve">17.3355464935303</t>
@@ -1973,22 +1973,22 @@
     <t xml:space="preserve">15.8757133483887</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9088897705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1577243804932</t>
+    <t xml:space="preserve">15.9088916778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1577262878418</t>
   </si>
   <si>
     <t xml:space="preserve">16.1411361694336</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4729194641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7595872879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.676643371582</t>
+    <t xml:space="preserve">16.4729175567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7595891952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6766443252563</t>
   </si>
   <si>
     <t xml:space="preserve">15.5936994552612</t>
@@ -2006,7 +2006,7 @@
     <t xml:space="preserve">15.8425340652466</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3567943572998</t>
+    <t xml:space="preserve">16.3567924499512</t>
   </si>
   <si>
     <t xml:space="preserve">16.3236179351807</t>
@@ -2045,7 +2045,7 @@
     <t xml:space="preserve">13.93479347229</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6361923217773</t>
+    <t xml:space="preserve">13.636191368103</t>
   </si>
   <si>
     <t xml:space="preserve">13.4371242523193</t>
@@ -2057,13 +2057,13 @@
     <t xml:space="preserve">13.3873567581177</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7616310119629</t>
+    <t xml:space="preserve">11.7616300582886</t>
   </si>
   <si>
     <t xml:space="preserve">11.9607000350952</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4251918792725</t>
+    <t xml:space="preserve">12.4251909255981</t>
   </si>
   <si>
     <t xml:space="preserve">11.0317125320435</t>
@@ -2105,16 +2105,16 @@
     <t xml:space="preserve">10.9155883789062</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6667528152466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.202260017395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.451096534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5174522399902</t>
+    <t xml:space="preserve">10.6667537689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2022609710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4510955810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5174531936646</t>
   </si>
   <si>
     <t xml:space="preserve">10.5340414047241</t>
@@ -2123,43 +2123,43 @@
     <t xml:space="preserve">10.4013290405273</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1524925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0529584884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97001361846924</t>
+    <t xml:space="preserve">10.1524934768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0529594421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97001457214355</t>
   </si>
   <si>
     <t xml:space="preserve">10.4676856994629</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6999320983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3017950057983</t>
+    <t xml:space="preserve">10.6999311447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.301794052124</t>
   </si>
   <si>
     <t xml:space="preserve">10.0695476531982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2520275115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.003191947937</t>
+    <t xml:space="preserve">10.2520265579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0031929016113</t>
   </si>
   <si>
     <t xml:space="preserve">10.0363702774048</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1193151473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92024707794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4557523727417</t>
+    <t xml:space="preserve">10.1193161010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92024803161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45575332641602</t>
   </si>
   <si>
     <t xml:space="preserve">9.50552082061768</t>
@@ -2168,10 +2168,10 @@
     <t xml:space="preserve">9.32304096221924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14056205749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07420539855957</t>
+    <t xml:space="preserve">9.14056301116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07420444488525</t>
   </si>
   <si>
     <t xml:space="preserve">9.68800163269043</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">10.4179182052612</t>
   </si>
   <si>
-    <t xml:space="preserve">10.99853515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.899001121521</t>
+    <t xml:space="preserve">10.9985342025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8990001678467</t>
   </si>
   <si>
     <t xml:space="preserve">10.9819450378418</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">11.595739364624</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3634939193726</t>
+    <t xml:space="preserve">11.3634929656982</t>
   </si>
   <si>
     <t xml:space="preserve">10.6833429336548</t>
@@ -2237,13 +2237,13 @@
     <t xml:space="preserve">11.2805490493774</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1810140609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3303146362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.297137260437</t>
+    <t xml:space="preserve">11.1810150146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3303155899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2971382141113</t>
   </si>
   <si>
     <t xml:space="preserve">11.0814800262451</t>
@@ -2258,13 +2258,13 @@
     <t xml:space="preserve">10.8326444625854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.849232673645</t>
+    <t xml:space="preserve">10.8492317199707</t>
   </si>
   <si>
     <t xml:space="preserve">10.5838088989258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3847408294678</t>
+    <t xml:space="preserve">10.3847398757935</t>
   </si>
   <si>
     <t xml:space="preserve">10.650164604187</t>
@@ -2288,16 +2288,16 @@
     <t xml:space="preserve">10.6169862747192</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4842758178711</t>
+    <t xml:space="preserve">10.4842748641968</t>
   </si>
   <si>
     <t xml:space="preserve">10.0197811126709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3349733352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7828769683838</t>
+    <t xml:space="preserve">10.3349723815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7828779220581</t>
   </si>
   <si>
     <t xml:space="preserve">10.6003980636597</t>
@@ -2312,10 +2312,10 @@
     <t xml:space="preserve">11.4298486709595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2307806015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8658218383789</t>
+    <t xml:space="preserve">11.2307815551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8658227920532</t>
   </si>
   <si>
     <t xml:space="preserve">11.3137273788452</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">11.396671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5127954483032</t>
+    <t xml:space="preserve">11.5127944946289</t>
   </si>
   <si>
     <t xml:space="preserve">11.8611650466919</t>
@@ -2333,7 +2333,7 @@
     <t xml:space="preserve">12.2095346450806</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9772872924805</t>
+    <t xml:space="preserve">11.9772882461548</t>
   </si>
   <si>
     <t xml:space="preserve">12.0602340698242</t>
@@ -2342,13 +2342,13 @@
     <t xml:space="preserve">12.2593021392822</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3800830841064</t>
+    <t xml:space="preserve">11.3800840377808</t>
   </si>
   <si>
     <t xml:space="preserve">11.1146574020386</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6335754394531</t>
+    <t xml:space="preserve">10.6335763931274</t>
   </si>
   <si>
     <t xml:space="preserve">10.2686157226562</t>
@@ -2363,7 +2363,7 @@
     <t xml:space="preserve">9.65482234954834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60505485534668</t>
+    <t xml:space="preserve">9.605055809021</t>
   </si>
   <si>
     <t xml:space="preserve">9.75435638427734</t>
@@ -2378,7 +2378,7 @@
     <t xml:space="preserve">12.1929454803467</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8399171829224</t>
+    <t xml:space="preserve">12.8399181365967</t>
   </si>
   <si>
     <t xml:space="preserve">13.3210000991821</t>
@@ -2399,7 +2399,7 @@
     <t xml:space="preserve">13.1053428649902</t>
   </si>
   <si>
-    <t xml:space="preserve">12.989218711853</t>
+    <t xml:space="preserve">12.9892196655273</t>
   </si>
   <si>
     <t xml:space="preserve">13.0721654891968</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">12.6740283966064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4583711624146</t>
+    <t xml:space="preserve">12.4583702087402</t>
   </si>
   <si>
     <t xml:space="preserve">12.5081377029419</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">12.7403831481934</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3754253387451</t>
+    <t xml:space="preserve">12.3754243850708</t>
   </si>
   <si>
     <t xml:space="preserve">12.4749593734741</t>
@@ -2456,10 +2456,10 @@
     <t xml:space="preserve">14.6978912353516</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7642459869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6315336227417</t>
+    <t xml:space="preserve">14.7642469406128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.631534576416</t>
   </si>
   <si>
     <t xml:space="preserve">14.1006851196289</t>
@@ -2477,22 +2477,22 @@
     <t xml:space="preserve">14.4988212585449</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3495206832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2499876022339</t>
+    <t xml:space="preserve">14.3495197296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2499885559082</t>
   </si>
   <si>
     <t xml:space="preserve">14.2333965301514</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7854948043823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0177392959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0509195327759</t>
+    <t xml:space="preserve">13.785493850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0177402496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0509204864502</t>
   </si>
   <si>
     <t xml:space="preserve">14.283164024353</t>
@@ -2504,22 +2504,22 @@
     <t xml:space="preserve">14.930136680603</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3946313858032</t>
+    <t xml:space="preserve">15.3946304321289</t>
   </si>
   <si>
     <t xml:space="preserve">15.3448629379272</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9918365478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8969593048096</t>
+    <t xml:space="preserve">15.9918384552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8969583511353</t>
   </si>
   <si>
     <t xml:space="preserve">14.9799032211304</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9135475158691</t>
+    <t xml:space="preserve">14.9135484695435</t>
   </si>
   <si>
     <t xml:space="preserve">14.9964942932129</t>
@@ -2528,7 +2528,7 @@
     <t xml:space="preserve">15.825945854187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6434659957886</t>
+    <t xml:space="preserve">15.6434679031372</t>
   </si>
   <si>
     <t xml:space="preserve">16.0250148773193</t>
@@ -2540,13 +2540,13 @@
     <t xml:space="preserve">16.0581912994385</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5605220794678</t>
+    <t xml:space="preserve">15.5605211257935</t>
   </si>
   <si>
     <t xml:space="preserve">15.0130825042725</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2619190216064</t>
+    <t xml:space="preserve">15.2619180679321</t>
   </si>
   <si>
     <t xml:space="preserve">15.2287425994873</t>
@@ -2555,25 +2555,25 @@
     <t xml:space="preserve">15.1457939147949</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4941663742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6268768310547</t>
+    <t xml:space="preserve">15.4941654205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.626877784729</t>
   </si>
   <si>
     <t xml:space="preserve">15.2121515274048</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5024604797363</t>
+    <t xml:space="preserve">15.5024614334106</t>
   </si>
   <si>
     <t xml:space="preserve">15.2702112197876</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2536220550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5439329147339</t>
+    <t xml:space="preserve">15.253623008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5439310073853</t>
   </si>
   <si>
     <t xml:space="preserve">15.5771102905273</t>
@@ -2585,13 +2585,13 @@
     <t xml:space="preserve">15.7181177139282</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7347040176392</t>
+    <t xml:space="preserve">15.7347059249878</t>
   </si>
   <si>
     <t xml:space="preserve">15.8840084075928</t>
   </si>
   <si>
-    <t xml:space="preserve">15.751296043396</t>
+    <t xml:space="preserve">15.7512941360474</t>
   </si>
   <si>
     <t xml:space="preserve">15.4361038208008</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">16.3982677459717</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5807456970215</t>
+    <t xml:space="preserve">16.5807476043701</t>
   </si>
   <si>
     <t xml:space="preserve">15.8674182891846</t>
@@ -2609,28 +2609,28 @@
     <t xml:space="preserve">16.0830764770508</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1079578399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4646224975586</t>
+    <t xml:space="preserve">16.1079597473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4646244049072</t>
   </si>
   <si>
     <t xml:space="preserve">16.622220993042</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8212890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7051639556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9042358398438</t>
+    <t xml:space="preserve">16.8212871551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7051620483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9042339324951</t>
   </si>
   <si>
     <t xml:space="preserve">16.9374122619629</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1364784240723</t>
+    <t xml:space="preserve">17.1364803314209</t>
   </si>
   <si>
     <t xml:space="preserve">17.3023719787598</t>
@@ -2660,13 +2660,13 @@
     <t xml:space="preserve">16.8876457214355</t>
   </si>
   <si>
-    <t xml:space="preserve">16.771520614624</t>
+    <t xml:space="preserve">16.7715187072754</t>
   </si>
   <si>
     <t xml:space="preserve">16.8544673919678</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2028369903564</t>
+    <t xml:space="preserve">17.2028350830078</t>
   </si>
   <si>
     <t xml:space="preserve">17.1033039093018</t>
@@ -2687,10 +2687,10 @@
     <t xml:space="preserve">16.8710556030273</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9171867370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2074947357178</t>
+    <t xml:space="preserve">15.9171848297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2074966430664</t>
   </si>
   <si>
     <t xml:space="preserve">16.2323760986328</t>
@@ -2702,7 +2702,7 @@
     <t xml:space="preserve">18.6958503723145</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1981792449951</t>
+    <t xml:space="preserve">18.1981773376465</t>
   </si>
   <si>
     <t xml:space="preserve">18.1650009155273</t>
@@ -2717,58 +2717,58 @@
     <t xml:space="preserve">17.6507415771484</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8000411987305</t>
+    <t xml:space="preserve">17.8000392913818</t>
   </si>
   <si>
     <t xml:space="preserve">17.4019050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3189582824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.020357131958</t>
+    <t xml:space="preserve">17.3189601898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0203590393066</t>
   </si>
   <si>
     <t xml:space="preserve">16.7881107330322</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9705905914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1862468719482</t>
+    <t xml:space="preserve">16.9705924987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1862487792969</t>
   </si>
   <si>
     <t xml:space="preserve">16.4065628051758</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4148559570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.049898147583</t>
+    <t xml:space="preserve">16.4148578643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0498962402344</t>
   </si>
   <si>
     <t xml:space="preserve">16.1660213470459</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5346145629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0701236724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2360153198242</t>
+    <t xml:space="preserve">17.5346164703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.070125579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2360172271729</t>
   </si>
   <si>
     <t xml:space="preserve">17.6839179992676</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4848480224609</t>
+    <t xml:space="preserve">17.4848499298096</t>
   </si>
   <si>
     <t xml:space="preserve">17.276216506958</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2424755096436</t>
+    <t xml:space="preserve">17.2424736022949</t>
   </si>
   <si>
     <t xml:space="preserve">17.3437023162842</t>
@@ -2780,10 +2780,10 @@
     <t xml:space="preserve">17.4111862182617</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3774433135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6642570495605</t>
+    <t xml:space="preserve">17.3774452209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6642589569092</t>
   </si>
   <si>
     <t xml:space="preserve">17.4449291229248</t>
@@ -2795,7 +2795,7 @@
     <t xml:space="preserve">17.1749897003174</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0400199890137</t>
+    <t xml:space="preserve">17.040018081665</t>
   </si>
   <si>
     <t xml:space="preserve">17.0062770843506</t>
@@ -2804,7 +2804,7 @@
     <t xml:space="preserve">16.9556636810303</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8628692626953</t>
+    <t xml:space="preserve">16.8628711700439</t>
   </si>
   <si>
     <t xml:space="preserve">17.090633392334</t>
@@ -2813,10 +2813,10 @@
     <t xml:space="preserve">16.8713073730469</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7532081604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2087326049805</t>
+    <t xml:space="preserve">16.7532062530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2087306976318</t>
   </si>
   <si>
     <t xml:space="preserve">16.2048892974854</t>
@@ -2831,7 +2831,7 @@
     <t xml:space="preserve">15.7915410995483</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6903162002563</t>
+    <t xml:space="preserve">15.690315246582</t>
   </si>
   <si>
     <t xml:space="preserve">15.8590278625488</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">15.4119386672974</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5216016769409</t>
+    <t xml:space="preserve">15.5216007232666</t>
   </si>
   <si>
     <t xml:space="preserve">15.0998191833496</t>
@@ -2852,10 +2852,10 @@
     <t xml:space="preserve">15.60595703125</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5806503295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8337211608887</t>
+    <t xml:space="preserve">15.5806512832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8337202072144</t>
   </si>
   <si>
     <t xml:space="preserve">16.0446109771729</t>
@@ -2864,22 +2864,22 @@
     <t xml:space="preserve">15.8758993148804</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8927698135376</t>
+    <t xml:space="preserve">15.8927707672119</t>
   </si>
   <si>
     <t xml:space="preserve">16.0108680725098</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9349460601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7662363052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7746725082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5131635665894</t>
+    <t xml:space="preserve">15.934947013855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7662372589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7746715545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5131645202637</t>
   </si>
   <si>
     <t xml:space="preserve">15.4878606796265</t>
@@ -2894,7 +2894,7 @@
     <t xml:space="preserve">15.3950662612915</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9433832168579</t>
+    <t xml:space="preserve">15.9433841705322</t>
   </si>
   <si>
     <t xml:space="preserve">16.112096786499</t>
@@ -2903,10 +2903,10 @@
     <t xml:space="preserve">16.2976818084717</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4495220184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5890855789185</t>
+    <t xml:space="preserve">16.449520111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5890846252441</t>
   </si>
   <si>
     <t xml:space="preserve">15.6987504959106</t>
@@ -2918,40 +2918,40 @@
     <t xml:space="preserve">15.9686918258667</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3145523071289</t>
+    <t xml:space="preserve">16.3145542144775</t>
   </si>
   <si>
     <t xml:space="preserve">15.9180765151978</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0193061828613</t>
+    <t xml:space="preserve">16.0193042755127</t>
   </si>
   <si>
     <t xml:space="preserve">15.5384721755981</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0154609680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1504325866699</t>
+    <t xml:space="preserve">15.0154619216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1504316329956</t>
   </si>
   <si>
     <t xml:space="preserve">15.5300350189209</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8168497085571</t>
+    <t xml:space="preserve">15.8168506622314</t>
   </si>
   <si>
     <t xml:space="preserve">15.5637807846069</t>
   </si>
   <si>
-    <t xml:space="preserve">15.884334564209</t>
+    <t xml:space="preserve">15.8843355178833</t>
   </si>
   <si>
     <t xml:space="preserve">16.1374034881592</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8674612045288</t>
+    <t xml:space="preserve">15.8674621582031</t>
   </si>
   <si>
     <t xml:space="preserve">15.4541168212891</t>
@@ -2963,7 +2963,7 @@
     <t xml:space="preserve">15.0238981246948</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1673030853271</t>
+    <t xml:space="preserve">15.1673040390015</t>
   </si>
   <si>
     <t xml:space="preserve">15.4372434616089</t>
@@ -2975,16 +2975,16 @@
     <t xml:space="preserve">15.4794235229492</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1588678359985</t>
+    <t xml:space="preserve">15.1588687896729</t>
   </si>
   <si>
     <t xml:space="preserve">14.7623929977417</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4080944061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7416791915894</t>
+    <t xml:space="preserve">14.4080953598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.741678237915</t>
   </si>
   <si>
     <t xml:space="preserve">14.0537977218628</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">14.121283531189</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4295597076416</t>
+    <t xml:space="preserve">13.4295587539673</t>
   </si>
   <si>
     <t xml:space="preserve">13.5898380279541</t>
@@ -3020,13 +3020,13 @@
     <t xml:space="preserve">13.513916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9188280105591</t>
+    <t xml:space="preserve">13.9188270568848</t>
   </si>
   <si>
     <t xml:space="preserve">13.319896697998</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5307874679565</t>
+    <t xml:space="preserve">13.5307884216309</t>
   </si>
   <si>
     <t xml:space="preserve">12.8728065490723</t>
@@ -3038,7 +3038,7 @@
     <t xml:space="preserve">12.7631425857544</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6366081237793</t>
+    <t xml:space="preserve">12.636607170105</t>
   </si>
   <si>
     <t xml:space="preserve">12.4172811508179</t>
@@ -3050,7 +3050,7 @@
     <t xml:space="preserve">12.6872224807739</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6619157791138</t>
+    <t xml:space="preserve">12.6619148254395</t>
   </si>
   <si>
     <t xml:space="preserve">12.7209644317627</t>
@@ -3059,7 +3059,7 @@
     <t xml:space="preserve">12.4678955078125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1304683685303</t>
+    <t xml:space="preserve">12.1304693222046</t>
   </si>
   <si>
     <t xml:space="preserve">12.2823104858398</t>
@@ -3071,13 +3071,13 @@
     <t xml:space="preserve">12.3666677474976</t>
   </si>
   <si>
-    <t xml:space="preserve">12.585994720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4126882553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3958177566528</t>
+    <t xml:space="preserve">12.5859937667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4126873016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3958168029785</t>
   </si>
   <si>
     <t xml:space="preserve">13.4464302062988</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">12.7040939331055</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7715787887573</t>
+    <t xml:space="preserve">12.7715797424316</t>
   </si>
   <si>
     <t xml:space="preserve">12.4004096984863</t>
@@ -3143,7 +3143,7 @@
     <t xml:space="preserve">11.6487464904785</t>
   </si>
   <si>
-    <t xml:space="preserve">11.474102973938</t>
+    <t xml:space="preserve">11.4741039276123</t>
   </si>
   <si>
     <t xml:space="preserve">11.3693170547485</t>
@@ -3158,7 +3158,7 @@
     <t xml:space="preserve">12.4346437454224</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1028203964233</t>
+    <t xml:space="preserve">12.102819442749</t>
   </si>
   <si>
     <t xml:space="preserve">12.0154991149902</t>
@@ -3167,7 +3167,7 @@
     <t xml:space="preserve">11.9805698394775</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1901435852051</t>
+    <t xml:space="preserve">12.1901426315308</t>
   </si>
   <si>
     <t xml:space="preserve">12.3298578262329</t>
@@ -3188,7 +3188,7 @@
     <t xml:space="preserve">11.1946725845337</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7186050415039</t>
+    <t xml:space="preserve">11.7186040878296</t>
   </si>
   <si>
     <t xml:space="preserve">11.5788888931274</t>
@@ -3200,13 +3200,13 @@
     <t xml:space="preserve">11.8583192825317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7709970474243</t>
+    <t xml:space="preserve">11.7709980010986</t>
   </si>
   <si>
     <t xml:space="preserve">11.9631052017212</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7535333633423</t>
+    <t xml:space="preserve">11.753532409668</t>
   </si>
   <si>
     <t xml:space="preserve">11.49156665802</t>
@@ -3215,16 +3215,16 @@
     <t xml:space="preserve">11.2645301818848</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8104562759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0549573898315</t>
+    <t xml:space="preserve">10.8104553222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0549583435059</t>
   </si>
   <si>
     <t xml:space="preserve">11.1772079467773</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3867807388306</t>
+    <t xml:space="preserve">11.3867797851562</t>
   </si>
   <si>
     <t xml:space="preserve">11.2470655441284</t>
@@ -3236,13 +3236,13 @@
     <t xml:space="preserve">10.8453845977783</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3343868255615</t>
+    <t xml:space="preserve">11.3343877792358</t>
   </si>
   <si>
     <t xml:space="preserve">11.3169231414795</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4042453765869</t>
+    <t xml:space="preserve">11.4042463302612</t>
   </si>
   <si>
     <t xml:space="preserve">11.2296009063721</t>
@@ -3254,16 +3254,16 @@
     <t xml:space="preserve">11.7884616851807</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8233909606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.805926322937</t>
+    <t xml:space="preserve">11.823390007019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8059272766113</t>
   </si>
   <si>
     <t xml:space="preserve">11.5614242553711</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4566383361816</t>
+    <t xml:space="preserve">11.4566373825073</t>
   </si>
   <si>
     <t xml:space="preserve">11.5439605712891</t>
@@ -3275,7 +3275,7 @@
     <t xml:space="preserve">11.1073503494263</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0898866653442</t>
+    <t xml:space="preserve">11.0898857116699</t>
   </si>
   <si>
     <t xml:space="preserve">10.7231340408325</t>
@@ -3287,7 +3287,7 @@
     <t xml:space="preserve">10.6707401275635</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5135622024536</t>
+    <t xml:space="preserve">10.5135612487793</t>
   </si>
   <si>
     <t xml:space="preserve">10.2865238189697</t>
@@ -3299,7 +3299,7 @@
     <t xml:space="preserve">10.0594873428345</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1468095779419</t>
+    <t xml:space="preserve">10.1468086242676</t>
   </si>
   <si>
     <t xml:space="preserve">9.78005695343018</t>
@@ -3317,28 +3317,28 @@
     <t xml:space="preserve">9.98962879180908</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1992025375366</t>
+    <t xml:space="preserve">10.1992034912109</t>
   </si>
   <si>
     <t xml:space="preserve">9.29105472564697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51809120178223</t>
+    <t xml:space="preserve">9.51809215545654</t>
   </si>
   <si>
     <t xml:space="preserve">9.2211971282959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25612545013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0640172958374</t>
+    <t xml:space="preserve">9.25612640380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06401634216309</t>
   </si>
   <si>
     <t xml:space="preserve">8.80205154418945</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81951522827148</t>
+    <t xml:space="preserve">8.8195161819458</t>
   </si>
   <si>
     <t xml:space="preserve">8.60121154785156</t>
@@ -3347,19 +3347,19 @@
     <t xml:space="preserve">8.48769187927246</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19079875946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44403076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46149635314941</t>
+    <t xml:space="preserve">8.19079780578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44403171539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4614953994751</t>
   </si>
   <si>
     <t xml:space="preserve">8.3392448425293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56628322601318</t>
+    <t xml:space="preserve">8.56628227233887</t>
   </si>
   <si>
     <t xml:space="preserve">8.34797668457031</t>
@@ -3374,7 +3374,7 @@
     <t xml:space="preserve">8.85444450378418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88937282562256</t>
+    <t xml:space="preserve">8.88937377929688</t>
   </si>
   <si>
     <t xml:space="preserve">9.04655265808105</t>
@@ -3383,7 +3383,7 @@
     <t xml:space="preserve">9.01162433624268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83698081970215</t>
+    <t xml:space="preserve">8.83697986602783</t>
   </si>
   <si>
     <t xml:space="preserve">8.7321949005127</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">9.72766399383545</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55301952362061</t>
+    <t xml:space="preserve">9.55302047729492</t>
   </si>
   <si>
     <t xml:space="preserve">9.622878074646</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">9.91977119445801</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2690601348877</t>
+    <t xml:space="preserve">10.269061088562</t>
   </si>
   <si>
     <t xml:space="preserve">9.65780639648438</t>
@@ -3431,7 +3431,7 @@
     <t xml:space="preserve">9.67527103424072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8324499130249</t>
+    <t xml:space="preserve">9.83245086669922</t>
   </si>
   <si>
     <t xml:space="preserve">10.0420236587524</t>
@@ -3455,7 +3455,7 @@
     <t xml:space="preserve">10.0944156646729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0769519805908</t>
+    <t xml:space="preserve">10.0769510269165</t>
   </si>
   <si>
     <t xml:space="preserve">9.79752159118652</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">10.0070943832397</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4437046051025</t>
+    <t xml:space="preserve">10.4437036514282</t>
   </si>
   <si>
     <t xml:space="preserve">10.6532764434814</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">10.7405977249146</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7580623626709</t>
+    <t xml:space="preserve">10.7580633163452</t>
   </si>
   <si>
     <t xml:space="preserve">10.9152431488037</t>
@@ -3488,13 +3488,13 @@
     <t xml:space="preserve">11.0200290679932</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3518524169922</t>
+    <t xml:space="preserve">11.3518514633179</t>
   </si>
   <si>
     <t xml:space="preserve">11.0025644302368</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9676351547241</t>
+    <t xml:space="preserve">10.9676361083984</t>
   </si>
   <si>
     <t xml:space="preserve">10.5310258865356</t>
@@ -3506,7 +3506,7 @@
     <t xml:space="preserve">10.7056694030762</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6008834838867</t>
+    <t xml:space="preserve">10.6008825302124</t>
   </si>
   <si>
     <t xml:space="preserve">10.565954208374</t>
@@ -3521,10 +3521,10 @@
     <t xml:space="preserve">10.2166662216187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0245571136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84991455078125</t>
+    <t xml:space="preserve">10.0245580673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84991359710693</t>
   </si>
   <si>
     <t xml:space="preserve">10.1118803024292</t>
@@ -3542,13 +3542,13 @@
     <t xml:space="preserve">11.9456415176392</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7011394500732</t>
+    <t xml:space="preserve">11.7011404037476</t>
   </si>
   <si>
     <t xml:space="preserve">12.1202850341797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.399715423584</t>
+    <t xml:space="preserve">12.3997144699097</t>
   </si>
   <si>
     <t xml:space="preserve">11.9281768798828</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">11.8757839202881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0678911209106</t>
+    <t xml:space="preserve">12.067892074585</t>
   </si>
   <si>
     <t xml:space="preserve">12.0329627990723</t>
@@ -3575,7 +3575,7 @@
     <t xml:space="preserve">12.8712539672852</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6442155838013</t>
+    <t xml:space="preserve">12.6442165374756</t>
   </si>
   <si>
     <t xml:space="preserve">12.9491119384766</t>
@@ -4620,6 +4620,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.72000026702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02999973297119</t>
   </si>
 </sst>
 </file>
@@ -69906,7 +69909,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.6911574074</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>55392</v>
@@ -69927,6 +69930,32 @@
         <v>1516</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.6910532407</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>720325</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>9.02000045776367</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>9.73999977111816</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>9.02999973297119</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>1536</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARR.MI.xlsx
+++ b/data/MARR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="1536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1537" uniqueCount="1537">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4479522705078</t>
+    <t xml:space="preserve">13.4479513168335</t>
   </si>
   <si>
     <t xml:space="preserve">MARR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2894020080566</t>
+    <t xml:space="preserve">13.289400100708</t>
   </si>
   <si>
     <t xml:space="preserve">13.1812992095947</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9939203262329</t>
+    <t xml:space="preserve">12.9939193725586</t>
   </si>
   <si>
     <t xml:space="preserve">12.9506797790527</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5903367996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6551971435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7344751358032</t>
+    <t xml:space="preserve">12.5903358459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6551990509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7344741821289</t>
   </si>
   <si>
     <t xml:space="preserve">12.4389953613281</t>
@@ -71,25 +71,25 @@
     <t xml:space="preserve">12.4462013244629</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9849634170532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0858602523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6462421417236</t>
+    <t xml:space="preserve">11.9849615097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0858612060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6462430953979</t>
   </si>
   <si>
     <t xml:space="preserve">12.2155838012695</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8353700637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6768198013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5615110397339</t>
+    <t xml:space="preserve">12.8353691101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6768188476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5615100860596</t>
   </si>
   <si>
     <t xml:space="preserve">12.5543050765991</t>
@@ -98,85 +98,85 @@
     <t xml:space="preserve">12.6407861709595</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7200603485107</t>
+    <t xml:space="preserve">12.7200593948364</t>
   </si>
   <si>
     <t xml:space="preserve">12.9722986221313</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7777156829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3308925628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5110626220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2948570251465</t>
+    <t xml:space="preserve">12.7777137756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3308916091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5110645294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2948560714722</t>
   </si>
   <si>
     <t xml:space="preserve">11.4084167480469</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4516592025757</t>
+    <t xml:space="preserve">11.4516572952271</t>
   </si>
   <si>
     <t xml:space="preserve">11.8840684890747</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5885877609253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8912744522095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9273090362549</t>
+    <t xml:space="preserve">11.588586807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8912754058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9273080825806</t>
   </si>
   <si>
     <t xml:space="preserve">12.0426177978516</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2011680603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3957548141479</t>
+    <t xml:space="preserve">12.2011699676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3957538604736</t>
   </si>
   <si>
     <t xml:space="preserve">12.7056455612183</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6047525405884</t>
+    <t xml:space="preserve">12.6047506332397</t>
   </si>
   <si>
     <t xml:space="preserve">12.5759248733521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9362668991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1596765518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.943470954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0731964111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8858184814453</t>
+    <t xml:space="preserve">12.9362659454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1596784591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9434700012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0731935501099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.885817527771</t>
   </si>
   <si>
     <t xml:space="preserve">12.597544670105</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0786514282227</t>
+    <t xml:space="preserve">12.078652381897</t>
   </si>
   <si>
     <t xml:space="preserve">12.3597183227539</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6696128845215</t>
+    <t xml:space="preserve">12.6696119308472</t>
   </si>
   <si>
     <t xml:space="preserve">12.8137502670288</t>
@@ -188,49 +188,49 @@
     <t xml:space="preserve">12.8714046478271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.453408241272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3453044891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.684027671814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7560939788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1524696350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2677774429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3326406478882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0804004669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1885042190552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.260573387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7073955535889</t>
+    <t xml:space="preserve">12.4534091949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3453063964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6840267181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7560949325562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1524715423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2677803039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3326435089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0804033279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1885032653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2605743408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7073965072632</t>
   </si>
   <si>
     <t xml:space="preserve">13.4911909103394</t>
   </si>
   <si>
-    <t xml:space="preserve">13.347056388855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0011281967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9002323150635</t>
+    <t xml:space="preserve">13.347053527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0011262893677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9002313613892</t>
   </si>
   <si>
     <t xml:space="preserve">12.8281631469727</t>
@@ -242,16 +242,16 @@
     <t xml:space="preserve">13.058783531189</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1020231246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8065433502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2821941375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1380567550659</t>
+    <t xml:space="preserve">13.1020240783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.806544303894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2821950912476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1380558013916</t>
   </si>
   <si>
     <t xml:space="preserve">12.8425760269165</t>
@@ -260,25 +260,25 @@
     <t xml:space="preserve">12.8930244445801</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9074382781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0227470397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6624050140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8786115646362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6335783004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7488880157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0258731842041</t>
+    <t xml:space="preserve">12.9074373245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0227479934692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6624069213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8786125183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6335792541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7488899230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0258750915527</t>
   </si>
   <si>
     <t xml:space="preserve">13.0183887481689</t>
@@ -287,49 +287,49 @@
     <t xml:space="preserve">13.2579441070557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2504587173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4301261901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4825286865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3103485107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2654323577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4750423431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3702373504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2878904342651</t>
+    <t xml:space="preserve">13.2504606246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4301271438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4825305938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3103494644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2654304504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.475043296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3702383041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2878885269165</t>
   </si>
   <si>
     <t xml:space="preserve">13.2729177474976</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2804040908813</t>
+    <t xml:space="preserve">13.280403137207</t>
   </si>
   <si>
     <t xml:space="preserve">12.8012914657593</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8836374282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6141366958618</t>
+    <t xml:space="preserve">12.883638381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6141386032104</t>
   </si>
   <si>
     <t xml:space="preserve">12.3146934509277</t>
   </si>
   <si>
-    <t xml:space="preserve">12.44944190979</t>
+    <t xml:space="preserve">12.4494409561157</t>
   </si>
   <si>
     <t xml:space="preserve">12.8087778091431</t>
@@ -341,79 +341,79 @@
     <t xml:space="preserve">13.0782775878906</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4419584274292</t>
+    <t xml:space="preserve">12.4419574737549</t>
   </si>
   <si>
     <t xml:space="preserve">11.7831773757935</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2847480773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7339162826538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4226417541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5274457931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0558204650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4525842666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3328065872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7595167160034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7295722961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7220840454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.53493309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4900150299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7370586395264</t>
+    <t xml:space="preserve">12.2847471237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7339153289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4226398468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5274438858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0558195114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4525852203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3328075408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7595176696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7295703887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7220859527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5349340438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4900159835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7370576858521</t>
   </si>
   <si>
     <t xml:space="preserve">14.0140447616577</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7071123123169</t>
+    <t xml:space="preserve">13.7071132659912</t>
   </si>
   <si>
     <t xml:space="preserve">13.8493490219116</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1113653182983</t>
+    <t xml:space="preserve">14.111364364624</t>
   </si>
   <si>
     <t xml:space="preserve">13.9766149520874</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0814189910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7445468902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9990739822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5049896240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6397380828857</t>
+    <t xml:space="preserve">14.0814199447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7445440292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9990720748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5049886703491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6397371292114</t>
   </si>
   <si>
     <t xml:space="preserve">13.6621961593628</t>
@@ -428,61 +428,61 @@
     <t xml:space="preserve">13.415153503418</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2205152511597</t>
+    <t xml:space="preserve">13.2205142974854</t>
   </si>
   <si>
     <t xml:space="preserve">13.0857639312744</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1007375717163</t>
+    <t xml:space="preserve">13.1007356643677</t>
   </si>
   <si>
     <t xml:space="preserve">13.0633068084717</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2354869842529</t>
+    <t xml:space="preserve">13.2354850769043</t>
   </si>
   <si>
     <t xml:space="preserve">13.1456518173218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9285554885864</t>
+    <t xml:space="preserve">12.9285564422607</t>
   </si>
   <si>
     <t xml:space="preserve">13.2055416107178</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1082239151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1980543136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1157102584839</t>
+    <t xml:space="preserve">13.1082229614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1980571746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1157093048096</t>
   </si>
   <si>
     <t xml:space="preserve">13.0109014511108</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9135828018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8611822128296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9435272216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1905698776245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4076690673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3552665710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2130279541016</t>
+    <t xml:space="preserve">12.9135837554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.861180305481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.943528175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1905708312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4076671600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3552646636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2130289077759</t>
   </si>
   <si>
     <t xml:space="preserve">13.3402919769287</t>
@@ -491,67 +491,64 @@
     <t xml:space="preserve">12.9659852981567</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8761539459229</t>
+    <t xml:space="preserve">12.8761520385742</t>
   </si>
   <si>
     <t xml:space="preserve">12.8312339782715</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9809598922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7638597488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7114572525024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8686676025391</t>
+    <t xml:space="preserve">12.9809589385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.763858795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7114562988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8686666488647</t>
   </si>
   <si>
     <t xml:space="preserve">12.7563753128052</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7488889694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6815137863159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5767059326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.546760559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5317916870117</t>
+    <t xml:space="preserve">12.6815128326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5767068862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.546763420105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5317897796631</t>
   </si>
   <si>
     <t xml:space="preserve">12.5617341995239</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5542497634888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4194984436035</t>
+    <t xml:space="preserve">12.5542488098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4194974899292</t>
   </si>
   <si>
     <t xml:space="preserve">12.2772607803345</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4719018936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5018463134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3970394134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9778156280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3596096038818</t>
+    <t xml:space="preserve">12.4718999862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5018472671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3970384597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9778165817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3596086502075</t>
   </si>
   <si>
     <t xml:space="preserve">12.4943599700928</t>
@@ -560,1876 +557,1879 @@
     <t xml:space="preserve">12.3820686340332</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4045257568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.269775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1649694442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2548036575317</t>
+    <t xml:space="preserve">12.4045248031616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2697744369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1649703979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2548046112061</t>
   </si>
   <si>
     <t xml:space="preserve">12.3371505737305</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3221778869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.72642993927</t>
+    <t xml:space="preserve">12.3221788406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7264318466187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6740274429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7863178253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0932502746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9510135650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1306819915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9884443283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1381664276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.160626411438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.183084487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1681108474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2280015945435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0034170150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1755981445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4001817703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3852100372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8643226623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9167251586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5199604034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4450979232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3627529144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4600696563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5124731063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4376134872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8268928527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6247663497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8044338226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7819747924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6996269226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8418636322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6771688461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8568363189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7670021057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5648775100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8942680358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3359479904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5605335235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5156154632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6952819824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9722709655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9348402023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9423246383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8225479125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2043409347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.713397026062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.136962890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1594247817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2866878509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3615493774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2267999649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3465766906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6834526062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7208843231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5337314605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4588689804077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1669092178345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1968536376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5487051010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4214382171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6011066436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6460237503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7358570098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5861330032349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9080362319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.42458152771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1251373291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6984272003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2823467254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3272590637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2598876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2673683166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5967655181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.78391456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6641387939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.521900177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4470367431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6416778564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0758724212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7988872528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7464828491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8737506866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9560966491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1058197021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3946380615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5069274902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.684757232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1950397491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1641120910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0094814300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7620697021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6306343078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8471202850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0249462127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9398956298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7698001861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9940185546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1254539489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9553604125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5455837249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7156791687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8548488616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7466087341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0404109954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.731143951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5378551483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5687808990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6229038238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7079486846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7234115600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1822032928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0894222259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0816917419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.159008026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9347925186157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2363224029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0739593505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9966430664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3909587860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4914646148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8935050964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2414264678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0558681488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2878189086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2955474853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3960590362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.831657409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.280086517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7002182006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5533199310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4837341308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7775344848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5146617889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3832225799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3986854553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2749824523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2285919189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0584945678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9657163619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9502544403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0353012084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2827129364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4141483306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6074390411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5919723510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.932165145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0481376647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2646236419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9476280212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0713310241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0636005401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0790672302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2723560333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.303279876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3728656768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3187446594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.558422088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5893497467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4656410217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7207870483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5738849639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5429611206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6975898742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1073665618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0377807617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6125431060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6821308135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5197620391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3110122680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1099910736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3574028015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1795768737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1409206390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.086799621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8857765197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6151695251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.530122756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.352294921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0430355072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8265466690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9270601272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1976661682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6692905426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8703098297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7852649688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9630928039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8084602355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9244346618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4218807220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0507659912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4605388641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4528064727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.754337310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6383647918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7929973602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4064159393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.33420753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3805961608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.488842010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5506935119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6898574829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4115219116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6434669494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2568912506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2259654998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.504301071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.499195098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9785556793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3445663452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2981758117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9012393951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.653829574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2672481536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3136367797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4269886016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4475536346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3857021331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8805255889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1433982849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0042285919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.911449432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6949672698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6795024871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7413578033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6640377044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7877464294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2516384124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.437198638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3444213867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.406270980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5609016418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3289566040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1743240356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1124687194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1588611602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2825679779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2361755371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.205249786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2671012878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5299777984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6382179260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5918292999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4835891723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5145111083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4526596069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.607292175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1382923126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3547763824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0764408111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.03005027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1737804412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9501991271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3654174804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.205717086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6209373474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5091438293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5889987945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.557056427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4931774139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1578102111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4293003082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6848163604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.636905670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4133281707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4612369537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3175086975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.806468963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8224411010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7106533050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9182605743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9661693572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0300483703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8863220214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9981117248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3973598480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5251178741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4452686309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1479434967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1639156341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0201873779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8604869842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7806377410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5730266571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0680961608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7646675109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4772090911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7007884979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2437648773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4513740539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4992847442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2118244171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1319732666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0042152404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1160049438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0361557006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1798839569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3236141204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3395843505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3076457977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7228622436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.467342376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3874969482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5631618499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8825607299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3616600036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4415092468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2658405303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7609081268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0962753295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8247871398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.249870300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4734477996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1540489196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1700210571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7548007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5312232971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4034652709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8125743865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7327270507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3813896179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2536315917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9342308044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3494491577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9243679046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7486953735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1258716583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7905006408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4391632080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1357307434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2155838012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9760341644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.550952911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8961849212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0718536376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.928129196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8323059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.05588722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1836433410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4551334381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8163356781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3532066345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9858999252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0976886749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1136589050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4269514083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3311328887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6505317687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4748592376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4429225921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7703046798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8421688079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7383651733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4490280151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2733592987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1615676879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.321268081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4809665679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6246967315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.768424987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1676769256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3433437347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2794628143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9440937042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0079727172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6406669616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.241418838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5608158111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7045440673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.848274230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3752822875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.103796005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8802165985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9121570587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8642463684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7205142974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6885776519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6087265014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7364864349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3052978515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8980646133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.193510055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2094783782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3851470947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.28932762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2573890686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2254486083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9140348434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.417085647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5288772583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7843971252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5767879486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.369176864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1775379180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4889507293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2494010925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3292541503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4091033935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1695537567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0497798919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5688037872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6486511230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2874507904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0878219604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0479011535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8083515167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9680500030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7285022735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8881988525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1277484893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8793506622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.045238494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9208221435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7964057922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2111282348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1281833648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1696586608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.418493270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3770217895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4599647521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2940769195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9622955322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7549324035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6305141448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3402061462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4895057678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5392742156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7088012695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.667329788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5014381408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.542911529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2526016235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7134609222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4231491088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3733825683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2406711578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.17431640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2738513946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1245498657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3070278167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8591241836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.726411819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7927665710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.074779510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5273418426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4278078079224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6600561141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1789703369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3614521026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6932344436646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6102876663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4609861373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4443988800049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.378041267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2950963973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.925479888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2904376983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3899726867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4397392272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.671989440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9576377868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0867118835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3355464935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8378772735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5890426635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2572593688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.87571144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9088907241821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1577262878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1411361694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4729175567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7595901489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.676643371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5937004089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.477578163147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7430009841919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7098236083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8425350189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3567943572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.323616027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.975248336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5843849182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0037670135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2240810394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0084228515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1909065246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5558643341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.532000541687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7974243164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.183629989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9347953796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6361932754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4371242523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2712345123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3873558044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7616300582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9607000350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4251918792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0317115783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4796171188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1690826416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3681507110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95342445373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3183841705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8777532577515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4417810440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8565082550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1763563156128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.29248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2141923904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9155893325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6667528152466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2022609710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.451096534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5174522399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5340404510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4013290405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1524934768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0529584884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97001457214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4676866531372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6999311447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3017950057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0695476531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2520275115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0031929016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0363702774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1193141937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92024707794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4557523727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50552082061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32304191589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14056205749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07420539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6879997253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1359043121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70458793640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38939762115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4345073699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2188501358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4179182052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9985342025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.899001121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9819450378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8160562515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8824119567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8113975524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7782201766968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5957384109497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3634929656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6833429336548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.948766708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9653568267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2639589309692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2805480957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1810131072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3303155899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2971382141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0814800262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0151224136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0648918151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8326454162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8492336273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5838088989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3847408294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.650164604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3515615463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2354393005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9321784973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.550630569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5008630752563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6169862747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4842748641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0197811126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3349733352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7828769683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6003971099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1312465667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4132614135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4298496246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2307806015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8658227920532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3137273788452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.396671295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5127944946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8611650466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2095346450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9772882461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0602331161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2593011856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3800830841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1146574020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6335754394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2686166763306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55528831481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62164402008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65482234954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.605055809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75435638427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.491548538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0058088302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1929454803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8399171829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3209991455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4086036682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2758922576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7237939834595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9062747955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1053428649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9892196655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0721645355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0223979949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.088752746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.038987159729</t>
   </si>
   <si>
     <t xml:space="preserve">12.6740264892578</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7863178253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0932521820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9510135650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1306810379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9884462356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1381664276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1606254577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1830854415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1681118011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2280006408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.00341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1755990982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.400182723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3852100372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8643236160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9167251586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5199594497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4450979232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3627510070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4600696563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.51247215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.437614440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8268918991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6247682571411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8044347763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7819719314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6996269226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8418636322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6771697998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8568363189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7670011520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5648794174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8942670822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3359498977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5605354309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5156173706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6952819824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9722719192505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9348402023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9423246383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8225479125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2043399810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.713397026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1369657516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1594219207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2866888046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3615493774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2267999649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3465785980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6834545135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7208833694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.533730506897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.458869934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1669101715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.196852684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5487012863159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4214353561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6011037826538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6460199356079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7358570098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5861320495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9080381393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.42458152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1251354217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6984243392944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2823429107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3272590637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2598857879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2673721313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5967617034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7839164733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6641368865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5218982696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4470386505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6416759490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0758781433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7988891601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7464847564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8737487792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9560985565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1058197021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3946380615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.506929397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.684757232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1950378417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1641120910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0094814300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7620697021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6306324005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8471183776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0249443054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9398975372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7698001861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9940166473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1254539489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.955358505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5455875396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7156810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8548469543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7466087341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0404071807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.731143951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5378532409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5687808990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6229000091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.707950592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.72340965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1822032928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0894203186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0816917419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1590042114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9347906112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2363224029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0739593505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9966430664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3909549713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4914646148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8935070037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2414283752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0558700561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2878170013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2955493927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3960590362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8316535949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2800884246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7002182006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5533180236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4837341308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7775363922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5146598815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3832263946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3986854553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2749805450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2285900115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0584945678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9657182693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9502544403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0353031158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2827129364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4141483306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6074390411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5919742584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9321670532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0481395721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2646217346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9476299285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0713329315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0636005401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0790672302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2723541259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.303279876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3728637695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3187446594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5584201812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5893516540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4656448364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7207851409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5738868713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5429611206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6975898742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1073665618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0377826690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6125450134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6821308135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5197639465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3110122680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1099910736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3574028015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1795768737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1409168243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0867958068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8857765197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6151695251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5301208496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3522968292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0430335998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.826548576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.927056312561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1976661682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6692905426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8703117370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7852649688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9630928039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8084602355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9244327545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4218788146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0507659912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4605350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.452808380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.754337310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6383666992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7929973602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4064178466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3342094421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3805980682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4888401031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5506935119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6898593902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4115238189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6434726715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2568874359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2259654998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5043029785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4991970062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9785575866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3445625305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2981739044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.901237487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6538276672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2672500610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3136386871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4269866943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4475555419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3857021331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8805236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1433963775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0042285919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.911449432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6949653625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6795043945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7413539886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6640396118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7877445220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2516384124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.437198638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3444213867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4062728881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5609016418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3289566040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1743240356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1124725341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1588611602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2825660705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.236177444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2052516937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2671031951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5299797058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.638219833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5918292999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4835891723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5145130157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4526615142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.607292175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1382923126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.354772567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0764408111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.03005027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1737804412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9502010345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3654193878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.205717086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6209373474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.509147644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5889987945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5570583343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4931793212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1578102111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4292984008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6848163604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6369094848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4133281707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4612407684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3175106048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8064708709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.822437286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7106513977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9182624816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9661693572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8863220214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9981098175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3973579406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5251197814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4452686309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1479454040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1639137268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0201854705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8604888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7806358337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5730285644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0680923461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7646675109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4772090911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7007884979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2437648773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4513740539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4992828369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2118244171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1319732666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0042133331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1160049438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0361576080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1798858642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.323616027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3395824432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3076438903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.722864151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.467342376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3874931335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5631637573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8825607299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3616600036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4415073394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2658386230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7609081268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0962772369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8247871398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.249870300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4734477996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1540508270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1700229644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7548007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5312232971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4034633636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8125762939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7327270507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3813877105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2536296844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9342308044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3494491577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9243640899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7486972808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1258716583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7905006408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4391632080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1357326507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2155838012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9760360717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5509510040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.896183013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0718517303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9281253814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8323040008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0558853149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1836452484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4551315307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8163356781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3532066345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9859008789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0976905822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1136589050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4269523620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3311319351196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6505308151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4748611450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4429206848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7703037261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.842170715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7383651733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4490242004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2733592987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1615695953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.321268081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4809646606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6246948242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.768424987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1676731109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3433437347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2794628143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9440956115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0079727172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6406650543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.241418838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5608177185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7045459747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8482761383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3752841949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.103796005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8802127838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9121551513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8642444610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7205142974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6885738372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6087265014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7364845275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3052978515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8980627059937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.193510055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2094764709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3851470947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2893295288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2573890686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2254505157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9140338897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4170875549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5288772583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7843971252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5767879486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3691787719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1775379180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4889526367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2494049072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.329252243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4091014862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1695518493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0497798919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5688018798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6486530303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.287446975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0878257751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0478992462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.808349609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9680500030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7285022735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8882007598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1277503967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8793506622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0452404022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9208240509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7964038848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2111301422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1281871795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1696586608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.418493270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3770236968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4599647521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2940769195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9622955322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7549324035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6305122375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3402061462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4895057678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5392742156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7088012695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6673278808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5014400482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.542911529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2526035308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7134590148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4231510162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.373384475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2406711578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1743144989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2738513946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.124547958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3070259094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8591232299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7264089584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7927675247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0747814178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5273418426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4278106689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6600532531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1789722442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3614540100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6932325363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6102886199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4609870910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4443998336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3780422210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2950983047485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.925479888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2904376983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3899745941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4397392272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6719875335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9576358795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0867118835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3355464935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8378753662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5890426635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2572612762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8757133483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9088897705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1577243804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1411361694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4729194641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7595872879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.676643371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5936994552612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4775772094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7429990768433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7098217010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8425340652466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3567943572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3236179351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9752464294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5843849182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0037689208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2240829467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0084247589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1909046173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5558624267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5320014953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7974262237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1836318969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.93479347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6361923217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4371242523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2712335586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3873567581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7616310119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9607000350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4251918792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0317125320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4796171188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1690816879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3681507110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95342445373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3183832168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8777532577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.441780090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8565073013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1763563156128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2924795150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2141923904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9155883789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6667528152466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.202260017395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.451096534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5174522399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5340414047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4013290405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1524925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0529584884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97001361846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4676856994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6999320983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3017950057983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0695476531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2520275115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.003191947937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0363702774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1193151473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92024707794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4557523727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50552082061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32304096221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14056205749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07420539855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68800163269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1359043121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70458889007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38939762115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4345073699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2188491821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4179182052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.99853515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.899001121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9819450378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8160543441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8824110031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8113975524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7782192230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.595739364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3634939193726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6833429336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.948766708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9653558731079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2639598846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2805490493774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1810140609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3303146362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.297137260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0814800262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0151224136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0648899078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8326444625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.849232673645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5838088989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3847408294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.650164604187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3515615463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2354383468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9321784973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.550630569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5008640289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6169862747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4842758178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0197811126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3349733352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7828769683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6003980636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1312465667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4132614135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4298486709595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2307806015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8658218383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3137273788452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.396671295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5127954483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8611650466919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2095346450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9772872924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0602340698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2593021392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3800830841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1146574020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6335754394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2686157226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55528736114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62164497375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65482234954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60505485534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75435638427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.491548538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0058088302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1929454803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8399171829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3210000991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4086027145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2758913040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7237949371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9062747955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1053428649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.989218711853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0721654891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0223970413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.088752746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0389862060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6740283966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4583711624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5081377029419</t>
+    <t xml:space="preserve">12.4583702087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5081367492676</t>
   </si>
   <si>
     <t xml:space="preserve">12.7403831481934</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3754253387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4749593734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6574392318726</t>
+    <t xml:space="preserve">12.3754262924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4749584197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6574382781982</t>
   </si>
   <si>
     <t xml:space="preserve">12.9560413360596</t>
@@ -2441,16 +2441,16 @@
     <t xml:space="preserve">13.536657333374</t>
   </si>
   <si>
-    <t xml:space="preserve">13.984561920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3661088943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5817670822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6978912353516</t>
+    <t xml:space="preserve">13.9845609664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3661108016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5817680358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6978893280029</t>
   </si>
   <si>
     <t xml:space="preserve">14.7642459869385</t>
@@ -2462,19 +2462,19 @@
     <t xml:space="preserve">14.1006851196289</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4324645996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7808351516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7476577758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4988212585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3495206832886</t>
+    <t xml:space="preserve">14.432466506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7808361053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7476587295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4988222122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3495216369629</t>
   </si>
   <si>
     <t xml:space="preserve">14.2499876022339</t>
@@ -2486,37 +2486,37 @@
     <t xml:space="preserve">13.7854948043823</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0177392959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0509195327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.283164024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0462608337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.930136680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3946313858032</t>
+    <t xml:space="preserve">14.0177402496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0509185791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2831649780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0462598800659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9301385879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3946294784546</t>
   </si>
   <si>
     <t xml:space="preserve">15.3448629379272</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9918365478516</t>
+    <t xml:space="preserve">15.9918355941772</t>
   </si>
   <si>
     <t xml:space="preserve">14.8969593048096</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9799032211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9135475158691</t>
+    <t xml:space="preserve">14.979905128479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9135484695435</t>
   </si>
   <si>
     <t xml:space="preserve">14.9964942932129</t>
@@ -2525,49 +2525,49 @@
     <t xml:space="preserve">15.825945854187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6434659957886</t>
+    <t xml:space="preserve">15.6434669494629</t>
   </si>
   <si>
     <t xml:space="preserve">16.0250148773193</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0913696289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0581912994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5605220794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0130825042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2619190216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2287425994873</t>
+    <t xml:space="preserve">16.0913715362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0581932067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5605211257935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0130834579468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2619180679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2287406921387</t>
   </si>
   <si>
     <t xml:space="preserve">15.1457939147949</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4941663742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6268768310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2121515274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5024604797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2702112197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2536220550537</t>
+    <t xml:space="preserve">15.4941654205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6268787384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2121505737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.502459526062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2702131271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.253623008728</t>
   </si>
   <si>
     <t xml:space="preserve">15.5439329147339</t>
@@ -2576,10 +2576,10 @@
     <t xml:space="preserve">15.5771102905273</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8508291244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7181177139282</t>
+    <t xml:space="preserve">15.850830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7181186676025</t>
   </si>
   <si>
     <t xml:space="preserve">15.7347040176392</t>
@@ -2588,10 +2588,10 @@
     <t xml:space="preserve">15.8840084075928</t>
   </si>
   <si>
-    <t xml:space="preserve">15.751296043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4361038208008</t>
+    <t xml:space="preserve">15.7512950897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4361028671265</t>
   </si>
   <si>
     <t xml:space="preserve">16.3982677459717</t>
@@ -2600,13 +2600,13 @@
     <t xml:space="preserve">16.5807456970215</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8674182891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0830764770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1079578399658</t>
+    <t xml:space="preserve">15.8674173355103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0830745697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1079597473145</t>
   </si>
   <si>
     <t xml:space="preserve">16.4646224975586</t>
@@ -2618,28 +2618,28 @@
     <t xml:space="preserve">16.8212890625</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7051639556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9042358398438</t>
+    <t xml:space="preserve">16.7051658630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9042320251465</t>
   </si>
   <si>
     <t xml:space="preserve">16.9374122619629</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1364784240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3023719787598</t>
+    <t xml:space="preserve">17.1364803314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3023700714111</t>
   </si>
   <si>
     <t xml:space="preserve">17.4350833892822</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4516735076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.219425201416</t>
+    <t xml:space="preserve">17.4516716003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2194232940674</t>
   </si>
   <si>
     <t xml:space="preserve">16.7217540740967</t>
@@ -2651,46 +2651,46 @@
     <t xml:space="preserve">17.0535354614258</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0369472503662</t>
+    <t xml:space="preserve">17.0369453430176</t>
   </si>
   <si>
     <t xml:space="preserve">16.8876457214355</t>
   </si>
   <si>
-    <t xml:space="preserve">16.771520614624</t>
+    <t xml:space="preserve">16.7715225219727</t>
   </si>
   <si>
     <t xml:space="preserve">16.8544673919678</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2028369903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1033039093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1198902130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7383422851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3521366119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2691917419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8710556030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9171867370605</t>
+    <t xml:space="preserve">17.2028350830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1033020019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1198883056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7383441925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3521385192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.269193649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8710536956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9171848297119</t>
   </si>
   <si>
     <t xml:space="preserve">16.2074947357178</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2323760986328</t>
+    <t xml:space="preserve">16.2323780059814</t>
   </si>
   <si>
     <t xml:space="preserve">16.6056308746338</t>
@@ -2699,10 +2699,10 @@
     <t xml:space="preserve">18.6958503723145</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1981792449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1650009155273</t>
+    <t xml:space="preserve">18.1981773376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1649990081787</t>
   </si>
   <si>
     <t xml:space="preserve">17.617561340332</t>
@@ -2714,28 +2714,28 @@
     <t xml:space="preserve">17.6507415771484</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8000411987305</t>
+    <t xml:space="preserve">17.8000392913818</t>
   </si>
   <si>
     <t xml:space="preserve">17.4019050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3189582824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.020357131958</t>
+    <t xml:space="preserve">17.3189601898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0203590393066</t>
   </si>
   <si>
     <t xml:space="preserve">16.7881107330322</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9705905914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1862468719482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4065628051758</t>
+    <t xml:space="preserve">16.970588684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1862449645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4065608978271</t>
   </si>
   <si>
     <t xml:space="preserve">16.4148559570312</t>
@@ -2744,10 +2744,10 @@
     <t xml:space="preserve">16.049898147583</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1660213470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5346145629883</t>
+    <t xml:space="preserve">16.1660194396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5346164703369</t>
   </si>
   <si>
     <t xml:space="preserve">17.0701236724854</t>
@@ -2759,19 +2759,19 @@
     <t xml:space="preserve">17.6839179992676</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4848480224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.276216506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2424755096436</t>
+    <t xml:space="preserve">17.4848499298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2762145996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2424736022949</t>
   </si>
   <si>
     <t xml:space="preserve">17.3437023162842</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5461578369141</t>
+    <t xml:space="preserve">17.5461559295654</t>
   </si>
   <si>
     <t xml:space="preserve">17.4111862182617</t>
@@ -2780,13 +2780,13 @@
     <t xml:space="preserve">17.3774433135986</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6642570495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4449291229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4618015289307</t>
+    <t xml:space="preserve">17.6642589569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4449310302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4618034362793</t>
   </si>
   <si>
     <t xml:space="preserve">17.1749897003174</t>
@@ -2798,19 +2798,19 @@
     <t xml:space="preserve">17.0062770843506</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9556636810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8628692626953</t>
+    <t xml:space="preserve">16.9556617736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8628711700439</t>
   </si>
   <si>
     <t xml:space="preserve">17.090633392334</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8713073730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7532081604004</t>
+    <t xml:space="preserve">16.8713054656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7532062530518</t>
   </si>
   <si>
     <t xml:space="preserve">17.2087326049805</t>
@@ -2822,22 +2822,22 @@
     <t xml:space="preserve">16.0952262878418</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1458396911621</t>
+    <t xml:space="preserve">16.1458377838135</t>
   </si>
   <si>
     <t xml:space="preserve">15.7915410995483</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6903162002563</t>
+    <t xml:space="preserve">15.690315246582</t>
   </si>
   <si>
     <t xml:space="preserve">15.8590278625488</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4119386672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5216016769409</t>
+    <t xml:space="preserve">15.4119396209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5215997695923</t>
   </si>
   <si>
     <t xml:space="preserve">15.0998191833496</t>
@@ -2846,13 +2846,13 @@
     <t xml:space="preserve">15.420373916626</t>
   </si>
   <si>
-    <t xml:space="preserve">15.60595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5806503295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8337211608887</t>
+    <t xml:space="preserve">15.6059589385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5806512832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.833722114563</t>
   </si>
   <si>
     <t xml:space="preserve">16.0446109771729</t>
@@ -2861,37 +2861,37 @@
     <t xml:space="preserve">15.8758993148804</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8927698135376</t>
+    <t xml:space="preserve">15.8927688598633</t>
   </si>
   <si>
     <t xml:space="preserve">16.0108680725098</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9349460601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7662363052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7746725082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5131635665894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4878606796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1841745376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.234787940979</t>
+    <t xml:space="preserve">15.9349479675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7662353515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7746715545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5131664276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4878587722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1841735839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2347888946533</t>
   </si>
   <si>
     <t xml:space="preserve">15.3950662612915</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9433832168579</t>
+    <t xml:space="preserve">15.9433822631836</t>
   </si>
   <si>
     <t xml:space="preserve">16.112096786499</t>
@@ -2903,7 +2903,7 @@
     <t xml:space="preserve">16.4495220184326</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5890855789185</t>
+    <t xml:space="preserve">15.5890846252441</t>
   </si>
   <si>
     <t xml:space="preserve">15.6987504959106</t>
@@ -2915,55 +2915,55 @@
     <t xml:space="preserve">15.9686918258667</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3145523071289</t>
+    <t xml:space="preserve">16.3145542144775</t>
   </si>
   <si>
     <t xml:space="preserve">15.9180765151978</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0193061828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5384721755981</t>
+    <t xml:space="preserve">16.0193042755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5384740829468</t>
   </si>
   <si>
     <t xml:space="preserve">15.0154609680176</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1504325866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5300350189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8168497085571</t>
+    <t xml:space="preserve">15.1504316329956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5300369262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8168487548828</t>
   </si>
   <si>
     <t xml:space="preserve">15.5637807846069</t>
   </si>
   <si>
-    <t xml:space="preserve">15.884334564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1374034881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8674612045288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4541168212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9732847213745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0238981246948</t>
+    <t xml:space="preserve">15.8843336105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1374053955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8674640655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4541149139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9732856750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0238971710205</t>
   </si>
   <si>
     <t xml:space="preserve">15.1673030853271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4372434616089</t>
+    <t xml:space="preserve">15.4372453689575</t>
   </si>
   <si>
     <t xml:space="preserve">15.6312656402588</t>
@@ -2972,10 +2972,10 @@
     <t xml:space="preserve">15.4794235229492</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1588678359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7623929977417</t>
+    <t xml:space="preserve">15.1588659286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7623920440674</t>
   </si>
   <si>
     <t xml:space="preserve">14.4080944061279</t>
@@ -2987,13 +2987,13 @@
     <t xml:space="preserve">14.0537977218628</t>
   </si>
   <si>
-    <t xml:space="preserve">14.121283531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4295597076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5898380279541</t>
+    <t xml:space="preserve">14.1212825775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4295587539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5898370742798</t>
   </si>
   <si>
     <t xml:space="preserve">13.142746925354</t>
@@ -3002,25 +3002,25 @@
     <t xml:space="preserve">12.7294006347656</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6028652191162</t>
+    <t xml:space="preserve">12.6028642654419</t>
   </si>
   <si>
     <t xml:space="preserve">12.906548500061</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3367671966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1258764266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.513916015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9188280105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.319896697998</t>
+    <t xml:space="preserve">13.3367681503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1258754730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5139169692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9188270568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3198957443237</t>
   </si>
   <si>
     <t xml:space="preserve">13.5307874679565</t>
@@ -3038,7 +3038,7 @@
     <t xml:space="preserve">12.6366081237793</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4172811508179</t>
+    <t xml:space="preserve">12.4172801971436</t>
   </si>
   <si>
     <t xml:space="preserve">12.484766960144</t>
@@ -3053,7 +3053,7 @@
     <t xml:space="preserve">12.7209644317627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4678955078125</t>
+    <t xml:space="preserve">12.4678945541382</t>
   </si>
   <si>
     <t xml:space="preserve">12.1304683685303</t>
@@ -3065,25 +3065,25 @@
     <t xml:space="preserve">12.3497953414917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3666677474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.585994720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4126882553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3958177566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4464302062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7838573455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3114595413208</t>
+    <t xml:space="preserve">12.3666658401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5859937667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4126873016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3958168029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4464311599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7838563919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3114604949951</t>
   </si>
   <si>
     <t xml:space="preserve">13.2271041870117</t>
@@ -3092,13 +3092,13 @@
     <t xml:space="preserve">12.9571619033813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0752620697021</t>
+    <t xml:space="preserve">13.0752630233765</t>
   </si>
   <si>
     <t xml:space="preserve">12.7040939331055</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7715787887573</t>
+    <t xml:space="preserve">12.7715797424316</t>
   </si>
   <si>
     <t xml:space="preserve">12.4004096984863</t>
@@ -3113,7 +3113,7 @@
     <t xml:space="preserve">11.8773994445801</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1473388671875</t>
+    <t xml:space="preserve">12.1473398208618</t>
   </si>
   <si>
     <t xml:space="preserve">12.1642122268677</t>
@@ -3134,7 +3134,7 @@
     <t xml:space="preserve">11.8267850875854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749439239502</t>
+    <t xml:space="preserve">11.6749429702759</t>
   </si>
   <si>
     <t xml:space="preserve">11.6487464904785</t>
@@ -3146,7 +3146,7 @@
     <t xml:space="preserve">11.3693170547485</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8932476043701</t>
+    <t xml:space="preserve">11.8932485580444</t>
   </si>
   <si>
     <t xml:space="preserve">11.9107131958008</t>
@@ -3155,16 +3155,16 @@
     <t xml:space="preserve">12.4346437454224</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1028203964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0154991149902</t>
+    <t xml:space="preserve">12.102819442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0154981613159</t>
   </si>
   <si>
     <t xml:space="preserve">11.9805698394775</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1901435852051</t>
+    <t xml:space="preserve">12.1901426315308</t>
   </si>
   <si>
     <t xml:space="preserve">12.3298578262329</t>
@@ -3176,16 +3176,16 @@
     <t xml:space="preserve">12.3123931884766</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5963525772095</t>
+    <t xml:space="preserve">11.5963535308838</t>
   </si>
   <si>
     <t xml:space="preserve">11.4391746520996</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1946725845337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7186050415039</t>
+    <t xml:space="preserve">11.1946716308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7186040878296</t>
   </si>
   <si>
     <t xml:space="preserve">11.5788888931274</t>
@@ -3197,7 +3197,7 @@
     <t xml:space="preserve">11.8583192825317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7709970474243</t>
+    <t xml:space="preserve">11.7709980010986</t>
   </si>
   <si>
     <t xml:space="preserve">11.9631052017212</t>
@@ -3209,25 +3209,25 @@
     <t xml:space="preserve">11.49156665802</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2645301818848</t>
+    <t xml:space="preserve">11.2645292282104</t>
   </si>
   <si>
     <t xml:space="preserve">10.8104562759399</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0549573898315</t>
+    <t xml:space="preserve">11.0549583435059</t>
   </si>
   <si>
     <t xml:space="preserve">11.1772079467773</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3867807388306</t>
+    <t xml:space="preserve">11.3867797851562</t>
   </si>
   <si>
     <t xml:space="preserve">11.2470655441284</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0374927520752</t>
+    <t xml:space="preserve">11.0374937057495</t>
   </si>
   <si>
     <t xml:space="preserve">10.8453845977783</t>
@@ -3245,7 +3245,7 @@
     <t xml:space="preserve">11.2296009063721</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6138172149658</t>
+    <t xml:space="preserve">11.6138181686401</t>
   </si>
   <si>
     <t xml:space="preserve">11.7884616851807</t>
@@ -3254,7 +3254,7 @@
     <t xml:space="preserve">11.8233909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">11.805926322937</t>
+    <t xml:space="preserve">11.8059272766113</t>
   </si>
   <si>
     <t xml:space="preserve">11.5614242553711</t>
@@ -3269,10 +3269,10 @@
     <t xml:space="preserve">11.4217090606689</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1073503494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0898866653442</t>
+    <t xml:space="preserve">11.1073513031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0898857116699</t>
   </si>
   <si>
     <t xml:space="preserve">10.7231340408325</t>
@@ -3281,19 +3281,19 @@
     <t xml:space="preserve">10.6882057189941</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6707401275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5135622024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2865238189697</t>
+    <t xml:space="preserve">10.6707410812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5135612487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.286524772644</t>
   </si>
   <si>
     <t xml:space="preserve">10.2341318130493</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0594873428345</t>
+    <t xml:space="preserve">10.0594882965088</t>
   </si>
   <si>
     <t xml:space="preserve">10.1468095779419</t>
@@ -3311,22 +3311,22 @@
     <t xml:space="preserve">9.76259326934814</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98962879180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1992025375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29105472564697</t>
+    <t xml:space="preserve">9.9896297454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1992034912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29105567932129</t>
   </si>
   <si>
     <t xml:space="preserve">9.51809120178223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2211971282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25612545013428</t>
+    <t xml:space="preserve">9.22119808197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25612640380859</t>
   </si>
   <si>
     <t xml:space="preserve">9.0640172958374</t>
@@ -3335,31 +3335,31 @@
     <t xml:space="preserve">8.80205154418945</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81951522827148</t>
+    <t xml:space="preserve">8.8195161819458</t>
   </si>
   <si>
     <t xml:space="preserve">8.60121154785156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48769187927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19079875946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44403076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46149635314941</t>
+    <t xml:space="preserve">8.48769283294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19079780578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44403171539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46149444580078</t>
   </si>
   <si>
     <t xml:space="preserve">8.3392448425293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56628322601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34797668457031</t>
+    <t xml:space="preserve">8.56628227233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34797763824463</t>
   </si>
   <si>
     <t xml:space="preserve">8.54881763458252</t>
@@ -3371,19 +3371,19 @@
     <t xml:space="preserve">8.85444450378418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88937282562256</t>
+    <t xml:space="preserve">8.88937377929688</t>
   </si>
   <si>
     <t xml:space="preserve">9.04655265808105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01162433624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83698081970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7321949005127</t>
+    <t xml:space="preserve">9.01162338256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83697986602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73219394683838</t>
   </si>
   <si>
     <t xml:space="preserve">9.02908897399902</t>
@@ -3395,10 +3395,10 @@
     <t xml:space="preserve">9.41330528259277</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30851936340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27358913421631</t>
+    <t xml:space="preserve">9.308518409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27359008789062</t>
   </si>
   <si>
     <t xml:space="preserve">9.39584064483643</t>
@@ -3410,13 +3410,13 @@
     <t xml:space="preserve">9.55301952362061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.622878074646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91977119445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2690601348877</t>
+    <t xml:space="preserve">9.62287712097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91977214813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.269061088562</t>
   </si>
   <si>
     <t xml:space="preserve">9.65780639648438</t>
@@ -3428,13 +3428,13 @@
     <t xml:space="preserve">9.67527103424072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8324499130249</t>
+    <t xml:space="preserve">9.83245086669922</t>
   </si>
   <si>
     <t xml:space="preserve">10.0420236587524</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69273567199707</t>
+    <t xml:space="preserve">9.69273471832275</t>
   </si>
   <si>
     <t xml:space="preserve">9.93723678588867</t>
@@ -3449,10 +3449,10 @@
     <t xml:space="preserve">9.8673791885376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0944156646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0769519805908</t>
+    <t xml:space="preserve">10.0944166183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0769510269165</t>
   </si>
   <si>
     <t xml:space="preserve">9.79752159118652</t>
@@ -3464,7 +3464,7 @@
     <t xml:space="preserve">10.0070943832397</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4437046051025</t>
+    <t xml:space="preserve">10.4437036514282</t>
   </si>
   <si>
     <t xml:space="preserve">10.6532764434814</t>
@@ -3473,10 +3473,10 @@
     <t xml:space="preserve">10.6358118057251</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7405977249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7580623626709</t>
+    <t xml:space="preserve">10.7405986785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7580633163452</t>
   </si>
   <si>
     <t xml:space="preserve">10.9152431488037</t>
@@ -3485,19 +3485,19 @@
     <t xml:space="preserve">11.0200290679932</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3518524169922</t>
+    <t xml:space="preserve">11.3518514633179</t>
   </si>
   <si>
     <t xml:space="preserve">11.0025644302368</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9676351547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5310258865356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6183481216431</t>
+    <t xml:space="preserve">10.9676361083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.53102684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6183471679688</t>
   </si>
   <si>
     <t xml:space="preserve">10.7056694030762</t>
@@ -3509,19 +3509,19 @@
     <t xml:space="preserve">10.565954208374</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4786329269409</t>
+    <t xml:space="preserve">10.4786319732666</t>
   </si>
   <si>
     <t xml:space="preserve">10.1817378997803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2166662216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0245571136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84991455078125</t>
+    <t xml:space="preserve">10.216667175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0245580673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84991359710693</t>
   </si>
   <si>
     <t xml:space="preserve">10.1118803024292</t>
@@ -3533,10 +3533,10 @@
     <t xml:space="preserve">10.3563814163208</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5264949798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9456415176392</t>
+    <t xml:space="preserve">11.5264959335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9456405639648</t>
   </si>
   <si>
     <t xml:space="preserve">11.7011394500732</t>
@@ -3545,7 +3545,7 @@
     <t xml:space="preserve">12.1202850341797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.399715423584</t>
+    <t xml:space="preserve">12.3997144699097</t>
   </si>
   <si>
     <t xml:space="preserve">11.9281768798828</t>
@@ -3554,13 +3554,13 @@
     <t xml:space="preserve">11.8757839202881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0678911209106</t>
+    <t xml:space="preserve">12.067892074585</t>
   </si>
   <si>
     <t xml:space="preserve">12.0329627990723</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4650430679321</t>
+    <t xml:space="preserve">13.4650440216064</t>
   </si>
   <si>
     <t xml:space="preserve">13.1681480407715</t>
@@ -3569,13 +3569,13 @@
     <t xml:space="preserve">13.063362121582</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8712539672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6442155838013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9491119384766</t>
+    <t xml:space="preserve">12.8712530136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6442165374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9491128921509</t>
   </si>
   <si>
     <t xml:space="preserve">13.0746583938599</t>
@@ -3584,13 +3584,13 @@
     <t xml:space="preserve">12.9132423400879</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0387878417969</t>
+    <t xml:space="preserve">13.0387887954712</t>
   </si>
   <si>
     <t xml:space="preserve">13.0567235946655</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1284637451172</t>
+    <t xml:space="preserve">13.1284627914429</t>
   </si>
   <si>
     <t xml:space="preserve">13.2540082931519</t>
@@ -3605,7 +3605,7 @@
     <t xml:space="preserve">13.5947751998901</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4871635437012</t>
+    <t xml:space="preserve">13.4871644973755</t>
   </si>
   <si>
     <t xml:space="preserve">13.4512939453125</t>
@@ -3620,7 +3620,7 @@
     <t xml:space="preserve">13.5051002502441</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2002038955688</t>
+    <t xml:space="preserve">13.2002029418945</t>
   </si>
   <si>
     <t xml:space="preserve">12.9849824905396</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">12.5366058349609</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4110612869263</t>
+    <t xml:space="preserve">12.411060333252</t>
   </si>
   <si>
     <t xml:space="preserve">12.2496452331543</t>
@@ -3680,7 +3680,7 @@
     <t xml:space="preserve">12.285514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2675809860229</t>
+    <t xml:space="preserve">12.2675800323486</t>
   </si>
   <si>
     <t xml:space="preserve">12.6262817382812</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">12.5724763870239</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2137746810913</t>
+    <t xml:space="preserve">12.2137756347656</t>
   </si>
   <si>
     <t xml:space="preserve">12.5007352828979</t>
@@ -3704,10 +3704,10 @@
     <t xml:space="preserve">11.2990875244141</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5681133270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.639853477478</t>
+    <t xml:space="preserve">11.5681123733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6398525238037</t>
   </si>
   <si>
     <t xml:space="preserve">11.675724029541</t>
@@ -3719,22 +3719,22 @@
     <t xml:space="preserve">11.6577882766724</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4605026245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3708276748657</t>
+    <t xml:space="preserve">11.4605016708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.37082862854</t>
   </si>
   <si>
     <t xml:space="preserve">11.3528928756714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3349571228027</t>
+    <t xml:space="preserve">11.3349580764771</t>
   </si>
   <si>
     <t xml:space="preserve">11.2811527252197</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4963731765747</t>
+    <t xml:space="preserve">11.4963722229004</t>
   </si>
   <si>
     <t xml:space="preserve">11.5501775741577</t>
@@ -3749,16 +3749,16 @@
     <t xml:space="preserve">11.8012685775757</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7833347320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.908878326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9268140792847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.016489982605</t>
+    <t xml:space="preserve">11.7833337783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9088792800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.926815032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0164890289307</t>
   </si>
   <si>
     <t xml:space="preserve">12.0882301330566</t>
@@ -3797,7 +3797,7 @@
     <t xml:space="preserve">10.5278797149658</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7610359191895</t>
+    <t xml:space="preserve">10.7610349655151</t>
   </si>
   <si>
     <t xml:space="preserve">10.5816850662231</t>
@@ -3812,7 +3812,7 @@
     <t xml:space="preserve">10.2947235107422</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3664636611938</t>
+    <t xml:space="preserve">10.3664646148682</t>
   </si>
   <si>
     <t xml:space="preserve">10.2229833602905</t>
@@ -3833,19 +3833,19 @@
     <t xml:space="preserve">9.86428260803223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68493175506592</t>
+    <t xml:space="preserve">9.68493270874023</t>
   </si>
   <si>
     <t xml:space="preserve">9.75667190551758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77460765838623</t>
+    <t xml:space="preserve">9.77460670471191</t>
   </si>
   <si>
     <t xml:space="preserve">9.70286750793457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79254245758057</t>
+    <t xml:space="preserve">9.79254150390625</t>
   </si>
   <si>
     <t xml:space="preserve">9.66699695587158</t>
@@ -3860,7 +3860,7 @@
     <t xml:space="preserve">10.0436325073242</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1871128082275</t>
+    <t xml:space="preserve">10.1871137619019</t>
   </si>
   <si>
     <t xml:space="preserve">10.5099449157715</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">10.7431001663208</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8148403167725</t>
+    <t xml:space="preserve">10.8148412704468</t>
   </si>
   <si>
     <t xml:space="preserve">10.4740753173828</t>
@@ -3881,7 +3881,7 @@
     <t xml:space="preserve">9.9001522064209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95395851135254</t>
+    <t xml:space="preserve">9.95395755767822</t>
   </si>
   <si>
     <t xml:space="preserve">10.0795030593872</t>
@@ -3893,7 +3893,7 @@
     <t xml:space="preserve">9.98982810974121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2588529586792</t>
+    <t xml:space="preserve">10.2588539123535</t>
   </si>
   <si>
     <t xml:space="preserve">10.3126592636108</t>
@@ -3905,7 +3905,7 @@
     <t xml:space="preserve">10.4561395645142</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3305940628052</t>
+    <t xml:space="preserve">10.3305950164795</t>
   </si>
   <si>
     <t xml:space="preserve">10.2050485610962</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">9.91808795928955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88221836090088</t>
+    <t xml:space="preserve">9.88221740722656</t>
   </si>
   <si>
     <t xml:space="preserve">10.0974388122559</t>
@@ -3941,31 +3941,31 @@
     <t xml:space="preserve">9.3262300491333</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45177555084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5996198654175</t>
+    <t xml:space="preserve">9.4517765045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5996189117432</t>
   </si>
   <si>
     <t xml:space="preserve">9.93602275848389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4920091629028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5637493133545</t>
+    <t xml:space="preserve">10.4920101165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5637502670288</t>
   </si>
   <si>
     <t xml:space="preserve">10.4382047653198</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6713600158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9045162200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8327760696411</t>
+    <t xml:space="preserve">10.6713590621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9045152664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8327751159668</t>
   </si>
   <si>
     <t xml:space="preserve">10.7251653671265</t>
@@ -3980,7 +3980,7 @@
     <t xml:space="preserve">10.9224510192871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6892957687378</t>
+    <t xml:space="preserve">10.6892948150635</t>
   </si>
   <si>
     <t xml:space="preserve">11.2094125747681</t>
@@ -4620,6 +4620,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.02999973297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22000026702881</t>
   </si>
 </sst>
 </file>
@@ -10384,7 +10387,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G209" t="s">
-        <v>166</v>
+        <v>87</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -10410,7 +10413,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G210" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -10436,7 +10439,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G211" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -10462,7 +10465,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G212" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -10488,7 +10491,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G213" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -10514,7 +10517,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G214" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -10540,7 +10543,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G215" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -10566,7 +10569,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G216" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -10592,7 +10595,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G217" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -10644,7 +10647,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G219" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -10748,7 +10751,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G223" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -10774,7 +10777,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G224" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -10800,7 +10803,7 @@
         <v>16</v>
       </c>
       <c r="G225" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -10826,7 +10829,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G226" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -10852,7 +10855,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G227" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -10878,7 +10881,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G228" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -10904,7 +10907,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G229" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -10930,7 +10933,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G230" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -10956,7 +10959,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G231" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -10982,7 +10985,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G232" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -11008,7 +11011,7 @@
         <v>16.5699996948242</v>
       </c>
       <c r="G233" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -11034,7 +11037,7 @@
         <v>16.3899993896484</v>
       </c>
       <c r="G234" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -11060,7 +11063,7 @@
         <v>16.25</v>
       </c>
       <c r="G235" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -11086,7 +11089,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G236" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -11112,7 +11115,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G237" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -11138,7 +11141,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G238" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -11190,7 +11193,7 @@
         <v>17</v>
       </c>
       <c r="G240" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -11242,7 +11245,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G242" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -11294,7 +11297,7 @@
         <v>17</v>
       </c>
       <c r="G244" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -11320,7 +11323,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G245" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -11346,7 +11349,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G246" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -11398,7 +11401,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G248" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -11450,7 +11453,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G250" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -11476,7 +11479,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G251" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -11528,7 +11531,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G253" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -11554,7 +11557,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G254" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -11580,7 +11583,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G255" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -11632,7 +11635,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G257" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -11684,7 +11687,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G259" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -11736,7 +11739,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G261" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -11762,7 +11765,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G262" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -11840,7 +11843,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G265" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -11918,7 +11921,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G268" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -11970,7 +11973,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G270" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -11996,7 +11999,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G271" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -12048,7 +12051,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G273" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -12074,7 +12077,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G274" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -12126,7 +12129,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G276" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -12152,7 +12155,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G277" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -12178,7 +12181,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G278" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -12204,7 +12207,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G279" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -12230,7 +12233,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G280" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -12256,7 +12259,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G281" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -12282,7 +12285,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G282" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -12308,7 +12311,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G283" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -12360,7 +12363,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G285" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -12386,7 +12389,7 @@
         <v>18.4099998474121</v>
       </c>
       <c r="G286" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -12412,7 +12415,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G287" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -12438,7 +12441,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G288" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -12464,7 +12467,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G289" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -12490,7 +12493,7 @@
         <v>18.4899997711182</v>
       </c>
       <c r="G290" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -12516,7 +12519,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G291" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -12542,7 +12545,7 @@
         <v>18.4099998474121</v>
       </c>
       <c r="G292" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -12594,7 +12597,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G294" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -12620,7 +12623,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G295" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -12646,7 +12649,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G296" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -12672,7 +12675,7 @@
         <v>18.1200008392334</v>
       </c>
       <c r="G297" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -12698,7 +12701,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G298" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -12724,7 +12727,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G299" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -12750,7 +12753,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G300" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -12776,7 +12779,7 @@
         <v>19.3899993896484</v>
       </c>
       <c r="G301" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -12802,7 +12805,7 @@
         <v>19.6299991607666</v>
       </c>
       <c r="G302" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -12828,7 +12831,7 @@
         <v>20</v>
       </c>
       <c r="G303" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -12854,7 +12857,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G304" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -12880,7 +12883,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G305" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -12906,7 +12909,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G306" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -12932,7 +12935,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G307" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -12958,7 +12961,7 @@
         <v>20.3099994659424</v>
       </c>
       <c r="G308" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -12984,7 +12987,7 @@
         <v>20.9899997711182</v>
       </c>
       <c r="G309" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -13010,7 +13013,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G310" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -13036,7 +13039,7 @@
         <v>20.25</v>
       </c>
       <c r="G311" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -13062,7 +13065,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G312" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -13088,7 +13091,7 @@
         <v>20.5200004577637</v>
       </c>
       <c r="G313" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -13114,7 +13117,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G314" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -13140,7 +13143,7 @@
         <v>20.5</v>
       </c>
       <c r="G315" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -13166,7 +13169,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G316" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -13192,7 +13195,7 @@
         <v>21</v>
       </c>
       <c r="G317" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -13218,7 +13221,7 @@
         <v>20.75</v>
       </c>
       <c r="G318" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -13244,7 +13247,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G319" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -13270,7 +13273,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G320" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -13296,7 +13299,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G321" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -13322,7 +13325,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G322" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -13348,7 +13351,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G323" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -13374,7 +13377,7 @@
         <v>20.7700004577637</v>
       </c>
       <c r="G324" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -13400,7 +13403,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G325" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -13426,7 +13429,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G326" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -13452,7 +13455,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G327" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -13478,7 +13481,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G328" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -13504,7 +13507,7 @@
         <v>21</v>
       </c>
       <c r="G329" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -13530,7 +13533,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G330" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -13556,7 +13559,7 @@
         <v>20.8199996948242</v>
       </c>
       <c r="G331" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -13582,7 +13585,7 @@
         <v>21.25</v>
       </c>
       <c r="G332" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -13608,7 +13611,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G333" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -13634,7 +13637,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G334" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -13660,7 +13663,7 @@
         <v>20.9699993133545</v>
       </c>
       <c r="G335" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -13686,7 +13689,7 @@
         <v>21.75</v>
       </c>
       <c r="G336" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -13712,7 +13715,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G337" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -13738,7 +13741,7 @@
         <v>21.7199993133545</v>
       </c>
       <c r="G338" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -13764,7 +13767,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G339" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -13790,7 +13793,7 @@
         <v>22.1700000762939</v>
       </c>
       <c r="G340" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -13816,7 +13819,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G341" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -13842,7 +13845,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G342" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -13868,7 +13871,7 @@
         <v>22.0699996948242</v>
       </c>
       <c r="G343" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -13894,7 +13897,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G344" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -13920,7 +13923,7 @@
         <v>22.2299995422363</v>
       </c>
       <c r="G345" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -13946,7 +13949,7 @@
         <v>22.8099994659424</v>
       </c>
       <c r="G346" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -13972,7 +13975,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G347" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -13998,7 +14001,7 @@
         <v>22.3700008392334</v>
       </c>
       <c r="G348" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -14024,7 +14027,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G349" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -14050,7 +14053,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G350" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -14076,7 +14079,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G351" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -14102,7 +14105,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G352" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -14128,7 +14131,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G353" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -14154,7 +14157,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G354" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -14180,7 +14183,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G355" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -14206,7 +14209,7 @@
         <v>22.2399997711182</v>
       </c>
       <c r="G356" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -14232,7 +14235,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G357" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -14258,7 +14261,7 @@
         <v>22</v>
       </c>
       <c r="G358" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -14284,7 +14287,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G359" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -14310,7 +14313,7 @@
         <v>21.5100002288818</v>
       </c>
       <c r="G360" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -14336,7 +14339,7 @@
         <v>21.7900009155273</v>
       </c>
       <c r="G361" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -14362,7 +14365,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G362" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -14388,7 +14391,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G363" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -14414,7 +14417,7 @@
         <v>21.9099998474121</v>
       </c>
       <c r="G364" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -14440,7 +14443,7 @@
         <v>21.6900005340576</v>
       </c>
       <c r="G365" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -14466,7 +14469,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G366" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -14492,7 +14495,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G367" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -14518,7 +14521,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G368" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -14544,7 +14547,7 @@
         <v>21.9300003051758</v>
       </c>
       <c r="G369" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -14570,7 +14573,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G370" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -14596,7 +14599,7 @@
         <v>21.6200008392334</v>
       </c>
       <c r="G371" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -14622,7 +14625,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G372" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -14648,7 +14651,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G373" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -14674,7 +14677,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G374" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -14700,7 +14703,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G375" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -14726,7 +14729,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G376" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -14752,7 +14755,7 @@
         <v>21.3899993896484</v>
       </c>
       <c r="G377" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -14778,7 +14781,7 @@
         <v>21.4300003051758</v>
       </c>
       <c r="G378" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -14804,7 +14807,7 @@
         <v>21.5</v>
       </c>
       <c r="G379" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -14830,7 +14833,7 @@
         <v>21.6100006103516</v>
       </c>
       <c r="G380" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -14856,7 +14859,7 @@
         <v>21.5100002288818</v>
       </c>
       <c r="G381" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -14882,7 +14885,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G382" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -14908,7 +14911,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G383" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -14934,7 +14937,7 @@
         <v>20.8099994659424</v>
       </c>
       <c r="G384" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -14960,7 +14963,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G385" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -14986,7 +14989,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G386" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -15012,7 +15015,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G387" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -15038,7 +15041,7 @@
         <v>20.6100006103516</v>
       </c>
       <c r="G388" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -15064,7 +15067,7 @@
         <v>21</v>
       </c>
       <c r="G389" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -15090,7 +15093,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G390" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -15116,7 +15119,7 @@
         <v>20.6900005340576</v>
       </c>
       <c r="G391" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -15142,7 +15145,7 @@
         <v>21</v>
       </c>
       <c r="G392" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -15168,7 +15171,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G393" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -15194,7 +15197,7 @@
         <v>21.3299999237061</v>
       </c>
       <c r="G394" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -15220,7 +15223,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G395" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -15246,7 +15249,7 @@
         <v>21.9300003051758</v>
       </c>
       <c r="G396" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -15272,7 +15275,7 @@
         <v>22</v>
       </c>
       <c r="G397" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -15298,7 +15301,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G398" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -15324,7 +15327,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G399" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -15350,7 +15353,7 @@
         <v>22.3600006103516</v>
       </c>
       <c r="G400" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -15376,7 +15379,7 @@
         <v>22.3600006103516</v>
       </c>
       <c r="G401" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -15402,7 +15405,7 @@
         <v>22.3700008392334</v>
       </c>
       <c r="G402" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -15428,7 +15431,7 @@
         <v>22.5</v>
       </c>
       <c r="G403" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -15454,7 +15457,7 @@
         <v>21.7700004577637</v>
       </c>
       <c r="G404" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -15480,7 +15483,7 @@
         <v>21.6200008392334</v>
       </c>
       <c r="G405" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -15506,7 +15509,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G406" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -15532,7 +15535,7 @@
         <v>21.6900005340576</v>
       </c>
       <c r="G407" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -15558,7 +15561,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G408" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -15584,7 +15587,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G409" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -15610,7 +15613,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G410" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -15636,7 +15639,7 @@
         <v>21.7700004577637</v>
       </c>
       <c r="G411" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -15662,7 +15665,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G412" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -15688,7 +15691,7 @@
         <v>21.4099998474121</v>
       </c>
       <c r="G413" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -15714,7 +15717,7 @@
         <v>21.3199996948242</v>
       </c>
       <c r="G414" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -15740,7 +15743,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G415" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -15766,7 +15769,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G416" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -15792,7 +15795,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G417" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -15818,7 +15821,7 @@
         <v>21.1900005340576</v>
       </c>
       <c r="G418" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -15844,7 +15847,7 @@
         <v>21.2099990844727</v>
       </c>
       <c r="G419" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -15870,7 +15873,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G420" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -15896,7 +15899,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G421" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -15922,7 +15925,7 @@
         <v>20.9899997711182</v>
       </c>
       <c r="G422" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -15948,7 +15951,7 @@
         <v>20.7700004577637</v>
       </c>
       <c r="G423" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -15974,7 +15977,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G424" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -16000,7 +16003,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G425" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -16026,7 +16029,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G426" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -16052,7 +16055,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G427" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -16078,7 +16081,7 @@
         <v>21.2299995422363</v>
       </c>
       <c r="G428" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -16104,7 +16107,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G429" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -16130,7 +16133,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G430" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -16156,7 +16159,7 @@
         <v>21.4599990844727</v>
       </c>
       <c r="G431" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -16182,7 +16185,7 @@
         <v>21.5100002288818</v>
       </c>
       <c r="G432" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -16208,7 +16211,7 @@
         <v>21.9300003051758</v>
       </c>
       <c r="G433" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -16234,7 +16237,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G434" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -16260,7 +16263,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G435" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -16286,7 +16289,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G436" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -16312,7 +16315,7 @@
         <v>22.3299999237061</v>
       </c>
       <c r="G437" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -16338,7 +16341,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G438" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -16364,7 +16367,7 @@
         <v>22</v>
       </c>
       <c r="G439" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -16390,7 +16393,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G440" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -16416,7 +16419,7 @@
         <v>22.0799999237061</v>
       </c>
       <c r="G441" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -16442,7 +16445,7 @@
         <v>22.0799999237061</v>
       </c>
       <c r="G442" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -16468,7 +16471,7 @@
         <v>22.0699996948242</v>
       </c>
       <c r="G443" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -16494,7 +16497,7 @@
         <v>22.0900001525879</v>
       </c>
       <c r="G444" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -16520,7 +16523,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G445" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -16546,7 +16549,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G446" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -16572,7 +16575,7 @@
         <v>22.3700008392334</v>
       </c>
       <c r="G447" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -16598,7 +16601,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G448" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -16624,7 +16627,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G449" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -16650,7 +16653,7 @@
         <v>22.4699993133545</v>
       </c>
       <c r="G450" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -16676,7 +16679,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G451" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -16702,7 +16705,7 @@
         <v>22.7099990844727</v>
       </c>
       <c r="G452" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -16728,7 +16731,7 @@
         <v>22.75</v>
       </c>
       <c r="G453" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -16754,7 +16757,7 @@
         <v>22.5900001525879</v>
       </c>
       <c r="G454" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -16780,7 +16783,7 @@
         <v>22.9200000762939</v>
       </c>
       <c r="G455" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -16806,7 +16809,7 @@
         <v>22.7299995422363</v>
       </c>
       <c r="G456" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -16832,7 +16835,7 @@
         <v>22.6900005340576</v>
       </c>
       <c r="G457" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -16858,7 +16861,7 @@
         <v>22.8899993896484</v>
       </c>
       <c r="G458" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -16884,7 +16887,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G459" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -16910,7 +16913,7 @@
         <v>23.3299999237061</v>
       </c>
       <c r="G460" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -16936,7 +16939,7 @@
         <v>22.7800006866455</v>
       </c>
       <c r="G461" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -16962,7 +16965,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G462" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -16988,7 +16991,7 @@
         <v>22.8700008392334</v>
       </c>
       <c r="G463" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -17014,7 +17017,7 @@
         <v>22.6599998474121</v>
       </c>
       <c r="G464" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -17040,7 +17043,7 @@
         <v>22.3899993896484</v>
       </c>
       <c r="G465" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -17066,7 +17069,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="G466" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -17092,7 +17095,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G467" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -17118,7 +17121,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G468" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -17144,7 +17147,7 @@
         <v>22.1700000762939</v>
       </c>
       <c r="G469" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -17170,7 +17173,7 @@
         <v>21.9300003051758</v>
       </c>
       <c r="G470" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -17196,7 +17199,7 @@
         <v>22.0900001525879</v>
       </c>
       <c r="G471" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -17222,7 +17225,7 @@
         <v>22</v>
       </c>
       <c r="G472" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -17248,7 +17251,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G473" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -17274,7 +17277,7 @@
         <v>21.8400001525879</v>
       </c>
       <c r="G474" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -17300,7 +17303,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G475" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -17326,7 +17329,7 @@
         <v>21.4899997711182</v>
       </c>
       <c r="G476" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -17352,7 +17355,7 @@
         <v>21.3799991607666</v>
       </c>
       <c r="G477" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -17378,7 +17381,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G478" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -17404,7 +17407,7 @@
         <v>20.75</v>
       </c>
       <c r="G479" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -17430,7 +17433,7 @@
         <v>20.4699993133545</v>
       </c>
       <c r="G480" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -17456,7 +17459,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G481" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -17482,7 +17485,7 @@
         <v>21.3199996948242</v>
       </c>
       <c r="G482" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -17508,7 +17511,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G483" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -17534,7 +17537,7 @@
         <v>21.5</v>
       </c>
       <c r="G484" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -17560,7 +17563,7 @@
         <v>21.7700004577637</v>
       </c>
       <c r="G485" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -17586,7 +17589,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G486" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -17612,7 +17615,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G487" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -17638,7 +17641,7 @@
         <v>21.5100002288818</v>
       </c>
       <c r="G488" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -17664,7 +17667,7 @@
         <v>21.4099998474121</v>
       </c>
       <c r="G489" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -17690,7 +17693,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G490" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -17716,7 +17719,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G491" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -17742,7 +17745,7 @@
         <v>21.7099990844727</v>
       </c>
       <c r="G492" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -17768,7 +17771,7 @@
         <v>21.5</v>
       </c>
       <c r="G493" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -17794,7 +17797,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G494" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -17820,7 +17823,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G495" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -17846,7 +17849,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G496" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -17872,7 +17875,7 @@
         <v>21.8899993896484</v>
       </c>
       <c r="G497" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -17898,7 +17901,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G498" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -17924,7 +17927,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G499" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -17950,7 +17953,7 @@
         <v>21.3899993896484</v>
       </c>
       <c r="G500" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -17976,7 +17979,7 @@
         <v>21.3799991607666</v>
       </c>
       <c r="G501" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -18002,7 +18005,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G502" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -18028,7 +18031,7 @@
         <v>21.2399997711182</v>
       </c>
       <c r="G503" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -18054,7 +18057,7 @@
         <v>21</v>
       </c>
       <c r="G504" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -18080,7 +18083,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G505" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -18106,7 +18109,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G506" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -18132,7 +18135,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G507" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -18158,7 +18161,7 @@
         <v>21.2800006866455</v>
       </c>
       <c r="G508" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -18184,7 +18187,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G509" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -18210,7 +18213,7 @@
         <v>21.6700000762939</v>
       </c>
       <c r="G510" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -18236,7 +18239,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G511" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -18262,7 +18265,7 @@
         <v>21.5</v>
       </c>
       <c r="G512" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -18288,7 +18291,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G513" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -18314,7 +18317,7 @@
         <v>21.7199993133545</v>
       </c>
       <c r="G514" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -18340,7 +18343,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G515" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -18366,7 +18369,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G516" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -18392,7 +18395,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G517" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -18418,7 +18421,7 @@
         <v>21.2199993133545</v>
       </c>
       <c r="G518" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -18444,7 +18447,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G519" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -18470,7 +18473,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G520" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -18496,7 +18499,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G521" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -18522,7 +18525,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G522" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -18548,7 +18551,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G523" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -18574,7 +18577,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G524" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -18600,7 +18603,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G525" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -18626,7 +18629,7 @@
         <v>22.6200008392334</v>
       </c>
       <c r="G526" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -18652,7 +18655,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G527" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -18678,7 +18681,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G528" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -18704,7 +18707,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G529" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -18730,7 +18733,7 @@
         <v>22.8199996948242</v>
       </c>
       <c r="G530" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -18756,7 +18759,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G531" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -18782,7 +18785,7 @@
         <v>22.3199996948242</v>
       </c>
       <c r="G532" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -18808,7 +18811,7 @@
         <v>22.2800006866455</v>
       </c>
       <c r="G533" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -18834,7 +18837,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G534" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -18860,7 +18863,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G535" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -18886,7 +18889,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G536" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -18912,7 +18915,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G537" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -18938,7 +18941,7 @@
         <v>21.9599990844727</v>
       </c>
       <c r="G538" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -18964,7 +18967,7 @@
         <v>21.1399993896484</v>
       </c>
       <c r="G539" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -18990,7 +18993,7 @@
         <v>21</v>
       </c>
       <c r="G540" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -19016,7 +19019,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G541" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -19042,7 +19045,7 @@
         <v>21</v>
       </c>
       <c r="G542" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -19068,7 +19071,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G543" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -19094,7 +19097,7 @@
         <v>21</v>
       </c>
       <c r="G544" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -19120,7 +19123,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G545" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -19146,7 +19149,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G546" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -19172,7 +19175,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G547" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -19198,7 +19201,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G548" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -19224,7 +19227,7 @@
         <v>21.4599990844727</v>
       </c>
       <c r="G549" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -19250,7 +19253,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G550" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -19276,7 +19279,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G551" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -19302,7 +19305,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G552" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -19328,7 +19331,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G553" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -19354,7 +19357,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G554" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -19380,7 +19383,7 @@
         <v>21.1399993896484</v>
       </c>
       <c r="G555" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -19406,7 +19409,7 @@
         <v>21</v>
       </c>
       <c r="G556" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -19432,7 +19435,7 @@
         <v>21.0400009155273</v>
       </c>
       <c r="G557" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -19458,7 +19461,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G558" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -19484,7 +19487,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G559" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -19510,7 +19513,7 @@
         <v>22.3600006103516</v>
       </c>
       <c r="G560" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -19536,7 +19539,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G561" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -19562,7 +19565,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G562" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -19588,7 +19591,7 @@
         <v>22.5</v>
       </c>
       <c r="G563" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -19614,7 +19617,7 @@
         <v>23.8600006103516</v>
       </c>
       <c r="G564" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -19640,7 +19643,7 @@
         <v>23.7800006866455</v>
       </c>
       <c r="G565" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -19666,7 +19669,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G566" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -19692,7 +19695,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G567" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -19718,7 +19721,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G568" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -19744,7 +19747,7 @@
         <v>24.4599990844727</v>
       </c>
       <c r="G569" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -19770,7 +19773,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G570" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -19796,7 +19799,7 @@
         <v>24.1599998474121</v>
       </c>
       <c r="G571" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -19822,7 +19825,7 @@
         <v>24.1599998474121</v>
       </c>
       <c r="G572" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -19848,7 +19851,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G573" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -19874,7 +19877,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G574" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -19900,7 +19903,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G575" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -19926,7 +19929,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G576" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -19952,7 +19955,7 @@
         <v>25.1399993896484</v>
       </c>
       <c r="G577" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -19978,7 +19981,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G578" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -20004,7 +20007,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G579" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -20030,7 +20033,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G580" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -20056,7 +20059,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G581" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -20082,7 +20085,7 @@
         <v>25</v>
       </c>
       <c r="G582" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -20108,7 +20111,7 @@
         <v>25.1399993896484</v>
       </c>
       <c r="G583" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -20134,7 +20137,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G584" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -20160,7 +20163,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G585" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -20186,7 +20189,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G586" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -20212,7 +20215,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G587" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -20238,7 +20241,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G588" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -20264,7 +20267,7 @@
         <v>24.8799991607666</v>
       </c>
       <c r="G589" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -20290,7 +20293,7 @@
         <v>24.8400001525879</v>
       </c>
       <c r="G590" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -20316,7 +20319,7 @@
         <v>24.8799991607666</v>
       </c>
       <c r="G591" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -20342,7 +20345,7 @@
         <v>24.9200000762939</v>
       </c>
       <c r="G592" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -20368,7 +20371,7 @@
         <v>24.8799991607666</v>
       </c>
       <c r="G593" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -20394,7 +20397,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G594" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -20420,7 +20423,7 @@
         <v>25.2600002288818</v>
       </c>
       <c r="G595" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -20446,7 +20449,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G596" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -20472,7 +20475,7 @@
         <v>25.3400001525879</v>
       </c>
       <c r="G597" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -20498,7 +20501,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G598" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -20524,7 +20527,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G599" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -20550,7 +20553,7 @@
         <v>25.1599998474121</v>
       </c>
       <c r="G600" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -20576,7 +20579,7 @@
         <v>25.1599998474121</v>
       </c>
       <c r="G601" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -20602,7 +20605,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G602" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -20628,7 +20631,7 @@
         <v>25.3600006103516</v>
       </c>
       <c r="G603" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -20654,7 +20657,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G604" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -20680,7 +20683,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G605" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -20706,7 +20709,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G606" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -20732,7 +20735,7 @@
         <v>23.4599990844727</v>
       </c>
       <c r="G607" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -20758,7 +20761,7 @@
         <v>23.7399997711182</v>
       </c>
       <c r="G608" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -20784,7 +20787,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G609" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -20810,7 +20813,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G610" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -20836,7 +20839,7 @@
         <v>23.3799991607666</v>
       </c>
       <c r="G611" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -20862,7 +20865,7 @@
         <v>23.3199996948242</v>
       </c>
       <c r="G612" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -20888,7 +20891,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G613" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -20914,7 +20917,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G614" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -20940,7 +20943,7 @@
         <v>23</v>
       </c>
       <c r="G615" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -20966,7 +20969,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G616" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -20992,7 +20995,7 @@
         <v>23.3199996948242</v>
       </c>
       <c r="G617" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -21018,7 +21021,7 @@
         <v>23.1800003051758</v>
       </c>
       <c r="G618" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -21044,7 +21047,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G619" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -21070,7 +21073,7 @@
         <v>23.2399997711182</v>
       </c>
       <c r="G620" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -21096,7 +21099,7 @@
         <v>23.1599998474121</v>
       </c>
       <c r="G621" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -21122,7 +21125,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G622" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -21148,7 +21151,7 @@
         <v>23.0799999237061</v>
       </c>
       <c r="G623" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -21174,7 +21177,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G624" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -21200,7 +21203,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G625" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -21226,7 +21229,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G626" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21252,7 +21255,7 @@
         <v>23.0599994659424</v>
       </c>
       <c r="G627" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -21278,7 +21281,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G628" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -21304,7 +21307,7 @@
         <v>23.0799999237061</v>
       </c>
       <c r="G629" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -21330,7 +21333,7 @@
         <v>22.9400005340576</v>
       </c>
       <c r="G630" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -21356,7 +21359,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G631" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -21382,7 +21385,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G632" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -21408,7 +21411,7 @@
         <v>22.3199996948242</v>
       </c>
       <c r="G633" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -21434,7 +21437,7 @@
         <v>22.1800003051758</v>
       </c>
       <c r="G634" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -21460,7 +21463,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G635" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -21486,7 +21489,7 @@
         <v>22.5</v>
       </c>
       <c r="G636" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -21512,7 +21515,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G637" t="s">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -21564,7 +21567,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G639" t="s">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -21616,7 +21619,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G641" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -21954,7 +21957,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G654" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -22032,7 +22035,7 @@
         <v>23.3199996948242</v>
       </c>
       <c r="G657" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -22058,7 +22061,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G658" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -23436,7 +23439,7 @@
         <v>23</v>
       </c>
       <c r="G711" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -70036,7 +70039,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6912731481</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>110149</v>
@@ -70057,6 +70060,32 @@
         <v>1521</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45966.6911805556</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>95386</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>9.22000026702881</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>9.02999973297119</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>9.05000019073486</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>9.22000026702881</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1536</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARR.MI.xlsx
+++ b/data/MARR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="1541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="1542">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,73 +44,73 @@
     <t xml:space="preserve">MARR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.289402961731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1812982559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9939203262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9506797790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5903377532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6552000045776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7344741821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4389934539795</t>
+    <t xml:space="preserve">13.2894010543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1812992095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9939212799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9506778717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5903367996216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.655198097229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7344732284546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4389953613281</t>
   </si>
   <si>
     <t xml:space="preserve">12.4462013244629</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9849643707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0858602523804</t>
+    <t xml:space="preserve">11.9849624633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0858583450317</t>
   </si>
   <si>
     <t xml:space="preserve">11.6462430953979</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2155828475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8353691101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6768178939819</t>
+    <t xml:space="preserve">12.2155838012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8353681564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6768188476562</t>
   </si>
   <si>
     <t xml:space="preserve">12.5615110397339</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5543041229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6407861709595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7200603485107</t>
+    <t xml:space="preserve">12.5543022155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6407871246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7200613021851</t>
   </si>
   <si>
     <t xml:space="preserve">12.9722995758057</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7777156829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3308916091919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5110635757446</t>
+    <t xml:space="preserve">12.7777137756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3308925628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5110654830933</t>
   </si>
   <si>
     <t xml:space="preserve">12.2948570251465</t>
@@ -125,280 +125,280 @@
     <t xml:space="preserve">11.8840684890747</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5885877609253</t>
+    <t xml:space="preserve">11.5885887145996</t>
   </si>
   <si>
     <t xml:space="preserve">11.8912754058838</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9273080825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0426177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2011690139771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3957548141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7056474685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6047515869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5759248733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9362659454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1596784591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9434719085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0731954574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8858184814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5975437164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.078652381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3597202301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6696147918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8137502670288</t>
+    <t xml:space="preserve">11.9273099899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0426168441772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2011671066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3957529067993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7056465148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6047496795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5759229660034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9362668991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1596765518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.943470954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0731945037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8858165740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.597544670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0786533355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3597183227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6696138381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8137512207031</t>
   </si>
   <si>
     <t xml:space="preserve">12.6984405517578</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8714027404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.453408241272</t>
+    <t xml:space="preserve">12.8714056015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4534072875977</t>
   </si>
   <si>
     <t xml:space="preserve">12.3453044891357</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6840267181396</t>
+    <t xml:space="preserve">12.6840257644653</t>
   </si>
   <si>
     <t xml:space="preserve">12.7560949325562</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1524715423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2677783966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3326406478882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0804042816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1885032653809</t>
+    <t xml:space="preserve">13.1524705886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2677803039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3326416015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0804023742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1885042190552</t>
   </si>
   <si>
     <t xml:space="preserve">13.2605724334717</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7073955535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4911918640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3470544815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.001127243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9002323150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.828164100647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7921276092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.058783531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1020212173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8065423965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2821922302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1380567550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8425760269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8930244445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9074373245239</t>
+    <t xml:space="preserve">13.7073965072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.491189956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.347056388855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0011281967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9002304077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8281621932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7921285629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0587816238403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1020231246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8065433502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2821941375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1380558013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8425769805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8930253982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9074382781982</t>
   </si>
   <si>
     <t xml:space="preserve">13.0227479934692</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6624050140381</t>
+    <t xml:space="preserve">12.6624069213867</t>
   </si>
   <si>
     <t xml:space="preserve">12.8786106109619</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6335773468018</t>
+    <t xml:space="preserve">12.6335802078247</t>
   </si>
   <si>
     <t xml:space="preserve">12.7488889694214</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0258741378784</t>
+    <t xml:space="preserve">13.0258750915527</t>
   </si>
   <si>
     <t xml:space="preserve">13.0183887481689</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2579460144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2504587173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4301271438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4825305938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3103485107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2654304504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4750423431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3702363967896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2878885269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2729177474976</t>
+    <t xml:space="preserve">13.25794506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2504596710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4301261901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4825286865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3103504180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2654323577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4750442504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3702392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2878904342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2729158401489</t>
   </si>
   <si>
     <t xml:space="preserve">13.2804040908813</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8012914657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8836374282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6141386032104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3146944046021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4494428634644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8087787628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7938070297241</t>
+    <t xml:space="preserve">12.801290512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8836364746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6141376495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3146924972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.44944190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8087778091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7938051223755</t>
   </si>
   <si>
     <t xml:space="preserve">13.0782775878906</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4419574737549</t>
+    <t xml:space="preserve">12.4419565200806</t>
   </si>
   <si>
     <t xml:space="preserve">11.7831764221191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2847471237183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7339172363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4226408004761</t>
+    <t xml:space="preserve">12.2847480773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7339153289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4226427078247</t>
   </si>
   <si>
     <t xml:space="preserve">13.5274467468262</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0558204650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4525852203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3328056335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7595167160034</t>
+    <t xml:space="preserve">13.0558214187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4525833129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3328046798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7595157623291</t>
   </si>
   <si>
     <t xml:space="preserve">13.7295722961426</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7220869064331</t>
+    <t xml:space="preserve">13.7220859527588</t>
   </si>
   <si>
     <t xml:space="preserve">13.5349321365356</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4900140762329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7370595932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.014045715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7071132659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8493499755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1113653182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9766149520874</t>
+    <t xml:space="preserve">13.4900150299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7370586395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0140438079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7071142196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8493490219116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.111364364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9766139984131</t>
   </si>
   <si>
     <t xml:space="preserve">14.0814199447632</t>
@@ -407,28 +407,28 @@
     <t xml:space="preserve">13.7445440292358</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9990730285645</t>
+    <t xml:space="preserve">13.9990720748901</t>
   </si>
   <si>
     <t xml:space="preserve">13.5049886703491</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6397390365601</t>
+    <t xml:space="preserve">13.6397361755371</t>
   </si>
   <si>
     <t xml:space="preserve">13.6621971130371</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6097927093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3477783203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4151544570923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2205152511597</t>
+    <t xml:space="preserve">13.6097917556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3477773666382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4151554107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.220513343811</t>
   </si>
   <si>
     <t xml:space="preserve">13.0857639312744</t>
@@ -437,28 +437,28 @@
     <t xml:space="preserve">13.1007375717163</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0633058547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2354869842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1456527709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9285554885864</t>
+    <t xml:space="preserve">13.063304901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2354888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1456508636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9285564422607</t>
   </si>
   <si>
     <t xml:space="preserve">13.2055416107178</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1082229614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1980562210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1157083511353</t>
+    <t xml:space="preserve">13.1082248687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.198055267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1157073974609</t>
   </si>
   <si>
     <t xml:space="preserve">13.0109014511108</t>
@@ -467,49 +467,49 @@
     <t xml:space="preserve">12.9135837554932</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8611812591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9435272216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1905708312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4076662063599</t>
+    <t xml:space="preserve">12.861180305481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9435291290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1905717849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4076671600342</t>
   </si>
   <si>
     <t xml:space="preserve">13.3552646636963</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2130289077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.340292930603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9659852981567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8761548995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8312349319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9809598922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7638597488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7114582061768</t>
+    <t xml:space="preserve">13.2130298614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3402948379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9659862518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8761529922485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8312339782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9809608459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7638607025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7114562988281</t>
   </si>
   <si>
     <t xml:space="preserve">12.8686666488647</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7563772201538</t>
+    <t xml:space="preserve">12.7563762664795</t>
   </si>
   <si>
     <t xml:space="preserve">12.7488880157471</t>
@@ -518,16 +518,16 @@
     <t xml:space="preserve">12.6815137863159</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5767049789429</t>
+    <t xml:space="preserve">12.5767068862915</t>
   </si>
   <si>
     <t xml:space="preserve">12.546763420105</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5317907333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5617341995239</t>
+    <t xml:space="preserve">12.5317897796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5617351531982</t>
   </si>
   <si>
     <t xml:space="preserve">12.5542497634888</t>
@@ -536,43 +536,43 @@
     <t xml:space="preserve">12.4194984436035</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2772617340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4719018936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5018472671509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3970394134521</t>
+    <t xml:space="preserve">12.2772607803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4718999862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5018463134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3970403671265</t>
   </si>
   <si>
     <t xml:space="preserve">11.9778156280518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3596096038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4943609237671</t>
+    <t xml:space="preserve">12.3596105575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4943599700928</t>
   </si>
   <si>
     <t xml:space="preserve">12.3820676803589</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4045248031616</t>
+    <t xml:space="preserve">12.4045257568359</t>
   </si>
   <si>
     <t xml:space="preserve">12.2697744369507</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1649684906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2548046112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3371515274048</t>
+    <t xml:space="preserve">12.1649694442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2548055648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3371505737305</t>
   </si>
   <si>
     <t xml:space="preserve">12.3221778869629</t>
@@ -581,1849 +581,1849 @@
     <t xml:space="preserve">12.7264289855957</t>
   </si>
   <si>
+    <t xml:space="preserve">12.6740255355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.786319732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0932502746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9510126113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1306829452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9884433746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1381692886353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.160626411438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1830854415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1681108474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2279996871948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.00341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1755962371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4001817703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3852071762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8643245697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.91672706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5199604034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4450988769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3627519607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4600696563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5124731063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4376134872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8268899917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6247682571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8044347763062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7819757461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6996250152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8418645858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.677170753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8568353652954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7670011520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5648775100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8942670822144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3359498977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5605354309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5156145095825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6952829360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9722700119019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9348392486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9423265457153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8225479125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2043409347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.713397026062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1369657516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1594257354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2866878509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3615493774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2267971038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3465757369995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6834545135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7208824157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5337314605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4588680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1669101715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1968536376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5487012863159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.421441078186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6011066436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6460199356079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7358589172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5861349105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9080362319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4245796203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1251354217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6984233856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2823448181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3272590637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2598876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.267370223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5967617034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7839183807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6641387939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5219020843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4470386505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6416797637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0758743286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7988891601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7464847564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8737487792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9560966491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1058177947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3946342468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5069274902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6847553253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1950378417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1641139984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0094814300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7620697021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.63063621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8471183776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0249443054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9398975372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7698040008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9940166473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1254539489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9553623199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5455875396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7156829833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8548488616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7466068267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0404071807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7311420440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5378532409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5687789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6229000091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.707950592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7234115600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.182201385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0894241333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0816898345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1590042114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9347906112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2363224029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0739593505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9966411590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3909549713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4914646148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8935070037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2414283752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0558700561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2878189086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2955513000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3960609436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8316535949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2800884246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7002143859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5533180236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4837341308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7775344848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5146598815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3832263946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3986854553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2749824523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2285919189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0584945678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9657163619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9502544403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0353031158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2827129364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4141483306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6074390411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5919761657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.932165145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0481376647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2646236419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9476261138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0713310241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0636024475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.079065322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2723541259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3032779693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3728637695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3187427520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5584239959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5893478393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4656429290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7207851409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5738868713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5429611206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6975898742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.107364654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0377807617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6125450134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6821308135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5197639465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3110122680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1099910736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3574028015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1795749664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1409187316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.086799621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8857746124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6151714324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.530122756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.352294921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0430335998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8265504837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9270620346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1976680755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6692905426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8703117370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7852630615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9630908966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8084583282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9244346618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4218788146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0507640838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4605388641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4528045654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.754337310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6383647918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7929992675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4064159393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3342113494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3805961608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4888401031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5506916046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6898593902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4115238189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6434707641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2568893432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2259674072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.504301071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4991970062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9785537719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3445644378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2981758117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9012413024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.653829574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2672481536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3136367797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4269886016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4475555419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3857021331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8805236816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1433982849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0042266845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.911449432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6949672698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6795043945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7413558959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6640357971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7877445220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2516384124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4371967315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3444213867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.406270980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5609016418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3289566040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1743240356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1124706268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1588611602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.282564163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.236177444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2052478790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2671031951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5299758911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.638219833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5918312072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4835910797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5145130157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4526596069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6072940826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1382904052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3547763824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0764408111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.03005027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1737785339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9501991271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3654193878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2057189941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6209373474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5091495513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5889987945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5570583343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4931793212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1578102111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4292984008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.684814453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6369075775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4133281707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4612369537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3175106048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8064708709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8224391937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7106513977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9182624816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9661712646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8863201141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9981117248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3973579406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5251178741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4452686309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1479454040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1639137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0201835632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8604888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7806377410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5730266571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0680961608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7646656036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4772090911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7007865905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2437629699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4513759613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4992828369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2118244171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1319732666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0042152404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1160068511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0361557006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1798877716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3236122131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3395843505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3076457977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7228622436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.467342376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3874950408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5631637573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8825607299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3616600036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4415092468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2658386230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7609081268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0962772369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8247890472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2498722076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4734477996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1540508270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1700191497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7548027038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5312232971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4034633636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8125762939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7327251434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3813877105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2536296844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9342308044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3494472503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9243679046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7486972808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1258697509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7905025482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4391613006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1357345581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2155838012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9760360717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5509510040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8961849212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0718536376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9281253814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8323059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0558853149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1836433410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.455135345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8163356781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3532047271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9859018325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0976867675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1136608123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4269523620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3311319351196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6505308151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4748620986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4429216384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7703065872192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8421678543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7383642196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4490299224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2733592987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1615695953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.321268081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4809665679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.624698638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.768424987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1676731109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3433456420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2794609069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9440937042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0079746246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6406669616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.241418838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5608177185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7045478820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.848274230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3752841949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1037940979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8802146911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9121551513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8642463684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7205142974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6885738372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6087245941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7364845275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3052978515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8980646133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1935119628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2094783782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3851470947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.28932762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2573890686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2254467010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9140357971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.417085647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5288772583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7843971252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5767860412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3691787719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1775398254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4889507293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2494029998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3292541503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4091014862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1695537567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0497798919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5688018798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6486530303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2874488830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0878257751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0478992462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8083515167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9680500030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7285041809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8881988525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1277484893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8793487548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.045238494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9208221435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7964057922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2111301422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1281833648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1696586608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.418493270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3770236968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4599666595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2940769195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9622955322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7549304962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6305141448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3402061462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4895076751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5392761230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7088012695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.667329788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5014381408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5429096221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2526016235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7134609222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4231510162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.373384475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2406711578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.17431640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2738494873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.124547958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3070278167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8591232299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7264099121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7927665710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0747814178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5273408889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4278078079224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6600542068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1789712905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3614549636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6932325363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6102876663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4609851837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4443969726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3780422210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2950963973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.925479888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2904396057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3899726867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4397392272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6719875335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9576377868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0867156982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3355464935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8378772735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5890407562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2572612762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8757123947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9088916778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1577262878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1411361694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4729194641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7595891952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6766443252563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5937004089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4775762557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7429990768433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7098236083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8425350189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3567943572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.323616027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9752464294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5843849182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0037689208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2240829467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0084247589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1909046173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5558643341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5319995880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7974243164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.183629989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9347944259644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6361932754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4371242523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2712335586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3873567581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7616300582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9606981277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4251909255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0317115783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4796171188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1690816879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3681507110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95342445373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3183841705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8777542114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4417810440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8565073013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1763572692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2924785614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2141923904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9155883789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6667537689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2022619247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4510974884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5174531936646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5340414047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4013290405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1524934768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0529594421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97001457214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4676847457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6999311447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.301794052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0695486068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2520275115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0031929016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0363693237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1193161010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92024707794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45575332641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50552082061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32304096221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14056205749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07420539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68800067901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1359043121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70458793640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38939666748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4345064163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2188501358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4179182052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.99853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8990001678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9819459915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8160552978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8824110031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8113975524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7782201766968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.595739364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3634920120239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6833438873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9487676620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9653568267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2639589309692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2805490493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1810140609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3303155899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.297137260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0814800262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0151233673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0648908615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8326444625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8492336273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5838088989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3847408294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.650164604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2354393005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9321784973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.550630569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5008630752563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6169862747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4842739105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0197811126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3349733352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7828769683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6003971099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1312465667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4132614135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4298496246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2307806015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8658227920532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3137273788452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3966703414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5127944946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8611650466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2095355987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9772872924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0602331161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2593011856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3800821304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1146583557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6335744857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2686166763306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55528736114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62164402008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65482234954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.605055809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75435638427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.491548538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0058097839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1929454803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8399171829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3210000991821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4086036682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2758913040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7237939834595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9062738418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1053438186646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9892196655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0721654891968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0223970413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0887537002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0389862060547</t>
+  </si>
+  <si>
     <t xml:space="preserve">12.6740283966064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7863187789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0932493209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9510126113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1306819915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9884443283081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1381664276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.160626411438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.183084487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1681108474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2279996871948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0034170150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1755981445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.400182723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3852100372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8643217086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9167242050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5199594497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4450998306274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3627519607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4600706100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5124731063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4376125335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8268938064575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6247663497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8044347763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7819738388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6996259689331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8418655395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6771678924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.856837272644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7670021057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5648794174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.89426612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3359479904175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5605325698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5156164169312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6952848434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9722681045532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9348411560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.942325592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.822548866272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2043418884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7133979797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1369657516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1594219207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2866897583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3615493774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2267999649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3465785980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6834554672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7208824157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.533730506897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1669120788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1968536376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5487031936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4214401245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6011056900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6460208892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7358541488647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5861320495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9080362319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4245796203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1251354217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6984262466431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2823448181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3272609710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2598876953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2673721313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5967597961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.78391456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6641387939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5218982696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4470386505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6416778564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0758724212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7988872528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7464866638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8737506866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9560966491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1058177947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3946361541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5069274902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6847534179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1950397491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1641120910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0094814300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7620716094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6306324005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8471202850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0249443054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9398975372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7698040008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9940166473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1254558563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.955358505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5455875396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7156810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8548488616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7466087341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0404090881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.731143951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5378551483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5687789916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6229019165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7079486846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7234134674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1822032928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0894222259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0816917419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1590099334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9347925186157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2363224029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0739612579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9966449737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3909549713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4914646148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8935089111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2414245605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0558700561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2878189086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2955513000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3960590362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8316555023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.280086517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7002182006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.553316116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4837322235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7775344848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5146598815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3832225799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3986835479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2749767303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2285919189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0584983825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9657173156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9502544403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0353031158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2827129364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4141464233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6074371337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5919742584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.932165145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0481395721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2646236419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9476280212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0713329315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0636005401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0790634155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2723560333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.303279876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3728656768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3187446594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5584239959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5893497467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4656429290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7207870483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5738868713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5429611206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6975917816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1073684692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0377807617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6125469207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.68212890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5197639465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3110122680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1099910736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3574047088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.179573059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1409168243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0867958068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8857746124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6151695251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.530122756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.352294921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0430335998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.826548576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9270601272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1976642608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6692924499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8703117370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7852630615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9630928039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8084602355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9244327545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4218807220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0507640838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.460542678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.452808380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7543411254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6383647918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7929973602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4064140319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.33420753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3805961608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4888381958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5506954193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6898593902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4115238189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6434707641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2568912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2259654998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5043029785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.499195098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9785556793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3445625305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2981739044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9012393951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6538276672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2672500610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3136386871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4269886016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4475574493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3857040405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8805236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1433963775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0042304992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.911449432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6949672698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6795024871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7413558959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6640377044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7877426147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2516403198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4371929168701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3444194793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.406270980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5609016418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3289566040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1743240356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1124706268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1588611602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2825679779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.236177444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.205249786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2671031951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5299777984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6382179260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5918292999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4835891723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5145130157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4526596069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6072940826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1382904052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3547763824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.07643699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.03005027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1737785339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9502010345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3654193878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2057189941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6209373474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.509147644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5889987945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5570602416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4931793212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.157808303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4292964935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6848182678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6369075775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4133281707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4612407684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3175086975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8064727783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8224391937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7106533050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9182605743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9661693572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8863201141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9981117248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3973598480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5251197814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4452686309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1479454040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1639156341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0201873779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8604850769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7806377410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5730266571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.06809425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7646675109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4772071838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7007904052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.243766784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4513759613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4992847442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2118263244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1319751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0042133331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1160068511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.036153793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1798858642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3236141204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3395824432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3076457977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7228622436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.467342376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3874969482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5631637573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8825588226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3616600036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4415073394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2658386230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7609100341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0962753295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8247871398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2498722076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4734477996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.154052734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1700191497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7548007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5312252044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4034652709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8125782012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7327270507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3813877105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2536296844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9342308044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3494472503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9243679046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7486972808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1258716583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7905025482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4391632080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1357326507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2155838012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9760341644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.550952911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8961849212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0718536376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9281253814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8323040008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0558853149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1836452484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4551315307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8163356781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3532066345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9859027862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0976886749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1136589050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4269514083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3311319351196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6505298614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4748592376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4429216384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7703056335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.842170715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7383651733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4490261077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2733573913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1615695953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3212661743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4809646606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6246948242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.768424987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1676712036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3433437347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2794628143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9440937042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0079746246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6406688690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.241418838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5608158111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7045459747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8482761383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3752822875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.103796005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8802127838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9121551513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8642482757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.720516204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6885757446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6087265014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7364845275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3052978515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8980646133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1935081481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2094783782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3851490020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.28932762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2573890686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2254467010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9140357971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4170875549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5288791656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7843952178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5767879486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.369176864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1775379180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4889507293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2494010925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3292541503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4091014862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1695518493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0497779846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5688037872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6486530303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2874488830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0878257751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0478992462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.808349609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9680500030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7285003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8882007598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1277503967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8793506622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0452404022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9208221435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7964019775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2111320495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1281852722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1696605682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.418493270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3770198822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4599666595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2940769195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9622955322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7549324035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6305141448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3402061462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4895057678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5392742156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7088012695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.667329788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5014381408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.542911529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2526016235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7134590148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4231510162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.373384475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2406711578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.17431640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2738494873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1245498657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3070278167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8591241836548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.726411819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7927675247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.074779510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5273427963257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4278087615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6600542068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.178973197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3614511489868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6932334899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6102895736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4609870910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4444007873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3780431747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2950963973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.925479888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2904376983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3899745941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4397411346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6719856262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9576358795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0867137908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3355484008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8378753662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5890407562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2572612762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8757133483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9088916778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1577281951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1411361694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4729194641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7595891952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.676643371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5936994552612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.477575302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7429990768433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7098217010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8425340652466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3567924499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3236179351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9752464294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5843849182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0037689208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2240829467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0084247589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1909065246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5558605194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5320014953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7974252700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1836309432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9347944259644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6361923217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4371252059937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2712335586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3873567581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7616310119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9606990814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4251918792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0317125320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4796161651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1690816879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3681516647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95342445373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3183822631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8777542114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.441780090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8565082550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1763572692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2924785614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2141933441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9155883789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6667537689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2022609710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4510955810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5174541473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5340414047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4013290405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1524934768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0529594421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97001457214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4676856994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6999311447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.301794052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0695486068726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2520275115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0031929016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0363702774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1193151473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92024707794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45575332641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50552082061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32304096221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14056205749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07420444488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68800067901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1359043121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70458889007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38939666748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4345073699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2188501358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4179182052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9985342025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8990001678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9819450378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8160543441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8824110031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8113975524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7782182693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.595739364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3634929656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6833429336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9487676620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9653568267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2639598846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2805490493774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1810150146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3303155899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2971382141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0814790725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0151233673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0648899078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8326444625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.849232673645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5838088989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3847398757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6501655578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3515615463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2354383468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9321784973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5506315231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.500864982605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6169862747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4842758178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0197811126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3349733352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7828769683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.600396156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1312465667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4132604598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4298496246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2307815551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8658227920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3137273788452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.396671295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5127944946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8611660003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2095336914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9772882461548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0602340698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2593011856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3800821304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1146574020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6335754394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2686166763306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55528831481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62164497375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65482234954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60505485534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75435733795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.491548538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0058088302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1929454803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8399181365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3210000991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4086027145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2758903503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7237949371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9062738418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1053428649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.989218711853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0721645355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0223960876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0887537002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0389862060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6740274429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4583692550659</t>
+    <t xml:space="preserve">12.4583702087402</t>
   </si>
   <si>
     <t xml:space="preserve">12.5081377029419</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7403831481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3754243850708</t>
+    <t xml:space="preserve">12.7403841018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3754253387451</t>
   </si>
   <si>
     <t xml:space="preserve">12.4749593734741</t>
@@ -2432,46 +2432,46 @@
     <t xml:space="preserve">12.6574392318726</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9560403823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9228620529175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.536657333374</t>
+    <t xml:space="preserve">12.9560413360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9228630065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5366582870483</t>
   </si>
   <si>
     <t xml:space="preserve">13.984561920166</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3661098480225</t>
+    <t xml:space="preserve">14.3661108016968</t>
   </si>
   <si>
     <t xml:space="preserve">14.5817680358887</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6978902816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7642459869385</t>
+    <t xml:space="preserve">14.6978912353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7642450332642</t>
   </si>
   <si>
     <t xml:space="preserve">14.6315336227417</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1006851196289</t>
+    <t xml:space="preserve">14.1006832122803</t>
   </si>
   <si>
     <t xml:space="preserve">14.432466506958</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7808361053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7476577758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4988212585449</t>
+    <t xml:space="preserve">14.780837059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7476596832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4988222122192</t>
   </si>
   <si>
     <t xml:space="preserve">14.3495197296143</t>
@@ -2483,22 +2483,22 @@
     <t xml:space="preserve">14.2333974838257</t>
   </si>
   <si>
-    <t xml:space="preserve">13.785493850708</t>
+    <t xml:space="preserve">13.7854948043823</t>
   </si>
   <si>
     <t xml:space="preserve">14.0177402496338</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0509185791016</t>
+    <t xml:space="preserve">14.0509195327759</t>
   </si>
   <si>
     <t xml:space="preserve">14.2831649780273</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0462589263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.930136680603</t>
+    <t xml:space="preserve">15.0462617874146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9301376342773</t>
   </si>
   <si>
     <t xml:space="preserve">15.3946304321289</t>
@@ -2513,10 +2513,10 @@
     <t xml:space="preserve">14.8969583511353</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9799041748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9135475158691</t>
+    <t xml:space="preserve">14.9799060821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9135465621948</t>
   </si>
   <si>
     <t xml:space="preserve">14.9964933395386</t>
@@ -2525,40 +2525,40 @@
     <t xml:space="preserve">15.825945854187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6434659957886</t>
+    <t xml:space="preserve">15.6434669494629</t>
   </si>
   <si>
     <t xml:space="preserve">16.0250148773193</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0913715362549</t>
+    <t xml:space="preserve">16.0913696289062</t>
   </si>
   <si>
     <t xml:space="preserve">16.0581912994385</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5605211257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0130834579468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2619180679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.228741645813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1457958221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4941635131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6268758773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2121505737305</t>
+    <t xml:space="preserve">15.5605192184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0130844116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2619171142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2287397384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1457939147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4941644668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.626877784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2121515274048</t>
   </si>
   <si>
     <t xml:space="preserve">15.502459526062</t>
@@ -2567,13 +2567,13 @@
     <t xml:space="preserve">15.2702140808105</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2536239624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5439329147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5771112442017</t>
+    <t xml:space="preserve">15.253623008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5439310073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5771102905273</t>
   </si>
   <si>
     <t xml:space="preserve">15.8508291244507</t>
@@ -2582,22 +2582,22 @@
     <t xml:space="preserve">15.7181177139282</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7347059249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8840065002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7512941360474</t>
+    <t xml:space="preserve">15.7347068786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8840084075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7512950897217</t>
   </si>
   <si>
     <t xml:space="preserve">15.4361047744751</t>
   </si>
   <si>
-    <t xml:space="preserve">16.398265838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5807476043701</t>
+    <t xml:space="preserve">16.3982696533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5807456970215</t>
   </si>
   <si>
     <t xml:space="preserve">15.8674182891846</t>
@@ -2612,10 +2612,10 @@
     <t xml:space="preserve">16.4646224975586</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6222190856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8212871551514</t>
+    <t xml:space="preserve">16.622220993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8212909698486</t>
   </si>
   <si>
     <t xml:space="preserve">16.7051639556885</t>
@@ -2627,31 +2627,31 @@
     <t xml:space="preserve">16.9374122619629</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1364803314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3023719787598</t>
+    <t xml:space="preserve">17.1364822387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3023700714111</t>
   </si>
   <si>
     <t xml:space="preserve">17.4350833892822</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4516735076904</t>
+    <t xml:space="preserve">17.4516716003418</t>
   </si>
   <si>
     <t xml:space="preserve">17.219425201416</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7217540740967</t>
+    <t xml:space="preserve">16.721752166748</t>
   </si>
   <si>
     <t xml:space="preserve">17.1530704498291</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0535354614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0369491577148</t>
+    <t xml:space="preserve">17.0535335540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0369453430176</t>
   </si>
   <si>
     <t xml:space="preserve">16.8876457214355</t>
@@ -2660,13 +2660,13 @@
     <t xml:space="preserve">16.771520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8544635772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2028350830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1033039093018</t>
+    <t xml:space="preserve">16.8544654846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2028369903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1033020019531</t>
   </si>
   <si>
     <t xml:space="preserve">17.1198902130127</t>
@@ -2678,64 +2678,64 @@
     <t xml:space="preserve">17.3521385192871</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2691898345947</t>
+    <t xml:space="preserve">17.269193649292</t>
   </si>
   <si>
     <t xml:space="preserve">16.8710556030273</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9171867370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2074928283691</t>
+    <t xml:space="preserve">15.9171857833862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2074947357178</t>
   </si>
   <si>
     <t xml:space="preserve">16.2323760986328</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6056308746338</t>
+    <t xml:space="preserve">16.6056327819824</t>
   </si>
   <si>
     <t xml:space="preserve">18.6958503723145</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1981773376465</t>
+    <t xml:space="preserve">18.1981792449951</t>
   </si>
   <si>
     <t xml:space="preserve">18.1649990081787</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6175632476807</t>
+    <t xml:space="preserve">17.617561340332</t>
   </si>
   <si>
     <t xml:space="preserve">18.0820541381836</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6507434844971</t>
+    <t xml:space="preserve">17.6507377624512</t>
   </si>
   <si>
     <t xml:space="preserve">17.8000411987305</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4019031524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3189601898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0203590393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7881088256836</t>
+    <t xml:space="preserve">17.4019069671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3189582824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.020357131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7881107330322</t>
   </si>
   <si>
     <t xml:space="preserve">16.970588684082</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1862468719482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4065628051758</t>
+    <t xml:space="preserve">17.1862449645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4065608978271</t>
   </si>
   <si>
     <t xml:space="preserve">16.4148578643799</t>
@@ -2747,13 +2747,13 @@
     <t xml:space="preserve">16.1660194396973</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5346145629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.070125579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2360134124756</t>
+    <t xml:space="preserve">17.5346164703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0701236724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2360153198242</t>
   </si>
   <si>
     <t xml:space="preserve">17.6839179992676</t>
@@ -2771,28 +2771,28 @@
     <t xml:space="preserve">17.3437023162842</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5461559295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4111862182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3774452209473</t>
+    <t xml:space="preserve">17.5461578369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4111881256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3774433135986</t>
   </si>
   <si>
     <t xml:space="preserve">17.6642589569092</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4449310302734</t>
+    <t xml:space="preserve">17.4449291229248</t>
   </si>
   <si>
     <t xml:space="preserve">17.4618034362793</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1749897003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0400199890137</t>
+    <t xml:space="preserve">17.1749877929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.040018081665</t>
   </si>
   <si>
     <t xml:space="preserve">17.0062770843506</t>
@@ -2801,7 +2801,7 @@
     <t xml:space="preserve">16.9556617736816</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8628711700439</t>
+    <t xml:space="preserve">16.8628692626953</t>
   </si>
   <si>
     <t xml:space="preserve">17.090633392334</t>
@@ -2810,16 +2810,16 @@
     <t xml:space="preserve">16.8713054656982</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7532081604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2087306976318</t>
+    <t xml:space="preserve">16.7532062530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2087326049805</t>
   </si>
   <si>
     <t xml:space="preserve">16.2048892974854</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0952262878418</t>
+    <t xml:space="preserve">16.0952243804932</t>
   </si>
   <si>
     <t xml:space="preserve">16.1458396911621</t>
@@ -2828,13 +2828,13 @@
     <t xml:space="preserve">15.7915420532227</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6903142929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8590278625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4119396209717</t>
+    <t xml:space="preserve">15.690315246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8590259552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4119367599487</t>
   </si>
   <si>
     <t xml:space="preserve">15.5216007232666</t>
@@ -2846,25 +2846,25 @@
     <t xml:space="preserve">15.420373916626</t>
   </si>
   <si>
-    <t xml:space="preserve">15.60595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5806493759155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.833722114563</t>
+    <t xml:space="preserve">15.6059598922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5806503295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8337211608887</t>
   </si>
   <si>
     <t xml:space="preserve">16.0446109771729</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8759002685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8927688598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0108680725098</t>
+    <t xml:space="preserve">15.8758993148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8927717208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0108699798584</t>
   </si>
   <si>
     <t xml:space="preserve">15.934947013855</t>
@@ -2873,22 +2873,22 @@
     <t xml:space="preserve">15.7662353515625</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7746725082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.513165473938</t>
+    <t xml:space="preserve">15.7746715545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5131645202637</t>
   </si>
   <si>
     <t xml:space="preserve">15.4878597259521</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1841745376587</t>
+    <t xml:space="preserve">15.1841735839844</t>
   </si>
   <si>
     <t xml:space="preserve">15.2347888946533</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3950672149658</t>
+    <t xml:space="preserve">15.3950662612915</t>
   </si>
   <si>
     <t xml:space="preserve">15.9433832168579</t>
@@ -2897,13 +2897,13 @@
     <t xml:space="preserve">16.112096786499</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2976818084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4495239257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5890846252441</t>
+    <t xml:space="preserve">16.297679901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4495220184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5890865325928</t>
   </si>
   <si>
     <t xml:space="preserve">15.698751449585</t>
@@ -2912,34 +2912,34 @@
     <t xml:space="preserve">16.0361766815186</t>
   </si>
   <si>
-    <t xml:space="preserve">15.968692779541</t>
+    <t xml:space="preserve">15.9686908721924</t>
   </si>
   <si>
     <t xml:space="preserve">16.3145523071289</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9180765151978</t>
+    <t xml:space="preserve">15.9180774688721</t>
   </si>
   <si>
     <t xml:space="preserve">16.0193042755127</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5384731292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0154609680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1504316329956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5300378799438</t>
+    <t xml:space="preserve">15.5384721755981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0154619216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1504306793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5300359725952</t>
   </si>
   <si>
     <t xml:space="preserve">15.8168497085571</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5637807846069</t>
+    <t xml:space="preserve">15.5637798309326</t>
   </si>
   <si>
     <t xml:space="preserve">15.8843336105347</t>
@@ -2948,34 +2948,34 @@
     <t xml:space="preserve">16.1374034881592</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8674631118774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4541139602661</t>
+    <t xml:space="preserve">15.8674612045288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4541149139404</t>
   </si>
   <si>
     <t xml:space="preserve">14.9732847213745</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0238971710205</t>
+    <t xml:space="preserve">15.0238962173462</t>
   </si>
   <si>
     <t xml:space="preserve">15.1673030853271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4372453689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6312646865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4794235229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1588659286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7623920440674</t>
+    <t xml:space="preserve">15.4372425079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6312656402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4794225692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1588668823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7623929977417</t>
   </si>
   <si>
     <t xml:space="preserve">14.4080944061279</t>
@@ -2996,28 +2996,28 @@
     <t xml:space="preserve">13.5898370742798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1427459716797</t>
+    <t xml:space="preserve">13.142746925354</t>
   </si>
   <si>
     <t xml:space="preserve">12.7294006347656</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6028652191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9065494537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3367681503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1258754730225</t>
+    <t xml:space="preserve">12.6028642654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.906548500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3367671966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1258764266968</t>
   </si>
   <si>
     <t xml:space="preserve">13.5139169692993</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9188270568848</t>
+    <t xml:space="preserve">13.9188289642334</t>
   </si>
   <si>
     <t xml:space="preserve">13.3198957443237</t>
@@ -3026,19 +3026,19 @@
     <t xml:space="preserve">13.5307874679565</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8728065490723</t>
+    <t xml:space="preserve">12.8728055953979</t>
   </si>
   <si>
     <t xml:space="preserve">12.9318561553955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7631425857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6366081237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4172801971436</t>
+    <t xml:space="preserve">12.7631435394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.636607170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4172811508179</t>
   </si>
   <si>
     <t xml:space="preserve">12.4847660064697</t>
@@ -3047,7 +3047,7 @@
     <t xml:space="preserve">12.6872224807739</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6619148254395</t>
+    <t xml:space="preserve">12.6619157791138</t>
   </si>
   <si>
     <t xml:space="preserve">12.7209644317627</t>
@@ -3068,13 +3068,13 @@
     <t xml:space="preserve">12.3666667938232</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5859937667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4126873016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3958158493042</t>
+    <t xml:space="preserve">12.585994720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4126882553101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3958168029785</t>
   </si>
   <si>
     <t xml:space="preserve">13.4464302062988</t>
@@ -3089,25 +3089,25 @@
     <t xml:space="preserve">13.2271041870117</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9571619033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0752630233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7040939331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7715787887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4004096984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.214825630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0461111068726</t>
+    <t xml:space="preserve">12.9571628570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0752611160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7040929794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.771577835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.400408744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2148246765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0461120605469</t>
   </si>
   <si>
     <t xml:space="preserve">11.8773994445801</t>
@@ -3128,16 +3128,16 @@
     <t xml:space="preserve">12.3835391998291</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2991819381714</t>
+    <t xml:space="preserve">12.2991809844971</t>
   </si>
   <si>
     <t xml:space="preserve">11.8267850875854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749429702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6487464904785</t>
+    <t xml:space="preserve">11.6749439239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6487474441528</t>
   </si>
   <si>
     <t xml:space="preserve">11.474102973938</t>
@@ -3149,10 +3149,10 @@
     <t xml:space="preserve">11.8932485580444</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9107131958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4346437454224</t>
+    <t xml:space="preserve">11.9107122421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.434642791748</t>
   </si>
   <si>
     <t xml:space="preserve">12.102819442749</t>
@@ -3164,7 +3164,7 @@
     <t xml:space="preserve">11.9805698394775</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1901426315308</t>
+    <t xml:space="preserve">12.1901416778564</t>
   </si>
   <si>
     <t xml:space="preserve">12.3298578262329</t>
@@ -3182,13 +3182,13 @@
     <t xml:space="preserve">11.4391746520996</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1946716308594</t>
+    <t xml:space="preserve">11.1946725845337</t>
   </si>
   <si>
     <t xml:space="preserve">11.7186040878296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5788888931274</t>
+    <t xml:space="preserve">11.5788898468018</t>
   </si>
   <si>
     <t xml:space="preserve">11.8408555984497</t>
@@ -3197,7 +3197,7 @@
     <t xml:space="preserve">11.8583192825317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7709980010986</t>
+    <t xml:space="preserve">11.7709970474243</t>
   </si>
   <si>
     <t xml:space="preserve">11.9631052017212</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">11.7535333633423</t>
   </si>
   <si>
-    <t xml:space="preserve">11.49156665802</t>
+    <t xml:space="preserve">11.4915676116943</t>
   </si>
   <si>
     <t xml:space="preserve">11.2645292282104</t>
@@ -3215,16 +3215,16 @@
     <t xml:space="preserve">10.8104562759399</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0549583435059</t>
+    <t xml:space="preserve">11.0549573898315</t>
   </si>
   <si>
     <t xml:space="preserve">11.1772079467773</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3867797851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2470655441284</t>
+    <t xml:space="preserve">11.3867807388306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2470664978027</t>
   </si>
   <si>
     <t xml:space="preserve">11.0374937057495</t>
@@ -3233,13 +3233,13 @@
     <t xml:space="preserve">10.8453845977783</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3343868255615</t>
+    <t xml:space="preserve">11.3343877792358</t>
   </si>
   <si>
     <t xml:space="preserve">11.3169231414795</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4042453765869</t>
+    <t xml:space="preserve">11.4042463302612</t>
   </si>
   <si>
     <t xml:space="preserve">11.2296009063721</t>
@@ -3248,13 +3248,13 @@
     <t xml:space="preserve">11.6138181686401</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7884616851807</t>
+    <t xml:space="preserve">11.788462638855</t>
   </si>
   <si>
     <t xml:space="preserve">11.8233909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8059272766113</t>
+    <t xml:space="preserve">11.805926322937</t>
   </si>
   <si>
     <t xml:space="preserve">11.5614242553711</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">11.4566383361816</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5439605712891</t>
+    <t xml:space="preserve">11.5439615249634</t>
   </si>
   <si>
     <t xml:space="preserve">11.4217090606689</t>
@@ -3278,7 +3278,7 @@
     <t xml:space="preserve">10.7231340408325</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6882057189941</t>
+    <t xml:space="preserve">10.6882047653198</t>
   </si>
   <si>
     <t xml:space="preserve">10.6707410812378</t>
@@ -3287,7 +3287,7 @@
     <t xml:space="preserve">10.5135612487793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.286524772644</t>
+    <t xml:space="preserve">10.2865238189697</t>
   </si>
   <si>
     <t xml:space="preserve">10.2341318130493</t>
@@ -3302,10 +3302,10 @@
     <t xml:space="preserve">9.78005695343018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90230846405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81498527526855</t>
+    <t xml:space="preserve">9.90230751037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81498622894287</t>
   </si>
   <si>
     <t xml:space="preserve">9.76259326934814</t>
@@ -3314,28 +3314,28 @@
     <t xml:space="preserve">9.9896297454834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1992034912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29105567932129</t>
+    <t xml:space="preserve">10.1992025375366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29105472564697</t>
   </si>
   <si>
     <t xml:space="preserve">9.51809120178223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22119808197021</t>
+    <t xml:space="preserve">9.2211971282959</t>
   </si>
   <si>
     <t xml:space="preserve">9.25612640380859</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0640172958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80205154418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8195161819458</t>
+    <t xml:space="preserve">9.06401634216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80205059051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81951522827148</t>
   </si>
   <si>
     <t xml:space="preserve">8.60121154785156</t>
@@ -3350,34 +3350,34 @@
     <t xml:space="preserve">8.44403171539307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46149444580078</t>
+    <t xml:space="preserve">8.46149635314941</t>
   </si>
   <si>
     <t xml:space="preserve">8.3392448425293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56628227233887</t>
+    <t xml:space="preserve">8.56628322601318</t>
   </si>
   <si>
     <t xml:space="preserve">8.34797763824463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54881763458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59247970581055</t>
+    <t xml:space="preserve">8.54881858825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59247875213623</t>
   </si>
   <si>
     <t xml:space="preserve">8.85444450378418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88937377929688</t>
+    <t xml:space="preserve">8.88937282562256</t>
   </si>
   <si>
     <t xml:space="preserve">9.04655265808105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01162338256836</t>
+    <t xml:space="preserve">9.01162433624268</t>
   </si>
   <si>
     <t xml:space="preserve">8.83697986602783</t>
@@ -3386,31 +3386,31 @@
     <t xml:space="preserve">8.73219394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02908897399902</t>
+    <t xml:space="preserve">9.02908802032471</t>
   </si>
   <si>
     <t xml:space="preserve">9.09894561767578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41330528259277</t>
+    <t xml:space="preserve">9.41330432891846</t>
   </si>
   <si>
     <t xml:space="preserve">9.308518409729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27359008789062</t>
+    <t xml:space="preserve">9.27358913421631</t>
   </si>
   <si>
     <t xml:space="preserve">9.39584064483643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72766399383545</t>
+    <t xml:space="preserve">9.72766494750977</t>
   </si>
   <si>
     <t xml:space="preserve">9.55301952362061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62287712097168</t>
+    <t xml:space="preserve">9.622878074646</t>
   </si>
   <si>
     <t xml:space="preserve">9.91977214813232</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">9.65780639648438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64034175872803</t>
+    <t xml:space="preserve">9.64034271240234</t>
   </si>
   <si>
     <t xml:space="preserve">9.67527103424072</t>
@@ -3431,19 +3431,19 @@
     <t xml:space="preserve">9.83245086669922</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0420236587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69273471832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93723678588867</t>
+    <t xml:space="preserve">10.0420227050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69273567199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93723773956299</t>
   </si>
   <si>
     <t xml:space="preserve">9.97216606140137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88484287261963</t>
+    <t xml:space="preserve">9.88484382629395</t>
   </si>
   <si>
     <t xml:space="preserve">9.8673791885376</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">10.0944166183472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0769510269165</t>
+    <t xml:space="preserve">10.0769519805908</t>
   </si>
   <si>
     <t xml:space="preserve">9.79752159118652</t>
@@ -3476,25 +3476,25 @@
     <t xml:space="preserve">10.7405986785889</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7580633163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9152431488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0200290679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3518514633179</t>
+    <t xml:space="preserve">10.7580623626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9152421951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0200281143188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3518524169922</t>
   </si>
   <si>
     <t xml:space="preserve">11.0025644302368</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9676361083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.53102684021</t>
+    <t xml:space="preserve">10.9676351547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5310258865356</t>
   </si>
   <si>
     <t xml:space="preserve">10.6183471679688</t>
@@ -3506,28 +3506,28 @@
     <t xml:space="preserve">10.6008834838867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.565954208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4786319732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1817378997803</t>
+    <t xml:space="preserve">10.5659551620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4786329269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1817388534546</t>
   </si>
   <si>
     <t xml:space="preserve">10.216667175293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0245580673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84991359710693</t>
+    <t xml:space="preserve">10.0245590209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84991455078125</t>
   </si>
   <si>
     <t xml:space="preserve">10.1118803024292</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5834188461304</t>
+    <t xml:space="preserve">10.5834178924561</t>
   </si>
   <si>
     <t xml:space="preserve">10.3563814163208</t>
@@ -3554,22 +3554,22 @@
     <t xml:space="preserve">11.8757839202881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.067892074585</t>
+    <t xml:space="preserve">12.0678911209106</t>
   </si>
   <si>
     <t xml:space="preserve">12.0329627990723</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4650440216064</t>
+    <t xml:space="preserve">13.4650430679321</t>
   </si>
   <si>
     <t xml:space="preserve">13.1681480407715</t>
   </si>
   <si>
-    <t xml:space="preserve">13.063362121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8712530136108</t>
+    <t xml:space="preserve">13.0633630752563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8712539672852</t>
   </si>
   <si>
     <t xml:space="preserve">12.6442165374756</t>
@@ -4635,6 +4635,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.59000015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47000026702881</t>
   </si>
 </sst>
 </file>
@@ -70285,7 +70288,7 @@
     </row>
     <row r="2513">
       <c r="A2513" s="1" t="n">
-        <v>45978.69125</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B2513" t="n">
         <v>506426</v>
@@ -70306,6 +70309,32 @@
         <v>1540</v>
       </c>
       <c r="H2513" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" s="1" t="n">
+        <v>45979.6941782407</v>
+      </c>
+      <c r="B2514" t="n">
+        <v>250620</v>
+      </c>
+      <c r="C2514" t="n">
+        <v>8.57999992370605</v>
+      </c>
+      <c r="D2514" t="n">
+        <v>8.39999961853027</v>
+      </c>
+      <c r="E2514" t="n">
+        <v>8.47999954223633</v>
+      </c>
+      <c r="F2514" t="n">
+        <v>8.47000026702881</v>
+      </c>
+      <c r="G2514" t="s">
+        <v>1541</v>
+      </c>
+      <c r="H2514" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARR.MI.xlsx
+++ b/data/MARR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="1542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="1543">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4479513168335</t>
+    <t xml:space="preserve">13.4479503631592</t>
   </si>
   <si>
     <t xml:space="preserve">MARR.MI</t>
@@ -50,82 +50,82 @@
     <t xml:space="preserve">13.1812992095947</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9939212799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9506778717041</t>
+    <t xml:space="preserve">12.9939203262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9506788253784</t>
   </si>
   <si>
     <t xml:space="preserve">12.5903367996216</t>
   </si>
   <si>
-    <t xml:space="preserve">12.655198097229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7344732284546</t>
+    <t xml:space="preserve">12.6552000045776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7344741821289</t>
   </si>
   <si>
     <t xml:space="preserve">12.4389953613281</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4462013244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9849624633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0858583450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6462430953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2155838012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8353681564331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6768188476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5615110397339</t>
+    <t xml:space="preserve">12.4462003707886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9849634170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0858602523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6462421417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2155818939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8353691101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6768198013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5615119934082</t>
   </si>
   <si>
     <t xml:space="preserve">12.5543022155762</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6407871246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7200613021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9722995758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7777137756348</t>
+    <t xml:space="preserve">12.6407861709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7200603485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.97230052948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7777156829834</t>
   </si>
   <si>
     <t xml:space="preserve">12.3308925628662</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5110654830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2948570251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4084167480469</t>
+    <t xml:space="preserve">12.5110635757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2948579788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4084186553955</t>
   </si>
   <si>
     <t xml:space="preserve">11.4516582489014</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8840684890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5885887145996</t>
+    <t xml:space="preserve">11.8840675354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5885877609253</t>
   </si>
   <si>
     <t xml:space="preserve">11.8912754058838</t>
@@ -134,13 +134,13 @@
     <t xml:space="preserve">11.9273099899292</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0426168441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2011671066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3957529067993</t>
+    <t xml:space="preserve">12.0426187515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2011680603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3957538604736</t>
   </si>
   <si>
     <t xml:space="preserve">12.7056465148926</t>
@@ -149,94 +149,94 @@
     <t xml:space="preserve">12.6047496795654</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5759229660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9362668991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1596765518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.943470954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0731945037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8858165740967</t>
+    <t xml:space="preserve">12.5759248733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9362659454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1596784591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9434700012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0731954574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.885817527771</t>
   </si>
   <si>
     <t xml:space="preserve">12.597544670105</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0786533355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3597183227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6696138381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8137512207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6984405517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8714056015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4534072875977</t>
+    <t xml:space="preserve">12.078652381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3597173690796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6696128845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8137493133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6984415054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8714036941528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4534101486206</t>
   </si>
   <si>
     <t xml:space="preserve">12.3453044891357</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6840257644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7560949325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1524705886841</t>
+    <t xml:space="preserve">12.6840286254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7560968399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1524686813354</t>
   </si>
   <si>
     <t xml:space="preserve">13.2677803039551</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3326416015625</t>
+    <t xml:space="preserve">13.3326396942139</t>
   </si>
   <si>
     <t xml:space="preserve">13.0804023742676</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1885042190552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2605724334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7073965072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.491189956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.347056388855</t>
+    <t xml:space="preserve">13.1885032653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2605743408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7073974609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4911918640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3470544815063</t>
   </si>
   <si>
     <t xml:space="preserve">13.0011281967163</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9002304077148</t>
+    <t xml:space="preserve">12.9002313613892</t>
   </si>
   <si>
     <t xml:space="preserve">12.8281621932983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7921285629272</t>
+    <t xml:space="preserve">12.7921304702759</t>
   </si>
   <si>
     <t xml:space="preserve">13.0587816238403</t>
@@ -245,91 +245,91 @@
     <t xml:space="preserve">13.1020231246948</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8065433502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2821941375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1380558013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8425769805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8930253982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9074382781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0227479934692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6624069213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8786106109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6335802078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7488889694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0258750915527</t>
+    <t xml:space="preserve">12.8065452575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2821950912476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1380577087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8425760269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8930244445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9074363708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0227460861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6624050140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8786115646362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6335783004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7488880157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0258722305298</t>
   </si>
   <si>
     <t xml:space="preserve">13.0183887481689</t>
   </si>
   <si>
-    <t xml:space="preserve">13.25794506073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2504596710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4301261901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4825286865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3103504180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2654323577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4750442504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3702392578125</t>
+    <t xml:space="preserve">13.2579441070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2504606246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4301280975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4825315475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3103494644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2654314041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.475043296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3702363967896</t>
   </si>
   <si>
     <t xml:space="preserve">13.2878904342651</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2729158401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2804040908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.801290512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8836364746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6141376495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3146924972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.44944190979</t>
+    <t xml:space="preserve">13.2729187011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.280403137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8012914657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8836393356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6141395568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3146915435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4494428634644</t>
   </si>
   <si>
     <t xml:space="preserve">12.8087778091431</t>
@@ -344,43 +344,43 @@
     <t xml:space="preserve">12.4419565200806</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7831764221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2847480773926</t>
+    <t xml:space="preserve">11.7831773757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2847490310669</t>
   </si>
   <si>
     <t xml:space="preserve">12.7339153289795</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4226427078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5274467468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0558214187622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4525833129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3328046798706</t>
+    <t xml:space="preserve">13.4226408004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5274448394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0558185577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4525842666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3328056335449</t>
   </si>
   <si>
     <t xml:space="preserve">13.7595157623291</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7295722961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7220859527588</t>
+    <t xml:space="preserve">13.7295713424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7220869064331</t>
   </si>
   <si>
     <t xml:space="preserve">13.5349321365356</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4900150299072</t>
+    <t xml:space="preserve">13.4900159835815</t>
   </si>
   <si>
     <t xml:space="preserve">13.7370586395264</t>
@@ -389,13 +389,13 @@
     <t xml:space="preserve">14.0140438079834</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7071142196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8493490219116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.111364364624</t>
+    <t xml:space="preserve">13.7071132659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8493499755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1113653182983</t>
   </si>
   <si>
     <t xml:space="preserve">13.9766139984131</t>
@@ -404,64 +404,64 @@
     <t xml:space="preserve">14.0814199447632</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7445440292358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9990720748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5049886703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6397361755371</t>
+    <t xml:space="preserve">13.7445468902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9990730285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5049896240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6397371292114</t>
   </si>
   <si>
     <t xml:space="preserve">13.6621971130371</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6097917556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3477773666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4151554107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.220513343811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0857639312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1007375717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.063304901123</t>
+    <t xml:space="preserve">13.6097946166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3477783203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4151544570923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2205142974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0857629776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.100736618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0633068084717</t>
   </si>
   <si>
     <t xml:space="preserve">13.2354888916016</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1456508636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9285564422607</t>
+    <t xml:space="preserve">13.1456527709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9285554885864</t>
   </si>
   <si>
     <t xml:space="preserve">13.2055416107178</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1082248687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.198055267334</t>
+    <t xml:space="preserve">13.1082229614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1980562210083</t>
   </si>
   <si>
     <t xml:space="preserve">13.1157073974609</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0109014511108</t>
+    <t xml:space="preserve">13.0109033584595</t>
   </si>
   <si>
     <t xml:space="preserve">12.9135837554932</t>
@@ -479,49 +479,46 @@
     <t xml:space="preserve">13.4076671600342</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3552646636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2130298614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3402948379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9659862518311</t>
+    <t xml:space="preserve">13.3552656173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2130279541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.340292930603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9659852981567</t>
   </si>
   <si>
     <t xml:space="preserve">12.8761529922485</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8312339782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9809608459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7638607025146</t>
+    <t xml:space="preserve">12.8312358856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9809589385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7638597488403</t>
   </si>
   <si>
     <t xml:space="preserve">12.7114562988281</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8686666488647</t>
+    <t xml:space="preserve">12.8686656951904</t>
   </si>
   <si>
     <t xml:space="preserve">12.7563762664795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7488880157471</t>
-  </si>
-  <si>
     <t xml:space="preserve">12.6815137863159</t>
   </si>
   <si>
     <t xml:space="preserve">12.5767068862915</t>
   </si>
   <si>
-    <t xml:space="preserve">12.546763420105</t>
+    <t xml:space="preserve">12.5467624664307</t>
   </si>
   <si>
     <t xml:space="preserve">12.5317897796631</t>
@@ -533,43 +530,43 @@
     <t xml:space="preserve">12.5542497634888</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4194984436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2772607803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4718999862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5018463134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3970403671265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9778156280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3596105575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4943599700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3820676803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4045257568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2697744369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1649694442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2548055648804</t>
+    <t xml:space="preserve">12.4194974899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2772617340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4719018936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5018482208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3970384597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9778165817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3596096038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4943590164185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3820686340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4045238494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.269775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1649703979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2548036575317</t>
   </si>
   <si>
     <t xml:space="preserve">12.3371505737305</t>
@@ -581,187 +578,187 @@
     <t xml:space="preserve">12.7264289855957</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6740255355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.786319732666</t>
+    <t xml:space="preserve">12.6740264892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7863187789917</t>
   </si>
   <si>
     <t xml:space="preserve">13.0932502746582</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9510126113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1306829452515</t>
+    <t xml:space="preserve">12.9510135650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1306819915771</t>
   </si>
   <si>
     <t xml:space="preserve">12.9884433746338</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1381692886353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.160626411438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1830854415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1681108474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2279996871948</t>
+    <t xml:space="preserve">13.1381664276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1606273651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1830835342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1681118011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2280015945435</t>
   </si>
   <si>
     <t xml:space="preserve">13.00341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1755962371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4001817703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3852071762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8643245697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.91672706604</t>
+    <t xml:space="preserve">13.1755990982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4001808166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3852081298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8643207550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9167242050171</t>
   </si>
   <si>
     <t xml:space="preserve">13.5199604034424</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4450988769531</t>
+    <t xml:space="preserve">13.4450969696045</t>
   </si>
   <si>
     <t xml:space="preserve">13.3627519607544</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4600696563721</t>
+    <t xml:space="preserve">13.4600706100464</t>
   </si>
   <si>
     <t xml:space="preserve">13.5124731063843</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4376134872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8268899917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6247682571411</t>
+    <t xml:space="preserve">13.4376125335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8268909454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6247663497925</t>
   </si>
   <si>
     <t xml:space="preserve">13.8044347763062</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7819757461548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6996250152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8418645858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.677170753479</t>
+    <t xml:space="preserve">13.7819747924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6996269226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8418636322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6771688461304</t>
   </si>
   <si>
     <t xml:space="preserve">13.8568353652954</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7670011520386</t>
+    <t xml:space="preserve">13.7670021057129</t>
   </si>
   <si>
     <t xml:space="preserve">13.5648775100708</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8942670822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3359498977661</t>
+    <t xml:space="preserve">13.8942651748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3359479904175</t>
   </si>
   <si>
     <t xml:space="preserve">14.5605354309082</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5156145095825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6952829360962</t>
+    <t xml:space="preserve">14.5156154632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6952819824219</t>
   </si>
   <si>
     <t xml:space="preserve">14.9722700119019</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9348392486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9423265457153</t>
+    <t xml:space="preserve">14.9348411560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.942325592041</t>
   </si>
   <si>
     <t xml:space="preserve">14.8225479125977</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2043409347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.713397026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1369657516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1594257354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2866878509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3615493774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2267971038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3465757369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6834545135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7208824157715</t>
+    <t xml:space="preserve">15.2043418884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.713399887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1369667053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1594247817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2866868972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3615503311157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2267980575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3465766906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6834535598755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7208833694458</t>
   </si>
   <si>
     <t xml:space="preserve">15.5337314605713</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4588680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1669101715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1968536376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5487012863159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.421441078186</t>
+    <t xml:space="preserve">15.458869934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1669082641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1968545913696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5487031936646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4214382171631</t>
   </si>
   <si>
     <t xml:space="preserve">15.6011066436768</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6460199356079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7358589172363</t>
+    <t xml:space="preserve">15.6460218429565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.735857963562</t>
   </si>
   <si>
     <t xml:space="preserve">15.5861349105835</t>
@@ -773,19 +770,19 @@
     <t xml:space="preserve">16.4245796203613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1251354217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6984233856201</t>
+    <t xml:space="preserve">16.1251373291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6984262466431</t>
   </si>
   <si>
     <t xml:space="preserve">16.2823448181152</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3272590637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2598876953125</t>
+    <t xml:space="preserve">16.3272609710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2598838806152</t>
   </si>
   <si>
     <t xml:space="preserve">16.267370223999</t>
@@ -794,10 +791,10 @@
     <t xml:space="preserve">16.5967617034912</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7839183807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6641387939453</t>
+    <t xml:space="preserve">16.78391456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6641368865967</t>
   </si>
   <si>
     <t xml:space="preserve">16.5219020843506</t>
@@ -806,28 +803,28 @@
     <t xml:space="preserve">16.4470386505127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6416797637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0758743286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7988891601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7464847564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8737487792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9560966491699</t>
+    <t xml:space="preserve">16.6416759490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0758762359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.798885345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7464866638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8737506866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9560947418213</t>
   </si>
   <si>
     <t xml:space="preserve">17.1058177947998</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3946342468262</t>
+    <t xml:space="preserve">16.3946361541748</t>
   </si>
   <si>
     <t xml:space="preserve">16.5069274902344</t>
@@ -839,7 +836,7 @@
     <t xml:space="preserve">17.1950378417969</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1641139984131</t>
+    <t xml:space="preserve">17.1641120910645</t>
   </si>
   <si>
     <t xml:space="preserve">17.0094814300537</t>
@@ -848,13 +845,13 @@
     <t xml:space="preserve">16.7620697021484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.63063621521</t>
+    <t xml:space="preserve">16.6306324005127</t>
   </si>
   <si>
     <t xml:space="preserve">16.8471183776855</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0249443054199</t>
+    <t xml:space="preserve">17.0249423980713</t>
   </si>
   <si>
     <t xml:space="preserve">16.9398975372314</t>
@@ -863,13 +860,13 @@
     <t xml:space="preserve">16.7698040008545</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9940166473389</t>
+    <t xml:space="preserve">16.9940185546875</t>
   </si>
   <si>
     <t xml:space="preserve">17.1254539489746</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9553623199463</t>
+    <t xml:space="preserve">16.9553604125977</t>
   </si>
   <si>
     <t xml:space="preserve">16.5455875396729</t>
@@ -884,28 +881,28 @@
     <t xml:space="preserve">16.7466068267822</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0404071807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7311420440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5378532409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5687789916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6229000091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.707950592041</t>
+    <t xml:space="preserve">17.0404109954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.731143951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5378551483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5687808990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6229038238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7079486846924</t>
   </si>
   <si>
     <t xml:space="preserve">16.7234115600586</t>
   </si>
   <si>
-    <t xml:space="preserve">16.182201385498</t>
+    <t xml:space="preserve">16.1821994781494</t>
   </si>
   <si>
     <t xml:space="preserve">16.0894241333008</t>
@@ -914,58 +911,58 @@
     <t xml:space="preserve">16.0816898345947</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1590042114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9347906112671</t>
+    <t xml:space="preserve">16.1590061187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9347915649414</t>
   </si>
   <si>
     <t xml:space="preserve">16.2363224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0739593505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9966411590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3909549713135</t>
+    <t xml:space="preserve">16.0739612579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9966440200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3909568786621</t>
   </si>
   <si>
     <t xml:space="preserve">16.4914646148682</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8935070037842</t>
+    <t xml:space="preserve">16.8935089111328</t>
   </si>
   <si>
     <t xml:space="preserve">17.2414283752441</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0558700561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2878189086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2955513000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3960609436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8316535949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2800884246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7002143859863</t>
+    <t xml:space="preserve">17.055871963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2878170013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2955493927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3960590362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8316555023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.280086517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7002182006836</t>
   </si>
   <si>
     <t xml:space="preserve">16.5533180236816</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4837341308594</t>
+    <t xml:space="preserve">16.4837303161621</t>
   </si>
   <si>
     <t xml:space="preserve">16.7775344848633</t>
@@ -974,73 +971,73 @@
     <t xml:space="preserve">16.5146598815918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3832263946533</t>
+    <t xml:space="preserve">16.3832225799561</t>
   </si>
   <si>
     <t xml:space="preserve">16.3986854553223</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2749824523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2285919189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0584945678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9657163619995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9502544403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0353031158447</t>
+    <t xml:space="preserve">16.2749805450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2285938262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0584983825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9657182693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.950252532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0353012084961</t>
   </si>
   <si>
     <t xml:space="preserve">16.2827129364014</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4141483306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6074390411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5919761657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.932165145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0481376647949</t>
+    <t xml:space="preserve">16.4141502380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6074371337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5919742584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9321670532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0481395721436</t>
   </si>
   <si>
     <t xml:space="preserve">17.2646236419678</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9476261138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0713310241699</t>
+    <t xml:space="preserve">16.9476280212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0713329315186</t>
   </si>
   <si>
     <t xml:space="preserve">17.0636024475098</t>
   </si>
   <si>
-    <t xml:space="preserve">17.079065322876</t>
+    <t xml:space="preserve">17.0790672302246</t>
   </si>
   <si>
     <t xml:space="preserve">17.2723541259766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3032779693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3728637695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3187427520752</t>
+    <t xml:space="preserve">17.3032817840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3728675842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3187408447266</t>
   </si>
   <si>
     <t xml:space="preserve">17.5584239959717</t>
@@ -1049,22 +1046,22 @@
     <t xml:space="preserve">17.5893478393555</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4656429290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7207851409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5738868713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5429611206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6975898742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.107364654541</t>
+    <t xml:space="preserve">17.4656448364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7207889556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5738887786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5429592132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6975936889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1073665618896</t>
   </si>
   <si>
     <t xml:space="preserve">18.0377807617188</t>
@@ -1073,7 +1070,7 @@
     <t xml:space="preserve">17.6125450134277</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6821308135986</t>
+    <t xml:space="preserve">17.68212890625</t>
   </si>
   <si>
     <t xml:space="preserve">17.5197639465332</t>
@@ -1085,70 +1082,70 @@
     <t xml:space="preserve">17.1099910736084</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3574028015137</t>
+    <t xml:space="preserve">17.357400894165</t>
   </si>
   <si>
     <t xml:space="preserve">17.1795749664307</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1409187316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.086799621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8857746124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6151714324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.530122756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.352294921875</t>
+    <t xml:space="preserve">17.1409168243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0867958068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8857765197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6151695251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5301208496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3522968292236</t>
   </si>
   <si>
     <t xml:space="preserve">16.0430335998535</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8265504837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9270620346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1976680755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6692905426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8703117370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7852630615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9630908966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8084583282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9244346618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4218788146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0507640838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4605388641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4528045654297</t>
+    <t xml:space="preserve">15.826548576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9270601272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1976661682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6692886352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8703136444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7852649688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9630928039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8084621429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9244327545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4218807220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0507659912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4605369567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4528064727783</t>
   </si>
   <si>
     <t xml:space="preserve">16.754337310791</t>
@@ -1157,13 +1154,13 @@
     <t xml:space="preserve">16.6383647918701</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7929992675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4064159393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3342113494873</t>
+    <t xml:space="preserve">16.7929954528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4064140319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.33420753479</t>
   </si>
   <si>
     <t xml:space="preserve">17.3805961608887</t>
@@ -1172,7 +1169,7 @@
     <t xml:space="preserve">17.4888401031494</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5506916046143</t>
+    <t xml:space="preserve">17.5506935119629</t>
   </si>
   <si>
     <t xml:space="preserve">17.6898593902588</t>
@@ -1184,19 +1181,19 @@
     <t xml:space="preserve">17.6434707641602</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2568893432617</t>
+    <t xml:space="preserve">17.2568912506104</t>
   </si>
   <si>
     <t xml:space="preserve">17.2259674072266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.504301071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4991970062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9785537719727</t>
+    <t xml:space="preserve">17.5043029785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.499195098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9785556793213</t>
   </si>
   <si>
     <t xml:space="preserve">16.3445644378662</t>
@@ -1205,49 +1202,49 @@
     <t xml:space="preserve">16.2981758117676</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9012413024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.653829574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2672481536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3136367797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4269886016846</t>
+    <t xml:space="preserve">16.9012393951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6538276672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2672500610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3136386871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4269905090332</t>
   </si>
   <si>
     <t xml:space="preserve">18.4475555419922</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3857021331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8805236816406</t>
+    <t xml:space="preserve">18.3857040405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8805255889893</t>
   </si>
   <si>
     <t xml:space="preserve">19.1433982849121</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0042266845703</t>
+    <t xml:space="preserve">19.0042285919189</t>
   </si>
   <si>
     <t xml:space="preserve">18.911449432373</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6949672698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6795043945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7413558959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6640357971191</t>
+    <t xml:space="preserve">18.6949653625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6795024871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7413539886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6640377044678</t>
   </si>
   <si>
     <t xml:space="preserve">18.7877445220947</t>
@@ -1256,22 +1253,22 @@
     <t xml:space="preserve">19.2516384124756</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4371967315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3444213867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.406270980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5609016418457</t>
+    <t xml:space="preserve">19.437198638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3444175720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4062728881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5609035491943</t>
   </si>
   <si>
     <t xml:space="preserve">19.3289566040039</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1743240356445</t>
+    <t xml:space="preserve">19.1743221282959</t>
   </si>
   <si>
     <t xml:space="preserve">19.1124706268311</t>
@@ -1280,37 +1277,37 @@
     <t xml:space="preserve">19.1588611602783</t>
   </si>
   <si>
-    <t xml:space="preserve">19.282564163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.236177444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2052478790283</t>
+    <t xml:space="preserve">19.2825660705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2361755371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2052516937256</t>
   </si>
   <si>
     <t xml:space="preserve">19.2671031951904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5299758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.638219833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5918312072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4835910797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5145130157471</t>
+    <t xml:space="preserve">19.5299777984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6382179260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.591833114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.483585357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5145149230957</t>
   </si>
   <si>
     <t xml:space="preserve">19.4526596069336</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6072940826416</t>
+    <t xml:space="preserve">19.6072902679443</t>
   </si>
   <si>
     <t xml:space="preserve">18.1382904052734</t>
@@ -1319,100 +1316,103 @@
     <t xml:space="preserve">18.3547763824463</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0764408111572</t>
+    <t xml:space="preserve">18.07643699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0300521850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1737804412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9502010345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3654155731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2057189941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6209373474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5091495513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5889987945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.557056427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4931774139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1578102111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4292984008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6848182678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6369075775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4133281707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4612369537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3175106048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8064727783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8224411010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7106513977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9182586669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9661693572998</t>
   </si>
   <si>
     <t xml:space="preserve">18.03005027771</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1737785339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9501991271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3654193878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2057189941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6209373474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5091495513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5889987945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5570583343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4931793212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1578102111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4292984008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.684814453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6369075775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4133281707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4612369537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3175106048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8064708709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8224391937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7106513977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9182624816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9661712646484</t>
-  </si>
-  <si>
     <t xml:space="preserve">17.8863201141357</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9981117248535</t>
+    <t xml:space="preserve">17.9981136322021</t>
   </si>
   <si>
     <t xml:space="preserve">18.3973579406738</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5251178741455</t>
+    <t xml:space="preserve">18.5251159667969</t>
   </si>
   <si>
     <t xml:space="preserve">18.4452686309814</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1479454040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1639137268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0201835632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8604888916016</t>
+    <t xml:space="preserve">19.1479434967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1639156341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0201873779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8604869842529</t>
   </si>
   <si>
     <t xml:space="preserve">18.7806377410889</t>
@@ -1421,73 +1421,73 @@
     <t xml:space="preserve">18.5730266571045</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0680961608887</t>
+    <t xml:space="preserve">19.06809425354</t>
   </si>
   <si>
     <t xml:space="preserve">18.7646656036377</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4772090911865</t>
+    <t xml:space="preserve">18.4772071838379</t>
   </si>
   <si>
     <t xml:space="preserve">18.7007865905762</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2437629699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4513759613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4992828369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2118244171143</t>
+    <t xml:space="preserve">19.2437648773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4513740539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4992847442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2118263244629</t>
   </si>
   <si>
     <t xml:space="preserve">19.1319732666016</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0042152404785</t>
+    <t xml:space="preserve">19.0042133331299</t>
   </si>
   <si>
     <t xml:space="preserve">19.1160068511963</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0361557006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1798877716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3236122131348</t>
+    <t xml:space="preserve">19.0361576080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1798839569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.323616027832</t>
   </si>
   <si>
     <t xml:space="preserve">19.3395843505859</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3076457977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7228622436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.467342376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3874950408936</t>
+    <t xml:space="preserve">19.3076438903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.722864151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4673442840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3874931335449</t>
   </si>
   <si>
     <t xml:space="preserve">19.5631637573242</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8825607299805</t>
+    <t xml:space="preserve">19.8825588226318</t>
   </si>
   <si>
     <t xml:space="preserve">20.3616600036621</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4415092468262</t>
+    <t xml:space="preserve">20.4415111541748</t>
   </si>
   <si>
     <t xml:space="preserve">20.2658386230469</t>
@@ -1496,28 +1496,28 @@
     <t xml:space="preserve">20.7609081268311</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0962772369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8247890472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2498722076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4734477996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1540508270264</t>
+    <t xml:space="preserve">21.0962753295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8247871398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.249870300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4734497070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1540489196777</t>
   </si>
   <si>
     <t xml:space="preserve">20.1700191497803</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7548027038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5312232971191</t>
+    <t xml:space="preserve">19.7548046112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5312213897705</t>
   </si>
   <si>
     <t xml:space="preserve">19.4034633636475</t>
@@ -1526,46 +1526,46 @@
     <t xml:space="preserve">18.8125762939453</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7327251434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3813877105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2536296844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9342308044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3494472503662</t>
+    <t xml:space="preserve">18.7327270507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3813896179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2536315917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9342288970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3494491577148</t>
   </si>
   <si>
     <t xml:space="preserve">18.9243679046631</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7486972808838</t>
+    <t xml:space="preserve">18.7486953735352</t>
   </si>
   <si>
     <t xml:space="preserve">18.1258697509766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7905025482178</t>
+    <t xml:space="preserve">17.7905006408691</t>
   </si>
   <si>
     <t xml:space="preserve">17.4391613006592</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1357345581055</t>
+    <t xml:space="preserve">17.1357326507568</t>
   </si>
   <si>
     <t xml:space="preserve">17.2155838012695</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9760360717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5509510040283</t>
+    <t xml:space="preserve">16.9760341644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.550952911377</t>
   </si>
   <si>
     <t xml:space="preserve">16.8961849212646</t>
@@ -1574,37 +1574,37 @@
     <t xml:space="preserve">17.0718536376953</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9281253814697</t>
+    <t xml:space="preserve">16.9281272888184</t>
   </si>
   <si>
     <t xml:space="preserve">16.8323059082031</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0558853149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1836433410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.455135345459</t>
+    <t xml:space="preserve">17.0558834075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1836452484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4551334381104</t>
   </si>
   <si>
     <t xml:space="preserve">16.8163356781006</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3532047271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9859018325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0976867675781</t>
+    <t xml:space="preserve">16.3532085418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9858989715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0976886749268</t>
   </si>
   <si>
     <t xml:space="preserve">16.1136608123779</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4269523620605</t>
+    <t xml:space="preserve">15.4269514083862</t>
   </si>
   <si>
     <t xml:space="preserve">15.3311319351196</t>
@@ -1613,25 +1613,25 @@
     <t xml:space="preserve">15.6505308151245</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4748620986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4429216384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7703065872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8421678543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7383642196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4490299224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2733592987061</t>
+    <t xml:space="preserve">15.4748601913452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4429244995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7703046798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.842170715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7383651733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4490280151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2733554840088</t>
   </si>
   <si>
     <t xml:space="preserve">16.1615695953369</t>
@@ -1640,43 +1640,43 @@
     <t xml:space="preserve">16.321268081665</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4809665679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.624698638916</t>
+    <t xml:space="preserve">16.4809684753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6246967315674</t>
   </si>
   <si>
     <t xml:space="preserve">16.768424987793</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1676731109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3433456420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2794609069824</t>
+    <t xml:space="preserve">17.1676750183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3433418273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2794628143311</t>
   </si>
   <si>
     <t xml:space="preserve">16.9440937042236</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0079746246338</t>
+    <t xml:space="preserve">17.0079727172852</t>
   </si>
   <si>
     <t xml:space="preserve">16.6406669616699</t>
   </si>
   <si>
-    <t xml:space="preserve">16.241418838501</t>
+    <t xml:space="preserve">16.2414169311523</t>
   </si>
   <si>
     <t xml:space="preserve">16.5608177185059</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7045478820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.848274230957</t>
+    <t xml:space="preserve">16.7045459747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8482761383057</t>
   </si>
   <si>
     <t xml:space="preserve">17.3752841949463</t>
@@ -1694,76 +1694,76 @@
     <t xml:space="preserve">16.8642463684082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7205142974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6885738372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6087245941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7364845275879</t>
+    <t xml:space="preserve">16.720516204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6885776519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6087265014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7364864349365</t>
   </si>
   <si>
     <t xml:space="preserve">16.3052978515625</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8980646133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1935119628906</t>
+    <t xml:space="preserve">15.8980665206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1935062408447</t>
   </si>
   <si>
     <t xml:space="preserve">16.2094783782959</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3851470947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.28932762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2573890686035</t>
+    <t xml:space="preserve">16.3851490020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2893257141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2573871612549</t>
   </si>
   <si>
     <t xml:space="preserve">16.2254467010498</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9140357971191</t>
+    <t xml:space="preserve">15.9140348434448</t>
   </si>
   <si>
     <t xml:space="preserve">16.417085647583</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5288772583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7843971252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5767860412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3691787719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1775398254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4889507293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2494029998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3292541503906</t>
+    <t xml:space="preserve">16.5288753509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7843990325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5767841339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.369176864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1775379180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4889526367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2494049072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.329252243042</t>
   </si>
   <si>
     <t xml:space="preserve">16.4091014862061</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1695537567139</t>
+    <t xml:space="preserve">16.1695556640625</t>
   </si>
   <si>
     <t xml:space="preserve">16.0497798919678</t>
@@ -1781,28 +1781,28 @@
     <t xml:space="preserve">17.0878257751465</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0478992462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8083515167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9680500030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7285041809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8881988525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1277484893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8793487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.045238494873</t>
+    <t xml:space="preserve">17.0479011535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.808349609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9680480957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7285003662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8882007598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1277523040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8793506622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0452404022217</t>
   </si>
   <si>
     <t xml:space="preserve">16.9208221435547</t>
@@ -1814,7 +1814,7 @@
     <t xml:space="preserve">17.2111301422119</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1281833648682</t>
+    <t xml:space="preserve">17.1281871795654</t>
   </si>
   <si>
     <t xml:space="preserve">17.1696586608887</t>
@@ -1823,10 +1823,10 @@
     <t xml:space="preserve">17.418493270874</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3770236968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4599666595459</t>
+    <t xml:space="preserve">17.3770217895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4599647521973</t>
   </si>
   <si>
     <t xml:space="preserve">17.2940769195557</t>
@@ -1835,7 +1835,7 @@
     <t xml:space="preserve">16.9622955322266</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7549304962158</t>
+    <t xml:space="preserve">16.7549324035645</t>
   </si>
   <si>
     <t xml:space="preserve">16.6305141448975</t>
@@ -1847,25 +1847,25 @@
     <t xml:space="preserve">16.4895076751709</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5392761230469</t>
+    <t xml:space="preserve">16.5392742156982</t>
   </si>
   <si>
     <t xml:space="preserve">17.7088012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">17.667329788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5014381408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5429096221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2526016235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7134609222412</t>
+    <t xml:space="preserve">17.6673278808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5014400482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.542911529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2526035308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7134571075439</t>
   </si>
   <si>
     <t xml:space="preserve">16.4231510162354</t>
@@ -1880,43 +1880,43 @@
     <t xml:space="preserve">16.17431640625</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2738494873047</t>
+    <t xml:space="preserve">16.2738513946533</t>
   </si>
   <si>
     <t xml:space="preserve">16.124547958374</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3070278167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8591232299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7264099121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7927665710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0747814178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5273408889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4278078079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6600542068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1789712905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3614549636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6932325363159</t>
+    <t xml:space="preserve">16.3070259094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8591251373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7264108657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7927684783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.074779510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5273427963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4278087615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6600532531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1789722442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3614511489868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6932334899902</t>
   </si>
   <si>
     <t xml:space="preserve">15.6102876663208</t>
@@ -1925,19 +1925,19 @@
     <t xml:space="preserve">15.4609851837158</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4443969726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3780422210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2950963973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.925479888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2904396057129</t>
+    <t xml:space="preserve">15.4443979263306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3780403137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2950973510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9254808425903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2904376983643</t>
   </si>
   <si>
     <t xml:space="preserve">16.3899726867676</t>
@@ -1949,16 +1949,16 @@
     <t xml:space="preserve">16.6719875335693</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9576377868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0867156982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3355464935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8378772735596</t>
+    <t xml:space="preserve">17.9576358795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0867137908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3355484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8378753662109</t>
   </si>
   <si>
     <t xml:space="preserve">16.5890407562256</t>
@@ -1973,34 +1973,34 @@
     <t xml:space="preserve">15.9088916778564</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1577262878418</t>
+    <t xml:space="preserve">16.1577243804932</t>
   </si>
   <si>
     <t xml:space="preserve">16.1411361694336</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4729194641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7595891952515</t>
+    <t xml:space="preserve">16.4729175567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7595911026001</t>
   </si>
   <si>
     <t xml:space="preserve">15.6766443252563</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5937004089355</t>
+    <t xml:space="preserve">15.5936975479126</t>
   </si>
   <si>
     <t xml:space="preserve">15.4775762557983</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7429990768433</t>
+    <t xml:space="preserve">15.7430000305176</t>
   </si>
   <si>
     <t xml:space="preserve">15.7098236083984</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8425350189209</t>
+    <t xml:space="preserve">15.8425340652466</t>
   </si>
   <si>
     <t xml:space="preserve">16.3567943572998</t>
@@ -2009,7 +2009,7 @@
     <t xml:space="preserve">16.323616027832</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9752464294434</t>
+    <t xml:space="preserve">15.975248336792</t>
   </si>
   <si>
     <t xml:space="preserve">17.5843849182129</t>
@@ -2018,79 +2018,79 @@
     <t xml:space="preserve">17.0037689208984</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2240829467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0084247589111</t>
+    <t xml:space="preserve">16.2240810394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0084266662598</t>
   </si>
   <si>
     <t xml:space="preserve">16.1909046173096</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5558643341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5319995880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7974243164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.183629989624</t>
+    <t xml:space="preserve">16.5558624267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5319986343384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7974262237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1836309432983</t>
   </si>
   <si>
     <t xml:space="preserve">13.9347944259644</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6361932754517</t>
+    <t xml:space="preserve">13.6361923217773</t>
   </si>
   <si>
     <t xml:space="preserve">13.4371242523193</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2712335586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3873567581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7616300582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9606981277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4251909255981</t>
+    <t xml:space="preserve">13.2712326049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3873558044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7616310119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9606990814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4251918792725</t>
   </si>
   <si>
     <t xml:space="preserve">11.0317115783691</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4796171188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1690816879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3681507110596</t>
+    <t xml:space="preserve">11.4796180725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1690826416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3681516647339</t>
   </si>
   <si>
     <t xml:space="preserve">9.95342445373535</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3183841705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8777542114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4417810440063</t>
+    <t xml:space="preserve">10.3183832168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8777532577515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4417819976807</t>
   </si>
   <si>
     <t xml:space="preserve">12.8565073013306</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1763572692871</t>
+    <t xml:space="preserve">12.1763563156128</t>
   </si>
   <si>
     <t xml:space="preserve">12.2924785614014</t>
@@ -2099,31 +2099,31 @@
     <t xml:space="preserve">11.2141923904419</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9155883789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6667537689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2022619247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4510974884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5174531936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5340414047241</t>
+    <t xml:space="preserve">10.9155893325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6667528152466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2022609710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.451096534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5174512863159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5340404510498</t>
   </si>
   <si>
     <t xml:space="preserve">10.4013290405273</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1524934768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0529594421387</t>
+    <t xml:space="preserve">10.1524925231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0529584884644</t>
   </si>
   <si>
     <t xml:space="preserve">9.97001457214355</t>
@@ -2135,31 +2135,31 @@
     <t xml:space="preserve">10.6999311447144</t>
   </si>
   <si>
-    <t xml:space="preserve">10.301794052124</t>
+    <t xml:space="preserve">10.3017950057983</t>
   </si>
   <si>
     <t xml:space="preserve">10.0695486068726</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2520275115967</t>
+    <t xml:space="preserve">10.252028465271</t>
   </si>
   <si>
     <t xml:space="preserve">10.0031929016113</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0363693237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1193161010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92024707794189</t>
+    <t xml:space="preserve">10.0363702774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1193151473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92024612426758</t>
   </si>
   <si>
     <t xml:space="preserve">9.45575332641602</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50552082061768</t>
+    <t xml:space="preserve">9.50552177429199</t>
   </si>
   <si>
     <t xml:space="preserve">9.32304096221924</t>
@@ -2177,55 +2177,55 @@
     <t xml:space="preserve">10.1359043121338</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70458793640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38939666748047</t>
+    <t xml:space="preserve">9.70458984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38939762115479</t>
   </si>
   <si>
     <t xml:space="preserve">10.4345064163208</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2188501358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4179182052612</t>
+    <t xml:space="preserve">10.2188491821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4179172515869</t>
   </si>
   <si>
     <t xml:space="preserve">10.99853515625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8990001678467</t>
+    <t xml:space="preserve">10.899001121521</t>
   </si>
   <si>
     <t xml:space="preserve">10.9819459915161</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8160552978516</t>
+    <t xml:space="preserve">10.8160543441772</t>
   </si>
   <si>
     <t xml:space="preserve">10.8824110031128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8113975524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7782201766968</t>
+    <t xml:space="preserve">11.8113965988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7782192230225</t>
   </si>
   <si>
     <t xml:space="preserve">11.595739364624</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3634920120239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6833438873291</t>
+    <t xml:space="preserve">11.3634939193726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6833429336548</t>
   </si>
   <si>
     <t xml:space="preserve">10.9487676620483</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9653568267822</t>
+    <t xml:space="preserve">10.9653577804565</t>
   </si>
   <si>
     <t xml:space="preserve">11.2639589309692</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">11.297137260437</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0814800262451</t>
+    <t xml:space="preserve">11.0814790725708</t>
   </si>
   <si>
     <t xml:space="preserve">11.0151233673096</t>
@@ -2258,19 +2258,19 @@
     <t xml:space="preserve">10.8492336273193</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5838088989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3847408294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.650164604187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2354393005371</t>
+    <t xml:space="preserve">10.5838098526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3847398757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6501636505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3515615463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2354383468628</t>
   </si>
   <si>
     <t xml:space="preserve">10.9321784973145</t>
@@ -2279,43 +2279,43 @@
     <t xml:space="preserve">10.550630569458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5008630752563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6169862747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4842739105225</t>
+    <t xml:space="preserve">10.5008640289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6169872283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4842748641968</t>
   </si>
   <si>
     <t xml:space="preserve">10.0197811126709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3349733352661</t>
+    <t xml:space="preserve">10.3349723815918</t>
   </si>
   <si>
     <t xml:space="preserve">10.7828769683838</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6003971099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1312465667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4132614135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4298496246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2307806015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8658227920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3137273788452</t>
+    <t xml:space="preserve">10.600399017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1312456130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4132595062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4298486709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2307815551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8658237457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3137264251709</t>
   </si>
   <si>
     <t xml:space="preserve">11.3966703414917</t>
@@ -2327,25 +2327,25 @@
     <t xml:space="preserve">11.8611650466919</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2095355987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9772872924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0602331161499</t>
+    <t xml:space="preserve">12.2095346450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9772882461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0602340698242</t>
   </si>
   <si>
     <t xml:space="preserve">12.2593011856079</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3800821304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1146583557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6335744857788</t>
+    <t xml:space="preserve">11.3800830841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1146564483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6335754394531</t>
   </si>
   <si>
     <t xml:space="preserve">10.2686166763306</t>
@@ -2354,28 +2354,28 @@
     <t xml:space="preserve">9.55528736114502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62164402008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65482234954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.605055809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75435638427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.491548538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0058097839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1929454803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8399171829224</t>
+    <t xml:space="preserve">9.62164497375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65482139587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60505485534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75435733795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4915494918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0058088302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1929445266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8399181365967</t>
   </si>
   <si>
     <t xml:space="preserve">13.3210000991821</t>
@@ -2384,10 +2384,10 @@
     <t xml:space="preserve">12.4086036682129</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2758913040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7237939834595</t>
+    <t xml:space="preserve">12.2758893966675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7237958908081</t>
   </si>
   <si>
     <t xml:space="preserve">12.9062738418579</t>
@@ -2399,7 +2399,7 @@
     <t xml:space="preserve">12.9892196655273</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0721654891968</t>
+    <t xml:space="preserve">13.0721645355225</t>
   </si>
   <si>
     <t xml:space="preserve">13.0223970413208</t>
@@ -2408,22 +2408,22 @@
     <t xml:space="preserve">13.0887537002563</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0389862060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6740283966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4583702087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5081377029419</t>
+    <t xml:space="preserve">13.038987159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6740274429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4583711624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5081367492676</t>
   </si>
   <si>
     <t xml:space="preserve">12.7403841018677</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3754253387451</t>
+    <t xml:space="preserve">12.3754243850708</t>
   </si>
   <si>
     <t xml:space="preserve">12.4749593734741</t>
@@ -2441,91 +2441,91 @@
     <t xml:space="preserve">13.5366582870483</t>
   </si>
   <si>
-    <t xml:space="preserve">13.984561920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3661108016968</t>
+    <t xml:space="preserve">13.9845628738403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3661088943481</t>
   </si>
   <si>
     <t xml:space="preserve">14.5817680358887</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6978912353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7642450332642</t>
+    <t xml:space="preserve">14.6978921890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7642459869385</t>
   </si>
   <si>
     <t xml:space="preserve">14.6315336227417</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1006832122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.432466506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.780837059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7476596832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4988222122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3495197296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2499876022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2333974838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7854948043823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0177402496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0509195327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2831649780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0462617874146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9301376342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3946304321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3448629379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9918365478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8969583511353</t>
+    <t xml:space="preserve">14.1006851196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4324645996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7808351516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7476577758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4988212585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3495206832886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2499856948853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7854928970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0177392959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0509185791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.283164024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0462608337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.930136680603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3946294784546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3448619842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9918384552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8969573974609</t>
   </si>
   <si>
     <t xml:space="preserve">14.9799060821533</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9135465621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9964933395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.825945854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6434669494629</t>
+    <t xml:space="preserve">14.9135475158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9964923858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8259449005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6434659957886</t>
   </si>
   <si>
     <t xml:space="preserve">16.0250148773193</t>
@@ -2540,73 +2540,73 @@
     <t xml:space="preserve">15.5605192184448</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0130844116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2619171142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2287397384644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1457939147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4941644668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.626877784729</t>
+    <t xml:space="preserve">15.0130825042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2619209289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2287425994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1457958221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4941654205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6268768310547</t>
   </si>
   <si>
     <t xml:space="preserve">15.2121515274048</t>
   </si>
   <si>
-    <t xml:space="preserve">15.502459526062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2702140808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.253623008728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5439310073853</t>
+    <t xml:space="preserve">15.5024585723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2702121734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2536239624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5439319610596</t>
   </si>
   <si>
     <t xml:space="preserve">15.5771102905273</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8508291244507</t>
+    <t xml:space="preserve">15.8508310317993</t>
   </si>
   <si>
     <t xml:space="preserve">15.7181177139282</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7347068786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8840084075928</t>
+    <t xml:space="preserve">15.7347049713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8840074539185</t>
   </si>
   <si>
     <t xml:space="preserve">15.7512950897217</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4361047744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3982696533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5807456970215</t>
+    <t xml:space="preserve">15.4361028671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3982677459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5807476043701</t>
   </si>
   <si>
     <t xml:space="preserve">15.8674182891846</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0830745697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1079597473145</t>
+    <t xml:space="preserve">16.0830764770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1079578399658</t>
   </si>
   <si>
     <t xml:space="preserve">16.4646224975586</t>
@@ -2615,52 +2615,52 @@
     <t xml:space="preserve">16.622220993042</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8212909698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7051639556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9042339324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9374122619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1364822387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3023700714111</t>
+    <t xml:space="preserve">16.8212871551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7051658630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9042320251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9374103546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1364784240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3023719787598</t>
   </si>
   <si>
     <t xml:space="preserve">17.4350833892822</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4516716003418</t>
+    <t xml:space="preserve">17.4516735076904</t>
   </si>
   <si>
     <t xml:space="preserve">17.219425201416</t>
   </si>
   <si>
-    <t xml:space="preserve">16.721752166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1530704498291</t>
+    <t xml:space="preserve">16.7217540740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1530685424805</t>
   </si>
   <si>
     <t xml:space="preserve">17.0535335540771</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0369453430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8876457214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.771520614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8544654846191</t>
+    <t xml:space="preserve">17.0369434356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8876438140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7715225219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8544635772705</t>
   </si>
   <si>
     <t xml:space="preserve">17.2028369903564</t>
@@ -2672,16 +2672,16 @@
     <t xml:space="preserve">17.1198902130127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7383441925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3521385192871</t>
+    <t xml:space="preserve">16.7383460998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3521366119385</t>
   </si>
   <si>
     <t xml:space="preserve">17.269193649292</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8710556030273</t>
+    <t xml:space="preserve">16.8710536956787</t>
   </si>
   <si>
     <t xml:space="preserve">15.9171857833862</t>
@@ -2693,16 +2693,16 @@
     <t xml:space="preserve">16.2323760986328</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6056327819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6958503723145</t>
+    <t xml:space="preserve">16.6056308746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6958522796631</t>
   </si>
   <si>
     <t xml:space="preserve">18.1981792449951</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1649990081787</t>
+    <t xml:space="preserve">18.1650009155273</t>
   </si>
   <si>
     <t xml:space="preserve">17.617561340332</t>
@@ -2711,31 +2711,31 @@
     <t xml:space="preserve">18.0820541381836</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6507377624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8000411987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4019069671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3189582824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.020357131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7881107330322</t>
+    <t xml:space="preserve">17.6507415771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8000392913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4019050598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3189563751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0203590393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7881088256836</t>
   </si>
   <si>
     <t xml:space="preserve">16.970588684082</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1862449645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4065608978271</t>
+    <t xml:space="preserve">17.1862468719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4065628051758</t>
   </si>
   <si>
     <t xml:space="preserve">16.4148578643799</t>
@@ -2744,13 +2744,13 @@
     <t xml:space="preserve">16.0499000549316</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1660194396973</t>
+    <t xml:space="preserve">16.1660213470459</t>
   </si>
   <si>
     <t xml:space="preserve">17.5346164703369</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0701236724854</t>
+    <t xml:space="preserve">17.0701217651367</t>
   </si>
   <si>
     <t xml:space="preserve">17.2360153198242</t>
@@ -2759,13 +2759,13 @@
     <t xml:space="preserve">17.6839179992676</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4848499298096</t>
+    <t xml:space="preserve">17.4848518371582</t>
   </si>
   <si>
     <t xml:space="preserve">17.276216506958</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2424736022949</t>
+    <t xml:space="preserve">17.2424755096436</t>
   </si>
   <si>
     <t xml:space="preserve">17.3437023162842</t>
@@ -2777,28 +2777,28 @@
     <t xml:space="preserve">17.4111881256104</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3774433135986</t>
+    <t xml:space="preserve">17.3774452209473</t>
   </si>
   <si>
     <t xml:space="preserve">17.6642589569092</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4449291229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4618034362793</t>
+    <t xml:space="preserve">17.4449310302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4618015289307</t>
   </si>
   <si>
     <t xml:space="preserve">17.1749877929688</t>
   </si>
   <si>
-    <t xml:space="preserve">17.040018081665</t>
+    <t xml:space="preserve">17.0400199890137</t>
   </si>
   <si>
     <t xml:space="preserve">17.0062770843506</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9556617736816</t>
+    <t xml:space="preserve">16.9556636810303</t>
   </si>
   <si>
     <t xml:space="preserve">16.8628692626953</t>
@@ -2813,40 +2813,40 @@
     <t xml:space="preserve">16.7532062530518</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2087326049805</t>
+    <t xml:space="preserve">17.2087306976318</t>
   </si>
   <si>
     <t xml:space="preserve">16.2048892974854</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0952243804932</t>
+    <t xml:space="preserve">16.0952262878418</t>
   </si>
   <si>
     <t xml:space="preserve">16.1458396911621</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7915420532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.690315246582</t>
+    <t xml:space="preserve">15.7915410995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6903142929077</t>
   </si>
   <si>
     <t xml:space="preserve">15.8590259552002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4119367599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5216007232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0998182296753</t>
+    <t xml:space="preserve">15.4119386672974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5216026306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.099817276001</t>
   </si>
   <si>
     <t xml:space="preserve">15.420373916626</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6059598922729</t>
+    <t xml:space="preserve">15.60595703125</t>
   </si>
   <si>
     <t xml:space="preserve">15.5806503295898</t>
@@ -2855,37 +2855,37 @@
     <t xml:space="preserve">15.8337211608887</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0446109771729</t>
+    <t xml:space="preserve">16.0446128845215</t>
   </si>
   <si>
     <t xml:space="preserve">15.8758993148804</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8927717208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0108699798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.934947013855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7662353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7746715545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5131645202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4878597259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1841735839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2347888946533</t>
+    <t xml:space="preserve">15.8927698135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0108680725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9349479675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7662343978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7746725082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.513165473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4878606796265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1841745376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2347898483276</t>
   </si>
   <si>
     <t xml:space="preserve">15.3950662612915</t>
@@ -2897,52 +2897,52 @@
     <t xml:space="preserve">16.112096786499</t>
   </si>
   <si>
-    <t xml:space="preserve">16.297679901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4495220184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5890865325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.698751449585</t>
+    <t xml:space="preserve">16.2976818084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4495239257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5890855789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6987504959106</t>
   </si>
   <si>
     <t xml:space="preserve">16.0361766815186</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9686908721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3145523071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9180774688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0193042755127</t>
+    <t xml:space="preserve">15.9686899185181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3145542144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9180784225464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0193061828613</t>
   </si>
   <si>
     <t xml:space="preserve">15.5384721755981</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0154619216919</t>
+    <t xml:space="preserve">15.0154609680176</t>
   </si>
   <si>
     <t xml:space="preserve">15.1504306793213</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5300359725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8168497085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5637798309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8843336105347</t>
+    <t xml:space="preserve">15.5300369262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8168478012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5637807846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.884334564209</t>
   </si>
   <si>
     <t xml:space="preserve">16.1374034881592</t>
@@ -2951,28 +2951,28 @@
     <t xml:space="preserve">15.8674612045288</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4541149139404</t>
+    <t xml:space="preserve">15.4541168212891</t>
   </si>
   <si>
     <t xml:space="preserve">14.9732847213745</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0238962173462</t>
+    <t xml:space="preserve">15.0238971710205</t>
   </si>
   <si>
     <t xml:space="preserve">15.1673030853271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4372425079346</t>
+    <t xml:space="preserve">15.4372434616089</t>
   </si>
   <si>
     <t xml:space="preserve">15.6312656402588</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4794225692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1588668823242</t>
+    <t xml:space="preserve">15.4794235229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1588678359985</t>
   </si>
   <si>
     <t xml:space="preserve">14.7623929977417</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">14.4080944061279</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7416791915894</t>
+    <t xml:space="preserve">13.7416801452637</t>
   </si>
   <si>
     <t xml:space="preserve">14.0537977218628</t>
@@ -2999,43 +2999,43 @@
     <t xml:space="preserve">13.142746925354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7294006347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6028642654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.906548500061</t>
+    <t xml:space="preserve">12.7293996810913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6028652191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9065494537354</t>
   </si>
   <si>
     <t xml:space="preserve">13.3367671966553</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1258764266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5139169692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9188289642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3198957443237</t>
+    <t xml:space="preserve">13.1258754730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.513916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9188280105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.319896697998</t>
   </si>
   <si>
     <t xml:space="preserve">13.5307874679565</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8728055953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9318561553955</t>
+    <t xml:space="preserve">12.8728065490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9318552017212</t>
   </si>
   <si>
     <t xml:space="preserve">12.7631435394287</t>
   </si>
   <si>
-    <t xml:space="preserve">12.636607170105</t>
+    <t xml:space="preserve">12.6366081237793</t>
   </si>
   <si>
     <t xml:space="preserve">12.4172811508179</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">12.4678945541382</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1304693222046</t>
+    <t xml:space="preserve">12.1304683685303</t>
   </si>
   <si>
     <t xml:space="preserve">12.2823114395142</t>
@@ -3077,25 +3077,25 @@
     <t xml:space="preserve">13.3958168029785</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4464302062988</t>
+    <t xml:space="preserve">13.4464311599731</t>
   </si>
   <si>
     <t xml:space="preserve">13.7838573455811</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3114604949951</t>
+    <t xml:space="preserve">13.3114595413208</t>
   </si>
   <si>
     <t xml:space="preserve">13.2271041870117</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9571628570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0752611160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7040929794312</t>
+    <t xml:space="preserve">12.9571619033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0752620697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7040939331055</t>
   </si>
   <si>
     <t xml:space="preserve">12.771577835083</t>
@@ -3110,7 +3110,7 @@
     <t xml:space="preserve">12.0461120605469</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8773994445801</t>
+    <t xml:space="preserve">11.8773984909058</t>
   </si>
   <si>
     <t xml:space="preserve">12.1473398208618</t>
@@ -3119,16 +3119,16 @@
     <t xml:space="preserve">12.1642112731934</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2316970825195</t>
+    <t xml:space="preserve">12.2316961288452</t>
   </si>
   <si>
     <t xml:space="preserve">12.4510231018066</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3835391998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2991809844971</t>
+    <t xml:space="preserve">12.3835382461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2991819381714</t>
   </si>
   <si>
     <t xml:space="preserve">11.8267850875854</t>
@@ -3137,13 +3137,13 @@
     <t xml:space="preserve">11.6749439239502</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6487474441528</t>
+    <t xml:space="preserve">11.6487464904785</t>
   </si>
   <si>
     <t xml:space="preserve">11.474102973938</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3693170547485</t>
+    <t xml:space="preserve">11.3693161010742</t>
   </si>
   <si>
     <t xml:space="preserve">11.8932485580444</t>
@@ -3152,10 +3152,10 @@
     <t xml:space="preserve">11.9107122421265</t>
   </si>
   <si>
-    <t xml:space="preserve">12.434642791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.102819442749</t>
+    <t xml:space="preserve">12.4346437454224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1028203964233</t>
   </si>
   <si>
     <t xml:space="preserve">12.0154981613159</t>
@@ -3164,7 +3164,7 @@
     <t xml:space="preserve">11.9805698394775</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1901416778564</t>
+    <t xml:space="preserve">12.1901426315308</t>
   </si>
   <si>
     <t xml:space="preserve">12.3298578262329</t>
@@ -3188,7 +3188,7 @@
     <t xml:space="preserve">11.7186040878296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5788898468018</t>
+    <t xml:space="preserve">11.5788888931274</t>
   </si>
   <si>
     <t xml:space="preserve">11.8408555984497</t>
@@ -3212,7 +3212,7 @@
     <t xml:space="preserve">11.2645292282104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8104562759399</t>
+    <t xml:space="preserve">10.8104572296143</t>
   </si>
   <si>
     <t xml:space="preserve">11.0549573898315</t>
@@ -3227,25 +3227,25 @@
     <t xml:space="preserve">11.2470664978027</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0374937057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8453845977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3343877792358</t>
+    <t xml:space="preserve">11.0374927520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8453855514526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3343868255615</t>
   </si>
   <si>
     <t xml:space="preserve">11.3169231414795</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4042463302612</t>
+    <t xml:space="preserve">11.4042453765869</t>
   </si>
   <si>
     <t xml:space="preserve">11.2296009063721</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6138181686401</t>
+    <t xml:space="preserve">11.6138172149658</t>
   </si>
   <si>
     <t xml:space="preserve">11.788462638855</t>
@@ -3263,13 +3263,13 @@
     <t xml:space="preserve">11.4566383361816</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5439615249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4217090606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1073513031006</t>
+    <t xml:space="preserve">11.5439605712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4217100143433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1073503494263</t>
   </si>
   <si>
     <t xml:space="preserve">11.0898857116699</t>
@@ -3284,31 +3284,31 @@
     <t xml:space="preserve">10.6707410812378</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5135612487793</t>
+    <t xml:space="preserve">10.5135622024536</t>
   </si>
   <si>
     <t xml:space="preserve">10.2865238189697</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2341318130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0594882965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1468095779419</t>
+    <t xml:space="preserve">10.234130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0594873428345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1468086242676</t>
   </si>
   <si>
     <t xml:space="preserve">9.78005695343018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90230751037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81498622894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76259326934814</t>
+    <t xml:space="preserve">9.90230846405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81498527526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76259231567383</t>
   </si>
   <si>
     <t xml:space="preserve">9.9896297454834</t>
@@ -3320,19 +3320,19 @@
     <t xml:space="preserve">9.29105472564697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51809120178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2211971282959</t>
+    <t xml:space="preserve">9.51809024810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22119617462158</t>
   </si>
   <si>
     <t xml:space="preserve">9.25612640380859</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06401634216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80205059051514</t>
+    <t xml:space="preserve">9.0640172958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80205154418945</t>
   </si>
   <si>
     <t xml:space="preserve">8.81951522827148</t>
@@ -3341,7 +3341,7 @@
     <t xml:space="preserve">8.60121154785156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48769283294678</t>
+    <t xml:space="preserve">8.48769187927246</t>
   </si>
   <si>
     <t xml:space="preserve">8.19079780578613</t>
@@ -3362,7 +3362,7 @@
     <t xml:space="preserve">8.34797763824463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54881858825684</t>
+    <t xml:space="preserve">8.54881763458252</t>
   </si>
   <si>
     <t xml:space="preserve">8.59247875213623</t>
@@ -3386,10 +3386,10 @@
     <t xml:space="preserve">8.73219394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02908802032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09894561767578</t>
+    <t xml:space="preserve">9.02908897399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0989465713501</t>
   </si>
   <si>
     <t xml:space="preserve">9.41330432891846</t>
@@ -3398,13 +3398,13 @@
     <t xml:space="preserve">9.308518409729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27358913421631</t>
+    <t xml:space="preserve">9.27359008789062</t>
   </si>
   <si>
     <t xml:space="preserve">9.39584064483643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72766494750977</t>
+    <t xml:space="preserve">9.72766399383545</t>
   </si>
   <si>
     <t xml:space="preserve">9.55301952362061</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">9.91977214813232</t>
   </si>
   <si>
-    <t xml:space="preserve">10.269061088562</t>
+    <t xml:space="preserve">10.2690601348877</t>
   </si>
   <si>
     <t xml:space="preserve">9.65780639648438</t>
@@ -3428,7 +3428,7 @@
     <t xml:space="preserve">9.67527103424072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83245086669922</t>
+    <t xml:space="preserve">9.8324499130249</t>
   </si>
   <si>
     <t xml:space="preserve">10.0420227050781</t>
@@ -3449,13 +3449,13 @@
     <t xml:space="preserve">9.8673791885376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0944166183472</t>
+    <t xml:space="preserve">10.0944156646729</t>
   </si>
   <si>
     <t xml:space="preserve">10.0769519805908</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79752159118652</t>
+    <t xml:space="preserve">9.79752063751221</t>
   </si>
   <si>
     <t xml:space="preserve">9.9547004699707</t>
@@ -3473,13 +3473,13 @@
     <t xml:space="preserve">10.6358118057251</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7405986785889</t>
+    <t xml:space="preserve">10.7405977249146</t>
   </si>
   <si>
     <t xml:space="preserve">10.7580623626709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9152421951294</t>
+    <t xml:space="preserve">10.9152431488037</t>
   </si>
   <si>
     <t xml:space="preserve">11.0200281143188</t>
@@ -3497,7 +3497,7 @@
     <t xml:space="preserve">10.5310258865356</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6183471679688</t>
+    <t xml:space="preserve">10.6183481216431</t>
   </si>
   <si>
     <t xml:space="preserve">10.7056694030762</t>
@@ -3518,7 +3518,7 @@
     <t xml:space="preserve">10.216667175293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0245590209961</t>
+    <t xml:space="preserve">10.0245580673218</t>
   </si>
   <si>
     <t xml:space="preserve">9.84991455078125</t>
@@ -3527,7 +3527,7 @@
     <t xml:space="preserve">10.1118803024292</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5834178924561</t>
+    <t xml:space="preserve">10.5834188461304</t>
   </si>
   <si>
     <t xml:space="preserve">10.3563814163208</t>
@@ -3539,13 +3539,13 @@
     <t xml:space="preserve">11.9456405639648</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7011394500732</t>
+    <t xml:space="preserve">11.7011384963989</t>
   </si>
   <si>
     <t xml:space="preserve">12.1202850341797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3997144699097</t>
+    <t xml:space="preserve">12.399715423584</t>
   </si>
   <si>
     <t xml:space="preserve">11.9281768798828</t>
@@ -3554,7 +3554,7 @@
     <t xml:space="preserve">11.8757839202881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0678911209106</t>
+    <t xml:space="preserve">12.067892074585</t>
   </si>
   <si>
     <t xml:space="preserve">12.0329627990723</t>
@@ -3572,10 +3572,10 @@
     <t xml:space="preserve">12.8712539672852</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6442165374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9491128921509</t>
+    <t xml:space="preserve">12.6442155838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9491119384766</t>
   </si>
   <si>
     <t xml:space="preserve">13.0746583938599</t>
@@ -3584,13 +3584,13 @@
     <t xml:space="preserve">12.9132423400879</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0387887954712</t>
+    <t xml:space="preserve">13.0387878417969</t>
   </si>
   <si>
     <t xml:space="preserve">13.0567235946655</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1284627914429</t>
+    <t xml:space="preserve">13.1284637451172</t>
   </si>
   <si>
     <t xml:space="preserve">13.2540082931519</t>
@@ -3605,7 +3605,7 @@
     <t xml:space="preserve">13.5947751998901</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4871644973755</t>
+    <t xml:space="preserve">13.4871635437012</t>
   </si>
   <si>
     <t xml:space="preserve">13.4512939453125</t>
@@ -3620,7 +3620,7 @@
     <t xml:space="preserve">13.5051002502441</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2002029418945</t>
+    <t xml:space="preserve">13.2002038955688</t>
   </si>
   <si>
     <t xml:space="preserve">12.9849824905396</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">12.5366058349609</t>
   </si>
   <si>
-    <t xml:space="preserve">12.411060333252</t>
+    <t xml:space="preserve">12.4110612869263</t>
   </si>
   <si>
     <t xml:space="preserve">12.2496452331543</t>
@@ -3680,7 +3680,7 @@
     <t xml:space="preserve">12.285514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2675800323486</t>
+    <t xml:space="preserve">12.2675809860229</t>
   </si>
   <si>
     <t xml:space="preserve">12.6262817382812</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">12.5724763870239</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2137756347656</t>
+    <t xml:space="preserve">12.2137746810913</t>
   </si>
   <si>
     <t xml:space="preserve">12.5007352828979</t>
@@ -3704,10 +3704,10 @@
     <t xml:space="preserve">11.2990875244141</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5681123733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6398525238037</t>
+    <t xml:space="preserve">11.5681133270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.639853477478</t>
   </si>
   <si>
     <t xml:space="preserve">11.675724029541</t>
@@ -3719,22 +3719,22 @@
     <t xml:space="preserve">11.6577882766724</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4605016708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.37082862854</t>
+    <t xml:space="preserve">11.4605026245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3708276748657</t>
   </si>
   <si>
     <t xml:space="preserve">11.3528928756714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3349580764771</t>
+    <t xml:space="preserve">11.3349571228027</t>
   </si>
   <si>
     <t xml:space="preserve">11.2811527252197</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4963722229004</t>
+    <t xml:space="preserve">11.4963731765747</t>
   </si>
   <si>
     <t xml:space="preserve">11.5501775741577</t>
@@ -3749,16 +3749,16 @@
     <t xml:space="preserve">11.8012685775757</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7833337783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9088792800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.926815032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0164890289307</t>
+    <t xml:space="preserve">11.7833347320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.908878326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9268140792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.016489982605</t>
   </si>
   <si>
     <t xml:space="preserve">12.0882301330566</t>
@@ -3797,7 +3797,7 @@
     <t xml:space="preserve">10.5278797149658</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7610349655151</t>
+    <t xml:space="preserve">10.7610359191895</t>
   </si>
   <si>
     <t xml:space="preserve">10.5816850662231</t>
@@ -3812,7 +3812,7 @@
     <t xml:space="preserve">10.2947235107422</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3664646148682</t>
+    <t xml:space="preserve">10.3664636611938</t>
   </si>
   <si>
     <t xml:space="preserve">10.2229833602905</t>
@@ -3833,19 +3833,19 @@
     <t xml:space="preserve">9.86428260803223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68493270874023</t>
+    <t xml:space="preserve">9.68493175506592</t>
   </si>
   <si>
     <t xml:space="preserve">9.75667190551758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77460670471191</t>
+    <t xml:space="preserve">9.77460765838623</t>
   </si>
   <si>
     <t xml:space="preserve">9.70286750793457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79254150390625</t>
+    <t xml:space="preserve">9.79254245758057</t>
   </si>
   <si>
     <t xml:space="preserve">9.66699695587158</t>
@@ -3860,7 +3860,7 @@
     <t xml:space="preserve">10.0436325073242</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1871137619019</t>
+    <t xml:space="preserve">10.1871128082275</t>
   </si>
   <si>
     <t xml:space="preserve">10.5099449157715</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">10.7431001663208</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8148412704468</t>
+    <t xml:space="preserve">10.8148403167725</t>
   </si>
   <si>
     <t xml:space="preserve">10.4740753173828</t>
@@ -3881,7 +3881,7 @@
     <t xml:space="preserve">9.9001522064209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95395755767822</t>
+    <t xml:space="preserve">9.95395851135254</t>
   </si>
   <si>
     <t xml:space="preserve">10.0795030593872</t>
@@ -3893,7 +3893,7 @@
     <t xml:space="preserve">9.98982810974121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2588539123535</t>
+    <t xml:space="preserve">10.2588529586792</t>
   </si>
   <si>
     <t xml:space="preserve">10.3126592636108</t>
@@ -3905,7 +3905,7 @@
     <t xml:space="preserve">10.4561395645142</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3305950164795</t>
+    <t xml:space="preserve">10.3305940628052</t>
   </si>
   <si>
     <t xml:space="preserve">10.2050485610962</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">9.91808795928955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88221740722656</t>
+    <t xml:space="preserve">9.88221836090088</t>
   </si>
   <si>
     <t xml:space="preserve">10.0974388122559</t>
@@ -3941,31 +3941,31 @@
     <t xml:space="preserve">9.3262300491333</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4517765045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5996189117432</t>
+    <t xml:space="preserve">9.45177555084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5996198654175</t>
   </si>
   <si>
     <t xml:space="preserve">9.93602275848389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4920101165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5637502670288</t>
+    <t xml:space="preserve">10.4920091629028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5637493133545</t>
   </si>
   <si>
     <t xml:space="preserve">10.4382047653198</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6713590621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9045152664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8327751159668</t>
+    <t xml:space="preserve">10.6713600158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9045162200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8327760696411</t>
   </si>
   <si>
     <t xml:space="preserve">10.7251653671265</t>
@@ -3980,7 +3980,7 @@
     <t xml:space="preserve">10.9224510192871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6892948150635</t>
+    <t xml:space="preserve">10.6892957687378</t>
   </si>
   <si>
     <t xml:space="preserve">11.2094125747681</t>
@@ -4638,6 +4638,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.47000026702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44999980926514</t>
   </si>
 </sst>
 </file>
@@ -10402,7 +10405,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G209" t="s">
-        <v>166</v>
+        <v>87</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -10428,7 +10431,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G210" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -10454,7 +10457,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G211" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -10480,7 +10483,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G212" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -10506,7 +10509,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G213" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -10532,7 +10535,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G214" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -10558,7 +10561,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G215" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -10584,7 +10587,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G216" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -10610,7 +10613,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G217" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -10662,7 +10665,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G219" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -10766,7 +10769,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G223" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -10792,7 +10795,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G224" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -10818,7 +10821,7 @@
         <v>16</v>
       </c>
       <c r="G225" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -10844,7 +10847,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G226" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -10870,7 +10873,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G227" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -10896,7 +10899,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G228" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -10922,7 +10925,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G229" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -10948,7 +10951,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G230" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -10974,7 +10977,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G231" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -11000,7 +11003,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G232" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -11026,7 +11029,7 @@
         <v>16.5699996948242</v>
       </c>
       <c r="G233" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -11052,7 +11055,7 @@
         <v>16.3899993896484</v>
       </c>
       <c r="G234" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -11078,7 +11081,7 @@
         <v>16.25</v>
       </c>
       <c r="G235" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -11104,7 +11107,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G236" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -11130,7 +11133,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G237" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -11156,7 +11159,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G238" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -11208,7 +11211,7 @@
         <v>17</v>
       </c>
       <c r="G240" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -11260,7 +11263,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G242" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -11312,7 +11315,7 @@
         <v>17</v>
       </c>
       <c r="G244" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -11338,7 +11341,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G245" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -11364,7 +11367,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G246" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -11416,7 +11419,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G248" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -11468,7 +11471,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G250" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -11494,7 +11497,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G251" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -11546,7 +11549,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G253" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -11572,7 +11575,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G254" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -11598,7 +11601,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G255" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -11650,7 +11653,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G257" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -11702,7 +11705,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G259" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -11754,7 +11757,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G261" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -11780,7 +11783,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G262" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -11858,7 +11861,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G265" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -11936,7 +11939,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G268" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -11988,7 +11991,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G270" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -12014,7 +12017,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G271" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -12066,7 +12069,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G273" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -12092,7 +12095,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G274" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -12144,7 +12147,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G276" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -12170,7 +12173,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G277" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -12196,7 +12199,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G278" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -12222,7 +12225,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G279" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -12248,7 +12251,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G280" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -12274,7 +12277,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G281" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -12300,7 +12303,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G282" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -12326,7 +12329,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G283" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -12378,7 +12381,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G285" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -12404,7 +12407,7 @@
         <v>18.4099998474121</v>
       </c>
       <c r="G286" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -12430,7 +12433,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G287" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H287" t="s">
         <v>9</v>
@@ -12456,7 +12459,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G288" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -12482,7 +12485,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G289" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -12508,7 +12511,7 @@
         <v>18.4899997711182</v>
       </c>
       <c r="G290" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -12534,7 +12537,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G291" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -12560,7 +12563,7 @@
         <v>18.4099998474121</v>
       </c>
       <c r="G292" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -12612,7 +12615,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G294" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -12638,7 +12641,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G295" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -12664,7 +12667,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G296" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -12690,7 +12693,7 @@
         <v>18.1200008392334</v>
       </c>
       <c r="G297" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -12716,7 +12719,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G298" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -12742,7 +12745,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G299" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -12768,7 +12771,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G300" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -12794,7 +12797,7 @@
         <v>19.3899993896484</v>
       </c>
       <c r="G301" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -12820,7 +12823,7 @@
         <v>19.6299991607666</v>
       </c>
       <c r="G302" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H302" t="s">
         <v>9</v>
@@ -12846,7 +12849,7 @@
         <v>20</v>
       </c>
       <c r="G303" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -12872,7 +12875,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G304" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -12898,7 +12901,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G305" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -12924,7 +12927,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G306" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -12950,7 +12953,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G307" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -12976,7 +12979,7 @@
         <v>20.3099994659424</v>
       </c>
       <c r="G308" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -13002,7 +13005,7 @@
         <v>20.9899997711182</v>
       </c>
       <c r="G309" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -13028,7 +13031,7 @@
         <v>20.2199993133545</v>
       </c>
       <c r="G310" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -13054,7 +13057,7 @@
         <v>20.25</v>
       </c>
       <c r="G311" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -13080,7 +13083,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G312" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -13106,7 +13109,7 @@
         <v>20.5200004577637</v>
       </c>
       <c r="G313" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -13132,7 +13135,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G314" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -13158,7 +13161,7 @@
         <v>20.5</v>
       </c>
       <c r="G315" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -13184,7 +13187,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G316" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -13210,7 +13213,7 @@
         <v>21</v>
       </c>
       <c r="G317" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -13236,7 +13239,7 @@
         <v>20.75</v>
       </c>
       <c r="G318" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -13262,7 +13265,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G319" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -13288,7 +13291,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G320" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -13314,7 +13317,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G321" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H321" t="s">
         <v>9</v>
@@ -13340,7 +13343,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G322" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -13366,7 +13369,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G323" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -13392,7 +13395,7 @@
         <v>20.7700004577637</v>
       </c>
       <c r="G324" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -13418,7 +13421,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G325" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -13444,7 +13447,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G326" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -13470,7 +13473,7 @@
         <v>20.8400001525879</v>
       </c>
       <c r="G327" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H327" t="s">
         <v>9</v>
@@ -13496,7 +13499,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G328" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -13522,7 +13525,7 @@
         <v>21</v>
       </c>
       <c r="G329" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -13548,7 +13551,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G330" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -13574,7 +13577,7 @@
         <v>20.8199996948242</v>
       </c>
       <c r="G331" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -13600,7 +13603,7 @@
         <v>21.25</v>
       </c>
       <c r="G332" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -13626,7 +13629,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G333" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -13652,7 +13655,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G334" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -13678,7 +13681,7 @@
         <v>20.9699993133545</v>
       </c>
       <c r="G335" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -13704,7 +13707,7 @@
         <v>21.75</v>
       </c>
       <c r="G336" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -13730,7 +13733,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G337" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -13756,7 +13759,7 @@
         <v>21.7199993133545</v>
       </c>
       <c r="G338" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -13782,7 +13785,7 @@
         <v>21.7299995422363</v>
       </c>
       <c r="G339" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -13808,7 +13811,7 @@
         <v>22.1700000762939</v>
       </c>
       <c r="G340" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -13834,7 +13837,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G341" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -13860,7 +13863,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G342" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -13886,7 +13889,7 @@
         <v>22.0699996948242</v>
       </c>
       <c r="G343" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -13912,7 +13915,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G344" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -13938,7 +13941,7 @@
         <v>22.2299995422363</v>
       </c>
       <c r="G345" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -13964,7 +13967,7 @@
         <v>22.8099994659424</v>
       </c>
       <c r="G346" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -13990,7 +13993,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G347" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -14016,7 +14019,7 @@
         <v>22.3700008392334</v>
       </c>
       <c r="G348" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -14042,7 +14045,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G349" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -14068,7 +14071,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G350" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -14094,7 +14097,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G351" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -14120,7 +14123,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G352" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -14146,7 +14149,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G353" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -14172,7 +14175,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G354" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -14198,7 +14201,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G355" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -14224,7 +14227,7 @@
         <v>22.2399997711182</v>
       </c>
       <c r="G356" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -14250,7 +14253,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G357" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -14276,7 +14279,7 @@
         <v>22</v>
       </c>
       <c r="G358" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -14302,7 +14305,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G359" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -14328,7 +14331,7 @@
         <v>21.5100002288818</v>
       </c>
       <c r="G360" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -14354,7 +14357,7 @@
         <v>21.7900009155273</v>
       </c>
       <c r="G361" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -14380,7 +14383,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G362" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -14406,7 +14409,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G363" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -14432,7 +14435,7 @@
         <v>21.9099998474121</v>
       </c>
       <c r="G364" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -14458,7 +14461,7 @@
         <v>21.6900005340576</v>
       </c>
       <c r="G365" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -14484,7 +14487,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G366" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -14510,7 +14513,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G367" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -14536,7 +14539,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G368" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -14562,7 +14565,7 @@
         <v>21.9300003051758</v>
       </c>
       <c r="G369" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -14588,7 +14591,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G370" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -14614,7 +14617,7 @@
         <v>21.6200008392334</v>
       </c>
       <c r="G371" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -14640,7 +14643,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G372" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -14666,7 +14669,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G373" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -14692,7 +14695,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G374" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -14718,7 +14721,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G375" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -14744,7 +14747,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G376" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -14770,7 +14773,7 @@
         <v>21.3899993896484</v>
       </c>
       <c r="G377" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -14796,7 +14799,7 @@
         <v>21.4300003051758</v>
       </c>
       <c r="G378" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -14822,7 +14825,7 @@
         <v>21.5</v>
       </c>
       <c r="G379" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -14848,7 +14851,7 @@
         <v>21.6100006103516</v>
       </c>
       <c r="G380" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -14874,7 +14877,7 @@
         <v>21.5100002288818</v>
       </c>
       <c r="G381" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -14900,7 +14903,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G382" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -14926,7 +14929,7 @@
         <v>20.9300003051758</v>
       </c>
       <c r="G383" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -14952,7 +14955,7 @@
         <v>20.8099994659424</v>
       </c>
       <c r="G384" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -14978,7 +14981,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G385" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -15004,7 +15007,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G386" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -15030,7 +15033,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G387" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -15056,7 +15059,7 @@
         <v>20.6100006103516</v>
       </c>
       <c r="G388" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -15082,7 +15085,7 @@
         <v>21</v>
       </c>
       <c r="G389" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -15108,7 +15111,7 @@
         <v>20.7900009155273</v>
       </c>
       <c r="G390" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -15134,7 +15137,7 @@
         <v>20.6900005340576</v>
       </c>
       <c r="G391" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -15160,7 +15163,7 @@
         <v>21</v>
       </c>
       <c r="G392" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -15186,7 +15189,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G393" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -15212,7 +15215,7 @@
         <v>21.3299999237061</v>
       </c>
       <c r="G394" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -15238,7 +15241,7 @@
         <v>21.8500003814697</v>
       </c>
       <c r="G395" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -15264,7 +15267,7 @@
         <v>21.9300003051758</v>
       </c>
       <c r="G396" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -15290,7 +15293,7 @@
         <v>22</v>
       </c>
       <c r="G397" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -15316,7 +15319,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G398" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -15342,7 +15345,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G399" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -15368,7 +15371,7 @@
         <v>22.3600006103516</v>
       </c>
       <c r="G400" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -15394,7 +15397,7 @@
         <v>22.3600006103516</v>
       </c>
       <c r="G401" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -15420,7 +15423,7 @@
         <v>22.3700008392334</v>
       </c>
       <c r="G402" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -15446,7 +15449,7 @@
         <v>22.5</v>
       </c>
       <c r="G403" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -15472,7 +15475,7 @@
         <v>21.7700004577637</v>
       </c>
       <c r="G404" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -15498,7 +15501,7 @@
         <v>21.6200008392334</v>
       </c>
       <c r="G405" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -15524,7 +15527,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G406" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -15550,7 +15553,7 @@
         <v>21.6900005340576</v>
       </c>
       <c r="G407" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -15576,7 +15579,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G408" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -15602,7 +15605,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G409" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -15628,7 +15631,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G410" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -15654,7 +15657,7 @@
         <v>21.7700004577637</v>
       </c>
       <c r="G411" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -15680,7 +15683,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G412" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -15706,7 +15709,7 @@
         <v>21.4099998474121</v>
       </c>
       <c r="G413" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -15732,7 +15735,7 @@
         <v>21.3199996948242</v>
       </c>
       <c r="G414" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -15758,7 +15761,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G415" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -15784,7 +15787,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G416" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -15810,7 +15813,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G417" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -15836,7 +15839,7 @@
         <v>21.1900005340576</v>
       </c>
       <c r="G418" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -15862,7 +15865,7 @@
         <v>21.2099990844727</v>
       </c>
       <c r="G419" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -15888,7 +15891,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G420" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -15914,7 +15917,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G421" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -15940,7 +15943,7 @@
         <v>20.9899997711182</v>
       </c>
       <c r="G422" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -15966,7 +15969,7 @@
         <v>20.7700004577637</v>
       </c>
       <c r="G423" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -15992,7 +15995,7 @@
         <v>20.6499996185303</v>
       </c>
       <c r="G424" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -16018,7 +16021,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G425" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -16044,7 +16047,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G426" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -16070,7 +16073,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G427" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -16096,7 +16099,7 @@
         <v>21.2299995422363</v>
       </c>
       <c r="G428" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -16122,7 +16125,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G429" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -16148,7 +16151,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G430" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -16174,7 +16177,7 @@
         <v>21.4599990844727</v>
       </c>
       <c r="G431" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -16200,7 +16203,7 @@
         <v>21.5100002288818</v>
       </c>
       <c r="G432" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -16226,7 +16229,7 @@
         <v>21.9300003051758</v>
       </c>
       <c r="G433" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -16252,7 +16255,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G434" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -16278,7 +16281,7 @@
         <v>22.0499992370605</v>
       </c>
       <c r="G435" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -16304,7 +16307,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G436" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -16330,7 +16333,7 @@
         <v>22.3299999237061</v>
       </c>
       <c r="G437" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -16356,7 +16359,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G438" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -16382,7 +16385,7 @@
         <v>22</v>
       </c>
       <c r="G439" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -16408,7 +16411,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G440" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -16434,7 +16437,7 @@
         <v>22.0799999237061</v>
       </c>
       <c r="G441" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -16460,7 +16463,7 @@
         <v>22.0799999237061</v>
       </c>
       <c r="G442" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -16486,7 +16489,7 @@
         <v>22.0699996948242</v>
       </c>
       <c r="G443" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -16512,7 +16515,7 @@
         <v>22.0900001525879</v>
       </c>
       <c r="G444" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -16538,7 +16541,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G445" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -16564,7 +16567,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G446" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -16590,7 +16593,7 @@
         <v>22.3700008392334</v>
       </c>
       <c r="G447" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -16616,7 +16619,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G448" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -16642,7 +16645,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G449" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -16668,7 +16671,7 @@
         <v>22.4699993133545</v>
       </c>
       <c r="G450" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -16694,7 +16697,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G451" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -16720,7 +16723,7 @@
         <v>22.7099990844727</v>
       </c>
       <c r="G452" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -16746,7 +16749,7 @@
         <v>22.75</v>
       </c>
       <c r="G453" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -16772,7 +16775,7 @@
         <v>22.5900001525879</v>
       </c>
       <c r="G454" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -16798,7 +16801,7 @@
         <v>22.9200000762939</v>
       </c>
       <c r="G455" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -16824,7 +16827,7 @@
         <v>22.7299995422363</v>
       </c>
       <c r="G456" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -16850,7 +16853,7 @@
         <v>22.6900005340576</v>
       </c>
       <c r="G457" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -16876,7 +16879,7 @@
         <v>22.8899993896484</v>
       </c>
       <c r="G458" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -16902,7 +16905,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G459" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -16928,7 +16931,7 @@
         <v>23.3299999237061</v>
       </c>
       <c r="G460" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -16954,7 +16957,7 @@
         <v>22.7800006866455</v>
       </c>
       <c r="G461" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -16980,7 +16983,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G462" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -17006,7 +17009,7 @@
         <v>22.8700008392334</v>
       </c>
       <c r="G463" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -17032,7 +17035,7 @@
         <v>22.6599998474121</v>
       </c>
       <c r="G464" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -17058,7 +17061,7 @@
         <v>22.3899993896484</v>
       </c>
       <c r="G465" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -17084,7 +17087,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="G466" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -17110,7 +17113,7 @@
         <v>22.4500007629395</v>
       </c>
       <c r="G467" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -17136,7 +17139,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G468" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -17162,7 +17165,7 @@
         <v>22.1700000762939</v>
       </c>
       <c r="G469" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -17188,7 +17191,7 @@
         <v>21.9300003051758</v>
       </c>
       <c r="G470" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -17214,7 +17217,7 @@
         <v>22.0900001525879</v>
       </c>
       <c r="G471" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -17240,7 +17243,7 @@
         <v>22</v>
       </c>
       <c r="G472" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -17266,7 +17269,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G473" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -17292,7 +17295,7 @@
         <v>21.8400001525879</v>
       </c>
       <c r="G474" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -17318,7 +17321,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G475" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -17344,7 +17347,7 @@
         <v>21.4899997711182</v>
       </c>
       <c r="G476" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -17370,7 +17373,7 @@
         <v>21.3799991607666</v>
       </c>
       <c r="G477" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -17396,7 +17399,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G478" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -17422,7 +17425,7 @@
         <v>20.75</v>
       </c>
       <c r="G479" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -17448,7 +17451,7 @@
         <v>20.4699993133545</v>
       </c>
       <c r="G480" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -17474,7 +17477,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G481" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -17500,7 +17503,7 @@
         <v>21.3199996948242</v>
       </c>
       <c r="G482" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -17526,7 +17529,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G483" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -17552,7 +17555,7 @@
         <v>21.5</v>
       </c>
       <c r="G484" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -17578,7 +17581,7 @@
         <v>21.7700004577637</v>
       </c>
       <c r="G485" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -17604,7 +17607,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G486" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -17630,7 +17633,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G487" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -17656,7 +17659,7 @@
         <v>21.5100002288818</v>
       </c>
       <c r="G488" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -17682,7 +17685,7 @@
         <v>21.4099998474121</v>
       </c>
       <c r="G489" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -17708,7 +17711,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G490" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -17734,7 +17737,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G491" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -17760,7 +17763,7 @@
         <v>21.7099990844727</v>
       </c>
       <c r="G492" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -17786,7 +17789,7 @@
         <v>21.5</v>
       </c>
       <c r="G493" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -17812,7 +17815,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G494" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -17838,7 +17841,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G495" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -17864,7 +17867,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G496" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -17890,7 +17893,7 @@
         <v>21.8899993896484</v>
       </c>
       <c r="G497" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -17916,7 +17919,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G498" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -17942,7 +17945,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G499" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -17968,7 +17971,7 @@
         <v>21.3899993896484</v>
       </c>
       <c r="G500" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -17994,7 +17997,7 @@
         <v>21.3799991607666</v>
       </c>
       <c r="G501" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -18020,7 +18023,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G502" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -18046,7 +18049,7 @@
         <v>21.2399997711182</v>
       </c>
       <c r="G503" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -18072,7 +18075,7 @@
         <v>21</v>
       </c>
       <c r="G504" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -18098,7 +18101,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G505" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -18124,7 +18127,7 @@
         <v>21.2900009155273</v>
       </c>
       <c r="G506" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -18150,7 +18153,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G507" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -18176,7 +18179,7 @@
         <v>21.2800006866455</v>
       </c>
       <c r="G508" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -18202,7 +18205,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G509" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -18228,7 +18231,7 @@
         <v>21.6700000762939</v>
       </c>
       <c r="G510" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -18254,7 +18257,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G511" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -18280,7 +18283,7 @@
         <v>21.5</v>
       </c>
       <c r="G512" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -18306,7 +18309,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G513" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -18332,7 +18335,7 @@
         <v>21.7199993133545</v>
       </c>
       <c r="G514" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -18358,7 +18361,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G515" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -18384,7 +18387,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G516" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -18410,7 +18413,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G517" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -18436,7 +18439,7 @@
         <v>21.2199993133545</v>
       </c>
       <c r="G518" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -18462,7 +18465,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G519" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -18488,7 +18491,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G520" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -18514,7 +18517,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G521" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -18540,7 +18543,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G522" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -18566,7 +18569,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G523" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -18592,7 +18595,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G524" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -18618,7 +18621,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G525" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -18644,7 +18647,7 @@
         <v>22.6200008392334</v>
       </c>
       <c r="G526" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -18670,7 +18673,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G527" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -18696,7 +18699,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G528" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -18722,7 +18725,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G529" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -18748,7 +18751,7 @@
         <v>22.8199996948242</v>
       </c>
       <c r="G530" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -18774,7 +18777,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G531" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -18800,7 +18803,7 @@
         <v>22.3199996948242</v>
       </c>
       <c r="G532" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -18826,7 +18829,7 @@
         <v>22.2800006866455</v>
       </c>
       <c r="G533" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -18852,7 +18855,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G534" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -18878,7 +18881,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G535" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -18904,7 +18907,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G536" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -18930,7 +18933,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G537" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -18956,7 +18959,7 @@
         <v>21.9599990844727</v>
       </c>
       <c r="G538" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -18982,7 +18985,7 @@
         <v>21.1399993896484</v>
       </c>
       <c r="G539" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -19008,7 +19011,7 @@
         <v>21</v>
       </c>
       <c r="G540" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -19034,7 +19037,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G541" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -19060,7 +19063,7 @@
         <v>21</v>
       </c>
       <c r="G542" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -19086,7 +19089,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G543" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -19112,7 +19115,7 @@
         <v>21</v>
       </c>
       <c r="G544" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -19138,7 +19141,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G545" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -19164,7 +19167,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G546" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -19190,7 +19193,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G547" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -19216,7 +19219,7 @@
         <v>21.4799995422363</v>
       </c>
       <c r="G548" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -19242,7 +19245,7 @@
         <v>21.4599990844727</v>
       </c>
       <c r="G549" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -19268,7 +19271,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G550" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -19294,7 +19297,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G551" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -19320,7 +19323,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G552" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -19346,7 +19349,7 @@
         <v>21.8600006103516</v>
       </c>
       <c r="G553" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -19372,7 +19375,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G554" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -19398,7 +19401,7 @@
         <v>21.1399993896484</v>
       </c>
       <c r="G555" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -19424,7 +19427,7 @@
         <v>21</v>
       </c>
       <c r="G556" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -19450,7 +19453,7 @@
         <v>21.0400009155273</v>
       </c>
       <c r="G557" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -19476,7 +19479,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G558" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -19502,7 +19505,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G559" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -19528,7 +19531,7 @@
         <v>22.3600006103516</v>
       </c>
       <c r="G560" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -19554,7 +19557,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G561" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -19580,7 +19583,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G562" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -19606,7 +19609,7 @@
         <v>22.5</v>
       </c>
       <c r="G563" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -19632,7 +19635,7 @@
         <v>23.8600006103516</v>
       </c>
       <c r="G564" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -19658,7 +19661,7 @@
         <v>23.7800006866455</v>
       </c>
       <c r="G565" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -19684,7 +19687,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G566" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -19710,7 +19713,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G567" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -19736,7 +19739,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G568" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -19762,7 +19765,7 @@
         <v>24.4599990844727</v>
       </c>
       <c r="G569" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -19788,7 +19791,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G570" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -19814,7 +19817,7 @@
         <v>24.1599998474121</v>
       </c>
       <c r="G571" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -19840,7 +19843,7 @@
         <v>24.1599998474121</v>
       </c>
       <c r="G572" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -19866,7 +19869,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G573" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -19892,7 +19895,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G574" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -19918,7 +19921,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G575" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -19944,7 +19947,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G576" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -19970,7 +19973,7 @@
         <v>25.1399993896484</v>
       </c>
       <c r="G577" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -19996,7 +19999,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G578" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -20022,7 +20025,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G579" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -20048,7 +20051,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G580" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -20074,7 +20077,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G581" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -20100,7 +20103,7 @@
         <v>25</v>
       </c>
       <c r="G582" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -20126,7 +20129,7 @@
         <v>25.1399993896484</v>
       </c>
       <c r="G583" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -20152,7 +20155,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G584" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -20178,7 +20181,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G585" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -20204,7 +20207,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G586" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -20230,7 +20233,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G587" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -20256,7 +20259,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G588" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -20282,7 +20285,7 @@
         <v>24.8799991607666</v>
       </c>
       <c r="G589" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -20308,7 +20311,7 @@
         <v>24.8400001525879</v>
       </c>
       <c r="G590" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -20334,7 +20337,7 @@
         <v>24.8799991607666</v>
       </c>
       <c r="G591" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -20360,7 +20363,7 @@
         <v>24.9200000762939</v>
       </c>
       <c r="G592" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -20386,7 +20389,7 @@
         <v>24.8799991607666</v>
       </c>
       <c r="G593" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -20412,7 +20415,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G594" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -20438,7 +20441,7 @@
         <v>25.2600002288818</v>
       </c>
       <c r="G595" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -20464,7 +20467,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G596" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -20490,7 +20493,7 @@
         <v>25.3400001525879</v>
       </c>
       <c r="G597" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -20516,7 +20519,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G598" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -20542,7 +20545,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G599" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -20568,7 +20571,7 @@
         <v>25.1599998474121</v>
       </c>
       <c r="G600" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -20594,7 +20597,7 @@
         <v>25.1599998474121</v>
       </c>
       <c r="G601" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -20620,7 +20623,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G602" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -20646,7 +20649,7 @@
         <v>25.3600006103516</v>
       </c>
       <c r="G603" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -20672,7 +20675,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G604" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -20698,7 +20701,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G605" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -20724,7 +20727,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G606" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -20750,7 +20753,7 @@
         <v>23.4599990844727</v>
       </c>
       <c r="G607" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -20776,7 +20779,7 @@
         <v>23.7399997711182</v>
       </c>
       <c r="G608" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -20802,7 +20805,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G609" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -20828,7 +20831,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G610" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -20854,7 +20857,7 @@
         <v>23.3799991607666</v>
       </c>
       <c r="G611" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -20880,7 +20883,7 @@
         <v>23.3199996948242</v>
       </c>
       <c r="G612" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -20906,7 +20909,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G613" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -20932,7 +20935,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G614" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -20958,7 +20961,7 @@
         <v>23</v>
       </c>
       <c r="G615" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -20984,7 +20987,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G616" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -21010,7 +21013,7 @@
         <v>23.3199996948242</v>
       </c>
       <c r="G617" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -21036,7 +21039,7 @@
         <v>23.1800003051758</v>
       </c>
       <c r="G618" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -21062,7 +21065,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G619" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -21088,7 +21091,7 @@
         <v>23.2399997711182</v>
       </c>
       <c r="G620" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -21114,7 +21117,7 @@
         <v>23.1599998474121</v>
       </c>
       <c r="G621" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -21140,7 +21143,7 @@
         <v>22.7399997711182</v>
       </c>
       <c r="G622" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -21166,7 +21169,7 @@
         <v>23.0799999237061</v>
       </c>
       <c r="G623" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -21192,7 +21195,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G624" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -21218,7 +21221,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G625" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -21244,7 +21247,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G626" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21270,7 +21273,7 @@
         <v>23.0599994659424</v>
       </c>
       <c r="G627" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -21296,7 +21299,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G628" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -21322,7 +21325,7 @@
         <v>23.0799999237061</v>
       </c>
       <c r="G629" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -21348,7 +21351,7 @@
         <v>22.9400005340576</v>
       </c>
       <c r="G630" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -21374,7 +21377,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G631" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -21400,7 +21403,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G632" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -21426,7 +21429,7 @@
         <v>22.3199996948242</v>
       </c>
       <c r="G633" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -21452,7 +21455,7 @@
         <v>22.1800003051758</v>
       </c>
       <c r="G634" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -21478,7 +21481,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G635" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -21504,7 +21507,7 @@
         <v>22.5</v>
       </c>
       <c r="G636" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -21530,7 +21533,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G637" t="s">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -21582,7 +21585,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G639" t="s">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -21634,7 +21637,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G641" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -21972,7 +21975,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G654" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -22050,7 +22053,7 @@
         <v>23.3199996948242</v>
       </c>
       <c r="G657" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -22076,7 +22079,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G658" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -23454,7 +23457,7 @@
         <v>23</v>
       </c>
       <c r="G711" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -70314,7 +70317,7 @@
     </row>
     <row r="2514">
       <c r="A2514" s="1" t="n">
-        <v>45979.6941782407</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2514" t="n">
         <v>250620</v>
@@ -70335,6 +70338,32 @@
         <v>1541</v>
       </c>
       <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>45980.6909953704</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>286594</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>8.46000003814697</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>8.27000045776367</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>8.39999961853027</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>8.44999980926514</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>1542</v>
+      </c>
+      <c r="H2515" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARR.MI.xlsx
+++ b/data/MARR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="1546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1547" uniqueCount="1547">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,61 +38,61 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4479503631592</t>
+    <t xml:space="preserve">13.4479513168335</t>
   </si>
   <si>
     <t xml:space="preserve">MARR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.289400100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1812982559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9939203262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9506788253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5903358459473</t>
+    <t xml:space="preserve">13.2894010543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1812992095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9939222335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9506778717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5903377532959</t>
   </si>
   <si>
     <t xml:space="preserve">12.6552000045776</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7344732284546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4389953613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4462003707886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9849615097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0858592987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6462430953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2155828475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8353681564331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6768188476562</t>
+    <t xml:space="preserve">12.7344741821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4389934539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4462013244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9849624633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0858583450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6462421417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2155818939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8353691101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6768207550049</t>
   </si>
   <si>
     <t xml:space="preserve">12.5615110397339</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5543041229248</t>
+    <t xml:space="preserve">12.5543031692505</t>
   </si>
   <si>
     <t xml:space="preserve">12.6407871246338</t>
@@ -104,13 +104,13 @@
     <t xml:space="preserve">12.9722995758057</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7777137756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3308916091919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5110645294189</t>
+    <t xml:space="preserve">12.7777156829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3308925628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5110635757446</t>
   </si>
   <si>
     <t xml:space="preserve">12.2948570251465</t>
@@ -119,64 +119,64 @@
     <t xml:space="preserve">11.4084177017212</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4516592025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8840665817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5885858535767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8912754058838</t>
+    <t xml:space="preserve">11.4516582489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8840684890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5885877609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8912744522095</t>
   </si>
   <si>
     <t xml:space="preserve">11.9273080825806</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0426177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2011680603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3957538604736</t>
+    <t xml:space="preserve">12.0426187515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2011690139771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3957548141479</t>
   </si>
   <si>
     <t xml:space="preserve">12.7056455612183</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6047496795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5759248733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9362678527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1596784591675</t>
+    <t xml:space="preserve">12.6047506332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5759239196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9362668991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1596775054932</t>
   </si>
   <si>
     <t xml:space="preserve">12.9434719085693</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0731945037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8858165740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5975456237793</t>
+    <t xml:space="preserve">13.0731964111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.885817527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5975437164307</t>
   </si>
   <si>
     <t xml:space="preserve">12.078652381897</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3597202301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6696119308472</t>
+    <t xml:space="preserve">12.3597192764282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6696128845215</t>
   </si>
   <si>
     <t xml:space="preserve">12.8137502670288</t>
@@ -185,10 +185,10 @@
     <t xml:space="preserve">12.6984405517578</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8714036941528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4534091949463</t>
+    <t xml:space="preserve">12.8714046478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4534072875977</t>
   </si>
   <si>
     <t xml:space="preserve">12.3453054428101</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">12.6840257644653</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7560949325562</t>
+    <t xml:space="preserve">12.7560968399048</t>
   </si>
   <si>
     <t xml:space="preserve">13.1524715423584</t>
@@ -206,70 +206,70 @@
     <t xml:space="preserve">13.2677793502808</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3326425552368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0804014205933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1885061264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2605743408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7073984146118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4911909103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.347056388855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.001127243042</t>
+    <t xml:space="preserve">13.3326416015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0804004669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1885051727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.260570526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7073974609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.491189956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3470554351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0011291503906</t>
   </si>
   <si>
     <t xml:space="preserve">12.9002313613892</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8281631469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7921285629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0587825775146</t>
+    <t xml:space="preserve">12.828164100647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7921304702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.058783531189</t>
   </si>
   <si>
     <t xml:space="preserve">13.1020231246948</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8065433502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2821931838989</t>
+    <t xml:space="preserve">12.8065423965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2821941375732</t>
   </si>
   <si>
     <t xml:space="preserve">13.1380567550659</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8425760269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8930234909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9074363708496</t>
+    <t xml:space="preserve">12.8425779342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8930253982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9074392318726</t>
   </si>
   <si>
     <t xml:space="preserve">13.0227479934692</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6624069213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8786125183105</t>
+    <t xml:space="preserve">12.6624059677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8786134719849</t>
   </si>
   <si>
     <t xml:space="preserve">12.6335792541504</t>
@@ -278,64 +278,64 @@
     <t xml:space="preserve">12.7488899230957</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0258760452271</t>
+    <t xml:space="preserve">13.0258750915527</t>
   </si>
   <si>
     <t xml:space="preserve">13.0183887481689</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2579431533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2504587173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4301261901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4825305938721</t>
+    <t xml:space="preserve">13.25794506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2504606246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4301271438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4825286865234</t>
   </si>
   <si>
     <t xml:space="preserve">13.3103494644165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2654314041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4750442504883</t>
+    <t xml:space="preserve">13.2654304504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.475043296814</t>
   </si>
   <si>
     <t xml:space="preserve">13.3702383041382</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2878894805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2729167938232</t>
+    <t xml:space="preserve">13.2878904342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2729177474976</t>
   </si>
   <si>
     <t xml:space="preserve">13.280403137207</t>
   </si>
   <si>
-    <t xml:space="preserve">12.801290512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8836364746094</t>
+    <t xml:space="preserve">12.8012914657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.883638381958</t>
   </si>
   <si>
     <t xml:space="preserve">12.6141386032104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3146934509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4494409561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8087768554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7938060760498</t>
+    <t xml:space="preserve">12.3146924972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.44944190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8087787628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7938051223755</t>
   </si>
   <si>
     <t xml:space="preserve">13.0782775878906</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">12.4419574737549</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7831754684448</t>
+    <t xml:space="preserve">11.7831773757935</t>
   </si>
   <si>
     <t xml:space="preserve">12.2847471237183</t>
@@ -353,25 +353,25 @@
     <t xml:space="preserve">12.7339153289795</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4226408004761</t>
+    <t xml:space="preserve">13.4226417541504</t>
   </si>
   <si>
     <t xml:space="preserve">13.5274457931519</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0558195114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4525861740112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3328065872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7595157623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7295703887939</t>
+    <t xml:space="preserve">13.0558204650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4525833129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3328056335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7595167160034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7295722961426</t>
   </si>
   <si>
     <t xml:space="preserve">13.7220849990845</t>
@@ -380,10 +380,10 @@
     <t xml:space="preserve">13.5349321365356</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4900178909302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7370595932007</t>
+    <t xml:space="preserve">13.4900169372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7370586395264</t>
   </si>
   <si>
     <t xml:space="preserve">14.0140438079834</t>
@@ -395,49 +395,49 @@
     <t xml:space="preserve">13.8493499755859</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1113653182983</t>
+    <t xml:space="preserve">14.1113634109497</t>
   </si>
   <si>
     <t xml:space="preserve">13.9766139984131</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0814180374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7445449829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9990730285645</t>
+    <t xml:space="preserve">14.0814189910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7445459365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9990739822388</t>
   </si>
   <si>
     <t xml:space="preserve">13.5049896240234</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6397371292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6621961593628</t>
+    <t xml:space="preserve">13.6397380828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6621971130371</t>
   </si>
   <si>
     <t xml:space="preserve">13.6097936630249</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3477811813354</t>
+    <t xml:space="preserve">13.3477773666382</t>
   </si>
   <si>
     <t xml:space="preserve">13.4151544570923</t>
   </si>
   <si>
-    <t xml:space="preserve">13.220513343811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0857629776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1007375717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0633068084717</t>
+    <t xml:space="preserve">13.2205152511597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0857639312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.100736618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0633058547974</t>
   </si>
   <si>
     <t xml:space="preserve">13.2354869842529</t>
@@ -449,34 +449,34 @@
     <t xml:space="preserve">12.9285554885864</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2055416107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1082239151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1980562210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1157093048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0109033584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9135828018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8611822128296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.943528175354</t>
+    <t xml:space="preserve">13.2055425643921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1082220077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1980543136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1157083511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0109014511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9135847091675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8611812591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9435272216797</t>
   </si>
   <si>
     <t xml:space="preserve">13.1905708312988</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4076681137085</t>
+    <t xml:space="preserve">13.4076690673828</t>
   </si>
   <si>
     <t xml:space="preserve">13.3552656173706</t>
@@ -485,82 +485,82 @@
     <t xml:space="preserve">13.2130279541016</t>
   </si>
   <si>
-    <t xml:space="preserve">13.340292930603</t>
+    <t xml:space="preserve">13.3402938842773</t>
   </si>
   <si>
     <t xml:space="preserve">12.9659862518311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8761529922485</t>
+    <t xml:space="preserve">12.8761539459229</t>
   </si>
   <si>
     <t xml:space="preserve">12.8312358856201</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9809579849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7638597488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7114582061768</t>
+    <t xml:space="preserve">12.9809598922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7638607025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7114572525024</t>
   </si>
   <si>
     <t xml:space="preserve">12.8686676025391</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7563753128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6815137863159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5767068862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5467643737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5317907333374</t>
+    <t xml:space="preserve">12.7563762664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6815128326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5767059326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5467624664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5317897796631</t>
   </si>
   <si>
     <t xml:space="preserve">12.5617351531982</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5542488098145</t>
+    <t xml:space="preserve">12.5542478561401</t>
   </si>
   <si>
     <t xml:space="preserve">12.4194984436035</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2772607803345</t>
+    <t xml:space="preserve">12.2772617340088</t>
   </si>
   <si>
     <t xml:space="preserve">12.4719009399414</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5018453598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3970403671265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9778156280518</t>
+    <t xml:space="preserve">12.5018472671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3970394134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9778165817261</t>
   </si>
   <si>
     <t xml:space="preserve">12.3596096038818</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4943599700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3820686340332</t>
+    <t xml:space="preserve">12.4943609237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3820695877075</t>
   </si>
   <si>
     <t xml:space="preserve">12.4045248031616</t>
   </si>
   <si>
-    <t xml:space="preserve">12.269775390625</t>
+    <t xml:space="preserve">12.2697744369507</t>
   </si>
   <si>
     <t xml:space="preserve">12.1649694442749</t>
@@ -572,7 +572,7 @@
     <t xml:space="preserve">12.3371505737305</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3221778869629</t>
+    <t xml:space="preserve">12.3221759796143</t>
   </si>
   <si>
     <t xml:space="preserve">12.72642993927</t>
@@ -584,127 +584,127 @@
     <t xml:space="preserve">12.7863178253174</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0932502746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9510135650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1306838989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9884452819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1381673812866</t>
+    <t xml:space="preserve">13.0932493209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9510126113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1306819915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9884462356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1381683349609</t>
   </si>
   <si>
     <t xml:space="preserve">13.1606254577637</t>
   </si>
   <si>
-    <t xml:space="preserve">13.183084487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1681137084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2279996871948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.00341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1755990982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4001808166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3852100372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8643207550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9167242050171</t>
+    <t xml:space="preserve">13.1830835342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1681127548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2280006408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0034170150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1755971908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4001817703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3852090835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8643226623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9167261123657</t>
   </si>
   <si>
     <t xml:space="preserve">13.5199594497681</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4450969696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3627519607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4600715637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5124731063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4376125335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8268918991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6247653961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8044357299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7819757461548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6996278762817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8418655395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6771697998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.856837272644</t>
+    <t xml:space="preserve">13.4450988769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3627500534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4600706100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5124750137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4376134872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8268909454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6247673034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8044338226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7819738388062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6996269226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8418626785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.677170753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8568353652954</t>
   </si>
   <si>
     <t xml:space="preserve">13.7670021057129</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5648765563965</t>
+    <t xml:space="preserve">13.5648794174194</t>
   </si>
   <si>
     <t xml:space="preserve">13.8942651748657</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3359508514404</t>
+    <t xml:space="preserve">14.3359479904175</t>
   </si>
   <si>
     <t xml:space="preserve">14.5605325698853</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5156173706055</t>
+    <t xml:space="preserve">14.5156164169312</t>
   </si>
   <si>
     <t xml:space="preserve">14.6952829360962</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9722709655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9348392486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.942325592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8225469589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2043390274048</t>
+    <t xml:space="preserve">14.9722700119019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9348402023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9423274993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.822548866272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2043409347534</t>
   </si>
   <si>
     <t xml:space="preserve">15.713397026062</t>
@@ -713,106 +713,106 @@
     <t xml:space="preserve">15.1369647979736</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1594266891479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2866907119751</t>
+    <t xml:space="preserve">15.1594228744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2866878509521</t>
   </si>
   <si>
     <t xml:space="preserve">15.3615493774414</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2267980575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3465747833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6834545135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7208824157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5337295532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588670730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1669120788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.196852684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5487012863159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4214401245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6011056900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6460237503052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7358560562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5861320495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9080381393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.42458152771</t>
+    <t xml:space="preserve">15.2267971038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3465766906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6834554672241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7208843231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.533730506897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4588689804077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1669082641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1968545913696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5487031936646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4214382171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6011085510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6460208892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.735857963562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5861339569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9080362319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4245777130127</t>
   </si>
   <si>
     <t xml:space="preserve">16.1251373291016</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6984252929688</t>
+    <t xml:space="preserve">15.6984243392944</t>
   </si>
   <si>
     <t xml:space="preserve">16.2823448181152</t>
   </si>
   <si>
-    <t xml:space="preserve">16.327262878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2598857879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.267370223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5967617034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7839183807373</t>
+    <t xml:space="preserve">16.3272609710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2598838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2673721313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5967597961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7839126586914</t>
   </si>
   <si>
     <t xml:space="preserve">16.6641368865967</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5219020843506</t>
+    <t xml:space="preserve">16.521900177002</t>
   </si>
   <si>
     <t xml:space="preserve">16.4470386505127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6416778564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0758743286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7988891601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7464847564697</t>
+    <t xml:space="preserve">16.6416797637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0758724212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7988872528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7464866638184</t>
   </si>
   <si>
     <t xml:space="preserve">16.8737506866455</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">16.9560966491699</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1058197021484</t>
+    <t xml:space="preserve">17.1058177947998</t>
   </si>
   <si>
     <t xml:space="preserve">16.3946380615234</t>
@@ -830,79 +830,79 @@
     <t xml:space="preserve">16.5069255828857</t>
   </si>
   <si>
-    <t xml:space="preserve">16.684757232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1950378417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1641120910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0094814300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7620697021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6306343078613</t>
+    <t xml:space="preserve">16.6847534179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1950397491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1641139984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0094776153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7620716094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6306324005127</t>
   </si>
   <si>
     <t xml:space="preserve">16.8471183776855</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0249462127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9398975372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7698020935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9940185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1254539489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9553604125977</t>
+    <t xml:space="preserve">17.0249443054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9398956298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7698040008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9940166473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1254558563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.955358505249</t>
   </si>
   <si>
     <t xml:space="preserve">16.5455856323242</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7156829833984</t>
+    <t xml:space="preserve">16.7156810760498</t>
   </si>
   <si>
     <t xml:space="preserve">16.8548488616943</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7466068267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0404071807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7311420440674</t>
+    <t xml:space="preserve">16.7466049194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0404109954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.731143951416</t>
   </si>
   <si>
     <t xml:space="preserve">16.5378532409668</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5687808990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6229038238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7079486846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7234115600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1822032928467</t>
+    <t xml:space="preserve">16.5687789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6229019165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.707950592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7234134674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.182201385498</t>
   </si>
   <si>
     <t xml:space="preserve">16.0894222259521</t>
@@ -911,37 +911,37 @@
     <t xml:space="preserve">16.0816898345947</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1590061187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9347925186157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2363243103027</t>
+    <t xml:space="preserve">16.159008026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9347887039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2363224029541</t>
   </si>
   <si>
     <t xml:space="preserve">16.0739593505859</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9966440200806</t>
+    <t xml:space="preserve">15.9966468811035</t>
   </si>
   <si>
     <t xml:space="preserve">16.3909549713135</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4914665222168</t>
+    <t xml:space="preserve">16.4914646148682</t>
   </si>
   <si>
     <t xml:space="preserve">16.8935070037842</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2414283752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0558700561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.28782081604</t>
+    <t xml:space="preserve">17.2414264678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.055871963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2878189086914</t>
   </si>
   <si>
     <t xml:space="preserve">17.2955513000488</t>
@@ -956,13 +956,13 @@
     <t xml:space="preserve">17.280086517334</t>
   </si>
   <si>
-    <t xml:space="preserve">16.700216293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.553316116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4837341308594</t>
+    <t xml:space="preserve">16.7002182006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5533180236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4837322235107</t>
   </si>
   <si>
     <t xml:space="preserve">16.7775344848633</t>
@@ -971,40 +971,40 @@
     <t xml:space="preserve">16.5146598815918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3832225799561</t>
+    <t xml:space="preserve">16.3832206726074</t>
   </si>
   <si>
     <t xml:space="preserve">16.3986835479736</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2749805450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2285900115967</t>
+    <t xml:space="preserve">16.2749786376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2285938262939</t>
   </si>
   <si>
     <t xml:space="preserve">16.0584964752197</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9657182693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9502544403076</t>
+    <t xml:space="preserve">15.9657173156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.950252532959</t>
   </si>
   <si>
     <t xml:space="preserve">16.0353012084961</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2827129364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4141483306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6074371337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5919761657715</t>
+    <t xml:space="preserve">16.2827110290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4141502380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6074390411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5919742584229</t>
   </si>
   <si>
     <t xml:space="preserve">16.932165145874</t>
@@ -1013,34 +1013,34 @@
     <t xml:space="preserve">17.0481395721436</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2646217346191</t>
+    <t xml:space="preserve">17.2646236419678</t>
   </si>
   <si>
     <t xml:space="preserve">16.9476280212402</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0713310241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0636024475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0790634155273</t>
+    <t xml:space="preserve">17.0713329315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0636005401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.079065322876</t>
   </si>
   <si>
     <t xml:space="preserve">17.2723541259766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3032817840576</t>
+    <t xml:space="preserve">17.303279876709</t>
   </si>
   <si>
     <t xml:space="preserve">17.3728637695312</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3187446594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.558422088623</t>
+    <t xml:space="preserve">17.3187465667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5584239959717</t>
   </si>
   <si>
     <t xml:space="preserve">17.5893497467041</t>
@@ -1049,52 +1049,52 @@
     <t xml:space="preserve">17.4656429290771</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7207870483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5738849639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5429592132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6975936889648</t>
+    <t xml:space="preserve">17.7207851409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5738868713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5429630279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6975917816162</t>
   </si>
   <si>
     <t xml:space="preserve">18.1073665618896</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0377826690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6125450134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6821308135986</t>
+    <t xml:space="preserve">18.0377807617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6125469207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.68212890625</t>
   </si>
   <si>
     <t xml:space="preserve">17.5197639465332</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3110122680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1099891662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3574047088623</t>
+    <t xml:space="preserve">17.311014175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.109992980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3574028015137</t>
   </si>
   <si>
     <t xml:space="preserve">17.1795749664307</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1409168243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0867958068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8857765197754</t>
+    <t xml:space="preserve">17.1409187316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0867977142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8857727050781</t>
   </si>
   <si>
     <t xml:space="preserve">16.6151695251465</t>
@@ -1109,22 +1109,22 @@
     <t xml:space="preserve">16.0430316925049</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8265495300293</t>
+    <t xml:space="preserve">15.826548576355</t>
   </si>
   <si>
     <t xml:space="preserve">15.9270601272583</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1976642608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6692924499512</t>
+    <t xml:space="preserve">16.1976661682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6692905426025</t>
   </si>
   <si>
     <t xml:space="preserve">16.8703117370605</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7852630615234</t>
+    <t xml:space="preserve">16.7852649688721</t>
   </si>
   <si>
     <t xml:space="preserve">16.9630928039551</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">16.8084602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9244327545166</t>
+    <t xml:space="preserve">16.9244289398193</t>
   </si>
   <si>
     <t xml:space="preserve">16.4218807220459</t>
@@ -1142,22 +1142,22 @@
     <t xml:space="preserve">16.0507640838623</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4605388641357</t>
+    <t xml:space="preserve">16.4605407714844</t>
   </si>
   <si>
     <t xml:space="preserve">16.4528064727783</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7543354034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6383666992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7929954528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4064159393311</t>
+    <t xml:space="preserve">16.7543411254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6383647918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7929973602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4064178466797</t>
   </si>
   <si>
     <t xml:space="preserve">17.33420753479</t>
@@ -1169,16 +1169,16 @@
     <t xml:space="preserve">17.4888401031494</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5506916046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6898612976074</t>
+    <t xml:space="preserve">17.5506935119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6898593902588</t>
   </si>
   <si>
     <t xml:space="preserve">17.4115219116211</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6434707641602</t>
+    <t xml:space="preserve">17.6434688568115</t>
   </si>
   <si>
     <t xml:space="preserve">17.256893157959</t>
@@ -1187,10 +1187,10 @@
     <t xml:space="preserve">17.2259654998779</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5043029785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4991970062256</t>
+    <t xml:space="preserve">17.504301071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4991989135742</t>
   </si>
   <si>
     <t xml:space="preserve">16.9785537719727</t>
@@ -1199,55 +1199,55 @@
     <t xml:space="preserve">16.3445644378662</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2981758117676</t>
+    <t xml:space="preserve">16.2981739044189</t>
   </si>
   <si>
     <t xml:space="preserve">16.9012393951416</t>
   </si>
   <si>
-    <t xml:space="preserve">16.653829574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2672500610352</t>
+    <t xml:space="preserve">16.6538276672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2672519683838</t>
   </si>
   <si>
     <t xml:space="preserve">16.3136386871338</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4269847869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4475555419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3857021331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8805255889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1433963775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0042285919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9114475250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6949672698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6795043945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7413539886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6640396118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7877445220947</t>
+    <t xml:space="preserve">17.4269866943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4475574493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.385705947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8805236816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1433982849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0042304992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9114513397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6949634552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6795024871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7413578033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6640377044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7877407073975</t>
   </si>
   <si>
     <t xml:space="preserve">19.2516384124756</t>
@@ -1256,7 +1256,7 @@
     <t xml:space="preserve">19.4371967315674</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3444175720215</t>
+    <t xml:space="preserve">19.3444213867188</t>
   </si>
   <si>
     <t xml:space="preserve">19.406270980835</t>
@@ -1265,31 +1265,31 @@
     <t xml:space="preserve">19.5609016418457</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3289566040039</t>
+    <t xml:space="preserve">19.3289546966553</t>
   </si>
   <si>
     <t xml:space="preserve">19.1743240356445</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1124725341797</t>
+    <t xml:space="preserve">19.1124706268311</t>
   </si>
   <si>
     <t xml:space="preserve">19.1588611602783</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2825660705566</t>
+    <t xml:space="preserve">19.2825679779053</t>
   </si>
   <si>
     <t xml:space="preserve">19.2361755371094</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2052516937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2671031951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5299758911133</t>
+    <t xml:space="preserve">19.205249786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2671051025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5299777984619</t>
   </si>
   <si>
     <t xml:space="preserve">19.638219833374</t>
@@ -1301,19 +1301,19 @@
     <t xml:space="preserve">19.4835891723633</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5145130157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4526615142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.607292175293</t>
+    <t xml:space="preserve">19.5145149230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4526596069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6072940826416</t>
   </si>
   <si>
     <t xml:space="preserve">18.1382904052734</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3547782897949</t>
+    <t xml:space="preserve">18.3547763824463</t>
   </si>
   <si>
     <t xml:space="preserve">18.0764389038086</t>
@@ -1322,13 +1322,13 @@
     <t xml:space="preserve">18.03005027771</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1737804412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9501991271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3654174804688</t>
+    <t xml:space="preserve">18.1737785339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9502010345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.365421295166</t>
   </si>
   <si>
     <t xml:space="preserve">18.2057189941406</t>
@@ -1346,10 +1346,10 @@
     <t xml:space="preserve">18.5570583343506</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4931774139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1578102111816</t>
+    <t xml:space="preserve">18.4931793212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.157808303833</t>
   </si>
   <si>
     <t xml:space="preserve">18.4292984008789</t>
@@ -1361,13 +1361,13 @@
     <t xml:space="preserve">18.6369075775146</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4133262634277</t>
+    <t xml:space="preserve">18.4133281707764</t>
   </si>
   <si>
     <t xml:space="preserve">18.461238861084</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3175086975098</t>
+    <t xml:space="preserve">18.3175067901611</t>
   </si>
   <si>
     <t xml:space="preserve">17.8064708709717</t>
@@ -1379,28 +1379,28 @@
     <t xml:space="preserve">17.7106533050537</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9182624816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9661731719971</t>
+    <t xml:space="preserve">17.9182605743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9661712646484</t>
   </si>
   <si>
     <t xml:space="preserve">17.8863201141357</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9981079101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3973598480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5251178741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4452686309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1479454040527</t>
+    <t xml:space="preserve">17.9981117248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3973617553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5251216888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4452667236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1479434967041</t>
   </si>
   <si>
     <t xml:space="preserve">19.1639137268066</t>
@@ -1412,19 +1412,19 @@
     <t xml:space="preserve">18.8604869842529</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7806358337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5730285644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.06809425354</t>
+    <t xml:space="preserve">18.7806377410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5730266571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0680961608887</t>
   </si>
   <si>
     <t xml:space="preserve">18.7646675109863</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4772071838379</t>
+    <t xml:space="preserve">18.4772052764893</t>
   </si>
   <si>
     <t xml:space="preserve">18.7007884979248</t>
@@ -1442,31 +1442,31 @@
     <t xml:space="preserve">19.2118244171143</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1319751739502</t>
+    <t xml:space="preserve">19.1319732666016</t>
   </si>
   <si>
     <t xml:space="preserve">19.0042152404785</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1160068511963</t>
+    <t xml:space="preserve">19.1160049438477</t>
   </si>
   <si>
     <t xml:space="preserve">19.0361557006836</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1798839569092</t>
+    <t xml:space="preserve">19.1798858642578</t>
   </si>
   <si>
     <t xml:space="preserve">19.323616027832</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3395862579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3076457977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7228622436523</t>
+    <t xml:space="preserve">19.3395843505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3076438903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.722864151001</t>
   </si>
   <si>
     <t xml:space="preserve">19.467342376709</t>
@@ -1475,16 +1475,16 @@
     <t xml:space="preserve">19.3874950408936</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5631618499756</t>
+    <t xml:space="preserve">19.5631637573242</t>
   </si>
   <si>
     <t xml:space="preserve">19.8825607299805</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3616600036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4415111541748</t>
+    <t xml:space="preserve">20.3616580963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4415092468262</t>
   </si>
   <si>
     <t xml:space="preserve">20.2658386230469</t>
@@ -1493,28 +1493,28 @@
     <t xml:space="preserve">20.7609100341797</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0962753295898</t>
+    <t xml:space="preserve">21.0962772369385</t>
   </si>
   <si>
     <t xml:space="preserve">20.8247871398926</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2498683929443</t>
+    <t xml:space="preserve">20.2498741149902</t>
   </si>
   <si>
     <t xml:space="preserve">20.4734477996826</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1540489196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1700210571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7548046112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5312213897705</t>
+    <t xml:space="preserve">20.1540508270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1700191497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7548027038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5312252044678</t>
   </si>
   <si>
     <t xml:space="preserve">19.4034633636475</t>
@@ -1523,13 +1523,13 @@
     <t xml:space="preserve">18.8125782012939</t>
   </si>
   <si>
-    <t xml:space="preserve">18.732723236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3813896179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2536315917969</t>
+    <t xml:space="preserve">18.7327251434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3813877105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2536296844482</t>
   </si>
   <si>
     <t xml:space="preserve">17.9342308044434</t>
@@ -1541,10 +1541,10 @@
     <t xml:space="preserve">18.9243679046631</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7486972808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1258697509766</t>
+    <t xml:space="preserve">18.7486953735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1258716583252</t>
   </si>
   <si>
     <t xml:space="preserve">17.7905006408691</t>
@@ -1556,13 +1556,13 @@
     <t xml:space="preserve">17.1357326507568</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2155857086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9760360717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.550952911377</t>
+    <t xml:space="preserve">17.2155818939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9760341644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5509510040283</t>
   </si>
   <si>
     <t xml:space="preserve">16.8961849212646</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">17.0718536376953</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9281253814697</t>
+    <t xml:space="preserve">16.9281272888184</t>
   </si>
   <si>
     <t xml:space="preserve">16.8323059082031</t>
@@ -1580,10 +1580,10 @@
     <t xml:space="preserve">17.0558853149414</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1836452484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4551315307617</t>
+    <t xml:space="preserve">17.1836433410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4551334381104</t>
   </si>
   <si>
     <t xml:space="preserve">16.8163356781006</t>
@@ -1592,52 +1592,52 @@
     <t xml:space="preserve">16.3532066345215</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9858999252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0976886749268</t>
+    <t xml:space="preserve">15.9859008789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0976905822754</t>
   </si>
   <si>
     <t xml:space="preserve">16.1136589050293</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4269504547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3311328887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6505317687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4748611450195</t>
+    <t xml:space="preserve">15.4269514083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3311319351196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6505289077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4748601913452</t>
   </si>
   <si>
     <t xml:space="preserve">15.4429235458374</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7703065872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8421688079834</t>
+    <t xml:space="preserve">15.7703056335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.842170715332</t>
   </si>
   <si>
     <t xml:space="preserve">15.7383651733398</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4490280151367</t>
+    <t xml:space="preserve">16.4490261077881</t>
   </si>
   <si>
     <t xml:space="preserve">16.2733573913574</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1615676879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3212699890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4809665679932</t>
+    <t xml:space="preserve">16.1615695953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3212661743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4809646606445</t>
   </si>
   <si>
     <t xml:space="preserve">16.6246948242188</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">16.7684268951416</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1676750183105</t>
+    <t xml:space="preserve">17.1676731109619</t>
   </si>
   <si>
     <t xml:space="preserve">17.3433418273926</t>
@@ -1655,7 +1655,7 @@
     <t xml:space="preserve">17.2794628143311</t>
   </si>
   <si>
-    <t xml:space="preserve">16.944091796875</t>
+    <t xml:space="preserve">16.9440956115723</t>
   </si>
   <si>
     <t xml:space="preserve">17.0079746246338</t>
@@ -1664,40 +1664,40 @@
     <t xml:space="preserve">16.6406669616699</t>
   </si>
   <si>
-    <t xml:space="preserve">16.241418838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5608177185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7045459747314</t>
+    <t xml:space="preserve">16.2414169311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5608158111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7045478820801</t>
   </si>
   <si>
     <t xml:space="preserve">16.8482761383057</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3752841949463</t>
+    <t xml:space="preserve">17.3752822875977</t>
   </si>
   <si>
     <t xml:space="preserve">17.1037940979004</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8802165985107</t>
+    <t xml:space="preserve">16.8802146911621</t>
   </si>
   <si>
     <t xml:space="preserve">16.9121551513672</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8642463684082</t>
+    <t xml:space="preserve">16.8642482757568</t>
   </si>
   <si>
     <t xml:space="preserve">16.7205142974854</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6885757446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6087245941162</t>
+    <t xml:space="preserve">16.6885738372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6087265014648</t>
   </si>
   <si>
     <t xml:space="preserve">16.7364845275879</t>
@@ -1706,10 +1706,10 @@
     <t xml:space="preserve">16.3052959442139</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8980627059937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.193510055542</t>
+    <t xml:space="preserve">15.8980646133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1935081481934</t>
   </si>
   <si>
     <t xml:space="preserve">16.2094764709473</t>
@@ -1721,10 +1721,10 @@
     <t xml:space="preserve">16.28932762146</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2573871612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2254486083984</t>
+    <t xml:space="preserve">16.2573890686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2254467010498</t>
   </si>
   <si>
     <t xml:space="preserve">15.9140338897705</t>
@@ -1739,19 +1739,19 @@
     <t xml:space="preserve">16.7843971252441</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5767860412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.369176864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1775398254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4889526367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2494010925293</t>
+    <t xml:space="preserve">16.5767879486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3691787719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1775360107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4889507293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2494029998779</t>
   </si>
   <si>
     <t xml:space="preserve">16.3292541503906</t>
@@ -1760,25 +1760,25 @@
     <t xml:space="preserve">16.4091014862061</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1695537567139</t>
+    <t xml:space="preserve">16.1695518493652</t>
   </si>
   <si>
     <t xml:space="preserve">16.0497779846191</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5687999725342</t>
+    <t xml:space="preserve">16.5688018798828</t>
   </si>
   <si>
     <t xml:space="preserve">16.6486511230469</t>
   </si>
   <si>
-    <t xml:space="preserve">17.287446975708</t>
+    <t xml:space="preserve">17.2874488830566</t>
   </si>
   <si>
     <t xml:space="preserve">17.0878238677979</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0479011535645</t>
+    <t xml:space="preserve">17.0478973388672</t>
   </si>
   <si>
     <t xml:space="preserve">16.808349609375</t>
@@ -1787,43 +1787,43 @@
     <t xml:space="preserve">16.9680500030518</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7285022735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8882007598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1277503967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8793487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.045238494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9208221435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7964038848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2111301422119</t>
+    <t xml:space="preserve">16.7285003662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8881988525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1277523040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8793506622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0452404022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9208240509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7964019775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2111320495605</t>
   </si>
   <si>
     <t xml:space="preserve">17.1281852722168</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1696605682373</t>
+    <t xml:space="preserve">17.1696586608887</t>
   </si>
   <si>
     <t xml:space="preserve">17.418493270874</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3770217895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4599647521973</t>
+    <t xml:space="preserve">17.3770198822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4599666595459</t>
   </si>
   <si>
     <t xml:space="preserve">17.294075012207</t>
@@ -1835,46 +1835,46 @@
     <t xml:space="preserve">16.7549324035645</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6305141448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3402061462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4895038604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5392742156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7088031768799</t>
+    <t xml:space="preserve">16.6305122375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3402080535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4895057678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5392761230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7088012695312</t>
   </si>
   <si>
     <t xml:space="preserve">17.667329788208</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5014381408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.542911529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2526016235352</t>
+    <t xml:space="preserve">17.5014400482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5429096221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2526035308838</t>
   </si>
   <si>
     <t xml:space="preserve">16.7134590148926</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4231510162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.373384475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2406692504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1743144989014</t>
+    <t xml:space="preserve">16.4231491088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3733825683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2406711578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.17431640625</t>
   </si>
   <si>
     <t xml:space="preserve">16.2738513946533</t>
@@ -1889,46 +1889,46 @@
     <t xml:space="preserve">15.8591241836548</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7264137268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7927684783936</t>
+    <t xml:space="preserve">15.7264108657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7927675247192</t>
   </si>
   <si>
     <t xml:space="preserve">16.0747814178467</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5273418426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4278078079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6600561141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.178973197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3614511489868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6932344436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6102876663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4609861373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4443988800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3780403137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2950954437256</t>
+    <t xml:space="preserve">15.5273427963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.427809715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6600542068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1789722442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3614530563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6932334899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6102886199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4609880447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4443998336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.378041267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2950983047485</t>
   </si>
   <si>
     <t xml:space="preserve">15.925479888916</t>
@@ -1937,25 +1937,25 @@
     <t xml:space="preserve">16.2904376983643</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3899745941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4397411346436</t>
+    <t xml:space="preserve">16.3899726867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4397392272949</t>
   </si>
   <si>
     <t xml:space="preserve">16.6719875335693</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9576358795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0867137908936</t>
+    <t xml:space="preserve">17.9576377868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0867118835449</t>
   </si>
   <si>
     <t xml:space="preserve">17.3355484008789</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8378753662109</t>
+    <t xml:space="preserve">16.8378734588623</t>
   </si>
   <si>
     <t xml:space="preserve">16.5890407562256</t>
@@ -1967,40 +1967,40 @@
     <t xml:space="preserve">15.8757133483887</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9088907241821</t>
+    <t xml:space="preserve">15.9088916778564</t>
   </si>
   <si>
     <t xml:space="preserve">16.1577243804932</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1411361694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4729194641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7595901489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6766452789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5936985015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4775762557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7429990768433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7098236083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8425350189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3567962646484</t>
+    <t xml:space="preserve">16.1411380767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.47292137146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7595891952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.676643371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5936994552612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.477575302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7430009841919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7098226547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8425340652466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3567924499512</t>
   </si>
   <si>
     <t xml:space="preserve">16.3236179351807</t>
@@ -2009,52 +2009,52 @@
     <t xml:space="preserve">15.975248336792</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5843830108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0037670135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2240829467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0084247589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1909046173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5558624267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.532000541687</t>
+    <t xml:space="preserve">17.5843849182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0037689208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2240810394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0084266662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1909065246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5558605194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5320014953613</t>
   </si>
   <si>
     <t xml:space="preserve">14.7974252700806</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1836309432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.93479347229</t>
+    <t xml:space="preserve">14.183629989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9347944259644</t>
   </si>
   <si>
     <t xml:space="preserve">13.6361923217773</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4371252059937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2712326049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3873567581177</t>
+    <t xml:space="preserve">13.4371242523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2712335586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3873558044434</t>
   </si>
   <si>
     <t xml:space="preserve">11.7616310119629</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9606990814209</t>
+    <t xml:space="preserve">11.9607000350952</t>
   </si>
   <si>
     <t xml:space="preserve">12.4251909255981</t>
@@ -2066,7 +2066,7 @@
     <t xml:space="preserve">11.4796171188354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1690816879272</t>
+    <t xml:space="preserve">10.1690826416016</t>
   </si>
   <si>
     <t xml:space="preserve">10.3681507110596</t>
@@ -2075,46 +2075,46 @@
     <t xml:space="preserve">9.95342445373535</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3183832168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8777532577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4417810440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8565082550049</t>
+    <t xml:space="preserve">10.3183822631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8777542114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.441780090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8565073013306</t>
   </si>
   <si>
     <t xml:space="preserve">12.1763563156128</t>
   </si>
   <si>
-    <t xml:space="preserve">12.29248046875</t>
+    <t xml:space="preserve">12.2924785614014</t>
   </si>
   <si>
     <t xml:space="preserve">11.2141933441162</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9155902862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6667537689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.202260017395</t>
+    <t xml:space="preserve">10.9155893325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6667547225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2022609710693</t>
   </si>
   <si>
     <t xml:space="preserve">10.4510955810547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5174512863159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5340404510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4013299942017</t>
+    <t xml:space="preserve">10.5174531936646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5340414047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4013290405273</t>
   </si>
   <si>
     <t xml:space="preserve">10.1524934768677</t>
@@ -2123,22 +2123,22 @@
     <t xml:space="preserve">10.0529584884644</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97001361846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4676847457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6999311447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3017950057983</t>
+    <t xml:space="preserve">9.97001457214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4676856994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6999320983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.301794052124</t>
   </si>
   <si>
     <t xml:space="preserve">10.0695486068726</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2520275115967</t>
+    <t xml:space="preserve">10.2520265579224</t>
   </si>
   <si>
     <t xml:space="preserve">10.0031929016113</t>
@@ -2147,43 +2147,43 @@
     <t xml:space="preserve">10.0363702774048</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1193151473999</t>
+    <t xml:space="preserve">10.1193141937256</t>
   </si>
   <si>
     <t xml:space="preserve">9.92024707794189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4557523727417</t>
+    <t xml:space="preserve">9.45575332641602</t>
   </si>
   <si>
     <t xml:space="preserve">9.50552082061768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32304191589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1405611038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07420539855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6879997253418</t>
+    <t xml:space="preserve">9.32304096221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14056301116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07420444488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68800067901611</t>
   </si>
   <si>
     <t xml:space="preserve">10.1359043121338</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70458889007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38939666748047</t>
+    <t xml:space="preserve">9.70458984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38939762115479</t>
   </si>
   <si>
     <t xml:space="preserve">10.4345073699951</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2188501358032</t>
+    <t xml:space="preserve">10.2188491821289</t>
   </si>
   <si>
     <t xml:space="preserve">10.4179182052612</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">10.8990001678467</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9819459915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8160552978516</t>
+    <t xml:space="preserve">10.9819450378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8160543441772</t>
   </si>
   <si>
     <t xml:space="preserve">10.8824110031128</t>
@@ -2222,22 +2222,22 @@
     <t xml:space="preserve">10.9487676620483</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9653577804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2639598846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2805480957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1810131072998</t>
+    <t xml:space="preserve">10.9653568267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2639589309692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2805490493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1810150146484</t>
   </si>
   <si>
     <t xml:space="preserve">11.3303146362305</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2971382141113</t>
+    <t xml:space="preserve">11.297137260437</t>
   </si>
   <si>
     <t xml:space="preserve">11.0814790725708</t>
@@ -2246,7 +2246,7 @@
     <t xml:space="preserve">11.0151233673096</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0648908615112</t>
+    <t xml:space="preserve">11.0648899078369</t>
   </si>
   <si>
     <t xml:space="preserve">10.8326444625854</t>
@@ -2255,19 +2255,19 @@
     <t xml:space="preserve">10.849232673645</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5838098526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3847408294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6501655578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3515615463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2354393005371</t>
+    <t xml:space="preserve">10.5838088989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3847389221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.650164604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3515605926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2354383468628</t>
   </si>
   <si>
     <t xml:space="preserve">10.9321794509888</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">10.550630569458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.500862121582</t>
+    <t xml:space="preserve">10.5008640289307</t>
   </si>
   <si>
     <t xml:space="preserve">10.6169862747192</t>
@@ -2285,40 +2285,40 @@
     <t xml:space="preserve">10.4842748641968</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0197811126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3349733352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7828760147095</t>
+    <t xml:space="preserve">10.0197801589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3349723815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7828769683838</t>
   </si>
   <si>
     <t xml:space="preserve">10.6003971099854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1312475204468</t>
+    <t xml:space="preserve">11.1312465667725</t>
   </si>
   <si>
     <t xml:space="preserve">11.4132604598999</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4298486709595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2307806015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8658218383789</t>
+    <t xml:space="preserve">11.4298496246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2307815551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8658227920532</t>
   </si>
   <si>
     <t xml:space="preserve">11.3137273788452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3966722488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5127944946289</t>
+    <t xml:space="preserve">11.396671295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5127954483032</t>
   </si>
   <si>
     <t xml:space="preserve">11.8611650466919</t>
@@ -2327,22 +2327,22 @@
     <t xml:space="preserve">12.2095346450806</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9772882461548</t>
+    <t xml:space="preserve">11.9772891998291</t>
   </si>
   <si>
     <t xml:space="preserve">12.0602331161499</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2593002319336</t>
+    <t xml:space="preserve">12.2593011856079</t>
   </si>
   <si>
     <t xml:space="preserve">11.3800830841064</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1146574020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6335763931274</t>
+    <t xml:space="preserve">11.1146564483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6335754394531</t>
   </si>
   <si>
     <t xml:space="preserve">10.2686166763306</t>
@@ -2354,28 +2354,28 @@
     <t xml:space="preserve">9.62164402008057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65482330322266</t>
+    <t xml:space="preserve">9.65482234954834</t>
   </si>
   <si>
     <t xml:space="preserve">9.60505485534668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75435733795166</t>
+    <t xml:space="preserve">9.75435638427734</t>
   </si>
   <si>
     <t xml:space="preserve">12.491548538208</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0058088302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1929454803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8399171829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3209991455078</t>
+    <t xml:space="preserve">13.0058097839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1929445266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8399181365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3210000991821</t>
   </si>
   <si>
     <t xml:space="preserve">12.4086027145386</t>
@@ -2390,7 +2390,7 @@
     <t xml:space="preserve">12.9062747955322</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1053438186646</t>
+    <t xml:space="preserve">13.1053419113159</t>
   </si>
   <si>
     <t xml:space="preserve">12.9892196655273</t>
@@ -2399,31 +2399,31 @@
     <t xml:space="preserve">13.0721645355225</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0223979949951</t>
+    <t xml:space="preserve">13.0223970413208</t>
   </si>
   <si>
     <t xml:space="preserve">13.0887537002563</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0389881134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4583711624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5081367492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7403831481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3754253387451</t>
+    <t xml:space="preserve">13.038987159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4583702087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5081377029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7403841018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3754243850708</t>
   </si>
   <si>
     <t xml:space="preserve">12.4749593734741</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6574392318726</t>
+    <t xml:space="preserve">12.6574382781982</t>
   </si>
   <si>
     <t xml:space="preserve">12.9560403823853</t>
@@ -2435,13 +2435,13 @@
     <t xml:space="preserve">13.536657333374</t>
   </si>
   <si>
-    <t xml:space="preserve">13.984561920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3661098480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5817670822144</t>
+    <t xml:space="preserve">13.9845628738403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3661088943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5817699432373</t>
   </si>
   <si>
     <t xml:space="preserve">14.6978902816772</t>
@@ -2450,145 +2450,145 @@
     <t xml:space="preserve">14.7642459869385</t>
   </si>
   <si>
-    <t xml:space="preserve">14.631534576416</t>
+    <t xml:space="preserve">14.6315336227417</t>
   </si>
   <si>
     <t xml:space="preserve">14.1006851196289</t>
   </si>
   <si>
-    <t xml:space="preserve">14.432466506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.780837059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7476596832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4988222122192</t>
+    <t xml:space="preserve">14.4324655532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7808351516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7476568222046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4988212585449</t>
   </si>
   <si>
     <t xml:space="preserve">14.3495197296143</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2499885559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2333974838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.785493850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0177402496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0509185791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2831630706787</t>
+    <t xml:space="preserve">14.2499866485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2333965301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7854948043823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0177412033081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0509195327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2831649780273</t>
   </si>
   <si>
     <t xml:space="preserve">15.0462589263916</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9301376342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3946294784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3448638916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9918355941772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8969583511353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.979905128479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9135484695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9964942932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8259477615356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6434669494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0250148773193</t>
+    <t xml:space="preserve">14.930136680603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3946313858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3448619842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9918365478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8969573974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9799041748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9135465621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9964933395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8259439468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6434659957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0250129699707</t>
   </si>
   <si>
     <t xml:space="preserve">16.0913677215576</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0581932067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5605211257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0130825042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2619180679321</t>
+    <t xml:space="preserve">16.0581912994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5605220794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0130834579468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2619190216064</t>
   </si>
   <si>
     <t xml:space="preserve">15.228741645813</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1457958221436</t>
+    <t xml:space="preserve">15.1457948684692</t>
   </si>
   <si>
     <t xml:space="preserve">15.4941654205322</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6268787384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2121496200562</t>
+    <t xml:space="preserve">15.6268768310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2121505737305</t>
   </si>
   <si>
     <t xml:space="preserve">15.502459526062</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2702131271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2536220550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5439329147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5771102905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.850830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7181186676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7347040176392</t>
+    <t xml:space="preserve">15.2702121734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.253623008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5439319610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5771112442017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8508291244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7181177139282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7347059249878</t>
   </si>
   <si>
     <t xml:space="preserve">15.8840065002441</t>
   </si>
   <si>
-    <t xml:space="preserve">15.751293182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4361028671265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3982696533203</t>
+    <t xml:space="preserve">15.7512941360474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4361047744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3982677459717</t>
   </si>
   <si>
     <t xml:space="preserve">16.5807476043701</t>
@@ -2606,34 +2606,34 @@
     <t xml:space="preserve">16.4646244049072</t>
   </si>
   <si>
-    <t xml:space="preserve">16.622220993042</t>
+    <t xml:space="preserve">16.6222190856934</t>
   </si>
   <si>
     <t xml:space="preserve">16.8212871551514</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7051620483398</t>
+    <t xml:space="preserve">16.7051639556885</t>
   </si>
   <si>
     <t xml:space="preserve">16.9042320251465</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9374122619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1364822387695</t>
+    <t xml:space="preserve">16.9374103546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1364803314209</t>
   </si>
   <si>
     <t xml:space="preserve">17.3023700714111</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4350833892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4516716003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.219425201416</t>
+    <t xml:space="preserve">17.4350814819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4516735076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2194271087646</t>
   </si>
   <si>
     <t xml:space="preserve">16.7217540740967</t>
@@ -2642,7 +2642,7 @@
     <t xml:space="preserve">17.1530685424805</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0535335540771</t>
+    <t xml:space="preserve">17.0535354614258</t>
   </si>
   <si>
     <t xml:space="preserve">17.0369472503662</t>
@@ -2651,16 +2651,16 @@
     <t xml:space="preserve">16.8876457214355</t>
   </si>
   <si>
-    <t xml:space="preserve">16.771520614624</t>
+    <t xml:space="preserve">16.7715187072754</t>
   </si>
   <si>
     <t xml:space="preserve">16.8544654846191</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2028350830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1033039093018</t>
+    <t xml:space="preserve">17.2028369903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1033020019531</t>
   </si>
   <si>
     <t xml:space="preserve">17.1198902130127</t>
@@ -2675,16 +2675,16 @@
     <t xml:space="preserve">17.2691917419434</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8710536956787</t>
+    <t xml:space="preserve">16.8710556030273</t>
   </si>
   <si>
     <t xml:space="preserve">15.9171848297119</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2074928283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2323780059814</t>
+    <t xml:space="preserve">16.2074947357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2323741912842</t>
   </si>
   <si>
     <t xml:space="preserve">16.6056327819824</t>
@@ -2699,7 +2699,7 @@
     <t xml:space="preserve">18.1649990081787</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6175594329834</t>
+    <t xml:space="preserve">17.6175632476807</t>
   </si>
   <si>
     <t xml:space="preserve">18.0820541381836</t>
@@ -2720,10 +2720,10 @@
     <t xml:space="preserve">17.020357131958</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7881088256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9705905914307</t>
+    <t xml:space="preserve">16.7881107330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.970588684082</t>
   </si>
   <si>
     <t xml:space="preserve">17.1862468719482</t>
@@ -2732,28 +2732,28 @@
     <t xml:space="preserve">16.4065628051758</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4148578643799</t>
+    <t xml:space="preserve">16.4148559570312</t>
   </si>
   <si>
     <t xml:space="preserve">16.049898147583</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1660194396973</t>
+    <t xml:space="preserve">16.1660213470459</t>
   </si>
   <si>
     <t xml:space="preserve">17.5346164703369</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0701236724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2360153198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6839199066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4848518371582</t>
+    <t xml:space="preserve">17.070125579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2360134124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6839179992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4848499298096</t>
   </si>
   <si>
     <t xml:space="preserve">17.276216506958</t>
@@ -2762,28 +2762,28 @@
     <t xml:space="preserve">17.2424736022949</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3437004089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5461559295654</t>
+    <t xml:space="preserve">17.3437023162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5461578369141</t>
   </si>
   <si>
     <t xml:space="preserve">17.4111862182617</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3774452209473</t>
+    <t xml:space="preserve">17.3774433135986</t>
   </si>
   <si>
     <t xml:space="preserve">17.6642570495605</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4449310302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4618034362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.174991607666</t>
+    <t xml:space="preserve">17.4449291229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4618015289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1749897003174</t>
   </si>
   <si>
     <t xml:space="preserve">17.0400199890137</t>
@@ -2798,76 +2798,76 @@
     <t xml:space="preserve">16.8628711700439</t>
   </si>
   <si>
-    <t xml:space="preserve">17.090633392334</t>
+    <t xml:space="preserve">17.0906314849854</t>
   </si>
   <si>
     <t xml:space="preserve">16.8713054656982</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7532062530518</t>
+    <t xml:space="preserve">16.753210067749</t>
   </si>
   <si>
     <t xml:space="preserve">17.2087326049805</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2048873901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0952281951904</t>
+    <t xml:space="preserve">16.2048892974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0952243804932</t>
   </si>
   <si>
     <t xml:space="preserve">16.1458396911621</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7915410995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6903133392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8590259552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.411937713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5216007232666</t>
+    <t xml:space="preserve">15.7915420532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.690315246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8590278625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4119386672974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5216016769409</t>
   </si>
   <si>
     <t xml:space="preserve">15.0998182296753</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4203748703003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6059589385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5806512832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8337202072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0446128845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8758974075317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8927707672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0108680725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9349479675293</t>
+    <t xml:space="preserve">15.420373916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6059560775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5806503295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8337211608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0446109771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8758993148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8927698135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0108699798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.934947013855</t>
   </si>
   <si>
     <t xml:space="preserve">15.7662353515625</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7746734619141</t>
+    <t xml:space="preserve">15.7746715545654</t>
   </si>
   <si>
     <t xml:space="preserve">15.5131645202637</t>
@@ -2876,85 +2876,85 @@
     <t xml:space="preserve">15.4878597259521</t>
   </si>
   <si>
-    <t xml:space="preserve">15.184175491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.234790802002</t>
+    <t xml:space="preserve">15.1841745376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2347888946533</t>
   </si>
   <si>
     <t xml:space="preserve">15.3950662612915</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9433841705322</t>
+    <t xml:space="preserve">15.9433832168579</t>
   </si>
   <si>
     <t xml:space="preserve">16.112096786499</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2976818084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4495220184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5890846252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.698748588562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0361766815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9686918258667</t>
+    <t xml:space="preserve">16.297679901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4495239257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5890865325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.698751449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0361747741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9686908721924</t>
   </si>
   <si>
     <t xml:space="preserve">16.3145542144775</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9180784225464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0193023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5384731292725</t>
+    <t xml:space="preserve">15.9180774688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0193042755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5384721755981</t>
   </si>
   <si>
     <t xml:space="preserve">15.0154609680176</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1504316329956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5300369262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8168487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5637807846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8843355178833</t>
+    <t xml:space="preserve">15.1504306793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5300359725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8168497085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5637817382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8843336105347</t>
   </si>
   <si>
     <t xml:space="preserve">16.1374053955078</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8674621582031</t>
+    <t xml:space="preserve">15.8674631118774</t>
   </si>
   <si>
     <t xml:space="preserve">15.4541158676147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9732837677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0238981246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1673040390015</t>
+    <t xml:space="preserve">14.9732856750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0238962173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1673021316528</t>
   </si>
   <si>
     <t xml:space="preserve">15.4372444152832</t>
@@ -2963,34 +2963,34 @@
     <t xml:space="preserve">15.6312656402588</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4794216156006</t>
+    <t xml:space="preserve">15.4794225692749</t>
   </si>
   <si>
     <t xml:space="preserve">15.1588668823242</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7623920440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4080953598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7416791915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0537977218628</t>
+    <t xml:space="preserve">14.7623929977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4080934524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7416801452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0537986755371</t>
   </si>
   <si>
     <t xml:space="preserve">14.121283531189</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4295597076416</t>
+    <t xml:space="preserve">13.4295587539673</t>
   </si>
   <si>
     <t xml:space="preserve">13.5898370742798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1427478790283</t>
+    <t xml:space="preserve">13.142746925354</t>
   </si>
   <si>
     <t xml:space="preserve">12.7294006347656</t>
@@ -3017,13 +3017,13 @@
     <t xml:space="preserve">13.3198957443237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5307884216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8728065490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9318552017212</t>
+    <t xml:space="preserve">13.5307874679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8728055953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9318561553955</t>
   </si>
   <si>
     <t xml:space="preserve">12.7631425857544</t>
@@ -3050,10 +3050,10 @@
     <t xml:space="preserve">12.4678945541382</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1304693222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2823114395142</t>
+    <t xml:space="preserve">12.1304683685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2823104858398</t>
   </si>
   <si>
     <t xml:space="preserve">12.3497953414917</t>
@@ -3065,40 +3065,40 @@
     <t xml:space="preserve">12.5859937667847</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4126882553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3958168029785</t>
+    <t xml:space="preserve">13.4126873016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3958158493042</t>
   </si>
   <si>
     <t xml:space="preserve">13.4464302062988</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7838563919067</t>
+    <t xml:space="preserve">13.7838573455811</t>
   </si>
   <si>
     <t xml:space="preserve">13.3114604949951</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2271041870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9571619033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0752630233765</t>
+    <t xml:space="preserve">13.227105140686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9571628570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0752620697021</t>
   </si>
   <si>
     <t xml:space="preserve">12.7040939331055</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7715797424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4004096984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2148246765137</t>
+    <t xml:space="preserve">12.7715787887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.400408744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.214825630188</t>
   </si>
   <si>
     <t xml:space="preserve">12.0461120605469</t>
@@ -3107,22 +3107,22 @@
     <t xml:space="preserve">11.8773994445801</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1473398208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1642112731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2316970825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4510231018066</t>
+    <t xml:space="preserve">12.1473407745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1642122268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2316961288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.451024055481</t>
   </si>
   <si>
     <t xml:space="preserve">12.3835382461548</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2991819381714</t>
+    <t xml:space="preserve">12.2991809844971</t>
   </si>
   <si>
     <t xml:space="preserve">11.8267850875854</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">11.6749439239502</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6487464904785</t>
+    <t xml:space="preserve">11.6487474441528</t>
   </si>
   <si>
     <t xml:space="preserve">11.474102973938</t>
@@ -3143,7 +3143,7 @@
     <t xml:space="preserve">11.8932485580444</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9107131958008</t>
+    <t xml:space="preserve">11.9107122421265</t>
   </si>
   <si>
     <t xml:space="preserve">12.4346437454224</t>
@@ -3161,10 +3161,10 @@
     <t xml:space="preserve">12.1901426315308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3298578262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5568952560425</t>
+    <t xml:space="preserve">12.3298568725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5568943023682</t>
   </si>
   <si>
     <t xml:space="preserve">12.3123931884766</t>
@@ -3176,13 +3176,13 @@
     <t xml:space="preserve">11.4391746520996</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1946716308594</t>
+    <t xml:space="preserve">11.1946725845337</t>
   </si>
   <si>
     <t xml:space="preserve">11.7186040878296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5788888931274</t>
+    <t xml:space="preserve">11.5788898468018</t>
   </si>
   <si>
     <t xml:space="preserve">11.8408555984497</t>
@@ -3203,19 +3203,19 @@
     <t xml:space="preserve">11.49156665802</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2645292282104</t>
+    <t xml:space="preserve">11.2645301818848</t>
   </si>
   <si>
     <t xml:space="preserve">10.8104562759399</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0549583435059</t>
+    <t xml:space="preserve">11.0549573898315</t>
   </si>
   <si>
     <t xml:space="preserve">11.1772079467773</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3867797851562</t>
+    <t xml:space="preserve">11.3867807388306</t>
   </si>
   <si>
     <t xml:space="preserve">11.2470655441284</t>
@@ -3236,10 +3236,10 @@
     <t xml:space="preserve">11.4042453765869</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2296009063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6138181686401</t>
+    <t xml:space="preserve">11.2296018600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6138191223145</t>
   </si>
   <si>
     <t xml:space="preserve">11.7884616851807</t>
@@ -3254,25 +3254,25 @@
     <t xml:space="preserve">11.5614242553711</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4566383361816</t>
+    <t xml:space="preserve">11.456639289856</t>
   </si>
   <si>
     <t xml:space="preserve">11.5439605712891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4217090606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1073513031006</t>
+    <t xml:space="preserve">11.4217100143433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1073503494263</t>
   </si>
   <si>
     <t xml:space="preserve">11.0898857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7231340408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6882057189941</t>
+    <t xml:space="preserve">10.7231330871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6882047653198</t>
   </si>
   <si>
     <t xml:space="preserve">10.6707410812378</t>
@@ -3299,7 +3299,7 @@
     <t xml:space="preserve">9.90230846405029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81498527526855</t>
+    <t xml:space="preserve">9.81498622894287</t>
   </si>
   <si>
     <t xml:space="preserve">9.76259326934814</t>
@@ -3311,28 +3311,28 @@
     <t xml:space="preserve">10.1992034912109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29105567932129</t>
+    <t xml:space="preserve">9.29105472564697</t>
   </si>
   <si>
     <t xml:space="preserve">9.51809120178223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22119808197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25612640380859</t>
+    <t xml:space="preserve">9.2211971282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25612545013428</t>
   </si>
   <si>
     <t xml:space="preserve">9.0640172958374</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80205154418945</t>
+    <t xml:space="preserve">8.80205059051514</t>
   </si>
   <si>
     <t xml:space="preserve">8.8195161819458</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60121154785156</t>
+    <t xml:space="preserve">8.60121250152588</t>
   </si>
   <si>
     <t xml:space="preserve">8.48769283294678</t>
@@ -3341,19 +3341,19 @@
     <t xml:space="preserve">8.19079780578613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44403171539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46149444580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3392448425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56628227233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34797763824463</t>
+    <t xml:space="preserve">8.44403266906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4614953994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33924579620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56628322601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34797859191895</t>
   </si>
   <si>
     <t xml:space="preserve">8.54881763458252</t>
@@ -3380,13 +3380,13 @@
     <t xml:space="preserve">8.73219394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02908897399902</t>
+    <t xml:space="preserve">9.02908802032471</t>
   </si>
   <si>
     <t xml:space="preserve">9.09894561767578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41330528259277</t>
+    <t xml:space="preserve">9.41330432891846</t>
   </si>
   <si>
     <t xml:space="preserve">9.308518409729</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">9.55301952362061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62287712097168</t>
+    <t xml:space="preserve">9.622878074646</t>
   </si>
   <si>
     <t xml:space="preserve">9.91977214813232</t>
@@ -3413,7 +3413,7 @@
     <t xml:space="preserve">10.269061088562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65780639648438</t>
+    <t xml:space="preserve">9.65780735015869</t>
   </si>
   <si>
     <t xml:space="preserve">9.64034175872803</t>
@@ -3428,7 +3428,7 @@
     <t xml:space="preserve">10.0420236587524</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69273471832275</t>
+    <t xml:space="preserve">9.69273567199707</t>
   </si>
   <si>
     <t xml:space="preserve">9.93723678588867</t>
@@ -3437,7 +3437,7 @@
     <t xml:space="preserve">9.97216606140137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88484287261963</t>
+    <t xml:space="preserve">9.88484382629395</t>
   </si>
   <si>
     <t xml:space="preserve">9.8673791885376</t>
@@ -3446,7 +3446,7 @@
     <t xml:space="preserve">10.0944166183472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0769510269165</t>
+    <t xml:space="preserve">10.0769519805908</t>
   </si>
   <si>
     <t xml:space="preserve">9.79752159118652</t>
@@ -3470,16 +3470,16 @@
     <t xml:space="preserve">10.7405986785889</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7580633163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9152431488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0200290679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3518514633179</t>
+    <t xml:space="preserve">10.7580623626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9152421951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0200281143188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3518524169922</t>
   </si>
   <si>
     <t xml:space="preserve">11.0025644302368</t>
@@ -3488,7 +3488,7 @@
     <t xml:space="preserve">10.9676361083984</t>
   </si>
   <si>
-    <t xml:space="preserve">10.53102684021</t>
+    <t xml:space="preserve">10.5310258865356</t>
   </si>
   <si>
     <t xml:space="preserve">10.6183471679688</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">10.0245580673218</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84991359710693</t>
+    <t xml:space="preserve">9.84991455078125</t>
   </si>
   <si>
     <t xml:space="preserve">10.1118803024292</t>
@@ -3548,13 +3548,13 @@
     <t xml:space="preserve">11.8757839202881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.067892074585</t>
+    <t xml:space="preserve">12.0678911209106</t>
   </si>
   <si>
     <t xml:space="preserve">12.0329627990723</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4650440216064</t>
+    <t xml:space="preserve">13.4650430679321</t>
   </si>
   <si>
     <t xml:space="preserve">13.1681480407715</t>
@@ -3566,7 +3566,7 @@
     <t xml:space="preserve">12.8712530136108</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6442165374756</t>
+    <t xml:space="preserve">12.6442155838013</t>
   </si>
   <si>
     <t xml:space="preserve">12.9491128921509</t>
@@ -4650,6 +4650,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.81999969482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89000034332275</t>
   </si>
 </sst>
 </file>
@@ -70482,7 +70485,7 @@
     </row>
     <row r="2520">
       <c r="A2520" s="1" t="n">
-        <v>45987.6911458333</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B2520" t="n">
         <v>104239</v>
@@ -70503,6 +70506,32 @@
         <v>1545</v>
       </c>
       <c r="H2520" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" s="1" t="n">
+        <v>45988.6910185185</v>
+      </c>
+      <c r="B2521" t="n">
+        <v>66452</v>
+      </c>
+      <c r="C2521" t="n">
+        <v>8.90999984741211</v>
+      </c>
+      <c r="D2521" t="n">
+        <v>8.81999969482422</v>
+      </c>
+      <c r="E2521" t="n">
+        <v>8.81999969482422</v>
+      </c>
+      <c r="F2521" t="n">
+        <v>8.89000034332275</v>
+      </c>
+      <c r="G2521" t="s">
+        <v>1546</v>
+      </c>
+      <c r="H2521" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARR.MI.xlsx
+++ b/data/MARR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1550" uniqueCount="1550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1551" uniqueCount="1551">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4479513168335</t>
+    <t xml:space="preserve">13.4479503631592</t>
   </si>
   <si>
     <t xml:space="preserve">MARR.MI</t>
@@ -47,16 +47,16 @@
     <t xml:space="preserve">13.2894010543823</t>
   </si>
   <si>
-    <t xml:space="preserve">13.181300163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9939222335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9506778717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5903348922729</t>
+    <t xml:space="preserve">13.1812982559204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9939212799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9506788253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5903377532959</t>
   </si>
   <si>
     <t xml:space="preserve">12.6551990509033</t>
@@ -68,31 +68,31 @@
     <t xml:space="preserve">12.4389953613281</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4462003707886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9849643707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0858602523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6462440490723</t>
+    <t xml:space="preserve">12.4461994171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9849634170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.085862159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6462430953979</t>
   </si>
   <si>
     <t xml:space="preserve">12.2155838012695</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8353691101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6768198013306</t>
+    <t xml:space="preserve">12.8353681564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6768217086792</t>
   </si>
   <si>
     <t xml:space="preserve">12.5615119934082</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5543012619019</t>
+    <t xml:space="preserve">12.5543031692505</t>
   </si>
   <si>
     <t xml:space="preserve">12.6407852172852</t>
@@ -104,85 +104,85 @@
     <t xml:space="preserve">12.9723014831543</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7777137756348</t>
+    <t xml:space="preserve">12.7777156829834</t>
   </si>
   <si>
     <t xml:space="preserve">12.3308906555176</t>
   </si>
   <si>
-    <t xml:space="preserve">12.511061668396</t>
+    <t xml:space="preserve">12.5110626220703</t>
   </si>
   <si>
     <t xml:space="preserve">12.2948570251465</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4084177017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4516572952271</t>
+    <t xml:space="preserve">11.4084157943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4516592025757</t>
   </si>
   <si>
     <t xml:space="preserve">11.8840665817261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5885877609253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8912744522095</t>
+    <t xml:space="preserve">11.588586807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8912754058838</t>
   </si>
   <si>
     <t xml:space="preserve">11.9273080825806</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0426187515259</t>
+    <t xml:space="preserve">12.0426168441772</t>
   </si>
   <si>
     <t xml:space="preserve">12.2011680603027</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3957538604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7056465148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6047515869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5759248733521</t>
+    <t xml:space="preserve">12.3957548141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7056455612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6047506332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5759239196777</t>
   </si>
   <si>
     <t xml:space="preserve">12.9362668991089</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1596765518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9434728622437</t>
+    <t xml:space="preserve">13.1596775054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9434700012207</t>
   </si>
   <si>
     <t xml:space="preserve">13.0731945037842</t>
   </si>
   <si>
-    <t xml:space="preserve">12.885817527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.597544670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0786542892456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3597183227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6696119308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8137512207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6984415054321</t>
+    <t xml:space="preserve">12.8858184814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5975456237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0786533355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3597192764282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6696128845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8137502670288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6984405517578</t>
   </si>
   <si>
     <t xml:space="preserve">12.8714046478271</t>
@@ -191,64 +191,64 @@
     <t xml:space="preserve">12.4534091949463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3453054428101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6840238571167</t>
+    <t xml:space="preserve">12.3453044891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.684027671814</t>
   </si>
   <si>
     <t xml:space="preserve">12.7560958862305</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1524724960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2677793502808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3326425552368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0804004669189</t>
+    <t xml:space="preserve">13.1524715423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2677803039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3326416015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0804023742676</t>
   </si>
   <si>
     <t xml:space="preserve">13.1885042190552</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2605724334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7073974609375</t>
+    <t xml:space="preserve">13.2605743408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7073965072632</t>
   </si>
   <si>
     <t xml:space="preserve">13.4911909103394</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3470544815063</t>
+    <t xml:space="preserve">13.3470554351807</t>
   </si>
   <si>
     <t xml:space="preserve">13.001127243042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9002304077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.828164100647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7921295166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0587844848633</t>
+    <t xml:space="preserve">12.9002313613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8281631469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7921285629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0587825775146</t>
   </si>
   <si>
     <t xml:space="preserve">13.1020231246948</t>
   </si>
   <si>
-    <t xml:space="preserve">12.806544303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2821941375732</t>
+    <t xml:space="preserve">12.8065423965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2821931838989</t>
   </si>
   <si>
     <t xml:space="preserve">13.1380577087402</t>
@@ -257,46 +257,46 @@
     <t xml:space="preserve">12.8425769805908</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8930234909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9074363708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0227479934692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6624069213867</t>
+    <t xml:space="preserve">12.8930244445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9074373245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0227470397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6624059677124</t>
   </si>
   <si>
     <t xml:space="preserve">12.8786125183105</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6335792541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7488889694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0258731842041</t>
+    <t xml:space="preserve">12.6335783004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7488880157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0258750915527</t>
   </si>
   <si>
     <t xml:space="preserve">13.0183897018433</t>
   </si>
   <si>
-    <t xml:space="preserve">13.25794506073</t>
+    <t xml:space="preserve">13.2579441070557</t>
   </si>
   <si>
     <t xml:space="preserve">13.2504606246948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4301290512085</t>
+    <t xml:space="preserve">13.4301280975342</t>
   </si>
   <si>
     <t xml:space="preserve">13.4825296401978</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3103504180908</t>
+    <t xml:space="preserve">13.3103485107422</t>
   </si>
   <si>
     <t xml:space="preserve">13.2654304504395</t>
@@ -305,7 +305,7 @@
     <t xml:space="preserve">13.4750442504883</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3702373504639</t>
+    <t xml:space="preserve">13.3702383041382</t>
   </si>
   <si>
     <t xml:space="preserve">13.2878904342651</t>
@@ -320,10 +320,10 @@
     <t xml:space="preserve">12.8012914657593</t>
   </si>
   <si>
-    <t xml:space="preserve">12.883638381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6141386032104</t>
+    <t xml:space="preserve">12.8836374282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6141376495361</t>
   </si>
   <si>
     <t xml:space="preserve">12.3146924972534</t>
@@ -332,25 +332,25 @@
     <t xml:space="preserve">12.4494428634644</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8087768554688</t>
+    <t xml:space="preserve">12.8087778091431</t>
   </si>
   <si>
     <t xml:space="preserve">12.7938051223755</t>
   </si>
   <si>
-    <t xml:space="preserve">13.078275680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4419574737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7831764221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2847490310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7339162826538</t>
+    <t xml:space="preserve">13.0782775878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4419565200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7831754684448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2847480773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7339153289795</t>
   </si>
   <si>
     <t xml:space="preserve">13.4226398468018</t>
@@ -359,67 +359,67 @@
     <t xml:space="preserve">13.5274467468262</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0558214187622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4525833129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3328056335449</t>
+    <t xml:space="preserve">13.0558195114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4525852203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3328065872192</t>
   </si>
   <si>
     <t xml:space="preserve">13.7595148086548</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7295722961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7220840454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5349321365356</t>
+    <t xml:space="preserve">13.7295713424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7220849990845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5349359512329</t>
   </si>
   <si>
     <t xml:space="preserve">13.4900159835815</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7370576858521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0140438079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7071123123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8493509292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1113634109497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9766139984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0814189910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7445449829102</t>
+    <t xml:space="preserve">13.7370567321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0140447616577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7071113586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8493499755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1113662719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9766130447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0814199447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7445459365845</t>
   </si>
   <si>
     <t xml:space="preserve">13.9990739822388</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5049877166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6397371292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6621990203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6097946166992</t>
+    <t xml:space="preserve">13.5049896240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6397390365601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6621971130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6097955703735</t>
   </si>
   <si>
     <t xml:space="preserve">13.3477792739868</t>
@@ -428,28 +428,28 @@
     <t xml:space="preserve">13.415153503418</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2205152511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0857639312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.100736618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0633068084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2354888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1456527709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9285554885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2055416107178</t>
+    <t xml:space="preserve">13.2205142974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0857620239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1007356643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.063304901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2354860305786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1456546783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9285545349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2055425643921</t>
   </si>
   <si>
     <t xml:space="preserve">13.1082229614258</t>
@@ -461,7 +461,7 @@
     <t xml:space="preserve">13.1157093048096</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0109014511108</t>
+    <t xml:space="preserve">13.0109033584595</t>
   </si>
   <si>
     <t xml:space="preserve">12.9135837554932</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">13.1905708312988</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4076671600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3552646636963</t>
+    <t xml:space="preserve">13.4076681137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3552665710449</t>
   </si>
   <si>
     <t xml:space="preserve">13.2130279541016</t>
   </si>
   <si>
-    <t xml:space="preserve">13.340292930603</t>
+    <t xml:space="preserve">13.3402910232544</t>
   </si>
   <si>
     <t xml:space="preserve">12.9659862518311</t>
@@ -500,58 +500,58 @@
     <t xml:space="preserve">12.9809579849243</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7638597488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7114572525024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8686666488647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7563762664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6815147399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5767059326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.546763420105</t>
+    <t xml:space="preserve">12.7638607025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7114582061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8686676025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7563734054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6815137863159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5767049789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5467624664307</t>
   </si>
   <si>
     <t xml:space="preserve">12.5317897796631</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5617351531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5542497634888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4194984436035</t>
+    <t xml:space="preserve">12.5617341995239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5542488098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4194974899292</t>
   </si>
   <si>
     <t xml:space="preserve">12.2772617340088</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4719018936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5018472671509</t>
+    <t xml:space="preserve">12.4719009399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5018463134766</t>
   </si>
   <si>
     <t xml:space="preserve">12.3970384597778</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9778165817261</t>
+    <t xml:space="preserve">11.9778175354004</t>
   </si>
   <si>
     <t xml:space="preserve">12.3596096038818</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4943599700928</t>
+    <t xml:space="preserve">12.4943590164185</t>
   </si>
   <si>
     <t xml:space="preserve">12.3820686340332</t>
@@ -560,25 +560,25 @@
     <t xml:space="preserve">12.4045257568359</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2697763442993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1649703979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2548046112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3371505737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3221769332886</t>
+    <t xml:space="preserve">12.2697744369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1649694442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2548036575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3371496200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3221778869629</t>
   </si>
   <si>
     <t xml:space="preserve">12.7264289855957</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6740264892578</t>
+    <t xml:space="preserve">12.6740274429321</t>
   </si>
   <si>
     <t xml:space="preserve">12.7863187789917</t>
@@ -587,37 +587,37 @@
     <t xml:space="preserve">13.0932502746582</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9510135650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1306810379028</t>
+    <t xml:space="preserve">12.9510145187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1306819915771</t>
   </si>
   <si>
     <t xml:space="preserve">12.9884452819824</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1381673812866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1606254577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.183084487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1681118011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2279996871948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0034189224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1755962371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4001808166504</t>
+    <t xml:space="preserve">13.1381664276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.160626411438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1830854415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1681127548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2280006408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.00341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1755990982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4001817703247</t>
   </si>
   <si>
     <t xml:space="preserve">13.3852090835571</t>
@@ -626,16 +626,16 @@
     <t xml:space="preserve">13.8643217086792</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9167251586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5199584960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4450988769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3627500534058</t>
+    <t xml:space="preserve">13.9167242050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5199594497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4450969696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3627510070801</t>
   </si>
   <si>
     <t xml:space="preserve">13.4600706100464</t>
@@ -644,40 +644,40 @@
     <t xml:space="preserve">13.5124750137329</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4376134872437</t>
+    <t xml:space="preserve">13.437614440918</t>
   </si>
   <si>
     <t xml:space="preserve">13.8268918991089</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6247673034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8044338226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7819738388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6996269226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8418645858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6771688461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8568363189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7670011520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5648794174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8942670822144</t>
+    <t xml:space="preserve">13.6247653961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8044328689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7819757461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6996259689331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8418636322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6771697998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8568382263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7670021057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5648784637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.89426612854</t>
   </si>
   <si>
     <t xml:space="preserve">14.3359479904175</t>
@@ -686,106 +686,106 @@
     <t xml:space="preserve">14.5605344772339</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5156154632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6952819824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9722719192505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9348411560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.942325592041</t>
+    <t xml:space="preserve">14.5156164169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6952810287476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9722709655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9348392486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9423246383667</t>
   </si>
   <si>
     <t xml:space="preserve">14.8225469589233</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2043399810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7133979797363</t>
+    <t xml:space="preserve">15.2043409347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7133960723877</t>
   </si>
   <si>
     <t xml:space="preserve">15.1369647979736</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1594247817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2866878509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3615503311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2267980575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3465766906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6834554672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7208833694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5337314605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.458869934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1669101715088</t>
+    <t xml:space="preserve">15.1594257354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2866897583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3615474700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2267990112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3465747833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6834535598755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7208824157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5337285995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4588689804077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1669120788574</t>
   </si>
   <si>
     <t xml:space="preserve">15.1968536376953</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5487031936646</t>
+    <t xml:space="preserve">15.5487051010132</t>
   </si>
   <si>
     <t xml:space="preserve">15.4214382171631</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6011066436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6460237503052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7358570098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5861330032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9080381393433</t>
+    <t xml:space="preserve">15.6011075973511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6460227966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7358560562134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5861339569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9080362319946</t>
   </si>
   <si>
     <t xml:space="preserve">16.4245796203613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1251373291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6984262466431</t>
+    <t xml:space="preserve">16.1251392364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6984233856201</t>
   </si>
   <si>
     <t xml:space="preserve">16.2823448181152</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3272571563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2598876953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2673740386963</t>
+    <t xml:space="preserve">16.3272609710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2598857879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2673721313477</t>
   </si>
   <si>
     <t xml:space="preserve">16.5967617034912</t>
@@ -794,40 +794,40 @@
     <t xml:space="preserve">16.78391456604</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6641368865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5219020843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4470405578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6416778564453</t>
+    <t xml:space="preserve">16.664134979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.521900177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4470367431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6416797637939</t>
   </si>
   <si>
     <t xml:space="preserve">17.0758743286133</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7988872528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7464847564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8737506866455</t>
+    <t xml:space="preserve">16.7988891601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7464828491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8737468719482</t>
   </si>
   <si>
     <t xml:space="preserve">16.9560947418213</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1058177947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3946361541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5069255828857</t>
+    <t xml:space="preserve">17.1058216094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3946342468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5069274902344</t>
   </si>
   <si>
     <t xml:space="preserve">16.6847553253174</t>
@@ -839,10 +839,10 @@
     <t xml:space="preserve">17.1641120910645</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0094814300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7620716094971</t>
+    <t xml:space="preserve">17.0094833374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7620697021484</t>
   </si>
   <si>
     <t xml:space="preserve">16.6306343078613</t>
@@ -851,13 +851,13 @@
     <t xml:space="preserve">16.8471202850342</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0249423980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9398956298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7698040008545</t>
+    <t xml:space="preserve">17.0249462127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9398975372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7698020935059</t>
   </si>
   <si>
     <t xml:space="preserve">16.9940185546875</t>
@@ -866,31 +866,31 @@
     <t xml:space="preserve">17.1254539489746</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9553623199463</t>
+    <t xml:space="preserve">16.9553604125977</t>
   </si>
   <si>
     <t xml:space="preserve">16.5455856323242</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7156810760498</t>
+    <t xml:space="preserve">16.7156829833984</t>
   </si>
   <si>
     <t xml:space="preserve">16.8548488616943</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7466068267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0404090881348</t>
+    <t xml:space="preserve">16.7466049194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0404071807861</t>
   </si>
   <si>
     <t xml:space="preserve">16.731143951416</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5378551483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5687808990479</t>
+    <t xml:space="preserve">16.5378513336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5687828063965</t>
   </si>
   <si>
     <t xml:space="preserve">16.6229038238525</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">16.7234115600586</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1821994781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0894241333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0816917419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.159008026123</t>
+    <t xml:space="preserve">16.182201385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0894222259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0816898345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1590061187744</t>
   </si>
   <si>
     <t xml:space="preserve">15.9347915649414</t>
@@ -920,16 +920,16 @@
     <t xml:space="preserve">16.2363224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0739612579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9966459274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3909568786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4914665222168</t>
+    <t xml:space="preserve">16.0739593505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9966440200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3909530639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4914646148682</t>
   </si>
   <si>
     <t xml:space="preserve">16.8935070037842</t>
@@ -938,16 +938,16 @@
     <t xml:space="preserve">17.2414264678955</t>
   </si>
   <si>
-    <t xml:space="preserve">17.055871963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2878170013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2955474853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3960590362549</t>
+    <t xml:space="preserve">17.0558700561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2878189086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2955493927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3960609436035</t>
   </si>
   <si>
     <t xml:space="preserve">16.8316535949707</t>
@@ -956,10 +956,10 @@
     <t xml:space="preserve">17.280086517334</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7002182006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5533199310303</t>
+    <t xml:space="preserve">16.700216293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.553316116333</t>
   </si>
   <si>
     <t xml:space="preserve">16.4837322235107</t>
@@ -968,28 +968,28 @@
     <t xml:space="preserve">16.7775344848633</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5146617889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3832225799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3986854553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2749824523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2285919189453</t>
+    <t xml:space="preserve">16.5146598815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3832244873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3986835479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2749805450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2285900115967</t>
   </si>
   <si>
     <t xml:space="preserve">16.0584964752197</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9657163619995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9502534866333</t>
+    <t xml:space="preserve">15.9657192230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9502544403076</t>
   </si>
   <si>
     <t xml:space="preserve">16.0353012084961</t>
@@ -998,34 +998,34 @@
     <t xml:space="preserve">16.2827110290527</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4141502380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6074371337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5919761657715</t>
+    <t xml:space="preserve">16.4141483306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6074390411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5919742584229</t>
   </si>
   <si>
     <t xml:space="preserve">16.932165145874</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0481376647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2646217346191</t>
+    <t xml:space="preserve">17.0481395721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2646236419678</t>
   </si>
   <si>
     <t xml:space="preserve">16.9476280212402</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0713329315186</t>
+    <t xml:space="preserve">17.0713310241699</t>
   </si>
   <si>
     <t xml:space="preserve">17.0636024475098</t>
   </si>
   <si>
-    <t xml:space="preserve">17.079065322876</t>
+    <t xml:space="preserve">17.0790634155273</t>
   </si>
   <si>
     <t xml:space="preserve">17.2723560333252</t>
@@ -1034,10 +1034,10 @@
     <t xml:space="preserve">17.3032817840576</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3728656768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3187427520752</t>
+    <t xml:space="preserve">17.3728637695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3187446594238</t>
   </si>
   <si>
     <t xml:space="preserve">17.5584239959717</t>
@@ -1064,7 +1064,7 @@
     <t xml:space="preserve">18.107364654541</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0377807617188</t>
+    <t xml:space="preserve">18.0377826690674</t>
   </si>
   <si>
     <t xml:space="preserve">17.6125450134277</t>
@@ -1079,22 +1079,22 @@
     <t xml:space="preserve">17.3110122680664</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1099910736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3574028015137</t>
+    <t xml:space="preserve">17.1099891662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3574047088623</t>
   </si>
   <si>
     <t xml:space="preserve">17.1795768737793</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1409187316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0867958068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.885778427124</t>
+    <t xml:space="preserve">17.1409206390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0867977142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8857746124268</t>
   </si>
   <si>
     <t xml:space="preserve">16.6151695251465</t>
@@ -1106,16 +1106,16 @@
     <t xml:space="preserve">16.3522968292236</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0430335998535</t>
+    <t xml:space="preserve">16.0430316925049</t>
   </si>
   <si>
     <t xml:space="preserve">15.8265466690063</t>
   </si>
   <si>
-    <t xml:space="preserve">15.927059173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1976661682129</t>
+    <t xml:space="preserve">15.9270610809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1976642608643</t>
   </si>
   <si>
     <t xml:space="preserve">16.6692924499512</t>
@@ -1127,16 +1127,16 @@
     <t xml:space="preserve">16.7852649688721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9630947113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8084621429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9244346618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4218807220459</t>
+    <t xml:space="preserve">16.9630928039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8084602355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9244327545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4218826293945</t>
   </si>
   <si>
     <t xml:space="preserve">16.0507659912109</t>
@@ -1145,22 +1145,22 @@
     <t xml:space="preserve">16.4605388641357</t>
   </si>
   <si>
-    <t xml:space="preserve">16.452808380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7543354034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6383647918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7929935455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4064159393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.33420753479</t>
+    <t xml:space="preserve">16.4528064727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7543392181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6383666992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7929954528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4064140319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3342056274414</t>
   </si>
   <si>
     <t xml:space="preserve">17.3805980682373</t>
@@ -1172,10 +1172,10 @@
     <t xml:space="preserve">17.5506916046143</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6898593902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4115238189697</t>
+    <t xml:space="preserve">17.6898612976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4115219116211</t>
   </si>
   <si>
     <t xml:space="preserve">17.6434707641602</t>
@@ -1187,10 +1187,10 @@
     <t xml:space="preserve">17.2259654998779</t>
   </si>
   <si>
-    <t xml:space="preserve">17.504301071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4991970062256</t>
+    <t xml:space="preserve">17.5043029785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.499195098877</t>
   </si>
   <si>
     <t xml:space="preserve">16.9785537719727</t>
@@ -1199,28 +1199,28 @@
     <t xml:space="preserve">16.3445663452148</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2981777191162</t>
+    <t xml:space="preserve">16.2981758117676</t>
   </si>
   <si>
     <t xml:space="preserve">16.9012393951416</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6538276672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2672519683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3136386871338</t>
+    <t xml:space="preserve">16.653829574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2672500610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3136405944824</t>
   </si>
   <si>
     <t xml:space="preserve">17.4269866943359</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4475555419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3857040405273</t>
+    <t xml:space="preserve">18.4475536346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3857021331787</t>
   </si>
   <si>
     <t xml:space="preserve">18.8805236816406</t>
@@ -1235,22 +1235,22 @@
     <t xml:space="preserve">18.911449432373</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6949653625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6795043945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7413558959961</t>
+    <t xml:space="preserve">18.6949672698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6795024871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7413539886475</t>
   </si>
   <si>
     <t xml:space="preserve">18.6640377044678</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7877464294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2516422271729</t>
+    <t xml:space="preserve">18.7877445220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2516384124756</t>
   </si>
   <si>
     <t xml:space="preserve">19.437198638916</t>
@@ -1259,28 +1259,28 @@
     <t xml:space="preserve">19.3444194793701</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4062690734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5609016418457</t>
+    <t xml:space="preserve">19.406270980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5609035491943</t>
   </si>
   <si>
     <t xml:space="preserve">19.3289566040039</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1743259429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1124706268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.158863067627</t>
+    <t xml:space="preserve">19.1743221282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1124725341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1588611602783</t>
   </si>
   <si>
     <t xml:space="preserve">19.2825660705566</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2361755371094</t>
+    <t xml:space="preserve">19.2361736297607</t>
   </si>
   <si>
     <t xml:space="preserve">19.205249786377</t>
@@ -1289,64 +1289,64 @@
     <t xml:space="preserve">19.2671031951904</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5299758911133</t>
+    <t xml:space="preserve">19.5299777984619</t>
   </si>
   <si>
     <t xml:space="preserve">19.6382179260254</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5918292999268</t>
+    <t xml:space="preserve">19.5918273925781</t>
   </si>
   <si>
     <t xml:space="preserve">19.4835872650146</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5145130157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4526596069336</t>
+    <t xml:space="preserve">19.5145111083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4526615142822</t>
   </si>
   <si>
     <t xml:space="preserve">19.607292175293</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1382942199707</t>
+    <t xml:space="preserve">18.1382904052734</t>
   </si>
   <si>
     <t xml:space="preserve">18.3547763824463</t>
   </si>
   <si>
-    <t xml:space="preserve">18.07643699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0300483703613</t>
+    <t xml:space="preserve">18.0764389038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0300521850586</t>
   </si>
   <si>
     <t xml:space="preserve">18.1737804412842</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9502029418945</t>
+    <t xml:space="preserve">17.9502010345459</t>
   </si>
   <si>
     <t xml:space="preserve">18.3654174804688</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2057189941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6209354400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5091495513916</t>
+    <t xml:space="preserve">18.205717086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6209392547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.509147644043</t>
   </si>
   <si>
     <t xml:space="preserve">18.5889987945557</t>
   </si>
   <si>
-    <t xml:space="preserve">18.557056427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4931793212891</t>
+    <t xml:space="preserve">18.5570583343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4931774139404</t>
   </si>
   <si>
     <t xml:space="preserve">18.157808303833</t>
@@ -1361,34 +1361,34 @@
     <t xml:space="preserve">18.6369075775146</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4133281707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4612369537354</t>
+    <t xml:space="preserve">18.4133262634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.461238861084</t>
   </si>
   <si>
     <t xml:space="preserve">18.3175086975098</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8064727783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8224391937256</t>
+    <t xml:space="preserve">17.8064708709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8224411010742</t>
   </si>
   <si>
     <t xml:space="preserve">17.7106533050537</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9182605743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9661693572998</t>
+    <t xml:space="preserve">17.9182643890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9661712646484</t>
   </si>
   <si>
     <t xml:space="preserve">18.03005027771</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8863220214844</t>
+    <t xml:space="preserve">17.8863201141357</t>
   </si>
   <si>
     <t xml:space="preserve">17.9981098175049</t>
@@ -1397,31 +1397,31 @@
     <t xml:space="preserve">18.3973598480225</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5251159667969</t>
+    <t xml:space="preserve">18.5251178741455</t>
   </si>
   <si>
     <t xml:space="preserve">18.4452686309814</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1479434967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1639156341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0201873779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8604850769043</t>
+    <t xml:space="preserve">19.1479473114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1639137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0201854705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8604869842529</t>
   </si>
   <si>
     <t xml:space="preserve">18.7806377410889</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5730266571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0680961608887</t>
+    <t xml:space="preserve">18.5730285644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0680923461914</t>
   </si>
   <si>
     <t xml:space="preserve">18.7646656036377</t>
@@ -1439,31 +1439,31 @@
     <t xml:space="preserve">19.4513740539551</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4992847442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2118263244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1319770812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0042133331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1160068511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0361557006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1798858642578</t>
+    <t xml:space="preserve">19.4992828369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2118244171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1319751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0042152404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1160049438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0361576080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1798839569092</t>
   </si>
   <si>
     <t xml:space="preserve">19.323616027832</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3395824432373</t>
+    <t xml:space="preserve">19.3395862579346</t>
   </si>
   <si>
     <t xml:space="preserve">19.3076457977295</t>
@@ -1475,28 +1475,28 @@
     <t xml:space="preserve">19.4673442840576</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3874931335449</t>
+    <t xml:space="preserve">19.3874950408936</t>
   </si>
   <si>
     <t xml:space="preserve">19.5631637573242</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8825626373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3616619110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4415111541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2658405303955</t>
+    <t xml:space="preserve">19.8825607299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3616600036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4415092468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2658386230469</t>
   </si>
   <si>
     <t xml:space="preserve">20.7609081268311</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0962734222412</t>
+    <t xml:space="preserve">21.0962753295898</t>
   </si>
   <si>
     <t xml:space="preserve">20.8247890472412</t>
@@ -1505,13 +1505,13 @@
     <t xml:space="preserve">20.249870300293</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4734477996826</t>
+    <t xml:space="preserve">20.4734497070312</t>
   </si>
   <si>
     <t xml:space="preserve">20.1540489196777</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1700191497803</t>
+    <t xml:space="preserve">20.1700210571289</t>
   </si>
   <si>
     <t xml:space="preserve">19.7548027038574</t>
@@ -1520,19 +1520,19 @@
     <t xml:space="preserve">19.5312213897705</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4034652709961</t>
+    <t xml:space="preserve">19.4034633636475</t>
   </si>
   <si>
     <t xml:space="preserve">18.8125762939453</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7327289581299</t>
+    <t xml:space="preserve">18.7327251434326</t>
   </si>
   <si>
     <t xml:space="preserve">18.3813877105713</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2536315917969</t>
+    <t xml:space="preserve">18.2536296844482</t>
   </si>
   <si>
     <t xml:space="preserve">17.9342308044434</t>
@@ -1547,7 +1547,7 @@
     <t xml:space="preserve">18.7486953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1258678436279</t>
+    <t xml:space="preserve">18.1258697509766</t>
   </si>
   <si>
     <t xml:space="preserve">17.7905006408691</t>
@@ -1556,13 +1556,13 @@
     <t xml:space="preserve">17.4391632080078</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1357345581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2155838012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9760360717773</t>
+    <t xml:space="preserve">17.1357326507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2155857086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9760341644287</t>
   </si>
   <si>
     <t xml:space="preserve">17.550952911377</t>
@@ -1571,13 +1571,13 @@
     <t xml:space="preserve">16.8961849212646</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0718555450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9281272888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8323078155518</t>
+    <t xml:space="preserve">17.0718536376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9281234741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8323059082031</t>
   </si>
   <si>
     <t xml:space="preserve">17.0558853149414</t>
@@ -1586,7 +1586,7 @@
     <t xml:space="preserve">17.1836452484131</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4551334381104</t>
+    <t xml:space="preserve">17.4551315307617</t>
   </si>
   <si>
     <t xml:space="preserve">16.816333770752</t>
@@ -1598,13 +1598,13 @@
     <t xml:space="preserve">15.9858989715576</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0976886749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1136589050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4269533157349</t>
+    <t xml:space="preserve">16.0976905822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1136608123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4269514083862</t>
   </si>
   <si>
     <t xml:space="preserve">15.3311319351196</t>
@@ -1613,19 +1613,19 @@
     <t xml:space="preserve">15.6505308151245</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4748601913452</t>
+    <t xml:space="preserve">15.4748620986938</t>
   </si>
   <si>
     <t xml:space="preserve">15.4429225921631</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7703037261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.842170715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7383651733398</t>
+    <t xml:space="preserve">15.7703056335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8421697616577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7383642196655</t>
   </si>
   <si>
     <t xml:space="preserve">16.4490280151367</t>
@@ -1640,7 +1640,7 @@
     <t xml:space="preserve">16.3212699890137</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4809665679932</t>
+    <t xml:space="preserve">16.4809684753418</t>
   </si>
   <si>
     <t xml:space="preserve">16.6246948242188</t>
@@ -1652,34 +1652,34 @@
     <t xml:space="preserve">17.1676750183105</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3433418273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2794647216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9440956115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0079727172852</t>
+    <t xml:space="preserve">17.3433437347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2794628143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.944091796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0079746246338</t>
   </si>
   <si>
     <t xml:space="preserve">16.6406669616699</t>
   </si>
   <si>
-    <t xml:space="preserve">16.241418838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5608177185059</t>
+    <t xml:space="preserve">16.2414169311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5608158111572</t>
   </si>
   <si>
     <t xml:space="preserve">16.7045459747314</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8482761383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3752841949463</t>
+    <t xml:space="preserve">16.8482780456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3752822875977</t>
   </si>
   <si>
     <t xml:space="preserve">17.1037940979004</t>
@@ -1688,19 +1688,19 @@
     <t xml:space="preserve">16.8802165985107</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9121551513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8642444610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.720516204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6885776519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6087265014648</t>
+    <t xml:space="preserve">16.9121570587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8642463684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7205142974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6885757446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6087245941162</t>
   </si>
   <si>
     <t xml:space="preserve">16.7364864349365</t>
@@ -1709,10 +1709,10 @@
     <t xml:space="preserve">16.3052978515625</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8980665206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1935062408447</t>
+    <t xml:space="preserve">15.8980627059937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1935081481934</t>
   </si>
   <si>
     <t xml:space="preserve">16.2094783782959</t>
@@ -1724,7 +1724,7 @@
     <t xml:space="preserve">16.2893257141113</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2573890686035</t>
+    <t xml:space="preserve">16.2573871612549</t>
   </si>
   <si>
     <t xml:space="preserve">16.2254467010498</t>
@@ -1733,28 +1733,28 @@
     <t xml:space="preserve">15.9140329360962</t>
   </si>
   <si>
-    <t xml:space="preserve">16.417085647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5288753509521</t>
+    <t xml:space="preserve">16.4170875549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.528881072998</t>
   </si>
   <si>
     <t xml:space="preserve">16.7843971252441</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5767860412598</t>
+    <t xml:space="preserve">16.5767879486084</t>
   </si>
   <si>
     <t xml:space="preserve">16.369176864624</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1775379180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4889507293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2494029998779</t>
+    <t xml:space="preserve">16.1775398254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4889526367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2494010925293</t>
   </si>
   <si>
     <t xml:space="preserve">16.3292541503906</t>
@@ -1766,28 +1766,28 @@
     <t xml:space="preserve">16.1695537567139</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0497779846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5688018798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6486530303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2874488830566</t>
+    <t xml:space="preserve">16.0497798919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5687999725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6486511230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.287446975708</t>
   </si>
   <si>
     <t xml:space="preserve">17.0878238677979</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0478992462158</t>
+    <t xml:space="preserve">17.0479011535645</t>
   </si>
   <si>
     <t xml:space="preserve">16.8083515167236</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9680480957031</t>
+    <t xml:space="preserve">16.9680500030518</t>
   </si>
   <si>
     <t xml:space="preserve">16.7285003662109</t>
@@ -1808,13 +1808,13 @@
     <t xml:space="preserve">16.9208221435547</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7964038848877</t>
+    <t xml:space="preserve">16.7964057922363</t>
   </si>
   <si>
     <t xml:space="preserve">17.2111301422119</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1281871795654</t>
+    <t xml:space="preserve">17.1281852722168</t>
   </si>
   <si>
     <t xml:space="preserve">17.1696586608887</t>
@@ -1832,7 +1832,7 @@
     <t xml:space="preserve">17.2940769195557</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9622955322266</t>
+    <t xml:space="preserve">16.9622936248779</t>
   </si>
   <si>
     <t xml:space="preserve">16.7549343109131</t>
@@ -1844,31 +1844,31 @@
     <t xml:space="preserve">16.3402061462402</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4895076751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5392742156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7088012695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6673278808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5014400482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5429134368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2526035308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7134571075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4231510162354</t>
+    <t xml:space="preserve">16.4895057678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5392761230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7088031768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6673316955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5014381408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.542911529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2525997161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7134590148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.423152923584</t>
   </si>
   <si>
     <t xml:space="preserve">16.373384475708</t>
@@ -1877,67 +1877,67 @@
     <t xml:space="preserve">16.2406711578369</t>
   </si>
   <si>
-    <t xml:space="preserve">16.17431640625</t>
+    <t xml:space="preserve">16.1743144989014</t>
   </si>
   <si>
     <t xml:space="preserve">16.2738494873047</t>
   </si>
   <si>
-    <t xml:space="preserve">16.124547958374</t>
+    <t xml:space="preserve">16.1245498657227</t>
   </si>
   <si>
     <t xml:space="preserve">16.3070259094238</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8591232299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7264108657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7927675247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.074779510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5273447036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4278087615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6600532531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1789741516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3614530563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6932334899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6102857589722</t>
+    <t xml:space="preserve">15.8591251373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.726411819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7927665710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0747814178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5273418426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4278078079224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6600542068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1789751052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3614511489868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6932344436646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6102876663208</t>
   </si>
   <si>
     <t xml:space="preserve">15.4609870910645</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4443998336792</t>
+    <t xml:space="preserve">15.4443969726562</t>
   </si>
   <si>
     <t xml:space="preserve">15.3780422210693</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2950973510742</t>
+    <t xml:space="preserve">15.2950963973999</t>
   </si>
   <si>
     <t xml:space="preserve">15.9254789352417</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2904376983643</t>
+    <t xml:space="preserve">16.2904396057129</t>
   </si>
   <si>
     <t xml:space="preserve">16.3899726867676</t>
@@ -1949,10 +1949,10 @@
     <t xml:space="preserve">16.6719875335693</t>
   </si>
   <si>
-    <t xml:space="preserve">17.957633972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0867118835449</t>
+    <t xml:space="preserve">17.9576377868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0867137908936</t>
   </si>
   <si>
     <t xml:space="preserve">17.3355484008789</t>
@@ -1964,22 +1964,22 @@
     <t xml:space="preserve">16.5890407562256</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2572631835938</t>
+    <t xml:space="preserve">16.2572612762451</t>
   </si>
   <si>
     <t xml:space="preserve">15.8757123947144</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9088897705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1577243804932</t>
+    <t xml:space="preserve">15.9088916778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1577281951904</t>
   </si>
   <si>
     <t xml:space="preserve">16.1411361694336</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4729175567627</t>
+    <t xml:space="preserve">16.4729194641113</t>
   </si>
   <si>
     <t xml:space="preserve">15.7595891952515</t>
@@ -1988,31 +1988,31 @@
     <t xml:space="preserve">15.6766443252563</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5936994552612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.477578163147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7430000305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7098236083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8425340652466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3567924499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3236179351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.975248336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5843830108643</t>
+    <t xml:space="preserve">15.5936985015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4775762557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7429971694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7098217010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8425350189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3567943572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.323616027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9752464294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5843849182129</t>
   </si>
   <si>
     <t xml:space="preserve">17.0037670135498</t>
@@ -2030,10 +2030,10 @@
     <t xml:space="preserve">16.5558624267578</t>
   </si>
   <si>
-    <t xml:space="preserve">14.532000541687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7974262237549</t>
+    <t xml:space="preserve">14.5320014953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7974243164062</t>
   </si>
   <si>
     <t xml:space="preserve">14.1836309432983</t>
@@ -2048,31 +2048,31 @@
     <t xml:space="preserve">13.4371242523193</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2712326049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3873558044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7616310119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9606990814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4251918792725</t>
+    <t xml:space="preserve">13.2712335586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3873567581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7616300582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9606981277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4251909255981</t>
   </si>
   <si>
     <t xml:space="preserve">11.0317125320435</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4796180725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1690826416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3681516647339</t>
+    <t xml:space="preserve">11.4796171188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1690816879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3681507110596</t>
   </si>
   <si>
     <t xml:space="preserve">9.95342445373535</t>
@@ -2081,25 +2081,25 @@
     <t xml:space="preserve">10.3183832168579</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8777523040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4417819976807</t>
+    <t xml:space="preserve">11.8777542114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4417810440063</t>
   </si>
   <si>
     <t xml:space="preserve">12.8565073013306</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1763563156128</t>
+    <t xml:space="preserve">12.1763572692871</t>
   </si>
   <si>
     <t xml:space="preserve">12.2924795150757</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2141923904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9155883789062</t>
+    <t xml:space="preserve">11.2141933441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9155902862549</t>
   </si>
   <si>
     <t xml:space="preserve">10.6667537689209</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">10.451096534729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5174512863159</t>
+    <t xml:space="preserve">10.5174522399902</t>
   </si>
   <si>
     <t xml:space="preserve">10.5340404510498</t>
@@ -2120,37 +2120,37 @@
     <t xml:space="preserve">10.4013299942017</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1524925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0529584884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97001361846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4676856994629</t>
+    <t xml:space="preserve">10.1524934768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0529594421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97001457214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4676847457886</t>
   </si>
   <si>
     <t xml:space="preserve">10.6999311447144</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3017959594727</t>
+    <t xml:space="preserve">10.3017950057983</t>
   </si>
   <si>
     <t xml:space="preserve">10.0695486068726</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2520275115967</t>
+    <t xml:space="preserve">10.252028465271</t>
   </si>
   <si>
     <t xml:space="preserve">10.0031929016113</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0363702774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1193151473999</t>
+    <t xml:space="preserve">10.0363712310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1193161010742</t>
   </si>
   <si>
     <t xml:space="preserve">9.92024707794189</t>
@@ -2159,7 +2159,7 @@
     <t xml:space="preserve">9.45575332641602</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50552082061768</t>
+    <t xml:space="preserve">9.50551986694336</t>
   </si>
   <si>
     <t xml:space="preserve">9.32304096221924</t>
@@ -2174,16 +2174,16 @@
     <t xml:space="preserve">9.68800067901611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1359033584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38939666748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4345073699951</t>
+    <t xml:space="preserve">10.1359043121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70458889007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38939762115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4345064163208</t>
   </si>
   <si>
     <t xml:space="preserve">10.2188491821289</t>
@@ -2195,13 +2195,13 @@
     <t xml:space="preserve">10.99853515625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.899001121521</t>
+    <t xml:space="preserve">10.8990001678467</t>
   </si>
   <si>
     <t xml:space="preserve">10.9819459915161</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8160543441772</t>
+    <t xml:space="preserve">10.8160552978516</t>
   </si>
   <si>
     <t xml:space="preserve">10.8824110031128</t>
@@ -2210,37 +2210,37 @@
     <t xml:space="preserve">11.8113975524902</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7782192230225</t>
+    <t xml:space="preserve">11.7782182693481</t>
   </si>
   <si>
     <t xml:space="preserve">11.595739364624</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3634939193726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6833419799805</t>
+    <t xml:space="preserve">11.3634929656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6833429336548</t>
   </si>
   <si>
     <t xml:space="preserve">10.9487676620483</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9653568267822</t>
+    <t xml:space="preserve">10.9653558731079</t>
   </si>
   <si>
     <t xml:space="preserve">11.2639589309692</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2805480957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1810140609741</t>
+    <t xml:space="preserve">11.2805490493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1810131072998</t>
   </si>
   <si>
     <t xml:space="preserve">11.3303146362305</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2971363067627</t>
+    <t xml:space="preserve">11.297137260437</t>
   </si>
   <si>
     <t xml:space="preserve">11.0814800262451</t>
@@ -2252,46 +2252,46 @@
     <t xml:space="preserve">11.0648908615112</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8326444625854</t>
+    <t xml:space="preserve">10.8326435089111</t>
   </si>
   <si>
     <t xml:space="preserve">10.8492336273193</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5838088989258</t>
+    <t xml:space="preserve">10.5838098526001</t>
   </si>
   <si>
     <t xml:space="preserve">10.3847408294678</t>
   </si>
   <si>
-    <t xml:space="preserve">10.650164604187</t>
+    <t xml:space="preserve">10.6501655578613</t>
   </si>
   <si>
     <t xml:space="preserve">10.3515615463257</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2354383468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9321784973145</t>
+    <t xml:space="preserve">10.2354373931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9321794509888</t>
   </si>
   <si>
     <t xml:space="preserve">10.550630569458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5008640289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6169862747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4842758178711</t>
+    <t xml:space="preserve">10.500862121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6169872283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4842748641968</t>
   </si>
   <si>
     <t xml:space="preserve">10.0197811126709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3349723815918</t>
+    <t xml:space="preserve">10.3349733352661</t>
   </si>
   <si>
     <t xml:space="preserve">10.7828769683838</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">11.1312475204468</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4132595062256</t>
+    <t xml:space="preserve">11.4132604598999</t>
   </si>
   <si>
     <t xml:space="preserve">11.4298486709595</t>
@@ -2312,16 +2312,16 @@
     <t xml:space="preserve">11.2307806015015</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8658227920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3137264251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3966703414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5127935409546</t>
+    <t xml:space="preserve">10.8658218383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3137273788452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.396671295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5127954483032</t>
   </si>
   <si>
     <t xml:space="preserve">11.8611660003662</t>
@@ -2330,10 +2330,10 @@
     <t xml:space="preserve">12.2095355987549</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9772882461548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0602331161499</t>
+    <t xml:space="preserve">11.9772872924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0602321624756</t>
   </si>
   <si>
     <t xml:space="preserve">12.2593011856079</t>
@@ -2342,19 +2342,19 @@
     <t xml:space="preserve">11.3800830841064</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1146583557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6335744857788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2686166763306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55528831481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62164497375488</t>
+    <t xml:space="preserve">11.1146574020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6335754394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2686176300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55528736114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62164402008057</t>
   </si>
   <si>
     <t xml:space="preserve">9.65482234954834</t>
@@ -2363,10 +2363,10 @@
     <t xml:space="preserve">9.60505485534668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75435733795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4915494918823</t>
+    <t xml:space="preserve">9.75435638427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.491548538208</t>
   </si>
   <si>
     <t xml:space="preserve">13.0058088302612</t>
@@ -2378,16 +2378,16 @@
     <t xml:space="preserve">12.8399181365967</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3209991455078</t>
+    <t xml:space="preserve">13.3210000991821</t>
   </si>
   <si>
     <t xml:space="preserve">12.4086027145386</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2758903503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7237949371338</t>
+    <t xml:space="preserve">12.2758913040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7237939834595</t>
   </si>
   <si>
     <t xml:space="preserve">12.9062747955322</t>
@@ -2408,10 +2408,10 @@
     <t xml:space="preserve">13.0887537002563</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0389881134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6740274429321</t>
+    <t xml:space="preserve">13.038987159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6740283966064</t>
   </si>
   <si>
     <t xml:space="preserve">12.4583711624146</t>
@@ -2423,43 +2423,43 @@
     <t xml:space="preserve">12.7403841018677</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3754243850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4749593734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6574392318726</t>
+    <t xml:space="preserve">12.3754253387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4749603271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6574382781982</t>
   </si>
   <si>
     <t xml:space="preserve">12.9560413360596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9228639602661</t>
+    <t xml:space="preserve">12.9228630065918</t>
   </si>
   <si>
     <t xml:space="preserve">13.5366582870483</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9845628738403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3661098480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5817670822144</t>
+    <t xml:space="preserve">13.9845638275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3661088943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5817680358887</t>
   </si>
   <si>
     <t xml:space="preserve">14.6978893280029</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7642459869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.631534576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1006851196289</t>
+    <t xml:space="preserve">14.7642450332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6315336227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1006832122803</t>
   </si>
   <si>
     <t xml:space="preserve">14.432466506958</t>
@@ -2468,64 +2468,64 @@
     <t xml:space="preserve">14.780837059021</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7476587295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4988212585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3495206832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2499866485596</t>
+    <t xml:space="preserve">14.7476596832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4988203048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3495197296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2499876022339</t>
   </si>
   <si>
     <t xml:space="preserve">14.2333984375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.785493850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0177392959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0509185791016</t>
+    <t xml:space="preserve">13.7854948043823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0177402496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0509204864502</t>
   </si>
   <si>
     <t xml:space="preserve">14.2831630706787</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0462589263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.930136680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3946294784546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3448638916016</t>
+    <t xml:space="preserve">15.0462598800659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9301376342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3946285247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3448648452759</t>
   </si>
   <si>
     <t xml:space="preserve">15.9918365478516</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8969593048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9799060821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9135475158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9964942932129</t>
+    <t xml:space="preserve">14.8969583511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9799041748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9135484695435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9964952468872</t>
   </si>
   <si>
     <t xml:space="preserve">15.8259449005127</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6434659957886</t>
+    <t xml:space="preserve">15.6434669494629</t>
   </si>
   <si>
     <t xml:space="preserve">16.0250148773193</t>
@@ -2534,19 +2534,19 @@
     <t xml:space="preserve">16.0913696289062</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0581932067871</t>
+    <t xml:space="preserve">16.0581912994385</t>
   </si>
   <si>
     <t xml:space="preserve">15.5605211257935</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0130825042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2619190216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2287406921387</t>
+    <t xml:space="preserve">15.0130815505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2619171142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2287397384644</t>
   </si>
   <si>
     <t xml:space="preserve">15.1457958221436</t>
@@ -2555,28 +2555,28 @@
     <t xml:space="preserve">15.4941663742065</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6268749237061</t>
+    <t xml:space="preserve">15.626877784729</t>
   </si>
   <si>
     <t xml:space="preserve">15.2121515274048</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5024604797363</t>
+    <t xml:space="preserve">15.502459526062</t>
   </si>
   <si>
     <t xml:space="preserve">15.2702121734619</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2536220550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5439319610596</t>
+    <t xml:space="preserve">15.253623008728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5439329147339</t>
   </si>
   <si>
     <t xml:space="preserve">15.5771102905273</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8508310317993</t>
+    <t xml:space="preserve">15.8508291244507</t>
   </si>
   <si>
     <t xml:space="preserve">15.7181177139282</t>
@@ -2585,16 +2585,16 @@
     <t xml:space="preserve">15.7347049713135</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8840093612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.751293182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4361028671265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3982677459717</t>
+    <t xml:space="preserve">15.8840084075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7512950897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4361047744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3982696533203</t>
   </si>
   <si>
     <t xml:space="preserve">16.5807476043701</t>
@@ -2603,10 +2603,10 @@
     <t xml:space="preserve">15.8674182891846</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0830764770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1079578399658</t>
+    <t xml:space="preserve">16.0830745697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1079597473145</t>
   </si>
   <si>
     <t xml:space="preserve">16.4646224975586</t>
@@ -2615,25 +2615,25 @@
     <t xml:space="preserve">16.622220993042</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8212871551514</t>
+    <t xml:space="preserve">16.8212890625</t>
   </si>
   <si>
     <t xml:space="preserve">16.7051639556885</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9042339324951</t>
+    <t xml:space="preserve">16.9042320251465</t>
   </si>
   <si>
     <t xml:space="preserve">16.9374122619629</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1364803314209</t>
+    <t xml:space="preserve">17.1364822387695</t>
   </si>
   <si>
     <t xml:space="preserve">17.3023700714111</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4350814819336</t>
+    <t xml:space="preserve">17.4350833892822</t>
   </si>
   <si>
     <t xml:space="preserve">17.4516735076904</t>
@@ -2645,19 +2645,19 @@
     <t xml:space="preserve">16.7217540740967</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1530685424805</t>
+    <t xml:space="preserve">17.1530704498291</t>
   </si>
   <si>
     <t xml:space="preserve">17.0535335540771</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0369434356689</t>
+    <t xml:space="preserve">17.0369453430176</t>
   </si>
   <si>
     <t xml:space="preserve">16.8876457214355</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7715225219727</t>
+    <t xml:space="preserve">16.771520614624</t>
   </si>
   <si>
     <t xml:space="preserve">16.8544654846191</t>
@@ -2666,19 +2666,19 @@
     <t xml:space="preserve">17.2028350830078</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1033020019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1198902130127</t>
+    <t xml:space="preserve">17.1033039093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1198883056641</t>
   </si>
   <si>
     <t xml:space="preserve">16.7383441925049</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3521366119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2691917419434</t>
+    <t xml:space="preserve">17.3521404266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.269193649292</t>
   </si>
   <si>
     <t xml:space="preserve">16.8710556030273</t>
@@ -2687,7 +2687,7 @@
     <t xml:space="preserve">15.9171857833862</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2074966430664</t>
+    <t xml:space="preserve">16.2074947357178</t>
   </si>
   <si>
     <t xml:space="preserve">16.2323780059814</t>
@@ -2702,25 +2702,25 @@
     <t xml:space="preserve">18.1981792449951</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1650009155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.617561340332</t>
+    <t xml:space="preserve">18.1649990081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6175632476807</t>
   </si>
   <si>
     <t xml:space="preserve">18.0820560455322</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6507415771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8000411987305</t>
+    <t xml:space="preserve">17.6507396697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8000431060791</t>
   </si>
   <si>
     <t xml:space="preserve">17.4019050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3189563751221</t>
+    <t xml:space="preserve">17.3189582824707</t>
   </si>
   <si>
     <t xml:space="preserve">17.020357131958</t>
@@ -2735,28 +2735,28 @@
     <t xml:space="preserve">17.1862449645996</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4065647125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4148559570312</t>
+    <t xml:space="preserve">16.4065628051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4148578643799</t>
   </si>
   <si>
     <t xml:space="preserve">16.0499000549316</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1660213470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5346164703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0701217651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2360134124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6839199066162</t>
+    <t xml:space="preserve">16.1660194396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5346183776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0701236724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2360153198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6839179992676</t>
   </si>
   <si>
     <t xml:space="preserve">17.4848518371582</t>
@@ -2774,7 +2774,7 @@
     <t xml:space="preserve">17.5461578369141</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4111862182617</t>
+    <t xml:space="preserve">17.4111881256104</t>
   </si>
   <si>
     <t xml:space="preserve">17.3774433135986</t>
@@ -2786,10 +2786,10 @@
     <t xml:space="preserve">17.4449310302734</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4618015289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1749897003174</t>
+    <t xml:space="preserve">17.4618034362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1749877929688</t>
   </si>
   <si>
     <t xml:space="preserve">17.0400199890137</t>
@@ -2798,7 +2798,7 @@
     <t xml:space="preserve">17.0062770843506</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9556636810303</t>
+    <t xml:space="preserve">16.9556617736816</t>
   </si>
   <si>
     <t xml:space="preserve">16.8628692626953</t>
@@ -2816,7 +2816,7 @@
     <t xml:space="preserve">17.2087326049805</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2048873901367</t>
+    <t xml:space="preserve">16.2048892974854</t>
   </si>
   <si>
     <t xml:space="preserve">16.0952262878418</t>
@@ -2828,25 +2828,25 @@
     <t xml:space="preserve">15.791543006897</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6903142929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8590278625488</t>
+    <t xml:space="preserve">15.690315246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8590259552002</t>
   </si>
   <si>
     <t xml:space="preserve">15.4119386672974</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5216016769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.099817276001</t>
+    <t xml:space="preserve">15.5216007232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0998182296753</t>
   </si>
   <si>
     <t xml:space="preserve">15.420373916626</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6059589385986</t>
+    <t xml:space="preserve">15.6059598922729</t>
   </si>
   <si>
     <t xml:space="preserve">15.5806503295898</t>
@@ -2861,64 +2861,64 @@
     <t xml:space="preserve">15.8758974075317</t>
   </si>
   <si>
-    <t xml:space="preserve">15.892767906189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0108680725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9349479675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7662363052368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7746725082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5131635665894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4878587722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1841745376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2347898483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3950662612915</t>
+    <t xml:space="preserve">15.8927717208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0108699798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.934947013855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7662353515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7746715545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5131645202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4878597259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.184175491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2347888946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3950681686401</t>
   </si>
   <si>
     <t xml:space="preserve">15.9433832168579</t>
   </si>
   <si>
-    <t xml:space="preserve">16.112096786499</t>
+    <t xml:space="preserve">16.1120986938477</t>
   </si>
   <si>
     <t xml:space="preserve">16.2976818084717</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4495239257812</t>
+    <t xml:space="preserve">16.4495220184326</t>
   </si>
   <si>
     <t xml:space="preserve">15.5890874862671</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6987504959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0361766815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9686918258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3145523071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9180784225464</t>
+    <t xml:space="preserve">15.698751449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0361747741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9686908721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3145542144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9180774688721</t>
   </si>
   <si>
     <t xml:space="preserve">16.0193042755127</t>
@@ -2927,22 +2927,22 @@
     <t xml:space="preserve">15.5384721755981</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0154609680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1504325866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5300369262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8168478012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5637807846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.884334564209</t>
+    <t xml:space="preserve">15.0154619216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1504306793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5300359725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8168497085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5637798309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8843336105347</t>
   </si>
   <si>
     <t xml:space="preserve">16.1374034881592</t>
@@ -2954,28 +2954,28 @@
     <t xml:space="preserve">15.4541149139404</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9732847213745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0238981246948</t>
+    <t xml:space="preserve">14.9732828140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0238971710205</t>
   </si>
   <si>
     <t xml:space="preserve">15.1673030853271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4372453689575</t>
+    <t xml:space="preserve">15.4372444152832</t>
   </si>
   <si>
     <t xml:space="preserve">15.6312637329102</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4794216156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1588678359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7623929977417</t>
+    <t xml:space="preserve">15.4794225692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1588668823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7623920440674</t>
   </si>
   <si>
     <t xml:space="preserve">14.4080944061279</t>
@@ -2996,13 +2996,13 @@
     <t xml:space="preserve">13.5898370742798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1427478790283</t>
+    <t xml:space="preserve">13.142746925354</t>
   </si>
   <si>
     <t xml:space="preserve">12.7294006347656</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6028652191162</t>
+    <t xml:space="preserve">12.6028642654419</t>
   </si>
   <si>
     <t xml:space="preserve">12.906548500061</t>
@@ -3014,28 +3014,28 @@
     <t xml:space="preserve">13.1258764266968</t>
   </si>
   <si>
-    <t xml:space="preserve">13.513916015625</t>
+    <t xml:space="preserve">13.5139169692993</t>
   </si>
   <si>
     <t xml:space="preserve">13.9188270568848</t>
   </si>
   <si>
-    <t xml:space="preserve">13.319896697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5307874679565</t>
+    <t xml:space="preserve">13.3198957443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5307884216309</t>
   </si>
   <si>
     <t xml:space="preserve">12.8728065490723</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9318552017212</t>
+    <t xml:space="preserve">12.9318561553955</t>
   </si>
   <si>
     <t xml:space="preserve">12.7631425857544</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6366081237793</t>
+    <t xml:space="preserve">12.636607170105</t>
   </si>
   <si>
     <t xml:space="preserve">12.4172821044922</t>
@@ -3047,7 +3047,7 @@
     <t xml:space="preserve">12.6872224807739</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6619157791138</t>
+    <t xml:space="preserve">12.6619148254395</t>
   </si>
   <si>
     <t xml:space="preserve">12.7209644317627</t>
@@ -3056,10 +3056,10 @@
     <t xml:space="preserve">12.4678945541382</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1304683685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2823104858398</t>
+    <t xml:space="preserve">12.1304693222046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2823114395142</t>
   </si>
   <si>
     <t xml:space="preserve">12.3497953414917</t>
@@ -3074,40 +3074,40 @@
     <t xml:space="preserve">13.4126882553101</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3958177566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4464302062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7838563919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3114595413208</t>
+    <t xml:space="preserve">13.3958168029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4464311599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7838573455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3114604949951</t>
   </si>
   <si>
     <t xml:space="preserve">13.2271041870117</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9571619033813</t>
+    <t xml:space="preserve">12.9571628570557</t>
   </si>
   <si>
     <t xml:space="preserve">13.0752620697021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7040939331055</t>
+    <t xml:space="preserve">12.7040929794312</t>
   </si>
   <si>
     <t xml:space="preserve">12.7715787887573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4004096984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2148246765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0461130142212</t>
+    <t xml:space="preserve">12.400408744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.214825630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0461120605469</t>
   </si>
   <si>
     <t xml:space="preserve">11.8773994445801</t>
@@ -3119,16 +3119,16 @@
     <t xml:space="preserve">12.1642112731934</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2316961288452</t>
+    <t xml:space="preserve">12.2316970825195</t>
   </si>
   <si>
     <t xml:space="preserve">12.4510231018066</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3835382461548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2991819381714</t>
+    <t xml:space="preserve">12.3835391998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2991809844971</t>
   </si>
   <si>
     <t xml:space="preserve">11.8267850875854</t>
@@ -3137,7 +3137,7 @@
     <t xml:space="preserve">11.6749439239502</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6487464904785</t>
+    <t xml:space="preserve">11.6487474441528</t>
   </si>
   <si>
     <t xml:space="preserve">11.474102973938</t>
@@ -3146,25 +3146,25 @@
     <t xml:space="preserve">11.3693170547485</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8932476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9107131958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4346437454224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1028203964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0154991149902</t>
+    <t xml:space="preserve">11.8932485580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9107122421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.434642791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.102819442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0154981613159</t>
   </si>
   <si>
     <t xml:space="preserve">11.9805698394775</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1901435852051</t>
+    <t xml:space="preserve">12.1901416778564</t>
   </si>
   <si>
     <t xml:space="preserve">12.3298578262329</t>
@@ -3176,7 +3176,7 @@
     <t xml:space="preserve">12.3123931884766</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5963525772095</t>
+    <t xml:space="preserve">11.5963535308838</t>
   </si>
   <si>
     <t xml:space="preserve">11.4391746520996</t>
@@ -3185,10 +3185,10 @@
     <t xml:space="preserve">11.1946725845337</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7186050415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5788888931274</t>
+    <t xml:space="preserve">11.7186040878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5788898468018</t>
   </si>
   <si>
     <t xml:space="preserve">11.8408555984497</t>
@@ -3206,10 +3206,10 @@
     <t xml:space="preserve">11.7535333633423</t>
   </si>
   <si>
-    <t xml:space="preserve">11.49156665802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2645301818848</t>
+    <t xml:space="preserve">11.4915676116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2645292282104</t>
   </si>
   <si>
     <t xml:space="preserve">10.8104562759399</t>
@@ -3224,31 +3224,31 @@
     <t xml:space="preserve">11.3867807388306</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2470655441284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0374927520752</t>
+    <t xml:space="preserve">11.2470664978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0374937057495</t>
   </si>
   <si>
     <t xml:space="preserve">10.8453845977783</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3343868255615</t>
+    <t xml:space="preserve">11.3343877792358</t>
   </si>
   <si>
     <t xml:space="preserve">11.3169231414795</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4042453765869</t>
+    <t xml:space="preserve">11.4042463302612</t>
   </si>
   <si>
     <t xml:space="preserve">11.2296009063721</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6138172149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7884616851807</t>
+    <t xml:space="preserve">11.6138181686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.788462638855</t>
   </si>
   <si>
     <t xml:space="preserve">11.8233909606934</t>
@@ -3263,28 +3263,28 @@
     <t xml:space="preserve">11.4566383361816</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5439605712891</t>
+    <t xml:space="preserve">11.5439615249634</t>
   </si>
   <si>
     <t xml:space="preserve">11.4217090606689</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1073503494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0898866653442</t>
+    <t xml:space="preserve">11.1073513031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0898857116699</t>
   </si>
   <si>
     <t xml:space="preserve">10.7231340408325</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6882057189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6707401275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5135622024536</t>
+    <t xml:space="preserve">10.6882047653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6707410812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5135612487793</t>
   </si>
   <si>
     <t xml:space="preserve">10.2865238189697</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">10.2341318130493</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0594873428345</t>
+    <t xml:space="preserve">10.0594882965088</t>
   </si>
   <si>
     <t xml:space="preserve">10.1468095779419</t>
@@ -3302,16 +3302,16 @@
     <t xml:space="preserve">9.78005695343018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90230846405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81498527526855</t>
+    <t xml:space="preserve">9.90230751037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81498622894287</t>
   </si>
   <si>
     <t xml:space="preserve">9.76259326934814</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98962879180908</t>
+    <t xml:space="preserve">9.9896297454834</t>
   </si>
   <si>
     <t xml:space="preserve">10.1992025375366</t>
@@ -3326,13 +3326,13 @@
     <t xml:space="preserve">9.2211971282959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25612545013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0640172958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80205154418945</t>
+    <t xml:space="preserve">9.25612640380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06401634216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80205059051514</t>
   </si>
   <si>
     <t xml:space="preserve">8.81951522827148</t>
@@ -3341,13 +3341,13 @@
     <t xml:space="preserve">8.60121154785156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48769187927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19079875946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44403076171875</t>
+    <t xml:space="preserve">8.48769283294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19079780578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44403171539307</t>
   </si>
   <si>
     <t xml:space="preserve">8.46149635314941</t>
@@ -3359,13 +3359,13 @@
     <t xml:space="preserve">8.56628322601318</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34797668457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54881763458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59247970581055</t>
+    <t xml:space="preserve">8.34797763824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54881858825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59247875213623</t>
   </si>
   <si>
     <t xml:space="preserve">8.85444450378418</t>
@@ -3380,22 +3380,22 @@
     <t xml:space="preserve">9.01162433624268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83698081970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7321949005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02908897399902</t>
+    <t xml:space="preserve">8.83697986602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73219394683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02908802032471</t>
   </si>
   <si>
     <t xml:space="preserve">9.09894561767578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41330528259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30851936340332</t>
+    <t xml:space="preserve">9.41330432891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.308518409729</t>
   </si>
   <si>
     <t xml:space="preserve">9.27358913421631</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">9.39584064483643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72766399383545</t>
+    <t xml:space="preserve">9.72766494750977</t>
   </si>
   <si>
     <t xml:space="preserve">9.55301952362061</t>
@@ -3413,43 +3413,43 @@
     <t xml:space="preserve">9.622878074646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91977119445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2690601348877</t>
+    <t xml:space="preserve">9.91977214813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.269061088562</t>
   </si>
   <si>
     <t xml:space="preserve">9.65780639648438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64034175872803</t>
+    <t xml:space="preserve">9.64034271240234</t>
   </si>
   <si>
     <t xml:space="preserve">9.67527103424072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8324499130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0420236587524</t>
+    <t xml:space="preserve">9.83245086669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0420227050781</t>
   </si>
   <si>
     <t xml:space="preserve">9.69273567199707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93723678588867</t>
+    <t xml:space="preserve">9.93723773956299</t>
   </si>
   <si>
     <t xml:space="preserve">9.97216606140137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88484287261963</t>
+    <t xml:space="preserve">9.88484382629395</t>
   </si>
   <si>
     <t xml:space="preserve">9.8673791885376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0944156646729</t>
+    <t xml:space="preserve">10.0944166183472</t>
   </si>
   <si>
     <t xml:space="preserve">10.0769519805908</t>
@@ -3464,7 +3464,7 @@
     <t xml:space="preserve">10.0070943832397</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4437046051025</t>
+    <t xml:space="preserve">10.4437036514282</t>
   </si>
   <si>
     <t xml:space="preserve">10.6532764434814</t>
@@ -3473,16 +3473,16 @@
     <t xml:space="preserve">10.6358118057251</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7405977249146</t>
+    <t xml:space="preserve">10.7405986785889</t>
   </si>
   <si>
     <t xml:space="preserve">10.7580623626709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9152431488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0200290679932</t>
+    <t xml:space="preserve">10.9152421951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0200281143188</t>
   </si>
   <si>
     <t xml:space="preserve">11.3518524169922</t>
@@ -3497,7 +3497,7 @@
     <t xml:space="preserve">10.5310258865356</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6183481216431</t>
+    <t xml:space="preserve">10.6183471679688</t>
   </si>
   <si>
     <t xml:space="preserve">10.7056694030762</t>
@@ -3506,19 +3506,19 @@
     <t xml:space="preserve">10.6008834838867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.565954208374</t>
+    <t xml:space="preserve">10.5659551620483</t>
   </si>
   <si>
     <t xml:space="preserve">10.4786329269409</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1817378997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2166662216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0245571136475</t>
+    <t xml:space="preserve">10.1817388534546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.216667175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0245590209961</t>
   </si>
   <si>
     <t xml:space="preserve">9.84991455078125</t>
@@ -3527,16 +3527,16 @@
     <t xml:space="preserve">10.1118803024292</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5834188461304</t>
+    <t xml:space="preserve">10.5834178924561</t>
   </si>
   <si>
     <t xml:space="preserve">10.3563814163208</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5264949798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9456415176392</t>
+    <t xml:space="preserve">11.5264959335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9456405639648</t>
   </si>
   <si>
     <t xml:space="preserve">11.7011394500732</t>
@@ -3545,7 +3545,7 @@
     <t xml:space="preserve">12.1202850341797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.399715423584</t>
+    <t xml:space="preserve">12.3997144699097</t>
   </si>
   <si>
     <t xml:space="preserve">11.9281768798828</t>
@@ -3566,16 +3566,16 @@
     <t xml:space="preserve">13.1681480407715</t>
   </si>
   <si>
-    <t xml:space="preserve">13.063362121582</t>
+    <t xml:space="preserve">13.0633630752563</t>
   </si>
   <si>
     <t xml:space="preserve">12.8712539672852</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6442155838013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9491119384766</t>
+    <t xml:space="preserve">12.6442165374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9491128921509</t>
   </si>
   <si>
     <t xml:space="preserve">13.0746583938599</t>
@@ -3584,13 +3584,13 @@
     <t xml:space="preserve">12.9132423400879</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0387878417969</t>
+    <t xml:space="preserve">13.0387887954712</t>
   </si>
   <si>
     <t xml:space="preserve">13.0567235946655</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1284637451172</t>
+    <t xml:space="preserve">13.1284627914429</t>
   </si>
   <si>
     <t xml:space="preserve">13.2540082931519</t>
@@ -3605,7 +3605,7 @@
     <t xml:space="preserve">13.5947751998901</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4871635437012</t>
+    <t xml:space="preserve">13.4871644973755</t>
   </si>
   <si>
     <t xml:space="preserve">13.4512939453125</t>
@@ -3620,7 +3620,7 @@
     <t xml:space="preserve">13.5051002502441</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2002038955688</t>
+    <t xml:space="preserve">13.2002029418945</t>
   </si>
   <si>
     <t xml:space="preserve">12.9849824905396</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">12.5366058349609</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4110612869263</t>
+    <t xml:space="preserve">12.411060333252</t>
   </si>
   <si>
     <t xml:space="preserve">12.2496452331543</t>
@@ -3680,7 +3680,7 @@
     <t xml:space="preserve">12.285514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2675809860229</t>
+    <t xml:space="preserve">12.2675800323486</t>
   </si>
   <si>
     <t xml:space="preserve">12.6262817382812</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">12.5724763870239</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2137746810913</t>
+    <t xml:space="preserve">12.2137756347656</t>
   </si>
   <si>
     <t xml:space="preserve">12.5007352828979</t>
@@ -3704,10 +3704,10 @@
     <t xml:space="preserve">11.2990875244141</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5681133270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.639853477478</t>
+    <t xml:space="preserve">11.5681123733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6398525238037</t>
   </si>
   <si>
     <t xml:space="preserve">11.675724029541</t>
@@ -3719,22 +3719,22 @@
     <t xml:space="preserve">11.6577882766724</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4605026245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3708276748657</t>
+    <t xml:space="preserve">11.4605016708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.37082862854</t>
   </si>
   <si>
     <t xml:space="preserve">11.3528928756714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3349571228027</t>
+    <t xml:space="preserve">11.3349580764771</t>
   </si>
   <si>
     <t xml:space="preserve">11.2811527252197</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4963731765747</t>
+    <t xml:space="preserve">11.4963722229004</t>
   </si>
   <si>
     <t xml:space="preserve">11.5501775741577</t>
@@ -3749,16 +3749,16 @@
     <t xml:space="preserve">11.8012685775757</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7833347320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.908878326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9268140792847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.016489982605</t>
+    <t xml:space="preserve">11.7833337783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9088792800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.926815032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0164890289307</t>
   </si>
   <si>
     <t xml:space="preserve">12.0882301330566</t>
@@ -3797,7 +3797,7 @@
     <t xml:space="preserve">10.5278797149658</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7610359191895</t>
+    <t xml:space="preserve">10.7610349655151</t>
   </si>
   <si>
     <t xml:space="preserve">10.5816850662231</t>
@@ -3812,7 +3812,7 @@
     <t xml:space="preserve">10.2947235107422</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3664636611938</t>
+    <t xml:space="preserve">10.3664646148682</t>
   </si>
   <si>
     <t xml:space="preserve">10.2229833602905</t>
@@ -3833,19 +3833,19 @@
     <t xml:space="preserve">9.86428260803223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68493175506592</t>
+    <t xml:space="preserve">9.68493270874023</t>
   </si>
   <si>
     <t xml:space="preserve">9.75667190551758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77460765838623</t>
+    <t xml:space="preserve">9.77460670471191</t>
   </si>
   <si>
     <t xml:space="preserve">9.70286750793457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79254245758057</t>
+    <t xml:space="preserve">9.79254150390625</t>
   </si>
   <si>
     <t xml:space="preserve">9.66699695587158</t>
@@ -3860,7 +3860,7 @@
     <t xml:space="preserve">10.0436325073242</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1871128082275</t>
+    <t xml:space="preserve">10.1871137619019</t>
   </si>
   <si>
     <t xml:space="preserve">10.5099449157715</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">10.7431001663208</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8148403167725</t>
+    <t xml:space="preserve">10.8148412704468</t>
   </si>
   <si>
     <t xml:space="preserve">10.4740753173828</t>
@@ -3881,7 +3881,7 @@
     <t xml:space="preserve">9.9001522064209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95395851135254</t>
+    <t xml:space="preserve">9.95395755767822</t>
   </si>
   <si>
     <t xml:space="preserve">10.0795030593872</t>
@@ -3893,7 +3893,7 @@
     <t xml:space="preserve">9.98982810974121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2588529586792</t>
+    <t xml:space="preserve">10.2588539123535</t>
   </si>
   <si>
     <t xml:space="preserve">10.3126592636108</t>
@@ -3905,7 +3905,7 @@
     <t xml:space="preserve">10.4561395645142</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3305940628052</t>
+    <t xml:space="preserve">10.3305950164795</t>
   </si>
   <si>
     <t xml:space="preserve">10.2050485610962</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">9.91808795928955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88221836090088</t>
+    <t xml:space="preserve">9.88221740722656</t>
   </si>
   <si>
     <t xml:space="preserve">10.0974388122559</t>
@@ -3941,31 +3941,31 @@
     <t xml:space="preserve">9.3262300491333</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45177555084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5996198654175</t>
+    <t xml:space="preserve">9.4517765045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5996189117432</t>
   </si>
   <si>
     <t xml:space="preserve">9.93602275848389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4920091629028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5637493133545</t>
+    <t xml:space="preserve">10.4920101165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5637502670288</t>
   </si>
   <si>
     <t xml:space="preserve">10.4382047653198</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6713600158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9045162200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8327760696411</t>
+    <t xml:space="preserve">10.6713590621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9045152664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8327751159668</t>
   </si>
   <si>
     <t xml:space="preserve">10.7251653671265</t>
@@ -3980,7 +3980,7 @@
     <t xml:space="preserve">10.9224510192871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6892957687378</t>
+    <t xml:space="preserve">10.6892948150635</t>
   </si>
   <si>
     <t xml:space="preserve">11.2094125747681</t>
@@ -4662,6 +4662,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.92000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88000011444092</t>
   </si>
 </sst>
 </file>
@@ -70546,7 +70549,7 @@
     </row>
     <row r="2522">
       <c r="A2522" s="1" t="n">
-        <v>45989.6910416667</v>
+        <v>45989.3333333333</v>
       </c>
       <c r="B2522" t="n">
         <v>75271</v>
@@ -70567,6 +70570,32 @@
         <v>1549</v>
       </c>
       <c r="H2522" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2523">
+      <c r="A2523" s="1" t="n">
+        <v>45992.691099537</v>
+      </c>
+      <c r="B2523" t="n">
+        <v>66059</v>
+      </c>
+      <c r="C2523" t="n">
+        <v>8.92000007629395</v>
+      </c>
+      <c r="D2523" t="n">
+        <v>8.77000045776367</v>
+      </c>
+      <c r="E2523" t="n">
+        <v>8.89999961853027</v>
+      </c>
+      <c r="F2523" t="n">
+        <v>8.88000011444092</v>
+      </c>
+      <c r="G2523" t="s">
+        <v>1550</v>
+      </c>
+      <c r="H2523" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARR.MI.xlsx
+++ b/data/MARR.MI.xlsx
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4479513168335</t>
+    <t xml:space="preserve">13.4479494094849</t>
   </si>
   <si>
     <t xml:space="preserve">MARR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2894020080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1812973022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9939212799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9506797790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5903377532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6551990509033</t>
+    <t xml:space="preserve">13.289400100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1812992095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9939203262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9506788253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5903387069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.655198097229</t>
   </si>
   <si>
     <t xml:space="preserve">12.7344751358032</t>
@@ -68,40 +68,40 @@
     <t xml:space="preserve">12.4389934539795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4462003707886</t>
+    <t xml:space="preserve">12.4462022781372</t>
   </si>
   <si>
     <t xml:space="preserve">11.9849634170532</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0858592987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6462421417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2155828475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8353691101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6768207550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5615110397339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5543022155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6407861709595</t>
+    <t xml:space="preserve">12.0858602523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6462430953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2155847549438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8353700637817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6768188476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5615091323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5543041229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6407852172852</t>
   </si>
   <si>
     <t xml:space="preserve">12.7200593948364</t>
   </si>
   <si>
-    <t xml:space="preserve">12.97230052948</t>
+    <t xml:space="preserve">12.9722986221313</t>
   </si>
   <si>
     <t xml:space="preserve">12.7777156829834</t>
@@ -113,70 +113,70 @@
     <t xml:space="preserve">12.5110645294189</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2948570251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4084177017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4516582489014</t>
+    <t xml:space="preserve">12.2948579788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4084167480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4516592025757</t>
   </si>
   <si>
     <t xml:space="preserve">11.8840675354004</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5885877609253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8912725448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9273080825806</t>
+    <t xml:space="preserve">11.588586807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8912754058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9273090362549</t>
   </si>
   <si>
     <t xml:space="preserve">12.0426177978516</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2011690139771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3957538604736</t>
+    <t xml:space="preserve">12.2011699676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3957529067993</t>
   </si>
   <si>
     <t xml:space="preserve">12.7056455612183</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6047506332397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5759248733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9362659454346</t>
+    <t xml:space="preserve">12.6047515869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5759229660034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9362678527832</t>
   </si>
   <si>
     <t xml:space="preserve">13.1596765518188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9434719085693</t>
+    <t xml:space="preserve">12.9434728622437</t>
   </si>
   <si>
     <t xml:space="preserve">13.0731954574585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8858165740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.597544670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.078652381897</t>
+    <t xml:space="preserve">12.885817527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5975427627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0786533355713</t>
   </si>
   <si>
     <t xml:space="preserve">12.3597192764282</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6696119308472</t>
+    <t xml:space="preserve">12.6696128845215</t>
   </si>
   <si>
     <t xml:space="preserve">12.8137502670288</t>
@@ -185,31 +185,31 @@
     <t xml:space="preserve">12.6984405517578</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8714056015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4534072875977</t>
+    <t xml:space="preserve">12.8714046478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4534091949463</t>
   </si>
   <si>
     <t xml:space="preserve">12.3453044891357</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6840257644653</t>
+    <t xml:space="preserve">12.6840267181396</t>
   </si>
   <si>
     <t xml:space="preserve">12.7560958862305</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1524705886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2677812576294</t>
+    <t xml:space="preserve">13.1524696350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2677803039551</t>
   </si>
   <si>
     <t xml:space="preserve">13.3326416015625</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0804004669189</t>
+    <t xml:space="preserve">13.0804014205933</t>
   </si>
   <si>
     <t xml:space="preserve">13.1885051727295</t>
@@ -218,55 +218,55 @@
     <t xml:space="preserve">13.2605724334717</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7073974609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.491192817688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.347056388855</t>
+    <t xml:space="preserve">13.7073984146118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4911918640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3470544815063</t>
   </si>
   <si>
     <t xml:space="preserve">13.001127243042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9002313613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8281621932983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7921314239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0587816238403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1020221710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8065414428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2821941375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1380558013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8425760269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8930253982544</t>
+    <t xml:space="preserve">12.9002323150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8281631469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7921295166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.058783531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1020231246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.806544303894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2821931838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1380577087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8425779342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8930234909058</t>
   </si>
   <si>
     <t xml:space="preserve">12.9074373245239</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0227470397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6624059677124</t>
+    <t xml:space="preserve">13.0227489471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6624050140381</t>
   </si>
   <si>
     <t xml:space="preserve">12.8786115646362</t>
@@ -275,139 +275,139 @@
     <t xml:space="preserve">12.6335783004761</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7488870620728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0258750915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0183897018433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.25794506073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2504606246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4301290512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4825286865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3103494644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2654314041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4750442504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3702402114868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2878913879395</t>
+    <t xml:space="preserve">12.7488889694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0258741378784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0183877944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2579460144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2504596710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4301261901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4825305938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3103485107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2654294967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4750423431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3702383041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2878904342651</t>
   </si>
   <si>
     <t xml:space="preserve">13.2729177474976</t>
   </si>
   <si>
-    <t xml:space="preserve">13.280403137207</t>
+    <t xml:space="preserve">13.2804040908813</t>
   </si>
   <si>
     <t xml:space="preserve">12.8012914657593</t>
   </si>
   <si>
-    <t xml:space="preserve">12.883638381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6141376495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3146934509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.44944190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8087768554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7938032150269</t>
+    <t xml:space="preserve">12.8836374282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6141386032104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3146924972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4494428634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8087778091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7938051223755</t>
   </si>
   <si>
     <t xml:space="preserve">13.0782785415649</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4419584274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7831773757935</t>
+    <t xml:space="preserve">12.4419574737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7831764221191</t>
   </si>
   <si>
     <t xml:space="preserve">12.2847480773926</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7339162826538</t>
+    <t xml:space="preserve">12.7339153289795</t>
   </si>
   <si>
     <t xml:space="preserve">13.4226408004761</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5274457931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0558195114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4525852203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3328056335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7595167160034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7295713424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7220859527588</t>
+    <t xml:space="preserve">13.5274477005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0558204650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4525842666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3328065872192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7595157623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7295742034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7220869064331</t>
   </si>
   <si>
     <t xml:space="preserve">13.5349340438843</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4900178909302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7370576858521</t>
+    <t xml:space="preserve">13.4900140762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7370586395264</t>
   </si>
   <si>
     <t xml:space="preserve">14.014045715332</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7071123123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8493499755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.111364364624</t>
+    <t xml:space="preserve">13.7071142196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8493490219116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1113653182983</t>
   </si>
   <si>
     <t xml:space="preserve">13.9766130447388</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0814208984375</t>
+    <t xml:space="preserve">14.0814199447632</t>
   </si>
   <si>
     <t xml:space="preserve">13.7445459365845</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9990720748901</t>
+    <t xml:space="preserve">13.9990739822388</t>
   </si>
   <si>
     <t xml:space="preserve">13.5049877166748</t>
@@ -416,46 +416,46 @@
     <t xml:space="preserve">13.6397380828857</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6621971130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6097927093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3477792739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4151563644409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.220513343811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0857639312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1007375717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0633068084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2354869842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1456527709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9285545349121</t>
+    <t xml:space="preserve">13.6621961593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6097936630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3477783203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4151544570923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.220516204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0857620239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.100736618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.063304901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2354888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1456508636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9285573959351</t>
   </si>
   <si>
     <t xml:space="preserve">13.2055425643921</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1082220077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1980543136597</t>
+    <t xml:space="preserve">13.1082229614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1980562210083</t>
   </si>
   <si>
     <t xml:space="preserve">13.1157083511353</t>
@@ -464,31 +464,31 @@
     <t xml:space="preserve">13.0109024047852</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9135828018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8611812591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9435291290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1905698776245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4076681137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3552646636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2130270004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3402919769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9659872055054</t>
+    <t xml:space="preserve">12.9135847091675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.861180305481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.943528175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1905708312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4076671600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3552665710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2130279541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3402948379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9659843444824</t>
   </si>
   <si>
     <t xml:space="preserve">12.8761529922485</t>
@@ -506,37 +506,37 @@
     <t xml:space="preserve">12.7114572525024</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8686676025391</t>
+    <t xml:space="preserve">12.8686666488647</t>
   </si>
   <si>
     <t xml:space="preserve">12.7563753128052</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7488889694214</t>
+    <t xml:space="preserve">12.7488880157471</t>
   </si>
   <si>
     <t xml:space="preserve">12.6815137863159</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5767059326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5467624664307</t>
+    <t xml:space="preserve">12.5767068862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.546763420105</t>
   </si>
   <si>
     <t xml:space="preserve">12.5317907333374</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5617361068726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5542488098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4194984436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2772617340088</t>
+    <t xml:space="preserve">12.5617351531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5542497634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4194974899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2772607803345</t>
   </si>
   <si>
     <t xml:space="preserve">12.4719009399414</t>
@@ -548,28 +548,28 @@
     <t xml:space="preserve">12.3970403671265</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9778156280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3596086502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4943599700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3820676803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4045257568359</t>
+    <t xml:space="preserve">11.9778175354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3596096038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4943618774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3820686340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4045267105103</t>
   </si>
   <si>
     <t xml:space="preserve">12.269775390625</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1649684906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2548055648804</t>
+    <t xml:space="preserve">12.1649694442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2548046112061</t>
   </si>
   <si>
     <t xml:space="preserve">12.3371505737305</t>
@@ -581,1846 +581,1846 @@
     <t xml:space="preserve">12.72642993927</t>
   </si>
   <si>
+    <t xml:space="preserve">12.6740283966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7863187789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0932502746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9510126113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1306810379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9884443283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1381664276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1606245040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.183084487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1681108474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2280015945435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0034160614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1755990982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.400182723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3852100372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8643207550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9167232513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5199613571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4450988769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3627519607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4600706100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5124731063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.437614440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8268928527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6247673034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8044328689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7819738388062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6996269226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8418645858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6771678924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8568363189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7670021057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5648784637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.89426612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3359479904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5605344772339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5156183242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6952838897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9722709655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9348411560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.942325592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8225479125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2043390274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.713399887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1369667053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1594247817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2866868972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3615503311157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2267990112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3465795516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6834545135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7208843231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5337324142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4588680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1669101715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1968517303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5487051010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4214382171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6011056900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6460208892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7358570098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5861330032349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9080381393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4245834350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1251335144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6984252929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2823448181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3272609710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2598857879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.267370223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5967597961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7839183807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6641387939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5219020843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4470367431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6416759490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0758762359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7988891601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7464866638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8737468719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9560947418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1058216094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3946342468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.506929397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6847534179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1950416564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1641120910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0094814300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7620697021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6306324005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8471183776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0249443054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9398956298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7698001861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9940185546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1254539489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.955358505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5455856323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7156791687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8548488616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7466068267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0404071807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7311420440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5378532409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5687808990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6229019165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7079486846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7234115600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1822032928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0894222259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0816898345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1590042114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9347925186157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2363224029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0739593505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9966440200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3909530639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4914665222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8935089111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2414283752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0558700561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2878189086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2955493927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3960590362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8316555023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.280086517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7002182006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5533180236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4837322235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7775325775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5146579742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3832244873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3986854553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2749824523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2285919189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0584964752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9657163619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9502515792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0353012084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2827129364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4141483306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6074390411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5919742584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.932165145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0481395721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2646236419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9476280212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0713329315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0636024475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.079065322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2723560333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3032817840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3728618621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3187465667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5584239959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5893497467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4656448364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7207870483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5738849639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5429611206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6975917816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.107364654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0377807617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6125450134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.68212890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5197658538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3110103607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.109992980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.357400894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1795768737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1409168243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0867977142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8857765197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6151695251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5301208496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3522968292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0430335998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.826548576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9270610809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1976680755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6692905426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8703117370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7852649688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9630928039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8084602355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9244327545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4218788146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0507659912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4605407714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4528064727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.754337310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6383666992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7929954528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4064159393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3342094421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3805980682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4888401031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5506954193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6898593902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4115238189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6434707641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.256893157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2259654998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5043029785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.499195098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9785537719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3445625305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2981739044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9012413024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.653829574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2672500610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3136367797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4269866943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4475555419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3857021331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.880521774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1433982849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0042285919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.911449432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6949653625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6795024871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7413539886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6640377044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7877445220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2516422271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.437198638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3444213867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4062728881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5609016418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3289585113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1743259429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1124687194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.158863067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2825660705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.236177444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2052516937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2671051025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5299777984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.638219833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5918292999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4835872650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5145149230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4526634216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6072940826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1382904052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3547763824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0764389038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0300483703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1737785339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9501991271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3654174804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.205717086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6209392547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.509147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5889987945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.557056427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4931774139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1578102111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4292984008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6848163604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6369075775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4133262634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4612407684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3175086975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8064708709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8224411010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7106533050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9182586669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9661712646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8863201141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9981117248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3973579406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5251178741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4452686309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1479454040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1639156341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0201854705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8604869842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7806377410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5730266571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.06809425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7646675109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4772090911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7007865905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2437648773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4513721466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4992828369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2118225097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1319732666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0042171478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1160049438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0361576080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1798839569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3236141204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3395843505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3076457977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7228622436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.467342376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3874969482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5631637573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8825626373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3616580963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4415092468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2658405303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7609081268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0962753295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8247890472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.249870300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4734477996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1540508270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1700210571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7548007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5312232971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4034633636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8125762939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7327270507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3813896179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2536296844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9342308044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3494491577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9243659973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7486972808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1258716583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7905006408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4391632080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1357326507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2155857086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9760341644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5509548187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8961868286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0718536376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.928129196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8323059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0558853149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1836452484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4551334381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8163356781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3532085418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9858999252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0976867675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1136589050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4269523620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3311338424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6505289077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4748620986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4429225921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7703037261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8421678543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7383651733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4490280151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2733592987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1615695953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3212699890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4809665679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6246967315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.768424987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1676750183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3433418273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2794628143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9440956115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0079727172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6406669616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.241418838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5608177185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7045459747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8482761383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3752822875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1037921905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8802146911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9121551513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8642463684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7205142974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6885757446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6087265014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7364864349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3052978515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8980646133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1935062408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2094783782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3851470947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2893295288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2573890686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2254467010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9140338897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4170875549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5288772583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7843971252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5767860412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.369176864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1775379180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4889526367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2494010925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3292541503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4091014862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1695556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0497779846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5688018798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6486511230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2874488830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0878238677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0479011535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.808349609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9680500030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7285003662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8882026672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1277503967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8793506622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0452423095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9208221435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7964038848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2111301422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1281833648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1696586608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.418493270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3770217895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4599666595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.294075012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9622955322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7549324035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6305141448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3402099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4895076751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5392742156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7088012695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.667329788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5014400482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5429096221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2526035308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7134590148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4231510162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3733825683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2406711578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.17431640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2738513946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.124547958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3070278167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8591232299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7264099121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7927665710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.074779510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5273418426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.427809715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6600551605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1789722442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3614521026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6932344436646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6102876663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4609870910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4443988800049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.378041267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2950983047485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.925479888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2904396057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3899726867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4397392272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6719875335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9576377868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0867118835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3355464935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8378772735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5890407562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2572593688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.875714302063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9088916778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1577281951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1411361694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4729194641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7595911026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6766424179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5936985015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4775762557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7430009841919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7098236083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8425350189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3567924499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.323616027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.975248336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5843849182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0037670135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2240810394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0084247589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1909046173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5558624267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.532000541687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7974262237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1836309432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9347953796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6361932754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4371242523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2712335586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3873558044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7616319656372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9607000350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4251918792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0317125320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4796171188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1690826416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3681516647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95342445373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3183822631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8777532577515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4417810440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8565082550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1763563156128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2924785614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2141923904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9155893325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6667537689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.202260017395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.451096534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5174522399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5340414047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4013290405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1524934768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0529594421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97001457214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4676856994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6999320983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3017950057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0695476531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2520275115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0031929016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0363702774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1193151473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92024707794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45575332641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50552082061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32304096221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14056301116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07420539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68800067901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1359043121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70458984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38939762115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4345073699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2188501358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4179191589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.99853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.899001121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9819450378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8160543441772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8824119567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8113965988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7782192230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5957403182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3634929656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6833429336548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9487676620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9653558731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2639579772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2805490493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1810140609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3303146362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.297137260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0814809799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0151243209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0648908615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8326444625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.849232673645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5838088989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3847398757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6501655578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3515615463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2354383468628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9321784973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5506296157837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5008630752563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6169862747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4842748641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0197811126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3349733352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7828769683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6003971099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1312465667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4132604598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4298486709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2307806015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8658227920532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3137273788452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.396671295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5127944946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8611640930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2095355987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9772882461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0602331161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2593011856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3800830841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1146574020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6335754394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2686166763306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55528831481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62164402008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65482234954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60505485534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75435733795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.491548538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0058088302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.192946434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8399181365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3209991455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4086036682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2758922576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7237939834595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9062747955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1053428649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9892206192017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0721645355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0223979949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0887537002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.038987159729</t>
+  </si>
+  <si>
     <t xml:space="preserve">12.6740274429321</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7863178253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0932502746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9510126113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1306810379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9884452819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.138165473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1606254577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1830854415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1681118011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2280006408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.00341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1755981445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4001808166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3852081298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8643236160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9167251586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5199594497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4450979232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3627519607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4600696563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5124750137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4376125335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8268928527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6247663497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8044347763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7819757461548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6996288299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8418655395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.677170753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8568344116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7670030593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5648756027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8942670822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3359498977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5605344772339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5156145095825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6952819824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9722709655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9348402023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9423236846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8225469589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2043399810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.713399887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1369657516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.159423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2866878509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3615503311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2267971038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3465766906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6834516525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7208843231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5337295532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588689804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1669082641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1968536376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5487070083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4214363098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6011075973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6460237503052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7358560562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5861330032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9080371856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.42458152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1251354217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6984224319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.282341003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3272571563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2598838806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.267370223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5967597961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.78391456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6641387939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.521900177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4470386505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6416778564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.075870513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.798885345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7464847564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8737487792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9560947418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1058197021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3946380615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5069274902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6847534179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1950378417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1641139984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0094795227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7620697021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6306324005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8471221923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0249423980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9398956298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7698001861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9940204620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1254558563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9553604125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5455875396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7156810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.854850769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7466068267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0404090881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7311420440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5378551483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5687828063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6228981018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7079486846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7234115600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1822032928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0894222259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0816898345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.159008026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9347896575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2363204956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0739593505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9966449737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3909530639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4914646148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8935089111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2414264678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0558681488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2878170013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2955513000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3960571289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8316555023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2800884246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7002201080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5533180236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4837341308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7775325775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5146598815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3832244873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3986854553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2749805450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2285919189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0584983825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9657163619995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.950252532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0353012084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2827110290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4141483306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6074371337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5919761657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.932165145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0481357574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2646236419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9476280212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0713329315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0636024475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.079065322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2723598480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.303279876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3728637695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3187446594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5584239959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5893497467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4656467437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7207832336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5738868713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5429611206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6975917816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.107364654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0377807617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6125431060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6821308135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5197639465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3110103607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1099910736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3574028015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1795749664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1409168243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0867977142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8857765197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6151695251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.530122756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.352294921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0430335998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8265476226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9270582199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1976642608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6692886352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8703136444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7852649688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9630908966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8084621429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.924430847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4218826293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0507659912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4605407714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.452808380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7543392181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6383647918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7929954528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4064159393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3342056274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3805980682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.488842010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5506935119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6898593902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4115238189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6434726715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.256893157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2259654998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.504301071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.499195098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9785537719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3445625305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2981739044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9012393951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.653829574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2672500610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3136405944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4269866943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4475536346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3857040405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.880521774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1434001922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0042285919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9114513397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6949672698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6795024871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7413558959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6640377044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7877445220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2516403198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4372005462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3444175720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.406270980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5608997344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3289566040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1743240356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1124706268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.158863067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2825660705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2361755371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.205249786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2671031951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5299777984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6382179260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5918292999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4835891723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5145130157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4526596069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.607292175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1382884979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3547782897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0764389038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.03005027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1737804412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9501991271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.365421295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.205717086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6209354400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5091495513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5890007019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5570583343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4931774139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1578102111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4293003082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6848182678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6369075775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.413330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4612369537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3175086975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8064708709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8224411010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7106513977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9182624816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9661712646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8863201141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9981117248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3973598480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5251197814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4452686309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1479434967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1639137268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0201854705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8604888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7806396484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5730266571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.06809425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7646675109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4772090911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7007884979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2437648773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4513740539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4992828369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2118244171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1319732666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0042133331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1160068511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0361557006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1798858642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3236122131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3395843505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3076438903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7228622436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.467342376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3874931335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.563159942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8825607299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3616619110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4415092468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2658386230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7609081268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0962772369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8247871398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.249870300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4734497070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1540508270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1700210571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7548007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5312252044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4034633636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8125762939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7327251434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3813877105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2536315917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9342308044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3494491577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9243659973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7486972808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1258716583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7905006408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4391613006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1357345581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2155838012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9760360717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.550952911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8961849212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0718536376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9281253814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8323059082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0558853149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1836452484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4551315307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.816333770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3532066345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9858999252319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0976886749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1136589050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4269523620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3311319351196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6505308151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4748620986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4429235458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7703046798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8421716690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7383661270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4490242004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2733554840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1615695953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.321268081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4809665679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6246948242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.768424987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1676731109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3433437347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2794628143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9440937042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0079746246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6406650543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.241418838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5608158111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7045459747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8482780456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3752841949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.103796005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8802127838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9121551513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8642463684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7205181121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6885738372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6087245941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7364826202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3052959442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8980627059937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1935081481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2094745635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3851451873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.28932762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2573890686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2254467010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9140357971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4170875549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5288753509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7843971252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5767860412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.369176864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1775379180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4889507293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2494029998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.329252243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4091033935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1695518493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0497779846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5688018798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6486492156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2874507904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0878219604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0479011535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8083515167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9680500030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7285022735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8881988525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1277503967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8793487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0452404022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9208221435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7964038848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2111301422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1281833648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.16965675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.418493270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3770217895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4599666595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2940731048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9622936248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7549324035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6305141448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3402099609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4895076751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5392761230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7088031768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.667329788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5014419555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5429096221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2526016235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7134571075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4231510162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.373384475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2406711578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.17431640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.273853302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.124547958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3070278167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8591251373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.726411819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7927684783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0747814178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5273418426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4278106689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6600551605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.178973197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3614530563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6932325363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6102895736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4609870910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4443988800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.378041267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2950983047485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.925479888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2904376983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3899726867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4397411346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6719856262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9576396942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0867099761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3355464935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8378734588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5890407562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2572612762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8757123947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9088935852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1577281951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1411380767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4729194641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7595911026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6766443252563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5936985015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4775762557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7430009841919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7098236083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8425369262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3567943572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3236179351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.975248336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5843849182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0037670135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2240829467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0084247589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1909065246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5558624267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5319995880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7974252700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1836309432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9347944259644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6361932754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4371242523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2712326049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.387354850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7616319656372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9606990814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4251918792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0317134857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4796161651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1690816879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3681516647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95342445373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3183832168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8777532577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4417810440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8565082550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1763563156128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2924785614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2141933441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9155893325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6667547225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.202260017395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.451096534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5174522399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5340414047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4013290405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1524925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0529594421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97001361846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4676847457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6999320983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3017950057983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0695476531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2520265579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.003191947937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0363693237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1193151473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92024707794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4557523727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50552082061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32304096221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14056301116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07420539855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68800163269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1359043121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38939762115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4345073699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2188491821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4179182052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.99853515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8990001678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9819450378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8160543441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8824119567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8113965988159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7782182693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.595739364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3634929656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6833419799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9487676620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9653568267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2639589309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2805490493774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1810150146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3303155899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.297137260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0814800262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0151243209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0648918151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8326444625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8492336273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5838088989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3847398757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.650164604187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3515615463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2354383468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9321794509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5506296157837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5008640289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6169862747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4842748641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0197811126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3349733352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7828769683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6003971099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1312465667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4132604598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4298486709595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2307815551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8658227920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3137264251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.396671295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5127944946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8611640930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2095346450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9772882461548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0602340698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2593011856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3800821304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1146574020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6335754394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2686166763306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55528831481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62164497375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65482330322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60505485534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75435829162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4915494918823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0058088302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1929454803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8399181365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3209991455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4086036682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2758922576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7237949371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9062738418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1053428649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9892196655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0721654891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0223970413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0887537002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0389862060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6740283966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4583711624146</t>
+    <t xml:space="preserve">12.4583692550659</t>
   </si>
   <si>
     <t xml:space="preserve">12.5081377029419</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7403841018677</t>
+    <t xml:space="preserve">12.7403831481934</t>
   </si>
   <si>
     <t xml:space="preserve">12.3754253387451</t>
@@ -2429,31 +2429,31 @@
     <t xml:space="preserve">12.4749593734741</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6574382781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9560403823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9228630065918</t>
+    <t xml:space="preserve">12.6574373245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9560413360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9228639602661</t>
   </si>
   <si>
     <t xml:space="preserve">13.536657333374</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9845628738403</t>
+    <t xml:space="preserve">13.984561920166</t>
   </si>
   <si>
     <t xml:space="preserve">14.3661098480225</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5817670822144</t>
+    <t xml:space="preserve">14.5817680358887</t>
   </si>
   <si>
     <t xml:space="preserve">14.6978902816772</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7642469406128</t>
+    <t xml:space="preserve">14.7642459869385</t>
   </si>
   <si>
     <t xml:space="preserve">14.6315336227417</t>
@@ -2465,19 +2465,19 @@
     <t xml:space="preserve">14.4324655532837</t>
   </si>
   <si>
-    <t xml:space="preserve">14.780834197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7476577758789</t>
+    <t xml:space="preserve">14.7808361053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7476587295532</t>
   </si>
   <si>
     <t xml:space="preserve">14.4988212585449</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3495206832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2499885559082</t>
+    <t xml:space="preserve">14.3495216369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2499876022339</t>
   </si>
   <si>
     <t xml:space="preserve">14.2333974838257</t>
@@ -2486,22 +2486,22 @@
     <t xml:space="preserve">13.785493850708</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0177402496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0509176254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2831659317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0462589263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9301376342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3946294784546</t>
+    <t xml:space="preserve">14.0177392959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0509185791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2831649780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0462579727173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.930136680603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3946285247803</t>
   </si>
   <si>
     <t xml:space="preserve">15.3448629379272</t>
@@ -2510,16 +2510,16 @@
     <t xml:space="preserve">15.9918365478516</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8969573974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9799041748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9135465621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9964952468872</t>
+    <t xml:space="preserve">14.8969583511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9799032211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9135475158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9964942932129</t>
   </si>
   <si>
     <t xml:space="preserve">15.825945854187</t>
@@ -2531,19 +2531,19 @@
     <t xml:space="preserve">16.0250148773193</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0913715362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0581912994385</t>
+    <t xml:space="preserve">16.0913696289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0581932067871</t>
   </si>
   <si>
     <t xml:space="preserve">15.5605211257935</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0130825042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2619171142578</t>
+    <t xml:space="preserve">15.0130834579468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2619199752808</t>
   </si>
   <si>
     <t xml:space="preserve">15.2287406921387</t>
@@ -2552,43 +2552,43 @@
     <t xml:space="preserve">15.1457948684692</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4941663742065</t>
+    <t xml:space="preserve">15.4941625595093</t>
   </si>
   <si>
     <t xml:space="preserve">15.6268758773804</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2121505737305</t>
+    <t xml:space="preserve">15.2121486663818</t>
   </si>
   <si>
     <t xml:space="preserve">15.502459526062</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2702131271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2536239624023</t>
+    <t xml:space="preserve">15.2702121734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.253623008728</t>
   </si>
   <si>
     <t xml:space="preserve">15.5439329147339</t>
   </si>
   <si>
-    <t xml:space="preserve">15.577112197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.850830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7181167602539</t>
+    <t xml:space="preserve">15.5771102905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8508319854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7181186676025</t>
   </si>
   <si>
     <t xml:space="preserve">15.7347059249878</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8840093612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.751296043396</t>
+    <t xml:space="preserve">15.8840074539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7512941360474</t>
   </si>
   <si>
     <t xml:space="preserve">15.4361038208008</t>
@@ -2597,13 +2597,13 @@
     <t xml:space="preserve">16.3982696533203</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5807476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8674192428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0830745697021</t>
+    <t xml:space="preserve">16.5807456970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8674173355103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0830764770508</t>
   </si>
   <si>
     <t xml:space="preserve">16.1079597473145</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">16.7051639556885</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9042301177979</t>
+    <t xml:space="preserve">16.9042320251465</t>
   </si>
   <si>
     <t xml:space="preserve">16.9374103546143</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">17.4350833892822</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4516716003418</t>
+    <t xml:space="preserve">17.4516735076904</t>
   </si>
   <si>
     <t xml:space="preserve">17.219425201416</t>
@@ -2645,7 +2645,7 @@
     <t xml:space="preserve">16.7217540740967</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1530685424805</t>
+    <t xml:space="preserve">17.1530666351318</t>
   </si>
   <si>
     <t xml:space="preserve">17.0535354614258</t>
@@ -2660,10 +2660,10 @@
     <t xml:space="preserve">16.771520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8544654846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2028350830078</t>
+    <t xml:space="preserve">16.8544673919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2028388977051</t>
   </si>
   <si>
     <t xml:space="preserve">17.1033000946045</t>
@@ -2672,16 +2672,16 @@
     <t xml:space="preserve">17.1198902130127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7383422851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3521366119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2691898345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8710556030273</t>
+    <t xml:space="preserve">16.7383441925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3521385192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2691917419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8710536956787</t>
   </si>
   <si>
     <t xml:space="preserve">15.9171848297119</t>
@@ -2690,19 +2690,19 @@
     <t xml:space="preserve">16.2074947357178</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2323780059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6056308746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6958503723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1981792449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1650009155273</t>
+    <t xml:space="preserve">16.2323760986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6056327819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6958484649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1981773376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1649990081787</t>
   </si>
   <si>
     <t xml:space="preserve">17.617561340332</t>
@@ -2720,10 +2720,10 @@
     <t xml:space="preserve">17.4019031524658</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3189601898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0203552246094</t>
+    <t xml:space="preserve">17.3189582824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0203590393066</t>
   </si>
   <si>
     <t xml:space="preserve">16.7881107330322</t>
@@ -2735,19 +2735,19 @@
     <t xml:space="preserve">17.1862468719482</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4065647125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4148597717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0499000549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1660213470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5346145629883</t>
+    <t xml:space="preserve">16.4065628051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4148578643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.049898147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1660194396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5346164703369</t>
   </si>
   <si>
     <t xml:space="preserve">17.070125579834</t>
@@ -2759,7 +2759,7 @@
     <t xml:space="preserve">17.6839160919189</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4848499298096</t>
+    <t xml:space="preserve">17.4848518371582</t>
   </si>
   <si>
     <t xml:space="preserve">17.276216506958</t>
@@ -2777,16 +2777,16 @@
     <t xml:space="preserve">17.4111862182617</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3774433135986</t>
+    <t xml:space="preserve">17.3774452209473</t>
   </si>
   <si>
     <t xml:space="preserve">17.6642589569092</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4449291229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4618015289307</t>
+    <t xml:space="preserve">17.4449310302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4618034362793</t>
   </si>
   <si>
     <t xml:space="preserve">17.1749897003174</t>
@@ -2795,7 +2795,7 @@
     <t xml:space="preserve">17.0400199890137</t>
   </si>
   <si>
-    <t xml:space="preserve">17.006275177002</t>
+    <t xml:space="preserve">17.0062770843506</t>
   </si>
   <si>
     <t xml:space="preserve">16.9556617736816</t>
@@ -2804,7 +2804,7 @@
     <t xml:space="preserve">16.8628711700439</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0906314849854</t>
+    <t xml:space="preserve">17.090633392334</t>
   </si>
   <si>
     <t xml:space="preserve">16.8713054656982</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">15.7915420532227</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6903162002563</t>
+    <t xml:space="preserve">15.6903142929077</t>
   </si>
   <si>
     <t xml:space="preserve">15.8590278625488</t>
@@ -2843,19 +2843,19 @@
     <t xml:space="preserve">15.0998182296753</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4203748703003</t>
+    <t xml:space="preserve">15.420373916626</t>
   </si>
   <si>
     <t xml:space="preserve">15.60595703125</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5806512832642</t>
+    <t xml:space="preserve">15.5806493759155</t>
   </si>
   <si>
     <t xml:space="preserve">15.833722114563</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0446128845215</t>
+    <t xml:space="preserve">16.0446109771729</t>
   </si>
   <si>
     <t xml:space="preserve">15.8759002685547</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">15.7662353515625</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7746706008911</t>
+    <t xml:space="preserve">15.7746725082397</t>
   </si>
   <si>
     <t xml:space="preserve">15.513165473938</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">15.4878597259521</t>
   </si>
   <si>
-    <t xml:space="preserve">15.184175491333</t>
+    <t xml:space="preserve">15.1841745376587</t>
   </si>
   <si>
     <t xml:space="preserve">15.2347888946533</t>
@@ -2891,10 +2891,10 @@
     <t xml:space="preserve">15.3950672149658</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9433841705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1120986938477</t>
+    <t xml:space="preserve">15.9433832168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.112096786499</t>
   </si>
   <si>
     <t xml:space="preserve">16.2976818084717</t>
@@ -2915,22 +2915,22 @@
     <t xml:space="preserve">15.968692779541</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3145542144775</t>
+    <t xml:space="preserve">16.3145523071289</t>
   </si>
   <si>
     <t xml:space="preserve">15.9180765151978</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0193061828613</t>
+    <t xml:space="preserve">16.0193042755127</t>
   </si>
   <si>
     <t xml:space="preserve">15.5384731292725</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0154619216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.150429725647</t>
+    <t xml:space="preserve">15.0154609680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1504316329956</t>
   </si>
   <si>
     <t xml:space="preserve">15.5300378799438</t>
@@ -2972,13 +2972,13 @@
     <t xml:space="preserve">15.4794235229492</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1588668823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7623929977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4080953598022</t>
+    <t xml:space="preserve">15.1588659286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7623920440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4080944061279</t>
   </si>
   <si>
     <t xml:space="preserve">13.7416791915894</t>
@@ -2987,7 +2987,7 @@
     <t xml:space="preserve">14.0537977218628</t>
   </si>
   <si>
-    <t xml:space="preserve">14.121283531189</t>
+    <t xml:space="preserve">14.1212825775146</t>
   </si>
   <si>
     <t xml:space="preserve">13.4295587539673</t>
@@ -3008,16 +3008,16 @@
     <t xml:space="preserve">12.9065494537354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3367671966553</t>
+    <t xml:space="preserve">13.3367681503296</t>
   </si>
   <si>
     <t xml:space="preserve">13.1258754730225</t>
   </si>
   <si>
-    <t xml:space="preserve">13.513916015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9188261032104</t>
+    <t xml:space="preserve">13.5139169692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9188270568848</t>
   </si>
   <si>
     <t xml:space="preserve">13.3198957443237</t>
@@ -3032,16 +3032,16 @@
     <t xml:space="preserve">12.9318561553955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7631435394287</t>
+    <t xml:space="preserve">12.7631425857544</t>
   </si>
   <si>
     <t xml:space="preserve">12.6366081237793</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4172811508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.484766960144</t>
+    <t xml:space="preserve">12.4172801971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4847660064697</t>
   </si>
   <si>
     <t xml:space="preserve">12.6872224807739</t>
@@ -3056,10 +3056,10 @@
     <t xml:space="preserve">12.4678945541382</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1304683685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2823104858398</t>
+    <t xml:space="preserve">12.1304693222046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2823114395142</t>
   </si>
   <si>
     <t xml:space="preserve">12.3497953414917</t>
@@ -3089,13 +3089,13 @@
     <t xml:space="preserve">13.2271041870117</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9571628570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0752620697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7040948867798</t>
+    <t xml:space="preserve">12.9571619033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0752630233765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7040939331055</t>
   </si>
   <si>
     <t xml:space="preserve">12.7715787887573</t>
@@ -3104,13 +3104,13 @@
     <t xml:space="preserve">12.4004096984863</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2148246765137</t>
+    <t xml:space="preserve">12.214825630188</t>
   </si>
   <si>
     <t xml:space="preserve">12.0461111068726</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8773984909058</t>
+    <t xml:space="preserve">11.8773994445801</t>
   </si>
   <si>
     <t xml:space="preserve">12.1473398208618</t>
@@ -3122,7 +3122,7 @@
     <t xml:space="preserve">12.2316970825195</t>
   </si>
   <si>
-    <t xml:space="preserve">12.451024055481</t>
+    <t xml:space="preserve">12.4510231018066</t>
   </si>
   <si>
     <t xml:space="preserve">12.3835391998291</t>
@@ -3137,7 +3137,7 @@
     <t xml:space="preserve">11.6749429702759</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6487474441528</t>
+    <t xml:space="preserve">11.6487464904785</t>
   </si>
   <si>
     <t xml:space="preserve">11.474102973938</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">11.8932485580444</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9107122421265</t>
+    <t xml:space="preserve">11.9107131958008</t>
   </si>
   <si>
     <t xml:space="preserve">12.4346437454224</t>
@@ -3167,10 +3167,10 @@
     <t xml:space="preserve">12.1901426315308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3298568725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5568943023682</t>
+    <t xml:space="preserve">12.3298578262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5568952560425</t>
   </si>
   <si>
     <t xml:space="preserve">12.3123931884766</t>
@@ -3182,13 +3182,13 @@
     <t xml:space="preserve">11.4391746520996</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1946725845337</t>
+    <t xml:space="preserve">11.1946716308594</t>
   </si>
   <si>
     <t xml:space="preserve">11.7186040878296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5788898468018</t>
+    <t xml:space="preserve">11.5788888931274</t>
   </si>
   <si>
     <t xml:space="preserve">11.8408555984497</t>
@@ -3209,19 +3209,19 @@
     <t xml:space="preserve">11.49156665802</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2645301818848</t>
+    <t xml:space="preserve">11.2645292282104</t>
   </si>
   <si>
     <t xml:space="preserve">10.8104562759399</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0549573898315</t>
+    <t xml:space="preserve">11.0549583435059</t>
   </si>
   <si>
     <t xml:space="preserve">11.1772079467773</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3867807388306</t>
+    <t xml:space="preserve">11.3867797851562</t>
   </si>
   <si>
     <t xml:space="preserve">11.2470655441284</t>
@@ -3242,10 +3242,10 @@
     <t xml:space="preserve">11.4042453765869</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2296018600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6138191223145</t>
+    <t xml:space="preserve">11.2296009063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6138181686401</t>
   </si>
   <si>
     <t xml:space="preserve">11.7884616851807</t>
@@ -3260,25 +3260,25 @@
     <t xml:space="preserve">11.5614242553711</t>
   </si>
   <si>
-    <t xml:space="preserve">11.456639289856</t>
+    <t xml:space="preserve">11.4566383361816</t>
   </si>
   <si>
     <t xml:space="preserve">11.5439605712891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4217100143433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1073503494263</t>
+    <t xml:space="preserve">11.4217090606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1073513031006</t>
   </si>
   <si>
     <t xml:space="preserve">11.0898857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7231330871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6882047653198</t>
+    <t xml:space="preserve">10.7231340408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6882057189941</t>
   </si>
   <si>
     <t xml:space="preserve">10.6707410812378</t>
@@ -3305,7 +3305,7 @@
     <t xml:space="preserve">9.90230846405029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81498622894287</t>
+    <t xml:space="preserve">9.81498527526855</t>
   </si>
   <si>
     <t xml:space="preserve">9.76259326934814</t>
@@ -3317,28 +3317,28 @@
     <t xml:space="preserve">10.1992034912109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29105472564697</t>
+    <t xml:space="preserve">9.29105567932129</t>
   </si>
   <si>
     <t xml:space="preserve">9.51809120178223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2211971282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25612545013428</t>
+    <t xml:space="preserve">9.22119808197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25612640380859</t>
   </si>
   <si>
     <t xml:space="preserve">9.0640172958374</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80205059051514</t>
+    <t xml:space="preserve">8.80205154418945</t>
   </si>
   <si>
     <t xml:space="preserve">8.8195161819458</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60121250152588</t>
+    <t xml:space="preserve">8.60121154785156</t>
   </si>
   <si>
     <t xml:space="preserve">8.48769283294678</t>
@@ -3347,19 +3347,19 @@
     <t xml:space="preserve">8.19079780578613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44403266906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4614953994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33924579620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56628322601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34797859191895</t>
+    <t xml:space="preserve">8.44403171539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46149444580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3392448425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56628227233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34797763824463</t>
   </si>
   <si>
     <t xml:space="preserve">8.54881763458252</t>
@@ -3386,13 +3386,13 @@
     <t xml:space="preserve">8.73219394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02908802032471</t>
+    <t xml:space="preserve">9.02908897399902</t>
   </si>
   <si>
     <t xml:space="preserve">9.09894561767578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41330432891846</t>
+    <t xml:space="preserve">9.41330528259277</t>
   </si>
   <si>
     <t xml:space="preserve">9.308518409729</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">9.55301952362061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.622878074646</t>
+    <t xml:space="preserve">9.62287712097168</t>
   </si>
   <si>
     <t xml:space="preserve">9.91977214813232</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">10.269061088562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65780735015869</t>
+    <t xml:space="preserve">9.65780639648438</t>
   </si>
   <si>
     <t xml:space="preserve">9.64034175872803</t>
@@ -3434,7 +3434,7 @@
     <t xml:space="preserve">10.0420236587524</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69273567199707</t>
+    <t xml:space="preserve">9.69273471832275</t>
   </si>
   <si>
     <t xml:space="preserve">9.93723678588867</t>
@@ -3443,7 +3443,7 @@
     <t xml:space="preserve">9.97216606140137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88484382629395</t>
+    <t xml:space="preserve">9.88484287261963</t>
   </si>
   <si>
     <t xml:space="preserve">9.8673791885376</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">10.0944166183472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0769519805908</t>
+    <t xml:space="preserve">10.0769510269165</t>
   </si>
   <si>
     <t xml:space="preserve">9.79752159118652</t>
@@ -3476,16 +3476,16 @@
     <t xml:space="preserve">10.7405986785889</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7580623626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9152421951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0200281143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3518524169922</t>
+    <t xml:space="preserve">10.7580633163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9152431488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0200290679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3518514633179</t>
   </si>
   <si>
     <t xml:space="preserve">11.0025644302368</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">10.9676361083984</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5310258865356</t>
+    <t xml:space="preserve">10.53102684021</t>
   </si>
   <si>
     <t xml:space="preserve">10.6183471679688</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">10.0245580673218</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84991455078125</t>
+    <t xml:space="preserve">9.84991359710693</t>
   </si>
   <si>
     <t xml:space="preserve">10.1118803024292</t>
@@ -3554,13 +3554,13 @@
     <t xml:space="preserve">11.8757839202881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0678911209106</t>
+    <t xml:space="preserve">12.067892074585</t>
   </si>
   <si>
     <t xml:space="preserve">12.0329627990723</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4650430679321</t>
+    <t xml:space="preserve">13.4650440216064</t>
   </si>
   <si>
     <t xml:space="preserve">13.1681480407715</t>
@@ -3572,7 +3572,7 @@
     <t xml:space="preserve">12.8712530136108</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6442155838013</t>
+    <t xml:space="preserve">12.6442165374756</t>
   </si>
   <si>
     <t xml:space="preserve">12.9491128921509</t>
@@ -70731,7 +70731,7 @@
     </row>
     <row r="2529">
       <c r="A2529" s="1" t="n">
-        <v>46000.6912037037</v>
+        <v>46000.3333333333</v>
       </c>
       <c r="B2529" t="n">
         <v>76238</v>
@@ -70752,6 +70752,32 @@
         <v>1548</v>
       </c>
       <c r="H2529" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2530">
+      <c r="A2530" s="1" t="n">
+        <v>46001.6913078704</v>
+      </c>
+      <c r="B2530" t="n">
+        <v>62054</v>
+      </c>
+      <c r="C2530" t="n">
+        <v>8.9399995803833</v>
+      </c>
+      <c r="D2530" t="n">
+        <v>8.81999969482422</v>
+      </c>
+      <c r="E2530" t="n">
+        <v>8.85000038146973</v>
+      </c>
+      <c r="F2530" t="n">
+        <v>8.92000007629395</v>
+      </c>
+      <c r="G2530" t="s">
+        <v>1549</v>
+      </c>
+      <c r="H2530" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARR.MI.xlsx
+++ b/data/MARR.MI.xlsx
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4479513168335</t>
+    <t xml:space="preserve">13.4479503631592</t>
   </si>
   <si>
     <t xml:space="preserve">MARR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.289400100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1812982559204</t>
+    <t xml:space="preserve">13.2894010543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.181300163269</t>
   </si>
   <si>
     <t xml:space="preserve">12.9939203262329</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9506797790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5903358459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6551990509033</t>
+    <t xml:space="preserve">12.9506778717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5903367996216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.655198097229</t>
   </si>
   <si>
     <t xml:space="preserve">12.7344751358032</t>
@@ -71,13 +71,13 @@
     <t xml:space="preserve">12.4462013244629</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9849624633789</t>
+    <t xml:space="preserve">11.9849634170532</t>
   </si>
   <si>
     <t xml:space="preserve">12.0858592987061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6462430953979</t>
+    <t xml:space="preserve">11.6462421417236</t>
   </si>
   <si>
     <t xml:space="preserve">12.2155838012695</t>
@@ -86,13 +86,13 @@
     <t xml:space="preserve">12.8353691101074</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6768188476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5615110397339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5543041229248</t>
+    <t xml:space="preserve">12.6768217086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5615100860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5543031692505</t>
   </si>
   <si>
     <t xml:space="preserve">12.6407861709595</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">12.7200613021851</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9722995758057</t>
+    <t xml:space="preserve">12.9722986221313</t>
   </si>
   <si>
     <t xml:space="preserve">12.7777147293091</t>
@@ -113,16 +113,16 @@
     <t xml:space="preserve">12.5110635757446</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2948579788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4084167480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4516582489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8840656280518</t>
+    <t xml:space="preserve">12.2948570251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4084177017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4516592025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8840675354004</t>
   </si>
   <si>
     <t xml:space="preserve">11.5885877609253</t>
@@ -131,13 +131,13 @@
     <t xml:space="preserve">11.8912744522095</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9273080825806</t>
+    <t xml:space="preserve">11.9273090362549</t>
   </si>
   <si>
     <t xml:space="preserve">12.0426168441772</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2011690139771</t>
+    <t xml:space="preserve">12.2011680603027</t>
   </si>
   <si>
     <t xml:space="preserve">12.3957548141479</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">12.6047515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5759229660034</t>
+    <t xml:space="preserve">12.5759239196777</t>
   </si>
   <si>
     <t xml:space="preserve">12.9362659454346</t>
@@ -164,10 +164,10 @@
     <t xml:space="preserve">13.0731945037842</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8858156204224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5975456237793</t>
+    <t xml:space="preserve">12.8858184814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5975437164307</t>
   </si>
   <si>
     <t xml:space="preserve">12.078652381897</t>
@@ -176,16 +176,16 @@
     <t xml:space="preserve">12.3597183227539</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6696119308472</t>
+    <t xml:space="preserve">12.6696128845215</t>
   </si>
   <si>
     <t xml:space="preserve">12.8137502670288</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6984405517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8714046478271</t>
+    <t xml:space="preserve">12.6984395980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8714056015015</t>
   </si>
   <si>
     <t xml:space="preserve">12.453408241272</t>
@@ -194,31 +194,31 @@
     <t xml:space="preserve">12.3453054428101</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6840267181396</t>
+    <t xml:space="preserve">12.684024810791</t>
   </si>
   <si>
     <t xml:space="preserve">12.7560949325562</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1524724960327</t>
+    <t xml:space="preserve">13.1524705886841</t>
   </si>
   <si>
     <t xml:space="preserve">13.2677803039551</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3326416015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0804014205933</t>
+    <t xml:space="preserve">13.3326435089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0804023742676</t>
   </si>
   <si>
     <t xml:space="preserve">13.1885051727295</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2605714797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7073974609375</t>
+    <t xml:space="preserve">13.2605724334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7073965072632</t>
   </si>
   <si>
     <t xml:space="preserve">13.4911909103394</t>
@@ -227,94 +227,94 @@
     <t xml:space="preserve">13.3470544815063</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0011262893677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9002304077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8281621932983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7921276092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0587825775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1020240783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8065452575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2821941375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1380567550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8425769805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8930253982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9074363708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0227489471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6624059677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8786115646362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6335783004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7488899230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0258760452271</t>
+    <t xml:space="preserve">13.001127243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9002313613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8281631469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7921314239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0587816238403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1020231246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8065433502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2821922302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1380577087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8425760269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8930244445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9074373245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0227479934692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.662407875061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8786125183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6335792541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7488889694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0258750915527</t>
   </si>
   <si>
     <t xml:space="preserve">13.0183897018433</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2579441070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2504596710205</t>
+    <t xml:space="preserve">13.25794506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2504606246948</t>
   </si>
   <si>
     <t xml:space="preserve">13.4301280975342</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4825305938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3103475570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2654304504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.475043296814</t>
+    <t xml:space="preserve">13.4825296401978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3103485107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2654314041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4750413894653</t>
   </si>
   <si>
     <t xml:space="preserve">13.3702383041382</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2878894805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2729187011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2804040908813</t>
+    <t xml:space="preserve">13.2878913879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2729177474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2804050445557</t>
   </si>
   <si>
     <t xml:space="preserve">12.8012914657593</t>
@@ -326,28 +326,28 @@
     <t xml:space="preserve">12.6141376495361</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3146944046021</t>
+    <t xml:space="preserve">12.3146934509277</t>
   </si>
   <si>
     <t xml:space="preserve">12.44944190979</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8087787628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7938051223755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0782785415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4419565200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7831773757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2847471237183</t>
+    <t xml:space="preserve">12.8087768554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7938032150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0782775878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4419555664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7831754684448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2847480773926</t>
   </si>
   <si>
     <t xml:space="preserve">12.7339162826538</t>
@@ -356,22 +356,22 @@
     <t xml:space="preserve">13.4226417541504</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5274467468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0558195114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4525852203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3328056335449</t>
+    <t xml:space="preserve">13.5274457931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0558204650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.452582359314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3328065872192</t>
   </si>
   <si>
     <t xml:space="preserve">13.7595157623291</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7295732498169</t>
+    <t xml:space="preserve">13.7295722961426</t>
   </si>
   <si>
     <t xml:space="preserve">13.7220859527588</t>
@@ -380,34 +380,34 @@
     <t xml:space="preserve">13.5349321365356</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4900169372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7370586395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0140438079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7071113586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8493499755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1113653182983</t>
+    <t xml:space="preserve">13.4900159835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7370595932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0140447616577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7071132659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8493518829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.111364364624</t>
   </si>
   <si>
     <t xml:space="preserve">13.9766130447388</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0814189910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7445459365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9990711212158</t>
+    <t xml:space="preserve">14.0814208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7445449829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9990739822388</t>
   </si>
   <si>
     <t xml:space="preserve">13.5049877166748</t>
@@ -416,19 +416,19 @@
     <t xml:space="preserve">13.6397361755371</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6621980667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6097946166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3477764129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4151544570923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2205142974854</t>
+    <t xml:space="preserve">13.6621971130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6097936630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3477792739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.415153503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2205152511597</t>
   </si>
   <si>
     <t xml:space="preserve">13.0857629776001</t>
@@ -458,7 +458,7 @@
     <t xml:space="preserve">13.1980562210083</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1157083511353</t>
+    <t xml:space="preserve">13.1157093048096</t>
   </si>
   <si>
     <t xml:space="preserve">13.0109033584595</t>
@@ -488,25 +488,25 @@
     <t xml:space="preserve">13.3402919769287</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9659852981567</t>
+    <t xml:space="preserve">12.9659862518311</t>
   </si>
   <si>
     <t xml:space="preserve">12.8761529922485</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8312358856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9809598922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.763861656189</t>
+    <t xml:space="preserve">12.8312339782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9809589385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7638597488403</t>
   </si>
   <si>
     <t xml:space="preserve">12.7114572525024</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8686676025391</t>
+    <t xml:space="preserve">12.8686666488647</t>
   </si>
   <si>
     <t xml:space="preserve">12.7563762664795</t>
@@ -518,16 +518,16 @@
     <t xml:space="preserve">12.5767068862915</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5467624664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5317888259888</t>
+    <t xml:space="preserve">12.546763420105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5317897796631</t>
   </si>
   <si>
     <t xml:space="preserve">12.5617351531982</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5542488098145</t>
+    <t xml:space="preserve">12.5542497634888</t>
   </si>
   <si>
     <t xml:space="preserve">12.4194974899292</t>
@@ -539,61 +539,61 @@
     <t xml:space="preserve">12.4719009399414</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5018463134766</t>
+    <t xml:space="preserve">12.5018453598022</t>
   </si>
   <si>
     <t xml:space="preserve">12.3970394134521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9778156280518</t>
+    <t xml:space="preserve">11.9778165817261</t>
   </si>
   <si>
     <t xml:space="preserve">12.3596096038818</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4943609237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3820676803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4045267105103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2697763442993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1649703979492</t>
+    <t xml:space="preserve">12.4943599700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3820667266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4045257568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2697744369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1649694442749</t>
   </si>
   <si>
     <t xml:space="preserve">12.2548046112061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3371505737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3221778869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.72642993927</t>
+    <t xml:space="preserve">12.3371515274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3221788406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7264308929443</t>
   </si>
   <si>
     <t xml:space="preserve">12.6740264892578</t>
   </si>
   <si>
-    <t xml:space="preserve">12.786319732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0932493209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9510135650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1306819915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9884462356567</t>
+    <t xml:space="preserve">12.7863187789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0932502746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9510126113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1306829452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9884452819824</t>
   </si>
   <si>
     <t xml:space="preserve">13.1381673812866</t>
@@ -602,10 +602,10 @@
     <t xml:space="preserve">13.160626411438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1830835342407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1681127548218</t>
+    <t xml:space="preserve">13.183084487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1681137084961</t>
   </si>
   <si>
     <t xml:space="preserve">13.2280006408691</t>
@@ -614,40 +614,40 @@
     <t xml:space="preserve">13.00341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1755971908569</t>
+    <t xml:space="preserve">13.1755962371826</t>
   </si>
   <si>
     <t xml:space="preserve">13.400182723999</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3852090835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8643217086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.91672706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5199594497681</t>
+    <t xml:space="preserve">13.3852109909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8643226623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9167251586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5199604034424</t>
   </si>
   <si>
     <t xml:space="preserve">13.4450979232788</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3627529144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4600706100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5124740600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4376106262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8268928527832</t>
+    <t xml:space="preserve">13.3627510070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4600715637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5124731063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4376125335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8268918991089</t>
   </si>
   <si>
     <t xml:space="preserve">13.6247663497925</t>
@@ -656,46 +656,46 @@
     <t xml:space="preserve">13.8044338226318</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7819747924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6996288299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8418626785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6771688461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8568363189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7670011520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5648775100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8942642211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3359498977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5605344772339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5156145095825</t>
+    <t xml:space="preserve">13.7819757461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6996278762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8418636322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6771697998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8568353652954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7670030593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5648756027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8942670822144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3359479904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5605325698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5156164169312</t>
   </si>
   <si>
     <t xml:space="preserve">14.6952838897705</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9722690582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9348411560059</t>
+    <t xml:space="preserve">14.9722700119019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9348402023315</t>
   </si>
   <si>
     <t xml:space="preserve">14.9423246383667</t>
@@ -704,46 +704,46 @@
     <t xml:space="preserve">14.8225479125977</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2043380737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7133960723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.136962890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1594209671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2866868972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3615493774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2267980575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3465757369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6834545135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7208805084229</t>
+    <t xml:space="preserve">15.2043418884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7133989334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1369638442993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1594219207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2866878509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3615503311157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2267999649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3465785980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6834526062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7208824157715</t>
   </si>
   <si>
     <t xml:space="preserve">15.5337314605713</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4588689804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1669111251831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1968536376953</t>
+    <t xml:space="preserve">15.458869934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1669092178345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.196852684021</t>
   </si>
   <si>
     <t xml:space="preserve">15.5487051010132</t>
@@ -752,31 +752,31 @@
     <t xml:space="preserve">15.4214372634888</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6011066436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6460237503052</t>
+    <t xml:space="preserve">15.6011047363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6460199356079</t>
   </si>
   <si>
     <t xml:space="preserve">15.7358570098877</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5861310958862</t>
+    <t xml:space="preserve">15.5861349105835</t>
   </si>
   <si>
     <t xml:space="preserve">15.9080381393433</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4245796203613</t>
+    <t xml:space="preserve">16.4245777130127</t>
   </si>
   <si>
     <t xml:space="preserve">16.1251354217529</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6984233856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2823429107666</t>
+    <t xml:space="preserve">15.6984252929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2823448181152</t>
   </si>
   <si>
     <t xml:space="preserve">16.3272590637207</t>
@@ -785,43 +785,43 @@
     <t xml:space="preserve">16.2598838806152</t>
   </si>
   <si>
-    <t xml:space="preserve">16.267370223999</t>
+    <t xml:space="preserve">16.2673683166504</t>
   </si>
   <si>
     <t xml:space="preserve">16.5967655181885</t>
   </si>
   <si>
-    <t xml:space="preserve">16.78391456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6641368865967</t>
+    <t xml:space="preserve">16.7839164733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6641387939453</t>
   </si>
   <si>
     <t xml:space="preserve">16.5219020843506</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4470367431641</t>
+    <t xml:space="preserve">16.4470386505127</t>
   </si>
   <si>
     <t xml:space="preserve">16.6416778564453</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0758724212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7988872528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7464847564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8737468719482</t>
+    <t xml:space="preserve">17.0758743286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7988891601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7464866638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8737506866455</t>
   </si>
   <si>
     <t xml:space="preserve">16.9560947418213</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1058216094971</t>
+    <t xml:space="preserve">17.1058197021484</t>
   </si>
   <si>
     <t xml:space="preserve">16.3946361541748</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">16.5069274902344</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6847553253174</t>
+    <t xml:space="preserve">16.6847534179688</t>
   </si>
   <si>
     <t xml:space="preserve">17.1950378417969</t>
@@ -839,19 +839,19 @@
     <t xml:space="preserve">17.1641120910645</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0094814300537</t>
+    <t xml:space="preserve">17.0094833374023</t>
   </si>
   <si>
     <t xml:space="preserve">16.7620697021484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6306324005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8471202850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0249443054199</t>
+    <t xml:space="preserve">16.6306343078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8471183776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0249462127686</t>
   </si>
   <si>
     <t xml:space="preserve">16.9398956298828</t>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">17.1254558563232</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9553604125977</t>
+    <t xml:space="preserve">16.955358505249</t>
   </si>
   <si>
     <t xml:space="preserve">16.5455856323242</t>
@@ -878,19 +878,19 @@
     <t xml:space="preserve">16.8548488616943</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7466049194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0404090881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7311458587646</t>
+    <t xml:space="preserve">16.7466068267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0404071807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.731143951416</t>
   </si>
   <si>
     <t xml:space="preserve">16.5378551483154</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5687808990479</t>
+    <t xml:space="preserve">16.5687789916992</t>
   </si>
   <si>
     <t xml:space="preserve">16.6229000091553</t>
@@ -908,16 +908,16 @@
     <t xml:space="preserve">16.0894222259521</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0816917419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1590061187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9347906112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2363204956055</t>
+    <t xml:space="preserve">16.0816898345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1590042114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9347925186157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2363224029541</t>
   </si>
   <si>
     <t xml:space="preserve">16.0739593505859</t>
@@ -929,16 +929,16 @@
     <t xml:space="preserve">16.3909549713135</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4914646148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8935070037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2414283752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0558700561523</t>
+    <t xml:space="preserve">16.4914627075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8935050964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2414302825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.055871963501</t>
   </si>
   <si>
     <t xml:space="preserve">17.28782081604</t>
@@ -947,31 +947,31 @@
     <t xml:space="preserve">17.2955513000488</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3960590362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8316555023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2800884246826</t>
+    <t xml:space="preserve">17.3960609436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8316535949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.280086517334</t>
   </si>
   <si>
     <t xml:space="preserve">16.7002182006836</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5533180236816</t>
+    <t xml:space="preserve">16.553316116333</t>
   </si>
   <si>
     <t xml:space="preserve">16.4837341308594</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7775344848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5146579742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3832225799561</t>
+    <t xml:space="preserve">16.7775325775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5146598815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3832244873047</t>
   </si>
   <si>
     <t xml:space="preserve">16.3986854553223</t>
@@ -980,22 +980,22 @@
     <t xml:space="preserve">16.2749824523926</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2285919189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0584964752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9657163619995</t>
+    <t xml:space="preserve">16.2285938262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0584983825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9657182693481</t>
   </si>
   <si>
     <t xml:space="preserve">15.950252532959</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0353031158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2827129364014</t>
+    <t xml:space="preserve">16.0353012084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2827110290527</t>
   </si>
   <si>
     <t xml:space="preserve">16.4141483306885</t>
@@ -1004,7 +1004,7 @@
     <t xml:space="preserve">16.6074390411377</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5919761657715</t>
+    <t xml:space="preserve">16.5919742584229</t>
   </si>
   <si>
     <t xml:space="preserve">16.932165145874</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">17.0481376647949</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2646217346191</t>
+    <t xml:space="preserve">17.2646255493164</t>
   </si>
   <si>
     <t xml:space="preserve">16.9476280212402</t>
@@ -1022,13 +1022,13 @@
     <t xml:space="preserve">17.0713310241699</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0636005401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.079065322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2723560333252</t>
+    <t xml:space="preserve">17.0636024475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0790672302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2723541259766</t>
   </si>
   <si>
     <t xml:space="preserve">17.303279876709</t>
@@ -1040,13 +1040,13 @@
     <t xml:space="preserve">17.3187427520752</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5584239959717</t>
+    <t xml:space="preserve">17.558422088623</t>
   </si>
   <si>
     <t xml:space="preserve">17.5893497467041</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4656448364258</t>
+    <t xml:space="preserve">17.4656429290771</t>
   </si>
   <si>
     <t xml:space="preserve">17.7207851409912</t>
@@ -1055,19 +1055,19 @@
     <t xml:space="preserve">17.5738868713379</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5429611206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6975917816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1073665618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0377826690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6125469207764</t>
+    <t xml:space="preserve">17.5429630279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6975936889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.107364654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0377788543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6125431060791</t>
   </si>
   <si>
     <t xml:space="preserve">17.6821308135986</t>
@@ -1085,13 +1085,13 @@
     <t xml:space="preserve">17.3574028015137</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1795749664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1409187316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0867977142334</t>
+    <t xml:space="preserve">17.1795768737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1409206390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.086799621582</t>
   </si>
   <si>
     <t xml:space="preserve">16.8857727050781</t>
@@ -1112,37 +1112,37 @@
     <t xml:space="preserve">15.826548576355</t>
   </si>
   <si>
-    <t xml:space="preserve">15.927056312561</t>
+    <t xml:space="preserve">15.9270582199097</t>
   </si>
   <si>
     <t xml:space="preserve">16.1976642608643</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6692905426025</t>
+    <t xml:space="preserve">16.6692924499512</t>
   </si>
   <si>
     <t xml:space="preserve">16.8703117370605</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7852668762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9630928039551</t>
+    <t xml:space="preserve">16.7852649688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9630889892578</t>
   </si>
   <si>
     <t xml:space="preserve">16.8084583282471</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9244346618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4218788146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0507640838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4605388641357</t>
+    <t xml:space="preserve">16.9244327545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4218807220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0507659912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4605407714844</t>
   </si>
   <si>
     <t xml:space="preserve">16.452808380127</t>
@@ -1151,13 +1151,13 @@
     <t xml:space="preserve">16.7543354034424</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6383666992188</t>
+    <t xml:space="preserve">16.6383647918701</t>
   </si>
   <si>
     <t xml:space="preserve">16.7929954528809</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4064178466797</t>
+    <t xml:space="preserve">16.4064159393311</t>
   </si>
   <si>
     <t xml:space="preserve">17.3342094421387</t>
@@ -1166,25 +1166,25 @@
     <t xml:space="preserve">17.3805980682373</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4888401031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5506935119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6898612976074</t>
+    <t xml:space="preserve">17.4888381958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5506916046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6898593902588</t>
   </si>
   <si>
     <t xml:space="preserve">17.4115238189697</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6434707641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2568893432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2259654998779</t>
+    <t xml:space="preserve">17.6434688568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2568912506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2259674072266</t>
   </si>
   <si>
     <t xml:space="preserve">17.5043029785156</t>
@@ -1199,52 +1199,52 @@
     <t xml:space="preserve">16.3445644378662</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2981758117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.901237487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.653829574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2672481536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3136405944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4269886016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4475574493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3857040405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8805236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1433982849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0042304992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9114513397217</t>
+    <t xml:space="preserve">16.2981777191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9012393951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6538276672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2672500610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3136367797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4269905090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4475555419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.385705947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8805255889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1434001922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0042285919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.911449432373</t>
   </si>
   <si>
     <t xml:space="preserve">18.6949672698975</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6795043945312</t>
+    <t xml:space="preserve">18.6795024871826</t>
   </si>
   <si>
     <t xml:space="preserve">18.7413558959961</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6640377044678</t>
+    <t xml:space="preserve">18.6640396118164</t>
   </si>
   <si>
     <t xml:space="preserve">18.7877445220947</t>
@@ -1262,10 +1262,10 @@
     <t xml:space="preserve">19.406270980835</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5608997344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3289566040039</t>
+    <t xml:space="preserve">19.5609035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3289585113525</t>
   </si>
   <si>
     <t xml:space="preserve">19.1743240356445</t>
@@ -1277,139 +1277,139 @@
     <t xml:space="preserve">19.1588592529297</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2825679779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.236177444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.205249786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2671031951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5299758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6382179260254</t>
+    <t xml:space="preserve">19.2825660705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2361755371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2052478790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2671012878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5299777984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.638219833374</t>
   </si>
   <si>
     <t xml:space="preserve">19.5918312072754</t>
   </si>
   <si>
-    <t xml:space="preserve">19.483585357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5145111083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4526596069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6072940826416</t>
+    <t xml:space="preserve">19.4835872650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5145130157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4526615142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6072959899902</t>
   </si>
   <si>
     <t xml:space="preserve">18.1382904052734</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3547782897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0764408111572</t>
+    <t xml:space="preserve">18.3547763824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0764389038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0300483703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1737785339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9502010345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3654193878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2057209014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6209354400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.509147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5889987945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5570583343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4931793212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1578102111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4292984008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6848182678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6369075775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4133262634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4612369537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3175086975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8064727783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8224411010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7106533050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9182624816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9661712646484</t>
   </si>
   <si>
     <t xml:space="preserve">18.03005027771</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1737804412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9502010345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3654193878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2057189941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6209373474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.509147644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5889987945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5570583343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4931755065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1578063964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4292984008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6848163604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6369075775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4133281707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.461238861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3175086975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8064708709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8224391937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7106533050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9182605743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9661693572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0300483703613</t>
-  </si>
-  <si>
     <t xml:space="preserve">17.8863201141357</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9981117248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3973598480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5251216888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4452667236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1479434967041</t>
+    <t xml:space="preserve">17.9981136322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3973617553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5251197814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4452686309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1479454040527</t>
   </si>
   <si>
     <t xml:space="preserve">19.1639137268066</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0201854705811</t>
+    <t xml:space="preserve">19.0201873779297</t>
   </si>
   <si>
     <t xml:space="preserve">18.8604888916016</t>
@@ -1418,28 +1418,28 @@
     <t xml:space="preserve">18.7806377410889</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5730285644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.06809425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7646675109863</t>
+    <t xml:space="preserve">18.5730266571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0680961608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7646656036377</t>
   </si>
   <si>
     <t xml:space="preserve">18.4772071838379</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7007884979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2437686920166</t>
+    <t xml:space="preserve">18.7007865905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2437648773193</t>
   </si>
   <si>
     <t xml:space="preserve">19.4513740539551</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4992828369141</t>
+    <t xml:space="preserve">19.4992847442627</t>
   </si>
   <si>
     <t xml:space="preserve">19.2118244171143</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">19.1319751739502</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0042152404785</t>
+    <t xml:space="preserve">19.0042133331299</t>
   </si>
   <si>
     <t xml:space="preserve">19.1160068511963</t>
@@ -1457,10 +1457,10 @@
     <t xml:space="preserve">19.0361557006836</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1798858642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.323616027832</t>
+    <t xml:space="preserve">19.1798877716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3236141204834</t>
   </si>
   <si>
     <t xml:space="preserve">19.3395843505859</t>
@@ -1469,13 +1469,13 @@
     <t xml:space="preserve">19.3076457977295</t>
   </si>
   <si>
-    <t xml:space="preserve">19.722864151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.467342376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3874969482422</t>
+    <t xml:space="preserve">19.7228622436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4673442840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3874950408936</t>
   </si>
   <si>
     <t xml:space="preserve">19.5631637573242</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">20.4415092468262</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2658367156982</t>
+    <t xml:space="preserve">20.2658386230469</t>
   </si>
   <si>
     <t xml:space="preserve">20.7609081268311</t>
@@ -1502,22 +1502,22 @@
     <t xml:space="preserve">20.8247871398926</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2498722076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4734477996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1540489196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1700191497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7548027038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5312252044678</t>
+    <t xml:space="preserve">20.2498741149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4734497070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1540508270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1700210571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7548007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5312232971191</t>
   </si>
   <si>
     <t xml:space="preserve">19.4034633636475</t>
@@ -1529,16 +1529,16 @@
     <t xml:space="preserve">18.7327251434326</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3813896179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2536315917969</t>
+    <t xml:space="preserve">18.3813877105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2536296844482</t>
   </si>
   <si>
     <t xml:space="preserve">17.9342308044434</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3494472503662</t>
+    <t xml:space="preserve">18.3494491577148</t>
   </si>
   <si>
     <t xml:space="preserve">18.9243679046631</t>
@@ -1547,22 +1547,22 @@
     <t xml:space="preserve">18.7486953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1258716583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7905006408691</t>
+    <t xml:space="preserve">18.1258697509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7905025482178</t>
   </si>
   <si>
     <t xml:space="preserve">17.4391593933105</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1357345581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2155838012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9760341644287</t>
+    <t xml:space="preserve">17.1357326507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2155857086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9760360717773</t>
   </si>
   <si>
     <t xml:space="preserve">17.550952911377</t>
@@ -1577,64 +1577,64 @@
     <t xml:space="preserve">16.9281253814697</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8323059082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0558834075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1836452484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4551315307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8163356781006</t>
+    <t xml:space="preserve">16.8323078155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0558853149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1836433410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4551334381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.816333770752</t>
   </si>
   <si>
     <t xml:space="preserve">16.3532066345215</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9858980178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0976867675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1136569976807</t>
+    <t xml:space="preserve">15.9858999252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0976886749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1136589050293</t>
   </si>
   <si>
     <t xml:space="preserve">15.4269523620605</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3311309814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6505289077759</t>
+    <t xml:space="preserve">15.3311319351196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6505308151245</t>
   </si>
   <si>
     <t xml:space="preserve">15.4748601913452</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4429216384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7703037261963</t>
+    <t xml:space="preserve">15.4429235458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7703065872192</t>
   </si>
   <si>
     <t xml:space="preserve">15.8421697616577</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7383651733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4490242004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2733573913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1615695953369</t>
+    <t xml:space="preserve">15.7383642196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4490261077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2733592987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1615676879883</t>
   </si>
   <si>
     <t xml:space="preserve">16.321268081665</t>
@@ -1643,10 +1643,10 @@
     <t xml:space="preserve">16.4809665679932</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6246948242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7684230804443</t>
+    <t xml:space="preserve">16.6246967315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.768424987793</t>
   </si>
   <si>
     <t xml:space="preserve">17.1676731109619</t>
@@ -1655,10 +1655,10 @@
     <t xml:space="preserve">17.3433418273926</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2794647216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9440956115723</t>
+    <t xml:space="preserve">17.2794628143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9440937042236</t>
   </si>
   <si>
     <t xml:space="preserve">17.0079746246338</t>
@@ -1667,46 +1667,46 @@
     <t xml:space="preserve">16.6406650543213</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2414169311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5608177185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7045459747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8482780456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3752841949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1037921905518</t>
+    <t xml:space="preserve">16.241418838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5608158111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7045478820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.848274230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3752822875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1037940979004</t>
   </si>
   <si>
     <t xml:space="preserve">16.8802146911621</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9121532440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8642463684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.720516204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6885757446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6087265014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7364826202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3052959442139</t>
+    <t xml:space="preserve">16.9121551513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8642482757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7205181121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6885738372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6087245941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7364845275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3052978515625</t>
   </si>
   <si>
     <t xml:space="preserve">15.8980627059937</t>
@@ -1718,46 +1718,46 @@
     <t xml:space="preserve">16.2094764709473</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3851451873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.28932762146</t>
+    <t xml:space="preserve">16.3851490020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2893295288086</t>
   </si>
   <si>
     <t xml:space="preserve">16.2573890686035</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2254486083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9140319824219</t>
+    <t xml:space="preserve">16.2254467010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9140338897705</t>
   </si>
   <si>
     <t xml:space="preserve">16.4170875549316</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5288772583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7843952178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5767860412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.369176864624</t>
+    <t xml:space="preserve">16.5288791656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7843971252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5767879486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3691787719727</t>
   </si>
   <si>
     <t xml:space="preserve">16.1775379180908</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4889507293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2494010925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.329252243042</t>
+    <t xml:space="preserve">16.4889526367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2494029998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3292541503906</t>
   </si>
   <si>
     <t xml:space="preserve">16.4091033935547</t>
@@ -1766,13 +1766,13 @@
     <t xml:space="preserve">16.1695518493652</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0497760772705</t>
+    <t xml:space="preserve">16.0497779846191</t>
   </si>
   <si>
     <t xml:space="preserve">16.5688018798828</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6486511230469</t>
+    <t xml:space="preserve">16.6486530303955</t>
   </si>
   <si>
     <t xml:space="preserve">17.2874488830566</t>
@@ -1787,7 +1787,7 @@
     <t xml:space="preserve">16.8083515167236</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9680480957031</t>
+    <t xml:space="preserve">16.9680500030518</t>
   </si>
   <si>
     <t xml:space="preserve">16.7285003662109</t>
@@ -1799,10 +1799,10 @@
     <t xml:space="preserve">17.1277503967285</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8793487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0452423095703</t>
+    <t xml:space="preserve">16.8793506622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0452404022217</t>
   </si>
   <si>
     <t xml:space="preserve">16.9208240509033</t>
@@ -1817,19 +1817,19 @@
     <t xml:space="preserve">17.1281852722168</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1696586608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4184913635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3770217895508</t>
+    <t xml:space="preserve">17.1696605682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.418493270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3770198822021</t>
   </si>
   <si>
     <t xml:space="preserve">17.4599666595459</t>
   </si>
   <si>
-    <t xml:space="preserve">17.294075012207</t>
+    <t xml:space="preserve">17.2940769195557</t>
   </si>
   <si>
     <t xml:space="preserve">16.9622955322266</t>
@@ -1844,7 +1844,7 @@
     <t xml:space="preserve">16.3402080535889</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4895076751709</t>
+    <t xml:space="preserve">16.4895057678223</t>
   </si>
   <si>
     <t xml:space="preserve">16.5392742156982</t>
@@ -1856,13 +1856,13 @@
     <t xml:space="preserve">17.667329788208</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5014419555664</t>
+    <t xml:space="preserve">17.5014381408691</t>
   </si>
   <si>
     <t xml:space="preserve">17.5429096221924</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2526035308838</t>
+    <t xml:space="preserve">17.2526016235352</t>
   </si>
   <si>
     <t xml:space="preserve">16.7134590148926</t>
@@ -1877,34 +1877,34 @@
     <t xml:space="preserve">16.2406711578369</t>
   </si>
   <si>
-    <t xml:space="preserve">16.17431640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2738513946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.124547958374</t>
+    <t xml:space="preserve">16.1743144989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2738494873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1245498657227</t>
   </si>
   <si>
     <t xml:space="preserve">16.3070278167725</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8591251373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.726411819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7927684783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0747814178467</t>
+    <t xml:space="preserve">15.8591241836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7264108657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7927675247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.074779510498</t>
   </si>
   <si>
     <t xml:space="preserve">15.5273418426514</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4278106689453</t>
+    <t xml:space="preserve">15.427809715271</t>
   </si>
   <si>
     <t xml:space="preserve">15.6600532531738</t>
@@ -1913,37 +1913,37 @@
     <t xml:space="preserve">15.178973197937</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3614540100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6932325363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6102895736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4609870910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4443988800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.378041267395</t>
+    <t xml:space="preserve">15.3614521026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6932334899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6102886199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4609861373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4444007873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3780431747437</t>
   </si>
   <si>
     <t xml:space="preserve">15.2950973510742</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9254779815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2904376983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3899707794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4397411346436</t>
+    <t xml:space="preserve">15.925479888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2904396057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3899726867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4397392272949</t>
   </si>
   <si>
     <t xml:space="preserve">16.6719856262207</t>
@@ -1952,10 +1952,10 @@
     <t xml:space="preserve">17.9576377868652</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0867099761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3355484008789</t>
+    <t xml:space="preserve">17.0867118835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3355464935303</t>
   </si>
   <si>
     <t xml:space="preserve">16.8378753662109</t>
@@ -1964,10 +1964,10 @@
     <t xml:space="preserve">16.5890407562256</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2572593688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8757123947144</t>
+    <t xml:space="preserve">16.2572612762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.87571144104</t>
   </si>
   <si>
     <t xml:space="preserve">15.9088916778564</t>
@@ -1976,37 +1976,37 @@
     <t xml:space="preserve">16.1577281951904</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1411380767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4729194641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7595911026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6766443252563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5936985015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4775762557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7430009841919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7098236083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8425350189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3567924499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.323616027832</t>
+    <t xml:space="preserve">16.1411361694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4729175567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7595891952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6766424179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5936994552612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.477575302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7429990768433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7098217010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8425340652466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3567943572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3236179351807</t>
   </si>
   <si>
     <t xml:space="preserve">15.9752464294434</t>
@@ -2015,28 +2015,28 @@
     <t xml:space="preserve">17.5843849182129</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0037670135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2240829467773</t>
+    <t xml:space="preserve">17.0037689208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2240810394287</t>
   </si>
   <si>
     <t xml:space="preserve">16.0084247589111</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1909046173096</t>
+    <t xml:space="preserve">16.1909065246582</t>
   </si>
   <si>
     <t xml:space="preserve">16.5558624267578</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5319995880127</t>
+    <t xml:space="preserve">14.5320014953613</t>
   </si>
   <si>
     <t xml:space="preserve">14.7974252700806</t>
   </si>
   <si>
-    <t xml:space="preserve">14.183629989624</t>
+    <t xml:space="preserve">14.1836309432983</t>
   </si>
   <si>
     <t xml:space="preserve">13.9347944259644</t>
@@ -2045,19 +2045,19 @@
     <t xml:space="preserve">13.6361923217773</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4371242523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2712326049805</t>
+    <t xml:space="preserve">13.4371252059937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2712335586548</t>
   </si>
   <si>
     <t xml:space="preserve">13.3873558044434</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7616319656372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9606990814209</t>
+    <t xml:space="preserve">11.7616310119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9607000350952</t>
   </si>
   <si>
     <t xml:space="preserve">12.4251918792725</t>
@@ -2069,7 +2069,7 @@
     <t xml:space="preserve">11.4796161651611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1690826416016</t>
+    <t xml:space="preserve">10.1690816879272</t>
   </si>
   <si>
     <t xml:space="preserve">10.3681516647339</t>
@@ -2084,7 +2084,7 @@
     <t xml:space="preserve">11.8777532577515</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4417810440063</t>
+    <t xml:space="preserve">12.441780090332</t>
   </si>
   <si>
     <t xml:space="preserve">12.8565082550049</t>
@@ -2093,13 +2093,13 @@
     <t xml:space="preserve">12.1763563156128</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2924795150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2141933441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9155893325806</t>
+    <t xml:space="preserve">12.2924785614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2141923904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9155883789062</t>
   </si>
   <si>
     <t xml:space="preserve">10.6667537689209</t>
@@ -2111,13 +2111,13 @@
     <t xml:space="preserve">10.4510955810547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5174531936646</t>
+    <t xml:space="preserve">10.5174541473389</t>
   </si>
   <si>
     <t xml:space="preserve">10.5340414047241</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4013290405273</t>
+    <t xml:space="preserve">10.401328086853</t>
   </si>
   <si>
     <t xml:space="preserve">10.1524934768677</t>
@@ -2129,13 +2129,13 @@
     <t xml:space="preserve">9.97001457214355</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4676847457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6999320983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3017950057983</t>
+    <t xml:space="preserve">10.4676856994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6999311447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.301794052124</t>
   </si>
   <si>
     <t xml:space="preserve">10.0695486068726</t>
@@ -2156,28 +2156,28 @@
     <t xml:space="preserve">9.92024707794189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45575332641602</t>
+    <t xml:space="preserve">9.45575428009033</t>
   </si>
   <si>
     <t xml:space="preserve">9.50552082061768</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32304096221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14056301116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07420539855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68800163269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1359043121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70458889007568</t>
+    <t xml:space="preserve">9.32304191589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14056205749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07420444488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68800067901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1359052658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70458984375</t>
   </si>
   <si>
     <t xml:space="preserve">9.38939762115479</t>
@@ -2186,10 +2186,10 @@
     <t xml:space="preserve">10.4345073699951</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2188491821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4179182052612</t>
+    <t xml:space="preserve">10.2188501358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4179191589355</t>
   </si>
   <si>
     <t xml:space="preserve">10.9985342025757</t>
@@ -2204,22 +2204,22 @@
     <t xml:space="preserve">10.8160543441772</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8824119567871</t>
+    <t xml:space="preserve">10.8824110031128</t>
   </si>
   <si>
     <t xml:space="preserve">11.8113975524902</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7782192230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5957403182983</t>
+    <t xml:space="preserve">11.7782182693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.595739364624</t>
   </si>
   <si>
     <t xml:space="preserve">11.3634929656982</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6833429336548</t>
+    <t xml:space="preserve">10.6833419799805</t>
   </si>
   <si>
     <t xml:space="preserve">10.9487676620483</t>
@@ -2231,16 +2231,16 @@
     <t xml:space="preserve">11.2639589309692</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2805480957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1810140609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3303146362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.297137260437</t>
+    <t xml:space="preserve">11.2805490493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1810150146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3303155899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2971382141113</t>
   </si>
   <si>
     <t xml:space="preserve">11.0814800262451</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">11.0151233673096</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0648908615112</t>
+    <t xml:space="preserve">11.0648899078369</t>
   </si>
   <si>
     <t xml:space="preserve">10.8326435089111</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">10.3847398757935</t>
   </si>
   <si>
-    <t xml:space="preserve">10.650164604187</t>
+    <t xml:space="preserve">10.6501655578613</t>
   </si>
   <si>
     <t xml:space="preserve">10.3515615463257</t>
@@ -2285,13 +2285,13 @@
     <t xml:space="preserve">10.6169862747192</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4842739105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0197811126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3349742889404</t>
+    <t xml:space="preserve">10.4842748641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0197801589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3349723815918</t>
   </si>
   <si>
     <t xml:space="preserve">10.7828769683838</t>
@@ -2306,76 +2306,76 @@
     <t xml:space="preserve">11.4132604598999</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4298496246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2307815551758</t>
+    <t xml:space="preserve">11.4298486709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2307825088501</t>
   </si>
   <si>
     <t xml:space="preserve">10.8658227920532</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3137264251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3966722488403</t>
+    <t xml:space="preserve">11.3137273788452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.396671295166</t>
   </si>
   <si>
     <t xml:space="preserve">11.5127944946289</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8611640930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2095346450806</t>
+    <t xml:space="preserve">11.8611650466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2095336914062</t>
   </si>
   <si>
     <t xml:space="preserve">11.9772882461548</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0602331161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2593021392822</t>
+    <t xml:space="preserve">12.0602340698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2593011856079</t>
   </si>
   <si>
     <t xml:space="preserve">11.3800830841064</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1146574020386</t>
+    <t xml:space="preserve">11.1146564483643</t>
   </si>
   <si>
     <t xml:space="preserve">10.6335754394531</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2686166763306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55528831481934</t>
+    <t xml:space="preserve">10.2686176300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55528926849365</t>
   </si>
   <si>
     <t xml:space="preserve">9.62164497375488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65482330322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60505390167236</t>
+    <t xml:space="preserve">9.65482234954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.605055809021</t>
   </si>
   <si>
     <t xml:space="preserve">9.75435733795166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4915494918823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0058097839355</t>
+    <t xml:space="preserve">12.491548538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0058088302612</t>
   </si>
   <si>
     <t xml:space="preserve">12.1929454803467</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8399181365967</t>
+    <t xml:space="preserve">12.839919090271</t>
   </si>
   <si>
     <t xml:space="preserve">13.3210000991821</t>
@@ -2384,43 +2384,43 @@
     <t xml:space="preserve">12.4086027145386</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2758922576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7237939834595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9062747955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1053428649902</t>
+    <t xml:space="preserve">12.2758913040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7237949371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9062738418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1053419113159</t>
   </si>
   <si>
     <t xml:space="preserve">12.9892196655273</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0721654891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0223970413208</t>
+    <t xml:space="preserve">13.0721645355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0223960876465</t>
   </si>
   <si>
     <t xml:space="preserve">13.0887537002563</t>
   </si>
   <si>
-    <t xml:space="preserve">13.038987159729</t>
+    <t xml:space="preserve">13.0389862060547</t>
   </si>
   <si>
     <t xml:space="preserve">12.6740274429321</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4583711624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5081367492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7403841018677</t>
+    <t xml:space="preserve">12.4583702087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5081377029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7403831481934</t>
   </si>
   <si>
     <t xml:space="preserve">12.3754243850708</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">12.4749593734741</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6574382781982</t>
+    <t xml:space="preserve">12.6574392318726</t>
   </si>
   <si>
     <t xml:space="preserve">12.9560403823853</t>
@@ -2441,19 +2441,19 @@
     <t xml:space="preserve">13.536657333374</t>
   </si>
   <si>
-    <t xml:space="preserve">13.984561920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3661088943481</t>
+    <t xml:space="preserve">13.9845628738403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3661098480225</t>
   </si>
   <si>
     <t xml:space="preserve">14.5817680358887</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6978902816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7642469406128</t>
+    <t xml:space="preserve">14.6978912353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7642459869385</t>
   </si>
   <si>
     <t xml:space="preserve">14.6315336227417</t>
@@ -2468,13 +2468,13 @@
     <t xml:space="preserve">14.7808351516724</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7476587295532</t>
+    <t xml:space="preserve">14.7476577758789</t>
   </si>
   <si>
     <t xml:space="preserve">14.4988212585449</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3495206832886</t>
+    <t xml:space="preserve">14.3495197296143</t>
   </si>
   <si>
     <t xml:space="preserve">14.2499876022339</t>
@@ -2483,13 +2483,13 @@
     <t xml:space="preserve">14.2333974838257</t>
   </si>
   <si>
-    <t xml:space="preserve">13.785493850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0177392959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0509176254272</t>
+    <t xml:space="preserve">13.7854928970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0177402496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0509185791016</t>
   </si>
   <si>
     <t xml:space="preserve">14.2831649780273</t>
@@ -2498,43 +2498,43 @@
     <t xml:space="preserve">15.0462598800659</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9301376342773</t>
+    <t xml:space="preserve">14.9301357269287</t>
   </si>
   <si>
     <t xml:space="preserve">15.3946304321289</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3448629379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9918355941772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8969573974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9799032211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9135465621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9964942932129</t>
+    <t xml:space="preserve">15.3448648452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9918384552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8969583511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9799041748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9135475158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9964933395386</t>
   </si>
   <si>
     <t xml:space="preserve">15.825945854187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6434650421143</t>
+    <t xml:space="preserve">15.6434679031372</t>
   </si>
   <si>
     <t xml:space="preserve">16.0250148773193</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0913715362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0581912994385</t>
+    <t xml:space="preserve">16.0913696289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0581932067871</t>
   </si>
   <si>
     <t xml:space="preserve">15.5605211257935</t>
@@ -2549,61 +2549,61 @@
     <t xml:space="preserve">15.2287406921387</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1457948684692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4941663742065</t>
+    <t xml:space="preserve">15.1457958221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4941654205322</t>
   </si>
   <si>
     <t xml:space="preserve">15.6268758773804</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2121496200562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5024576187134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2702140808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2536239624023</t>
+    <t xml:space="preserve">15.2121515274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.502459526062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2702131271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2536249160767</t>
   </si>
   <si>
     <t xml:space="preserve">15.5439329147339</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5771102905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8508281707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7181167602539</t>
+    <t xml:space="preserve">15.577112197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8508291244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7181177139282</t>
   </si>
   <si>
     <t xml:space="preserve">15.7347059249878</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8840093612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.751296043396</t>
+    <t xml:space="preserve">15.8840065002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7512941360474</t>
   </si>
   <si>
     <t xml:space="preserve">15.4361038208008</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3982677459717</t>
+    <t xml:space="preserve">16.398265838623</t>
   </si>
   <si>
     <t xml:space="preserve">16.5807476043701</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8674173355103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0830745697021</t>
+    <t xml:space="preserve">15.8674192428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0830764770508</t>
   </si>
   <si>
     <t xml:space="preserve">16.1079597473145</t>
@@ -2612,19 +2612,19 @@
     <t xml:space="preserve">16.4646244049072</t>
   </si>
   <si>
-    <t xml:space="preserve">16.622220993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8212890625</t>
+    <t xml:space="preserve">16.6222190856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8212871551514</t>
   </si>
   <si>
     <t xml:space="preserve">16.7051639556885</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9042320251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9374103546143</t>
+    <t xml:space="preserve">16.9042339324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9374122619629</t>
   </si>
   <si>
     <t xml:space="preserve">17.1364803314209</t>
@@ -2636,46 +2636,46 @@
     <t xml:space="preserve">17.4350833892822</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4516716003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.219425201416</t>
+    <t xml:space="preserve">17.4516735076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2194271087646</t>
   </si>
   <si>
     <t xml:space="preserve">16.7217540740967</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1530685424805</t>
+    <t xml:space="preserve">17.1530704498291</t>
   </si>
   <si>
     <t xml:space="preserve">17.0535354614258</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0369453430176</t>
+    <t xml:space="preserve">17.0369472503662</t>
   </si>
   <si>
     <t xml:space="preserve">16.8876457214355</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7715225219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8544673919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2028369903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1033000946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1198921203613</t>
+    <t xml:space="preserve">16.771520614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8544654846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2028350830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1033039093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1198902130127</t>
   </si>
   <si>
     <t xml:space="preserve">16.7383422851562</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3521366119385</t>
+    <t xml:space="preserve">17.3521385192871</t>
   </si>
   <si>
     <t xml:space="preserve">17.2691917419434</t>
@@ -2690,31 +2690,31 @@
     <t xml:space="preserve">16.2074947357178</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2323780059814</t>
+    <t xml:space="preserve">16.2323760986328</t>
   </si>
   <si>
     <t xml:space="preserve">16.6056308746338</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6958503723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1981792449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1650009155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.617561340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0820560455322</t>
+    <t xml:space="preserve">18.6958522796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1981773376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1649990081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6175632476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0820541381836</t>
   </si>
   <si>
     <t xml:space="preserve">17.6507415771484</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8000411987305</t>
+    <t xml:space="preserve">17.8000392913818</t>
   </si>
   <si>
     <t xml:space="preserve">17.4019031524658</t>
@@ -2723,16 +2723,16 @@
     <t xml:space="preserve">17.3189601898193</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0203552246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7881126403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9705867767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1862487792969</t>
+    <t xml:space="preserve">17.0203590393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7881088256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9705905914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1862468719482</t>
   </si>
   <si>
     <t xml:space="preserve">16.4065628051758</t>
@@ -2750,7 +2750,7 @@
     <t xml:space="preserve">17.5346164703369</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0701236724854</t>
+    <t xml:space="preserve">17.070125579834</t>
   </si>
   <si>
     <t xml:space="preserve">17.2360134124756</t>
@@ -2759,10 +2759,10 @@
     <t xml:space="preserve">17.6839179992676</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4848499298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.276216506958</t>
+    <t xml:space="preserve">17.4848518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2762145996094</t>
   </si>
   <si>
     <t xml:space="preserve">17.2424736022949</t>
@@ -2783,10 +2783,10 @@
     <t xml:space="preserve">17.6642589569092</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4449291229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4618015289307</t>
+    <t xml:space="preserve">17.4449310302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4618034362793</t>
   </si>
   <si>
     <t xml:space="preserve">17.1749897003174</t>
@@ -2795,7 +2795,7 @@
     <t xml:space="preserve">17.0400199890137</t>
   </si>
   <si>
-    <t xml:space="preserve">17.006275177002</t>
+    <t xml:space="preserve">17.0062770843506</t>
   </si>
   <si>
     <t xml:space="preserve">16.9556617736816</t>
@@ -2804,16 +2804,16 @@
     <t xml:space="preserve">16.8628711700439</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0906314849854</t>
+    <t xml:space="preserve">17.090633392334</t>
   </si>
   <si>
     <t xml:space="preserve">16.8713054656982</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7532081604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2087306976318</t>
+    <t xml:space="preserve">16.7532062530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2087326049805</t>
   </si>
   <si>
     <t xml:space="preserve">16.2048892974854</t>
@@ -2822,13 +2822,13 @@
     <t xml:space="preserve">16.0952262878418</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1458396911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7915420532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6903162002563</t>
+    <t xml:space="preserve">16.1458377838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7915410995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.690315246582</t>
   </si>
   <si>
     <t xml:space="preserve">15.8590278625488</t>
@@ -2837,16 +2837,16 @@
     <t xml:space="preserve">15.4119396209717</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5216007232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0998182296753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4203748703003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.60595703125</t>
+    <t xml:space="preserve">15.5215997695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0998191833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.420373916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6059589385986</t>
   </si>
   <si>
     <t xml:space="preserve">15.5806512832642</t>
@@ -2855,10 +2855,10 @@
     <t xml:space="preserve">15.833722114563</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0446128845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8759002685547</t>
+    <t xml:space="preserve">16.0446109771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8758993148804</t>
   </si>
   <si>
     <t xml:space="preserve">15.8927688598633</t>
@@ -2867,52 +2867,52 @@
     <t xml:space="preserve">16.0108680725098</t>
   </si>
   <si>
-    <t xml:space="preserve">15.934947013855</t>
+    <t xml:space="preserve">15.9349479675293</t>
   </si>
   <si>
     <t xml:space="preserve">15.7662353515625</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7746706008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.513165473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4878597259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.184175491333</t>
+    <t xml:space="preserve">15.7746715545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5131664276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4878587722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1841735839844</t>
   </si>
   <si>
     <t xml:space="preserve">15.2347888946533</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3950672149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9433841705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1120986938477</t>
+    <t xml:space="preserve">15.3950662612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9433822631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.112096786499</t>
   </si>
   <si>
     <t xml:space="preserve">16.2976818084717</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4495239257812</t>
+    <t xml:space="preserve">16.4495220184326</t>
   </si>
   <si>
     <t xml:space="preserve">15.5890846252441</t>
   </si>
   <si>
-    <t xml:space="preserve">15.698751449585</t>
+    <t xml:space="preserve">15.6987504959106</t>
   </si>
   <si>
     <t xml:space="preserve">16.0361766815186</t>
   </si>
   <si>
-    <t xml:space="preserve">15.968692779541</t>
+    <t xml:space="preserve">15.9686918258667</t>
   </si>
   <si>
     <t xml:space="preserve">16.3145542144775</t>
@@ -2921,22 +2921,22 @@
     <t xml:space="preserve">15.9180765151978</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0193061828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5384731292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0154619216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.150429725647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5300378799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8168497085571</t>
+    <t xml:space="preserve">16.0193042755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5384740829468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0154609680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1504316329956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5300369262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8168487548828</t>
   </si>
   <si>
     <t xml:space="preserve">15.5637807846069</t>
@@ -2945,16 +2945,16 @@
     <t xml:space="preserve">15.8843336105347</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1374034881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8674631118774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4541139602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9732847213745</t>
+    <t xml:space="preserve">16.1374053955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8674640655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4541149139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9732856750488</t>
   </si>
   <si>
     <t xml:space="preserve">15.0238971710205</t>
@@ -2966,19 +2966,19 @@
     <t xml:space="preserve">15.4372453689575</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6312646865845</t>
+    <t xml:space="preserve">15.6312656402588</t>
   </si>
   <si>
     <t xml:space="preserve">15.4794235229492</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1588668823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7623929977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4080953598022</t>
+    <t xml:space="preserve">15.1588659286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7623920440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4080944061279</t>
   </si>
   <si>
     <t xml:space="preserve">13.7416791915894</t>
@@ -2987,7 +2987,7 @@
     <t xml:space="preserve">14.0537977218628</t>
   </si>
   <si>
-    <t xml:space="preserve">14.121283531189</t>
+    <t xml:space="preserve">14.1212825775146</t>
   </si>
   <si>
     <t xml:space="preserve">13.4295587539673</t>
@@ -2996,28 +2996,28 @@
     <t xml:space="preserve">13.5898370742798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1427459716797</t>
+    <t xml:space="preserve">13.142746925354</t>
   </si>
   <si>
     <t xml:space="preserve">12.7294006347656</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6028652191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9065494537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3367671966553</t>
+    <t xml:space="preserve">12.6028642654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.906548500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3367681503296</t>
   </si>
   <si>
     <t xml:space="preserve">13.1258754730225</t>
   </si>
   <si>
-    <t xml:space="preserve">13.513916015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9188261032104</t>
+    <t xml:space="preserve">13.5139169692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9188270568848</t>
   </si>
   <si>
     <t xml:space="preserve">13.3198957443237</t>
@@ -3029,16 +3029,16 @@
     <t xml:space="preserve">12.8728065490723</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9318561553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7631435394287</t>
+    <t xml:space="preserve">12.9318552017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7631425857544</t>
   </si>
   <si>
     <t xml:space="preserve">12.6366081237793</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4172811508179</t>
+    <t xml:space="preserve">12.4172801971436</t>
   </si>
   <si>
     <t xml:space="preserve">12.484766960144</t>
@@ -3047,7 +3047,7 @@
     <t xml:space="preserve">12.6872224807739</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6619148254395</t>
+    <t xml:space="preserve">12.6619157791138</t>
   </si>
   <si>
     <t xml:space="preserve">12.7209644317627</t>
@@ -3065,7 +3065,7 @@
     <t xml:space="preserve">12.3497953414917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3666667938232</t>
+    <t xml:space="preserve">12.3666658401489</t>
   </si>
   <si>
     <t xml:space="preserve">12.5859937667847</t>
@@ -3074,13 +3074,13 @@
     <t xml:space="preserve">13.4126873016357</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3958158493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4464302062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7838573455811</t>
+    <t xml:space="preserve">13.3958168029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4464311599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7838563919067</t>
   </si>
   <si>
     <t xml:space="preserve">13.3114604949951</t>
@@ -3089,16 +3089,16 @@
     <t xml:space="preserve">13.2271041870117</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9571628570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0752620697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7040948867798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7715787887573</t>
+    <t xml:space="preserve">12.9571619033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0752630233765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7040939331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7715797424316</t>
   </si>
   <si>
     <t xml:space="preserve">12.4004096984863</t>
@@ -3107,25 +3107,25 @@
     <t xml:space="preserve">12.2148246765137</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0461111068726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8773984909058</t>
+    <t xml:space="preserve">12.0461120605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8773994445801</t>
   </si>
   <si>
     <t xml:space="preserve">12.1473398208618</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1642112731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2316970825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.451024055481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3835391998291</t>
+    <t xml:space="preserve">12.1642122268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2316961288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4510231018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3835382461548</t>
   </si>
   <si>
     <t xml:space="preserve">12.2991819381714</t>
@@ -3137,7 +3137,7 @@
     <t xml:space="preserve">11.6749429702759</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6487474441528</t>
+    <t xml:space="preserve">11.6487464904785</t>
   </si>
   <si>
     <t xml:space="preserve">11.474102973938</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">11.8932485580444</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9107122421265</t>
+    <t xml:space="preserve">11.9107131958008</t>
   </si>
   <si>
     <t xml:space="preserve">12.4346437454224</t>
@@ -3167,10 +3167,10 @@
     <t xml:space="preserve">12.1901426315308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3298568725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5568943023682</t>
+    <t xml:space="preserve">12.3298578262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5568952560425</t>
   </si>
   <si>
     <t xml:space="preserve">12.3123931884766</t>
@@ -3182,13 +3182,13 @@
     <t xml:space="preserve">11.4391746520996</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1946725845337</t>
+    <t xml:space="preserve">11.1946716308594</t>
   </si>
   <si>
     <t xml:space="preserve">11.7186040878296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5788898468018</t>
+    <t xml:space="preserve">11.5788888931274</t>
   </si>
   <si>
     <t xml:space="preserve">11.8408555984497</t>
@@ -3209,19 +3209,19 @@
     <t xml:space="preserve">11.49156665802</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2645301818848</t>
+    <t xml:space="preserve">11.2645292282104</t>
   </si>
   <si>
     <t xml:space="preserve">10.8104562759399</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0549573898315</t>
+    <t xml:space="preserve">11.0549583435059</t>
   </si>
   <si>
     <t xml:space="preserve">11.1772079467773</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3867807388306</t>
+    <t xml:space="preserve">11.3867797851562</t>
   </si>
   <si>
     <t xml:space="preserve">11.2470655441284</t>
@@ -3242,10 +3242,10 @@
     <t xml:space="preserve">11.4042453765869</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2296018600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6138191223145</t>
+    <t xml:space="preserve">11.2296009063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6138181686401</t>
   </si>
   <si>
     <t xml:space="preserve">11.7884616851807</t>
@@ -3260,25 +3260,25 @@
     <t xml:space="preserve">11.5614242553711</t>
   </si>
   <si>
-    <t xml:space="preserve">11.456639289856</t>
+    <t xml:space="preserve">11.4566383361816</t>
   </si>
   <si>
     <t xml:space="preserve">11.5439605712891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4217100143433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1073503494263</t>
+    <t xml:space="preserve">11.4217090606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1073513031006</t>
   </si>
   <si>
     <t xml:space="preserve">11.0898857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7231330871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6882047653198</t>
+    <t xml:space="preserve">10.7231340408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6882057189941</t>
   </si>
   <si>
     <t xml:space="preserve">10.6707410812378</t>
@@ -3305,7 +3305,7 @@
     <t xml:space="preserve">9.90230846405029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81498622894287</t>
+    <t xml:space="preserve">9.81498527526855</t>
   </si>
   <si>
     <t xml:space="preserve">9.76259326934814</t>
@@ -3317,28 +3317,28 @@
     <t xml:space="preserve">10.1992034912109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29105472564697</t>
+    <t xml:space="preserve">9.29105567932129</t>
   </si>
   <si>
     <t xml:space="preserve">9.51809120178223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2211971282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25612545013428</t>
+    <t xml:space="preserve">9.22119808197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25612640380859</t>
   </si>
   <si>
     <t xml:space="preserve">9.0640172958374</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80205059051514</t>
+    <t xml:space="preserve">8.80205154418945</t>
   </si>
   <si>
     <t xml:space="preserve">8.8195161819458</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60121250152588</t>
+    <t xml:space="preserve">8.60121154785156</t>
   </si>
   <si>
     <t xml:space="preserve">8.48769283294678</t>
@@ -3347,19 +3347,19 @@
     <t xml:space="preserve">8.19079780578613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44403266906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4614953994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33924579620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56628322601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34797859191895</t>
+    <t xml:space="preserve">8.44403171539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46149444580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3392448425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56628227233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34797763824463</t>
   </si>
   <si>
     <t xml:space="preserve">8.54881763458252</t>
@@ -3386,13 +3386,13 @@
     <t xml:space="preserve">8.73219394683838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02908802032471</t>
+    <t xml:space="preserve">9.02908897399902</t>
   </si>
   <si>
     <t xml:space="preserve">9.09894561767578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41330432891846</t>
+    <t xml:space="preserve">9.41330528259277</t>
   </si>
   <si>
     <t xml:space="preserve">9.308518409729</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">9.55301952362061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.622878074646</t>
+    <t xml:space="preserve">9.62287712097168</t>
   </si>
   <si>
     <t xml:space="preserve">9.91977214813232</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">10.269061088562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65780735015869</t>
+    <t xml:space="preserve">9.65780639648438</t>
   </si>
   <si>
     <t xml:space="preserve">9.64034175872803</t>
@@ -3434,7 +3434,7 @@
     <t xml:space="preserve">10.0420236587524</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69273567199707</t>
+    <t xml:space="preserve">9.69273471832275</t>
   </si>
   <si>
     <t xml:space="preserve">9.93723678588867</t>
@@ -3443,7 +3443,7 @@
     <t xml:space="preserve">9.97216606140137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88484382629395</t>
+    <t xml:space="preserve">9.88484287261963</t>
   </si>
   <si>
     <t xml:space="preserve">9.8673791885376</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">10.0944166183472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0769519805908</t>
+    <t xml:space="preserve">10.0769510269165</t>
   </si>
   <si>
     <t xml:space="preserve">9.79752159118652</t>
@@ -3476,16 +3476,16 @@
     <t xml:space="preserve">10.7405986785889</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7580623626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9152421951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0200281143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3518524169922</t>
+    <t xml:space="preserve">10.7580633163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9152431488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0200290679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3518514633179</t>
   </si>
   <si>
     <t xml:space="preserve">11.0025644302368</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">10.9676361083984</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5310258865356</t>
+    <t xml:space="preserve">10.53102684021</t>
   </si>
   <si>
     <t xml:space="preserve">10.6183471679688</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">10.0245580673218</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84991455078125</t>
+    <t xml:space="preserve">9.84991359710693</t>
   </si>
   <si>
     <t xml:space="preserve">10.1118803024292</t>
@@ -3554,13 +3554,13 @@
     <t xml:space="preserve">11.8757839202881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0678911209106</t>
+    <t xml:space="preserve">12.067892074585</t>
   </si>
   <si>
     <t xml:space="preserve">12.0329627990723</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4650430679321</t>
+    <t xml:space="preserve">13.4650440216064</t>
   </si>
   <si>
     <t xml:space="preserve">13.1681480407715</t>
@@ -3572,7 +3572,7 @@
     <t xml:space="preserve">12.8712530136108</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6442155838013</t>
+    <t xml:space="preserve">12.6442165374756</t>
   </si>
   <si>
     <t xml:space="preserve">12.9491128921509</t>
@@ -70815,7 +70815,7 @@
     </row>
     <row r="2532">
       <c r="A2532" s="1" t="n">
-        <v>46003.6913078704</v>
+        <v>46003.3333333333</v>
       </c>
       <c r="B2532" t="n">
         <v>90807</v>
@@ -70836,6 +70836,32 @@
         <v>1552</v>
       </c>
       <c r="H2532" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2533">
+      <c r="A2533" s="1" t="n">
+        <v>46006.6911689815</v>
+      </c>
+      <c r="B2533" t="n">
+        <v>64263</v>
+      </c>
+      <c r="C2533" t="n">
+        <v>9.02999973297119</v>
+      </c>
+      <c r="D2533" t="n">
+        <v>8.93000030517578</v>
+      </c>
+      <c r="E2533" t="n">
+        <v>8.96000003814697</v>
+      </c>
+      <c r="F2533" t="n">
+        <v>8.98999977111816</v>
+      </c>
+      <c r="G2533" t="s">
+        <v>1485</v>
+      </c>
+      <c r="H2533" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARR.MI.xlsx
+++ b/data/MARR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="1554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="1555">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4479522705078</t>
+    <t xml:space="preserve">13.4479503631592</t>
   </si>
   <si>
     <t xml:space="preserve">MARR.MI</t>
@@ -50,61 +50,61 @@
     <t xml:space="preserve">13.1812992095947</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9939212799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9506788253784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5903358459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6551990509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7344751358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4389953613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4462032318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9849624633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0858602523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6462430953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2155838012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8353700637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6768198013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5615110397339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5543060302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6407861709595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7200603485107</t>
+    <t xml:space="preserve">12.9939193725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9506778717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5903377532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.655198097229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7344732284546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4389944076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4462022781372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9849634170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0858612060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6462421417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2155828475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8353710174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6768207550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5615100860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5543041229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6407871246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7200622558594</t>
   </si>
   <si>
     <t xml:space="preserve">12.9722995758057</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7777166366577</t>
+    <t xml:space="preserve">12.7777156829834</t>
   </si>
   <si>
     <t xml:space="preserve">12.3308935165405</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">12.5110635757446</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2948560714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4084167480469</t>
+    <t xml:space="preserve">12.2948570251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4084177017212</t>
   </si>
   <si>
     <t xml:space="preserve">11.4516582489014</t>
@@ -125,10 +125,10 @@
     <t xml:space="preserve">11.8840684890747</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5885877609253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8912744522095</t>
+    <t xml:space="preserve">11.588586807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8912754058838</t>
   </si>
   <si>
     <t xml:space="preserve">11.9273071289062</t>
@@ -137,43 +137,43 @@
     <t xml:space="preserve">12.0426187515259</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2011680603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3957557678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7056465148926</t>
+    <t xml:space="preserve">12.2011690139771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3957529067993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7056446075439</t>
   </si>
   <si>
     <t xml:space="preserve">12.6047515869141</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5759248733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9362678527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1596784591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9434728622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0731954574585</t>
+    <t xml:space="preserve">12.5759239196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9362668991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1596765518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9434719085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0731945037842</t>
   </si>
   <si>
     <t xml:space="preserve">12.8858184814453</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5975437164307</t>
+    <t xml:space="preserve">12.597544670105</t>
   </si>
   <si>
     <t xml:space="preserve">12.078652381897</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3597183227539</t>
+    <t xml:space="preserve">12.3597192764282</t>
   </si>
   <si>
     <t xml:space="preserve">12.6696128845215</t>
@@ -182,40 +182,40 @@
     <t xml:space="preserve">12.8137493133545</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6984415054321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8714046478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.453408241272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3453054428101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6840286254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7560939788818</t>
+    <t xml:space="preserve">12.6984405517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8714027404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4534091949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3453044891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6840267181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7560949325562</t>
   </si>
   <si>
     <t xml:space="preserve">13.1524696350098</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2677803039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3326406478882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0804023742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1885032653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2605724334717</t>
+    <t xml:space="preserve">13.2677793502808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3326396942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0804014205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1885042190552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2605714797974</t>
   </si>
   <si>
     <t xml:space="preserve">13.7073984146118</t>
@@ -224,49 +224,49 @@
     <t xml:space="preserve">13.491192817688</t>
   </si>
   <si>
-    <t xml:space="preserve">13.347056388855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0011281967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9002313613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8281650543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7921285629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.058783531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1020240783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8065414428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2821941375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1380567550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8425779342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8930253982544</t>
+    <t xml:space="preserve">13.3470554351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.001127243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9002323150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.828164100647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7921295166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0587825775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1020231246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8065433502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2821960449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1380548477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8425760269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8930244445801</t>
   </si>
   <si>
     <t xml:space="preserve">12.9074382781982</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0227460861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6624069213867</t>
+    <t xml:space="preserve">13.0227489471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6624059677124</t>
   </si>
   <si>
     <t xml:space="preserve">12.8786115646362</t>
@@ -275,70 +275,70 @@
     <t xml:space="preserve">12.6335783004761</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7488880157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0258750915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0183877944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2579441070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2504587173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4301271438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4825277328491</t>
+    <t xml:space="preserve">12.7488889694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0258741378784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0183887481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.25794506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2504596710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4301252365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4825286865234</t>
   </si>
   <si>
     <t xml:space="preserve">13.3103485107422</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2654314041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.475043296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3702383041382</t>
+    <t xml:space="preserve">13.2654323577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4750442504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3702373504639</t>
   </si>
   <si>
     <t xml:space="preserve">13.2878894805908</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2729187011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2804040908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8012924194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8836374282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6141366958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3146934509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.44944190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8087787628174</t>
+    <t xml:space="preserve">13.2729177474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.280403137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8012933731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.883638381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6141376495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3146915435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4494428634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8087778091431</t>
   </si>
   <si>
     <t xml:space="preserve">12.7938051223755</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0782766342163</t>
+    <t xml:space="preserve">13.0782785415649</t>
   </si>
   <si>
     <t xml:space="preserve">12.4419574737549</t>
@@ -353,40 +353,40 @@
     <t xml:space="preserve">12.7339153289795</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4226398468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5274448394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0558195114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4525842666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3328065872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7595167160034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7295722961426</t>
+    <t xml:space="preserve">13.4226408004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5274467468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0558204650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4525852203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3328084945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7595157623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7295703887939</t>
   </si>
   <si>
     <t xml:space="preserve">13.7220859527588</t>
   </si>
   <si>
-    <t xml:space="preserve">13.53493309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4900150299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.737060546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.014045715332</t>
+    <t xml:space="preserve">13.5349311828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4900169372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7370595932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0140447616577</t>
   </si>
   <si>
     <t xml:space="preserve">13.7071132659912</t>
@@ -395,19 +395,19 @@
     <t xml:space="preserve">13.8493490219116</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1113653182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9766149520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0814208984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7445440292358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9990749359131</t>
+    <t xml:space="preserve">14.111367225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9766159057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0814189910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7445449829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9990730285645</t>
   </si>
   <si>
     <t xml:space="preserve">13.5049886703491</t>
@@ -416,13 +416,13 @@
     <t xml:space="preserve">13.6397380828857</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6621952056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6097946166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3477792739868</t>
+    <t xml:space="preserve">13.6621961593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6097936630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3477802276611</t>
   </si>
   <si>
     <t xml:space="preserve">13.4151544570923</t>
@@ -431,13 +431,13 @@
     <t xml:space="preserve">13.220516204834</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0857639312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1007375717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0633068084717</t>
+    <t xml:space="preserve">13.0857620239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.100736618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0633058547974</t>
   </si>
   <si>
     <t xml:space="preserve">13.2354879379272</t>
@@ -446,25 +446,25 @@
     <t xml:space="preserve">13.1456527709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9285573959351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2055406570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1082239151001</t>
+    <t xml:space="preserve">12.9285564422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2055416107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1082220077515</t>
   </si>
   <si>
     <t xml:space="preserve">13.1980562210083</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1157083511353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0109014511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9135828018188</t>
+    <t xml:space="preserve">13.1157112121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0109024047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9135818481445</t>
   </si>
   <si>
     <t xml:space="preserve">12.8611812591553</t>
@@ -473,52 +473,52 @@
     <t xml:space="preserve">12.943528175354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1905717849731</t>
+    <t xml:space="preserve">13.1905698776245</t>
   </si>
   <si>
     <t xml:space="preserve">13.4076681137085</t>
   </si>
   <si>
-    <t xml:space="preserve">13.355263710022</t>
+    <t xml:space="preserve">13.3552646636963</t>
   </si>
   <si>
     <t xml:space="preserve">13.2130279541016</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3402938842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9659862518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8761548995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8312358856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9809579849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.763858795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7114572525024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8686676025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7563762664795</t>
+    <t xml:space="preserve">13.340292930603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9659852981567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8761529922485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8312349319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9809598922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7638607025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7114562988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8686666488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7563743591309</t>
   </si>
   <si>
     <t xml:space="preserve">12.6815147399902</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5767049789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5467624664307</t>
+    <t xml:space="preserve">12.5767068862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.546763420105</t>
   </si>
   <si>
     <t xml:space="preserve">12.5317907333374</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">12.5617361068726</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5542497634888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4194993972778</t>
+    <t xml:space="preserve">12.5542488098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4194974899292</t>
   </si>
   <si>
     <t xml:space="preserve">12.2772617340088</t>
@@ -539,37 +539,37 @@
     <t xml:space="preserve">12.4719009399414</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5018472671509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3970394134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9778156280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3596096038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4943599700928</t>
+    <t xml:space="preserve">12.5018453598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3970384597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9778175354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3596086502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4943609237671</t>
   </si>
   <si>
     <t xml:space="preserve">12.3820676803589</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4045257568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2697763442993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1649684906006</t>
+    <t xml:space="preserve">12.4045267105103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2697744369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1649694442749</t>
   </si>
   <si>
     <t xml:space="preserve">12.2548027038574</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3371496200562</t>
+    <t xml:space="preserve">12.3371505737305</t>
   </si>
   <si>
     <t xml:space="preserve">12.3221788406372</t>
@@ -578,1858 +578,1858 @@
     <t xml:space="preserve">12.72642993927</t>
   </si>
   <si>
+    <t xml:space="preserve">12.6740255355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7863178253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0932512283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9510126113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1306819915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9884452819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.138165473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1606254577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.183084487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1681127548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2279996871948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.00341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1755981445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4001817703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3852100372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8643236160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9167242050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5199594497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4450979232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3627519607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4600715637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5124740600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4376134872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8268909454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6247663497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8044357299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7819747924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6996269226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8418626785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.677170753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8568363189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7670030593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5648784637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.89426612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3359470367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5605354309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5156154632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6952829360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9722700119019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9348411560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9423246383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.822546005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2043428421021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.713397026062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1369647979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.159423828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2866888046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3615503311157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2268009185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3465785980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6834545135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7208843231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5337295532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4588689804077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1669082641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1968536376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5487022399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4214363098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6011056900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6460218429565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7358560562134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5861320495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9080381393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4245796203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1251373291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6984252929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2823448181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3272590637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2598876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2673721313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5967597961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7839164733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6641368865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.521900177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4470405578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6416759490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0758743286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7988891601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7464847564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8737468719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9560966491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1058158874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3946361541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5069255828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6847534179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1950397491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1641120910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0094814300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7620716094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6306324005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8471183776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0249443054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9398994445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7698001861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9940185546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1254558563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.955358505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5455856323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7156810760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8548488616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7466087341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0404071807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.731143951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5378513336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5687808990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6229038238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.707950592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.72340965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1822032928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0894222259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0816898345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1590061187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9347925186157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2363224029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0739631652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9966440200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3909568786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4914646148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8935070037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2414283752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.055871963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.28782081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2955493927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3960609436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8316555023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.280086517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.700216293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5533199310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4837341308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7775363922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5146579742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3832225799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3986835479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2749824523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2285900115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0584964752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9657182693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.950252532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0352993011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2827110290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4141502380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6074390411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5919742584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9321632385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0481376647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2646217346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9476280212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0713310241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0636024475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.079065322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2723541259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3032817840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3728656768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3187427520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5584239959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5893516540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4656448364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7207870483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5738868713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5429611206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6975936889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1073665618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0377807617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6125450134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.68212890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5197658538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.311014175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1099910736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3574028015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.179573059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1409168243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0867958068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8857746124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6151695251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5301246643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.352294921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0430335998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8265495300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9270582199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1976661682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6692924499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8703136444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7852630615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9630908966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8084621429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9244346618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4218788146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0507640838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4605407714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4528064727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.754337310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6383666992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7929954528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4064159393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3342094421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3805961608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4888381958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5506896972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6898574829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4115238189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6434726715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.256893157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2259654998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5043029785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4991989135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9785537719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3445644378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2981758117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9012393951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6538276672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2672481536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3136386871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4269886016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4475555419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3857040405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.880521774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1433963775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0042285919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.911449432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6949653625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6795024871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7413539886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.664041519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7877464294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2516384124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4371967315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3444175720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.406270980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5609016418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3289566040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1743240356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1124706268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1588592529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2825660705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.236177444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.205249786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2671031951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5299758911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.638219833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5918273925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4835872650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5145149230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4526615142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6072940826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1382942199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3547744750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0764389038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0300483703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1737785339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9501991271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3654193878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2057189941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6209373474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.509147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.588996887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.557056427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4931793212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.157808303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4292984008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6848163604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.636905670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4133262634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4612369537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3175086975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8064708709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8224411010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7106513977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9182605743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9661712646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.03005027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8863201141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9981117248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3973579406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5251197814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4452667236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1479473114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1639175415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0201854705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8604869842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7806377410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5730266571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.06809425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7646656036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4772090911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7007865905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2437648773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4513740539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4992828369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2118263244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1319751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0042152404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1160049438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0361576080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1798858642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3236141204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3395843505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3076438903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.722864151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.467342376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3874950408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5631618499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8825607299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3616619110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4415073394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2658386230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7609100341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0962753295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8247871398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2498683929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4734497070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1540508270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1700210571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7548027038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5312232971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4034671783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8125743865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7327270507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3813896179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2536315917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9342308044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3494491577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9243679046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7486972808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1258697509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7905025482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4391632080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1357307434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2155838012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9760360717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.550952911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8961849212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0718536376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9281272888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8323059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0558853149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1836433410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4551315307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.816333770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3532066345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9858999252319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0976886749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1136589050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4269514083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3311328887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6505317687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4748630523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4429206848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7703046798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.842170715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7383632659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4490261077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2733592987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1615676879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.321268081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4809665679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6246967315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7684230804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1676750183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3433437347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2794647216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.944091796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0079746246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6406669616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.241418838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5608158111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7045440673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8482761383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3752822875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.103796005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8802146911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9121570587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8642463684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.720516204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6885776519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6087265014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7364845275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3052959442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8980646133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1935081481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2094783782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3851490020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.28932762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2573890686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2254505157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9140367507935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4170875549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5288772583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7843971252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5767860412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3691787719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1775379180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4889526367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2494010925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3292541503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4091014862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1695537567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0497779846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5688018798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6486492156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2874488830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0878238677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0479011535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8083515167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9680519104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7285041809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8881988525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1277484893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8793487548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.045238494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9208221435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7964057922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2111301422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1281852722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1696586608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.418493270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3770217895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4599647521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2940731048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9622955322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7549324035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6305122375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3402061462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4895057678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5392742156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7088031768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.667329788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5014381408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.542911529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2526016235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7134609222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4231491088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3733825683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2406692504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1743144989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2738513946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1245460510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3070278167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8591241836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7264099121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7927684783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.074779510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5273418426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.427809715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6600542068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1789722442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3614540100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6932344436646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6102895736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4609842300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4443969726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3780431747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2950963973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.925479888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2904357910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3899726867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4397392272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6719875335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9576377868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0867118835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3355464935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8378772735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5890426635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2572612762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.87571144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9088926315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1577262878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1411361694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4729194641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7595901489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6766452789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5936985015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.477578163147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7430009841919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7098217010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8425350189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3567943572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3236179351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9752464294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5843849182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0037689208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2240829467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0084247589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1909046173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5558624267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.532000541687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7974252700806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1836309432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9347944259644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.636191368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4371242523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2712335586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3873567581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7616300582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9607000350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4251918792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0317115783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4796171188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1690826416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3681516647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95342540740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3183841705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8777542114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4417810440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8565073013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1763553619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.29248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2141923904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9155893325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6667528152466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2022590637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.451096534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5174522399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5340414047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4013299942017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1524934768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0529584884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97001361846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4676856994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6999311447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3017950057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0695476531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2520275115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.003191947937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0363702774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1193141937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92024707794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45575332641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50552082061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32304191589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14056205749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07420635223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68800067901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1359043121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70458793640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38939666748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4345073699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2188501358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4179191589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.99853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.899001121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9819450378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8160552978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8824110031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8113975524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7782201766968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.595739364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3634929656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6833419799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.948766708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9653568267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2639589309692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2805490493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1810140609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3303155899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.297137260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0814790725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0151224136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0648908615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8326454162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.849232673645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5838088989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3847408294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.650164604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2354383468628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9321784973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.550630569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5008640289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6169853210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4842739105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0197811126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3349733352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7828769683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6003971099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1312475204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4132614135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4298486709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2307806015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8658227920532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3137283325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.396671295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5127944946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8611650466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2095346450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9772872924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0602331161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2593011856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3800830841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1146574020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6335763931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2686166763306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55528736114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62164497375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65482234954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60505485534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75435638427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.491548538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0058088302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1929454803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8399181365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3210000991821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4086036682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2758922576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7237939834595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9062747955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1053438186646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.989218711853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0721645355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0223970413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.088752746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.038987159729</t>
+  </si>
+  <si>
     <t xml:space="preserve">12.6740264892578</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7863178253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0932502746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9510135650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1306819915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9884443283081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1381664276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1606254577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1830835342407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1681118011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2280015945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0034189224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1756000518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4001817703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3852100372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8643236160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9167261123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5199604034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4450988769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3627519607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4600706100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5124750137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.437614440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8268928527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6247673034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8044347763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7819747924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6996259689331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8418626785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6771697998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.856837272644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7670011520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5648784637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.89426612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3359489440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5605335235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5156154632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6952829360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9722700119019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9348392486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9423265457153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8225469589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2043399810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.713397026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.136962890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1594228744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2866888046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3615503311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2267980575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3465747833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6834545135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7208833694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5337295532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1669101715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1968517303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5487031936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4214382171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6011066436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6460227966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7358560562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5861330032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9080381393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.42458152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1251373291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6984262466431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2823429107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.327262878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2598857879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2673721313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5967617034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7839164733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6641387939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.521900177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4470367431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6416759490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0758743286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7988891601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7464847564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8737468719482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9560985565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1058177947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3946361541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.506929397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6847534179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1950359344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1641139984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0094814300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7620697021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6306343078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8471183776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0249443054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9398956298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7698020935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9940185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1254539489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.955358505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5455856323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7156810760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.854850769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7466068267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0404109954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7311458587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5378532409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5687828063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6229019165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7079486846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7234134674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1822052001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0894222259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0816898345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1590061187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9347887039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2363204956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0739612579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9966449737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3909549713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4914665222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8935070037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2414283752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.055871963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2878189086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2955513000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3960609436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8316535949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2800884246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7002182006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5533180236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4837341308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7775325775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5146617889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3832244873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.398681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2749805450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2285900115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0584964752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9657173156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9502544403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0352993011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2827110290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4141464233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6074390411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5919723510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.932165145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0481395721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2646217346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9476261138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0713310241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0636005401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.079065322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2723560333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3032817840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3728637695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3187446594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.558422088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5893516540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4656448364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7207870483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5738868713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5429611206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6975917816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1073665618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0377788543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6125450134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.68212890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5197658538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3110122680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1099910736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3574028015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1795749664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1409168243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0867958068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8857746124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6151695251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5301208496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.352294921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0430316925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8265504837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9270582199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1976680755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6692924499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8703136444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7852649688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9630928039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8084621429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9244346618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4218807220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0507640838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4605388641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.452808380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7543392181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6383628845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7929954528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4064140319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3342094421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.38059425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4888381958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5506935119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6898574829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4115257263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6434688568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2568912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2259654998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.504301071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4991970062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9785537719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3445625305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2981758117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.901237487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.653829574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2672519683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3136386871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4269847869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4475593566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3857040405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.880521774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1433944702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0042285919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.911449432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6949653625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6795043945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7413558959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.664041519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7877426147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2516403198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4371948242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3444194793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4062728881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5609016418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3289566040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1743221282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1124725341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.158863067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2825660705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.236177444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.205249786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2671051025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5299777984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.638219833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5918292999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4835891723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5145149230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4526596069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.607292175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1382923126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3547763824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0764389038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0300483703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1737785339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9502010345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3654193878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.205717086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6209354400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.509147644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5889987945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.557056427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4931793212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1578102111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4292984008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6848163604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6369094848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4133262634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.461238861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3175086975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8064708709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8224411010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7106533050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9182643890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9661712646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.03005027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8863220214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9981098175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3973579406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5251197814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4452667236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1479473114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1639137268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0201873779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8604888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7806358337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5730285644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.06809425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7646675109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4772071838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7007884979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.243766784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4513740539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4992828369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2118282318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1319732666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0042133331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1160068511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0361576080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1798858642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3236141204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3395824432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3076438903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7228622436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.467342376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3874931335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5631618499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8825588226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3616619110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4415092468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2658405303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7609081268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0962753295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8247852325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2498722076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4734497070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.154052734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1700210571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7548007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5312232971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4034633636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8125762939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7327270507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3813877105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2536296844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9342308044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3494472503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9243679046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7486953735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1258697509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7905025482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4391632080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1357326507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2155838012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9760360717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.550952911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8961811065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0718517303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9281253814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8323040008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0558853149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1836433410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4551315307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8163356781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3532085418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9859008789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0976905822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1136589050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4269523620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3311328887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6505317687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4748611450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4429225921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7703037261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8421688079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7383651733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4490280151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2733573913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1615715026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.321268081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4809665679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6246948242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7684268951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1676750183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3433418273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2794628143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9440956115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0079727172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6406669616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2414169311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5608158111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7045459747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8482761383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3752822875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.103796005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8802146911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9121551513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8642444610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.720516204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6885738372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6087284088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7364864349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3052978515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8980646133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.193510055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2094764709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3851490020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.28932762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2573890686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2254505157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9140377044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4170875549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5288772583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7843952178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5767879486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3691787719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1775379180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4889507293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2494029998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.329252243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4091014862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1695537567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0497798919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5688018798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6486511230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2874507904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0878238677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0479011535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.808349609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9680500030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7285022735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8882007598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1277503967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8793506622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0452404022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9208221435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7964038848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2111301422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1281852722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1696586608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.418493270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3770217895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4599647521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.294075012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9622955322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7549304962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6305122375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3402080535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4895057678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5392742156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7088031768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6673278808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5014381408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5429096221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2526035308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7134590148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4231510162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.373384475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2406711578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1743125915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2738513946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.124547958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3070259094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8591241836548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7264089584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7927675247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0747814178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5273418426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.427809715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6600532531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1789722442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3614540100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6932334899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6102886199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4609861373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4443988800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.378041267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2950973510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.925479888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2904376983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3899745941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4397392272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6719875335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9576377868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0867137908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3355464935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8378753662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5890426635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2572612762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8757133483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9088916778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1577262878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1411361694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4729175567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7595891952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6766443252563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5936994552612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4775772094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7429990768433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7098217010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8425340652466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3567924499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3236179351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9752464294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5843849182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0037689208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2240829467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0084247589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1909046173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5558624267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5320014953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7974262237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1836318969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.93479347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.636191368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4371242523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2712335586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3873567581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7616300582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9607000350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4251909255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0317125320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4796171188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1690816879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3681507110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95342445373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3183832168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8777532577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.441780090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8565073013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1763563156128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2924795150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2141923904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9155883789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6667537689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2022609710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4510955810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5174531936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5340414047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4013290405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1524934768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0529594421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97001457214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4676856994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6999311447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.301794052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0695476531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2520265579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0031929016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0363702774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1193161010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92024803161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45575332641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50552082061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32304096221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14056301116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07420444488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68800163269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1359043121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70458889007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38939762115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4345073699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2188491821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4179182052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9985342025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8990001678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9819450378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8160543441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8824110031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8113975524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7782192230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.595739364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3634929656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6833429336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.948766708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9653558731079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2639598846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2805490493774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1810150146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3303155899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2971382141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0814800262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0151224136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0648899078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8326444625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8492317199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5838088989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3847398757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.650164604187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3515615463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2354383468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9321784973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.550630569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5008640289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6169862747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4842748641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0197811126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3349723815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7828779220581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6003980636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1312465667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4132614135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4298486709595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2307815551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8658227920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3137273788452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.396671295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5127944946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8611650466919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2095346450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9772882461548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0602340698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2593021392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3800840377808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1146574020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6335763931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2686157226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55528736114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62164497375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65482234954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.605055809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75435638427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.491548538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0058088302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1929454803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8399181365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3210000991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4086027145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2758913040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7237949371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9062747955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1053428649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9892196655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0721654891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0223970413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.088752746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0389862060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6740283966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4583702087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5081377029419</t>
+    <t xml:space="preserve">12.4583711624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5081367492676</t>
   </si>
   <si>
     <t xml:space="preserve">12.7403831481934</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3754243850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4749593734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6574392318726</t>
+    <t xml:space="preserve">12.3754253387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4749584197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6574382781982</t>
   </si>
   <si>
     <t xml:space="preserve">12.9560413360596</t>
@@ -2441,13 +2441,13 @@
     <t xml:space="preserve">13.536657333374</t>
   </si>
   <si>
-    <t xml:space="preserve">13.984561920166</t>
+    <t xml:space="preserve">13.9845609664917</t>
   </si>
   <si>
     <t xml:space="preserve">14.3661088943481</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5817670822144</t>
+    <t xml:space="preserve">14.5817680358887</t>
   </si>
   <si>
     <t xml:space="preserve">14.6978912353516</t>
@@ -2456,16 +2456,16 @@
     <t xml:space="preserve">14.7642469406128</t>
   </si>
   <si>
-    <t xml:space="preserve">14.631534576416</t>
+    <t xml:space="preserve">14.6315326690674</t>
   </si>
   <si>
     <t xml:space="preserve">14.1006851196289</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4324645996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7808351516724</t>
+    <t xml:space="preserve">14.4324655532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7808361053467</t>
   </si>
   <si>
     <t xml:space="preserve">14.7476577758789</t>
@@ -2474,58 +2474,58 @@
     <t xml:space="preserve">14.4988212585449</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3495197296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2499885559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2333965301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.785493850708</t>
+    <t xml:space="preserve">14.3495206832886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2499876022339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2333955764771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7854948043823</t>
   </si>
   <si>
     <t xml:space="preserve">14.0177402496338</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0509204864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.283164024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0462608337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.930136680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3946304321289</t>
+    <t xml:space="preserve">14.0509185791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2831649780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0462589263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9301385879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3946294784546</t>
   </si>
   <si>
     <t xml:space="preserve">15.3448629379272</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9918384552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8969583511353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9799032211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9135484695435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9964942932129</t>
+    <t xml:space="preserve">15.9918355941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8969593048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.979905128479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9135475158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9964933395386</t>
   </si>
   <si>
     <t xml:space="preserve">15.825945854187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6434679031372</t>
+    <t xml:space="preserve">15.6434688568115</t>
   </si>
   <si>
     <t xml:space="preserve">16.0250148773193</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">16.0913696289062</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0581912994385</t>
+    <t xml:space="preserve">16.0581932067871</t>
   </si>
   <si>
     <t xml:space="preserve">15.5605211257935</t>
@@ -2546,70 +2546,70 @@
     <t xml:space="preserve">15.2619180679321</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2287425994873</t>
+    <t xml:space="preserve">15.228741645813</t>
   </si>
   <si>
     <t xml:space="preserve">15.1457939147949</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4941654205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.626877784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2121515274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5024614334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2702112197876</t>
+    <t xml:space="preserve">15.4941673278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6268787384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2121505737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.502459526062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2702131271362</t>
   </si>
   <si>
     <t xml:space="preserve">15.253623008728</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5439310073853</t>
+    <t xml:space="preserve">15.5439329147339</t>
   </si>
   <si>
     <t xml:space="preserve">15.5771102905273</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8508291244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7181177139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7347059249878</t>
+    <t xml:space="preserve">15.850830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7181186676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7347040176392</t>
   </si>
   <si>
     <t xml:space="preserve">15.8840084075928</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7512941360474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4361038208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3982677459717</t>
+    <t xml:space="preserve">15.7512950897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4361047744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3982696533203</t>
   </si>
   <si>
     <t xml:space="preserve">16.5807476043701</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8674182891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0830764770508</t>
+    <t xml:space="preserve">15.8674192428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0830745697021</t>
   </si>
   <si>
     <t xml:space="preserve">16.1079597473145</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4646244049072</t>
+    <t xml:space="preserve">16.4646224975586</t>
   </si>
   <si>
     <t xml:space="preserve">16.622220993042</t>
@@ -2618,10 +2618,10 @@
     <t xml:space="preserve">16.8212871551514</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7051620483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9042339324951</t>
+    <t xml:space="preserve">16.7051639556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9042320251465</t>
   </si>
   <si>
     <t xml:space="preserve">16.9374122619629</t>
@@ -2636,13 +2636,13 @@
     <t xml:space="preserve">17.4350833892822</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4516735076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.219425201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7217540740967</t>
+    <t xml:space="preserve">17.4516716003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2194232940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7217559814453</t>
   </si>
   <si>
     <t xml:space="preserve">17.1530685424805</t>
@@ -2657,7 +2657,7 @@
     <t xml:space="preserve">16.8876457214355</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7715187072754</t>
+    <t xml:space="preserve">16.771520614624</t>
   </si>
   <si>
     <t xml:space="preserve">16.8544673919678</t>
@@ -2672,7 +2672,7 @@
     <t xml:space="preserve">17.1198902130127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7383422851562</t>
+    <t xml:space="preserve">16.7383441925049</t>
   </si>
   <si>
     <t xml:space="preserve">17.3521366119385</t>
@@ -2687,13 +2687,13 @@
     <t xml:space="preserve">15.9171848297119</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2074966430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2323760986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6056308746338</t>
+    <t xml:space="preserve">16.2074947357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2323780059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6056327819824</t>
   </si>
   <si>
     <t xml:space="preserve">18.6958503723145</t>
@@ -2702,13 +2702,13 @@
     <t xml:space="preserve">18.1981773376465</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1650009155273</t>
+    <t xml:space="preserve">18.1649990081787</t>
   </si>
   <si>
     <t xml:space="preserve">17.617561340332</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0820541381836</t>
+    <t xml:space="preserve">18.0820560455322</t>
   </si>
   <si>
     <t xml:space="preserve">17.6507415771484</t>
@@ -2720,43 +2720,43 @@
     <t xml:space="preserve">17.4019050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3189601898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0203590393066</t>
+    <t xml:space="preserve">17.3189582824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.020357131958</t>
   </si>
   <si>
     <t xml:space="preserve">16.7881107330322</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9705924987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1862487792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4065628051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4148578643799</t>
+    <t xml:space="preserve">16.970588684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1862468719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4065608978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4148559570312</t>
   </si>
   <si>
     <t xml:space="preserve">16.0498962402344</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1660213470459</t>
+    <t xml:space="preserve">16.1660194396973</t>
   </si>
   <si>
     <t xml:space="preserve">17.5346164703369</t>
   </si>
   <si>
-    <t xml:space="preserve">17.070125579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2360172271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6839179992676</t>
+    <t xml:space="preserve">17.0701236724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2360153198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6839199066162</t>
   </si>
   <si>
     <t xml:space="preserve">17.4848499298096</t>
@@ -2771,34 +2771,34 @@
     <t xml:space="preserve">17.3437023162842</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5461578369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4111862182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3774452209473</t>
+    <t xml:space="preserve">17.5461559295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4111881256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3774433135986</t>
   </si>
   <si>
     <t xml:space="preserve">17.6642589569092</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4449291229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4618015289307</t>
+    <t xml:space="preserve">17.4449310302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4618034362793</t>
   </si>
   <si>
     <t xml:space="preserve">17.1749897003174</t>
   </si>
   <si>
-    <t xml:space="preserve">17.040018081665</t>
+    <t xml:space="preserve">17.0400199890137</t>
   </si>
   <si>
     <t xml:space="preserve">17.0062770843506</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9556636810303</t>
+    <t xml:space="preserve">16.9556617736816</t>
   </si>
   <si>
     <t xml:space="preserve">16.8628711700439</t>
@@ -2813,7 +2813,7 @@
     <t xml:space="preserve">16.7532062530518</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2087306976318</t>
+    <t xml:space="preserve">17.2087326049805</t>
   </si>
   <si>
     <t xml:space="preserve">16.2048892974854</t>
@@ -2822,7 +2822,7 @@
     <t xml:space="preserve">16.0952262878418</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1458396911621</t>
+    <t xml:space="preserve">16.1458377838135</t>
   </si>
   <si>
     <t xml:space="preserve">15.7915410995483</t>
@@ -2831,13 +2831,13 @@
     <t xml:space="preserve">15.690315246582</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8590278625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4119386672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5216007232666</t>
+    <t xml:space="preserve">15.8590259552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4119396209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5215997695923</t>
   </si>
   <si>
     <t xml:space="preserve">15.0998191833496</t>
@@ -2846,16 +2846,16 @@
     <t xml:space="preserve">15.420373916626</t>
   </si>
   <si>
-    <t xml:space="preserve">15.60595703125</t>
+    <t xml:space="preserve">15.6059589385986</t>
   </si>
   <si>
     <t xml:space="preserve">15.5806512832642</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8337202072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0446109771729</t>
+    <t xml:space="preserve">15.833722114563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0446128845215</t>
   </si>
   <si>
     <t xml:space="preserve">15.8758993148804</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">15.934947013855</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7662372589111</t>
+    <t xml:space="preserve">15.7662353515625</t>
   </si>
   <si>
     <t xml:space="preserve">15.7746715545654</t>
@@ -2882,10 +2882,10 @@
     <t xml:space="preserve">15.4878606796265</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1841745376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.234787940979</t>
+    <t xml:space="preserve">15.184175491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2347888946533</t>
   </si>
   <si>
     <t xml:space="preserve">15.3950662612915</t>
@@ -2900,10 +2900,10 @@
     <t xml:space="preserve">16.2976818084717</t>
   </si>
   <si>
-    <t xml:space="preserve">16.449520111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5890846252441</t>
+    <t xml:space="preserve">16.4495220184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5890865325928</t>
   </si>
   <si>
     <t xml:space="preserve">15.6987504959106</t>
@@ -2927,13 +2927,13 @@
     <t xml:space="preserve">15.5384721755981</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0154619216919</t>
+    <t xml:space="preserve">15.0154628753662</t>
   </si>
   <si>
     <t xml:space="preserve">15.1504316329956</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5300350189209</t>
+    <t xml:space="preserve">15.5300369262695</t>
   </si>
   <si>
     <t xml:space="preserve">15.8168506622314</t>
@@ -2945,7 +2945,7 @@
     <t xml:space="preserve">15.8843355178833</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1374034881592</t>
+    <t xml:space="preserve">16.1374053955078</t>
   </si>
   <si>
     <t xml:space="preserve">15.8674621582031</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">15.0238981246948</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1673040390015</t>
+    <t xml:space="preserve">15.1673030853271</t>
   </si>
   <si>
     <t xml:space="preserve">15.4372434616089</t>
@@ -2972,28 +2972,28 @@
     <t xml:space="preserve">15.4794235229492</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1588687896729</t>
+    <t xml:space="preserve">15.1588678359985</t>
   </si>
   <si>
     <t xml:space="preserve">14.7623929977417</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4080953598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.741678237915</t>
+    <t xml:space="preserve">14.4080944061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7416791915894</t>
   </si>
   <si>
     <t xml:space="preserve">14.0537977218628</t>
   </si>
   <si>
-    <t xml:space="preserve">14.121283531189</t>
+    <t xml:space="preserve">14.1212825775146</t>
   </si>
   <si>
     <t xml:space="preserve">13.4295587539673</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5898380279541</t>
+    <t xml:space="preserve">13.5898370742798</t>
   </si>
   <si>
     <t xml:space="preserve">13.142746925354</t>
@@ -3002,13 +3002,13 @@
     <t xml:space="preserve">12.7294006347656</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6028652191162</t>
+    <t xml:space="preserve">12.6028642654419</t>
   </si>
   <si>
     <t xml:space="preserve">12.906548500061</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3367671966553</t>
+    <t xml:space="preserve">13.3367681503296</t>
   </si>
   <si>
     <t xml:space="preserve">13.1258764266968</t>
@@ -3020,10 +3020,10 @@
     <t xml:space="preserve">13.9188270568848</t>
   </si>
   <si>
-    <t xml:space="preserve">13.319896697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5307884216309</t>
+    <t xml:space="preserve">13.3198957443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5307874679565</t>
   </si>
   <si>
     <t xml:space="preserve">12.8728065490723</t>
@@ -3032,10 +3032,10 @@
     <t xml:space="preserve">12.9318552017212</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7631425857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.636607170105</t>
+    <t xml:space="preserve">12.7631435394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6366081237793</t>
   </si>
   <si>
     <t xml:space="preserve">12.4172811508179</t>
@@ -3044,28 +3044,28 @@
     <t xml:space="preserve">12.484766960144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6872224807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6619148254395</t>
+    <t xml:space="preserve">12.6872215270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6619157791138</t>
   </si>
   <si>
     <t xml:space="preserve">12.7209644317627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4678955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1304693222046</t>
+    <t xml:space="preserve">12.4678945541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1304683685303</t>
   </si>
   <si>
     <t xml:space="preserve">12.2823104858398</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3497953414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3666677474976</t>
+    <t xml:space="preserve">12.349796295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3666667938232</t>
   </si>
   <si>
     <t xml:space="preserve">12.5859937667847</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">13.4464302062988</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7838573455811</t>
+    <t xml:space="preserve">13.7838563919067</t>
   </si>
   <si>
     <t xml:space="preserve">13.3114595413208</t>
@@ -3113,7 +3113,7 @@
     <t xml:space="preserve">11.8773994445801</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1473388671875</t>
+    <t xml:space="preserve">12.1473398208618</t>
   </si>
   <si>
     <t xml:space="preserve">12.1642122268677</t>
@@ -4674,6 +4674,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.9399995803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90999984741211</t>
   </si>
 </sst>
 </file>
@@ -70922,7 +70925,7 @@
     </row>
     <row r="2536">
       <c r="A2536" s="1" t="n">
-        <v>46009.6910648148</v>
+        <v>46009.3333333333</v>
       </c>
       <c r="B2536" t="n">
         <v>153987</v>
@@ -70943,6 +70946,32 @@
         <v>1482</v>
       </c>
       <c r="H2536" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2537">
+      <c r="A2537" s="1" t="n">
+        <v>46010.6909722222</v>
+      </c>
+      <c r="B2537" t="n">
+        <v>255081</v>
+      </c>
+      <c r="C2537" t="n">
+        <v>9.07999992370605</v>
+      </c>
+      <c r="D2537" t="n">
+        <v>8.875</v>
+      </c>
+      <c r="E2537" t="n">
+        <v>9.0600004196167</v>
+      </c>
+      <c r="F2537" t="n">
+        <v>8.90999984741211</v>
+      </c>
+      <c r="G2537" t="s">
+        <v>1554</v>
+      </c>
+      <c r="H2537" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARR.MI.xlsx
+++ b/data/MARR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="1553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="1554">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4479513168335</t>
+    <t xml:space="preserve">13.4479503631592</t>
   </si>
   <si>
     <t xml:space="preserve">MARR.MI</t>
@@ -50,73 +50,73 @@
     <t xml:space="preserve">13.1812982559204</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9939212799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9506778717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5903387069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6551990509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7344732284546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4389944076538</t>
+    <t xml:space="preserve">12.9939203262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9506788253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5903377532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.655198097229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7344741821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4389953613281</t>
   </si>
   <si>
     <t xml:space="preserve">12.4462003707886</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9849634170532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0858602523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6462421417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2155828475952</t>
+    <t xml:space="preserve">11.9849624633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0858592987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6462430953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2155818939209</t>
   </si>
   <si>
     <t xml:space="preserve">12.8353691101074</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6768188476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5615100860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5543041229248</t>
+    <t xml:space="preserve">12.6768198013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5615119934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5543031692505</t>
   </si>
   <si>
     <t xml:space="preserve">12.6407880783081</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7200584411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.97230052948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7777147293091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3308925628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5110635757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2948579788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4084167480469</t>
+    <t xml:space="preserve">12.7200613021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9722995758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7777156829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3308916091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5110645294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2948560714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4084177017212</t>
   </si>
   <si>
     <t xml:space="preserve">11.4516582489014</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">11.8912744522095</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9273090362549</t>
+    <t xml:space="preserve">11.9273080825806</t>
   </si>
   <si>
     <t xml:space="preserve">12.0426177978516</t>
@@ -140,58 +140,58 @@
     <t xml:space="preserve">12.2011690139771</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3957538604736</t>
+    <t xml:space="preserve">12.3957548141479</t>
   </si>
   <si>
     <t xml:space="preserve">12.7056465148926</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6047525405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5759229660034</t>
+    <t xml:space="preserve">12.6047506332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5759239196777</t>
   </si>
   <si>
     <t xml:space="preserve">12.9362659454346</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1596794128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9434719085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0731945037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.885817527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5975437164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0786533355713</t>
+    <t xml:space="preserve">13.1596784591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9434700012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0731954574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8858165740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5975456237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0786514282227</t>
   </si>
   <si>
     <t xml:space="preserve">12.3597202301025</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6696128845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8137493133545</t>
+    <t xml:space="preserve">12.6696109771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8137483596802</t>
   </si>
   <si>
     <t xml:space="preserve">12.6984415054321</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8714046478271</t>
+    <t xml:space="preserve">12.8714036941528</t>
   </si>
   <si>
     <t xml:space="preserve">12.4534091949463</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3453044891357</t>
+    <t xml:space="preserve">12.3453054428101</t>
   </si>
   <si>
     <t xml:space="preserve">12.6840267181396</t>
@@ -203,49 +203,49 @@
     <t xml:space="preserve">13.1524705886841</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2677803039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3326416015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0804033279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1885042190552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2605714797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7073965072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4911918640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.347056388855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.001127243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9002323150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8281631469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7921295166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0587844848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1020212173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8065452575684</t>
+    <t xml:space="preserve">13.2677793502808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3326425552368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0804014205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1885051727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.260573387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7073974609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.491189956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3470544815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0011262893677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9002313613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.828161239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7921276092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0587825775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1020231246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.806544303894</t>
   </si>
   <si>
     <t xml:space="preserve">13.2821931838989</t>
@@ -254,58 +254,58 @@
     <t xml:space="preserve">13.1380567550659</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8425760269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8930234909058</t>
+    <t xml:space="preserve">12.8425779342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8930253982544</t>
   </si>
   <si>
     <t xml:space="preserve">12.9074373245239</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0227489471436</t>
+    <t xml:space="preserve">13.0227479934692</t>
   </si>
   <si>
     <t xml:space="preserve">12.6624050140381</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8786125183105</t>
+    <t xml:space="preserve">12.8786115646362</t>
   </si>
   <si>
     <t xml:space="preserve">12.6335783004761</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7488889694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0258750915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0183877944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2579441070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2504606246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4301271438599</t>
+    <t xml:space="preserve">12.7488899230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0258760452271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0183887481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.25794506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2504587173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4301280975342</t>
   </si>
   <si>
     <t xml:space="preserve">13.4825296401978</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3103475570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2654294967651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.475043296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3702373504639</t>
+    <t xml:space="preserve">13.3103466033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2654314041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4750442504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3702383041382</t>
   </si>
   <si>
     <t xml:space="preserve">13.2878904342651</t>
@@ -314,265 +314,265 @@
     <t xml:space="preserve">13.2729177474976</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2804050445557</t>
+    <t xml:space="preserve">13.2804021835327</t>
   </si>
   <si>
     <t xml:space="preserve">12.8012914657593</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8836364746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6141386032104</t>
+    <t xml:space="preserve">12.883638381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6141376495361</t>
   </si>
   <si>
     <t xml:space="preserve">12.3146924972534</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4494438171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8087768554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7938051223755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0782785415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4419565200806</t>
+    <t xml:space="preserve">12.44944190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8087778091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7938060760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0782775878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4419584274292</t>
   </si>
   <si>
     <t xml:space="preserve">11.7831764221191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2847490310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7339162826538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4226417541504</t>
+    <t xml:space="preserve">12.2847461700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7339172363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4226408004761</t>
   </si>
   <si>
     <t xml:space="preserve">13.5274467468262</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0558204650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.452582359314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3328056335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7595167160034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7295732498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7220869064331</t>
+    <t xml:space="preserve">13.0558195114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4525833129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3328046798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7595157623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7295722961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7220859527588</t>
   </si>
   <si>
     <t xml:space="preserve">13.53493309021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4900150299072</t>
+    <t xml:space="preserve">13.4900169372559</t>
   </si>
   <si>
     <t xml:space="preserve">13.7370576858521</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0140466690063</t>
+    <t xml:space="preserve">14.014045715332</t>
   </si>
   <si>
     <t xml:space="preserve">13.7071123123169</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8493509292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1113662719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9766139984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0814180374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7445440292358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9990720748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5049896240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6397371292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6621980667114</t>
+    <t xml:space="preserve">13.8493499755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1113634109497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9766120910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0814199447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7445459365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9990730285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5049886703491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6397361755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6621961593628</t>
   </si>
   <si>
     <t xml:space="preserve">13.6097927093506</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3477783203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4151554107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.220516204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0857629776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1007375717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0633058547974</t>
+    <t xml:space="preserve">13.3477792739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4151563644409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2205123901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0857639312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.100736618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.063307762146</t>
   </si>
   <si>
     <t xml:space="preserve">13.2354869842529</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1456518173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9285564422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2055406570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1082220077515</t>
+    <t xml:space="preserve">13.1456527709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9285554885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2055416107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1082229614258</t>
   </si>
   <si>
     <t xml:space="preserve">13.1980562210083</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1157093048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0109024047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9135847091675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.861180305481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9435272216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1905717849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4076671600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3552656173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2130279541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3402938842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9659852981567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8761548995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8312339782715</t>
+    <t xml:space="preserve">13.1157083511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0109033584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9135828018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8611812591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9435291290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1905679702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4076700210571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3552646636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2130270004272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3402919769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9659872055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8761529922485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8312349319458</t>
   </si>
   <si>
     <t xml:space="preserve">12.9809589385986</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7638597488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7114582061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8686666488647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7563753128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6815128326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5767059326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.546763420105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5317897796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5617341995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5542497634888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4194984436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2772607803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.47190284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5018463134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3970394134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9778165817261</t>
+    <t xml:space="preserve">12.763861656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7114562988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8686676025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7563743591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6815137863159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5767068862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5467624664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5317916870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5617370605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5542478561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4194974899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2772617340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4719018936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5018472671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3970403671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9778156280518</t>
   </si>
   <si>
     <t xml:space="preserve">12.3596096038818</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4943609237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3820686340332</t>
+    <t xml:space="preserve">12.4943599700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3820676803589</t>
   </si>
   <si>
     <t xml:space="preserve">12.4045248031616</t>
   </si>
   <si>
-    <t xml:space="preserve">12.269775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1649694442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2548046112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3371515274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3221788406372</t>
+    <t xml:space="preserve">12.2697763442993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1649703979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2548036575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3371505737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3221769332886</t>
   </si>
   <si>
     <t xml:space="preserve">12.72642993927</t>
@@ -581,13 +581,13 @@
     <t xml:space="preserve">12.6740274429321</t>
   </si>
   <si>
-    <t xml:space="preserve">12.786319732666</t>
+    <t xml:space="preserve">12.7863168716431</t>
   </si>
   <si>
     <t xml:space="preserve">13.0932502746582</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9510135650635</t>
+    <t xml:space="preserve">12.9510126113892</t>
   </si>
   <si>
     <t xml:space="preserve">13.1306819915771</t>
@@ -596,40 +596,40 @@
     <t xml:space="preserve">12.9884452819824</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1381673812866</t>
+    <t xml:space="preserve">13.1381664276123</t>
   </si>
   <si>
     <t xml:space="preserve">13.1606254577637</t>
   </si>
   <si>
-    <t xml:space="preserve">13.183084487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1681108474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2280015945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.00341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1755990982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4001808166504</t>
+    <t xml:space="preserve">13.1830835342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1681127548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2280025482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0034189224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1755971908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4001817703247</t>
   </si>
   <si>
     <t xml:space="preserve">13.3852100372314</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8643245697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9167242050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5199604034424</t>
+    <t xml:space="preserve">13.8643236160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9167251586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5199594497681</t>
   </si>
   <si>
     <t xml:space="preserve">13.4450988769531</t>
@@ -641,145 +641,145 @@
     <t xml:space="preserve">13.4600706100464</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5124731063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4376134872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8268928527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6247673034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8044338226318</t>
+    <t xml:space="preserve">13.5124740600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.437614440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8268899917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6247653961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8044357299805</t>
   </si>
   <si>
     <t xml:space="preserve">13.7819747924805</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6996259689331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8418645858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6771688461304</t>
+    <t xml:space="preserve">13.6996288299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8418636322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6771697998047</t>
   </si>
   <si>
     <t xml:space="preserve">13.8568344116211</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7670030593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5648775100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8942642211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3359479904175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5605335235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5156154632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6952838897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9722681045532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9348392486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.942325592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8225479125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2043418884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7133979797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1369647979736</t>
+    <t xml:space="preserve">13.7670011520386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5648765563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8942680358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3359498977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5605344772339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5156145095825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6952819824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9722700119019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9348411560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9423236846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.822546005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2043399810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7133960723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1369657516479</t>
   </si>
   <si>
     <t xml:space="preserve">15.1594228744507</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2866878509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3615503311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2267980575562</t>
+    <t xml:space="preserve">15.2866888046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3615522384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2267999649048</t>
   </si>
   <si>
     <t xml:space="preserve">15.3465766906738</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6834535598755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7208814620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5337314605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.458869934082</t>
+    <t xml:space="preserve">15.6834516525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7208843231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.533727645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4588670730591</t>
   </si>
   <si>
     <t xml:space="preserve">15.1669101715088</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1968564987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5487051010132</t>
+    <t xml:space="preserve">15.1968536376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5487031936646</t>
   </si>
   <si>
     <t xml:space="preserve">15.4214382171631</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6011047363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6460237503052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.735857963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5861349105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9080362319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.42458152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1251373291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6984252929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2823448181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3272590637207</t>
+    <t xml:space="preserve">15.6011056900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6460218429565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7358541488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5861310958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9080390930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4245834350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1251354217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6984262466431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.282341003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3272609710693</t>
   </si>
   <si>
     <t xml:space="preserve">16.2598838806152</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">16.267370223999</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5967597961426</t>
+    <t xml:space="preserve">16.5967617034912</t>
   </si>
   <si>
     <t xml:space="preserve">16.78391456604</t>
@@ -797,43 +797,43 @@
     <t xml:space="preserve">16.6641368865967</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5219020843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4470367431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6416797637939</t>
+    <t xml:space="preserve">16.5218982696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4470386505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6416759490967</t>
   </si>
   <si>
     <t xml:space="preserve">17.0758724212646</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7988872528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7464847564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8737506866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9560947418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1058177947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3946361541748</t>
+    <t xml:space="preserve">16.7988891601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7464809417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8737487792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9560966491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1058197021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3946380615234</t>
   </si>
   <si>
     <t xml:space="preserve">16.5069274902344</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6847553253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1950397491455</t>
+    <t xml:space="preserve">16.6847534179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1950378417969</t>
   </si>
   <si>
     <t xml:space="preserve">17.1641139984131</t>
@@ -842,25 +842,25 @@
     <t xml:space="preserve">17.0094814300537</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7620697021484</t>
+    <t xml:space="preserve">16.7620677947998</t>
   </si>
   <si>
     <t xml:space="preserve">16.6306324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8471183776855</t>
+    <t xml:space="preserve">16.8471202850342</t>
   </si>
   <si>
     <t xml:space="preserve">17.0249443054199</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9398956298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7698040008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9940185546875</t>
+    <t xml:space="preserve">16.9398975372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7698020935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9940166473389</t>
   </si>
   <si>
     <t xml:space="preserve">17.1254539489746</t>
@@ -875,10 +875,10 @@
     <t xml:space="preserve">16.7156810760498</t>
   </si>
   <si>
-    <t xml:space="preserve">16.854850769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7466068267822</t>
+    <t xml:space="preserve">16.8548488616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7466049194336</t>
   </si>
   <si>
     <t xml:space="preserve">17.0404090881348</t>
@@ -890,40 +890,40 @@
     <t xml:space="preserve">16.5378551483154</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5687789916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6229038238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7079486846924</t>
+    <t xml:space="preserve">16.5687808990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6229000091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.707950592041</t>
   </si>
   <si>
     <t xml:space="preserve">16.7234115600586</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1821994781494</t>
+    <t xml:space="preserve">16.182201385498</t>
   </si>
   <si>
     <t xml:space="preserve">16.0894203186035</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0816898345947</t>
+    <t xml:space="preserve">16.0816917419434</t>
   </si>
   <si>
     <t xml:space="preserve">16.1590061187744</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9347915649414</t>
+    <t xml:space="preserve">15.9347896575928</t>
   </si>
   <si>
     <t xml:space="preserve">16.2363224029541</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0739593505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9966440200806</t>
+    <t xml:space="preserve">16.0739574432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9966430664062</t>
   </si>
   <si>
     <t xml:space="preserve">16.3909549713135</t>
@@ -935,67 +935,67 @@
     <t xml:space="preserve">16.8935089111328</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2414264678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0558700561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2878170013428</t>
+    <t xml:space="preserve">17.2414283752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0558681488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2878189086914</t>
   </si>
   <si>
     <t xml:space="preserve">17.2955493927002</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3960590362549</t>
+    <t xml:space="preserve">17.3960609436035</t>
   </si>
   <si>
     <t xml:space="preserve">16.8316555023193</t>
   </si>
   <si>
-    <t xml:space="preserve">17.280086517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.700216293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5533180236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4837303161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7775325775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5146617889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3832225799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3986873626709</t>
+    <t xml:space="preserve">17.2800884246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7002182006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.553316116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4837341308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7775344848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5146579742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3832206726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3986854553223</t>
   </si>
   <si>
     <t xml:space="preserve">16.2749805450439</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2285919189453</t>
+    <t xml:space="preserve">16.2285900115967</t>
   </si>
   <si>
     <t xml:space="preserve">16.0584983825684</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9657182693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.950252532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0352993011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2827110290527</t>
+    <t xml:space="preserve">15.9657163619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9502563476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0353012084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2827129364014</t>
   </si>
   <si>
     <t xml:space="preserve">16.4141502380371</t>
@@ -1004,34 +1004,34 @@
     <t xml:space="preserve">16.6074390411377</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5919742584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9321670532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0481376647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2646255493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.947624206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0713329315186</t>
+    <t xml:space="preserve">16.5919761657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.932165145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0481395721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2646236419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9476261138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0713348388672</t>
   </si>
   <si>
     <t xml:space="preserve">17.0636024475098</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0790672302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2723560333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3032817840576</t>
+    <t xml:space="preserve">17.0790615081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2723579406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.303279876709</t>
   </si>
   <si>
     <t xml:space="preserve">17.3728656768799</t>
@@ -1040,34 +1040,34 @@
     <t xml:space="preserve">17.3187427520752</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5584201812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5893478393555</t>
+    <t xml:space="preserve">17.558422088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5893516540527</t>
   </si>
   <si>
     <t xml:space="preserve">17.4656448364258</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7207889556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5738887786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5429592132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6975917816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1073665618896</t>
+    <t xml:space="preserve">17.7207870483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5738830566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5429630279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6975936889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.107364654541</t>
   </si>
   <si>
     <t xml:space="preserve">18.0377807617188</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6125469207764</t>
+    <t xml:space="preserve">17.6125431060791</t>
   </si>
   <si>
     <t xml:space="preserve">17.6821308135986</t>
@@ -1076,67 +1076,67 @@
     <t xml:space="preserve">17.5197658538818</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3110122680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.109992980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.357400894165</t>
+    <t xml:space="preserve">17.3110103607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1099910736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3574028015137</t>
   </si>
   <si>
     <t xml:space="preserve">17.1795749664307</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1409168243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0867958068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8857765197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6151714324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5301189422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3522987365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0430355072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.826548576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9270601272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1976680755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6692905426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8703117370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7852649688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9630947113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8084621429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9244327545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4218807220459</t>
+    <t xml:space="preserve">17.1409187316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0867977142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8857727050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6151676177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.530122756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.352294921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0430335998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8265476226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.927059173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1976642608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6692924499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8703136444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7852630615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9630928039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8084602355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.924430847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4218826293945</t>
   </si>
   <si>
     <t xml:space="preserve">16.0507659912109</t>
@@ -1145,40 +1145,40 @@
     <t xml:space="preserve">16.4605407714844</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4528064727783</t>
+    <t xml:space="preserve">16.452808380127</t>
   </si>
   <si>
     <t xml:space="preserve">16.754337310791</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6383628845215</t>
+    <t xml:space="preserve">16.6383647918701</t>
   </si>
   <si>
     <t xml:space="preserve">16.7929954528809</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4064159393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.33420753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3805980682373</t>
+    <t xml:space="preserve">16.4064178466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3342094421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3805961608887</t>
   </si>
   <si>
     <t xml:space="preserve">17.4888381958008</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5506935119629</t>
+    <t xml:space="preserve">17.5506896972656</t>
   </si>
   <si>
     <t xml:space="preserve">17.6898593902588</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4115219116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6434726715088</t>
+    <t xml:space="preserve">17.4115257263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6434688568115</t>
   </si>
   <si>
     <t xml:space="preserve">17.2568893432617</t>
@@ -1187,10 +1187,10 @@
     <t xml:space="preserve">17.2259674072266</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5043029785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4991970062256</t>
+    <t xml:space="preserve">17.504301071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.499195098877</t>
   </si>
   <si>
     <t xml:space="preserve">16.9785537719727</t>
@@ -1202,25 +1202,25 @@
     <t xml:space="preserve">16.2981758117676</t>
   </si>
   <si>
-    <t xml:space="preserve">16.901237487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.653829574585</t>
+    <t xml:space="preserve">16.9012393951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6538276672363</t>
   </si>
   <si>
     <t xml:space="preserve">16.2672500610352</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3136405944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4269886016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4475574493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3857040405273</t>
+    <t xml:space="preserve">16.3136386871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4269866943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4475555419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3857021331787</t>
   </si>
   <si>
     <t xml:space="preserve">18.8805236816406</t>
@@ -1235,25 +1235,25 @@
     <t xml:space="preserve">18.9114513397217</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6949653625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6795043945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7413558959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6640377044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7877445220947</t>
+    <t xml:space="preserve">18.6949672698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.679500579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7413539886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6640396118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7877464294434</t>
   </si>
   <si>
     <t xml:space="preserve">19.2516403198242</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4371967315674</t>
+    <t xml:space="preserve">19.437198638916</t>
   </si>
   <si>
     <t xml:space="preserve">19.3444194793701</t>
@@ -1262,13 +1262,13 @@
     <t xml:space="preserve">19.4062728881836</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5609035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3289566040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1743240356445</t>
+    <t xml:space="preserve">19.5608997344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3289546966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1743221282959</t>
   </si>
   <si>
     <t xml:space="preserve">19.1124687194824</t>
@@ -1277,16 +1277,16 @@
     <t xml:space="preserve">19.158863067627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2825660705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2361736297607</t>
+    <t xml:space="preserve">19.2825679779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2361755371094</t>
   </si>
   <si>
     <t xml:space="preserve">19.205249786377</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2671051025391</t>
+    <t xml:space="preserve">19.2671031951904</t>
   </si>
   <si>
     <t xml:space="preserve">19.5299777984619</t>
@@ -1298,10 +1298,10 @@
     <t xml:space="preserve">19.5918292999268</t>
   </si>
   <si>
-    <t xml:space="preserve">19.483585357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5145149230957</t>
+    <t xml:space="preserve">19.4835872650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5145130157471</t>
   </si>
   <si>
     <t xml:space="preserve">19.4526615142822</t>
@@ -1310,31 +1310,31 @@
     <t xml:space="preserve">19.607292175293</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1382904052734</t>
+    <t xml:space="preserve">18.1382884979248</t>
   </si>
   <si>
     <t xml:space="preserve">18.3547763824463</t>
   </si>
   <si>
-    <t xml:space="preserve">18.07643699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0300521850586</t>
+    <t xml:space="preserve">18.0764389038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.03005027771</t>
   </si>
   <si>
     <t xml:space="preserve">18.1737804412842</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9502010345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3654174804688</t>
+    <t xml:space="preserve">17.9501991271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3654193878174</t>
   </si>
   <si>
     <t xml:space="preserve">18.2057189941406</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6209354400635</t>
+    <t xml:space="preserve">18.6209373474121</t>
   </si>
   <si>
     <t xml:space="preserve">18.509147644043</t>
@@ -1343,22 +1343,22 @@
     <t xml:space="preserve">18.5889987945557</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5570583343506</t>
+    <t xml:space="preserve">18.5570602416992</t>
   </si>
   <si>
     <t xml:space="preserve">18.4931774139404</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1578102111816</t>
+    <t xml:space="preserve">18.157808303833</t>
   </si>
   <si>
     <t xml:space="preserve">18.4292984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6848163604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6369075775146</t>
+    <t xml:space="preserve">18.6848182678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.636905670166</t>
   </si>
   <si>
     <t xml:space="preserve">18.4133281707764</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">18.3175086975098</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8064708709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8224391937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7106513977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9182605743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9661693572998</t>
+    <t xml:space="preserve">17.8064727783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8224411010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7106533050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9182624816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9661731719971</t>
   </si>
   <si>
     <t xml:space="preserve">17.8863201141357</t>
@@ -1391,34 +1391,34 @@
     <t xml:space="preserve">17.9981117248535</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3973579406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5251159667969</t>
+    <t xml:space="preserve">18.3973598480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5251178741455</t>
   </si>
   <si>
     <t xml:space="preserve">18.4452667236328</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1479434967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1639156341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0201854705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8604869842529</t>
+    <t xml:space="preserve">19.1479454040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1639137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0201873779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8604888916016</t>
   </si>
   <si>
     <t xml:space="preserve">18.7806377410889</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5730266571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.06809425354</t>
+    <t xml:space="preserve">18.5730247497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0680980682373</t>
   </si>
   <si>
     <t xml:space="preserve">18.7646656036377</t>
@@ -1439,52 +1439,52 @@
     <t xml:space="preserve">19.4992847442627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2118263244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1319732666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0042133331299</t>
+    <t xml:space="preserve">19.2118244171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1319751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0042152404785</t>
   </si>
   <si>
     <t xml:space="preserve">19.1160068511963</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0361576080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1798839569092</t>
+    <t xml:space="preserve">19.0361557006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1798858642578</t>
   </si>
   <si>
     <t xml:space="preserve">19.3236141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3395843505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3076438903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7228660583496</t>
+    <t xml:space="preserve">19.3395862579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3076457977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7228622436523</t>
   </si>
   <si>
     <t xml:space="preserve">19.4673442840576</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3874931335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5631637573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8825588226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3616600036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4415111541748</t>
+    <t xml:space="preserve">19.3874950408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5631618499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8825626373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3616619110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4415092468262</t>
   </si>
   <si>
     <t xml:space="preserve">20.2658386230469</t>
@@ -1508,13 +1508,13 @@
     <t xml:space="preserve">20.1540508270264</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1700191497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7548046112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5312213897705</t>
+    <t xml:space="preserve">20.1700210571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7548007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5312252044678</t>
   </si>
   <si>
     <t xml:space="preserve">19.4034652709961</t>
@@ -1523,16 +1523,16 @@
     <t xml:space="preserve">18.8125762939453</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7327289581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3813896179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2536315917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9342288970947</t>
+    <t xml:space="preserve">18.732723236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3813877105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2536277770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9342308044434</t>
   </si>
   <si>
     <t xml:space="preserve">18.3494491577148</t>
@@ -1541,25 +1541,25 @@
     <t xml:space="preserve">18.9243679046631</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7486953735352</t>
+    <t xml:space="preserve">18.7486972808838</t>
   </si>
   <si>
     <t xml:space="preserve">18.1258697509766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7905006408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4391613006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1357326507568</t>
+    <t xml:space="preserve">17.7905025482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4391593933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1357345581055</t>
   </si>
   <si>
     <t xml:space="preserve">17.2155838012695</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9760341644287</t>
+    <t xml:space="preserve">16.9760360717773</t>
   </si>
   <si>
     <t xml:space="preserve">17.550952911377</t>
@@ -1577,13 +1577,13 @@
     <t xml:space="preserve">16.8323059082031</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0558834075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1836452484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4551315307617</t>
+    <t xml:space="preserve">17.0558853149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1836433410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4551334381104</t>
   </si>
   <si>
     <t xml:space="preserve">16.8163356781006</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">16.3532085418701</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9859008789062</t>
+    <t xml:space="preserve">15.9859018325806</t>
   </si>
   <si>
     <t xml:space="preserve">16.0976886749268</t>
@@ -1601,82 +1601,82 @@
     <t xml:space="preserve">16.1136589050293</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4269514083862</t>
+    <t xml:space="preserve">15.4269504547119</t>
   </si>
   <si>
     <t xml:space="preserve">15.3311319351196</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6505317687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4748601913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4429225921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7703037261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.842170715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7383651733398</t>
+    <t xml:space="preserve">15.6505308151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4748620986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4429235458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7703046798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8421697616577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7383661270142</t>
   </si>
   <si>
     <t xml:space="preserve">16.4490261077881</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2733554840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1615715026855</t>
+    <t xml:space="preserve">16.2733573913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1615695953369</t>
   </si>
   <si>
     <t xml:space="preserve">16.321268081665</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4809684753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6246948242188</t>
+    <t xml:space="preserve">16.4809665679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6246967315674</t>
   </si>
   <si>
     <t xml:space="preserve">16.768424987793</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1676750183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3433437347412</t>
+    <t xml:space="preserve">17.1676712036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3433418273926</t>
   </si>
   <si>
     <t xml:space="preserve">17.2794628143311</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9440937042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0079727172852</t>
+    <t xml:space="preserve">16.9440956115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0079746246338</t>
   </si>
   <si>
     <t xml:space="preserve">16.6406669616699</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2414169311523</t>
+    <t xml:space="preserve">16.241418838501</t>
   </si>
   <si>
     <t xml:space="preserve">16.5608177185059</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7045459747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8482780456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3752841949463</t>
+    <t xml:space="preserve">16.7045478820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8482761383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3752822875977</t>
   </si>
   <si>
     <t xml:space="preserve">17.1037940979004</t>
@@ -1694,58 +1694,58 @@
     <t xml:space="preserve">16.720516204834</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6885776519775</t>
+    <t xml:space="preserve">16.6885757446289</t>
   </si>
   <si>
     <t xml:space="preserve">16.6087265014648</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7364864349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3052997589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8980646133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1935062408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2094764709473</t>
+    <t xml:space="preserve">16.7364845275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3052959442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8980627059937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1935081481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2094745635986</t>
   </si>
   <si>
     <t xml:space="preserve">16.3851470947266</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2893257141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2573871612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2254486083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9140348434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.417085647583</t>
+    <t xml:space="preserve">16.2893295288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2573890686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2254467010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9140338897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4170875549316</t>
   </si>
   <si>
     <t xml:space="preserve">16.5288772583008</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7843990325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5767841339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.369176864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1775379180908</t>
+    <t xml:space="preserve">16.7843952178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5767879486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3691787719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1775360107422</t>
   </si>
   <si>
     <t xml:space="preserve">16.4889526367188</t>
@@ -1754,22 +1754,22 @@
     <t xml:space="preserve">16.2494029998779</t>
   </si>
   <si>
-    <t xml:space="preserve">16.329252243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4091014862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1695556640625</t>
+    <t xml:space="preserve">16.3292541503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4091033935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1695518493652</t>
   </si>
   <si>
     <t xml:space="preserve">16.0497798919678</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5688018798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6486530303955</t>
+    <t xml:space="preserve">16.5688037872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6486511230469</t>
   </si>
   <si>
     <t xml:space="preserve">17.2874488830566</t>
@@ -1778,55 +1778,55 @@
     <t xml:space="preserve">17.0878257751465</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0479011535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.808349609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9680480957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7285022735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8882007598877</t>
+    <t xml:space="preserve">17.0478992462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8083515167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9680500030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7285003662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8881988525391</t>
   </si>
   <si>
     <t xml:space="preserve">17.1277503967285</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8793487548828</t>
+    <t xml:space="preserve">16.8793506622314</t>
   </si>
   <si>
     <t xml:space="preserve">17.0452404022217</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9208221435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7964057922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2111301422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1281871795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1696605682373</t>
+    <t xml:space="preserve">16.9208240509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7964019775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2111320495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1281852722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1696586608887</t>
   </si>
   <si>
     <t xml:space="preserve">17.418493270874</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3770236968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4599647521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2940769195557</t>
+    <t xml:space="preserve">17.3770198822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4599666595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.294075012207</t>
   </si>
   <si>
     <t xml:space="preserve">16.9622955322266</t>
@@ -1835,28 +1835,28 @@
     <t xml:space="preserve">16.7549324035645</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6305141448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3402061462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4895076751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5392742156982</t>
+    <t xml:space="preserve">16.6305122375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3402080535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4895057678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5392761230469</t>
   </si>
   <si>
     <t xml:space="preserve">17.7088012695312</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6673278808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5014419555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.542911529541</t>
+    <t xml:space="preserve">17.667329788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5014400482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5429096221924</t>
   </si>
   <si>
     <t xml:space="preserve">17.2526035308838</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">16.7134590148926</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4231510162354</t>
+    <t xml:space="preserve">16.4231491088867</t>
   </si>
   <si>
     <t xml:space="preserve">16.3733825683594</t>
@@ -1874,7 +1874,7 @@
     <t xml:space="preserve">16.2406711578369</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1743144989014</t>
+    <t xml:space="preserve">16.17431640625</t>
   </si>
   <si>
     <t xml:space="preserve">16.2738513946533</t>
@@ -1883,10 +1883,10 @@
     <t xml:space="preserve">16.124547958374</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3070259094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8591232299805</t>
+    <t xml:space="preserve">16.3070278167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8591241836548</t>
   </si>
   <si>
     <t xml:space="preserve">15.7264108657837</t>
@@ -1895,19 +1895,19 @@
     <t xml:space="preserve">15.7927675247192</t>
   </si>
   <si>
-    <t xml:space="preserve">16.074779510498</t>
+    <t xml:space="preserve">16.0747814178467</t>
   </si>
   <si>
     <t xml:space="preserve">15.5273427963257</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4278087615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6600532531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1789741516113</t>
+    <t xml:space="preserve">15.427809715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6600542068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1789722442627</t>
   </si>
   <si>
     <t xml:space="preserve">15.3614530563354</t>
@@ -1916,22 +1916,22 @@
     <t xml:space="preserve">15.6932334899902</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6102876663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4609851837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4443979263306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3780422210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2950973510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9254808425903</t>
+    <t xml:space="preserve">15.6102886199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4609880447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4443998336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.378041267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2950983047485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.925479888916</t>
   </si>
   <si>
     <t xml:space="preserve">16.2904376983643</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">16.6719875335693</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9576358795166</t>
+    <t xml:space="preserve">17.9576377868652</t>
   </si>
   <si>
     <t xml:space="preserve">17.0867118835449</t>
@@ -1958,13 +1958,13 @@
     <t xml:space="preserve">16.8378734588623</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5890426635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2572631835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.875714302063</t>
+    <t xml:space="preserve">16.5890407562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2572612762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8757133483887</t>
   </si>
   <si>
     <t xml:space="preserve">15.9088916778564</t>
@@ -1973,28 +1973,28 @@
     <t xml:space="preserve">16.1577243804932</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1411361694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4729194641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7595911026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6766443252563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5936975479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4775762557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7430019378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7098236083984</t>
+    <t xml:space="preserve">16.1411380767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.47292137146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7595891952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.676643371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5936994552612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.477575302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7430009841919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7098226547241</t>
   </si>
   <si>
     <t xml:space="preserve">15.8425340652466</t>
@@ -2009,7 +2009,7 @@
     <t xml:space="preserve">15.975248336792</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5843830108643</t>
+    <t xml:space="preserve">17.5843849182129</t>
   </si>
   <si>
     <t xml:space="preserve">17.0037689208984</t>
@@ -2021,19 +2021,19 @@
     <t xml:space="preserve">16.0084266662598</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1909027099609</t>
+    <t xml:space="preserve">16.1909065246582</t>
   </si>
   <si>
     <t xml:space="preserve">16.5558605194092</t>
   </si>
   <si>
-    <t xml:space="preserve">14.532000541687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7974243164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1836318969727</t>
+    <t xml:space="preserve">14.5320014953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7974252700806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.183629989624</t>
   </si>
   <si>
     <t xml:space="preserve">13.9347944259644</t>
@@ -2045,7 +2045,7 @@
     <t xml:space="preserve">13.4371242523193</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2712326049805</t>
+    <t xml:space="preserve">13.2712335586548</t>
   </si>
   <si>
     <t xml:space="preserve">13.3873558044434</t>
@@ -2057,10 +2057,10 @@
     <t xml:space="preserve">11.9607000350952</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4251918792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0317115783691</t>
+    <t xml:space="preserve">12.4251909255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0317125320435</t>
   </si>
   <si>
     <t xml:space="preserve">11.4796171188354</t>
@@ -2069,19 +2069,19 @@
     <t xml:space="preserve">10.1690826416016</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3681516647339</t>
+    <t xml:space="preserve">10.3681507110596</t>
   </si>
   <si>
     <t xml:space="preserve">9.95342445373535</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3183832168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8777532577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4417810440063</t>
+    <t xml:space="preserve">10.3183822631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8777542114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.441780090332</t>
   </si>
   <si>
     <t xml:space="preserve">12.8565073013306</t>
@@ -2090,25 +2090,25 @@
     <t xml:space="preserve">12.1763563156128</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2924795150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2141923904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9155883789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6667528152466</t>
+    <t xml:space="preserve">12.2924785614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2141933441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9155893325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6667547225952</t>
   </si>
   <si>
     <t xml:space="preserve">10.2022609710693</t>
   </si>
   <si>
-    <t xml:space="preserve">10.451096534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5174522399902</t>
+    <t xml:space="preserve">10.4510955810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5174531936646</t>
   </si>
   <si>
     <t xml:space="preserve">10.5340414047241</t>
@@ -2123,7 +2123,7 @@
     <t xml:space="preserve">10.0529584884644</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97001361846924</t>
+    <t xml:space="preserve">9.97001457214355</t>
   </si>
   <si>
     <t xml:space="preserve">10.4676856994629</t>
@@ -2138,16 +2138,16 @@
     <t xml:space="preserve">10.0695486068726</t>
   </si>
   <si>
-    <t xml:space="preserve">10.252028465271</t>
+    <t xml:space="preserve">10.2520265579224</t>
   </si>
   <si>
     <t xml:space="preserve">10.0031929016113</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0363693237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1193151473999</t>
+    <t xml:space="preserve">10.0363702774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1193141937256</t>
   </si>
   <si>
     <t xml:space="preserve">9.92024707794189</t>
@@ -2156,28 +2156,28 @@
     <t xml:space="preserve">9.45575332641602</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50552177429199</t>
+    <t xml:space="preserve">9.50552082061768</t>
   </si>
   <si>
     <t xml:space="preserve">9.32304096221924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14056205749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07420539855957</t>
+    <t xml:space="preserve">9.14056301116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07420444488525</t>
   </si>
   <si>
     <t xml:space="preserve">9.68800067901611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1359033584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70458889007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38939666748047</t>
+    <t xml:space="preserve">10.1359043121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70458984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38939762115479</t>
   </si>
   <si>
     <t xml:space="preserve">10.4345073699951</t>
@@ -2186,16 +2186,16 @@
     <t xml:space="preserve">10.2188491821289</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4179172515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.99853515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.899001121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9819459915161</t>
+    <t xml:space="preserve">10.4179182052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9985342025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8990001678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9819450378418</t>
   </si>
   <si>
     <t xml:space="preserve">10.8160543441772</t>
@@ -2204,7 +2204,7 @@
     <t xml:space="preserve">10.8824110031128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8113965988159</t>
+    <t xml:space="preserve">11.8113975524902</t>
   </si>
   <si>
     <t xml:space="preserve">11.7782192230225</t>
@@ -2213,16 +2213,16 @@
     <t xml:space="preserve">11.595739364624</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3634939193726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6833419799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.948766708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9653577804565</t>
+    <t xml:space="preserve">11.3634929656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6833429336548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9487676620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9653568267822</t>
   </si>
   <si>
     <t xml:space="preserve">11.2639589309692</t>
@@ -2231,22 +2231,22 @@
     <t xml:space="preserve">11.2805490493774</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1810140609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3303155899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2971363067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0814800262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0151224136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0648908615112</t>
+    <t xml:space="preserve">11.1810150146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3303146362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.297137260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0814790725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0151233673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0648899078369</t>
   </si>
   <si>
     <t xml:space="preserve">10.8326444625854</t>
@@ -2258,19 +2258,19 @@
     <t xml:space="preserve">10.5838088989258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3847398757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6501636505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3515615463257</t>
+    <t xml:space="preserve">10.3847389221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.650164604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3515605926514</t>
   </si>
   <si>
     <t xml:space="preserve">10.2354383468628</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9321784973145</t>
+    <t xml:space="preserve">10.9321794509888</t>
   </si>
   <si>
     <t xml:space="preserve">10.550630569458</t>
@@ -2279,22 +2279,22 @@
     <t xml:space="preserve">10.5008640289307</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6169872283936</t>
+    <t xml:space="preserve">10.6169862747192</t>
   </si>
   <si>
     <t xml:space="preserve">10.4842748641968</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0197811126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3349733352661</t>
+    <t xml:space="preserve">10.0197801589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3349723815918</t>
   </si>
   <si>
     <t xml:space="preserve">10.7828769683838</t>
   </si>
   <si>
-    <t xml:space="preserve">10.600399017334</t>
+    <t xml:space="preserve">10.6003971099854</t>
   </si>
   <si>
     <t xml:space="preserve">11.1312465667725</t>
@@ -2303,34 +2303,34 @@
     <t xml:space="preserve">11.4132604598999</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4298486709595</t>
+    <t xml:space="preserve">11.4298496246338</t>
   </si>
   <si>
     <t xml:space="preserve">11.2307815551758</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8658237457275</t>
+    <t xml:space="preserve">10.8658227920532</t>
   </si>
   <si>
     <t xml:space="preserve">11.3137273788452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3966703414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5127944946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8611660003662</t>
+    <t xml:space="preserve">11.396671295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5127954483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8611650466919</t>
   </si>
   <si>
     <t xml:space="preserve">12.2095346450806</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9772882461548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0602340698242</t>
+    <t xml:space="preserve">11.9772891998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0602331161499</t>
   </si>
   <si>
     <t xml:space="preserve">12.2593011856079</t>
@@ -2339,7 +2339,7 @@
     <t xml:space="preserve">11.3800830841064</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1146574020386</t>
+    <t xml:space="preserve">11.1146564483643</t>
   </si>
   <si>
     <t xml:space="preserve">10.6335754394531</t>
@@ -2348,10 +2348,10 @@
     <t xml:space="preserve">10.2686166763306</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55528736114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62164497375488</t>
+    <t xml:space="preserve">9.55528831481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62164402008057</t>
   </si>
   <si>
     <t xml:space="preserve">9.65482234954834</t>
@@ -2360,19 +2360,19 @@
     <t xml:space="preserve">9.60505485534668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75435733795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4915494918823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0058088302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1929454803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.839919090271</t>
+    <t xml:space="preserve">9.75435638427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.491548538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0058097839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1929445266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8399181365967</t>
   </si>
   <si>
     <t xml:space="preserve">13.3210000991821</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">12.4086027145386</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2758893966675</t>
+    <t xml:space="preserve">12.2758913040161</t>
   </si>
   <si>
     <t xml:space="preserve">12.7237949371338</t>
@@ -2390,7 +2390,7 @@
     <t xml:space="preserve">12.9062747955322</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1053438186646</t>
+    <t xml:space="preserve">13.1053419113159</t>
   </si>
   <si>
     <t xml:space="preserve">12.9892196655273</t>
@@ -2408,13 +2408,13 @@
     <t xml:space="preserve">13.038987159729</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4583711624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5081367492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.740385055542</t>
+    <t xml:space="preserve">12.4583702087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5081377029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7403841018677</t>
   </si>
   <si>
     <t xml:space="preserve">12.3754243850708</t>
@@ -2423,16 +2423,16 @@
     <t xml:space="preserve">12.4749593734741</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6574392318726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9560413360596</t>
+    <t xml:space="preserve">12.6574382781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9560403823853</t>
   </si>
   <si>
     <t xml:space="preserve">12.9228630065918</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5366582870483</t>
+    <t xml:space="preserve">13.536657333374</t>
   </si>
   <si>
     <t xml:space="preserve">13.9845628738403</t>
@@ -2441,10 +2441,10 @@
     <t xml:space="preserve">14.3661088943481</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5817680358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6978921890259</t>
+    <t xml:space="preserve">14.5817699432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6978902816772</t>
   </si>
   <si>
     <t xml:space="preserve">14.7642459869385</t>
@@ -2456,46 +2456,46 @@
     <t xml:space="preserve">14.1006851196289</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4324645996094</t>
+    <t xml:space="preserve">14.4324655532837</t>
   </si>
   <si>
     <t xml:space="preserve">14.7808351516724</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7476577758789</t>
+    <t xml:space="preserve">14.7476568222046</t>
   </si>
   <si>
     <t xml:space="preserve">14.4988212585449</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3495206832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2499876022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2333974838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.785493850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0177392959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0509185791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.283164024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0462608337402</t>
+    <t xml:space="preserve">14.3495197296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2499866485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2333965301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7854948043823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0177412033081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0509195327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2831649780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0462589263916</t>
   </si>
   <si>
     <t xml:space="preserve">14.930136680603</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3946294784546</t>
+    <t xml:space="preserve">15.3946313858032</t>
   </si>
   <si>
     <t xml:space="preserve">15.3448619842529</t>
@@ -2504,46 +2504,46 @@
     <t xml:space="preserve">15.9918365478516</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8969593048096</t>
+    <t xml:space="preserve">14.8969573974609</t>
   </si>
   <si>
     <t xml:space="preserve">14.9799041748047</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9135475158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9964942932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8259449005127</t>
+    <t xml:space="preserve">14.9135465621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9964933395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8259439468384</t>
   </si>
   <si>
     <t xml:space="preserve">15.6434659957886</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0250148773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0913696289062</t>
+    <t xml:space="preserve">16.0250129699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0913677215576</t>
   </si>
   <si>
     <t xml:space="preserve">16.0581912994385</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5605211257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0130825042725</t>
+    <t xml:space="preserve">15.5605220794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0130834579468</t>
   </si>
   <si>
     <t xml:space="preserve">15.2619190216064</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2287425994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1457939147949</t>
+    <t xml:space="preserve">15.228741645813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1457948684692</t>
   </si>
   <si>
     <t xml:space="preserve">15.4941654205322</t>
@@ -2552,22 +2552,22 @@
     <t xml:space="preserve">15.6268768310547</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2121515274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5024585723877</t>
+    <t xml:space="preserve">15.2121505737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.502459526062</t>
   </si>
   <si>
     <t xml:space="preserve">15.2702121734619</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2536239624023</t>
+    <t xml:space="preserve">15.253623008728</t>
   </si>
   <si>
     <t xml:space="preserve">15.5439319610596</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5771102905273</t>
+    <t xml:space="preserve">15.5771112442017</t>
   </si>
   <si>
     <t xml:space="preserve">15.8508291244507</t>
@@ -2576,16 +2576,16 @@
     <t xml:space="preserve">15.7181177139282</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7347049713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8840093612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7512950897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4361028671265</t>
+    <t xml:space="preserve">15.7347059249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8840065002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7512941360474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4361047744751</t>
   </si>
   <si>
     <t xml:space="preserve">16.3982677459717</t>
@@ -2594,19 +2594,19 @@
     <t xml:space="preserve">16.5807476043701</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8674182891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0830764770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1079578399658</t>
+    <t xml:space="preserve">15.8674192428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0830745697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1079597473145</t>
   </si>
   <si>
     <t xml:space="preserve">16.4646244049072</t>
   </si>
   <si>
-    <t xml:space="preserve">16.622220993042</t>
+    <t xml:space="preserve">16.6222190856934</t>
   </si>
   <si>
     <t xml:space="preserve">16.8212871551514</t>
@@ -2618,22 +2618,22 @@
     <t xml:space="preserve">16.9042320251465</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9374122619629</t>
+    <t xml:space="preserve">16.9374103546143</t>
   </si>
   <si>
     <t xml:space="preserve">17.1364803314209</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3023719787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4350833892822</t>
+    <t xml:space="preserve">17.3023700714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4350814819336</t>
   </si>
   <si>
     <t xml:space="preserve">17.4516735076904</t>
   </si>
   <si>
-    <t xml:space="preserve">17.219425201416</t>
+    <t xml:space="preserve">17.2194271087646</t>
   </si>
   <si>
     <t xml:space="preserve">16.7217540740967</t>
@@ -2642,16 +2642,16 @@
     <t xml:space="preserve">17.1530685424805</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0535335540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0369453430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8876438140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7715225219727</t>
+    <t xml:space="preserve">17.0535354614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0369472503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8876457214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7715187072754</t>
   </si>
   <si>
     <t xml:space="preserve">16.8544654846191</t>
@@ -2666,25 +2666,25 @@
     <t xml:space="preserve">17.1198902130127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7383441925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3521366119385</t>
+    <t xml:space="preserve">16.7383422851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3521385192871</t>
   </si>
   <si>
     <t xml:space="preserve">17.2691917419434</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8710536956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9171857833862</t>
+    <t xml:space="preserve">16.8710556030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9171848297119</t>
   </si>
   <si>
     <t xml:space="preserve">16.2074947357178</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2323760986328</t>
+    <t xml:space="preserve">16.2323741912842</t>
   </si>
   <si>
     <t xml:space="preserve">16.6056327819824</t>
@@ -2696,25 +2696,25 @@
     <t xml:space="preserve">18.1981792449951</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1650009155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6175594329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0820560455322</t>
+    <t xml:space="preserve">18.1649990081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6175632476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0820541381836</t>
   </si>
   <si>
     <t xml:space="preserve">17.6507415771484</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8000392913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4019050598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3189582824707</t>
+    <t xml:space="preserve">17.8000411987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4019031524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3189601898193</t>
   </si>
   <si>
     <t xml:space="preserve">17.020357131958</t>
@@ -2723,19 +2723,19 @@
     <t xml:space="preserve">16.7881107330322</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9705905914307</t>
+    <t xml:space="preserve">16.970588684082</t>
   </si>
   <si>
     <t xml:space="preserve">17.1862468719482</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4065647125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4148578643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0499000549316</t>
+    <t xml:space="preserve">16.4065628051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4148559570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.049898147583</t>
   </si>
   <si>
     <t xml:space="preserve">16.1660213470459</t>
@@ -2744,22 +2744,22 @@
     <t xml:space="preserve">17.5346164703369</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0701217651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2360153198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6839199066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4848518371582</t>
+    <t xml:space="preserve">17.070125579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2360134124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6839179992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4848499298096</t>
   </si>
   <si>
     <t xml:space="preserve">17.276216506958</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2424755096436</t>
+    <t xml:space="preserve">17.2424736022949</t>
   </si>
   <si>
     <t xml:space="preserve">17.3437023162842</t>
@@ -2768,22 +2768,22 @@
     <t xml:space="preserve">17.5461578369141</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4111881256104</t>
+    <t xml:space="preserve">17.4111862182617</t>
   </si>
   <si>
     <t xml:space="preserve">17.3774433135986</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6642589569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4449310302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4618034362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1749877929688</t>
+    <t xml:space="preserve">17.6642570495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4449291229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4618015289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1749897003174</t>
   </si>
   <si>
     <t xml:space="preserve">17.0400199890137</t>
@@ -2795,37 +2795,37 @@
     <t xml:space="preserve">16.9556636810303</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8628692626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.090633392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8713073730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7532081604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2087306976318</t>
+    <t xml:space="preserve">16.8628711700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0906314849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8713054656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.753210067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2087326049805</t>
   </si>
   <si>
     <t xml:space="preserve">16.2048892974854</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0952262878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1458415985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7915410995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6903142929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8590259552002</t>
+    <t xml:space="preserve">16.0952243804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1458396911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7915420532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.690315246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8590278625488</t>
   </si>
   <si>
     <t xml:space="preserve">15.4119386672974</t>
@@ -2834,13 +2834,13 @@
     <t xml:space="preserve">15.5216016769409</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0998191833496</t>
+    <t xml:space="preserve">15.0998182296753</t>
   </si>
   <si>
     <t xml:space="preserve">15.420373916626</t>
   </si>
   <si>
-    <t xml:space="preserve">15.60595703125</t>
+    <t xml:space="preserve">15.6059560775757</t>
   </si>
   <si>
     <t xml:space="preserve">15.5806503295898</t>
@@ -2849,7 +2849,7 @@
     <t xml:space="preserve">15.8337211608887</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0446128845215</t>
+    <t xml:space="preserve">16.0446109771729</t>
   </si>
   <si>
     <t xml:space="preserve">15.8758993148804</t>
@@ -2861,25 +2861,25 @@
     <t xml:space="preserve">16.0108699798584</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9349460601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7662343978882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7746706008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.513165473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4878606796265</t>
+    <t xml:space="preserve">15.934947013855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7662353515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7746715545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5131645202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4878597259521</t>
   </si>
   <si>
     <t xml:space="preserve">15.1841745376587</t>
   </si>
   <si>
-    <t xml:space="preserve">15.234787940979</t>
+    <t xml:space="preserve">15.2347888946533</t>
   </si>
   <si>
     <t xml:space="preserve">15.3950662612915</t>
@@ -2891,31 +2891,31 @@
     <t xml:space="preserve">16.112096786499</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2976818084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4495220184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5890855789185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6987504959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0361766815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9686918258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3145523071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9180765151978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0193061828613</t>
+    <t xml:space="preserve">16.297679901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4495239257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5890865325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.698751449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0361747741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9686908721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3145542144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9180774688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0193042755127</t>
   </si>
   <si>
     <t xml:space="preserve">15.5384721755981</t>
@@ -2924,118 +2924,118 @@
     <t xml:space="preserve">15.0154609680176</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1504325866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5300369262695</t>
+    <t xml:space="preserve">15.1504306793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5300359725952</t>
   </si>
   <si>
     <t xml:space="preserve">15.8168497085571</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5637807846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.884334564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1374034881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8674612045288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4541168212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9732847213745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0238971710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1673030853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4372453689575</t>
+    <t xml:space="preserve">15.5637817382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8843336105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1374053955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8674631118774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4541158676147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9732856750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0238962173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1673021316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4372444152832</t>
   </si>
   <si>
     <t xml:space="preserve">15.6312656402588</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4794254302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1588678359985</t>
+    <t xml:space="preserve">15.4794225692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1588668823242</t>
   </si>
   <si>
     <t xml:space="preserve">14.7623929977417</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4080944061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7416791915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0537977218628</t>
+    <t xml:space="preserve">14.4080934524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7416801452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0537986755371</t>
   </si>
   <si>
     <t xml:space="preserve">14.121283531189</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4295597076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5898380279541</t>
+    <t xml:space="preserve">13.4295587539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5898370742798</t>
   </si>
   <si>
     <t xml:space="preserve">13.142746925354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7293996810913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6028652191162</t>
+    <t xml:space="preserve">12.7294006347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6028642654419</t>
   </si>
   <si>
     <t xml:space="preserve">12.906548500061</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3367671966553</t>
+    <t xml:space="preserve">13.3367681503296</t>
   </si>
   <si>
     <t xml:space="preserve">13.1258764266968</t>
   </si>
   <si>
-    <t xml:space="preserve">13.513916015625</t>
+    <t xml:space="preserve">13.5139169692993</t>
   </si>
   <si>
     <t xml:space="preserve">13.9188270568848</t>
   </si>
   <si>
-    <t xml:space="preserve">13.319896697998</t>
+    <t xml:space="preserve">13.3198957443237</t>
   </si>
   <si>
     <t xml:space="preserve">13.5307874679565</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8728065490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9318552017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7631435394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6366081237793</t>
+    <t xml:space="preserve">12.8728055953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9318561553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7631425857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.636607170105</t>
   </si>
   <si>
     <t xml:space="preserve">12.4172811508179</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4847660064697</t>
+    <t xml:space="preserve">12.484766960144</t>
   </si>
   <si>
     <t xml:space="preserve">12.6872224807739</t>
@@ -3050,7 +3050,7 @@
     <t xml:space="preserve">12.4678945541382</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1304693222046</t>
+    <t xml:space="preserve">12.1304683685303</t>
   </si>
   <si>
     <t xml:space="preserve">12.2823104858398</t>
@@ -3059,16 +3059,16 @@
     <t xml:space="preserve">12.3497953414917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3666667938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.585994720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4126882553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3958177566528</t>
+    <t xml:space="preserve">12.3666658401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5859937667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4126873016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3958158493042</t>
   </si>
   <si>
     <t xml:space="preserve">13.4464302062988</t>
@@ -3077,10 +3077,10 @@
     <t xml:space="preserve">13.7838573455811</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3114595413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2271041870117</t>
+    <t xml:space="preserve">13.3114604949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.227105140686</t>
   </si>
   <si>
     <t xml:space="preserve">12.9571628570557</t>
@@ -3095,10 +3095,10 @@
     <t xml:space="preserve">12.7715787887573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4004096984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2148246765137</t>
+    <t xml:space="preserve">12.400408744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.214825630188</t>
   </si>
   <si>
     <t xml:space="preserve">12.0461120605469</t>
@@ -3107,31 +3107,31 @@
     <t xml:space="preserve">11.8773994445801</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1473398208618</t>
+    <t xml:space="preserve">12.1473407745361</t>
   </si>
   <si>
     <t xml:space="preserve">12.1642122268677</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2316970825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4510231018066</t>
+    <t xml:space="preserve">12.2316961288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.451024055481</t>
   </si>
   <si>
     <t xml:space="preserve">12.3835382461548</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2991819381714</t>
+    <t xml:space="preserve">12.2991809844971</t>
   </si>
   <si>
     <t xml:space="preserve">11.8267850875854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749429702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6487464904785</t>
+    <t xml:space="preserve">11.6749439239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6487474441528</t>
   </si>
   <si>
     <t xml:space="preserve">11.474102973938</t>
@@ -3140,37 +3140,37 @@
     <t xml:space="preserve">11.3693170547485</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8932476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9107131958008</t>
+    <t xml:space="preserve">11.8932485580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9107122421265</t>
   </si>
   <si>
     <t xml:space="preserve">12.4346437454224</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1028203964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0154991149902</t>
+    <t xml:space="preserve">12.102819442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0154981613159</t>
   </si>
   <si>
     <t xml:space="preserve">11.9805698394775</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1901435852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3298578262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5568952560425</t>
+    <t xml:space="preserve">12.1901426315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3298568725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5568943023682</t>
   </si>
   <si>
     <t xml:space="preserve">12.3123931884766</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5963525772095</t>
+    <t xml:space="preserve">11.5963535308838</t>
   </si>
   <si>
     <t xml:space="preserve">11.4391746520996</t>
@@ -3179,10 +3179,10 @@
     <t xml:space="preserve">11.1946725845337</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7186050415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5788888931274</t>
+    <t xml:space="preserve">11.7186040878296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5788898468018</t>
   </si>
   <si>
     <t xml:space="preserve">11.8408555984497</t>
@@ -3191,7 +3191,7 @@
     <t xml:space="preserve">11.8583192825317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7709970474243</t>
+    <t xml:space="preserve">11.7709980010986</t>
   </si>
   <si>
     <t xml:space="preserve">11.9631052017212</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">11.2470655441284</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0374927520752</t>
+    <t xml:space="preserve">11.0374937057495</t>
   </si>
   <si>
     <t xml:space="preserve">10.8453845977783</t>
@@ -3236,10 +3236,10 @@
     <t xml:space="preserve">11.4042453765869</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2296009063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6138172149658</t>
+    <t xml:space="preserve">11.2296018600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6138191223145</t>
   </si>
   <si>
     <t xml:space="preserve">11.7884616851807</t>
@@ -3248,46 +3248,46 @@
     <t xml:space="preserve">11.8233909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">11.805926322937</t>
+    <t xml:space="preserve">11.8059272766113</t>
   </si>
   <si>
     <t xml:space="preserve">11.5614242553711</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4566383361816</t>
+    <t xml:space="preserve">11.456639289856</t>
   </si>
   <si>
     <t xml:space="preserve">11.5439605712891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4217090606689</t>
+    <t xml:space="preserve">11.4217100143433</t>
   </si>
   <si>
     <t xml:space="preserve">11.1073503494263</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0898866653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7231340408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6882057189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6707401275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5135622024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2865238189697</t>
+    <t xml:space="preserve">11.0898857116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7231330871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6882047653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6707410812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5135612487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.286524772644</t>
   </si>
   <si>
     <t xml:space="preserve">10.2341318130493</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0594873428345</t>
+    <t xml:space="preserve">10.0594882965088</t>
   </si>
   <si>
     <t xml:space="preserve">10.1468095779419</t>
@@ -3299,16 +3299,16 @@
     <t xml:space="preserve">9.90230846405029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81498527526855</t>
+    <t xml:space="preserve">9.81498622894287</t>
   </si>
   <si>
     <t xml:space="preserve">9.76259326934814</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98962879180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1992025375366</t>
+    <t xml:space="preserve">9.9896297454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1992034912109</t>
   </si>
   <si>
     <t xml:space="preserve">9.29105472564697</t>
@@ -3326,34 +3326,34 @@
     <t xml:space="preserve">9.0640172958374</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80205154418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81951522827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60121154785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48769187927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19079875946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44403076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46149635314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3392448425293</t>
+    <t xml:space="preserve">8.80205059051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8195161819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60121250152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48769283294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19079780578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44403266906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4614953994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33924579620361</t>
   </si>
   <si>
     <t xml:space="preserve">8.56628322601318</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34797668457031</t>
+    <t xml:space="preserve">8.34797859191895</t>
   </si>
   <si>
     <t xml:space="preserve">8.54881763458252</t>
@@ -3365,34 +3365,34 @@
     <t xml:space="preserve">8.85444450378418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88937282562256</t>
+    <t xml:space="preserve">8.88937377929688</t>
   </si>
   <si>
     <t xml:space="preserve">9.04655265808105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01162433624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83698081970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7321949005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02908897399902</t>
+    <t xml:space="preserve">9.01162338256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83697986602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73219394683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02908802032471</t>
   </si>
   <si>
     <t xml:space="preserve">9.09894561767578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41330528259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30851936340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27358913421631</t>
+    <t xml:space="preserve">9.41330432891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.308518409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27359008789062</t>
   </si>
   <si>
     <t xml:space="preserve">9.39584064483643</t>
@@ -3407,13 +3407,13 @@
     <t xml:space="preserve">9.622878074646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91977119445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2690601348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65780639648438</t>
+    <t xml:space="preserve">9.91977214813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.269061088562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65780735015869</t>
   </si>
   <si>
     <t xml:space="preserve">9.64034175872803</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">9.67527103424072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8324499130249</t>
+    <t xml:space="preserve">9.83245086669922</t>
   </si>
   <si>
     <t xml:space="preserve">10.0420236587524</t>
@@ -3437,13 +3437,13 @@
     <t xml:space="preserve">9.97216606140137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88484287261963</t>
+    <t xml:space="preserve">9.88484382629395</t>
   </si>
   <si>
     <t xml:space="preserve">9.8673791885376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0944156646729</t>
+    <t xml:space="preserve">10.0944166183472</t>
   </si>
   <si>
     <t xml:space="preserve">10.0769519805908</t>
@@ -3458,7 +3458,7 @@
     <t xml:space="preserve">10.0070943832397</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4437046051025</t>
+    <t xml:space="preserve">10.4437036514282</t>
   </si>
   <si>
     <t xml:space="preserve">10.6532764434814</t>
@@ -3467,16 +3467,16 @@
     <t xml:space="preserve">10.6358118057251</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7405977249146</t>
+    <t xml:space="preserve">10.7405986785889</t>
   </si>
   <si>
     <t xml:space="preserve">10.7580623626709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9152431488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0200290679932</t>
+    <t xml:space="preserve">10.9152421951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0200281143188</t>
   </si>
   <si>
     <t xml:space="preserve">11.3518524169922</t>
@@ -3485,13 +3485,13 @@
     <t xml:space="preserve">11.0025644302368</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9676351547241</t>
+    <t xml:space="preserve">10.9676361083984</t>
   </si>
   <si>
     <t xml:space="preserve">10.5310258865356</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6183481216431</t>
+    <t xml:space="preserve">10.6183471679688</t>
   </si>
   <si>
     <t xml:space="preserve">10.7056694030762</t>
@@ -3503,16 +3503,16 @@
     <t xml:space="preserve">10.565954208374</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4786329269409</t>
+    <t xml:space="preserve">10.4786319732666</t>
   </si>
   <si>
     <t xml:space="preserve">10.1817378997803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2166662216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0245571136475</t>
+    <t xml:space="preserve">10.216667175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0245580673218</t>
   </si>
   <si>
     <t xml:space="preserve">9.84991455078125</t>
@@ -3527,10 +3527,10 @@
     <t xml:space="preserve">10.3563814163208</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5264949798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9456415176392</t>
+    <t xml:space="preserve">11.5264959335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9456405639648</t>
   </si>
   <si>
     <t xml:space="preserve">11.7011394500732</t>
@@ -3539,7 +3539,7 @@
     <t xml:space="preserve">12.1202850341797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.399715423584</t>
+    <t xml:space="preserve">12.3997144699097</t>
   </si>
   <si>
     <t xml:space="preserve">11.9281768798828</t>
@@ -3563,13 +3563,13 @@
     <t xml:space="preserve">13.063362121582</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8712539672852</t>
+    <t xml:space="preserve">12.8712530136108</t>
   </si>
   <si>
     <t xml:space="preserve">12.6442155838013</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9491119384766</t>
+    <t xml:space="preserve">12.9491128921509</t>
   </si>
   <si>
     <t xml:space="preserve">13.0746583938599</t>
@@ -3578,13 +3578,13 @@
     <t xml:space="preserve">12.9132423400879</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0387878417969</t>
+    <t xml:space="preserve">13.0387887954712</t>
   </si>
   <si>
     <t xml:space="preserve">13.0567235946655</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1284637451172</t>
+    <t xml:space="preserve">13.1284627914429</t>
   </si>
   <si>
     <t xml:space="preserve">13.2540082931519</t>
@@ -3599,7 +3599,7 @@
     <t xml:space="preserve">13.5947751998901</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4871635437012</t>
+    <t xml:space="preserve">13.4871644973755</t>
   </si>
   <si>
     <t xml:space="preserve">13.4512939453125</t>
@@ -3614,7 +3614,7 @@
     <t xml:space="preserve">13.5051002502441</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2002038955688</t>
+    <t xml:space="preserve">13.2002029418945</t>
   </si>
   <si>
     <t xml:space="preserve">12.9849824905396</t>
@@ -3647,7 +3647,7 @@
     <t xml:space="preserve">12.5366058349609</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4110612869263</t>
+    <t xml:space="preserve">12.411060333252</t>
   </si>
   <si>
     <t xml:space="preserve">12.2496452331543</t>
@@ -3674,7 +3674,7 @@
     <t xml:space="preserve">12.285514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2675809860229</t>
+    <t xml:space="preserve">12.2675800323486</t>
   </si>
   <si>
     <t xml:space="preserve">12.6262817382812</t>
@@ -3686,7 +3686,7 @@
     <t xml:space="preserve">12.5724763870239</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2137746810913</t>
+    <t xml:space="preserve">12.2137756347656</t>
   </si>
   <si>
     <t xml:space="preserve">12.5007352828979</t>
@@ -3698,10 +3698,10 @@
     <t xml:space="preserve">11.2990875244141</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5681133270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.639853477478</t>
+    <t xml:space="preserve">11.5681123733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6398525238037</t>
   </si>
   <si>
     <t xml:space="preserve">11.675724029541</t>
@@ -3713,22 +3713,22 @@
     <t xml:space="preserve">11.6577882766724</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4605026245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3708276748657</t>
+    <t xml:space="preserve">11.4605016708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.37082862854</t>
   </si>
   <si>
     <t xml:space="preserve">11.3528928756714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3349571228027</t>
+    <t xml:space="preserve">11.3349580764771</t>
   </si>
   <si>
     <t xml:space="preserve">11.2811527252197</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4963731765747</t>
+    <t xml:space="preserve">11.4963722229004</t>
   </si>
   <si>
     <t xml:space="preserve">11.5501775741577</t>
@@ -3743,16 +3743,16 @@
     <t xml:space="preserve">11.8012685775757</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7833347320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.908878326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9268140792847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.016489982605</t>
+    <t xml:space="preserve">11.7833337783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9088792800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.926815032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0164890289307</t>
   </si>
   <si>
     <t xml:space="preserve">12.0882301330566</t>
@@ -3791,7 +3791,7 @@
     <t xml:space="preserve">10.5278797149658</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7610359191895</t>
+    <t xml:space="preserve">10.7610349655151</t>
   </si>
   <si>
     <t xml:space="preserve">10.5816850662231</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">10.2947235107422</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3664636611938</t>
+    <t xml:space="preserve">10.3664646148682</t>
   </si>
   <si>
     <t xml:space="preserve">10.2229833602905</t>
@@ -3827,19 +3827,19 @@
     <t xml:space="preserve">9.86428260803223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68493175506592</t>
+    <t xml:space="preserve">9.68493270874023</t>
   </si>
   <si>
     <t xml:space="preserve">9.75667190551758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77460765838623</t>
+    <t xml:space="preserve">9.77460670471191</t>
   </si>
   <si>
     <t xml:space="preserve">9.70286750793457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79254245758057</t>
+    <t xml:space="preserve">9.79254150390625</t>
   </si>
   <si>
     <t xml:space="preserve">9.66699695587158</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">10.0436325073242</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1871128082275</t>
+    <t xml:space="preserve">10.1871137619019</t>
   </si>
   <si>
     <t xml:space="preserve">10.5099449157715</t>
@@ -3863,7 +3863,7 @@
     <t xml:space="preserve">10.7431001663208</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8148403167725</t>
+    <t xml:space="preserve">10.8148412704468</t>
   </si>
   <si>
     <t xml:space="preserve">10.4740753173828</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">9.9001522064209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95395851135254</t>
+    <t xml:space="preserve">9.95395755767822</t>
   </si>
   <si>
     <t xml:space="preserve">10.0795030593872</t>
@@ -3887,7 +3887,7 @@
     <t xml:space="preserve">9.98982810974121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2588529586792</t>
+    <t xml:space="preserve">10.2588539123535</t>
   </si>
   <si>
     <t xml:space="preserve">10.3126592636108</t>
@@ -3899,7 +3899,7 @@
     <t xml:space="preserve">10.4561395645142</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3305940628052</t>
+    <t xml:space="preserve">10.3305950164795</t>
   </si>
   <si>
     <t xml:space="preserve">10.2050485610962</t>
@@ -3914,7 +3914,7 @@
     <t xml:space="preserve">9.91808795928955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88221836090088</t>
+    <t xml:space="preserve">9.88221740722656</t>
   </si>
   <si>
     <t xml:space="preserve">10.0974388122559</t>
@@ -3935,31 +3935,31 @@
     <t xml:space="preserve">9.3262300491333</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45177555084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5996198654175</t>
+    <t xml:space="preserve">9.4517765045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5996189117432</t>
   </si>
   <si>
     <t xml:space="preserve">9.93602275848389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4920091629028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5637493133545</t>
+    <t xml:space="preserve">10.4920101165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5637502670288</t>
   </si>
   <si>
     <t xml:space="preserve">10.4382047653198</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6713600158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9045162200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8327760696411</t>
+    <t xml:space="preserve">10.6713590621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9045152664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8327751159668</t>
   </si>
   <si>
     <t xml:space="preserve">10.7251653671265</t>
@@ -3974,7 +3974,7 @@
     <t xml:space="preserve">10.9224510192871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6892957687378</t>
+    <t xml:space="preserve">10.6892948150635</t>
   </si>
   <si>
     <t xml:space="preserve">11.2094125747681</t>
@@ -4671,6 +4671,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.90999984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85000038146973</t>
   </si>
 </sst>
 </file>
@@ -70971,7 +70974,7 @@
     </row>
     <row r="2538">
       <c r="A2538" s="1" t="n">
-        <v>46013.6912615741</v>
+        <v>46013.3333333333</v>
       </c>
       <c r="B2538" t="n">
         <v>175691</v>
@@ -70992,6 +70995,32 @@
         <v>1548</v>
       </c>
       <c r="H2538" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2539">
+      <c r="A2539" s="1" t="n">
+        <v>46014.6912152778</v>
+      </c>
+      <c r="B2539" t="n">
+        <v>75094</v>
+      </c>
+      <c r="C2539" t="n">
+        <v>8.94999980926514</v>
+      </c>
+      <c r="D2539" t="n">
+        <v>8.85000038146973</v>
+      </c>
+      <c r="E2539" t="n">
+        <v>8.86999988555908</v>
+      </c>
+      <c r="F2539" t="n">
+        <v>8.85000038146973</v>
+      </c>
+      <c r="G2539" t="s">
+        <v>1553</v>
+      </c>
+      <c r="H2539" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MARR.MI.xlsx
+++ b/data/MARR.MI.xlsx
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4479532241821</t>
+    <t xml:space="preserve">13.4479513168335</t>
   </si>
   <si>
     <t xml:space="preserve">MARR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2894020080566</t>
+    <t xml:space="preserve">13.2894010543823</t>
   </si>
   <si>
     <t xml:space="preserve">13.1812992095947</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9939222335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9506788253784</t>
+    <t xml:space="preserve">12.9939203262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9506797790527</t>
   </si>
   <si>
     <t xml:space="preserve">12.5903377532959</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6551971435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7344741821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4389944076538</t>
+    <t xml:space="preserve">12.6551990509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7344732284546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4389934539795</t>
   </si>
   <si>
     <t xml:space="preserve">12.4462013244629</t>
@@ -74,16 +74,16 @@
     <t xml:space="preserve">11.9849634170532</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0858602523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6462430953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2155838012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8353681564331</t>
+    <t xml:space="preserve">12.0858592987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6462421417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2155828475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8353691101074</t>
   </si>
   <si>
     <t xml:space="preserve">12.6768198013306</t>
@@ -95,40 +95,40 @@
     <t xml:space="preserve">12.5543041229248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6407880783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7200613021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9723014831543</t>
+    <t xml:space="preserve">12.6407861709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7200593948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9722986221313</t>
   </si>
   <si>
     <t xml:space="preserve">12.7777156829834</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3308935165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5110626220703</t>
+    <t xml:space="preserve">12.3308906555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5110635757446</t>
   </si>
   <si>
     <t xml:space="preserve">12.2948570251465</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4084167480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4516582489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8840684890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5885887145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8912734985352</t>
+    <t xml:space="preserve">11.4084177017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4516572952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8840675354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5885877609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8912744522095</t>
   </si>
   <si>
     <t xml:space="preserve">11.9273090362549</t>
@@ -137,37 +137,37 @@
     <t xml:space="preserve">12.0426168441772</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2011671066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3957548141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7056465148926</t>
+    <t xml:space="preserve">12.2011680603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3957529067993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7056474685669</t>
   </si>
   <si>
     <t xml:space="preserve">12.6047506332397</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5759239196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9362649917603</t>
+    <t xml:space="preserve">12.5759258270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9362659454346</t>
   </si>
   <si>
     <t xml:space="preserve">13.1596765518188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9434728622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0731973648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.885817527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5975456237793</t>
+    <t xml:space="preserve">12.9434719085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0731954574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8858165740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.597544670105</t>
   </si>
   <si>
     <t xml:space="preserve">12.078652381897</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">12.6696128845215</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8137512207031</t>
+    <t xml:space="preserve">12.8137493133545</t>
   </si>
   <si>
     <t xml:space="preserve">12.6984405517578</t>
@@ -191,118 +191,118 @@
     <t xml:space="preserve">12.453408241272</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3453044891357</t>
+    <t xml:space="preserve">12.3453054428101</t>
   </si>
   <si>
     <t xml:space="preserve">12.684027671814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7560949325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1524696350098</t>
+    <t xml:space="preserve">12.7560939788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1524724960327</t>
   </si>
   <si>
     <t xml:space="preserve">13.2677822113037</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3326416015625</t>
+    <t xml:space="preserve">13.3326425552368</t>
   </si>
   <si>
     <t xml:space="preserve">13.0804023742676</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1885032653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.260573387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7073984146118</t>
+    <t xml:space="preserve">13.1885042190552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2605724334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7073965072632</t>
   </si>
   <si>
     <t xml:space="preserve">13.4911918640137</t>
   </si>
   <si>
-    <t xml:space="preserve">13.347056388855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0011262893677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9002294540405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8281631469727</t>
+    <t xml:space="preserve">13.3470544815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.001127243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9002304077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8281621932983</t>
   </si>
   <si>
     <t xml:space="preserve">12.7921295166016</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0587825775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1020231246948</t>
+    <t xml:space="preserve">13.058783531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1020240783691</t>
   </si>
   <si>
     <t xml:space="preserve">12.8065423965454</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2821941375732</t>
+    <t xml:space="preserve">13.2821931838989</t>
   </si>
   <si>
     <t xml:space="preserve">13.1380567550659</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8425779342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8930253982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9074382781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0227479934692</t>
+    <t xml:space="preserve">12.8425769805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8930244445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9074373245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0227470397949</t>
   </si>
   <si>
     <t xml:space="preserve">12.6624069213867</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8786096572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6335792541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7488880157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0258750915527</t>
+    <t xml:space="preserve">12.8786125183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6335783004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7488899230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0258741378784</t>
   </si>
   <si>
     <t xml:space="preserve">13.0183897018433</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2579460144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2504587173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4301261901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4825277328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3103494644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2654314041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4750452041626</t>
+    <t xml:space="preserve">13.2579441070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2504596710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4301252365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4825286865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3103504180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2654323577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.475043296814</t>
   </si>
   <si>
     <t xml:space="preserve">13.3702383041382</t>
@@ -314,25 +314,25 @@
     <t xml:space="preserve">13.2729167938232</t>
   </si>
   <si>
-    <t xml:space="preserve">13.280403137207</t>
+    <t xml:space="preserve">13.2804040908813</t>
   </si>
   <si>
     <t xml:space="preserve">12.8012914657593</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8836374282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6141395568848</t>
+    <t xml:space="preserve">12.883638381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6141386032104</t>
   </si>
   <si>
     <t xml:space="preserve">12.3146934509277</t>
   </si>
   <si>
-    <t xml:space="preserve">12.44944190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8087787628174</t>
+    <t xml:space="preserve">12.4494409561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8087768554688</t>
   </si>
   <si>
     <t xml:space="preserve">12.7938060760498</t>
@@ -347,196 +347,196 @@
     <t xml:space="preserve">11.7831773757935</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2847490310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7339172363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4226417541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5274467468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0558204650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4525842666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3328046798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7595167160034</t>
+    <t xml:space="preserve">12.2847480773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7339162826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4226388931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5274457931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0558185577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4525833129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3328056335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7595148086548</t>
   </si>
   <si>
     <t xml:space="preserve">13.7295722961426</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7220859527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5349311828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4900150299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7370586395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0140447616577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7071142196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8493499755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1113634109497</t>
+    <t xml:space="preserve">13.7220869064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.53493309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4900169372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7370595932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.014045715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7071123123169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8493490219116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1113662719727</t>
   </si>
   <si>
     <t xml:space="preserve">13.9766139984131</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0814208984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7445440292358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9990720748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5049877166748</t>
+    <t xml:space="preserve">14.0814189910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7445449829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9990711212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5049896240234</t>
   </si>
   <si>
     <t xml:space="preserve">13.6397371292114</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6621952056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6097946166992</t>
+    <t xml:space="preserve">13.6621961593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6097936630249</t>
   </si>
   <si>
     <t xml:space="preserve">13.3477783203125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4151544570923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.220513343811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.085765838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.100736618042</t>
+    <t xml:space="preserve">13.415153503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2205171585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0857639312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1007347106934</t>
   </si>
   <si>
     <t xml:space="preserve">13.0633068084717</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2354879379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1456518173218</t>
+    <t xml:space="preserve">13.2354860305786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1456527709961</t>
   </si>
   <si>
     <t xml:space="preserve">12.9285564422607</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2055435180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1082239151001</t>
+    <t xml:space="preserve">13.2055425643921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1082220077515</t>
   </si>
   <si>
     <t xml:space="preserve">13.198055267334</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1157083511353</t>
+    <t xml:space="preserve">13.1157093048096</t>
   </si>
   <si>
     <t xml:space="preserve">13.0109004974365</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9135837554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8611812591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9435291290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1905708312988</t>
+    <t xml:space="preserve">12.9135818481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.861180305481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.943528175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1905689239502</t>
   </si>
   <si>
     <t xml:space="preserve">13.4076681137085</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3552646636963</t>
+    <t xml:space="preserve">13.3552656173706</t>
   </si>
   <si>
     <t xml:space="preserve">13.2130289077759</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3402938842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9659852981567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8761539459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8312339782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9809598922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7638597488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7114582061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8686676025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7563762664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6815128326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5767078399658</t>
+    <t xml:space="preserve">13.3402919769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9659843444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8761520385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8312349319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9809589385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.763858795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7114572525024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8686656951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7563753128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6815137863159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5767068862915</t>
   </si>
   <si>
     <t xml:space="preserve">12.5467624664307</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5317916870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5617361068726</t>
+    <t xml:space="preserve">12.5317897796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5617351531982</t>
   </si>
   <si>
     <t xml:space="preserve">12.5542497634888</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4194984436035</t>
+    <t xml:space="preserve">12.4194974899292</t>
   </si>
   <si>
     <t xml:space="preserve">12.2772607803345</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4719009399414</t>
+    <t xml:space="preserve">12.4719018936157</t>
   </si>
   <si>
     <t xml:space="preserve">12.5018463134766</t>
@@ -548,55 +548,55 @@
     <t xml:space="preserve">11.9778156280518</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3596096038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4943599700928</t>
+    <t xml:space="preserve">12.3596086502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4943590164185</t>
   </si>
   <si>
     <t xml:space="preserve">12.3820676803589</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4045248031616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2697744369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1649694442749</t>
+    <t xml:space="preserve">12.4045257568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.269775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1649703979492</t>
   </si>
   <si>
     <t xml:space="preserve">12.2548046112061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3371515274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3221778869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7264280319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6740264892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7863187789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0932493209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9510145187378</t>
+    <t xml:space="preserve">12.3371505737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3221788406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7264308929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6740255355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7863178253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0932502746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9510135650635</t>
   </si>
   <si>
     <t xml:space="preserve">13.1306829452515</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9884433746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1381683349609</t>
+    <t xml:space="preserve">12.9884443283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1381673812866</t>
   </si>
   <si>
     <t xml:space="preserve">13.160626411438</t>
@@ -608,100 +608,100 @@
     <t xml:space="preserve">13.1681108474731</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2280006408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.00341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1755981445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4001808166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3852090835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8643245697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9167251586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5199613571167</t>
+    <t xml:space="preserve">13.2280015945435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0034170150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1755990982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.400182723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3852081298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8643236160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9167261123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5199594497681</t>
   </si>
   <si>
     <t xml:space="preserve">13.4450988769531</t>
   </si>
   <si>
-    <t xml:space="preserve">13.362753868103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4600687026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.51247215271</t>
+    <t xml:space="preserve">13.3627519607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4600715637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5124740600586</t>
   </si>
   <si>
     <t xml:space="preserve">13.437611579895</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8268909454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6247682571411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8044347763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7819766998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6996259689331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8418645858765</t>
+    <t xml:space="preserve">13.8268918991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6247663497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8044328689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7819757461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6996278762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8418617248535</t>
   </si>
   <si>
     <t xml:space="preserve">13.6771697998047</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8568353652954</t>
+    <t xml:space="preserve">13.8568363189697</t>
   </si>
   <si>
     <t xml:space="preserve">13.7670021057129</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5648775100708</t>
+    <t xml:space="preserve">13.5648765563965</t>
   </si>
   <si>
     <t xml:space="preserve">13.8942670822144</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3359498977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5605335235596</t>
+    <t xml:space="preserve">14.3359489440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5605344772339</t>
   </si>
   <si>
     <t xml:space="preserve">14.5156154632568</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6952838897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9722719192505</t>
+    <t xml:space="preserve">14.6952829360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9722700119019</t>
   </si>
   <si>
     <t xml:space="preserve">14.9348411560059</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9423236846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.822548866272</t>
+    <t xml:space="preserve">14.9423246383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.822546005249</t>
   </si>
   <si>
     <t xml:space="preserve">15.2043418884277</t>
@@ -710,10 +710,10 @@
     <t xml:space="preserve">15.7133989334106</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1369638442993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.159423828125</t>
+    <t xml:space="preserve">15.1369647979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1594228744507</t>
   </si>
   <si>
     <t xml:space="preserve">15.2866888046265</t>
@@ -722,16 +722,16 @@
     <t xml:space="preserve">15.36155128479</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2267961502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3465785980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6834526062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7208814620972</t>
+    <t xml:space="preserve">15.2267990112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3465766906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6834545135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7208852767944</t>
   </si>
   <si>
     <t xml:space="preserve">15.533730506897</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">15.4588680267334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1669120788574</t>
+    <t xml:space="preserve">15.1669092178345</t>
   </si>
   <si>
     <t xml:space="preserve">15.1968545913696</t>
@@ -755,52 +755,52 @@
     <t xml:space="preserve">15.6011056900024</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6460218429565</t>
+    <t xml:space="preserve">15.6460237503052</t>
   </si>
   <si>
     <t xml:space="preserve">15.7358570098877</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5861339569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9080381393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4245796203613</t>
+    <t xml:space="preserve">15.5861320495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9080362319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.42458152771</t>
   </si>
   <si>
     <t xml:space="preserve">16.1251373291016</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6984224319458</t>
+    <t xml:space="preserve">15.6984262466431</t>
   </si>
   <si>
     <t xml:space="preserve">16.2823429107666</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3272590637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2598857879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.267370223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5967617034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7839164733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.664134979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.521900177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4470367431641</t>
+    <t xml:space="preserve">16.3272609710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2598838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2673721313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5967597961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7839126586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6641387939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5219020843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4470386505127</t>
   </si>
   <si>
     <t xml:space="preserve">16.6416778564453</t>
@@ -812,73 +812,73 @@
     <t xml:space="preserve">16.7988872528076</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7464866638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8737506866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9560985565186</t>
+    <t xml:space="preserve">16.7464828491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8737487792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9560947418213</t>
   </si>
   <si>
     <t xml:space="preserve">17.1058197021484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3946342468262</t>
+    <t xml:space="preserve">16.3946361541748</t>
   </si>
   <si>
     <t xml:space="preserve">16.5069274902344</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6847553253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1950397491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1641101837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0094833374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7620697021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.63063621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8471202850342</t>
+    <t xml:space="preserve">16.6847534179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1950378417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1641120910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0094795227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7620716094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6306324005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8471183776855</t>
   </si>
   <si>
     <t xml:space="preserve">17.0249443054199</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9398975372314</t>
+    <t xml:space="preserve">16.9398956298828</t>
   </si>
   <si>
     <t xml:space="preserve">16.7698040008545</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9940185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1254558563232</t>
+    <t xml:space="preserve">16.9940166473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1254539489746</t>
   </si>
   <si>
     <t xml:space="preserve">16.9553604125977</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5455894470215</t>
+    <t xml:space="preserve">16.5455875396729</t>
   </si>
   <si>
     <t xml:space="preserve">16.7156829833984</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8548488616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7466068267822</t>
+    <t xml:space="preserve">16.8548469543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7466106414795</t>
   </si>
   <si>
     <t xml:space="preserve">17.0404090881348</t>
@@ -890,61 +890,61 @@
     <t xml:space="preserve">16.5378551483154</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5687808990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6229000091553</t>
+    <t xml:space="preserve">16.5687789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6229038238525</t>
   </si>
   <si>
     <t xml:space="preserve">16.7079486846924</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7234115600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1822032928467</t>
+    <t xml:space="preserve">16.72340965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.182201385498</t>
   </si>
   <si>
     <t xml:space="preserve">16.0894241333008</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0816917419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1590061187744</t>
+    <t xml:space="preserve">16.0816898345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.159008026123</t>
   </si>
   <si>
     <t xml:space="preserve">15.9347925186157</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2363204956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0739593505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9966430664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3909549713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4914665222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8935070037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2414302825928</t>
+    <t xml:space="preserve">16.2363243103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0739612579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9966459274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3909568786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4914646148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8935089111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2414264678955</t>
   </si>
   <si>
     <t xml:space="preserve">17.0558700561523</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2878189086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2955513000488</t>
+    <t xml:space="preserve">17.2878170013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2955474853516</t>
   </si>
   <si>
     <t xml:space="preserve">17.3960609436035</t>
@@ -956,10 +956,10 @@
     <t xml:space="preserve">17.2800884246826</t>
   </si>
   <si>
-    <t xml:space="preserve">16.700216293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5533180236816</t>
+    <t xml:space="preserve">16.7002182006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5533199310303</t>
   </si>
   <si>
     <t xml:space="preserve">16.4837322235107</t>
@@ -974,10 +974,10 @@
     <t xml:space="preserve">16.3832244873047</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3986835479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2749824523926</t>
+    <t xml:space="preserve">16.3986873626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2749786376953</t>
   </si>
   <si>
     <t xml:space="preserve">16.2285919189453</t>
@@ -992,55 +992,55 @@
     <t xml:space="preserve">15.9502544403076</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0353031158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2827110290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4141483306885</t>
+    <t xml:space="preserve">16.0353012084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2827091217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4141502380371</t>
   </si>
   <si>
     <t xml:space="preserve">16.6074390411377</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5919742584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9321632385254</t>
+    <t xml:space="preserve">16.5919761657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.932165145874</t>
   </si>
   <si>
     <t xml:space="preserve">17.0481376647949</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2646217346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9476299285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0713310241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0636024475098</t>
+    <t xml:space="preserve">17.2646236419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9476280212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0713329315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0636043548584</t>
   </si>
   <si>
     <t xml:space="preserve">17.079065322876</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2723522186279</t>
+    <t xml:space="preserve">17.2723560333252</t>
   </si>
   <si>
     <t xml:space="preserve">17.303279876709</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3728637695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3187427520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5584201812744</t>
+    <t xml:space="preserve">17.3728675842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3187446594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5584259033203</t>
   </si>
   <si>
     <t xml:space="preserve">17.5893497467041</t>
@@ -1049,13 +1049,13 @@
     <t xml:space="preserve">17.4656448364258</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7207851409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5738868713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5429592132568</t>
+    <t xml:space="preserve">17.7207870483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5738849639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5429611206055</t>
   </si>
   <si>
     <t xml:space="preserve">17.6975917816162</t>
@@ -1064,16 +1064,16 @@
     <t xml:space="preserve">18.107364654541</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0377807617188</t>
+    <t xml:space="preserve">18.0377826690674</t>
   </si>
   <si>
     <t xml:space="preserve">17.6125450134277</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6821308135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5197658538818</t>
+    <t xml:space="preserve">17.6821269989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5197639465332</t>
   </si>
   <si>
     <t xml:space="preserve">17.3110103607178</t>
@@ -1082,25 +1082,25 @@
     <t xml:space="preserve">17.1099910736084</t>
   </si>
   <si>
-    <t xml:space="preserve">17.357400894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1795749664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1409187316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0867958068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8857746124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6151676177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5301208496094</t>
+    <t xml:space="preserve">17.3574028015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1795768737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1409149169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0867977142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8857765197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6151695251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5301246643066</t>
   </si>
   <si>
     <t xml:space="preserve">16.352294921875</t>
@@ -1109,13 +1109,13 @@
     <t xml:space="preserve">16.0430335998535</t>
   </si>
   <si>
-    <t xml:space="preserve">15.826548576355</t>
+    <t xml:space="preserve">15.8265476226807</t>
   </si>
   <si>
     <t xml:space="preserve">15.9270601272583</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1976642608643</t>
+    <t xml:space="preserve">16.1976661682129</t>
   </si>
   <si>
     <t xml:space="preserve">16.6692905426025</t>
@@ -1127,22 +1127,22 @@
     <t xml:space="preserve">16.7852649688721</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9630908966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8084583282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9244346618652</t>
+    <t xml:space="preserve">16.9630928039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8084602355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9244327545166</t>
   </si>
   <si>
     <t xml:space="preserve">16.4218788146973</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0507640838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4605388641357</t>
+    <t xml:space="preserve">16.0507659912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4605407714844</t>
   </si>
   <si>
     <t xml:space="preserve">16.452808380127</t>
@@ -1154,55 +1154,55 @@
     <t xml:space="preserve">16.6383647918701</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7929973602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4064159393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3342094421387</t>
+    <t xml:space="preserve">16.7929954528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4064178466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3342056274414</t>
   </si>
   <si>
     <t xml:space="preserve">17.3805961608887</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4888401031494</t>
+    <t xml:space="preserve">17.4888381958008</t>
   </si>
   <si>
     <t xml:space="preserve">17.5506916046143</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6898612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4115238189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6434707641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2568893432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2259674072266</t>
+    <t xml:space="preserve">17.6898593902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4115257263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6434688568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.256893157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2259654998779</t>
   </si>
   <si>
     <t xml:space="preserve">17.504301071167</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4991989135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.978551864624</t>
+    <t xml:space="preserve">16.499195098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9785537719727</t>
   </si>
   <si>
     <t xml:space="preserve">16.3445644378662</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2981739044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9012413024902</t>
+    <t xml:space="preserve">16.2981758117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9012393951416</t>
   </si>
   <si>
     <t xml:space="preserve">16.653829574585</t>
@@ -1211,19 +1211,19 @@
     <t xml:space="preserve">16.2672500610352</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3136386871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4269886016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4475574493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3857040405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8805236816406</t>
+    <t xml:space="preserve">16.3136367797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4269866943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4475555419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.385705947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8805255889893</t>
   </si>
   <si>
     <t xml:space="preserve">19.1433982849121</t>
@@ -1238,25 +1238,25 @@
     <t xml:space="preserve">18.6949653625488</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6795043945312</t>
+    <t xml:space="preserve">18.6795024871826</t>
   </si>
   <si>
     <t xml:space="preserve">18.7413539886475</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6640377044678</t>
+    <t xml:space="preserve">18.6640396118164</t>
   </si>
   <si>
     <t xml:space="preserve">18.7877445220947</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2516384124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4371967315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3444213867188</t>
+    <t xml:space="preserve">19.2516422271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.437198638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3444194793701</t>
   </si>
   <si>
     <t xml:space="preserve">19.406270980835</t>
@@ -1265,43 +1265,43 @@
     <t xml:space="preserve">19.5609016418457</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3289566040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1743221282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1124687194824</t>
+    <t xml:space="preserve">19.3289546966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1743240356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1124725341797</t>
   </si>
   <si>
     <t xml:space="preserve">19.1588611602783</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2825679779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2361793518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2052478790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2671012878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5299777984619</t>
+    <t xml:space="preserve">19.2825660705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.236177444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2052516937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2671031951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5299758911133</t>
   </si>
   <si>
     <t xml:space="preserve">19.638219833374</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5918312072754</t>
+    <t xml:space="preserve">19.5918292999268</t>
   </si>
   <si>
     <t xml:space="preserve">19.4835891723633</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5145130157471</t>
+    <t xml:space="preserve">19.5145111083984</t>
   </si>
   <si>
     <t xml:space="preserve">19.4526615142822</t>
@@ -1313,13 +1313,13 @@
     <t xml:space="preserve">18.1382923126221</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3547763824463</t>
+    <t xml:space="preserve">18.3547744750977</t>
   </si>
   <si>
     <t xml:space="preserve">18.0764408111572</t>
   </si>
   <si>
-    <t xml:space="preserve">18.03005027771</t>
+    <t xml:space="preserve">18.0300483703613</t>
   </si>
   <si>
     <t xml:space="preserve">18.1737804412842</t>
@@ -1343,13 +1343,13 @@
     <t xml:space="preserve">18.5889987945557</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5570583343506</t>
+    <t xml:space="preserve">18.557056427002</t>
   </si>
   <si>
     <t xml:space="preserve">18.4931774139404</t>
   </si>
   <si>
-    <t xml:space="preserve">18.157808303833</t>
+    <t xml:space="preserve">18.1578102111816</t>
   </si>
   <si>
     <t xml:space="preserve">18.4292984008789</t>
@@ -1361,16 +1361,16 @@
     <t xml:space="preserve">18.6369075775146</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4133262634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4612369537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3175106048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8064727783203</t>
+    <t xml:space="preserve">18.4133281707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.461238861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3175067901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8064708709717</t>
   </si>
   <si>
     <t xml:space="preserve">17.8224391937256</t>
@@ -1379,16 +1379,16 @@
     <t xml:space="preserve">17.7106513977051</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9182605743408</t>
+    <t xml:space="preserve">17.9182624816895</t>
   </si>
   <si>
     <t xml:space="preserve">17.9661712646484</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8863201141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9981117248535</t>
+    <t xml:space="preserve">17.8863220214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9981098175049</t>
   </si>
   <si>
     <t xml:space="preserve">18.3973598480225</t>
@@ -1397,64 +1397,64 @@
     <t xml:space="preserve">18.5251197814941</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4452686309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1479473114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1639137268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0201835632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8604888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7806377410889</t>
+    <t xml:space="preserve">18.4452667236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1479454040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1639156341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0201873779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8604869842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7806358337402</t>
   </si>
   <si>
     <t xml:space="preserve">18.5730285644531</t>
   </si>
   <si>
-    <t xml:space="preserve">19.06809425354</t>
+    <t xml:space="preserve">19.0680961608887</t>
   </si>
   <si>
     <t xml:space="preserve">18.7646675109863</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4772090911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7007865905762</t>
+    <t xml:space="preserve">18.4772071838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7007884979248</t>
   </si>
   <si>
     <t xml:space="preserve">19.2437648773193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4513759613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4992828369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2118225097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1319713592529</t>
+    <t xml:space="preserve">19.4513740539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4992847442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2118263244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1319751739502</t>
   </si>
   <si>
     <t xml:space="preserve">19.0042152404785</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1160049438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0361557006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1798858642578</t>
+    <t xml:space="preserve">19.1160068511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.036153793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1798839569092</t>
   </si>
   <si>
     <t xml:space="preserve">19.3236141204834</t>
@@ -1463,46 +1463,46 @@
     <t xml:space="preserve">19.3395843505859</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3076438903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7228622436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.467342376709</t>
+    <t xml:space="preserve">19.3076477050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.722864151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4673404693604</t>
   </si>
   <si>
     <t xml:space="preserve">19.3874950408936</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5631656646729</t>
+    <t xml:space="preserve">19.5631618499756</t>
   </si>
   <si>
     <t xml:space="preserve">19.8825607299805</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3616580963135</t>
+    <t xml:space="preserve">20.3616600036621</t>
   </si>
   <si>
     <t xml:space="preserve">20.4415111541748</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2658386230469</t>
+    <t xml:space="preserve">20.2658424377441</t>
   </si>
   <si>
     <t xml:space="preserve">20.7609081268311</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0962772369385</t>
+    <t xml:space="preserve">21.0962753295898</t>
   </si>
   <si>
     <t xml:space="preserve">20.8247871398926</t>
   </si>
   <si>
-    <t xml:space="preserve">20.249870300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4734477996826</t>
+    <t xml:space="preserve">20.2498683929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.473445892334</t>
   </si>
   <si>
     <t xml:space="preserve">20.1540508270264</t>
@@ -1523,22 +1523,22 @@
     <t xml:space="preserve">18.8125762939453</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7327270507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3813915252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2536277770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9342288970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3494453430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9243659973145</t>
+    <t xml:space="preserve">18.7327251434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3813877105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2536315917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9342308044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3494510650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9243679046631</t>
   </si>
   <si>
     <t xml:space="preserve">18.7486972808838</t>
@@ -1547,16 +1547,16 @@
     <t xml:space="preserve">18.1258697509766</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7905044555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4391613006592</t>
+    <t xml:space="preserve">17.7905006408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4391651153564</t>
   </si>
   <si>
     <t xml:space="preserve">17.1357326507568</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2155838012695</t>
+    <t xml:space="preserve">17.2155857086182</t>
   </si>
   <si>
     <t xml:space="preserve">16.9760360717773</t>
@@ -1565,31 +1565,31 @@
     <t xml:space="preserve">17.550952911377</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8961868286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0718517303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9281253814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8323040008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0558834075928</t>
+    <t xml:space="preserve">16.8961849212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0718555450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9281272888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8323078155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0558853149414</t>
   </si>
   <si>
     <t xml:space="preserve">17.1836433410645</t>
   </si>
   <si>
-    <t xml:space="preserve">17.455135345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.816333770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3532047271729</t>
+    <t xml:space="preserve">17.4551334381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8163356781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3532066345215</t>
   </si>
   <si>
     <t xml:space="preserve">15.9858999252319</t>
@@ -1598,91 +1598,91 @@
     <t xml:space="preserve">16.0976886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1136608123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4269523620605</t>
+    <t xml:space="preserve">16.1136589050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4269504547119</t>
   </si>
   <si>
     <t xml:space="preserve">15.3311319351196</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6505308151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4748601913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4429216384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7703037261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8421678543091</t>
+    <t xml:space="preserve">15.6505298614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4748611450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4429225921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.770302772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8421688079834</t>
   </si>
   <si>
     <t xml:space="preserve">15.7383651733398</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4490280151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2733592987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1615695953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.321268081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4809665679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6246967315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7684230804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1676731109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3433437347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2794628143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9440937042236</t>
+    <t xml:space="preserve">16.4490261077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2733573913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1615676879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3212699890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4809684753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6246948242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.768424987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1676750183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3433418273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2794647216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.944091796875</t>
   </si>
   <si>
     <t xml:space="preserve">17.0079746246338</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6406669616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2414150238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5608177185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7045478820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8482761383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3752841949463</t>
+    <t xml:space="preserve">16.6406688690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2414207458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5608158111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7045440673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.848274230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3752861022949</t>
   </si>
   <si>
     <t xml:space="preserve">17.1037940979004</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8802146911621</t>
+    <t xml:space="preserve">16.8802165985107</t>
   </si>
   <si>
     <t xml:space="preserve">16.9121551513672</t>
@@ -1691,13 +1691,13 @@
     <t xml:space="preserve">16.8642463684082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7205123901367</t>
+    <t xml:space="preserve">16.7205181121826</t>
   </si>
   <si>
     <t xml:space="preserve">16.6885757446289</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6087265014648</t>
+    <t xml:space="preserve">16.6087245941162</t>
   </si>
   <si>
     <t xml:space="preserve">16.7364864349365</t>
@@ -1709,28 +1709,28 @@
     <t xml:space="preserve">15.8980646133423</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1935081481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2094783782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3851490020752</t>
+    <t xml:space="preserve">16.193510055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2094764709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3851470947266</t>
   </si>
   <si>
     <t xml:space="preserve">16.28932762146</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2573871612549</t>
+    <t xml:space="preserve">16.2573890686035</t>
   </si>
   <si>
     <t xml:space="preserve">16.2254486083984</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9140357971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4170875549316</t>
+    <t xml:space="preserve">15.9140338897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4170894622803</t>
   </si>
   <si>
     <t xml:space="preserve">16.5288772583008</t>
@@ -1745,7 +1745,7 @@
     <t xml:space="preserve">16.3691787719727</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1775398254395</t>
+    <t xml:space="preserve">16.1775379180908</t>
   </si>
   <si>
     <t xml:space="preserve">16.4889507293701</t>
@@ -1754,7 +1754,7 @@
     <t xml:space="preserve">16.2494029998779</t>
   </si>
   <si>
-    <t xml:space="preserve">16.329252243042</t>
+    <t xml:space="preserve">16.3292541503906</t>
   </si>
   <si>
     <t xml:space="preserve">16.4091014862061</t>
@@ -1763,7 +1763,7 @@
     <t xml:space="preserve">16.1695537567139</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0497779846191</t>
+    <t xml:space="preserve">16.0497798919678</t>
   </si>
   <si>
     <t xml:space="preserve">16.5688018798828</t>
@@ -1775,37 +1775,37 @@
     <t xml:space="preserve">17.2874488830566</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0878276824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0478992462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8083515167236</t>
+    <t xml:space="preserve">17.0878219604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0479011535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.808349609375</t>
   </si>
   <si>
     <t xml:space="preserve">16.9680500030518</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7285003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8881988525391</t>
+    <t xml:space="preserve">16.7285022735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8882007598877</t>
   </si>
   <si>
     <t xml:space="preserve">17.1277484893799</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8793506622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0452404022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9208240509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7964057922363</t>
+    <t xml:space="preserve">16.8793487548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.045238494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9208221435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7964038848877</t>
   </si>
   <si>
     <t xml:space="preserve">17.2111301422119</t>
@@ -1814,58 +1814,58 @@
     <t xml:space="preserve">17.1281852722168</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1696586608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.418493270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3770236968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4599666595459</t>
+    <t xml:space="preserve">17.1696605682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4184951782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3770217895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4599647521973</t>
   </si>
   <si>
     <t xml:space="preserve">17.294075012207</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9622955322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7549304962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6305141448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3402080535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4895076751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5392761230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7088012695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.667329788208</t>
+    <t xml:space="preserve">16.9622974395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7549343109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6305122375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3402061462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4895057678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5392742156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7088031768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6673278808594</t>
   </si>
   <si>
     <t xml:space="preserve">17.5014381408691</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5429096221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2526035308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7134571075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4231510162354</t>
+    <t xml:space="preserve">17.542911529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2526016235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7134590148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4231491088867</t>
   </si>
   <si>
     <t xml:space="preserve">16.3733825683594</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">16.1743144989014</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2738513946533</t>
+    <t xml:space="preserve">16.2738494873047</t>
   </si>
   <si>
     <t xml:space="preserve">16.124547958374</t>
@@ -1886,40 +1886,40 @@
     <t xml:space="preserve">16.3070278167725</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8591232299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7264099121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7927665710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0747814178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5273418426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4278078079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6600532531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1789712905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3614530563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6932325363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6102876663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4609851837158</t>
+    <t xml:space="preserve">15.8591241836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7264137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7927684783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.074779510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5273427963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4278087615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6600542068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.178973197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3614521026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6932344436646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6102857589722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4609861373901</t>
   </si>
   <si>
     <t xml:space="preserve">15.4443979263306</t>
@@ -1937,25 +1937,25 @@
     <t xml:space="preserve">16.2904376983643</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3899726867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4397392272949</t>
+    <t xml:space="preserve">16.3899745941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4397430419922</t>
   </si>
   <si>
     <t xml:space="preserve">16.6719875335693</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9576396942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0867137908936</t>
+    <t xml:space="preserve">17.9576358795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0867118835449</t>
   </si>
   <si>
     <t xml:space="preserve">17.3355484008789</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8378772735596</t>
+    <t xml:space="preserve">16.8378753662109</t>
   </si>
   <si>
     <t xml:space="preserve">16.5890407562256</t>
@@ -1964,43 +1964,43 @@
     <t xml:space="preserve">16.2572612762451</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8757123947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9088916778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1577262878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1411361694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4729194641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7595891952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6766443252563</t>
+    <t xml:space="preserve">15.8757133483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9088907241821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1577243804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1411380767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4729175567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7595882415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.676643371582</t>
   </si>
   <si>
     <t xml:space="preserve">15.5936985015869</t>
   </si>
   <si>
-    <t xml:space="preserve">15.477578163147</t>
+    <t xml:space="preserve">15.4775772094727</t>
   </si>
   <si>
     <t xml:space="preserve">15.7429990768433</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7098236083984</t>
+    <t xml:space="preserve">15.7098217010498</t>
   </si>
   <si>
     <t xml:space="preserve">15.8425350189209</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3567943572998</t>
+    <t xml:space="preserve">16.3567962646484</t>
   </si>
   <si>
     <t xml:space="preserve">16.323616027832</t>
@@ -2009,37 +2009,37 @@
     <t xml:space="preserve">15.975248336792</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5843849182129</t>
+    <t xml:space="preserve">17.5843830108643</t>
   </si>
   <si>
     <t xml:space="preserve">17.0037670135498</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2240810394287</t>
+    <t xml:space="preserve">16.2240829467773</t>
   </si>
   <si>
     <t xml:space="preserve">16.0084247589111</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1909046173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5558643341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5319995880127</t>
+    <t xml:space="preserve">16.1909065246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5558624267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.532000541687</t>
   </si>
   <si>
     <t xml:space="preserve">14.7974243164062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.183629989624</t>
+    <t xml:space="preserve">14.1836309432983</t>
   </si>
   <si>
     <t xml:space="preserve">13.9347944259644</t>
   </si>
   <si>
-    <t xml:space="preserve">13.636194229126</t>
+    <t xml:space="preserve">13.6361923217773</t>
   </si>
   <si>
     <t xml:space="preserve">13.4371242523193</t>
@@ -2057,16 +2057,16 @@
     <t xml:space="preserve">11.9606990814209</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4251918792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0317115783691</t>
+    <t xml:space="preserve">12.4251909255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0317125320435</t>
   </si>
   <si>
     <t xml:space="preserve">11.4796171188354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1690826416016</t>
+    <t xml:space="preserve">10.1690816879272</t>
   </si>
   <si>
     <t xml:space="preserve">10.3681507110596</t>
@@ -2081,7 +2081,7 @@
     <t xml:space="preserve">11.8777532577515</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4417819976807</t>
+    <t xml:space="preserve">12.4417810440063</t>
   </si>
   <si>
     <t xml:space="preserve">12.8565082550049</t>
@@ -2090,22 +2090,22 @@
     <t xml:space="preserve">12.1763563156128</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2924795150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2141923904419</t>
+    <t xml:space="preserve">12.29248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2141933441162</t>
   </si>
   <si>
     <t xml:space="preserve">10.9155893325806</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6667537689209</t>
+    <t xml:space="preserve">10.6667547225952</t>
   </si>
   <si>
     <t xml:space="preserve">10.2022609710693</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4510974884033</t>
+    <t xml:space="preserve">10.4510955810547</t>
   </si>
   <si>
     <t xml:space="preserve">10.5174522399902</t>
@@ -2114,40 +2114,40 @@
     <t xml:space="preserve">10.5340414047241</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4013290405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1524925231934</t>
+    <t xml:space="preserve">10.4013299942017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1524934768677</t>
   </si>
   <si>
     <t xml:space="preserve">10.0529584884644</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97001457214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4676847457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6999320983887</t>
+    <t xml:space="preserve">9.97001361846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4676856994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6999311447144</t>
   </si>
   <si>
     <t xml:space="preserve">10.3017950057983</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0695476531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2520265579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.003191947937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0363693237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1193161010742</t>
+    <t xml:space="preserve">10.0695486068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2520275115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0031929016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0363702774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1193151473999</t>
   </si>
   <si>
     <t xml:space="preserve">9.92024707794189</t>
@@ -2162,7 +2162,7 @@
     <t xml:space="preserve">9.32304096221924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14056205749512</t>
+    <t xml:space="preserve">9.1405611038208</t>
   </si>
   <si>
     <t xml:space="preserve">9.07420539855957</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">10.1359043121338</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70458889007568</t>
+    <t xml:space="preserve">9.70458793640137</t>
   </si>
   <si>
     <t xml:space="preserve">9.38939666748047</t>
@@ -2189,16 +2189,16 @@
     <t xml:space="preserve">10.4179182052612</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9985342025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8990001678467</t>
+    <t xml:space="preserve">10.99853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.899001121521</t>
   </si>
   <si>
     <t xml:space="preserve">10.9819459915161</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8160543441772</t>
+    <t xml:space="preserve">10.8160552978516</t>
   </si>
   <si>
     <t xml:space="preserve">10.8824110031128</t>
@@ -2207,16 +2207,16 @@
     <t xml:space="preserve">11.8113975524902</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7782192230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5957403182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3634920120239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6833429336548</t>
+    <t xml:space="preserve">11.7782201766968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5957384109497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3634929656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6833419799805</t>
   </si>
   <si>
     <t xml:space="preserve">10.9487676620483</t>
@@ -2225,7 +2225,7 @@
     <t xml:space="preserve">10.9653568267822</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2639579772949</t>
+    <t xml:space="preserve">11.2639589309692</t>
   </si>
   <si>
     <t xml:space="preserve">11.2805480957031</t>
@@ -2234,16 +2234,16 @@
     <t xml:space="preserve">11.1810140609741</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3303155899048</t>
+    <t xml:space="preserve">11.3303146362305</t>
   </si>
   <si>
     <t xml:space="preserve">11.297137260437</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0814800262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0151243209839</t>
+    <t xml:space="preserve">11.0814790725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0151224136353</t>
   </si>
   <si>
     <t xml:space="preserve">11.0648908615112</t>
@@ -2252,31 +2252,31 @@
     <t xml:space="preserve">10.8326444625854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.849232673645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5838079452515</t>
+    <t xml:space="preserve">10.8492336273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5838088989258</t>
   </si>
   <si>
     <t xml:space="preserve">10.3847408294678</t>
   </si>
   <si>
-    <t xml:space="preserve">10.650164604187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3515615463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2354393005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9321784973145</t>
+    <t xml:space="preserve">10.6501655578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3515605926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2354383468628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9321794509888</t>
   </si>
   <si>
     <t xml:space="preserve">10.550630569458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5008630752563</t>
+    <t xml:space="preserve">10.500862121582</t>
   </si>
   <si>
     <t xml:space="preserve">10.6169862747192</t>
@@ -2285,10 +2285,10 @@
     <t xml:space="preserve">10.4842748641968</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0197820663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3349742889404</t>
+    <t xml:space="preserve">10.0197811126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3349733352661</t>
   </si>
   <si>
     <t xml:space="preserve">10.7828760147095</t>
@@ -2297,37 +2297,37 @@
     <t xml:space="preserve">10.6003971099854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1312465667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4132614135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4298496246338</t>
+    <t xml:space="preserve">11.1312475204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4132604598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4298486709595</t>
   </si>
   <si>
     <t xml:space="preserve">11.2307815551758</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8658227920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3137264251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3966703414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5127944946289</t>
+    <t xml:space="preserve">10.8658218383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3137273788452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.396671295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5127954483032</t>
   </si>
   <si>
     <t xml:space="preserve">11.8611650466919</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2095346450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9772872924805</t>
+    <t xml:space="preserve">12.2095355987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9772882461548</t>
   </si>
   <si>
     <t xml:space="preserve">12.0602331161499</t>
@@ -2339,7 +2339,7 @@
     <t xml:space="preserve">11.3800830841064</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1146583557129</t>
+    <t xml:space="preserve">11.1146574020386</t>
   </si>
   <si>
     <t xml:space="preserve">10.6335754394531</t>
@@ -2354,19 +2354,19 @@
     <t xml:space="preserve">9.62164402008057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65482330322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60505485534668</t>
+    <t xml:space="preserve">9.65482234954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60505390167236</t>
   </si>
   <si>
     <t xml:space="preserve">9.75435733795166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.491548538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0058097839355</t>
+    <t xml:space="preserve">12.4915494918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0058088302612</t>
   </si>
   <si>
     <t xml:space="preserve">12.1929454803467</t>
@@ -2375,16 +2375,16 @@
     <t xml:space="preserve">12.8399171829224</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3210000991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4086036682129</t>
+    <t xml:space="preserve">13.3209991455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4086017608643</t>
   </si>
   <si>
     <t xml:space="preserve">12.2758913040161</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7237939834595</t>
+    <t xml:space="preserve">12.7237949371338</t>
   </si>
   <si>
     <t xml:space="preserve">12.9062747955322</t>
@@ -2393,7 +2393,7 @@
     <t xml:space="preserve">13.1053428649902</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9892196655273</t>
+    <t xml:space="preserve">12.989218711853</t>
   </si>
   <si>
     <t xml:space="preserve">13.0721645355225</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">13.0887537002563</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0389862060547</t>
+    <t xml:space="preserve">13.038987159729</t>
   </si>
   <si>
     <t xml:space="preserve">12.6740274429321</t>
@@ -2414,19 +2414,19 @@
     <t xml:space="preserve">12.4583702087402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5081377029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7403841018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3754262924194</t>
+    <t xml:space="preserve">12.5081357955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7403831481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3754243850708</t>
   </si>
   <si>
     <t xml:space="preserve">12.4749593734741</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6574392318726</t>
+    <t xml:space="preserve">12.6574382781982</t>
   </si>
   <si>
     <t xml:space="preserve">12.9560413360596</t>
@@ -2435,10 +2435,10 @@
     <t xml:space="preserve">12.9228630065918</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5366582870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9845609664917</t>
+    <t xml:space="preserve">13.536657333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9845628738403</t>
   </si>
   <si>
     <t xml:space="preserve">14.3661098480225</t>
@@ -2447,13 +2447,13 @@
     <t xml:space="preserve">14.5817680358887</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6978912353516</t>
+    <t xml:space="preserve">14.6978902816772</t>
   </si>
   <si>
     <t xml:space="preserve">14.7642459869385</t>
   </si>
   <si>
-    <t xml:space="preserve">14.631534576416</t>
+    <t xml:space="preserve">14.6315355300903</t>
   </si>
   <si>
     <t xml:space="preserve">14.1006841659546</t>
@@ -2465,16 +2465,16 @@
     <t xml:space="preserve">14.780837059021</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7476596832275</t>
+    <t xml:space="preserve">14.7476587295532</t>
   </si>
   <si>
     <t xml:space="preserve">14.4988222122192</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3495206832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2499876022339</t>
+    <t xml:space="preserve">14.3495197296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2499885559082</t>
   </si>
   <si>
     <t xml:space="preserve">14.2333974838257</t>
@@ -2489,40 +2489,40 @@
     <t xml:space="preserve">14.0509185791016</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2831649780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0462608337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9301376342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3946313858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3448629379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9918365478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8969602584839</t>
+    <t xml:space="preserve">14.2831630706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0462598800659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.930136680603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3946285247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3448638916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9918375015259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8969593048096</t>
   </si>
   <si>
     <t xml:space="preserve">14.979905128479</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9135475158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9964933395386</t>
+    <t xml:space="preserve">14.9135494232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9964952468872</t>
   </si>
   <si>
     <t xml:space="preserve">15.8259477615356</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6434650421143</t>
+    <t xml:space="preserve">15.6434669494629</t>
   </si>
   <si>
     <t xml:space="preserve">16.0250148773193</t>
@@ -2534,31 +2534,31 @@
     <t xml:space="preserve">16.0581932067871</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5605211257935</t>
+    <t xml:space="preserve">15.5605201721191</t>
   </si>
   <si>
     <t xml:space="preserve">15.0130834579468</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2619180679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2287397384644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1457929611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4941644668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.626877784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2121515274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5024576187134</t>
+    <t xml:space="preserve">15.2619190216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.228741645813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1457948684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4941654205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6268768310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2121505737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5024585723877</t>
   </si>
   <si>
     <t xml:space="preserve">15.2702140808105</t>
@@ -2567,40 +2567,40 @@
     <t xml:space="preserve">15.253623008728</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5439310073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5771102905273</t>
+    <t xml:space="preserve">15.5439329147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.577109336853</t>
   </si>
   <si>
     <t xml:space="preserve">15.850830078125</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7181167602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7347059249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8840074539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7512941360474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4361019134521</t>
+    <t xml:space="preserve">15.7181186676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7347040176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8840084075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.751293182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4361028671265</t>
   </si>
   <si>
     <t xml:space="preserve">16.3982696533203</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5807437896729</t>
+    <t xml:space="preserve">16.5807456970215</t>
   </si>
   <si>
     <t xml:space="preserve">15.8674173355103</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0830745697021</t>
+    <t xml:space="preserve">16.0830764770508</t>
   </si>
   <si>
     <t xml:space="preserve">16.1079597473145</t>
@@ -2612,7 +2612,7 @@
     <t xml:space="preserve">16.622220993042</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8212890625</t>
+    <t xml:space="preserve">16.8212871551514</t>
   </si>
   <si>
     <t xml:space="preserve">16.7051639556885</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">17.4516716003418</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2194232940674</t>
+    <t xml:space="preserve">17.219425201416</t>
   </si>
   <si>
     <t xml:space="preserve">16.7217540740967</t>
@@ -2645,10 +2645,10 @@
     <t xml:space="preserve">17.1530685424805</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0535354614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0369472503662</t>
+    <t xml:space="preserve">17.0535335540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0369453430176</t>
   </si>
   <si>
     <t xml:space="preserve">16.8876457214355</t>
@@ -2657,43 +2657,43 @@
     <t xml:space="preserve">16.771520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8544654846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2028369903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1033000946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1198921203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7383441925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3521366119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.269193649292</t>
+    <t xml:space="preserve">16.8544673919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2028350830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1033039093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1198902130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7383403778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3521385192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2691917419434</t>
   </si>
   <si>
     <t xml:space="preserve">16.8710536956787</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9171867370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2074966430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2323760986328</t>
+    <t xml:space="preserve">15.9171829223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2074928283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2323780059814</t>
   </si>
   <si>
     <t xml:space="preserve">16.6056327819824</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6958503723145</t>
+    <t xml:space="preserve">18.6958484649658</t>
   </si>
   <si>
     <t xml:space="preserve">18.1981792449951</t>
@@ -2702,19 +2702,19 @@
     <t xml:space="preserve">18.1649990081787</t>
   </si>
   <si>
-    <t xml:space="preserve">17.617561340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0820541381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6507396697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8000392913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4019050598145</t>
+    <t xml:space="preserve">17.6175594329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0820560455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6507415771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8000411987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4019031524658</t>
   </si>
   <si>
     <t xml:space="preserve">17.3189601898193</t>
@@ -2723,13 +2723,13 @@
     <t xml:space="preserve">17.020357131958</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7881107330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.970588684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1862468719482</t>
+    <t xml:space="preserve">16.7881088256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9705905914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1862449645996</t>
   </si>
   <si>
     <t xml:space="preserve">16.4065628051758</t>
@@ -2741,61 +2741,61 @@
     <t xml:space="preserve">16.049898147583</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1660213470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5346145629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0701217651367</t>
+    <t xml:space="preserve">16.1660194396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5346164703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0701236724854</t>
   </si>
   <si>
     <t xml:space="preserve">17.2360153198242</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6839160919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4848480224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2762184143066</t>
+    <t xml:space="preserve">17.6839199066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4848518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.276216506958</t>
   </si>
   <si>
     <t xml:space="preserve">17.2424736022949</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3437023162842</t>
+    <t xml:space="preserve">17.3437004089355</t>
   </si>
   <si>
     <t xml:space="preserve">17.5461559295654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4111881256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3774471282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6642589569092</t>
+    <t xml:space="preserve">17.4111862182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3774452209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6642570495605</t>
   </si>
   <si>
     <t xml:space="preserve">17.4449310302734</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4618015289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1749877929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.040018081665</t>
+    <t xml:space="preserve">17.4618034362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.174991607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0400199890137</t>
   </si>
   <si>
     <t xml:space="preserve">17.0062770843506</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9556617736816</t>
+    <t xml:space="preserve">16.9556636810303</t>
   </si>
   <si>
     <t xml:space="preserve">16.8628711700439</t>
@@ -2810,52 +2810,52 @@
     <t xml:space="preserve">16.7532062530518</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2087306976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2048892974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0952262878418</t>
+    <t xml:space="preserve">17.2087326049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2048873901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0952281951904</t>
   </si>
   <si>
     <t xml:space="preserve">16.1458396911621</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7915420532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6903162002563</t>
+    <t xml:space="preserve">15.7915410995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6903133392334</t>
   </si>
   <si>
     <t xml:space="preserve">15.8590259552002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4119386672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5216026306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.099817276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.420373916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.60595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5806493759155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.833722114563</t>
+    <t xml:space="preserve">15.411937713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5216007232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0998182296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4203748703003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6059589385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5806512832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8337202072144</t>
   </si>
   <si>
     <t xml:space="preserve">16.0446128845215</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8758983612061</t>
+    <t xml:space="preserve">15.8758974075317</t>
   </si>
   <si>
     <t xml:space="preserve">15.8927707672119</t>
@@ -2864,16 +2864,16 @@
     <t xml:space="preserve">16.0108680725098</t>
   </si>
   <si>
-    <t xml:space="preserve">15.934947013855</t>
+    <t xml:space="preserve">15.9349479675293</t>
   </si>
   <si>
     <t xml:space="preserve">15.7662353515625</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7746725082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.513165473938</t>
+    <t xml:space="preserve">15.7746734619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5131645202637</t>
   </si>
   <si>
     <t xml:space="preserve">15.4878597259521</t>
@@ -2882,58 +2882,58 @@
     <t xml:space="preserve">15.184175491333</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2347898483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3950653076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9433832168579</t>
+    <t xml:space="preserve">15.234790802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3950662612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9433841705322</t>
   </si>
   <si>
     <t xml:space="preserve">16.112096786499</t>
   </si>
   <si>
-    <t xml:space="preserve">16.297679901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4495239257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5890865325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.698751449585</t>
+    <t xml:space="preserve">16.2976818084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4495220184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5890846252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.698748588562</t>
   </si>
   <si>
     <t xml:space="preserve">16.0361766815186</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9686908721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3145523071289</t>
+    <t xml:space="preserve">15.9686918258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3145542144775</t>
   </si>
   <si>
     <t xml:space="preserve">15.9180784225464</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0193061828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5384712219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0154619216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1504306793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5300359725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8168497085571</t>
+    <t xml:space="preserve">16.0193023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5384731292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0154609680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1504316329956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5300369262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8168487548828</t>
   </si>
   <si>
     <t xml:space="preserve">15.5637807846069</t>
@@ -2942,10 +2942,10 @@
     <t xml:space="preserve">15.8843355178833</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1374015808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8674612045288</t>
+    <t xml:space="preserve">16.1374053955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8674621582031</t>
   </si>
   <si>
     <t xml:space="preserve">15.4541158676147</t>
@@ -2957,22 +2957,22 @@
     <t xml:space="preserve">15.0238981246948</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1673030853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4372425079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6312665939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4794225692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1588678359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7623929977417</t>
+    <t xml:space="preserve">15.1673040390015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4372444152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6312656402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4794216156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1588668823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7623920440674</t>
   </si>
   <si>
     <t xml:space="preserve">14.4080953598022</t>
@@ -2984,40 +2984,40 @@
     <t xml:space="preserve">14.0537977218628</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1212825775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4295587539673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5898361206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.142746925354</t>
+    <t xml:space="preserve">14.121283531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4295597076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5898370742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1427478790283</t>
   </si>
   <si>
     <t xml:space="preserve">12.7294006347656</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6028652191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9065494537354</t>
+    <t xml:space="preserve">12.6028642654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.906548500061</t>
   </si>
   <si>
     <t xml:space="preserve">13.3367681503296</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1258754730225</t>
+    <t xml:space="preserve">13.1258764266968</t>
   </si>
   <si>
     <t xml:space="preserve">13.5139169692993</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9188280105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.319896697998</t>
+    <t xml:space="preserve">13.9188270568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3198957443237</t>
   </si>
   <si>
     <t xml:space="preserve">13.5307884216309</t>
@@ -3029,7 +3029,7 @@
     <t xml:space="preserve">12.9318552017212</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7631435394287</t>
+    <t xml:space="preserve">12.7631425857544</t>
   </si>
   <si>
     <t xml:space="preserve">12.636607170105</t>
@@ -3038,13 +3038,13 @@
     <t xml:space="preserve">12.4172811508179</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4847650527954</t>
+    <t xml:space="preserve">12.484766960144</t>
   </si>
   <si>
     <t xml:space="preserve">12.6872224807739</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6619148254395</t>
+    <t xml:space="preserve">12.6619157791138</t>
   </si>
   <si>
     <t xml:space="preserve">12.7209644317627</t>
@@ -3062,22 +3062,22 @@
     <t xml:space="preserve">12.3497953414917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3666667938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.585994720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4126873016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3958158493042</t>
+    <t xml:space="preserve">12.3666658401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5859937667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4126882553101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3958168029785</t>
   </si>
   <si>
     <t xml:space="preserve">13.4464302062988</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7838573455811</t>
+    <t xml:space="preserve">13.7838563919067</t>
   </si>
   <si>
     <t xml:space="preserve">13.3114604949951</t>
@@ -3089,13 +3089,13 @@
     <t xml:space="preserve">12.9571619033813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0752620697021</t>
+    <t xml:space="preserve">13.0752630233765</t>
   </si>
   <si>
     <t xml:space="preserve">12.7040939331055</t>
   </si>
   <si>
-    <t xml:space="preserve">12.771577835083</t>
+    <t xml:space="preserve">12.7715797424316</t>
   </si>
   <si>
     <t xml:space="preserve">12.4004096984863</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">12.0461120605469</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8773984909058</t>
+    <t xml:space="preserve">11.8773994445801</t>
   </si>
   <si>
     <t xml:space="preserve">12.1473398208618</t>
@@ -3122,7 +3122,7 @@
     <t xml:space="preserve">12.4510231018066</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3835391998291</t>
+    <t xml:space="preserve">12.3835382461548</t>
   </si>
   <si>
     <t xml:space="preserve">12.2991819381714</t>
@@ -3140,19 +3140,19 @@
     <t xml:space="preserve">11.474102973938</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3693161010742</t>
+    <t xml:space="preserve">11.3693170547485</t>
   </si>
   <si>
     <t xml:space="preserve">11.8932485580444</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9107122421265</t>
+    <t xml:space="preserve">11.9107131958008</t>
   </si>
   <si>
     <t xml:space="preserve">12.4346437454224</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1028203964233</t>
+    <t xml:space="preserve">12.102819442749</t>
   </si>
   <si>
     <t xml:space="preserve">12.0154981613159</t>
@@ -3179,7 +3179,7 @@
     <t xml:space="preserve">11.4391746520996</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1946725845337</t>
+    <t xml:space="preserve">11.1946716308594</t>
   </si>
   <si>
     <t xml:space="preserve">11.7186040878296</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">11.8583192825317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7709970474243</t>
+    <t xml:space="preserve">11.7709980010986</t>
   </si>
   <si>
     <t xml:space="preserve">11.9631052017212</t>
@@ -3203,31 +3203,31 @@
     <t xml:space="preserve">11.7535333633423</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4915676116943</t>
+    <t xml:space="preserve">11.49156665802</t>
   </si>
   <si>
     <t xml:space="preserve">11.2645292282104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8104572296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0549573898315</t>
+    <t xml:space="preserve">10.8104562759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0549583435059</t>
   </si>
   <si>
     <t xml:space="preserve">11.1772079467773</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3867807388306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2470664978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0374927520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8453855514526</t>
+    <t xml:space="preserve">11.3867797851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2470655441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0374937057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8453845977783</t>
   </si>
   <si>
     <t xml:space="preserve">11.3343868255615</t>
@@ -3242,16 +3242,16 @@
     <t xml:space="preserve">11.2296009063721</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6138172149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.788462638855</t>
+    <t xml:space="preserve">11.6138181686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7884616851807</t>
   </si>
   <si>
     <t xml:space="preserve">11.8233909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">11.805926322937</t>
+    <t xml:space="preserve">11.8059272766113</t>
   </si>
   <si>
     <t xml:space="preserve">11.5614242553711</t>
@@ -3263,10 +3263,10 @@
     <t xml:space="preserve">11.5439605712891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4217100143433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1073503494263</t>
+    <t xml:space="preserve">11.4217090606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1073513031006</t>
   </si>
   <si>
     <t xml:space="preserve">11.0898857116699</t>
@@ -3275,25 +3275,25 @@
     <t xml:space="preserve">10.7231340408325</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6882047653198</t>
+    <t xml:space="preserve">10.6882057189941</t>
   </si>
   <si>
     <t xml:space="preserve">10.6707410812378</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5135622024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2865238189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.234130859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0594873428345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1468086242676</t>
+    <t xml:space="preserve">10.5135612487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.286524772644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2341318130493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0594882965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1468095779419</t>
   </si>
   <si>
     <t xml:space="preserve">9.78005695343018</t>
@@ -3305,22 +3305,22 @@
     <t xml:space="preserve">9.81498527526855</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76259231567383</t>
+    <t xml:space="preserve">9.76259326934814</t>
   </si>
   <si>
     <t xml:space="preserve">9.9896297454834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1992025375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29105472564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51809024810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22119617462158</t>
+    <t xml:space="preserve">10.1992034912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29105567932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51809120178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22119808197021</t>
   </si>
   <si>
     <t xml:space="preserve">9.25612640380859</t>
@@ -3332,13 +3332,13 @@
     <t xml:space="preserve">8.80205154418945</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81951522827148</t>
+    <t xml:space="preserve">8.8195161819458</t>
   </si>
   <si>
     <t xml:space="preserve">8.60121154785156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48769187927246</t>
+    <t xml:space="preserve">8.48769283294678</t>
   </si>
   <si>
     <t xml:space="preserve">8.19079780578613</t>
@@ -3347,13 +3347,13 @@
     <t xml:space="preserve">8.44403171539307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46149635314941</t>
+    <t xml:space="preserve">8.46149444580078</t>
   </si>
   <si>
     <t xml:space="preserve">8.3392448425293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56628322601318</t>
+    <t xml:space="preserve">8.56628227233887</t>
   </si>
   <si>
     <t xml:space="preserve">8.34797763824463</t>
@@ -3362,19 +3362,19 @@
     <t xml:space="preserve">8.54881763458252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59247875213623</t>
+    <t xml:space="preserve">8.59247970581055</t>
   </si>
   <si>
     <t xml:space="preserve">8.85444450378418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88937282562256</t>
+    <t xml:space="preserve">8.88937377929688</t>
   </si>
   <si>
     <t xml:space="preserve">9.04655265808105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01162433624268</t>
+    <t xml:space="preserve">9.01162338256836</t>
   </si>
   <si>
     <t xml:space="preserve">8.83697986602783</t>
@@ -3386,10 +3386,10 @@
     <t xml:space="preserve">9.02908897399902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0989465713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41330432891846</t>
+    <t xml:space="preserve">9.09894561767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41330528259277</t>
   </si>
   <si>
     <t xml:space="preserve">9.308518409729</t>
@@ -3407,52 +3407,52 @@
     <t xml:space="preserve">9.55301952362061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.622878074646</t>
+    <t xml:space="preserve">9.62287712097168</t>
   </si>
   <si>
     <t xml:space="preserve">9.91977214813232</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2690601348877</t>
+    <t xml:space="preserve">10.269061088562</t>
   </si>
   <si>
     <t xml:space="preserve">9.65780639648438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64034271240234</t>
+    <t xml:space="preserve">9.64034175872803</t>
   </si>
   <si>
     <t xml:space="preserve">9.67527103424072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8324499130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0420227050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69273567199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93723773956299</t>
+    <t xml:space="preserve">9.83245086669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0420236587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69273471832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93723678588867</t>
   </si>
   <si>
     <t xml:space="preserve">9.97216606140137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88484382629395</t>
+    <t xml:space="preserve">9.88484287261963</t>
   </si>
   <si>
     <t xml:space="preserve">9.8673791885376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0944156646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0769519805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79752063751221</t>
+    <t xml:space="preserve">10.0944166183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0769510269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79752159118652</t>
   </si>
   <si>
     <t xml:space="preserve">9.9547004699707</t>
@@ -3470,31 +3470,31 @@
     <t xml:space="preserve">10.6358118057251</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7405977249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7580623626709</t>
+    <t xml:space="preserve">10.7405986785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7580633163452</t>
   </si>
   <si>
     <t xml:space="preserve">10.9152431488037</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0200281143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3518524169922</t>
+    <t xml:space="preserve">11.0200290679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3518514633179</t>
   </si>
   <si>
     <t xml:space="preserve">11.0025644302368</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9676351547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5310258865356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6183481216431</t>
+    <t xml:space="preserve">10.9676361083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.53102684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6183471679688</t>
   </si>
   <si>
     <t xml:space="preserve">10.7056694030762</t>
@@ -3503,13 +3503,13 @@
     <t xml:space="preserve">10.6008834838867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5659551620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4786329269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1817388534546</t>
+    <t xml:space="preserve">10.565954208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4786319732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1817378997803</t>
   </si>
   <si>
     <t xml:space="preserve">10.216667175293</t>
@@ -3518,7 +3518,7 @@
     <t xml:space="preserve">10.0245580673218</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84991455078125</t>
+    <t xml:space="preserve">9.84991359710693</t>
   </si>
   <si>
     <t xml:space="preserve">10.1118803024292</t>
@@ -3536,13 +3536,13 @@
     <t xml:space="preserve">11.9456405639648</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7011384963989</t>
+    <t xml:space="preserve">11.7011394500732</t>
   </si>
   <si>
     <t xml:space="preserve">12.1202850341797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.399715423584</t>
+    <t xml:space="preserve">12.3997144699097</t>
   </si>
   <si>
     <t xml:space="preserve">11.9281768798828</t>
@@ -3557,22 +3557,22 @@
     <t xml:space="preserve">12.0329627990723</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4650430679321</t>
+    <t xml:space="preserve">13.4650440216064</t>
   </si>
   <si>
     <t xml:space="preserve">13.1681480407715</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0633630752563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8712539672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6442155838013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9491119384766</t>
+    <t xml:space="preserve">13.063362121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8712530136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6442165374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9491128921509</t>
   </si>
   <si>
     <t xml:space="preserve">13.0746583938599</t>
@@ -3581,13 +3581,13 @@
     <t xml:space="preserve">12.9132423400879</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0387878417969</t>
+    <t xml:space="preserve">13.0387887954712</t>
   </si>
   <si>
     <t xml:space="preserve">13.0567235946655</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1284637451172</t>
+    <t xml:space="preserve">13.1284627914429</t>
   </si>
   <si>
     <t xml:space="preserve">13.2540082931519</t>
@@ -3602,7 +3602,7 @@
     <t xml:space="preserve">13.5947751998901</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4871635437012</t>
+    <t xml:space="preserve">13.4871644973755</t>
   </si>
   <si>
     <t xml:space="preserve">13.4512939453125</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">13.5051002502441</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2002038955688</t>
+    <t xml:space="preserve">13.2002029418945</t>
   </si>
   <si>
     <t xml:space="preserve">12.9849824905396</t>
@@ -3650,7 +3650,7 @@
     <t xml:space="preserve">12.5366058349609</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4110612869263</t>
+    <t xml:space="preserve">12.411060333252</t>
   </si>
   <si>
     <t xml:space="preserve">12.2496452331543</t>
@@ -3677,7 +3677,7 @@
     <t xml:space="preserve">12.285514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2675809860229</t>
+    <t xml:space="preserve">12.2675800323486</t>
   </si>
   <si>
     <t xml:space="preserve">12.6262817382812</t>
@@ -3689,7 +3689,7 @@
     <t xml:space="preserve">12.5724763870239</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2137746810913</t>
+    <t xml:space="preserve">12.2137756347656</t>
   </si>
   <si>
     <t xml:space="preserve">12.5007352828979</t>
@@ -3701,10 +3701,10 @@
     <t xml:space="preserve">11.2990875244141</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5681133270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.639853477478</t>
+    <t xml:space="preserve">11.5681123733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6398525238037</t>
   </si>
   <si>
     <t xml:space="preserve">11.675724029541</t>
@@ -3716,22 +3716,22 @@
     <t xml:space="preserve">11.6577882766724</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4605026245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3708276748657</t>
+    <t xml:space="preserve">11.4605016708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.37082862854</t>
   </si>
   <si>
     <t xml:space="preserve">11.3528928756714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3349571228027</t>
+    <t xml:space="preserve">11.3349580764771</t>
   </si>
   <si>
     <t xml:space="preserve">11.2811527252197</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4963731765747</t>
+    <t xml:space="preserve">11.4963722229004</t>
   </si>
   <si>
     <t xml:space="preserve">11.5501775741577</t>
@@ -3746,16 +3746,16 @@
     <t xml:space="preserve">11.8012685775757</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7833347320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.908878326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9268140792847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.016489982605</t>
+    <t xml:space="preserve">11.7833337783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9088792800903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.926815032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0164890289307</t>
   </si>
   <si>
     <t xml:space="preserve">12.0882301330566</t>
@@ -3794,7 +3794,7 @@
     <t xml:space="preserve">10.5278797149658</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7610359191895</t>
+    <t xml:space="preserve">10.7610349655151</t>
   </si>
   <si>
     <t xml:space="preserve">10.5816850662231</t>
@@ -3809,7 +3809,7 @@
     <t xml:space="preserve">10.2947235107422</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3664636611938</t>
+    <t xml:space="preserve">10.3664646148682</t>
   </si>
   <si>
     <t xml:space="preserve">10.2229833602905</t>
@@ -3830,19 +3830,19 @@
     <t xml:space="preserve">9.86428260803223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68493175506592</t>
+    <t xml:space="preserve">9.68493270874023</t>
   </si>
   <si>
     <t xml:space="preserve">9.75667190551758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77460765838623</t>
+    <t xml:space="preserve">9.77460670471191</t>
   </si>
   <si>
     <t xml:space="preserve">9.70286750793457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79254245758057</t>
+    <t xml:space="preserve">9.79254150390625</t>
   </si>
   <si>
     <t xml:space="preserve">9.66699695587158</t>
@@ -3857,7 +3857,7 @@
     <t xml:space="preserve">10.0436325073242</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1871128082275</t>
+    <t xml:space="preserve">10.1871137619019</t>
   </si>
   <si>
     <t xml:space="preserve">10.5099449157715</t>
@@ -3866,7 +3866,7 @@
     <t xml:space="preserve">10.7431001663208</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8148403167725</t>
+    <t xml:space="preserve">10.8148412704468</t>
   </si>
   <si>
     <t xml:space="preserve">10.4740753173828</t>
@@ -3878,7 +3878,7 @@
     <t xml:space="preserve">9.9001522064209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95395851135254</t>
+    <t xml:space="preserve">9.95395755767822</t>
   </si>
   <si>
     <t xml:space="preserve">10.0795030593872</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">9.98982810974121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2588529586792</t>
+    <t xml:space="preserve">10.2588539123535</t>
   </si>
   <si>
     <t xml:space="preserve">10.3126592636108</t>
@@ -3902,7 +3902,7 @@
     <t xml:space="preserve">10.4561395645142</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3305940628052</t>
+    <t xml:space="preserve">10.3305950164795</t>
   </si>
   <si>
     <t xml:space="preserve">10.2050485610962</t>
@@ -3917,7 +3917,7 @@
     <t xml:space="preserve">9.91808795928955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88221836090088</t>
+    <t xml:space="preserve">9.88221740722656</t>
   </si>
   <si>
     <t xml:space="preserve">10.0974388122559</t>
@@ -3938,31 +3938,31 @@
     <t xml:space="preserve">9.3262300491333</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45177555084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5996198654175</t>
+    <t xml:space="preserve">9.4517765045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5996189117432</t>
   </si>
   <si>
     <t xml:space="preserve">9.93602275848389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4920091629028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5637493133545</t>
+    <t xml:space="preserve">10.4920101165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5637502670288</t>
   </si>
   <si>
     <t xml:space="preserve">10.4382047653198</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6713600158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9045162200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8327760696411</t>
+    <t xml:space="preserve">10.6713590621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9045152664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8327751159668</t>
   </si>
   <si>
     <t xml:space="preserve">10.7251653671265</t>
@@ -3977,7 +3977,7 @@
     <t xml:space="preserve">10.9224510192871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6892957687378</t>
+    <t xml:space="preserve">10.6892948150635</t>
   </si>
   <si>
     <t xml:space="preserve">11.2094125747681</t>

--- a/data/MARR.MI.xlsx
+++ b/data/MARR.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4479522705078</t>
+    <t xml:space="preserve">13.4479513168335</t>
   </si>
   <si>
     <t xml:space="preserve">MARR.MI</t>
@@ -47,19 +47,19 @@
     <t xml:space="preserve">13.289400100708</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1812992095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9939212799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9506797790527</t>
+    <t xml:space="preserve">13.1812982559204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9939222335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9506788253784</t>
   </si>
   <si>
     <t xml:space="preserve">12.5903367996216</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6552000045776</t>
+    <t xml:space="preserve">12.655198097229</t>
   </si>
   <si>
     <t xml:space="preserve">12.7344741821289</t>
@@ -68,100 +68,100 @@
     <t xml:space="preserve">12.4389944076538</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4462003707886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9849624633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.085862159729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6462430953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2155828475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8353681564331</t>
+    <t xml:space="preserve">12.4462022781372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9849615097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0858592987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6462421417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2155818939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8353710174561</t>
   </si>
   <si>
     <t xml:space="preserve">12.6768198013306</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5615110397339</t>
+    <t xml:space="preserve">12.5615100860596</t>
   </si>
   <si>
     <t xml:space="preserve">12.5543031692505</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6407861709595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7200603485107</t>
+    <t xml:space="preserve">12.6407871246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7200593948364</t>
   </si>
   <si>
     <t xml:space="preserve">12.9722986221313</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7777147293091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3308935165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.511061668396</t>
+    <t xml:space="preserve">12.7777156829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3308925628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5110635757446</t>
   </si>
   <si>
     <t xml:space="preserve">12.2948560714722</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4084167480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4516572952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8840675354004</t>
+    <t xml:space="preserve">11.4084157943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4516582489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.884069442749</t>
   </si>
   <si>
     <t xml:space="preserve">11.5885887145996</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8912744522095</t>
+    <t xml:space="preserve">11.8912763595581</t>
   </si>
   <si>
     <t xml:space="preserve">11.9273080825806</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0426177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2011690139771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3957548141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7056455612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6047515869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5759229660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9362668991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1596775054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9434700012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0731945037842</t>
+    <t xml:space="preserve">12.0426187515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2011680603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3957538604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7056465148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6047506332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5759248733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9362659454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1596765518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9434719085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0731935501099</t>
   </si>
   <si>
     <t xml:space="preserve">12.8858165740967</t>
@@ -170,34 +170,34 @@
     <t xml:space="preserve">12.5975437164307</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0786533355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3597202301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6696119308472</t>
+    <t xml:space="preserve">12.0786542892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3597192764282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6696128845215</t>
   </si>
   <si>
     <t xml:space="preserve">12.8137502670288</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6984395980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8714036941528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.453408241272</t>
+    <t xml:space="preserve">12.6984415054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8714027404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4534091949463</t>
   </si>
   <si>
     <t xml:space="preserve">12.3453054428101</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6840267181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7560949325562</t>
+    <t xml:space="preserve">12.6840257644653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7560958862305</t>
   </si>
   <si>
     <t xml:space="preserve">13.1524724960327</t>
@@ -206,37 +206,37 @@
     <t xml:space="preserve">13.2677803039551</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3326425552368</t>
+    <t xml:space="preserve">13.3326396942139</t>
   </si>
   <si>
     <t xml:space="preserve">13.0804014205933</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1885051727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.260573387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7073974609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4911918640137</t>
+    <t xml:space="preserve">13.1885061264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2605743408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7073984146118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.491189956665</t>
   </si>
   <si>
     <t xml:space="preserve">13.3470554351807</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0011281967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9002313613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8281621932983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7921276092529</t>
+    <t xml:space="preserve">13.001127243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9002304077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.828164100647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7921304702759</t>
   </si>
   <si>
     <t xml:space="preserve">13.058783531189</t>
@@ -248,31 +248,31 @@
     <t xml:space="preserve">12.8065423965454</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2821960449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1380567550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8425769805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8930244445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9074382781982</t>
+    <t xml:space="preserve">13.2821941375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1380577087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8425760269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8930253982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9074373245239</t>
   </si>
   <si>
     <t xml:space="preserve">13.0227479934692</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6624050140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8786106109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6335763931274</t>
+    <t xml:space="preserve">12.6624059677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8786125183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6335802078247</t>
   </si>
   <si>
     <t xml:space="preserve">12.7488889694214</t>
@@ -281,16 +281,16 @@
     <t xml:space="preserve">13.0258741378784</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0183887481689</t>
+    <t xml:space="preserve">13.0183906555176</t>
   </si>
   <si>
     <t xml:space="preserve">13.2579441070557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2504606246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4301280975342</t>
+    <t xml:space="preserve">13.2504596710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4301271438599</t>
   </si>
   <si>
     <t xml:space="preserve">13.4825286865234</t>
@@ -299,25 +299,25 @@
     <t xml:space="preserve">13.3103494644165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2654314041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4750442504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3702383041382</t>
+    <t xml:space="preserve">13.2654304504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4750423431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3702363967896</t>
   </si>
   <si>
     <t xml:space="preserve">13.2878904342651</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2729167938232</t>
+    <t xml:space="preserve">13.2729187011719</t>
   </si>
   <si>
     <t xml:space="preserve">13.280403137207</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8012933731079</t>
+    <t xml:space="preserve">12.8012914657593</t>
   </si>
   <si>
     <t xml:space="preserve">12.883638381958</t>
@@ -326,100 +326,100 @@
     <t xml:space="preserve">12.6141386032104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3146924972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.44944190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8087768554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7938060760498</t>
+    <t xml:space="preserve">12.3146915435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4494409561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8087787628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7938051223755</t>
   </si>
   <si>
     <t xml:space="preserve">13.0782775878906</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4419584274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7831764221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2847480773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7339153289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4226408004761</t>
+    <t xml:space="preserve">12.4419574737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7831773757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2847471237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7339143753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4226398468018</t>
   </si>
   <si>
     <t xml:space="preserve">13.5274457931519</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0558195114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4525833129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3328056335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7595157623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7295722961426</t>
+    <t xml:space="preserve">13.0558214187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4525842666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3328075408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7595167160034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7295703887939</t>
   </si>
   <si>
     <t xml:space="preserve">13.7220849990845</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5349311828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4900159835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7370576858521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0140428543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7071123123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8493499755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.111364364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9766149520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0814189910889</t>
+    <t xml:space="preserve">13.5349321365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4900169372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7370586395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0140438079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7071142196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8493480682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1113634109497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9766159057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0814199447632</t>
   </si>
   <si>
     <t xml:space="preserve">13.7445440292358</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9990730285645</t>
+    <t xml:space="preserve">13.9990739822388</t>
   </si>
   <si>
     <t xml:space="preserve">13.5049886703491</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6397371292114</t>
+    <t xml:space="preserve">13.6397380828857</t>
   </si>
   <si>
     <t xml:space="preserve">13.6621971130371</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6097946166992</t>
+    <t xml:space="preserve">13.6097936630249</t>
   </si>
   <si>
     <t xml:space="preserve">13.3477783203125</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">13.0857639312744</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1007375717163</t>
+    <t xml:space="preserve">13.100736618042</t>
   </si>
   <si>
     <t xml:space="preserve">13.0633058547974</t>
@@ -443,31 +443,31 @@
     <t xml:space="preserve">13.2354869842529</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1456527709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9285554885864</t>
+    <t xml:space="preserve">13.1456518173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9285564422607</t>
   </si>
   <si>
     <t xml:space="preserve">13.2055416107178</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1082220077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1980543136597</t>
+    <t xml:space="preserve">13.1082210540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.198055267334</t>
   </si>
   <si>
     <t xml:space="preserve">13.1157083511353</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0109024047852</t>
+    <t xml:space="preserve">13.0109014511108</t>
   </si>
   <si>
     <t xml:space="preserve">12.9135837554932</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8611812591553</t>
+    <t xml:space="preserve">12.8611822128296</t>
   </si>
   <si>
     <t xml:space="preserve">12.9435272216797</t>
@@ -476,22 +476,22 @@
     <t xml:space="preserve">13.1905727386475</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4076681137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3552656173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2130279541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3402938842773</t>
+    <t xml:space="preserve">13.4076671600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3552646636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2130270004272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.340292930603</t>
   </si>
   <si>
     <t xml:space="preserve">12.9659862518311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8761539459229</t>
+    <t xml:space="preserve">12.8761529922485</t>
   </si>
   <si>
     <t xml:space="preserve">12.8312349319458</t>
@@ -500,34 +500,37 @@
     <t xml:space="preserve">12.9809589385986</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7638607025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7114582061768</t>
+    <t xml:space="preserve">12.763858795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7114572525024</t>
   </si>
   <si>
     <t xml:space="preserve">12.8686666488647</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7563753128052</t>
+    <t xml:space="preserve">12.7563762664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7488899230957</t>
   </si>
   <si>
     <t xml:space="preserve">12.6815147399902</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5767059326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.546763420105</t>
+    <t xml:space="preserve">12.5767068862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5467643737793</t>
   </si>
   <si>
     <t xml:space="preserve">12.5317897796631</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5617370605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5542497634888</t>
+    <t xml:space="preserve">12.5617361068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5542488098145</t>
   </si>
   <si>
     <t xml:space="preserve">12.4194974899292</t>
@@ -548,7 +551,7 @@
     <t xml:space="preserve">11.9778165817261</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3596086502075</t>
+    <t xml:space="preserve">12.3596096038818</t>
   </si>
   <si>
     <t xml:space="preserve">12.4943599700928</t>
@@ -563,1858 +566,1855 @@
     <t xml:space="preserve">12.269775390625</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1649703979492</t>
+    <t xml:space="preserve">12.1649694442749</t>
   </si>
   <si>
     <t xml:space="preserve">12.2548027038574</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3371496200562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3221778869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7264289855957</t>
+    <t xml:space="preserve">12.3371505737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3221769332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7264308929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6740274429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7863178253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0932493209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9510135650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1306829452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9884462356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1381673812866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1606245040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.183084487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1681127548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2280006408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.00341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1755981445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4001817703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3852090835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8643226623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.91672706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5199584960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4450998306274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3627510070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4600706100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5124731063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4376134872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8268899917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6247673034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8044338226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7819747924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6996278762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8418645858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6771688461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8568353652954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7670021057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5648794174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.89426612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3359479904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5605344772339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5156173706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6952800750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9722709655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9348402023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9423265457153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.822548866272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2043399810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7133979797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.136962890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1594247817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2866888046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3615522384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2267999649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3465766906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6834545135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7208833694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5337314605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.458869934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1669101715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1968517303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5487022399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4214391708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6011047363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6460218429565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.735857963562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5861349105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9080362319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4245796203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1251373291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6984262466431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2823448181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.327262878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2598876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2673721313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5967617034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7839126586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6641368865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.521900177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4470367431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6416778564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0758743286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.798885345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7464866638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8737506866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9560947418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1058197021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3946361541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5069274902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6847534179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1950397491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1641139984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0094814300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7620716094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6306324005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8471183776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0249443054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9398975372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7698020935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9940185546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1254558563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9553604125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5455856323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7156829833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8548488616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7466068267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0404090881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7311458587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5378551483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5687808990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6229019165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7079486846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7234134674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1822032928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0894222259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0816898345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.159008026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9347906112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2363204956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0739612579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9966449737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3909549713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4914646148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8935070037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2414283752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0558700561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.28782081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2955513000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3960609436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8316555023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2800884246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7002182006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5533180236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4837322235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7775344848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5146579742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3832244873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3986854553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2749805450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2285900115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0584945678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9657173156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.950252532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0353012084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2827129364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4141483306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6074371337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5919742584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.932165145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0481395721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2646236419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9476261138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0713348388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0636005401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.079065322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2723560333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3032836914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3728656768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3187446594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5584259033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5893497467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4656448364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7207851409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5738849639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5429611206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6975917816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.107364654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0377807617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6125431060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.68212890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5197620391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3110122680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.109992980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3574028015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1795749664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1409168243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0867977142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8857746124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6151695251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.530122756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3522968292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0430316925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.826548576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9270601272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1976642608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6692905426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8703136444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7852630615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9630908966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8084602355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9244327545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4218807220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0507640838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4605407714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.452808380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7543411254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6383666992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7929973602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4064140319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3342094421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3805961608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4888381958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5506916046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6898593902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4115238189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6434707641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.256893157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2259674072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.504301071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4991970062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9785537719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3445644378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2981758117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9012393951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6538276672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2672519683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3136367797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4269866943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4475574493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3857040405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8805255889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1433982849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0042285919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.911449432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6949653625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6795043945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7413539886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6640377044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7877445220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2516403198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4371967315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3444175720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4062728881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5609035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3289585113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1743221282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1124706268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.158863067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2825660705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.236177444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.205249786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2671031951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5299797058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6382179260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5918312072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4835891723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5145149230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4526615142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6072940826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1382904052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3547763824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0764389038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.03005027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1737804412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9502010345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3654193878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.205717086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6209373474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5091457366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.588996887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.557056427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4931774139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1578102111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4292964935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6848163604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6369075775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4133281707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.461238861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3175086975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8064708709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8224411010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7106533050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9182605743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9661693572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8863220214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9981098175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3973598480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5251197814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4452686309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1479473114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1639156341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0201873779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8604869842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7806358337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5730285644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0680961608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7646656036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4772052764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7007865905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2437648773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4513740539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4992847442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2118244171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1319751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0042152404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1160087585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0361576080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1798858642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.323616027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3395843505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3076457977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7228622436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.467342376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3874969482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5631637573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8825607299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3616600036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4415092468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2658386230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7609081268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0962772369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8247890472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.249870300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4734477996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1540508270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1700210571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7548027038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5312232971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4034633636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8125762939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7327270507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3813896179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2536296844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9342288970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3494472503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9243659973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7486953735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1258716583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7905025482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4391632080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1357345581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2155838012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9760360717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.550952911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8961868286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0718536376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9281272888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8323059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.05588722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1836452484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4551334381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8163375854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3532066345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9858989715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0976886749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1136589050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4269514083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3311328887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6505327224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4748592376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4429216384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7703056335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.842170715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7383651733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4490261077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2733554840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1615695953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.321268081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4809665679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6246967315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.768424987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1676750183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3433418273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2794628143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9440956115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0079746246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6406669616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2414169311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5608158111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7045459747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8482761383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3752841949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1037940979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8802165985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9121570587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8642463684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.720516204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6885757446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6087265014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7364864349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3052978515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8980665206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.193510055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2094764709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3851470947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2893257141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2573871612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2254467010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9140338897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.417085647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5288753509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7843971252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5767860412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.369176864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1775379180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4889507293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2494029998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.329252243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4091014862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1695537567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0497779846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5688018798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6486530303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2874488830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0878257751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0479030609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8083515167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9680519104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7285022735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8882007598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1277523040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8793506622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0452404022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9208240509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7964038848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2111301422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1281852722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1696605682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.418493270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3770217895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4599647521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2940769195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9622974395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7549324035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6305141448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3402061462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4895057678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5392742156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7088012695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6673278808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5014400482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.542911529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2526035308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7134571075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4231510162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.373384475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2406711578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.17431640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2738513946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1245498657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3070259094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8591241836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7264099121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7927675247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0747814178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5273418426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4278087615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6600551605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1789722442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3614521026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6932325363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6102886199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4609851837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4443998336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3780422210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2950963973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9254817962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2904376983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3899726867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4397392272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6719856262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9576358795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0867137908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3355464935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8378753662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5890407562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2572612762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8757133483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9088916778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1577243804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1411361694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4729175567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7595872879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.676643371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5936975479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.477575302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7429990768433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7098236083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8425340652466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3567943572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3236179351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.975248336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5843849182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0037689208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2240829467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0084247589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1909065246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5558624267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.532000541687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7974262237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1836309432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9347944259644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6361923217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4371242523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2712335586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3873567581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7616310119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9606990814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4251918792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0317115783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4796171188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1690826416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3681507110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95342445373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3183841705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8777532577515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4417810440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8565073013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1763563156128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2924795150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2141923904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9155893325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6667528152466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.202260017395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.451096534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5174531936646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5340414047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4013290405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1524925231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0529584884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97001457214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4676847457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6999311447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3017950057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0695486068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2520275115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.003191947937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0363712310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1193151473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92024612426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4557523727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50552082061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32304096221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14056301116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07420539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6879997253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1359052658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70458889007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38939762115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4345064163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2188491821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4179182052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9985342025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8990001678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9819450378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8160552978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8824110031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8113975524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7782182693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.595739364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3634939193726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6833438873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9487676620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9653558731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2639598846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2805490493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1810140609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3303155899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2971382141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0814790725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0151233673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0648899078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8326444625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8492336273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5838098526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3847408294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6501655578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2354383468628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9321775436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5506324768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5008640289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6169872283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4842758178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0197801589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3349723815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7828779220581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6003980636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1312465667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4132614135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4298496246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2307806015015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8658218383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3137273788452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.396671295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5127954483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8611650466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2095346450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9772872924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0602331161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2593021392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3800830841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1146564483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6335754394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2686166763306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55528736114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62164402008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65482139587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60505485534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75435543060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.491548538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0058088302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1929454803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8399171829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3210000991821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4086027145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2758903503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7237958908081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9062747955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1053428649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.989218711853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0721645355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0223970413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.088752746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0389862060547</t>
   </si>
   <si>
     <t xml:space="preserve">12.6740283966064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7863178253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0932493209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9510135650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1306819915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9884452819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1381664276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1606254577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1830854415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1681127548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2280006408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.00341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1755962371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4001817703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3852090835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8643226623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9167251586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5199604034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4450988769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3627510070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4600715637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5124759674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4376134872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8268909454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6247663497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8044338226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7819747924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6996278762817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8418626785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6771688461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8568353652954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7670021057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5648765563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8942651748657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3359489440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5605344772339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5156164169312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6952810287476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9722700119019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9348402023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.942325592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8225479125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2043399810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.713397026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1369647979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.159423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2866878509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3615522384644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2267990112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3465785980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6834545135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7208862304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5337314605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4588680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1669092178345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1968545913696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5487041473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4214382171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6011075973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6460208892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7358560562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5861330032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9080381393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4245796203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1251354217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6984252929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2823448181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.327262878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2598857879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2673721313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5967597961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.78391456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.664134979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5219020843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4470386505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6416797637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.075870513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.798885345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7464866638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8737487792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9560947418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1058197021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3946380615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5069274902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6847534179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1950397491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1641120910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0094814300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7620716094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6306343078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8471183776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0249443054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9398937225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7698040008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9940204620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1254558563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.955358505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5455856323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7156829833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8548488616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7466068267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0404071807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.731143951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5378551483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5687808990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6229019165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.707950592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7234134674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1822032928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0894203186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0816898345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1590061187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9347906112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2363243103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0739593505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9966430664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3909549713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4914627075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8935070037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2414283752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.055871963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2878227233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2955493927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3960609436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.831657409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.280086517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7002182006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5533180236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4837341308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7775344848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5146598815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3832225799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3986854553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2749805450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2285919189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0584964752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9657173156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.950252532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0353012084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2827110290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4141502380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6074390411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5919742584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9321632385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0481376647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2646255493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9476261138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0713329315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0636024475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.079065322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2723579406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.303279876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3728618621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3187446594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5584239959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5893497467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4656410217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7207870483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5738868713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5429630279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6975936889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1073665618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0377788543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6125431060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6821308135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5197620391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3110103607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1099910736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3574047088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1795749664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1409187316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0867977142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8857727050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6151676177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.530122756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.352294921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0430335998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8265466690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9270582199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1976642608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6692905426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8703117370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7852649688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9630908966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8084602355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9244327545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4218807220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0507659912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4605407714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.452808380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7543392181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6383628845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7929954528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4064159393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3342094421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3805980682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4888381958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5506916046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6898593902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4115257263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6434688568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.256893157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2259654998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.504301071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.499195098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9785537719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3445625305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2981758117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9012393951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6538276672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2672500610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3136386871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4269886016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4475574493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.385705947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8805236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1433982849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0042285919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.911449432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6949653625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6795024871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7413558959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.664041519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7877445220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2516384124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4371948242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3444156646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.406270980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5609035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3289585113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1743240356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1124706268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1588592529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2825660705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.236177444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.205249786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2671031951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5299758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6382179260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5918312072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4835891723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5145149230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4526615142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6072959899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1382923126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3547763824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0764389038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0300483703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1737785339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9502029418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3654193878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2057189941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6209373474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.509147644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5889987945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5570583343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4931793212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.157808303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4292984008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6848182678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6369094848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4133262634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.461238861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3175067901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8064727783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8224411010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7106552124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9182624816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9661712646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.03005027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8863220214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9981117248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3973617553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5251197814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4452667236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1479454040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1639137268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0201873779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8604869842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7806377410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5730285644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.06809425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7646675109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4772052764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7007884979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.243766784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4513740539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4992847442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2118263244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1319751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0042133331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1160087585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0361557006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1798877716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3236141204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3395824432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3076438903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7228622436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.467342376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3874950408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5631637573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8825588226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3616600036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4415092468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2658386230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7609062194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0962772369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8247852325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2498741149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4734477996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.154052734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1700191497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7548007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5312232971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4034633636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8125782012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7327270507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3813877105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2536296844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9342308044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3494472503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9243679046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7486953735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1258697509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7905025482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4391613006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1357326507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2155838012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9760360717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.550952911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.896183013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0718536376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9281253814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8323059082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0558853149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1836433410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4551334381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8163356781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3532066345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9859008789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0976905822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1136589050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4269523620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3311328887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6505317687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4748592376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4429225921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7703056335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8421688079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7383651733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4490261077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2733573913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1615695953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.321268081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4809665679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6246948242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7684268951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1676731109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3433418273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2794628143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9440937042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0079746246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6406669616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.241418838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5608158111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7045478820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8482761383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.375280380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1037940979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8802146911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9121551513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8642463684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.720516204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6885738372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6087265014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7364864349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3052978515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8980646133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.193510055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2094764709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3851490020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2893295288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2573890686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2254486083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9140357971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4170875549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5288791656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7843952178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.576789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3691787719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1775379180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4889507293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2494010925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.329252243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4091014862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1695537567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0497779846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5688018798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6486530303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2874507904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0878238677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0479011535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8083515167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9680480957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7285003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8882007598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1277503967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8793506622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0452404022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9208240509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7964038848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2111301422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1281852722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1696605682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.418493270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3770198822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4599666595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2940769195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9622955322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7549324035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6305141448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3402080535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4895057678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5392742156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7088031768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.667329788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5014381408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5429096221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2526016235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7134590148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4231510162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3733825683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2406711578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1743144989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2738494873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1245498657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3070278167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8591241836548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7264108657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7927675247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.074779510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5273418426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.427809715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6600532531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.178973197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3614521026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6932334899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6102886199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4609861373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4444007873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3780431747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2950973510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.925479888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2904396057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3899726867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4397392272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6719856262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9576377868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0867118835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3355464935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8378753662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5890407562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2572612762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.87571144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9088916778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1577281951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1411361694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4729175567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7595891952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6766424179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5936994552612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.477575302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7429990768433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7098217010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8425340652466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3567943572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3236179351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9752464294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5843849182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0037689208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2240810394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0084247589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1909065246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5558624267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5320014953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7974252700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1836309432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9347944259644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6361923217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4371252059937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2712335586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3873558044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7616310119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9607000350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4251918792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0317134857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4796161651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1690816879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3681516647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95342445373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3183832168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8777532577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.441780090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8565082550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1763563156128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2924785614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2141923904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9155883789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6667537689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2022609710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4510955810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5174541473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5340414047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.401328086853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1524934768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0529594421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97001457214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4676856994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6999311447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.301794052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0695486068726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2520265579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0031929016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0363702774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1193151473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92024707794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45575428009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50552082061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32304191589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14056205749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07420444488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68800067901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1359052658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38939762115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4345073699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2188501358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4179191589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9985342025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8990001678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9819450378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8160543441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8824110031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8113975524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7782182693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.595739364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3634929656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6833419799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9487676620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9653558731079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2639589309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2805490493774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1810150146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3303155899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2971382141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0814800262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0151233673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0648899078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8326435089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.849232673645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5838088989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3847398757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6501655578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3515615463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2354383468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9321784973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.550630569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5008640289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6169862747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4842748641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0197801589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3349723815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7828769683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6003971099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1312465667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4132604598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4298486709595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2307825088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8658227920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3137273788452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.396671295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5127944946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8611650466919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2095336914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9772882461548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0602340698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2593011856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3800830841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1146564483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6335754394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2686176300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55528926849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62164497375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65482234954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.605055809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75435733795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.491548538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0058088302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1929454803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.839919090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3210000991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4086027145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2758913040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7237949371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9062738418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1053419113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9892196655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0721645355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0223960876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0887537002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0389862060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6740274429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4583702087402</t>
+    <t xml:space="preserve">12.4583711624146</t>
   </si>
   <si>
     <t xml:space="preserve">12.5081377029419</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">12.7403831481934</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3754243850708</t>
+    <t xml:space="preserve">12.3754253387451</t>
   </si>
   <si>
     <t xml:space="preserve">12.4749593734741</t>
@@ -2432,10 +2432,10 @@
     <t xml:space="preserve">12.6574392318726</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9560403823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9228630065918</t>
+    <t xml:space="preserve">12.9560413360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9228639602661</t>
   </si>
   <si>
     <t xml:space="preserve">13.536657333374</t>
@@ -2450,58 +2450,58 @@
     <t xml:space="preserve">14.5817680358887</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6978912353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7642459869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6315336227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1006860733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.432466506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7808351516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7476577758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4988212585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3495197296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2499876022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2333974838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7854928970337</t>
+    <t xml:space="preserve">14.6978921890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7642469406128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.631534576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1006851196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4324655532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7808361053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7476596832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4988231658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3495187759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2499866485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.785493850708</t>
   </si>
   <si>
     <t xml:space="preserve">14.0177402496338</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0509185791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2831649780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0462598800659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9301357269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3946304321289</t>
+    <t xml:space="preserve">14.0509195327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2831630706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0462608337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.930136680603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3946294784546</t>
   </si>
   <si>
     <t xml:space="preserve">15.3448648452759</t>
@@ -2510,25 +2510,25 @@
     <t xml:space="preserve">15.9918384552002</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8969583511353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9799041748047</t>
+    <t xml:space="preserve">14.8969573974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.979905128479</t>
   </si>
   <si>
     <t xml:space="preserve">14.9135475158691</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9964933395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.825945854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6434679031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0250148773193</t>
+    <t xml:space="preserve">14.9964923858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8259439468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6434659957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0250129699707</t>
   </si>
   <si>
     <t xml:space="preserve">16.0913696289062</t>
@@ -2537,13 +2537,13 @@
     <t xml:space="preserve">16.0581932067871</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5605211257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0130834579468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2619171142578</t>
+    <t xml:space="preserve">15.5605201721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0130825042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2619190216064</t>
   </si>
   <si>
     <t xml:space="preserve">15.2287406921387</t>
@@ -2552,40 +2552,40 @@
     <t xml:space="preserve">15.1457958221436</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4941654205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6268758773804</t>
+    <t xml:space="preserve">15.4941644668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6268768310547</t>
   </si>
   <si>
     <t xml:space="preserve">15.2121515274048</t>
   </si>
   <si>
-    <t xml:space="preserve">15.502459526062</t>
+    <t xml:space="preserve">15.5024604797363</t>
   </si>
   <si>
     <t xml:space="preserve">15.2702131271362</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2536249160767</t>
+    <t xml:space="preserve">15.2536239624023</t>
   </si>
   <si>
     <t xml:space="preserve">15.5439329147339</t>
   </si>
   <si>
-    <t xml:space="preserve">15.577112197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8508291244507</t>
+    <t xml:space="preserve">15.5771102905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8508310317993</t>
   </si>
   <si>
     <t xml:space="preserve">15.7181177139282</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7347059249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8840065002441</t>
+    <t xml:space="preserve">15.7347040176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8840045928955</t>
   </si>
   <si>
     <t xml:space="preserve">15.7512941360474</t>
@@ -2594,43 +2594,43 @@
     <t xml:space="preserve">15.4361038208008</t>
   </si>
   <si>
-    <t xml:space="preserve">16.398265838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5807476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8674192428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0830764770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1079597473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4646244049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6222190856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8212871551514</t>
+    <t xml:space="preserve">16.3982677459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5807456970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8674182891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0830726623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1079578399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4646224975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.622220993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8212890625</t>
   </si>
   <si>
     <t xml:space="preserve">16.7051639556885</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9042339324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9374122619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1364803314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3023700714111</t>
+    <t xml:space="preserve">16.9042358398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9374103546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1364784240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3023738861084</t>
   </si>
   <si>
     <t xml:space="preserve">17.4350833892822</t>
@@ -2639,7 +2639,7 @@
     <t xml:space="preserve">17.4516735076904</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2194271087646</t>
+    <t xml:space="preserve">17.219425201416</t>
   </si>
   <si>
     <t xml:space="preserve">16.7217540740967</t>
@@ -2657,19 +2657,19 @@
     <t xml:space="preserve">16.8876457214355</t>
   </si>
   <si>
-    <t xml:space="preserve">16.771520614624</t>
+    <t xml:space="preserve">16.7715187072754</t>
   </si>
   <si>
     <t xml:space="preserve">16.8544654846191</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2028350830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1033039093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1198902130127</t>
+    <t xml:space="preserve">17.2028369903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1033058166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1198921203613</t>
   </si>
   <si>
     <t xml:space="preserve">16.7383422851562</t>
@@ -2684,13 +2684,13 @@
     <t xml:space="preserve">16.8710556030273</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9171848297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2074947357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2323760986328</t>
+    <t xml:space="preserve">15.9171867370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2074928283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2323780059814</t>
   </si>
   <si>
     <t xml:space="preserve">16.6056308746338</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">18.1649990081787</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6175632476807</t>
+    <t xml:space="preserve">17.617561340332</t>
   </si>
   <si>
     <t xml:space="preserve">18.0820541381836</t>
@@ -2720,7 +2720,7 @@
     <t xml:space="preserve">17.4019031524658</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3189601898193</t>
+    <t xml:space="preserve">17.3189582824707</t>
   </si>
   <si>
     <t xml:space="preserve">17.0203590393066</t>
@@ -2735,49 +2735,49 @@
     <t xml:space="preserve">17.1862468719482</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4065628051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4148578643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.049898147583</t>
+    <t xml:space="preserve">16.4065608978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4148559570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0499000549316</t>
   </si>
   <si>
     <t xml:space="preserve">16.1660213470459</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5346164703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.070125579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2360134124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6839179992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4848518371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2762145996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2424736022949</t>
+    <t xml:space="preserve">17.5346145629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0701236724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2360153198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6839160919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4848499298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.276216506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2424755096436</t>
   </si>
   <si>
     <t xml:space="preserve">17.3437023162842</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5461559295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4111862182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3774433135986</t>
+    <t xml:space="preserve">17.5461578369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4111881256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3774452209473</t>
   </si>
   <si>
     <t xml:space="preserve">17.6642589569092</t>
@@ -2801,7 +2801,7 @@
     <t xml:space="preserve">16.9556617736816</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8628711700439</t>
+    <t xml:space="preserve">16.8628692626953</t>
   </si>
   <si>
     <t xml:space="preserve">17.090633392334</t>
@@ -2816,28 +2816,28 @@
     <t xml:space="preserve">17.2087326049805</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2048892974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0952262878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1458377838135</t>
+    <t xml:space="preserve">16.2048873901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0952243804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1458396911621</t>
   </si>
   <si>
     <t xml:space="preserve">15.7915410995483</t>
   </si>
   <si>
-    <t xml:space="preserve">15.690315246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8590278625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4119396209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5215997695923</t>
+    <t xml:space="preserve">15.6903142929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8590259552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4119367599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5216016769409</t>
   </si>
   <si>
     <t xml:space="preserve">15.0998191833496</t>
@@ -2849,19 +2849,19 @@
     <t xml:space="preserve">15.6059589385986</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5806512832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.833722114563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0446109771729</t>
+    <t xml:space="preserve">15.5806503295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8337211608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0446128845215</t>
   </si>
   <si>
     <t xml:space="preserve">15.8758993148804</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8927688598633</t>
+    <t xml:space="preserve">15.8927698135376</t>
   </si>
   <si>
     <t xml:space="preserve">16.0108680725098</t>
@@ -2870,118 +2870,118 @@
     <t xml:space="preserve">15.9349479675293</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7662353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7746715545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5131664276123</t>
+    <t xml:space="preserve">15.7662363052368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7746725082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.513165473938</t>
   </si>
   <si>
     <t xml:space="preserve">15.4878587722778</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1841735839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2347888946533</t>
+    <t xml:space="preserve">15.1841745376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2347898483276</t>
   </si>
   <si>
     <t xml:space="preserve">15.3950662612915</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9433822631836</t>
+    <t xml:space="preserve">15.9433832168579</t>
   </si>
   <si>
     <t xml:space="preserve">16.112096786499</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2976818084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4495220184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5890846252441</t>
+    <t xml:space="preserve">16.297679901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4495239257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5890855789185</t>
   </si>
   <si>
     <t xml:space="preserve">15.6987504959106</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0361766815186</t>
+    <t xml:space="preserve">16.0361785888672</t>
   </si>
   <si>
     <t xml:space="preserve">15.9686918258667</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3145542144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9180765151978</t>
+    <t xml:space="preserve">16.3145523071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9180784225464</t>
   </si>
   <si>
     <t xml:space="preserve">16.0193042755127</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5384740829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0154609680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1504316329956</t>
+    <t xml:space="preserve">15.5384721755981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0154619216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1504306793213</t>
   </si>
   <si>
     <t xml:space="preserve">15.5300369262695</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8168487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5637807846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8843336105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1374053955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8674640655518</t>
+    <t xml:space="preserve">15.8168478012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5637788772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8843326568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1374034881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8674612045288</t>
   </si>
   <si>
     <t xml:space="preserve">15.4541149139404</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9732856750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0238971710205</t>
+    <t xml:space="preserve">14.9732847213745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0238962173462</t>
   </si>
   <si>
     <t xml:space="preserve">15.1673030853271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4372453689575</t>
+    <t xml:space="preserve">15.4372434616089</t>
   </si>
   <si>
     <t xml:space="preserve">15.6312656402588</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4794235229492</t>
+    <t xml:space="preserve">15.4794216156006</t>
   </si>
   <si>
     <t xml:space="preserve">15.1588659286499</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7623920440674</t>
+    <t xml:space="preserve">14.7623929977417</t>
   </si>
   <si>
     <t xml:space="preserve">14.4080944061279</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7416791915894</t>
+    <t xml:space="preserve">13.7416801452637</t>
   </si>
   <si>
     <t xml:space="preserve">14.0537977218628</t>
@@ -2993,34 +2993,34 @@
     <t xml:space="preserve">13.4295587539673</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5898370742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.142746925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7294006347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6028642654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.906548500061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3367681503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1258754730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5139169692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9188270568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3198957443237</t>
+    <t xml:space="preserve">13.5898380279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1427478790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7293996810913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6028652191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9065494537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3367671966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1258764266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.513916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9188289642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.319896697998</t>
   </si>
   <si>
     <t xml:space="preserve">13.5307874679565</t>
@@ -3032,16 +3032,16 @@
     <t xml:space="preserve">12.9318552017212</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7631425857544</t>
+    <t xml:space="preserve">12.7631435394287</t>
   </si>
   <si>
     <t xml:space="preserve">12.6366081237793</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4172801971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.484766960144</t>
+    <t xml:space="preserve">12.4172811508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4847660064697</t>
   </si>
   <si>
     <t xml:space="preserve">12.6872224807739</t>
@@ -3053,7 +3053,7 @@
     <t xml:space="preserve">12.7209644317627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4678945541382</t>
+    <t xml:space="preserve">12.4678955078125</t>
   </si>
   <si>
     <t xml:space="preserve">12.1304683685303</t>
@@ -3065,25 +3065,25 @@
     <t xml:space="preserve">12.3497953414917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3666658401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5859937667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4126873016357</t>
+    <t xml:space="preserve">12.3666667938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.585994720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4126882553101</t>
   </si>
   <si>
     <t xml:space="preserve">13.3958168029785</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4464311599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7838563919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3114604949951</t>
+    <t xml:space="preserve">13.4464302062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7838573455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3114595413208</t>
   </si>
   <si>
     <t xml:space="preserve">13.2271041870117</t>
@@ -3092,13 +3092,13 @@
     <t xml:space="preserve">12.9571619033813</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0752630233765</t>
+    <t xml:space="preserve">13.0752620697021</t>
   </si>
   <si>
     <t xml:space="preserve">12.7040939331055</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7715797424316</t>
+    <t xml:space="preserve">12.7715787887573</t>
   </si>
   <si>
     <t xml:space="preserve">12.4004096984863</t>
@@ -3110,13 +3110,13 @@
     <t xml:space="preserve">12.0461120605469</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8773994445801</t>
+    <t xml:space="preserve">11.8773984909058</t>
   </si>
   <si>
     <t xml:space="preserve">12.1473398208618</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1642122268677</t>
+    <t xml:space="preserve">12.1642112731934</t>
   </si>
   <si>
     <t xml:space="preserve">12.2316961288452</t>
@@ -3128,13 +3128,13 @@
     <t xml:space="preserve">12.3835382461548</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2991819381714</t>
+    <t xml:space="preserve">12.2991809844971</t>
   </si>
   <si>
     <t xml:space="preserve">11.8267850875854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6749429702759</t>
+    <t xml:space="preserve">11.6749439239502</t>
   </si>
   <si>
     <t xml:space="preserve">11.6487464904785</t>
@@ -3143,19 +3143,19 @@
     <t xml:space="preserve">11.474102973938</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3693170547485</t>
+    <t xml:space="preserve">11.3693161010742</t>
   </si>
   <si>
     <t xml:space="preserve">11.8932485580444</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9107131958008</t>
+    <t xml:space="preserve">11.9107122421265</t>
   </si>
   <si>
     <t xml:space="preserve">12.4346437454224</t>
   </si>
   <si>
-    <t xml:space="preserve">12.102819442749</t>
+    <t xml:space="preserve">12.1028203964233</t>
   </si>
   <si>
     <t xml:space="preserve">12.0154981613159</t>
@@ -3182,7 +3182,7 @@
     <t xml:space="preserve">11.4391746520996</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1946716308594</t>
+    <t xml:space="preserve">11.1946725845337</t>
   </si>
   <si>
     <t xml:space="preserve">11.7186040878296</t>
@@ -3197,7 +3197,7 @@
     <t xml:space="preserve">11.8583192825317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7709980010986</t>
+    <t xml:space="preserve">11.7709970474243</t>
   </si>
   <si>
     <t xml:space="preserve">11.9631052017212</t>
@@ -3206,31 +3206,31 @@
     <t xml:space="preserve">11.7535333633423</t>
   </si>
   <si>
-    <t xml:space="preserve">11.49156665802</t>
+    <t xml:space="preserve">11.4915676116943</t>
   </si>
   <si>
     <t xml:space="preserve">11.2645292282104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8104562759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0549583435059</t>
+    <t xml:space="preserve">10.8104572296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0549573898315</t>
   </si>
   <si>
     <t xml:space="preserve">11.1772079467773</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3867797851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2470655441284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0374937057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8453845977783</t>
+    <t xml:space="preserve">11.3867807388306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2470664978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0374927520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8453855514526</t>
   </si>
   <si>
     <t xml:space="preserve">11.3343868255615</t>
@@ -3245,16 +3245,16 @@
     <t xml:space="preserve">11.2296009063721</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6138181686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7884616851807</t>
+    <t xml:space="preserve">11.6138172149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.788462638855</t>
   </si>
   <si>
     <t xml:space="preserve">11.8233909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8059272766113</t>
+    <t xml:space="preserve">11.805926322937</t>
   </si>
   <si>
     <t xml:space="preserve">11.5614242553711</t>
@@ -3266,10 +3266,10 @@
     <t xml:space="preserve">11.5439605712891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4217090606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1073513031006</t>
+    <t xml:space="preserve">11.4217100143433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1073503494263</t>
   </si>
   <si>
     <t xml:space="preserve">11.0898857116699</t>
@@ -3278,25 +3278,25 @@
     <t xml:space="preserve">10.7231340408325</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6882057189941</t>
+    <t xml:space="preserve">10.6882047653198</t>
   </si>
   <si>
     <t xml:space="preserve">10.6707410812378</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5135612487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.286524772644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2341318130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0594882965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1468095779419</t>
+    <t xml:space="preserve">10.5135622024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2865238189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.234130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0594873428345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1468086242676</t>
   </si>
   <si>
     <t xml:space="preserve">9.78005695343018</t>
@@ -3308,22 +3308,22 @@
     <t xml:space="preserve">9.81498527526855</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76259326934814</t>
+    <t xml:space="preserve">9.76259231567383</t>
   </si>
   <si>
     <t xml:space="preserve">9.9896297454834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1992034912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29105567932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51809120178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22119808197021</t>
+    <t xml:space="preserve">10.1992025375366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29105472564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51809024810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22119617462158</t>
   </si>
   <si>
     <t xml:space="preserve">9.25612640380859</t>
@@ -3335,13 +3335,13 @@
     <t xml:space="preserve">8.80205154418945</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8195161819458</t>
+    <t xml:space="preserve">8.81951522827148</t>
   </si>
   <si>
     <t xml:space="preserve">8.60121154785156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48769283294678</t>
+    <t xml:space="preserve">8.48769187927246</t>
   </si>
   <si>
     <t xml:space="preserve">8.19079780578613</t>
@@ -3350,13 +3350,13 @@
     <t xml:space="preserve">8.44403171539307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46149444580078</t>
+    <t xml:space="preserve">8.46149635314941</t>
   </si>
   <si>
     <t xml:space="preserve">8.3392448425293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56628227233887</t>
+    <t xml:space="preserve">8.56628322601318</t>
   </si>
   <si>
     <t xml:space="preserve">8.34797763824463</t>
@@ -3365,19 +3365,19 @@
     <t xml:space="preserve">8.54881763458252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59247970581055</t>
+    <t xml:space="preserve">8.59247875213623</t>
   </si>
   <si>
     <t xml:space="preserve">8.85444450378418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88937377929688</t>
+    <t xml:space="preserve">8.88937282562256</t>
   </si>
   <si>
     <t xml:space="preserve">9.04655265808105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01162338256836</t>
+    <t xml:space="preserve">9.01162433624268</t>
   </si>
   <si>
     <t xml:space="preserve">8.83697986602783</t>
@@ -3389,10 +3389,10 @@
     <t xml:space="preserve">9.02908897399902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09894561767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41330528259277</t>
+    <t xml:space="preserve">9.0989465713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41330432891846</t>
   </si>
   <si>
     <t xml:space="preserve">9.308518409729</t>
@@ -3410,52 +3410,52 @@
     <t xml:space="preserve">9.55301952362061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62287712097168</t>
+    <t xml:space="preserve">9.622878074646</t>
   </si>
   <si>
     <t xml:space="preserve">9.91977214813232</t>
   </si>
   <si>
-    <t xml:space="preserve">10.269061088562</t>
+    <t xml:space="preserve">10.2690601348877</t>
   </si>
   <si>
     <t xml:space="preserve">9.65780639648438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64034175872803</t>
+    <t xml:space="preserve">9.64034271240234</t>
   </si>
   <si>
     <t xml:space="preserve">9.67527103424072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83245086669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0420236587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69273471832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93723678588867</t>
+    <t xml:space="preserve">9.8324499130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0420227050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69273567199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93723773956299</t>
   </si>
   <si>
     <t xml:space="preserve">9.97216606140137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88484287261963</t>
+    <t xml:space="preserve">9.88484382629395</t>
   </si>
   <si>
     <t xml:space="preserve">9.8673791885376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0944166183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0769510269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79752159118652</t>
+    <t xml:space="preserve">10.0944156646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0769519805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79752063751221</t>
   </si>
   <si>
     <t xml:space="preserve">9.9547004699707</t>
@@ -3473,31 +3473,31 @@
     <t xml:space="preserve">10.6358118057251</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7405986785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7580633163452</t>
+    <t xml:space="preserve">10.7405977249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7580623626709</t>
   </si>
   <si>
     <t xml:space="preserve">10.9152431488037</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0200290679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3518514633179</t>
+    <t xml:space="preserve">11.0200281143188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3518524169922</t>
   </si>
   <si>
     <t xml:space="preserve">11.0025644302368</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9676361083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.53102684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6183471679688</t>
+    <t xml:space="preserve">10.9676351547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5310258865356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6183481216431</t>
   </si>
   <si>
     <t xml:space="preserve">10.7056694030762</t>
@@ -3506,13 +3506,13 @@
     <t xml:space="preserve">10.6008834838867</t>
   </si>
   <si>
-    <t xml:space="preserve">10.565954208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4786319732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1817378997803</t>
+    <t xml:space="preserve">10.5659551620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4786329269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1817388534546</t>
   </si>
   <si>
     <t xml:space="preserve">10.216667175293</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">10.0245580673218</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84991359710693</t>
+    <t xml:space="preserve">9.84991455078125</t>
   </si>
   <si>
     <t xml:space="preserve">10.1118803024292</t>
@@ -3539,13 +3539,13 @@
     <t xml:space="preserve">11.9456405639648</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7011394500732</t>
+    <t xml:space="preserve">11.7011384963989</t>
   </si>
   <si>
     <t xml:space="preserve">12.1202850341797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3997144699097</t>
+    <t xml:space="preserve">12.399715423584</t>
   </si>
   <si>
     <t xml:space="preserve">11.9281768798828</t>
@@ -3560,22 +3560,22 @@
     <t xml:space="preserve">12.0329627990723</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4650440216064</t>
+    <t xml:space="preserve">13.4650430679321</t>
   </si>
   <si>
     <t xml:space="preserve">13.1681480407715</t>
   </si>
   <si>
-    <t xml:space="preserve">13.063362121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8712530136108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6442165374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9491128921509</t>
+    <t xml:space="preserve">13.0633630752563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8712539672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6442155838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9491119384766</t>
   </si>
   <si>
     <t xml:space="preserve">13.0746583938599</t>
@@ -3584,13 +3584,13 @@
     <t xml:space="preserve">12.9132423400879</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0387887954712</t>
+    <t xml:space="preserve">13.0387878417969</t>
   </si>
   <si>
     <t xml:space="preserve">13.0567235946655</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1284627914429</t>
+    <t xml:space="preserve">13.1284637451172</t>
   </si>
   <si>
     <t xml:space="preserve">13.2540082931519</t>
@@ -3605,7 +3605,7 @@
     <t xml:space="preserve">13.5947751998901</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4871644973755</t>
+    <t xml:space="preserve">13.4871635437012</t>
   </si>
   <si>
     <t xml:space="preserve">13.4512939453125</t>
@@ -3620,7 +3620,7 @@
     <t xml:space="preserve">13.5051002502441</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2002029418945</t>
+    <t xml:space="preserve">13.2002038955688</t>
   </si>
   <si>
     <t xml:space="preserve">12.9849824905396</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">12.5366058349609</t>
   </si>
   <si>
-    <t xml:space="preserve">12.411060333252</t>
+    <t xml:space="preserve">12.4110612869263</t>
   </si>
   <si>
     <t xml:space="preserve">12.2496452331543</t>
@@ -3680,7 +3680,7 @@
     <t xml:space="preserve">12.285514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2675800323486</t>
+    <t xml:space="preserve">12.2675809860229</t>
   </si>
   <si>
     <t xml:space="preserve">12.6262817382812</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">12.5724763870239</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2137756347656</t>
+    <t xml:space="preserve">12.2137746810913</t>
   </si>
   <si>
     <t xml:space="preserve">12.5007352828979</t>
@@ -3704,10 +3704,10 @@
     <t xml:space="preserve">11.2990875244141</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5681123733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6398525238037</t>
+    <t xml:space="preserve">11.5681133270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.639853477478</t>
   </si>
   <si>
     <t xml:space="preserve">11.675724029541</t>
@@ -3719,22 +3719,22 @@
     <t xml:space="preserve">11.6577882766724</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4605016708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.37082862854</t>
+    <t xml:space="preserve">11.4605026245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3708276748657</t>
   </si>
   <si>
     <t xml:space="preserve">11.3528928756714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3349580764771</t>
+    <t xml:space="preserve">11.3349571228027</t>
   </si>
   <si>
     <t xml:space="preserve">11.2811527252197</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4963722229004</t>
+    <t xml:space="preserve">11.4963731765747</t>
   </si>
   <si>
     <t xml:space="preserve">11.5501775741577</t>
@@ -3749,16 +3749,16 @@
     <t xml:space="preserve">11.8012685775757</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7833337783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9088792800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.926815032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0164890289307</t>
+    <t xml:space="preserve">11.7833347320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.908878326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9268140792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.016489982605</t>
   </si>
   <si>
     <t xml:space="preserve">12.0882301330566</t>
@@ -3797,7 +3797,7 @@
     <t xml:space="preserve">10.5278797149658</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7610349655151</t>
+    <t xml:space="preserve">10.7610359191895</t>
   </si>
   <si>
     <t xml:space="preserve">10.5816850662231</t>
@@ -3812,7 +3812,7 @@
     <t xml:space="preserve">10.2947235107422</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3664646148682</t>
+    <t xml:space="preserve">10.3664636611938</t>
   </si>
   <si>
     <t xml:space="preserve">10.2229833602905</t>
@@ -3833,19 +3833,19 @@
     <t xml:space="preserve">9.86428260803223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68493270874023</t>
+    <t xml:space="preserve">9.68493175506592</t>
   </si>
   <si>
     <t xml:space="preserve">9.75667190551758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77460670471191</t>
+    <t xml:space="preserve">9.77460765838623</t>
   </si>
   <si>
     <t xml:space="preserve">9.70286750793457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79254150390625</t>
+    <t xml:space="preserve">9.79254245758057</t>
   </si>
   <si>
     <t xml:space="preserve">9.66699695587158</t>
@@ -3860,7 +3860,7 @@
     <t xml:space="preserve">10.0436325073242</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1871137619019</t>
+    <t xml:space="preserve">10.1871128082275</t>
   </si>
   <si>
     <t xml:space="preserve">10.5099449157715</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">10.7431001663208</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8148412704468</t>
+    <t xml:space="preserve">10.8148403167725</t>
   </si>
   <si>
     <t xml:space="preserve">10.4740753173828</t>
@@ -3881,7 +3881,7 @@
     <t xml:space="preserve">9.9001522064209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95395755767822</t>
+    <t xml:space="preserve">9.95395851135254</t>
   </si>
   <si>
     <t xml:space="preserve">10.0795030593872</t>
@@ -3893,7 +3893,7 @@
     <t xml:space="preserve">9.98982810974121</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2588539123535</t>
+    <t xml:space="preserve">10.2588529586792</t>
   </si>
   <si>
     <t xml:space="preserve">10.3126592636108</t>
@@ -3905,7 +3905,7 @@
     <t xml:space="preserve">10.4561395645142</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3305950164795</t>
+    <t xml:space="preserve">10.3305940628052</t>
   </si>
   <si>
     <t xml:space="preserve">10.2050485610962</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">9.91808795928955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88221740722656</t>
+    <t xml:space="preserve">9.88221836090088</t>
   </si>
   <si>
     <t xml:space="preserve">10.0974388122559</t>
@@ -3941,31 +3941,31 @@
     <t xml:space="preserve">9.3262300491333</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4517765045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5996189117432</t>
+    <t xml:space="preserve">9.45177555084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5996198654175</t>
   </si>
   <si>
     <t xml:space="preserve">9.93602275848389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4920101165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5637502670288</t>
+    <t xml:space="preserve">10.4920091629028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5637493133545</t>
   </si>
   <si>
     <t xml:space="preserve">10.4382047653198</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6713590621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9045152664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8327751159668</t>
+    <t xml:space="preserve">10.6713600158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9045162200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8327760696411</t>
   </si>
   <si>
     <t xml:space="preserve">10.7251653671265</t>
@@ -3980,7 +3980,7 @@
     <t xml:space="preserve">10.9224510192871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6892948150635</t>
+    <t xml:space="preserve">10.6892957687378</t>
   </si>
   <si>
     <t xml:space="preserve">11.2094125747681</t>
@@ -10444,7 +10444,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G209" t="s">
-        <v>87</v>
+        <v>166</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -10470,7 +10470,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G210" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -10496,7 +10496,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G211" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -10522,7 +10522,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G212" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -10548,7 +10548,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G213" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -10574,7 +10574,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G214" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -10600,7 +10600,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G215" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -10626,7 +10626,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G216" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -10652,7 +10652,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G217" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -10704,7 +10704,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G219" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -10808,7 +10808,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G223" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -10834,7 +10834,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G224" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -10860,7 +10860,7 @@
         <v>16</v>
       </c>
       <c r="G225" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -10886,7 +10886,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G226" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -10912,7 +10912,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G227" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -10938,7 +10938,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G228" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -10964,7 +10964,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G229" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -10990,7 +10990,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G230" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -11016,7 +11016,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G231" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -11042,7 +11042,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G232" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -11068,7 +11068,7 @@
         <v>16.5699996948242</v>
       </c>
       <c r="G233" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -11094,7 +11094,7 @@
         <v>16.3899993896484</v>
       </c>
       <c r="G234" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -11120,7 +11120,7 @@
         <v>16.25</v>
       </c>
       <c r="G235" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -11146,7 +11146,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G236" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -11172,7 +11172,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G237" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -11198,7 +11198,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G238" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -11250,7 +11250,7 @@
         <v>17</v>
       </c>
       <c r="G240" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -11302,7 +11302,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G242" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -11354,7 +11354,7 @@
         <v>17</v>
       </c>
       <c r="G244" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -11380,7 +11380,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G245" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -11406,7 +11406,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G246" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -11458,7 +11458,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G248" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -11510,7 +11510,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G250" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -11536,7 +11536,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G251" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -11588,7 +11588,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G253" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -11614,7 +11614,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G254" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -11640,7 +11640,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G255" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -11692,7 +11692,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G257" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -11744,7 +11744,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G259" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -11796,7 +11796,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G261" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -11822,7 +11822,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G262" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -11900,7 +11900,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G265" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -11978,7 +11978,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G268" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -12030,7 +12030,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G270" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -12056,7 +12056,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G271" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -12108,7 +12108,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G273" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -12134,7 +12134,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G274" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -12186,7 +12186,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G276" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -12212,7 +12212,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G277" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -12238,7 +12238,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G278" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -12264,7 +12264,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G279" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -12290,7 +12290,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G280" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -12316,7 +12316,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G281" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -12342,7 +12342,7 @@
         <v>18.4699993133545</v>
       </c>